--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R834f8b96e8664207"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Rf5fef861a52348ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="Rb8d5dc6877cc48d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R18837502142343cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R9db952d3f83a468a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R7240b13cab8948d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R8422424ed3254cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R5c91082a1e444c94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R2078ee11a4bc45e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R257a5564b1894f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R6a0c7ecdfe164073"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R66855269f32c48a3"/>
   </x:sheets>
   <x:definedNames>
+    <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
     <x:definedName name="CashFlowSelectedScenario">'Assumptions'!$B$12</x:definedName>
     <x:definedName name="CashFlowScenarioList">'Assumptions'!$B$15:$B$17</x:definedName>
   </x:definedNames>
@@ -27,7 +28,7 @@
     <x:numFmt numFmtId="201" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0);-"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -76,11 +77,6 @@
     </x:font>
     <x:font>
       <x:sz val="11"/>
-      <x:color rgb="FF7A5AB5"/>
-      <x:name val="Aptos"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
       <x:color rgb="FF4F485E"/>
       <x:name val="Aptos"/>
     </x:font>
@@ -103,7 +99,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -142,6 +138,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7A5AB5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDED9E8"/>
       </x:patternFill>
     </x:fill>
@@ -162,7 +163,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -193,31 +194,32 @@
     <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -479,13 +481,13 @@
       <x:c r="B6" t="str">
         <x:v>1.0 scaffold</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="str">
+      <x:c r="D6" s="23" t="str">
         <x:v>Quick links</x:v>
       </x:c>
-      <x:c r="E6" s="14"/>
-      <x:c r="F6" s="14"/>
-      <x:c r="G6" s="14"/>
-      <x:c r="H6" s="14"/>
+      <x:c r="E6" s="23"/>
+      <x:c r="F6" s="23"/>
+      <x:c r="G6" s="23"/>
+      <x:c r="H6" s="23"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -494,7 +496,7 @@
       <x:c r="B7" s="11" t="n">
         <x:v>46260</x:v>
       </x:c>
-      <x:c r="D7" s="22" t="e">
+      <x:c r="D7" s="12" t="e">
         <x:f>HYPERLINK("#'Dashboard'!A1","Dashboard")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=#'Dashboard'!A1, friendlyName=Dashboard</x:v>
       </x:c>
@@ -506,7 +508,7 @@
       <x:c r="B8" t="str">
         <x:v>AUD</x:v>
       </x:c>
-      <x:c r="D8" s="22" t="e">
+      <x:c r="D8" s="12" t="e">
         <x:f>HYPERLINK("#'Assumptions'!A1","Assumptions")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=#'Assumptions'!A1, friendlyName=Assumptions</x:v>
       </x:c>
@@ -518,7 +520,7 @@
       <x:c r="B9" t="str">
         <x:v>Whole dollars</x:v>
       </x:c>
-      <x:c r="D9" s="22" t="e">
+      <x:c r="D9" s="12" t="e">
         <x:f>HYPERLINK("#'13-Week Forecast'!A1","13-Week Forecast")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=#'13-Week Forecast'!A1, friendlyName=13-Week Forecast</x:v>
       </x:c>
@@ -531,13 +533,13 @@
         <x:f>'Assumptions'!$B$12</x:f>
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="D10" s="22" t="e">
+      <x:c r="D10" s="12" t="e">
         <x:f>HYPERLINK("#'Weekly Review'!A1","Weekly Review")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=#'Weekly Review'!A1, friendlyName=Weekly Review</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="D11" s="22" t="e">
+      <x:c r="D11" s="12" t="e">
         <x:f>HYPERLINK("#'Checks &amp; Sources'!A1","Checks &amp; Sources")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=#'Checks &amp; Sources'!A1, friendlyName=Checks &amp; Sources</x:v>
       </x:c>
@@ -647,26 +649,26 @@
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="26" t="str">
+      <x:c r="A27" s="27" t="str">
         <x:v>Scope limit: this workbook supports short-term cash planning. It is illustrative only and is not tax, payroll, legal or financial advice. Confirm statutory dates and classifications with your adviser.</x:v>
       </x:c>
-      <x:c r="B27" s="26"/>
-      <x:c r="C27" s="26"/>
-      <x:c r="D27" s="26"/>
-      <x:c r="E27" s="26"/>
-      <x:c r="F27" s="26"/>
-      <x:c r="G27" s="26"/>
-      <x:c r="H27" s="26"/>
+      <x:c r="B27" s="27"/>
+      <x:c r="C27" s="27"/>
+      <x:c r="D27" s="27"/>
+      <x:c r="E27" s="27"/>
+      <x:c r="F27" s="27"/>
+      <x:c r="G27" s="27"/>
+      <x:c r="H27" s="27"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="26"/>
-      <x:c r="B28" s="26"/>
-      <x:c r="C28" s="26"/>
-      <x:c r="D28" s="26"/>
-      <x:c r="E28" s="26"/>
-      <x:c r="F28" s="26"/>
-      <x:c r="G28" s="26"/>
-      <x:c r="H28" s="26"/>
+      <x:c r="A28" s="27"/>
+      <x:c r="B28" s="27"/>
+      <x:c r="C28" s="27"/>
+      <x:c r="D28" s="27"/>
+      <x:c r="E28" s="27"/>
+      <x:c r="F28" s="27"/>
+      <x:c r="G28" s="27"/>
+      <x:c r="H28" s="27"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -739,41 +741,41 @@
       <x:c r="O2" s="8"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="24" t="str">
+      <x:c r="A4" s="25" t="str">
         <x:v>No cash-flow inputs belong on this sheet. Update Assumptions and the 13-Week Forecast instead.</x:v>
       </x:c>
-      <x:c r="B4" s="24"/>
-      <x:c r="C4" s="24"/>
-      <x:c r="D4" s="24"/>
-      <x:c r="E4" s="24"/>
-      <x:c r="F4" s="24"/>
-      <x:c r="G4" s="24"/>
-      <x:c r="H4" s="24"/>
-      <x:c r="I4" s="24"/>
-      <x:c r="J4" s="24"/>
-      <x:c r="K4" s="24"/>
-      <x:c r="L4" s="24"/>
-      <x:c r="M4" s="24"/>
-      <x:c r="N4" s="24"/>
-      <x:c r="O4" s="24"/>
+      <x:c r="B4" s="25"/>
+      <x:c r="C4" s="25"/>
+      <x:c r="D4" s="25"/>
+      <x:c r="E4" s="25"/>
+      <x:c r="F4" s="25"/>
+      <x:c r="G4" s="25"/>
+      <x:c r="H4" s="25"/>
+      <x:c r="I4" s="25"/>
+      <x:c r="J4" s="25"/>
+      <x:c r="K4" s="25"/>
+      <x:c r="L4" s="25"/>
+      <x:c r="M4" s="25"/>
+      <x:c r="N4" s="25"/>
+      <x:c r="O4" s="25"/>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="27" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="28" t="str">
         <x:v>Week 13 closing cash</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="28" t="str">
         <x:v>Lowest closing cash</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="28" t="str">
         <x:v>Minimum buffer</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="28" t="str">
         <x:v>Minimum headroom</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="28" t="str">
         <x:v>Weeks below buffer</x:v>
       </x:c>
     </x:row>
@@ -865,7 +867,7 @@
       <x:c r="A5" t="str">
         <x:v>Business name</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="str">
+      <x:c r="B5" s="29" t="str">
         <x:v>Illustrative Australian business</x:v>
       </x:c>
     </x:row>
@@ -873,7 +875,7 @@
       <x:c r="A6" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="B6" s="28" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>AUD</x:v>
       </x:c>
     </x:row>
@@ -881,7 +883,7 @@
       <x:c r="A7" t="str">
         <x:v>Units</x:v>
       </x:c>
-      <x:c r="B7" s="28" t="str">
+      <x:c r="B7" s="29" t="str">
         <x:v>Whole dollars</x:v>
       </x:c>
     </x:row>
@@ -889,7 +891,7 @@
       <x:c r="A8" t="str">
         <x:v>Forecast start date</x:v>
       </x:c>
-      <x:c r="B8" s="29" t="n">
+      <x:c r="B8" s="30" t="n">
         <x:v>46265</x:v>
       </x:c>
     </x:row>
@@ -897,7 +899,7 @@
       <x:c r="A9" t="str">
         <x:v>As-at date</x:v>
       </x:c>
-      <x:c r="B9" s="29" t="n">
+      <x:c r="B9" s="30" t="n">
         <x:v>46271</x:v>
       </x:c>
     </x:row>
@@ -905,7 +907,7 @@
       <x:c r="A10" t="str">
         <x:v>Opening cash</x:v>
       </x:c>
-      <x:c r="B10" s="30" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>400000</x:v>
       </x:c>
     </x:row>
@@ -913,7 +915,7 @@
       <x:c r="A11" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B11" s="30" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>100000</x:v>
       </x:c>
     </x:row>
@@ -921,7 +923,7 @@
       <x:c r="A12" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B12" s="28" t="str">
+      <x:c r="B12" s="29" t="str">
         <x:v>Base</x:v>
       </x:c>
     </x:row>
@@ -946,10 +948,10 @@
       <x:c r="B15" s="16" t="str">
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="C15" s="31" t="n">
+      <x:c r="C15" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="D15" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="16" t="str">
@@ -960,10 +962,10 @@
       <x:c r="B16" s="16" t="str">
         <x:v>Upside</x:v>
       </x:c>
-      <x:c r="C16" s="31" t="n">
+      <x:c r="C16" s="32" t="n">
         <x:v>1.08</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="D16" s="32" t="n">
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="E16" s="16" t="str">
@@ -974,10 +976,10 @@
       <x:c r="B17" s="16" t="str">
         <x:v>Downside</x:v>
       </x:c>
-      <x:c r="C17" s="31" t="n">
+      <x:c r="C17" s="32" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="D17" s="32" t="n">
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
@@ -995,30 +997,30 @@
       <x:c r="F20" s="14"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="26" t="str">
+      <x:c r="A21" s="27" t="str">
         <x:v>Use a Monday forecast start. Keep the as-at date inside the 13-week horizon. Replace illustrative inputs before using this workbook for a decision. Statutory cash dates depend on your reporting cycle, agent concessions and entity circumstances.</x:v>
       </x:c>
-      <x:c r="B21" s="26"/>
-      <x:c r="C21" s="26"/>
-      <x:c r="D21" s="26"/>
-      <x:c r="E21" s="26"/>
-      <x:c r="F21" s="26"/>
+      <x:c r="B21" s="27"/>
+      <x:c r="C21" s="27"/>
+      <x:c r="D21" s="27"/>
+      <x:c r="E21" s="27"/>
+      <x:c r="F21" s="27"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="26"/>
-      <x:c r="B22" s="26"/>
-      <x:c r="C22" s="26"/>
-      <x:c r="D22" s="26"/>
-      <x:c r="E22" s="26"/>
-      <x:c r="F22" s="26"/>
+      <x:c r="A22" s="27"/>
+      <x:c r="B22" s="27"/>
+      <x:c r="C22" s="27"/>
+      <x:c r="D22" s="27"/>
+      <x:c r="E22" s="27"/>
+      <x:c r="F22" s="27"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="26"/>
-      <x:c r="B23" s="26"/>
-      <x:c r="C23" s="26"/>
-      <x:c r="D23" s="26"/>
-      <x:c r="E23" s="26"/>
-      <x:c r="F23" s="26"/>
+      <x:c r="A23" s="27"/>
+      <x:c r="B23" s="27"/>
+      <x:c r="C23" s="27"/>
+      <x:c r="D23" s="27"/>
+      <x:c r="E23" s="27"/>
+      <x:c r="F23" s="27"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1099,43 +1101,43 @@
       <x:c r="A5" t="str">
         <x:v>Week commencing</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="n">
+      <x:c r="C5" s="34" t="n">
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="D5" s="33" t="n">
+      <x:c r="D5" s="34" t="n">
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="34" t="n">
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="F5" s="33" t="n">
+      <x:c r="F5" s="34" t="n">
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="G5" s="33" t="n">
+      <x:c r="G5" s="34" t="n">
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="34" t="n">
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="I5" s="33" t="n">
+      <x:c r="I5" s="34" t="n">
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="J5" s="33" t="n">
+      <x:c r="J5" s="34" t="n">
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="34" t="n">
         <x:v>46328</x:v>
       </x:c>
-      <x:c r="L5" s="33" t="n">
+      <x:c r="L5" s="34" t="n">
         <x:v>46335</x:v>
       </x:c>
-      <x:c r="M5" s="33" t="n">
+      <x:c r="M5" s="34" t="n">
         <x:v>46342</x:v>
       </x:c>
-      <x:c r="N5" s="33" t="n">
+      <x:c r="N5" s="34" t="n">
         <x:v>46349</x:v>
       </x:c>
       <x:c r="O5" t="str">
@@ -1146,43 +1148,43 @@
       <x:c r="A6" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
+      <x:c r="B6" s="34" t="n">
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C6" s="33" t="n">
+      <x:c r="C6" s="34" t="n">
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="D6" s="33" t="n">
+      <x:c r="D6" s="34" t="n">
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="E6" s="33" t="n">
+      <x:c r="E6" s="34" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="F6" s="33" t="n">
+      <x:c r="F6" s="34" t="n">
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="G6" s="33" t="n">
+      <x:c r="G6" s="34" t="n">
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="H6" s="33" t="n">
+      <x:c r="H6" s="34" t="n">
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="I6" s="33" t="n">
+      <x:c r="I6" s="34" t="n">
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="J6" s="33" t="n">
+      <x:c r="J6" s="34" t="n">
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="K6" s="33" t="n">
+      <x:c r="K6" s="34" t="n">
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="L6" s="33" t="n">
+      <x:c r="L6" s="34" t="n">
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="M6" s="33" t="n">
+      <x:c r="M6" s="34" t="n">
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="N6" s="33" t="n">
+      <x:c r="N6" s="34" t="n">
         <x:v>46355</x:v>
       </x:c>
       <x:c r="O6" t="str">
@@ -1193,43 +1195,43 @@
       <x:c r="A7" t="str">
         <x:v>Actual / Forecast</x:v>
       </x:c>
-      <x:c r="B7" s="34" t="str">
+      <x:c r="B7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="C7" s="34" t="str">
+      <x:c r="C7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="D7" s="34" t="str">
+      <x:c r="D7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="E7" s="34" t="str">
+      <x:c r="E7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="F7" s="34" t="str">
+      <x:c r="F7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="G7" s="34" t="str">
+      <x:c r="G7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="H7" s="34" t="str">
+      <x:c r="H7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="I7" s="34" t="str">
+      <x:c r="I7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="J7" s="34" t="str">
+      <x:c r="J7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="K7" s="34" t="str">
+      <x:c r="K7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="L7" s="34" t="str">
+      <x:c r="L7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="M7" s="34" t="str">
+      <x:c r="M7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="N7" s="34" t="str">
+      <x:c r="N7" s="35" t="str">
         <x:v>Forecast</x:v>
       </x:c>
       <x:c r="O7" t="str"/>
@@ -1257,774 +1259,774 @@
       <x:c r="A10" t="str">
         <x:v>Customer receipts</x:v>
       </x:c>
-      <x:c r="B10" s="37"/>
-      <x:c r="C10" s="37"/>
-      <x:c r="D10" s="37"/>
-      <x:c r="E10" s="37"/>
-      <x:c r="F10" s="37"/>
-      <x:c r="G10" s="37"/>
-      <x:c r="H10" s="37"/>
-      <x:c r="I10" s="37"/>
-      <x:c r="J10" s="37"/>
-      <x:c r="K10" s="37"/>
-      <x:c r="L10" s="37"/>
-      <x:c r="M10" s="37"/>
-      <x:c r="N10" s="37"/>
-      <x:c r="O10" s="37"/>
+      <x:c r="B10" s="38"/>
+      <x:c r="C10" s="38"/>
+      <x:c r="D10" s="38"/>
+      <x:c r="E10" s="38"/>
+      <x:c r="F10" s="38"/>
+      <x:c r="G10" s="38"/>
+      <x:c r="H10" s="38"/>
+      <x:c r="I10" s="38"/>
+      <x:c r="J10" s="38"/>
+      <x:c r="K10" s="38"/>
+      <x:c r="L10" s="38"/>
+      <x:c r="M10" s="38"/>
+      <x:c r="N10" s="38"/>
+      <x:c r="O10" s="38"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
         <x:v>Overdue receipts</x:v>
       </x:c>
-      <x:c r="B11" s="37"/>
-      <x:c r="C11" s="37"/>
-      <x:c r="D11" s="37"/>
-      <x:c r="E11" s="37"/>
-      <x:c r="F11" s="37"/>
-      <x:c r="G11" s="37"/>
-      <x:c r="H11" s="37"/>
-      <x:c r="I11" s="37"/>
-      <x:c r="J11" s="37"/>
-      <x:c r="K11" s="37"/>
-      <x:c r="L11" s="37"/>
-      <x:c r="M11" s="37"/>
-      <x:c r="N11" s="37"/>
-      <x:c r="O11" s="37"/>
+      <x:c r="B11" s="38"/>
+      <x:c r="C11" s="38"/>
+      <x:c r="D11" s="38"/>
+      <x:c r="E11" s="38"/>
+      <x:c r="F11" s="38"/>
+      <x:c r="G11" s="38"/>
+      <x:c r="H11" s="38"/>
+      <x:c r="I11" s="38"/>
+      <x:c r="J11" s="38"/>
+      <x:c r="K11" s="38"/>
+      <x:c r="L11" s="38"/>
+      <x:c r="M11" s="38"/>
+      <x:c r="N11" s="38"/>
+      <x:c r="O11" s="38"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
         <x:v>Cash / EFTPOS sales</x:v>
       </x:c>
-      <x:c r="B12" s="37"/>
-      <x:c r="C12" s="37"/>
-      <x:c r="D12" s="37"/>
-      <x:c r="E12" s="37"/>
-      <x:c r="F12" s="37"/>
-      <x:c r="G12" s="37"/>
-      <x:c r="H12" s="37"/>
-      <x:c r="I12" s="37"/>
-      <x:c r="J12" s="37"/>
-      <x:c r="K12" s="37"/>
-      <x:c r="L12" s="37"/>
-      <x:c r="M12" s="37"/>
-      <x:c r="N12" s="37"/>
-      <x:c r="O12" s="37"/>
+      <x:c r="B12" s="38"/>
+      <x:c r="C12" s="38"/>
+      <x:c r="D12" s="38"/>
+      <x:c r="E12" s="38"/>
+      <x:c r="F12" s="38"/>
+      <x:c r="G12" s="38"/>
+      <x:c r="H12" s="38"/>
+      <x:c r="I12" s="38"/>
+      <x:c r="J12" s="38"/>
+      <x:c r="K12" s="38"/>
+      <x:c r="L12" s="38"/>
+      <x:c r="M12" s="38"/>
+      <x:c r="N12" s="38"/>
+      <x:c r="O12" s="38"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
         <x:v>GST refunds / credits</x:v>
       </x:c>
-      <x:c r="B13" s="37"/>
-      <x:c r="C13" s="37"/>
-      <x:c r="D13" s="37"/>
-      <x:c r="E13" s="37"/>
-      <x:c r="F13" s="37"/>
-      <x:c r="G13" s="37"/>
-      <x:c r="H13" s="37"/>
-      <x:c r="I13" s="37"/>
-      <x:c r="J13" s="37"/>
-      <x:c r="K13" s="37"/>
-      <x:c r="L13" s="37"/>
-      <x:c r="M13" s="37"/>
-      <x:c r="N13" s="37"/>
-      <x:c r="O13" s="37"/>
+      <x:c r="B13" s="38"/>
+      <x:c r="C13" s="38"/>
+      <x:c r="D13" s="38"/>
+      <x:c r="E13" s="38"/>
+      <x:c r="F13" s="38"/>
+      <x:c r="G13" s="38"/>
+      <x:c r="H13" s="38"/>
+      <x:c r="I13" s="38"/>
+      <x:c r="J13" s="38"/>
+      <x:c r="K13" s="38"/>
+      <x:c r="L13" s="38"/>
+      <x:c r="M13" s="38"/>
+      <x:c r="N13" s="38"/>
+      <x:c r="O13" s="38"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B14" s="37"/>
-      <x:c r="C14" s="37"/>
-      <x:c r="D14" s="37"/>
-      <x:c r="E14" s="37"/>
-      <x:c r="F14" s="37"/>
-      <x:c r="G14" s="37"/>
-      <x:c r="H14" s="37"/>
-      <x:c r="I14" s="37"/>
-      <x:c r="J14" s="37"/>
-      <x:c r="K14" s="37"/>
-      <x:c r="L14" s="37"/>
-      <x:c r="M14" s="37"/>
-      <x:c r="N14" s="37"/>
-      <x:c r="O14" s="37"/>
+      <x:c r="B14" s="38"/>
+      <x:c r="C14" s="38"/>
+      <x:c r="D14" s="38"/>
+      <x:c r="E14" s="38"/>
+      <x:c r="F14" s="38"/>
+      <x:c r="G14" s="38"/>
+      <x:c r="H14" s="38"/>
+      <x:c r="I14" s="38"/>
+      <x:c r="J14" s="38"/>
+      <x:c r="K14" s="38"/>
+      <x:c r="L14" s="38"/>
+      <x:c r="M14" s="38"/>
+      <x:c r="N14" s="38"/>
+      <x:c r="O14" s="38"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
         <x:v>Asset sale proceeds</x:v>
       </x:c>
-      <x:c r="B15" s="37"/>
-      <x:c r="C15" s="37"/>
-      <x:c r="D15" s="37"/>
-      <x:c r="E15" s="37"/>
-      <x:c r="F15" s="37"/>
-      <x:c r="G15" s="37"/>
-      <x:c r="H15" s="37"/>
-      <x:c r="I15" s="37"/>
-      <x:c r="J15" s="37"/>
-      <x:c r="K15" s="37"/>
-      <x:c r="L15" s="37"/>
-      <x:c r="M15" s="37"/>
-      <x:c r="N15" s="37"/>
-      <x:c r="O15" s="37"/>
+      <x:c r="B15" s="38"/>
+      <x:c r="C15" s="38"/>
+      <x:c r="D15" s="38"/>
+      <x:c r="E15" s="38"/>
+      <x:c r="F15" s="38"/>
+      <x:c r="G15" s="38"/>
+      <x:c r="H15" s="38"/>
+      <x:c r="I15" s="38"/>
+      <x:c r="J15" s="38"/>
+      <x:c r="K15" s="38"/>
+      <x:c r="L15" s="38"/>
+      <x:c r="M15" s="38"/>
+      <x:c r="N15" s="38"/>
+      <x:c r="O15" s="38"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
         <x:v>Equity / owner funding</x:v>
       </x:c>
-      <x:c r="B16" s="37"/>
-      <x:c r="C16" s="37"/>
-      <x:c r="D16" s="37"/>
-      <x:c r="E16" s="37"/>
-      <x:c r="F16" s="37"/>
-      <x:c r="G16" s="37"/>
-      <x:c r="H16" s="37"/>
-      <x:c r="I16" s="37"/>
-      <x:c r="J16" s="37"/>
-      <x:c r="K16" s="37"/>
-      <x:c r="L16" s="37"/>
-      <x:c r="M16" s="37"/>
-      <x:c r="N16" s="37"/>
-      <x:c r="O16" s="37"/>
+      <x:c r="B16" s="38"/>
+      <x:c r="C16" s="38"/>
+      <x:c r="D16" s="38"/>
+      <x:c r="E16" s="38"/>
+      <x:c r="F16" s="38"/>
+      <x:c r="G16" s="38"/>
+      <x:c r="H16" s="38"/>
+      <x:c r="I16" s="38"/>
+      <x:c r="J16" s="38"/>
+      <x:c r="K16" s="38"/>
+      <x:c r="L16" s="38"/>
+      <x:c r="M16" s="38"/>
+      <x:c r="N16" s="38"/>
+      <x:c r="O16" s="38"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
         <x:v>Loan proceeds</x:v>
       </x:c>
-      <x:c r="B17" s="37"/>
-      <x:c r="C17" s="37"/>
-      <x:c r="D17" s="37"/>
-      <x:c r="E17" s="37"/>
-      <x:c r="F17" s="37"/>
-      <x:c r="G17" s="37"/>
-      <x:c r="H17" s="37"/>
-      <x:c r="I17" s="37"/>
-      <x:c r="J17" s="37"/>
-      <x:c r="K17" s="37"/>
-      <x:c r="L17" s="37"/>
-      <x:c r="M17" s="37"/>
-      <x:c r="N17" s="37"/>
-      <x:c r="O17" s="37"/>
+      <x:c r="B17" s="38"/>
+      <x:c r="C17" s="38"/>
+      <x:c r="D17" s="38"/>
+      <x:c r="E17" s="38"/>
+      <x:c r="F17" s="38"/>
+      <x:c r="G17" s="38"/>
+      <x:c r="H17" s="38"/>
+      <x:c r="I17" s="38"/>
+      <x:c r="J17" s="38"/>
+      <x:c r="K17" s="38"/>
+      <x:c r="L17" s="38"/>
+      <x:c r="M17" s="38"/>
+      <x:c r="N17" s="38"/>
+      <x:c r="O17" s="38"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
         <x:v>Scenario receipt adjustment</x:v>
       </x:c>
-      <x:c r="B18" s="37"/>
-      <x:c r="C18" s="37"/>
-      <x:c r="D18" s="37"/>
-      <x:c r="E18" s="37"/>
-      <x:c r="F18" s="37"/>
-      <x:c r="G18" s="37"/>
-      <x:c r="H18" s="37"/>
-      <x:c r="I18" s="37"/>
-      <x:c r="J18" s="37"/>
-      <x:c r="K18" s="37"/>
-      <x:c r="L18" s="37"/>
-      <x:c r="M18" s="37"/>
-      <x:c r="N18" s="37"/>
-      <x:c r="O18" s="37"/>
+      <x:c r="B18" s="38"/>
+      <x:c r="C18" s="38"/>
+      <x:c r="D18" s="38"/>
+      <x:c r="E18" s="38"/>
+      <x:c r="F18" s="38"/>
+      <x:c r="G18" s="38"/>
+      <x:c r="H18" s="38"/>
+      <x:c r="I18" s="38"/>
+      <x:c r="J18" s="38"/>
+      <x:c r="K18" s="38"/>
+      <x:c r="L18" s="38"/>
+      <x:c r="M18" s="38"/>
+      <x:c r="N18" s="38"/>
+      <x:c r="O18" s="38"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="36" t="str">
+      <x:c r="A19" s="37" t="str">
         <x:v>Total cash receipts</x:v>
       </x:c>
-      <x:c r="B19" s="38"/>
-      <x:c r="C19" s="38"/>
-      <x:c r="D19" s="38"/>
-      <x:c r="E19" s="38"/>
-      <x:c r="F19" s="38"/>
-      <x:c r="G19" s="38"/>
-      <x:c r="H19" s="38"/>
-      <x:c r="I19" s="38"/>
-      <x:c r="J19" s="38"/>
-      <x:c r="K19" s="38"/>
-      <x:c r="L19" s="38"/>
-      <x:c r="M19" s="38"/>
-      <x:c r="N19" s="38"/>
-      <x:c r="O19" s="38"/>
+      <x:c r="B19" s="39"/>
+      <x:c r="C19" s="39"/>
+      <x:c r="D19" s="39"/>
+      <x:c r="E19" s="39"/>
+      <x:c r="F19" s="39"/>
+      <x:c r="G19" s="39"/>
+      <x:c r="H19" s="39"/>
+      <x:c r="I19" s="39"/>
+      <x:c r="J19" s="39"/>
+      <x:c r="K19" s="39"/>
+      <x:c r="L19" s="39"/>
+      <x:c r="M19" s="39"/>
+      <x:c r="N19" s="39"/>
+      <x:c r="O19" s="39"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="37"/>
-      <x:c r="C20" s="37"/>
-      <x:c r="D20" s="37"/>
-      <x:c r="E20" s="37"/>
-      <x:c r="F20" s="37"/>
-      <x:c r="G20" s="37"/>
-      <x:c r="H20" s="37"/>
-      <x:c r="I20" s="37"/>
-      <x:c r="J20" s="37"/>
-      <x:c r="K20" s="37"/>
-      <x:c r="L20" s="37"/>
-      <x:c r="M20" s="37"/>
-      <x:c r="N20" s="37"/>
-      <x:c r="O20" s="37"/>
+      <x:c r="B20" s="38"/>
+      <x:c r="C20" s="38"/>
+      <x:c r="D20" s="38"/>
+      <x:c r="E20" s="38"/>
+      <x:c r="F20" s="38"/>
+      <x:c r="G20" s="38"/>
+      <x:c r="H20" s="38"/>
+      <x:c r="I20" s="38"/>
+      <x:c r="J20" s="38"/>
+      <x:c r="K20" s="38"/>
+      <x:c r="L20" s="38"/>
+      <x:c r="M20" s="38"/>
+      <x:c r="N20" s="38"/>
+      <x:c r="O20" s="38"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
         <x:v>CASH PAYMENTS</x:v>
       </x:c>
-      <x:c r="B21" s="39"/>
-      <x:c r="C21" s="39"/>
-      <x:c r="D21" s="39"/>
-      <x:c r="E21" s="39"/>
-      <x:c r="F21" s="39"/>
-      <x:c r="G21" s="39"/>
-      <x:c r="H21" s="39"/>
-      <x:c r="I21" s="39"/>
-      <x:c r="J21" s="39"/>
-      <x:c r="K21" s="39"/>
-      <x:c r="L21" s="39"/>
-      <x:c r="M21" s="39"/>
-      <x:c r="N21" s="39"/>
-      <x:c r="O21" s="39"/>
+      <x:c r="B21" s="40"/>
+      <x:c r="C21" s="40"/>
+      <x:c r="D21" s="40"/>
+      <x:c r="E21" s="40"/>
+      <x:c r="F21" s="40"/>
+      <x:c r="G21" s="40"/>
+      <x:c r="H21" s="40"/>
+      <x:c r="I21" s="40"/>
+      <x:c r="J21" s="40"/>
+      <x:c r="K21" s="40"/>
+      <x:c r="L21" s="40"/>
+      <x:c r="M21" s="40"/>
+      <x:c r="N21" s="40"/>
+      <x:c r="O21" s="40"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
         <x:v>Suppliers and inventory</x:v>
       </x:c>
-      <x:c r="B22" s="37"/>
-      <x:c r="C22" s="37"/>
-      <x:c r="D22" s="37"/>
-      <x:c r="E22" s="37"/>
-      <x:c r="F22" s="37"/>
-      <x:c r="G22" s="37"/>
-      <x:c r="H22" s="37"/>
-      <x:c r="I22" s="37"/>
-      <x:c r="J22" s="37"/>
-      <x:c r="K22" s="37"/>
-      <x:c r="L22" s="37"/>
-      <x:c r="M22" s="37"/>
-      <x:c r="N22" s="37"/>
-      <x:c r="O22" s="37"/>
+      <x:c r="B22" s="38"/>
+      <x:c r="C22" s="38"/>
+      <x:c r="D22" s="38"/>
+      <x:c r="E22" s="38"/>
+      <x:c r="F22" s="38"/>
+      <x:c r="G22" s="38"/>
+      <x:c r="H22" s="38"/>
+      <x:c r="I22" s="38"/>
+      <x:c r="J22" s="38"/>
+      <x:c r="K22" s="38"/>
+      <x:c r="L22" s="38"/>
+      <x:c r="M22" s="38"/>
+      <x:c r="N22" s="38"/>
+      <x:c r="O22" s="38"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
         <x:v>Net wages</x:v>
       </x:c>
-      <x:c r="B23" s="37"/>
-      <x:c r="C23" s="37"/>
-      <x:c r="D23" s="37"/>
-      <x:c r="E23" s="37"/>
-      <x:c r="F23" s="37"/>
-      <x:c r="G23" s="37"/>
-      <x:c r="H23" s="37"/>
-      <x:c r="I23" s="37"/>
-      <x:c r="J23" s="37"/>
-      <x:c r="K23" s="37"/>
-      <x:c r="L23" s="37"/>
-      <x:c r="M23" s="37"/>
-      <x:c r="N23" s="37"/>
-      <x:c r="O23" s="37"/>
+      <x:c r="B23" s="38"/>
+      <x:c r="C23" s="38"/>
+      <x:c r="D23" s="38"/>
+      <x:c r="E23" s="38"/>
+      <x:c r="F23" s="38"/>
+      <x:c r="G23" s="38"/>
+      <x:c r="H23" s="38"/>
+      <x:c r="I23" s="38"/>
+      <x:c r="J23" s="38"/>
+      <x:c r="K23" s="38"/>
+      <x:c r="L23" s="38"/>
+      <x:c r="M23" s="38"/>
+      <x:c r="N23" s="38"/>
+      <x:c r="O23" s="38"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
         <x:v>PAYG withholding</x:v>
       </x:c>
-      <x:c r="B24" s="37"/>
-      <x:c r="C24" s="37"/>
-      <x:c r="D24" s="37"/>
-      <x:c r="E24" s="37"/>
-      <x:c r="F24" s="37"/>
-      <x:c r="G24" s="37"/>
-      <x:c r="H24" s="37"/>
-      <x:c r="I24" s="37"/>
-      <x:c r="J24" s="37"/>
-      <x:c r="K24" s="37"/>
-      <x:c r="L24" s="37"/>
-      <x:c r="M24" s="37"/>
-      <x:c r="N24" s="37"/>
-      <x:c r="O24" s="37"/>
+      <x:c r="B24" s="38"/>
+      <x:c r="C24" s="38"/>
+      <x:c r="D24" s="38"/>
+      <x:c r="E24" s="38"/>
+      <x:c r="F24" s="38"/>
+      <x:c r="G24" s="38"/>
+      <x:c r="H24" s="38"/>
+      <x:c r="I24" s="38"/>
+      <x:c r="J24" s="38"/>
+      <x:c r="K24" s="38"/>
+      <x:c r="L24" s="38"/>
+      <x:c r="M24" s="38"/>
+      <x:c r="N24" s="38"/>
+      <x:c r="O24" s="38"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
         <x:v>Superannuation</x:v>
       </x:c>
-      <x:c r="B25" s="37"/>
-      <x:c r="C25" s="37"/>
-      <x:c r="D25" s="37"/>
-      <x:c r="E25" s="37"/>
-      <x:c r="F25" s="37"/>
-      <x:c r="G25" s="37"/>
-      <x:c r="H25" s="37"/>
-      <x:c r="I25" s="37"/>
-      <x:c r="J25" s="37"/>
-      <x:c r="K25" s="37"/>
-      <x:c r="L25" s="37"/>
-      <x:c r="M25" s="37"/>
-      <x:c r="N25" s="37"/>
-      <x:c r="O25" s="37"/>
+      <x:c r="B25" s="38"/>
+      <x:c r="C25" s="38"/>
+      <x:c r="D25" s="38"/>
+      <x:c r="E25" s="38"/>
+      <x:c r="F25" s="38"/>
+      <x:c r="G25" s="38"/>
+      <x:c r="H25" s="38"/>
+      <x:c r="I25" s="38"/>
+      <x:c r="J25" s="38"/>
+      <x:c r="K25" s="38"/>
+      <x:c r="L25" s="38"/>
+      <x:c r="M25" s="38"/>
+      <x:c r="N25" s="38"/>
+      <x:c r="O25" s="38"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
         <x:v>Payroll tax / workers compensation</x:v>
       </x:c>
-      <x:c r="B26" s="37"/>
-      <x:c r="C26" s="37"/>
-      <x:c r="D26" s="37"/>
-      <x:c r="E26" s="37"/>
-      <x:c r="F26" s="37"/>
-      <x:c r="G26" s="37"/>
-      <x:c r="H26" s="37"/>
-      <x:c r="I26" s="37"/>
-      <x:c r="J26" s="37"/>
-      <x:c r="K26" s="37"/>
-      <x:c r="L26" s="37"/>
-      <x:c r="M26" s="37"/>
-      <x:c r="N26" s="37"/>
-      <x:c r="O26" s="37"/>
+      <x:c r="B26" s="38"/>
+      <x:c r="C26" s="38"/>
+      <x:c r="D26" s="38"/>
+      <x:c r="E26" s="38"/>
+      <x:c r="F26" s="38"/>
+      <x:c r="G26" s="38"/>
+      <x:c r="H26" s="38"/>
+      <x:c r="I26" s="38"/>
+      <x:c r="J26" s="38"/>
+      <x:c r="K26" s="38"/>
+      <x:c r="L26" s="38"/>
+      <x:c r="M26" s="38"/>
+      <x:c r="N26" s="38"/>
+      <x:c r="O26" s="38"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
         <x:v>Rent</x:v>
       </x:c>
-      <x:c r="B27" s="37"/>
-      <x:c r="C27" s="37"/>
-      <x:c r="D27" s="37"/>
-      <x:c r="E27" s="37"/>
-      <x:c r="F27" s="37"/>
-      <x:c r="G27" s="37"/>
-      <x:c r="H27" s="37"/>
-      <x:c r="I27" s="37"/>
-      <x:c r="J27" s="37"/>
-      <x:c r="K27" s="37"/>
-      <x:c r="L27" s="37"/>
-      <x:c r="M27" s="37"/>
-      <x:c r="N27" s="37"/>
-      <x:c r="O27" s="37"/>
+      <x:c r="B27" s="38"/>
+      <x:c r="C27" s="38"/>
+      <x:c r="D27" s="38"/>
+      <x:c r="E27" s="38"/>
+      <x:c r="F27" s="38"/>
+      <x:c r="G27" s="38"/>
+      <x:c r="H27" s="38"/>
+      <x:c r="I27" s="38"/>
+      <x:c r="J27" s="38"/>
+      <x:c r="K27" s="38"/>
+      <x:c r="L27" s="38"/>
+      <x:c r="M27" s="38"/>
+      <x:c r="N27" s="38"/>
+      <x:c r="O27" s="38"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
         <x:v>Utilities</x:v>
       </x:c>
-      <x:c r="B28" s="37"/>
-      <x:c r="C28" s="37"/>
-      <x:c r="D28" s="37"/>
-      <x:c r="E28" s="37"/>
-      <x:c r="F28" s="37"/>
-      <x:c r="G28" s="37"/>
-      <x:c r="H28" s="37"/>
-      <x:c r="I28" s="37"/>
-      <x:c r="J28" s="37"/>
-      <x:c r="K28" s="37"/>
-      <x:c r="L28" s="37"/>
-      <x:c r="M28" s="37"/>
-      <x:c r="N28" s="37"/>
-      <x:c r="O28" s="37"/>
+      <x:c r="B28" s="38"/>
+      <x:c r="C28" s="38"/>
+      <x:c r="D28" s="38"/>
+      <x:c r="E28" s="38"/>
+      <x:c r="F28" s="38"/>
+      <x:c r="G28" s="38"/>
+      <x:c r="H28" s="38"/>
+      <x:c r="I28" s="38"/>
+      <x:c r="J28" s="38"/>
+      <x:c r="K28" s="38"/>
+      <x:c r="L28" s="38"/>
+      <x:c r="M28" s="38"/>
+      <x:c r="N28" s="38"/>
+      <x:c r="O28" s="38"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
         <x:v>Insurance</x:v>
       </x:c>
-      <x:c r="B29" s="37"/>
-      <x:c r="C29" s="37"/>
-      <x:c r="D29" s="37"/>
-      <x:c r="E29" s="37"/>
-      <x:c r="F29" s="37"/>
-      <x:c r="G29" s="37"/>
-      <x:c r="H29" s="37"/>
-      <x:c r="I29" s="37"/>
-      <x:c r="J29" s="37"/>
-      <x:c r="K29" s="37"/>
-      <x:c r="L29" s="37"/>
-      <x:c r="M29" s="37"/>
-      <x:c r="N29" s="37"/>
-      <x:c r="O29" s="37"/>
+      <x:c r="B29" s="38"/>
+      <x:c r="C29" s="38"/>
+      <x:c r="D29" s="38"/>
+      <x:c r="E29" s="38"/>
+      <x:c r="F29" s="38"/>
+      <x:c r="G29" s="38"/>
+      <x:c r="H29" s="38"/>
+      <x:c r="I29" s="38"/>
+      <x:c r="J29" s="38"/>
+      <x:c r="K29" s="38"/>
+      <x:c r="L29" s="38"/>
+      <x:c r="M29" s="38"/>
+      <x:c r="N29" s="38"/>
+      <x:c r="O29" s="38"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
         <x:v>Software and subscriptions</x:v>
       </x:c>
-      <x:c r="B30" s="37"/>
-      <x:c r="C30" s="37"/>
-      <x:c r="D30" s="37"/>
-      <x:c r="E30" s="37"/>
-      <x:c r="F30" s="37"/>
-      <x:c r="G30" s="37"/>
-      <x:c r="H30" s="37"/>
-      <x:c r="I30" s="37"/>
-      <x:c r="J30" s="37"/>
-      <x:c r="K30" s="37"/>
-      <x:c r="L30" s="37"/>
-      <x:c r="M30" s="37"/>
-      <x:c r="N30" s="37"/>
-      <x:c r="O30" s="37"/>
+      <x:c r="B30" s="38"/>
+      <x:c r="C30" s="38"/>
+      <x:c r="D30" s="38"/>
+      <x:c r="E30" s="38"/>
+      <x:c r="F30" s="38"/>
+      <x:c r="G30" s="38"/>
+      <x:c r="H30" s="38"/>
+      <x:c r="I30" s="38"/>
+      <x:c r="J30" s="38"/>
+      <x:c r="K30" s="38"/>
+      <x:c r="L30" s="38"/>
+      <x:c r="M30" s="38"/>
+      <x:c r="N30" s="38"/>
+      <x:c r="O30" s="38"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
         <x:v>Marketing</x:v>
       </x:c>
-      <x:c r="B31" s="37"/>
-      <x:c r="C31" s="37"/>
-      <x:c r="D31" s="37"/>
-      <x:c r="E31" s="37"/>
-      <x:c r="F31" s="37"/>
-      <x:c r="G31" s="37"/>
-      <x:c r="H31" s="37"/>
-      <x:c r="I31" s="37"/>
-      <x:c r="J31" s="37"/>
-      <x:c r="K31" s="37"/>
-      <x:c r="L31" s="37"/>
-      <x:c r="M31" s="37"/>
-      <x:c r="N31" s="37"/>
-      <x:c r="O31" s="37"/>
+      <x:c r="B31" s="38"/>
+      <x:c r="C31" s="38"/>
+      <x:c r="D31" s="38"/>
+      <x:c r="E31" s="38"/>
+      <x:c r="F31" s="38"/>
+      <x:c r="G31" s="38"/>
+      <x:c r="H31" s="38"/>
+      <x:c r="I31" s="38"/>
+      <x:c r="J31" s="38"/>
+      <x:c r="K31" s="38"/>
+      <x:c r="L31" s="38"/>
+      <x:c r="M31" s="38"/>
+      <x:c r="N31" s="38"/>
+      <x:c r="O31" s="38"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
         <x:v>Professional services</x:v>
       </x:c>
-      <x:c r="B32" s="37"/>
-      <x:c r="C32" s="37"/>
-      <x:c r="D32" s="37"/>
-      <x:c r="E32" s="37"/>
-      <x:c r="F32" s="37"/>
-      <x:c r="G32" s="37"/>
-      <x:c r="H32" s="37"/>
-      <x:c r="I32" s="37"/>
-      <x:c r="J32" s="37"/>
-      <x:c r="K32" s="37"/>
-      <x:c r="L32" s="37"/>
-      <x:c r="M32" s="37"/>
-      <x:c r="N32" s="37"/>
-      <x:c r="O32" s="37"/>
+      <x:c r="B32" s="38"/>
+      <x:c r="C32" s="38"/>
+      <x:c r="D32" s="38"/>
+      <x:c r="E32" s="38"/>
+      <x:c r="F32" s="38"/>
+      <x:c r="G32" s="38"/>
+      <x:c r="H32" s="38"/>
+      <x:c r="I32" s="38"/>
+      <x:c r="J32" s="38"/>
+      <x:c r="K32" s="38"/>
+      <x:c r="L32" s="38"/>
+      <x:c r="M32" s="38"/>
+      <x:c r="N32" s="38"/>
+      <x:c r="O32" s="38"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
         <x:v>Freight, vehicles and travel</x:v>
       </x:c>
-      <x:c r="B33" s="37"/>
-      <x:c r="C33" s="37"/>
-      <x:c r="D33" s="37"/>
-      <x:c r="E33" s="37"/>
-      <x:c r="F33" s="37"/>
-      <x:c r="G33" s="37"/>
-      <x:c r="H33" s="37"/>
-      <x:c r="I33" s="37"/>
-      <x:c r="J33" s="37"/>
-      <x:c r="K33" s="37"/>
-      <x:c r="L33" s="37"/>
-      <x:c r="M33" s="37"/>
-      <x:c r="N33" s="37"/>
-      <x:c r="O33" s="37"/>
+      <x:c r="B33" s="38"/>
+      <x:c r="C33" s="38"/>
+      <x:c r="D33" s="38"/>
+      <x:c r="E33" s="38"/>
+      <x:c r="F33" s="38"/>
+      <x:c r="G33" s="38"/>
+      <x:c r="H33" s="38"/>
+      <x:c r="I33" s="38"/>
+      <x:c r="J33" s="38"/>
+      <x:c r="K33" s="38"/>
+      <x:c r="L33" s="38"/>
+      <x:c r="M33" s="38"/>
+      <x:c r="N33" s="38"/>
+      <x:c r="O33" s="38"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
         <x:v>GST / BAS payments</x:v>
       </x:c>
-      <x:c r="B34" s="37"/>
-      <x:c r="C34" s="37"/>
-      <x:c r="D34" s="37"/>
-      <x:c r="E34" s="37"/>
-      <x:c r="F34" s="37"/>
-      <x:c r="G34" s="37"/>
-      <x:c r="H34" s="37"/>
-      <x:c r="I34" s="37"/>
-      <x:c r="J34" s="37"/>
-      <x:c r="K34" s="37"/>
-      <x:c r="L34" s="37"/>
-      <x:c r="M34" s="37"/>
-      <x:c r="N34" s="37"/>
-      <x:c r="O34" s="37"/>
+      <x:c r="B34" s="38"/>
+      <x:c r="C34" s="38"/>
+      <x:c r="D34" s="38"/>
+      <x:c r="E34" s="38"/>
+      <x:c r="F34" s="38"/>
+      <x:c r="G34" s="38"/>
+      <x:c r="H34" s="38"/>
+      <x:c r="I34" s="38"/>
+      <x:c r="J34" s="38"/>
+      <x:c r="K34" s="38"/>
+      <x:c r="L34" s="38"/>
+      <x:c r="M34" s="38"/>
+      <x:c r="N34" s="38"/>
+      <x:c r="O34" s="38"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
         <x:v>PAYG income tax instalments</x:v>
       </x:c>
-      <x:c r="B35" s="37"/>
-      <x:c r="C35" s="37"/>
-      <x:c r="D35" s="37"/>
-      <x:c r="E35" s="37"/>
-      <x:c r="F35" s="37"/>
-      <x:c r="G35" s="37"/>
-      <x:c r="H35" s="37"/>
-      <x:c r="I35" s="37"/>
-      <x:c r="J35" s="37"/>
-      <x:c r="K35" s="37"/>
-      <x:c r="L35" s="37"/>
-      <x:c r="M35" s="37"/>
-      <x:c r="N35" s="37"/>
-      <x:c r="O35" s="37"/>
+      <x:c r="B35" s="38"/>
+      <x:c r="C35" s="38"/>
+      <x:c r="D35" s="38"/>
+      <x:c r="E35" s="38"/>
+      <x:c r="F35" s="38"/>
+      <x:c r="G35" s="38"/>
+      <x:c r="H35" s="38"/>
+      <x:c r="I35" s="38"/>
+      <x:c r="J35" s="38"/>
+      <x:c r="K35" s="38"/>
+      <x:c r="L35" s="38"/>
+      <x:c r="M35" s="38"/>
+      <x:c r="N35" s="38"/>
+      <x:c r="O35" s="38"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
         <x:v>FBT / other tax</x:v>
       </x:c>
-      <x:c r="B36" s="37"/>
-      <x:c r="C36" s="37"/>
-      <x:c r="D36" s="37"/>
-      <x:c r="E36" s="37"/>
-      <x:c r="F36" s="37"/>
-      <x:c r="G36" s="37"/>
-      <x:c r="H36" s="37"/>
-      <x:c r="I36" s="37"/>
-      <x:c r="J36" s="37"/>
-      <x:c r="K36" s="37"/>
-      <x:c r="L36" s="37"/>
-      <x:c r="M36" s="37"/>
-      <x:c r="N36" s="37"/>
-      <x:c r="O36" s="37"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
+      <x:c r="N36" s="38"/>
+      <x:c r="O36" s="38"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
         <x:v>Interest and bank fees</x:v>
       </x:c>
-      <x:c r="B37" s="37"/>
-      <x:c r="C37" s="37"/>
-      <x:c r="D37" s="37"/>
-      <x:c r="E37" s="37"/>
-      <x:c r="F37" s="37"/>
-      <x:c r="G37" s="37"/>
-      <x:c r="H37" s="37"/>
-      <x:c r="I37" s="37"/>
-      <x:c r="J37" s="37"/>
-      <x:c r="K37" s="37"/>
-      <x:c r="L37" s="37"/>
-      <x:c r="M37" s="37"/>
-      <x:c r="N37" s="37"/>
-      <x:c r="O37" s="37"/>
+      <x:c r="B37" s="38"/>
+      <x:c r="C37" s="38"/>
+      <x:c r="D37" s="38"/>
+      <x:c r="E37" s="38"/>
+      <x:c r="F37" s="38"/>
+      <x:c r="G37" s="38"/>
+      <x:c r="H37" s="38"/>
+      <x:c r="I37" s="38"/>
+      <x:c r="J37" s="38"/>
+      <x:c r="K37" s="38"/>
+      <x:c r="L37" s="38"/>
+      <x:c r="M37" s="38"/>
+      <x:c r="N37" s="38"/>
+      <x:c r="O37" s="38"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
         <x:v>Loan principal</x:v>
       </x:c>
-      <x:c r="B38" s="37"/>
-      <x:c r="C38" s="37"/>
-      <x:c r="D38" s="37"/>
-      <x:c r="E38" s="37"/>
-      <x:c r="F38" s="37"/>
-      <x:c r="G38" s="37"/>
-      <x:c r="H38" s="37"/>
-      <x:c r="I38" s="37"/>
-      <x:c r="J38" s="37"/>
-      <x:c r="K38" s="37"/>
-      <x:c r="L38" s="37"/>
-      <x:c r="M38" s="37"/>
-      <x:c r="N38" s="37"/>
-      <x:c r="O38" s="37"/>
+      <x:c r="B38" s="38"/>
+      <x:c r="C38" s="38"/>
+      <x:c r="D38" s="38"/>
+      <x:c r="E38" s="38"/>
+      <x:c r="F38" s="38"/>
+      <x:c r="G38" s="38"/>
+      <x:c r="H38" s="38"/>
+      <x:c r="I38" s="38"/>
+      <x:c r="J38" s="38"/>
+      <x:c r="K38" s="38"/>
+      <x:c r="L38" s="38"/>
+      <x:c r="M38" s="38"/>
+      <x:c r="N38" s="38"/>
+      <x:c r="O38" s="38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
         <x:v>Capital expenditure</x:v>
       </x:c>
-      <x:c r="B39" s="37"/>
-      <x:c r="C39" s="37"/>
-      <x:c r="D39" s="37"/>
-      <x:c r="E39" s="37"/>
-      <x:c r="F39" s="37"/>
-      <x:c r="G39" s="37"/>
-      <x:c r="H39" s="37"/>
-      <x:c r="I39" s="37"/>
-      <x:c r="J39" s="37"/>
-      <x:c r="K39" s="37"/>
-      <x:c r="L39" s="37"/>
-      <x:c r="M39" s="37"/>
-      <x:c r="N39" s="37"/>
-      <x:c r="O39" s="37"/>
+      <x:c r="B39" s="38"/>
+      <x:c r="C39" s="38"/>
+      <x:c r="D39" s="38"/>
+      <x:c r="E39" s="38"/>
+      <x:c r="F39" s="38"/>
+      <x:c r="G39" s="38"/>
+      <x:c r="H39" s="38"/>
+      <x:c r="I39" s="38"/>
+      <x:c r="J39" s="38"/>
+      <x:c r="K39" s="38"/>
+      <x:c r="L39" s="38"/>
+      <x:c r="M39" s="38"/>
+      <x:c r="N39" s="38"/>
+      <x:c r="O39" s="38"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
         <x:v>Dividends / distributions</x:v>
       </x:c>
-      <x:c r="B40" s="37"/>
-      <x:c r="C40" s="37"/>
-      <x:c r="D40" s="37"/>
-      <x:c r="E40" s="37"/>
-      <x:c r="F40" s="37"/>
-      <x:c r="G40" s="37"/>
-      <x:c r="H40" s="37"/>
-      <x:c r="I40" s="37"/>
-      <x:c r="J40" s="37"/>
-      <x:c r="K40" s="37"/>
-      <x:c r="L40" s="37"/>
-      <x:c r="M40" s="37"/>
-      <x:c r="N40" s="37"/>
-      <x:c r="O40" s="37"/>
+      <x:c r="B40" s="38"/>
+      <x:c r="C40" s="38"/>
+      <x:c r="D40" s="38"/>
+      <x:c r="E40" s="38"/>
+      <x:c r="F40" s="38"/>
+      <x:c r="G40" s="38"/>
+      <x:c r="H40" s="38"/>
+      <x:c r="I40" s="38"/>
+      <x:c r="J40" s="38"/>
+      <x:c r="K40" s="38"/>
+      <x:c r="L40" s="38"/>
+      <x:c r="M40" s="38"/>
+      <x:c r="N40" s="38"/>
+      <x:c r="O40" s="38"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B41" s="37"/>
-      <x:c r="C41" s="37"/>
-      <x:c r="D41" s="37"/>
-      <x:c r="E41" s="37"/>
-      <x:c r="F41" s="37"/>
-      <x:c r="G41" s="37"/>
-      <x:c r="H41" s="37"/>
-      <x:c r="I41" s="37"/>
-      <x:c r="J41" s="37"/>
-      <x:c r="K41" s="37"/>
-      <x:c r="L41" s="37"/>
-      <x:c r="M41" s="37"/>
-      <x:c r="N41" s="37"/>
-      <x:c r="O41" s="37"/>
+      <x:c r="B41" s="38"/>
+      <x:c r="C41" s="38"/>
+      <x:c r="D41" s="38"/>
+      <x:c r="E41" s="38"/>
+      <x:c r="F41" s="38"/>
+      <x:c r="G41" s="38"/>
+      <x:c r="H41" s="38"/>
+      <x:c r="I41" s="38"/>
+      <x:c r="J41" s="38"/>
+      <x:c r="K41" s="38"/>
+      <x:c r="L41" s="38"/>
+      <x:c r="M41" s="38"/>
+      <x:c r="N41" s="38"/>
+      <x:c r="O41" s="38"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
         <x:v>Scenario payment adjustment</x:v>
       </x:c>
-      <x:c r="B42" s="37"/>
-      <x:c r="C42" s="37"/>
-      <x:c r="D42" s="37"/>
-      <x:c r="E42" s="37"/>
-      <x:c r="F42" s="37"/>
-      <x:c r="G42" s="37"/>
-      <x:c r="H42" s="37"/>
-      <x:c r="I42" s="37"/>
-      <x:c r="J42" s="37"/>
-      <x:c r="K42" s="37"/>
-      <x:c r="L42" s="37"/>
-      <x:c r="M42" s="37"/>
-      <x:c r="N42" s="37"/>
-      <x:c r="O42" s="37"/>
+      <x:c r="B42" s="38"/>
+      <x:c r="C42" s="38"/>
+      <x:c r="D42" s="38"/>
+      <x:c r="E42" s="38"/>
+      <x:c r="F42" s="38"/>
+      <x:c r="G42" s="38"/>
+      <x:c r="H42" s="38"/>
+      <x:c r="I42" s="38"/>
+      <x:c r="J42" s="38"/>
+      <x:c r="K42" s="38"/>
+      <x:c r="L42" s="38"/>
+      <x:c r="M42" s="38"/>
+      <x:c r="N42" s="38"/>
+      <x:c r="O42" s="38"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="36" t="str">
+      <x:c r="A43" s="37" t="str">
         <x:v>Total cash payments</x:v>
       </x:c>
-      <x:c r="B43" s="38"/>
-      <x:c r="C43" s="38"/>
-      <x:c r="D43" s="38"/>
-      <x:c r="E43" s="38"/>
-      <x:c r="F43" s="38"/>
-      <x:c r="G43" s="38"/>
-      <x:c r="H43" s="38"/>
-      <x:c r="I43" s="38"/>
-      <x:c r="J43" s="38"/>
-      <x:c r="K43" s="38"/>
-      <x:c r="L43" s="38"/>
-      <x:c r="M43" s="38"/>
-      <x:c r="N43" s="38"/>
-      <x:c r="O43" s="38"/>
+      <x:c r="B43" s="39"/>
+      <x:c r="C43" s="39"/>
+      <x:c r="D43" s="39"/>
+      <x:c r="E43" s="39"/>
+      <x:c r="F43" s="39"/>
+      <x:c r="G43" s="39"/>
+      <x:c r="H43" s="39"/>
+      <x:c r="I43" s="39"/>
+      <x:c r="J43" s="39"/>
+      <x:c r="K43" s="39"/>
+      <x:c r="L43" s="39"/>
+      <x:c r="M43" s="39"/>
+      <x:c r="N43" s="39"/>
+      <x:c r="O43" s="39"/>
     </x:row>
     <x:row r="44">
-      <x:c r="B44" s="37"/>
-      <x:c r="C44" s="37"/>
-      <x:c r="D44" s="37"/>
-      <x:c r="E44" s="37"/>
-      <x:c r="F44" s="37"/>
-      <x:c r="G44" s="37"/>
-      <x:c r="H44" s="37"/>
-      <x:c r="I44" s="37"/>
-      <x:c r="J44" s="37"/>
-      <x:c r="K44" s="37"/>
-      <x:c r="L44" s="37"/>
-      <x:c r="M44" s="37"/>
-      <x:c r="N44" s="37"/>
-      <x:c r="O44" s="37"/>
+      <x:c r="B44" s="38"/>
+      <x:c r="C44" s="38"/>
+      <x:c r="D44" s="38"/>
+      <x:c r="E44" s="38"/>
+      <x:c r="F44" s="38"/>
+      <x:c r="G44" s="38"/>
+      <x:c r="H44" s="38"/>
+      <x:c r="I44" s="38"/>
+      <x:c r="J44" s="38"/>
+      <x:c r="K44" s="38"/>
+      <x:c r="L44" s="38"/>
+      <x:c r="M44" s="38"/>
+      <x:c r="N44" s="38"/>
+      <x:c r="O44" s="38"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="14" t="str">
         <x:v>CASH POSITION</x:v>
       </x:c>
-      <x:c r="B45" s="39"/>
-      <x:c r="C45" s="39"/>
-      <x:c r="D45" s="39"/>
-      <x:c r="E45" s="39"/>
-      <x:c r="F45" s="39"/>
-      <x:c r="G45" s="39"/>
-      <x:c r="H45" s="39"/>
-      <x:c r="I45" s="39"/>
-      <x:c r="J45" s="39"/>
-      <x:c r="K45" s="39"/>
-      <x:c r="L45" s="39"/>
-      <x:c r="M45" s="39"/>
-      <x:c r="N45" s="39"/>
-      <x:c r="O45" s="39"/>
+      <x:c r="B45" s="40"/>
+      <x:c r="C45" s="40"/>
+      <x:c r="D45" s="40"/>
+      <x:c r="E45" s="40"/>
+      <x:c r="F45" s="40"/>
+      <x:c r="G45" s="40"/>
+      <x:c r="H45" s="40"/>
+      <x:c r="I45" s="40"/>
+      <x:c r="J45" s="40"/>
+      <x:c r="K45" s="40"/>
+      <x:c r="L45" s="40"/>
+      <x:c r="M45" s="40"/>
+      <x:c r="N45" s="40"/>
+      <x:c r="O45" s="40"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
         <x:v>Opening cash balance</x:v>
       </x:c>
-      <x:c r="B46" s="37"/>
-      <x:c r="C46" s="37"/>
-      <x:c r="D46" s="37"/>
-      <x:c r="E46" s="37"/>
-      <x:c r="F46" s="37"/>
-      <x:c r="G46" s="37"/>
-      <x:c r="H46" s="37"/>
-      <x:c r="I46" s="37"/>
-      <x:c r="J46" s="37"/>
-      <x:c r="K46" s="37"/>
-      <x:c r="L46" s="37"/>
-      <x:c r="M46" s="37"/>
-      <x:c r="N46" s="37"/>
-      <x:c r="O46" s="37"/>
+      <x:c r="B46" s="38"/>
+      <x:c r="C46" s="38"/>
+      <x:c r="D46" s="38"/>
+      <x:c r="E46" s="38"/>
+      <x:c r="F46" s="38"/>
+      <x:c r="G46" s="38"/>
+      <x:c r="H46" s="38"/>
+      <x:c r="I46" s="38"/>
+      <x:c r="J46" s="38"/>
+      <x:c r="K46" s="38"/>
+      <x:c r="L46" s="38"/>
+      <x:c r="M46" s="38"/>
+      <x:c r="N46" s="38"/>
+      <x:c r="O46" s="38"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
         <x:v>Net cash movement</x:v>
       </x:c>
-      <x:c r="B47" s="37"/>
-      <x:c r="C47" s="37"/>
-      <x:c r="D47" s="37"/>
-      <x:c r="E47" s="37"/>
-      <x:c r="F47" s="37"/>
-      <x:c r="G47" s="37"/>
-      <x:c r="H47" s="37"/>
-      <x:c r="I47" s="37"/>
-      <x:c r="J47" s="37"/>
-      <x:c r="K47" s="37"/>
-      <x:c r="L47" s="37"/>
-      <x:c r="M47" s="37"/>
-      <x:c r="N47" s="37"/>
-      <x:c r="O47" s="37"/>
+      <x:c r="B47" s="38"/>
+      <x:c r="C47" s="38"/>
+      <x:c r="D47" s="38"/>
+      <x:c r="E47" s="38"/>
+      <x:c r="F47" s="38"/>
+      <x:c r="G47" s="38"/>
+      <x:c r="H47" s="38"/>
+      <x:c r="I47" s="38"/>
+      <x:c r="J47" s="38"/>
+      <x:c r="K47" s="38"/>
+      <x:c r="L47" s="38"/>
+      <x:c r="M47" s="38"/>
+      <x:c r="N47" s="38"/>
+      <x:c r="O47" s="38"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="36" t="str">
+      <x:c r="A48" s="37" t="str">
         <x:v>Closing cash balance</x:v>
       </x:c>
-      <x:c r="B48" s="38"/>
-      <x:c r="C48" s="38"/>
-      <x:c r="D48" s="38"/>
-      <x:c r="E48" s="38"/>
-      <x:c r="F48" s="38"/>
-      <x:c r="G48" s="38"/>
-      <x:c r="H48" s="38"/>
-      <x:c r="I48" s="38"/>
-      <x:c r="J48" s="38"/>
-      <x:c r="K48" s="38"/>
-      <x:c r="L48" s="38"/>
-      <x:c r="M48" s="38"/>
-      <x:c r="N48" s="38"/>
-      <x:c r="O48" s="38"/>
+      <x:c r="B48" s="39"/>
+      <x:c r="C48" s="39"/>
+      <x:c r="D48" s="39"/>
+      <x:c r="E48" s="39"/>
+      <x:c r="F48" s="39"/>
+      <x:c r="G48" s="39"/>
+      <x:c r="H48" s="39"/>
+      <x:c r="I48" s="39"/>
+      <x:c r="J48" s="39"/>
+      <x:c r="K48" s="39"/>
+      <x:c r="L48" s="39"/>
+      <x:c r="M48" s="39"/>
+      <x:c r="N48" s="39"/>
+      <x:c r="O48" s="39"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B49" s="37"/>
-      <x:c r="C49" s="37"/>
-      <x:c r="D49" s="37"/>
-      <x:c r="E49" s="37"/>
-      <x:c r="F49" s="37"/>
-      <x:c r="G49" s="37"/>
-      <x:c r="H49" s="37"/>
-      <x:c r="I49" s="37"/>
-      <x:c r="J49" s="37"/>
-      <x:c r="K49" s="37"/>
-      <x:c r="L49" s="37"/>
-      <x:c r="M49" s="37"/>
-      <x:c r="N49" s="37"/>
-      <x:c r="O49" s="37"/>
+      <x:c r="B49" s="38"/>
+      <x:c r="C49" s="38"/>
+      <x:c r="D49" s="38"/>
+      <x:c r="E49" s="38"/>
+      <x:c r="F49" s="38"/>
+      <x:c r="G49" s="38"/>
+      <x:c r="H49" s="38"/>
+      <x:c r="I49" s="38"/>
+      <x:c r="J49" s="38"/>
+      <x:c r="K49" s="38"/>
+      <x:c r="L49" s="38"/>
+      <x:c r="M49" s="38"/>
+      <x:c r="N49" s="38"/>
+      <x:c r="O49" s="38"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="36" t="str">
+      <x:c r="A50" s="37" t="str">
         <x:v>Headroom / (gap)</x:v>
       </x:c>
-      <x:c r="B50" s="38"/>
-      <x:c r="C50" s="38"/>
-      <x:c r="D50" s="38"/>
-      <x:c r="E50" s="38"/>
-      <x:c r="F50" s="38"/>
-      <x:c r="G50" s="38"/>
-      <x:c r="H50" s="38"/>
-      <x:c r="I50" s="38"/>
-      <x:c r="J50" s="38"/>
-      <x:c r="K50" s="38"/>
-      <x:c r="L50" s="38"/>
-      <x:c r="M50" s="38"/>
-      <x:c r="N50" s="38"/>
-      <x:c r="O50" s="38"/>
+      <x:c r="B50" s="39"/>
+      <x:c r="C50" s="39"/>
+      <x:c r="D50" s="39"/>
+      <x:c r="E50" s="39"/>
+      <x:c r="F50" s="39"/>
+      <x:c r="G50" s="39"/>
+      <x:c r="H50" s="39"/>
+      <x:c r="I50" s="39"/>
+      <x:c r="J50" s="39"/>
+      <x:c r="K50" s="39"/>
+      <x:c r="L50" s="39"/>
+      <x:c r="M50" s="39"/>
+      <x:c r="N50" s="39"/>
+      <x:c r="O50" s="39"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
@@ -2097,46 +2099,46 @@
       <x:c r="N2" s="8"/>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="27" t="str">
+      <x:c r="A5" s="28" t="str">
         <x:v>Week</x:v>
       </x:c>
-      <x:c r="B5" s="27" t="str">
+      <x:c r="B5" s="28" t="str">
         <x:v>Week commencing</x:v>
       </x:c>
-      <x:c r="C5" s="27" t="str">
+      <x:c r="C5" s="28" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="D5" s="27" t="str">
+      <x:c r="D5" s="28" t="str">
         <x:v>Forecast receipts</x:v>
       </x:c>
-      <x:c r="E5" s="27" t="str">
+      <x:c r="E5" s="28" t="str">
         <x:v>Actual receipts</x:v>
       </x:c>
-      <x:c r="F5" s="27" t="str">
+      <x:c r="F5" s="28" t="str">
         <x:v>Receipt variance</x:v>
       </x:c>
-      <x:c r="G5" s="27" t="str">
+      <x:c r="G5" s="28" t="str">
         <x:v>Forecast payments</x:v>
       </x:c>
-      <x:c r="H5" s="27" t="str">
+      <x:c r="H5" s="28" t="str">
         <x:v>Actual payments</x:v>
       </x:c>
-      <x:c r="I5" s="27" t="str">
+      <x:c r="I5" s="28" t="str">
         <x:v>Payment variance</x:v>
       </x:c>
-      <x:c r="J5" s="27" t="str">
+      <x:c r="J5" s="28" t="str">
         <x:v>Forecast closing cash</x:v>
       </x:c>
-      <x:c r="K5" s="27" t="str">
+      <x:c r="K5" s="28" t="str">
         <x:v>Actual closing cash</x:v>
       </x:c>
-      <x:c r="L5" s="27" t="str">
+      <x:c r="L5" s="28" t="str">
         <x:v>Cash variance</x:v>
       </x:c>
-      <x:c r="M5" s="27" t="str">
+      <x:c r="M5" s="28" t="str">
         <x:v>Owner</x:v>
       </x:c>
-      <x:c r="N5" s="27" t="str">
+      <x:c r="N5" s="28" t="str">
         <x:v>Commentary / action</x:v>
       </x:c>
     </x:row>
@@ -2279,16 +2281,16 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="40" t="str">
+      <x:c r="A6" s="41" t="str">
         <x:v>MODEL STATUS: prepared for formula-driven integrity checks</x:v>
       </x:c>
-      <x:c r="B6" s="40"/>
-      <x:c r="C6" s="40"/>
-      <x:c r="D6" s="40"/>
-      <x:c r="E6" s="40"/>
-      <x:c r="F6" s="40"/>
-      <x:c r="G6" s="40"/>
-      <x:c r="H6" s="40"/>
+      <x:c r="B6" s="41"/>
+      <x:c r="C6" s="41"/>
+      <x:c r="D6" s="41"/>
+      <x:c r="E6" s="41"/>
+      <x:c r="F6" s="41"/>
+      <x:c r="G6" s="41"/>
+      <x:c r="H6" s="41"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
@@ -2311,22 +2313,22 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="42" t="str">
+      <x:c r="A11" s="43" t="str">
         <x:v>Statutory dates and classifications require confirmation for your entity, reporting cycle and agent arrangements.</x:v>
       </x:c>
-      <x:c r="B11" s="42"/>
-      <x:c r="C11" s="42"/>
-      <x:c r="D11" s="42"/>
-      <x:c r="E11" s="42"/>
-      <x:c r="F11" s="42"/>
+      <x:c r="B11" s="43"/>
+      <x:c r="C11" s="43"/>
+      <x:c r="D11" s="43"/>
+      <x:c r="E11" s="43"/>
+      <x:c r="F11" s="43"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="42"/>
-      <x:c r="B12" s="42"/>
-      <x:c r="C12" s="42"/>
-      <x:c r="D12" s="42"/>
-      <x:c r="E12" s="42"/>
-      <x:c r="F12" s="42"/>
+      <x:c r="A12" s="43"/>
+      <x:c r="B12" s="43"/>
+      <x:c r="C12" s="43"/>
+      <x:c r="D12" s="43"/>
+      <x:c r="E12" s="43"/>
+      <x:c r="F12" s="43"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R8422424ed3254cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R5c91082a1e444c94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R2078ee11a4bc45e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R257a5564b1894f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R6a0c7ecdfe164073"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R66855269f32c48a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R163eef40803243ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R36a323b4bd524392"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R55e1d91aef2144cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R3a5216492bc244a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R6e15a48bc1404b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R40686c5f31a64d21"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -15,6 +15,59 @@
     <x:definedName name="CashFlowScenarioList">'Assumptions'!$B$15:$B$17</x:definedName>
   </x:definedNames>
 </x:workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author>tc={E28899D8-E974-D419-CBA0-A3EAED613B76}</x:author>
+    <x:author>tc={17D25D66-7DB0-58F0-CE5E-E2EB2DCDA11F}</x:author>
+    <x:author>tc={6D6F189E-71DD-5AB0-A5B5-8089484B0A68}</x:author>
+    <x:author>tc={E870F557-83E1-4DD3-E5B6-7E48039B894E}</x:author>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="B18" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Scenario receipt adjustment applies the selected scenario only to customer receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B42" authorId="1">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B34" authorId="2">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B35" authorId="3">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -28,7 +81,7 @@
     <x:numFmt numFmtId="201" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0);-"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -90,6 +143,12 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FF04001F"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Aptos"/>
     </x:font>
     <x:font>
@@ -163,7 +222,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="44">
+  <x:cellXfs count="50">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -216,10 +275,16 @@
     <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -230,7 +295,48 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="3">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5C2D91"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDED9E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:person displayName="User" id="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}"/>
+</xltc:personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -424,6 +530,23 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:threadedComment ref="B18" dT="2026-08-26T13:22:07.159" personId="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}" id="{E28899D8-E974-D419-CBA0-A3EAED613B76}">
+    <xltc:text>Scenario receipt adjustment applies the selected scenario only to customer receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="B42" dT="2026-08-26T13:22:07.159" personId="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}" id="{17D25D66-7DB0-58F0-CE5E-E2EB2DCDA11F}">
+    <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="B34" dT="2026-08-26T13:22:07.159" personId="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}" id="{6D6F189E-71DD-5AB0-A5B5-8089484B0A68}">
+    <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="B35" dT="2026-08-26T13:22:07.159" personId="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}" id="{E870F557-83E1-4DD3-E5B6-7E48039B894E}">
+    <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
+  </xltc:threadedComment>
+</xltc:ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -1080,7 +1203,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Weekly cash-flow structure. The forecast engine and editable operating inputs are added in the next build step.</x:v>
+        <x:v>Blue cells are illustrative weekly inputs. Formula and linked cells update automatically from the Assumptions control panel.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -1102,42 +1225,55 @@
         <x:v>Week commencing</x:v>
       </x:c>
       <x:c r="B5" s="34" t="n">
+        <x:f>'Assumptions'!$B$8</x:f>
         <x:v>46265</x:v>
       </x:c>
       <x:c r="C5" s="34" t="n">
+        <x:f>B5+7</x:f>
         <x:v>46272</x:v>
       </x:c>
       <x:c r="D5" s="34" t="n">
+        <x:f>C5+7</x:f>
         <x:v>46279</x:v>
       </x:c>
       <x:c r="E5" s="34" t="n">
+        <x:f>D5+7</x:f>
         <x:v>46286</x:v>
       </x:c>
       <x:c r="F5" s="34" t="n">
+        <x:f>E5+7</x:f>
         <x:v>46293</x:v>
       </x:c>
       <x:c r="G5" s="34" t="n">
+        <x:f>F5+7</x:f>
         <x:v>46300</x:v>
       </x:c>
       <x:c r="H5" s="34" t="n">
+        <x:f>G5+7</x:f>
         <x:v>46307</x:v>
       </x:c>
       <x:c r="I5" s="34" t="n">
+        <x:f>H5+7</x:f>
         <x:v>46314</x:v>
       </x:c>
       <x:c r="J5" s="34" t="n">
+        <x:f>I5+7</x:f>
         <x:v>46321</x:v>
       </x:c>
       <x:c r="K5" s="34" t="n">
+        <x:f>J5+7</x:f>
         <x:v>46328</x:v>
       </x:c>
       <x:c r="L5" s="34" t="n">
+        <x:f>K5+7</x:f>
         <x:v>46335</x:v>
       </x:c>
       <x:c r="M5" s="34" t="n">
+        <x:f>L5+7</x:f>
         <x:v>46342</x:v>
       </x:c>
       <x:c r="N5" s="34" t="n">
+        <x:f>M5+7</x:f>
         <x:v>46349</x:v>
       </x:c>
       <x:c r="O5" t="str">
@@ -1149,42 +1285,55 @@
         <x:v>Week ending</x:v>
       </x:c>
       <x:c r="B6" s="34" t="n">
+        <x:f>B5+6</x:f>
         <x:v>46271</x:v>
       </x:c>
       <x:c r="C6" s="34" t="n">
+        <x:f>C5+6</x:f>
         <x:v>46278</x:v>
       </x:c>
       <x:c r="D6" s="34" t="n">
+        <x:f>D5+6</x:f>
         <x:v>46285</x:v>
       </x:c>
       <x:c r="E6" s="34" t="n">
+        <x:f>E5+6</x:f>
         <x:v>46292</x:v>
       </x:c>
       <x:c r="F6" s="34" t="n">
+        <x:f>F5+6</x:f>
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G6" s="34" t="n">
+        <x:f>G5+6</x:f>
         <x:v>46306</x:v>
       </x:c>
       <x:c r="H6" s="34" t="n">
+        <x:f>H5+6</x:f>
         <x:v>46313</x:v>
       </x:c>
       <x:c r="I6" s="34" t="n">
+        <x:f>I5+6</x:f>
         <x:v>46320</x:v>
       </x:c>
       <x:c r="J6" s="34" t="n">
+        <x:f>J5+6</x:f>
         <x:v>46327</x:v>
       </x:c>
       <x:c r="K6" s="34" t="n">
+        <x:f>K5+6</x:f>
         <x:v>46334</x:v>
       </x:c>
       <x:c r="L6" s="34" t="n">
+        <x:f>L5+6</x:f>
         <x:v>46341</x:v>
       </x:c>
       <x:c r="M6" s="34" t="n">
+        <x:f>M5+6</x:f>
         <x:v>46348</x:v>
       </x:c>
       <x:c r="N6" s="34" t="n">
+        <x:f>N5+6</x:f>
         <x:v>46355</x:v>
       </x:c>
       <x:c r="O6" t="str">
@@ -1196,42 +1345,55 @@
         <x:v>Actual / Forecast</x:v>
       </x:c>
       <x:c r="B7" s="35" t="str">
+        <x:f>IF(B6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="C7" s="35" t="str">
+        <x:f>IF(C6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="C7" s="35" t="str">
+      <x:c r="D7" s="35" t="str">
+        <x:f>IF(D6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="D7" s="35" t="str">
+      <x:c r="E7" s="35" t="str">
+        <x:f>IF(E6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="E7" s="35" t="str">
+      <x:c r="F7" s="35" t="str">
+        <x:f>IF(F6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="F7" s="35" t="str">
+      <x:c r="G7" s="35" t="str">
+        <x:f>IF(G6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="G7" s="35" t="str">
+      <x:c r="H7" s="35" t="str">
+        <x:f>IF(H6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="H7" s="35" t="str">
+      <x:c r="I7" s="35" t="str">
+        <x:f>IF(I6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="I7" s="35" t="str">
+      <x:c r="J7" s="35" t="str">
+        <x:f>IF(J6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="J7" s="35" t="str">
+      <x:c r="K7" s="35" t="str">
+        <x:f>IF(K6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="K7" s="35" t="str">
+      <x:c r="L7" s="35" t="str">
+        <x:f>IF(L6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="L7" s="35" t="str">
+      <x:c r="M7" s="35" t="str">
+        <x:f>IF(M6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="M7" s="35" t="str">
-        <x:v>Forecast</x:v>
-      </x:c>
       <x:c r="N7" s="35" t="str">
+        <x:f>IF(N6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
       <x:c r="O7" t="str"/>
@@ -1259,778 +1421,2024 @@
       <x:c r="A10" t="str">
         <x:v>Customer receipts</x:v>
       </x:c>
-      <x:c r="B10" s="38"/>
-      <x:c r="C10" s="38"/>
-      <x:c r="D10" s="38"/>
-      <x:c r="E10" s="38"/>
-      <x:c r="F10" s="38"/>
-      <x:c r="G10" s="38"/>
-      <x:c r="H10" s="38"/>
-      <x:c r="I10" s="38"/>
-      <x:c r="J10" s="38"/>
-      <x:c r="K10" s="38"/>
-      <x:c r="L10" s="38"/>
-      <x:c r="M10" s="38"/>
-      <x:c r="N10" s="38"/>
-      <x:c r="O10" s="38"/>
+      <x:c r="B10" s="38" t="n">
+        <x:v>118000</x:v>
+      </x:c>
+      <x:c r="C10" s="38" t="n">
+        <x:v>125000</x:v>
+      </x:c>
+      <x:c r="D10" s="38" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="E10" s="38" t="n">
+        <x:v>115000</x:v>
+      </x:c>
+      <x:c r="F10" s="38" t="n">
+        <x:v>110000</x:v>
+      </x:c>
+      <x:c r="G10" s="38" t="n">
+        <x:v>112000</x:v>
+      </x:c>
+      <x:c r="H10" s="38" t="n">
+        <x:v>105000</x:v>
+      </x:c>
+      <x:c r="I10" s="38" t="n">
+        <x:v>108000</x:v>
+      </x:c>
+      <x:c r="J10" s="38" t="n">
+        <x:v>110000</x:v>
+      </x:c>
+      <x:c r="K10" s="38" t="n">
+        <x:v>116000</x:v>
+      </x:c>
+      <x:c r="L10" s="38" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="M10" s="38" t="n">
+        <x:v>125000</x:v>
+      </x:c>
+      <x:c r="N10" s="38" t="n">
+        <x:v>130000</x:v>
+      </x:c>
+      <x:c r="O10" s="39" t="n">
+        <x:f>SUM(B10:N10)</x:f>
+        <x:v>1514000</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
         <x:v>Overdue receipts</x:v>
       </x:c>
-      <x:c r="B11" s="38"/>
-      <x:c r="C11" s="38"/>
-      <x:c r="D11" s="38"/>
-      <x:c r="E11" s="38"/>
-      <x:c r="F11" s="38"/>
-      <x:c r="G11" s="38"/>
-      <x:c r="H11" s="38"/>
-      <x:c r="I11" s="38"/>
-      <x:c r="J11" s="38"/>
-      <x:c r="K11" s="38"/>
-      <x:c r="L11" s="38"/>
-      <x:c r="M11" s="38"/>
-      <x:c r="N11" s="38"/>
-      <x:c r="O11" s="38"/>
+      <x:c r="B11" s="38" t="n">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="C11" s="38" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D11" s="38" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="E11" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F11" s="38" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="G11" s="38" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="H11" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="I11" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="J11" s="38" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="K11" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="L11" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="M11" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="N11" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="O11" s="39" t="n">
+        <x:f>SUM(B11:N11)</x:f>
+        <x:v>152000</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
         <x:v>Cash / EFTPOS sales</x:v>
       </x:c>
-      <x:c r="B12" s="38"/>
-      <x:c r="C12" s="38"/>
-      <x:c r="D12" s="38"/>
-      <x:c r="E12" s="38"/>
-      <x:c r="F12" s="38"/>
-      <x:c r="G12" s="38"/>
-      <x:c r="H12" s="38"/>
-      <x:c r="I12" s="38"/>
-      <x:c r="J12" s="38"/>
-      <x:c r="K12" s="38"/>
-      <x:c r="L12" s="38"/>
-      <x:c r="M12" s="38"/>
-      <x:c r="N12" s="38"/>
-      <x:c r="O12" s="38"/>
+      <x:c r="B12" s="38" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="C12" s="38" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D12" s="38" t="n">
+        <x:v>19000</x:v>
+      </x:c>
+      <x:c r="E12" s="38" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="F12" s="38" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="G12" s="38" t="n">
+        <x:v>17000</x:v>
+      </x:c>
+      <x:c r="H12" s="38" t="n">
+        <x:v>17000</x:v>
+      </x:c>
+      <x:c r="I12" s="38" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="J12" s="38" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="K12" s="38" t="n">
+        <x:v>19000</x:v>
+      </x:c>
+      <x:c r="L12" s="38" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="M12" s="38" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="N12" s="38" t="n">
+        <x:v>22000</x:v>
+      </x:c>
+      <x:c r="O12" s="39" t="n">
+        <x:f>SUM(B12:N12)</x:f>
+        <x:v>245000</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
         <x:v>GST refunds / credits</x:v>
       </x:c>
-      <x:c r="B13" s="38"/>
-      <x:c r="C13" s="38"/>
-      <x:c r="D13" s="38"/>
-      <x:c r="E13" s="38"/>
-      <x:c r="F13" s="38"/>
-      <x:c r="G13" s="38"/>
-      <x:c r="H13" s="38"/>
-      <x:c r="I13" s="38"/>
-      <x:c r="J13" s="38"/>
-      <x:c r="K13" s="38"/>
-      <x:c r="L13" s="38"/>
-      <x:c r="M13" s="38"/>
-      <x:c r="N13" s="38"/>
-      <x:c r="O13" s="38"/>
+      <x:c r="B13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="39" t="n">
+        <x:f>SUM(B13:N13)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B14" s="38"/>
-      <x:c r="C14" s="38"/>
-      <x:c r="D14" s="38"/>
-      <x:c r="E14" s="38"/>
-      <x:c r="F14" s="38"/>
-      <x:c r="G14" s="38"/>
-      <x:c r="H14" s="38"/>
-      <x:c r="I14" s="38"/>
-      <x:c r="J14" s="38"/>
-      <x:c r="K14" s="38"/>
-      <x:c r="L14" s="38"/>
-      <x:c r="M14" s="38"/>
-      <x:c r="N14" s="38"/>
-      <x:c r="O14" s="38"/>
+      <x:c r="B14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="C14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="D14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="E14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="F14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="G14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="H14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="I14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="J14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="K14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="L14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="M14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="N14" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="O14" s="39" t="n">
+        <x:f>SUM(B14:N14)</x:f>
+        <x:v>52000</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
         <x:v>Asset sale proceeds</x:v>
       </x:c>
-      <x:c r="B15" s="38"/>
-      <x:c r="C15" s="38"/>
-      <x:c r="D15" s="38"/>
-      <x:c r="E15" s="38"/>
-      <x:c r="F15" s="38"/>
-      <x:c r="G15" s="38"/>
-      <x:c r="H15" s="38"/>
-      <x:c r="I15" s="38"/>
-      <x:c r="J15" s="38"/>
-      <x:c r="K15" s="38"/>
-      <x:c r="L15" s="38"/>
-      <x:c r="M15" s="38"/>
-      <x:c r="N15" s="38"/>
-      <x:c r="O15" s="38"/>
+      <x:c r="B15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="38" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="L15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="39" t="n">
+        <x:f>SUM(B15:N15)</x:f>
+        <x:v>100000</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
         <x:v>Equity / owner funding</x:v>
       </x:c>
-      <x:c r="B16" s="38"/>
-      <x:c r="C16" s="38"/>
-      <x:c r="D16" s="38"/>
-      <x:c r="E16" s="38"/>
-      <x:c r="F16" s="38"/>
-      <x:c r="G16" s="38"/>
-      <x:c r="H16" s="38"/>
-      <x:c r="I16" s="38"/>
-      <x:c r="J16" s="38"/>
-      <x:c r="K16" s="38"/>
-      <x:c r="L16" s="38"/>
-      <x:c r="M16" s="38"/>
-      <x:c r="N16" s="38"/>
-      <x:c r="O16" s="38"/>
+      <x:c r="B16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="38" t="n">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="I16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="39" t="n">
+        <x:f>SUM(B16:N16)</x:f>
+        <x:v>150000</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
         <x:v>Loan proceeds</x:v>
       </x:c>
-      <x:c r="B17" s="38"/>
-      <x:c r="C17" s="38"/>
-      <x:c r="D17" s="38"/>
-      <x:c r="E17" s="38"/>
-      <x:c r="F17" s="38"/>
-      <x:c r="G17" s="38"/>
-      <x:c r="H17" s="38"/>
-      <x:c r="I17" s="38"/>
-      <x:c r="J17" s="38"/>
-      <x:c r="K17" s="38"/>
-      <x:c r="L17" s="38"/>
-      <x:c r="M17" s="38"/>
-      <x:c r="N17" s="38"/>
-      <x:c r="O17" s="38"/>
+      <x:c r="B17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="38" t="n">
+        <x:v>125000</x:v>
+      </x:c>
+      <x:c r="K17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="39" t="n">
+        <x:f>SUM(B17:N17)</x:f>
+        <x:v>125000</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
         <x:v>Scenario receipt adjustment</x:v>
       </x:c>
-      <x:c r="B18" s="38"/>
-      <x:c r="C18" s="38"/>
-      <x:c r="D18" s="38"/>
-      <x:c r="E18" s="38"/>
-      <x:c r="F18" s="38"/>
-      <x:c r="G18" s="38"/>
-      <x:c r="H18" s="38"/>
-      <x:c r="I18" s="38"/>
-      <x:c r="J18" s="38"/>
-      <x:c r="K18" s="38"/>
-      <x:c r="L18" s="38"/>
-      <x:c r="M18" s="38"/>
-      <x:c r="N18" s="38"/>
-      <x:c r="O18" s="38"/>
+      <x:c r="B18" s="42" t="n">
+        <x:f>IF(B$7="Actual",0,SUM(B10:B12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="42" t="n">
+        <x:f>IF(C$7="Actual",0,SUM(C10:C12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="42" t="n">
+        <x:f>IF(D$7="Actual",0,SUM(D10:D12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="42" t="n">
+        <x:f>IF(E$7="Actual",0,SUM(E10:E12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="42" t="n">
+        <x:f>IF(F$7="Actual",0,SUM(F10:F12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="42" t="n">
+        <x:f>IF(G$7="Actual",0,SUM(G10:G12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="42" t="n">
+        <x:f>IF(H$7="Actual",0,SUM(H10:H12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="42" t="n">
+        <x:f>IF(I$7="Actual",0,SUM(I10:I12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="42" t="n">
+        <x:f>IF(J$7="Actual",0,SUM(J10:J12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="42" t="n">
+        <x:f>IF(K$7="Actual",0,SUM(K10:K12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="42" t="n">
+        <x:f>IF(L$7="Actual",0,SUM(L10:L12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="42" t="n">
+        <x:f>IF(M$7="Actual",0,SUM(M10:M12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="42" t="n">
+        <x:f>IF(N$7="Actual",0,SUM(N10:N12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="39" t="n">
+        <x:f>SUM(B18:N18)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="37" t="str">
         <x:v>Total cash receipts</x:v>
       </x:c>
-      <x:c r="B19" s="39"/>
-      <x:c r="C19" s="39"/>
-      <x:c r="D19" s="39"/>
-      <x:c r="E19" s="39"/>
-      <x:c r="F19" s="39"/>
-      <x:c r="G19" s="39"/>
-      <x:c r="H19" s="39"/>
-      <x:c r="I19" s="39"/>
-      <x:c r="J19" s="39"/>
-      <x:c r="K19" s="39"/>
-      <x:c r="L19" s="39"/>
-      <x:c r="M19" s="39"/>
-      <x:c r="N19" s="39"/>
-      <x:c r="O19" s="39"/>
+      <x:c r="B19" s="43" t="n">
+        <x:f>SUM(B10:B18)</x:f>
+        <x:v>170000</x:v>
+      </x:c>
+      <x:c r="C19" s="43" t="n">
+        <x:f>SUM(C10:C18)</x:f>
+        <x:v>169000</x:v>
+      </x:c>
+      <x:c r="D19" s="43" t="n">
+        <x:f>SUM(D10:D18)</x:f>
+        <x:v>158000</x:v>
+      </x:c>
+      <x:c r="E19" s="43" t="n">
+        <x:f>SUM(E10:E18)</x:f>
+        <x:v>147000</x:v>
+      </x:c>
+      <x:c r="F19" s="43" t="n">
+        <x:f>SUM(F10:F18)</x:f>
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="G19" s="43" t="n">
+        <x:f>SUM(G10:G18)</x:f>
+        <x:v>141000</x:v>
+      </x:c>
+      <x:c r="H19" s="43" t="n">
+        <x:f>SUM(H10:H18)</x:f>
+        <x:v>281000</x:v>
+      </x:c>
+      <x:c r="I19" s="43" t="n">
+        <x:f>SUM(I10:I18)</x:f>
+        <x:v>135000</x:v>
+      </x:c>
+      <x:c r="J19" s="43" t="n">
+        <x:f>SUM(J10:J18)</x:f>
+        <x:v>264000</x:v>
+      </x:c>
+      <x:c r="K19" s="43" t="n">
+        <x:f>SUM(K10:K18)</x:f>
+        <x:v>249000</x:v>
+      </x:c>
+      <x:c r="L19" s="43" t="n">
+        <x:f>SUM(L10:L18)</x:f>
+        <x:v>154000</x:v>
+      </x:c>
+      <x:c r="M19" s="43" t="n">
+        <x:f>SUM(M10:M18)</x:f>
+        <x:v>162000</x:v>
+      </x:c>
+      <x:c r="N19" s="43" t="n">
+        <x:f>SUM(N10:N18)</x:f>
+        <x:v>168000</x:v>
+      </x:c>
+      <x:c r="O19" s="40" t="n">
+        <x:f>SUM(B19:N19)</x:f>
+        <x:v>2338000</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="38"/>
-      <x:c r="C20" s="38"/>
-      <x:c r="D20" s="38"/>
-      <x:c r="E20" s="38"/>
-      <x:c r="F20" s="38"/>
-      <x:c r="G20" s="38"/>
-      <x:c r="H20" s="38"/>
-      <x:c r="I20" s="38"/>
-      <x:c r="J20" s="38"/>
-      <x:c r="K20" s="38"/>
-      <x:c r="L20" s="38"/>
-      <x:c r="M20" s="38"/>
-      <x:c r="N20" s="38"/>
-      <x:c r="O20" s="38"/>
+      <x:c r="B20" s="39"/>
+      <x:c r="C20" s="39"/>
+      <x:c r="D20" s="39"/>
+      <x:c r="E20" s="39"/>
+      <x:c r="F20" s="39"/>
+      <x:c r="G20" s="39"/>
+      <x:c r="H20" s="39"/>
+      <x:c r="I20" s="39"/>
+      <x:c r="J20" s="39"/>
+      <x:c r="K20" s="39"/>
+      <x:c r="L20" s="39"/>
+      <x:c r="M20" s="39"/>
+      <x:c r="N20" s="39"/>
+      <x:c r="O20" s="39"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
         <x:v>CASH PAYMENTS</x:v>
       </x:c>
-      <x:c r="B21" s="40"/>
-      <x:c r="C21" s="40"/>
-      <x:c r="D21" s="40"/>
-      <x:c r="E21" s="40"/>
-      <x:c r="F21" s="40"/>
-      <x:c r="G21" s="40"/>
-      <x:c r="H21" s="40"/>
-      <x:c r="I21" s="40"/>
-      <x:c r="J21" s="40"/>
-      <x:c r="K21" s="40"/>
-      <x:c r="L21" s="40"/>
-      <x:c r="M21" s="40"/>
-      <x:c r="N21" s="40"/>
-      <x:c r="O21" s="40"/>
+      <x:c r="B21" s="41"/>
+      <x:c r="C21" s="41"/>
+      <x:c r="D21" s="41"/>
+      <x:c r="E21" s="41"/>
+      <x:c r="F21" s="41"/>
+      <x:c r="G21" s="41"/>
+      <x:c r="H21" s="41"/>
+      <x:c r="I21" s="41"/>
+      <x:c r="J21" s="41"/>
+      <x:c r="K21" s="41"/>
+      <x:c r="L21" s="41"/>
+      <x:c r="M21" s="41"/>
+      <x:c r="N21" s="41"/>
+      <x:c r="O21" s="41"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
         <x:v>Suppliers and inventory</x:v>
       </x:c>
-      <x:c r="B22" s="38"/>
-      <x:c r="C22" s="38"/>
-      <x:c r="D22" s="38"/>
-      <x:c r="E22" s="38"/>
-      <x:c r="F22" s="38"/>
-      <x:c r="G22" s="38"/>
-      <x:c r="H22" s="38"/>
-      <x:c r="I22" s="38"/>
-      <x:c r="J22" s="38"/>
-      <x:c r="K22" s="38"/>
-      <x:c r="L22" s="38"/>
-      <x:c r="M22" s="38"/>
-      <x:c r="N22" s="38"/>
-      <x:c r="O22" s="38"/>
+      <x:c r="B22" s="38" t="n">
+        <x:v>82000</x:v>
+      </x:c>
+      <x:c r="C22" s="38" t="n">
+        <x:v>88000</x:v>
+      </x:c>
+      <x:c r="D22" s="38" t="n">
+        <x:v>90000</x:v>
+      </x:c>
+      <x:c r="E22" s="38" t="n">
+        <x:v>95000</x:v>
+      </x:c>
+      <x:c r="F22" s="38" t="n">
+        <x:v>98000</x:v>
+      </x:c>
+      <x:c r="G22" s="38" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="H22" s="38" t="n">
+        <x:v>105000</x:v>
+      </x:c>
+      <x:c r="I22" s="38" t="n">
+        <x:v>108000</x:v>
+      </x:c>
+      <x:c r="J22" s="38" t="n">
+        <x:v>110000</x:v>
+      </x:c>
+      <x:c r="K22" s="38" t="n">
+        <x:v>105000</x:v>
+      </x:c>
+      <x:c r="L22" s="38" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="M22" s="38" t="n">
+        <x:v>95000</x:v>
+      </x:c>
+      <x:c r="N22" s="38" t="n">
+        <x:v>90000</x:v>
+      </x:c>
+      <x:c r="O22" s="39" t="n">
+        <x:f>SUM(B22:N22)</x:f>
+        <x:v>1266000</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
         <x:v>Net wages</x:v>
       </x:c>
-      <x:c r="B23" s="38"/>
-      <x:c r="C23" s="38"/>
-      <x:c r="D23" s="38"/>
-      <x:c r="E23" s="38"/>
-      <x:c r="F23" s="38"/>
-      <x:c r="G23" s="38"/>
-      <x:c r="H23" s="38"/>
-      <x:c r="I23" s="38"/>
-      <x:c r="J23" s="38"/>
-      <x:c r="K23" s="38"/>
-      <x:c r="L23" s="38"/>
-      <x:c r="M23" s="38"/>
-      <x:c r="N23" s="38"/>
-      <x:c r="O23" s="38"/>
+      <x:c r="B23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="C23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="D23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="E23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="F23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="G23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="H23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="I23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="J23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="K23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="L23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="M23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="N23" s="38" t="n">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="O23" s="39" t="n">
+        <x:f>SUM(B23:N23)</x:f>
+        <x:v>546000</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
         <x:v>PAYG withholding</x:v>
       </x:c>
-      <x:c r="B24" s="38"/>
-      <x:c r="C24" s="38"/>
-      <x:c r="D24" s="38"/>
-      <x:c r="E24" s="38"/>
-      <x:c r="F24" s="38"/>
-      <x:c r="G24" s="38"/>
-      <x:c r="H24" s="38"/>
-      <x:c r="I24" s="38"/>
-      <x:c r="J24" s="38"/>
-      <x:c r="K24" s="38"/>
-      <x:c r="L24" s="38"/>
-      <x:c r="M24" s="38"/>
-      <x:c r="N24" s="38"/>
-      <x:c r="O24" s="38"/>
+      <x:c r="B24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="C24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="D24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="E24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="F24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="G24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="H24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="I24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="J24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="K24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="L24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="M24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="N24" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="O24" s="39" t="n">
+        <x:f>SUM(B24:N24)</x:f>
+        <x:v>156000</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
         <x:v>Superannuation</x:v>
       </x:c>
-      <x:c r="B25" s="38"/>
-      <x:c r="C25" s="38"/>
-      <x:c r="D25" s="38"/>
-      <x:c r="E25" s="38"/>
-      <x:c r="F25" s="38"/>
-      <x:c r="G25" s="38"/>
-      <x:c r="H25" s="38"/>
-      <x:c r="I25" s="38"/>
-      <x:c r="J25" s="38"/>
-      <x:c r="K25" s="38"/>
-      <x:c r="L25" s="38"/>
-      <x:c r="M25" s="38"/>
-      <x:c r="N25" s="38"/>
-      <x:c r="O25" s="38"/>
+      <x:c r="B25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="C25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="D25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="E25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="F25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="G25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="H25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="I25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="J25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="K25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="L25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="M25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="N25" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="O25" s="39" t="n">
+        <x:f>SUM(B25:N25)</x:f>
+        <x:v>78000</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
         <x:v>Payroll tax / workers compensation</x:v>
       </x:c>
-      <x:c r="B26" s="38"/>
-      <x:c r="C26" s="38"/>
-      <x:c r="D26" s="38"/>
-      <x:c r="E26" s="38"/>
-      <x:c r="F26" s="38"/>
-      <x:c r="G26" s="38"/>
-      <x:c r="H26" s="38"/>
-      <x:c r="I26" s="38"/>
-      <x:c r="J26" s="38"/>
-      <x:c r="K26" s="38"/>
-      <x:c r="L26" s="38"/>
-      <x:c r="M26" s="38"/>
-      <x:c r="N26" s="38"/>
-      <x:c r="O26" s="38"/>
+      <x:c r="B26" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="C26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="G26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="K26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" s="39" t="n">
+        <x:f>SUM(B26:N26)</x:f>
+        <x:v>15000</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
         <x:v>Rent</x:v>
       </x:c>
-      <x:c r="B27" s="38"/>
-      <x:c r="C27" s="38"/>
-      <x:c r="D27" s="38"/>
-      <x:c r="E27" s="38"/>
-      <x:c r="F27" s="38"/>
-      <x:c r="G27" s="38"/>
-      <x:c r="H27" s="38"/>
-      <x:c r="I27" s="38"/>
-      <x:c r="J27" s="38"/>
-      <x:c r="K27" s="38"/>
-      <x:c r="L27" s="38"/>
-      <x:c r="M27" s="38"/>
-      <x:c r="N27" s="38"/>
-      <x:c r="O27" s="38"/>
+      <x:c r="B27" s="38" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="C27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" s="38" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="G27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="38" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="K27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="38" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="O27" s="39" t="n">
+        <x:f>SUM(B27:N27)</x:f>
+        <x:v>100000</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
         <x:v>Utilities</x:v>
       </x:c>
-      <x:c r="B28" s="38"/>
-      <x:c r="C28" s="38"/>
-      <x:c r="D28" s="38"/>
-      <x:c r="E28" s="38"/>
-      <x:c r="F28" s="38"/>
-      <x:c r="G28" s="38"/>
-      <x:c r="H28" s="38"/>
-      <x:c r="I28" s="38"/>
-      <x:c r="J28" s="38"/>
-      <x:c r="K28" s="38"/>
-      <x:c r="L28" s="38"/>
-      <x:c r="M28" s="38"/>
-      <x:c r="N28" s="38"/>
-      <x:c r="O28" s="38"/>
+      <x:c r="B28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="G28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="K28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="O28" s="39" t="n">
+        <x:f>SUM(B28:N28)</x:f>
+        <x:v>12000</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
         <x:v>Insurance</x:v>
       </x:c>
-      <x:c r="B29" s="38"/>
-      <x:c r="C29" s="38"/>
-      <x:c r="D29" s="38"/>
-      <x:c r="E29" s="38"/>
-      <x:c r="F29" s="38"/>
-      <x:c r="G29" s="38"/>
-      <x:c r="H29" s="38"/>
-      <x:c r="I29" s="38"/>
-      <x:c r="J29" s="38"/>
-      <x:c r="K29" s="38"/>
-      <x:c r="L29" s="38"/>
-      <x:c r="M29" s="38"/>
-      <x:c r="N29" s="38"/>
-      <x:c r="O29" s="38"/>
+      <x:c r="B29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="D29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" s="39" t="n">
+        <x:f>SUM(B29:N29)</x:f>
+        <x:v>6000</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
         <x:v>Software and subscriptions</x:v>
       </x:c>
-      <x:c r="B30" s="38"/>
-      <x:c r="C30" s="38"/>
-      <x:c r="D30" s="38"/>
-      <x:c r="E30" s="38"/>
-      <x:c r="F30" s="38"/>
-      <x:c r="G30" s="38"/>
-      <x:c r="H30" s="38"/>
-      <x:c r="I30" s="38"/>
-      <x:c r="J30" s="38"/>
-      <x:c r="K30" s="38"/>
-      <x:c r="L30" s="38"/>
-      <x:c r="M30" s="38"/>
-      <x:c r="N30" s="38"/>
-      <x:c r="O30" s="38"/>
+      <x:c r="B30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="C30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="D30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="E30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="F30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="G30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="H30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="I30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="J30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="K30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="L30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="M30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="N30" s="38" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="O30" s="39" t="n">
+        <x:f>SUM(B30:N30)</x:f>
+        <x:v>39000</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
         <x:v>Marketing</x:v>
       </x:c>
-      <x:c r="B31" s="38"/>
-      <x:c r="C31" s="38"/>
-      <x:c r="D31" s="38"/>
-      <x:c r="E31" s="38"/>
-      <x:c r="F31" s="38"/>
-      <x:c r="G31" s="38"/>
-      <x:c r="H31" s="38"/>
-      <x:c r="I31" s="38"/>
-      <x:c r="J31" s="38"/>
-      <x:c r="K31" s="38"/>
-      <x:c r="L31" s="38"/>
-      <x:c r="M31" s="38"/>
-      <x:c r="N31" s="38"/>
-      <x:c r="O31" s="38"/>
+      <x:c r="B31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="C31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="D31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="E31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="F31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="G31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="H31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="I31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="J31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="K31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="L31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="M31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="N31" s="38" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="O31" s="39" t="n">
+        <x:f>SUM(B31:N31)</x:f>
+        <x:v>78000</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
         <x:v>Professional services</x:v>
       </x:c>
-      <x:c r="B32" s="38"/>
-      <x:c r="C32" s="38"/>
-      <x:c r="D32" s="38"/>
-      <x:c r="E32" s="38"/>
-      <x:c r="F32" s="38"/>
-      <x:c r="G32" s="38"/>
-      <x:c r="H32" s="38"/>
-      <x:c r="I32" s="38"/>
-      <x:c r="J32" s="38"/>
-      <x:c r="K32" s="38"/>
-      <x:c r="L32" s="38"/>
-      <x:c r="M32" s="38"/>
-      <x:c r="N32" s="38"/>
-      <x:c r="O32" s="38"/>
+      <x:c r="B32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="38" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="E32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="38" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="I32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="38" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="M32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O32" s="39" t="n">
+        <x:f>SUM(B32:N32)</x:f>
+        <x:v>24000</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
         <x:v>Freight, vehicles and travel</x:v>
       </x:c>
-      <x:c r="B33" s="38"/>
-      <x:c r="C33" s="38"/>
-      <x:c r="D33" s="38"/>
-      <x:c r="E33" s="38"/>
-      <x:c r="F33" s="38"/>
-      <x:c r="G33" s="38"/>
-      <x:c r="H33" s="38"/>
-      <x:c r="I33" s="38"/>
-      <x:c r="J33" s="38"/>
-      <x:c r="K33" s="38"/>
-      <x:c r="L33" s="38"/>
-      <x:c r="M33" s="38"/>
-      <x:c r="N33" s="38"/>
-      <x:c r="O33" s="38"/>
+      <x:c r="B33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="C33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="G33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="H33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="I33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="J33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="L33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="M33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="N33" s="38" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="O33" s="39" t="n">
+        <x:f>SUM(B33:N33)</x:f>
+        <x:v>130000</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
         <x:v>GST / BAS payments</x:v>
       </x:c>
-      <x:c r="B34" s="38"/>
-      <x:c r="C34" s="38"/>
-      <x:c r="D34" s="38"/>
-      <x:c r="E34" s="38"/>
-      <x:c r="F34" s="38"/>
-      <x:c r="G34" s="38"/>
-      <x:c r="H34" s="38"/>
-      <x:c r="I34" s="38"/>
-      <x:c r="J34" s="38"/>
-      <x:c r="K34" s="38"/>
-      <x:c r="L34" s="38"/>
-      <x:c r="M34" s="38"/>
-      <x:c r="N34" s="38"/>
-      <x:c r="O34" s="38"/>
+      <x:c r="B34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="38" t="n">
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="K34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34" s="39" t="n">
+        <x:f>SUM(B34:N34)</x:f>
+        <x:v>45000</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
         <x:v>PAYG income tax instalments</x:v>
       </x:c>
-      <x:c r="B35" s="38"/>
-      <x:c r="C35" s="38"/>
-      <x:c r="D35" s="38"/>
-      <x:c r="E35" s="38"/>
-      <x:c r="F35" s="38"/>
-      <x:c r="G35" s="38"/>
-      <x:c r="H35" s="38"/>
-      <x:c r="I35" s="38"/>
-      <x:c r="J35" s="38"/>
-      <x:c r="K35" s="38"/>
-      <x:c r="L35" s="38"/>
-      <x:c r="M35" s="38"/>
-      <x:c r="N35" s="38"/>
-      <x:c r="O35" s="38"/>
+      <x:c r="B35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="38" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+      <x:c r="K35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O35" s="39" t="n">
+        <x:f>SUM(B35:N35)</x:f>
+        <x:v>18000</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
         <x:v>FBT / other tax</x:v>
       </x:c>
-      <x:c r="B36" s="38"/>
-      <x:c r="C36" s="38"/>
-      <x:c r="D36" s="38"/>
-      <x:c r="E36" s="38"/>
-      <x:c r="F36" s="38"/>
-      <x:c r="G36" s="38"/>
-      <x:c r="H36" s="38"/>
-      <x:c r="I36" s="38"/>
-      <x:c r="J36" s="38"/>
-      <x:c r="K36" s="38"/>
-      <x:c r="L36" s="38"/>
-      <x:c r="M36" s="38"/>
-      <x:c r="N36" s="38"/>
-      <x:c r="O36" s="38"/>
+      <x:c r="B36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" s="39" t="n">
+        <x:f>SUM(B36:N36)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
         <x:v>Interest and bank fees</x:v>
       </x:c>
-      <x:c r="B37" s="38"/>
-      <x:c r="C37" s="38"/>
-      <x:c r="D37" s="38"/>
-      <x:c r="E37" s="38"/>
-      <x:c r="F37" s="38"/>
-      <x:c r="G37" s="38"/>
-      <x:c r="H37" s="38"/>
-      <x:c r="I37" s="38"/>
-      <x:c r="J37" s="38"/>
-      <x:c r="K37" s="38"/>
-      <x:c r="L37" s="38"/>
-      <x:c r="M37" s="38"/>
-      <x:c r="N37" s="38"/>
-      <x:c r="O37" s="38"/>
+      <x:c r="B37" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="C37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="G37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="K37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N37" s="38" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="O37" s="39" t="n">
+        <x:f>SUM(B37:N37)</x:f>
+        <x:v>16000</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
         <x:v>Loan principal</x:v>
       </x:c>
-      <x:c r="B38" s="38"/>
-      <x:c r="C38" s="38"/>
-      <x:c r="D38" s="38"/>
-      <x:c r="E38" s="38"/>
-      <x:c r="F38" s="38"/>
-      <x:c r="G38" s="38"/>
-      <x:c r="H38" s="38"/>
-      <x:c r="I38" s="38"/>
-      <x:c r="J38" s="38"/>
-      <x:c r="K38" s="38"/>
-      <x:c r="L38" s="38"/>
-      <x:c r="M38" s="38"/>
-      <x:c r="N38" s="38"/>
-      <x:c r="O38" s="38"/>
+      <x:c r="B38" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="C38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F38" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="G38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="K38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N38" s="38" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="O38" s="39" t="n">
+        <x:f>SUM(B38:N38)</x:f>
+        <x:v>48000</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
         <x:v>Capital expenditure</x:v>
       </x:c>
-      <x:c r="B39" s="38"/>
-      <x:c r="C39" s="38"/>
-      <x:c r="D39" s="38"/>
-      <x:c r="E39" s="38"/>
-      <x:c r="F39" s="38"/>
-      <x:c r="G39" s="38"/>
-      <x:c r="H39" s="38"/>
-      <x:c r="I39" s="38"/>
-      <x:c r="J39" s="38"/>
-      <x:c r="K39" s="38"/>
-      <x:c r="L39" s="38"/>
-      <x:c r="M39" s="38"/>
-      <x:c r="N39" s="38"/>
-      <x:c r="O39" s="38"/>
+      <x:c r="B39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G39" s="38" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="H39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39" s="38" t="n">
+        <x:v>40000</x:v>
+      </x:c>
+      <x:c r="L39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" s="39" t="n">
+        <x:f>SUM(B39:N39)</x:f>
+        <x:v>65000</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
         <x:v>Dividends / distributions</x:v>
       </x:c>
-      <x:c r="B40" s="38"/>
-      <x:c r="C40" s="38"/>
-      <x:c r="D40" s="38"/>
-      <x:c r="E40" s="38"/>
-      <x:c r="F40" s="38"/>
-      <x:c r="G40" s="38"/>
-      <x:c r="H40" s="38"/>
-      <x:c r="I40" s="38"/>
-      <x:c r="J40" s="38"/>
-      <x:c r="K40" s="38"/>
-      <x:c r="L40" s="38"/>
-      <x:c r="M40" s="38"/>
-      <x:c r="N40" s="38"/>
-      <x:c r="O40" s="38"/>
+      <x:c r="B40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" s="39" t="n">
+        <x:f>SUM(B40:N40)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B41" s="38"/>
-      <x:c r="C41" s="38"/>
-      <x:c r="D41" s="38"/>
-      <x:c r="E41" s="38"/>
-      <x:c r="F41" s="38"/>
-      <x:c r="G41" s="38"/>
-      <x:c r="H41" s="38"/>
-      <x:c r="I41" s="38"/>
-      <x:c r="J41" s="38"/>
-      <x:c r="K41" s="38"/>
-      <x:c r="L41" s="38"/>
-      <x:c r="M41" s="38"/>
-      <x:c r="N41" s="38"/>
-      <x:c r="O41" s="38"/>
+      <x:c r="B41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="C41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="D41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="E41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="F41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="G41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="H41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="I41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="J41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="K41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="L41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="N41" s="38" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="O41" s="39" t="n">
+        <x:f>SUM(B41:N41)</x:f>
+        <x:v>65000</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
         <x:v>Scenario payment adjustment</x:v>
       </x:c>
-      <x:c r="B42" s="38"/>
-      <x:c r="C42" s="38"/>
-      <x:c r="D42" s="38"/>
-      <x:c r="E42" s="38"/>
-      <x:c r="F42" s="38"/>
-      <x:c r="G42" s="38"/>
-      <x:c r="H42" s="38"/>
-      <x:c r="I42" s="38"/>
-      <x:c r="J42" s="38"/>
-      <x:c r="K42" s="38"/>
-      <x:c r="L42" s="38"/>
-      <x:c r="M42" s="38"/>
-      <x:c r="N42" s="38"/>
-      <x:c r="O42" s="38"/>
+      <x:c r="B42" s="42" t="n">
+        <x:f>IF(B$7="Actual",0,SUM(B22,B31,B33,B41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C42" s="42" t="n">
+        <x:f>IF(C$7="Actual",0,SUM(C22,C31,C33,C41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="42" t="n">
+        <x:f>IF(D$7="Actual",0,SUM(D22,D31,D33,D41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E42" s="42" t="n">
+        <x:f>IF(E$7="Actual",0,SUM(E22,E31,E33,E41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F42" s="42" t="n">
+        <x:f>IF(F$7="Actual",0,SUM(F22,F31,F33,F41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G42" s="42" t="n">
+        <x:f>IF(G$7="Actual",0,SUM(G22,G31,G33,G41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="42" t="n">
+        <x:f>IF(H$7="Actual",0,SUM(H22,H31,H33,H41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="42" t="n">
+        <x:f>IF(I$7="Actual",0,SUM(I22,I31,I33,I41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J42" s="42" t="n">
+        <x:f>IF(J$7="Actual",0,SUM(J22,J31,J33,J41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K42" s="42" t="n">
+        <x:f>IF(K$7="Actual",0,SUM(K22,K31,K33,K41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L42" s="42" t="n">
+        <x:f>IF(L$7="Actual",0,SUM(L22,L31,L33,L41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M42" s="42" t="n">
+        <x:f>IF(M$7="Actual",0,SUM(M22,M31,M33,M41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N42" s="42" t="n">
+        <x:f>IF(N$7="Actual",0,SUM(N22,N31,N33,N41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O42" s="39" t="n">
+        <x:f>SUM(B42:N42)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="37" t="str">
         <x:v>Total cash payments</x:v>
       </x:c>
-      <x:c r="B43" s="39"/>
-      <x:c r="C43" s="39"/>
-      <x:c r="D43" s="39"/>
-      <x:c r="E43" s="39"/>
-      <x:c r="F43" s="39"/>
-      <x:c r="G43" s="39"/>
-      <x:c r="H43" s="39"/>
-      <x:c r="I43" s="39"/>
-      <x:c r="J43" s="39"/>
-      <x:c r="K43" s="39"/>
-      <x:c r="L43" s="39"/>
-      <x:c r="M43" s="39"/>
-      <x:c r="N43" s="39"/>
-      <x:c r="O43" s="39"/>
+      <x:c r="B43" s="43" t="n">
+        <x:f>SUM(B22:B42)</x:f>
+        <x:v>212000</x:v>
+      </x:c>
+      <x:c r="C43" s="43" t="n">
+        <x:f>SUM(C22:C42)</x:f>
+        <x:v>178000</x:v>
+      </x:c>
+      <x:c r="D43" s="43" t="n">
+        <x:f>SUM(D22:D42)</x:f>
+        <x:v>182000</x:v>
+      </x:c>
+      <x:c r="E43" s="43" t="n">
+        <x:f>SUM(E22:E42)</x:f>
+        <x:v>179000</x:v>
+      </x:c>
+      <x:c r="F43" s="43" t="n">
+        <x:f>SUM(F22:F42)</x:f>
+        <x:v>232000</x:v>
+      </x:c>
+      <x:c r="G43" s="43" t="n">
+        <x:f>SUM(G22:G42)</x:f>
+        <x:v>209000</x:v>
+      </x:c>
+      <x:c r="H43" s="43" t="n">
+        <x:f>SUM(H22:H42)</x:f>
+        <x:v>197000</x:v>
+      </x:c>
+      <x:c r="I43" s="43" t="n">
+        <x:f>SUM(I22:I42)</x:f>
+        <x:v>192000</x:v>
+      </x:c>
+      <x:c r="J43" s="43" t="n">
+        <x:f>SUM(J22:J42)</x:f>
+        <x:v>307000</x:v>
+      </x:c>
+      <x:c r="K43" s="43" t="n">
+        <x:f>SUM(K22:K42)</x:f>
+        <x:v>229000</x:v>
+      </x:c>
+      <x:c r="L43" s="43" t="n">
+        <x:f>SUM(L22:L42)</x:f>
+        <x:v>192000</x:v>
+      </x:c>
+      <x:c r="M43" s="43" t="n">
+        <x:f>SUM(M22:M42)</x:f>
+        <x:v>179000</x:v>
+      </x:c>
+      <x:c r="N43" s="43" t="n">
+        <x:f>SUM(N22:N42)</x:f>
+        <x:v>219000</x:v>
+      </x:c>
+      <x:c r="O43" s="40" t="n">
+        <x:f>SUM(B43:N43)</x:f>
+        <x:v>2707000</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="B44" s="38"/>
-      <x:c r="C44" s="38"/>
-      <x:c r="D44" s="38"/>
-      <x:c r="E44" s="38"/>
-      <x:c r="F44" s="38"/>
-      <x:c r="G44" s="38"/>
-      <x:c r="H44" s="38"/>
-      <x:c r="I44" s="38"/>
-      <x:c r="J44" s="38"/>
-      <x:c r="K44" s="38"/>
-      <x:c r="L44" s="38"/>
-      <x:c r="M44" s="38"/>
-      <x:c r="N44" s="38"/>
-      <x:c r="O44" s="38"/>
+      <x:c r="B44" s="39"/>
+      <x:c r="C44" s="39"/>
+      <x:c r="D44" s="39"/>
+      <x:c r="E44" s="39"/>
+      <x:c r="F44" s="39"/>
+      <x:c r="G44" s="39"/>
+      <x:c r="H44" s="39"/>
+      <x:c r="I44" s="39"/>
+      <x:c r="J44" s="39"/>
+      <x:c r="K44" s="39"/>
+      <x:c r="L44" s="39"/>
+      <x:c r="M44" s="39"/>
+      <x:c r="N44" s="39"/>
+      <x:c r="O44" s="39"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="14" t="str">
         <x:v>CASH POSITION</x:v>
       </x:c>
-      <x:c r="B45" s="40"/>
-      <x:c r="C45" s="40"/>
-      <x:c r="D45" s="40"/>
-      <x:c r="E45" s="40"/>
-      <x:c r="F45" s="40"/>
-      <x:c r="G45" s="40"/>
-      <x:c r="H45" s="40"/>
-      <x:c r="I45" s="40"/>
-      <x:c r="J45" s="40"/>
-      <x:c r="K45" s="40"/>
-      <x:c r="L45" s="40"/>
-      <x:c r="M45" s="40"/>
-      <x:c r="N45" s="40"/>
-      <x:c r="O45" s="40"/>
+      <x:c r="B45" s="41"/>
+      <x:c r="C45" s="41"/>
+      <x:c r="D45" s="41"/>
+      <x:c r="E45" s="41"/>
+      <x:c r="F45" s="41"/>
+      <x:c r="G45" s="41"/>
+      <x:c r="H45" s="41"/>
+      <x:c r="I45" s="41"/>
+      <x:c r="J45" s="41"/>
+      <x:c r="K45" s="41"/>
+      <x:c r="L45" s="41"/>
+      <x:c r="M45" s="41"/>
+      <x:c r="N45" s="41"/>
+      <x:c r="O45" s="41"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
         <x:v>Opening cash balance</x:v>
       </x:c>
-      <x:c r="B46" s="38"/>
-      <x:c r="C46" s="38"/>
-      <x:c r="D46" s="38"/>
-      <x:c r="E46" s="38"/>
-      <x:c r="F46" s="38"/>
-      <x:c r="G46" s="38"/>
-      <x:c r="H46" s="38"/>
-      <x:c r="I46" s="38"/>
-      <x:c r="J46" s="38"/>
-      <x:c r="K46" s="38"/>
-      <x:c r="L46" s="38"/>
-      <x:c r="M46" s="38"/>
-      <x:c r="N46" s="38"/>
-      <x:c r="O46" s="38"/>
+      <x:c r="B46" s="44" t="n">
+        <x:f>'Assumptions'!$B$10</x:f>
+        <x:v>400000</x:v>
+      </x:c>
+      <x:c r="C46" s="44" t="n">
+        <x:f>B48</x:f>
+        <x:v>358000</x:v>
+      </x:c>
+      <x:c r="D46" s="44" t="n">
+        <x:f>C48</x:f>
+        <x:v>349000</x:v>
+      </x:c>
+      <x:c r="E46" s="44" t="n">
+        <x:f>D48</x:f>
+        <x:v>325000</x:v>
+      </x:c>
+      <x:c r="F46" s="44" t="n">
+        <x:f>E48</x:f>
+        <x:v>293000</x:v>
+      </x:c>
+      <x:c r="G46" s="44" t="n">
+        <x:f>F48</x:f>
+        <x:v>201000</x:v>
+      </x:c>
+      <x:c r="H46" s="44" t="n">
+        <x:f>G48</x:f>
+        <x:v>133000</x:v>
+      </x:c>
+      <x:c r="I46" s="44" t="n">
+        <x:f>H48</x:f>
+        <x:v>217000</x:v>
+      </x:c>
+      <x:c r="J46" s="44" t="n">
+        <x:f>I48</x:f>
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="K46" s="44" t="n">
+        <x:f>J48</x:f>
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="L46" s="44" t="n">
+        <x:f>K48</x:f>
+        <x:v>137000</x:v>
+      </x:c>
+      <x:c r="M46" s="44" t="n">
+        <x:f>L48</x:f>
+        <x:v>99000</x:v>
+      </x:c>
+      <x:c r="N46" s="44" t="n">
+        <x:f>M48</x:f>
+        <x:v>82000</x:v>
+      </x:c>
+      <x:c r="O46" s="39" t="n">
+        <x:f>N46</x:f>
+        <x:v>82000</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
         <x:v>Net cash movement</x:v>
       </x:c>
-      <x:c r="B47" s="38"/>
-      <x:c r="C47" s="38"/>
-      <x:c r="D47" s="38"/>
-      <x:c r="E47" s="38"/>
-      <x:c r="F47" s="38"/>
-      <x:c r="G47" s="38"/>
-      <x:c r="H47" s="38"/>
-      <x:c r="I47" s="38"/>
-      <x:c r="J47" s="38"/>
-      <x:c r="K47" s="38"/>
-      <x:c r="L47" s="38"/>
-      <x:c r="M47" s="38"/>
-      <x:c r="N47" s="38"/>
-      <x:c r="O47" s="38"/>
+      <x:c r="B47" s="42" t="n">
+        <x:f>B19-B43</x:f>
+        <x:v>-42000</x:v>
+      </x:c>
+      <x:c r="C47" s="42" t="n">
+        <x:f>C19-C43</x:f>
+        <x:v>-9000</x:v>
+      </x:c>
+      <x:c r="D47" s="42" t="n">
+        <x:f>D19-D43</x:f>
+        <x:v>-24000</x:v>
+      </x:c>
+      <x:c r="E47" s="42" t="n">
+        <x:f>E19-E43</x:f>
+        <x:v>-32000</x:v>
+      </x:c>
+      <x:c r="F47" s="42" t="n">
+        <x:f>F19-F43</x:f>
+        <x:v>-92000</x:v>
+      </x:c>
+      <x:c r="G47" s="42" t="n">
+        <x:f>G19-G43</x:f>
+        <x:v>-68000</x:v>
+      </x:c>
+      <x:c r="H47" s="42" t="n">
+        <x:f>H19-H43</x:f>
+        <x:v>84000</x:v>
+      </x:c>
+      <x:c r="I47" s="42" t="n">
+        <x:f>I19-I43</x:f>
+        <x:v>-57000</x:v>
+      </x:c>
+      <x:c r="J47" s="42" t="n">
+        <x:f>J19-J43</x:f>
+        <x:v>-43000</x:v>
+      </x:c>
+      <x:c r="K47" s="42" t="n">
+        <x:f>K19-K43</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="L47" s="42" t="n">
+        <x:f>L19-L43</x:f>
+        <x:v>-38000</x:v>
+      </x:c>
+      <x:c r="M47" s="42" t="n">
+        <x:f>M19-M43</x:f>
+        <x:v>-17000</x:v>
+      </x:c>
+      <x:c r="N47" s="42" t="n">
+        <x:f>N19-N43</x:f>
+        <x:v>-51000</x:v>
+      </x:c>
+      <x:c r="O47" s="39" t="n">
+        <x:f>N47</x:f>
+        <x:v>-51000</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="37" t="str">
         <x:v>Closing cash balance</x:v>
       </x:c>
-      <x:c r="B48" s="39"/>
-      <x:c r="C48" s="39"/>
-      <x:c r="D48" s="39"/>
-      <x:c r="E48" s="39"/>
-      <x:c r="F48" s="39"/>
-      <x:c r="G48" s="39"/>
-      <x:c r="H48" s="39"/>
-      <x:c r="I48" s="39"/>
-      <x:c r="J48" s="39"/>
-      <x:c r="K48" s="39"/>
-      <x:c r="L48" s="39"/>
-      <x:c r="M48" s="39"/>
-      <x:c r="N48" s="39"/>
-      <x:c r="O48" s="39"/>
+      <x:c r="B48" s="43" t="n">
+        <x:f>B46+B47</x:f>
+        <x:v>358000</x:v>
+      </x:c>
+      <x:c r="C48" s="43" t="n">
+        <x:f>C46+C47</x:f>
+        <x:v>349000</x:v>
+      </x:c>
+      <x:c r="D48" s="43" t="n">
+        <x:f>D46+D47</x:f>
+        <x:v>325000</x:v>
+      </x:c>
+      <x:c r="E48" s="43" t="n">
+        <x:f>E46+E47</x:f>
+        <x:v>293000</x:v>
+      </x:c>
+      <x:c r="F48" s="43" t="n">
+        <x:f>F46+F47</x:f>
+        <x:v>201000</x:v>
+      </x:c>
+      <x:c r="G48" s="43" t="n">
+        <x:f>G46+G47</x:f>
+        <x:v>133000</x:v>
+      </x:c>
+      <x:c r="H48" s="43" t="n">
+        <x:f>H46+H47</x:f>
+        <x:v>217000</x:v>
+      </x:c>
+      <x:c r="I48" s="43" t="n">
+        <x:f>I46+I47</x:f>
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="J48" s="43" t="n">
+        <x:f>J46+J47</x:f>
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="K48" s="43" t="n">
+        <x:f>K46+K47</x:f>
+        <x:v>137000</x:v>
+      </x:c>
+      <x:c r="L48" s="43" t="n">
+        <x:f>L46+L47</x:f>
+        <x:v>99000</x:v>
+      </x:c>
+      <x:c r="M48" s="43" t="n">
+        <x:f>M46+M47</x:f>
+        <x:v>82000</x:v>
+      </x:c>
+      <x:c r="N48" s="43" t="n">
+        <x:f>N46+N47</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="O48" s="40" t="n">
+        <x:f>N48</x:f>
+        <x:v>31000</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B49" s="38"/>
-      <x:c r="C49" s="38"/>
-      <x:c r="D49" s="38"/>
-      <x:c r="E49" s="38"/>
-      <x:c r="F49" s="38"/>
-      <x:c r="G49" s="38"/>
-      <x:c r="H49" s="38"/>
-      <x:c r="I49" s="38"/>
-      <x:c r="J49" s="38"/>
-      <x:c r="K49" s="38"/>
-      <x:c r="L49" s="38"/>
-      <x:c r="M49" s="38"/>
-      <x:c r="N49" s="38"/>
-      <x:c r="O49" s="38"/>
+      <x:c r="B49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="C49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="D49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="E49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="F49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="G49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="H49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="I49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="J49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="K49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="L49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="M49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="N49" s="44" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="O49" s="39" t="n">
+        <x:f>N49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="37" t="str">
         <x:v>Headroom / (gap)</x:v>
       </x:c>
-      <x:c r="B50" s="39"/>
-      <x:c r="C50" s="39"/>
-      <x:c r="D50" s="39"/>
-      <x:c r="E50" s="39"/>
-      <x:c r="F50" s="39"/>
-      <x:c r="G50" s="39"/>
-      <x:c r="H50" s="39"/>
-      <x:c r="I50" s="39"/>
-      <x:c r="J50" s="39"/>
-      <x:c r="K50" s="39"/>
-      <x:c r="L50" s="39"/>
-      <x:c r="M50" s="39"/>
-      <x:c r="N50" s="39"/>
-      <x:c r="O50" s="39"/>
+      <x:c r="B50" s="43" t="n">
+        <x:f>B48-B49</x:f>
+        <x:v>258000</x:v>
+      </x:c>
+      <x:c r="C50" s="43" t="n">
+        <x:f>C48-C49</x:f>
+        <x:v>249000</x:v>
+      </x:c>
+      <x:c r="D50" s="43" t="n">
+        <x:f>D48-D49</x:f>
+        <x:v>225000</x:v>
+      </x:c>
+      <x:c r="E50" s="43" t="n">
+        <x:f>E48-E49</x:f>
+        <x:v>193000</x:v>
+      </x:c>
+      <x:c r="F50" s="43" t="n">
+        <x:f>F48-F49</x:f>
+        <x:v>101000</x:v>
+      </x:c>
+      <x:c r="G50" s="43" t="n">
+        <x:f>G48-G49</x:f>
+        <x:v>33000</x:v>
+      </x:c>
+      <x:c r="H50" s="43" t="n">
+        <x:f>H48-H49</x:f>
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="I50" s="43" t="n">
+        <x:f>I48-I49</x:f>
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="J50" s="43" t="n">
+        <x:f>J48-J49</x:f>
+        <x:v>17000</x:v>
+      </x:c>
+      <x:c r="K50" s="43" t="n">
+        <x:f>K48-K49</x:f>
+        <x:v>37000</x:v>
+      </x:c>
+      <x:c r="L50" s="43" t="n">
+        <x:f>L48-L49</x:f>
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="M50" s="43" t="n">
+        <x:f>M48-M49</x:f>
+        <x:v>-18000</x:v>
+      </x:c>
+      <x:c r="N50" s="43" t="n">
+        <x:f>N48-N49</x:f>
+        <x:v>-69000</x:v>
+      </x:c>
+      <x:c r="O50" s="40" t="n">
+        <x:f>N50</x:f>
+        <x:v>-69000</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
         <x:v>Liquidity status</x:v>
+      </x:c>
+      <x:c r="B51" s="17" t="str">
+        <x:f>IF(B48&lt;B49,"BELOW BUFFER",IF(B48&lt;=B49*1.25,"WATCH","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="C51" s="17" t="str">
+        <x:f>IF(C48&lt;C49,"BELOW BUFFER",IF(C48&lt;=C49*1.25,"WATCH","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="D51" s="17" t="str">
+        <x:f>IF(D48&lt;D49,"BELOW BUFFER",IF(D48&lt;=D49*1.25,"WATCH","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E51" s="17" t="str">
+        <x:f>IF(E48&lt;E49,"BELOW BUFFER",IF(E48&lt;=E49*1.25,"WATCH","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="F51" s="17" t="str">
+        <x:f>IF(F48&lt;F49,"BELOW BUFFER",IF(F48&lt;=F49*1.25,"WATCH","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G51" s="17" t="str">
+        <x:f>IF(G48&lt;G49,"BELOW BUFFER",IF(G48&lt;=G49*1.25,"WATCH","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="H51" s="17" t="str">
+        <x:f>IF(H48&lt;H49,"BELOW BUFFER",IF(H48&lt;=H49*1.25,"WATCH","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="I51" s="17" t="str">
+        <x:f>IF(I48&lt;I49,"BELOW BUFFER",IF(I48&lt;=I49*1.25,"WATCH","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="J51" s="17" t="str">
+        <x:f>IF(J48&lt;J49,"BELOW BUFFER",IF(J48&lt;=J49*1.25,"WATCH","OK"))</x:f>
+        <x:v>WATCH</x:v>
+      </x:c>
+      <x:c r="K51" s="17" t="str">
+        <x:f>IF(K48&lt;K49,"BELOW BUFFER",IF(K48&lt;=K49*1.25,"WATCH","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="L51" s="17" t="str">
+        <x:f>IF(L48&lt;L49,"BELOW BUFFER",IF(L48&lt;=L49*1.25,"WATCH","OK"))</x:f>
+        <x:v>BELOW BUFFER</x:v>
+      </x:c>
+      <x:c r="M51" s="17" t="str">
+        <x:f>IF(M48&lt;M49,"BELOW BUFFER",IF(M48&lt;=M49*1.25,"WATCH","OK"))</x:f>
+        <x:v>BELOW BUFFER</x:v>
+      </x:c>
+      <x:c r="N51" s="17" t="str">
+        <x:f>IF(N48&lt;N49,"BELOW BUFFER",IF(N48&lt;=N49*1.25,"WATCH","OK"))</x:f>
+        <x:v>BELOW BUFFER</x:v>
+      </x:c>
+      <x:c r="O51" t="str">
+        <x:f>N51</x:f>
+        <x:v>BELOW BUFFER</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2038,7 +3446,19 @@
     <x:mergeCell ref="A1:O1"/>
     <x:mergeCell ref="A2:O2"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="B51:N51">
+    <x:cfRule type="expression" dxfId="0" priority="1">
+      <x:formula>B51="BELOW BUFFER"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="1" priority="2">
+      <x:formula>B51="WATCH"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="2" priority="3">
+      <x:formula>B51="OK"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4c825058279492f"/>
 </x:worksheet>
 </file>
 
@@ -2048,18 +3468,13 @@
   <x:cols>
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -2074,15 +3489,10 @@
       <x:c r="G1" s="4"/>
       <x:c r="H1" s="4"/>
       <x:c r="I1" s="4"/>
-      <x:c r="J1" s="4"/>
-      <x:c r="K1" s="4"/>
-      <x:c r="L1" s="4"/>
-      <x:c r="M1" s="4"/>
-      <x:c r="N1" s="4"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Forecast accuracy review. Actuals, commentary, owners and actions are added with the forecast engine.</x:v>
+        <x:v>Record actual closing cash, actions and ownership each week. Variance remains blank until an actual is entered.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -2092,126 +3502,319 @@
       <x:c r="G2" s="8"/>
       <x:c r="H2" s="8"/>
       <x:c r="I2" s="8"/>
-      <x:c r="J2" s="8"/>
-      <x:c r="K2" s="8"/>
-      <x:c r="L2" s="8"/>
-      <x:c r="M2" s="8"/>
-      <x:c r="N2" s="8"/>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
       <x:c r="A5" s="28" t="str">
         <x:v>Week</x:v>
       </x:c>
       <x:c r="B5" s="28" t="str">
-        <x:v>Week commencing</x:v>
+        <x:v>Week ending</x:v>
       </x:c>
       <x:c r="C5" s="28" t="str">
-        <x:v>Week ending</x:v>
+        <x:v>Forecast closing cash</x:v>
       </x:c>
       <x:c r="D5" s="28" t="str">
-        <x:v>Forecast receipts</x:v>
+        <x:v>Actual closing cash</x:v>
       </x:c>
       <x:c r="E5" s="28" t="str">
-        <x:v>Actual receipts</x:v>
+        <x:v>Variance</x:v>
       </x:c>
       <x:c r="F5" s="28" t="str">
-        <x:v>Receipt variance</x:v>
+        <x:v>Rolling forecast note</x:v>
       </x:c>
       <x:c r="G5" s="28" t="str">
-        <x:v>Forecast payments</x:v>
+        <x:v>Owner</x:v>
       </x:c>
       <x:c r="H5" s="28" t="str">
-        <x:v>Actual payments</x:v>
+        <x:v>Action</x:v>
       </x:c>
       <x:c r="I5" s="28" t="str">
-        <x:v>Payment variance</x:v>
-      </x:c>
-      <x:c r="J5" s="28" t="str">
-        <x:v>Forecast closing cash</x:v>
-      </x:c>
-      <x:c r="K5" s="28" t="str">
-        <x:v>Actual closing cash</x:v>
-      </x:c>
-      <x:c r="L5" s="28" t="str">
-        <x:v>Cash variance</x:v>
-      </x:c>
-      <x:c r="M5" s="28" t="str">
-        <x:v>Owner</x:v>
-      </x:c>
-      <x:c r="N5" s="28" t="str">
-        <x:v>Commentary / action</x:v>
+        <x:v>Status</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="B6" s="45" t="n">
+        <x:f>'13-Week Forecast'!B$6</x:f>
+        <x:v>46271</x:v>
+      </x:c>
+      <x:c r="C6" s="44" t="n">
+        <x:f>'13-Week Forecast'!B$48</x:f>
+        <x:v>358000</x:v>
+      </x:c>
+      <x:c r="D6" s="38"/>
+      <x:c r="E6" s="42" t="str">
+        <x:f>IF(D6="","",D6-C6)</x:f>
+      </x:c>
+      <x:c r="F6" s="16"/>
+      <x:c r="G6" s="16"/>
+      <x:c r="H6" s="16"/>
+      <x:c r="I6" s="16"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="B7" s="45" t="n">
+        <x:f>'13-Week Forecast'!C$6</x:f>
+        <x:v>46278</x:v>
+      </x:c>
+      <x:c r="C7" s="44" t="n">
+        <x:f>'13-Week Forecast'!C$48</x:f>
+        <x:v>349000</x:v>
+      </x:c>
+      <x:c r="D7" s="38"/>
+      <x:c r="E7" s="42" t="str">
+        <x:f>IF(D7="","",D7-C7)</x:f>
+      </x:c>
+      <x:c r="F7" s="16"/>
+      <x:c r="G7" s="16"/>
+      <x:c r="H7" s="16"/>
+      <x:c r="I7" s="16"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="n">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="B8" s="45" t="n">
+        <x:f>'13-Week Forecast'!D$6</x:f>
+        <x:v>46285</x:v>
+      </x:c>
+      <x:c r="C8" s="44" t="n">
+        <x:f>'13-Week Forecast'!D$48</x:f>
+        <x:v>325000</x:v>
+      </x:c>
+      <x:c r="D8" s="38"/>
+      <x:c r="E8" s="42" t="str">
+        <x:f>IF(D8="","",D8-C8)</x:f>
+      </x:c>
+      <x:c r="F8" s="16"/>
+      <x:c r="G8" s="16"/>
+      <x:c r="H8" s="16"/>
+      <x:c r="I8" s="16"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="B9" s="45" t="n">
+        <x:f>'13-Week Forecast'!E$6</x:f>
+        <x:v>46292</x:v>
+      </x:c>
+      <x:c r="C9" s="44" t="n">
+        <x:f>'13-Week Forecast'!E$48</x:f>
+        <x:v>293000</x:v>
+      </x:c>
+      <x:c r="D9" s="38"/>
+      <x:c r="E9" s="42" t="str">
+        <x:f>IF(D9="","",D9-C9)</x:f>
+      </x:c>
+      <x:c r="F9" s="16"/>
+      <x:c r="G9" s="16"/>
+      <x:c r="H9" s="16"/>
+      <x:c r="I9" s="16"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="n">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="B10" s="45" t="n">
+        <x:f>'13-Week Forecast'!F$6</x:f>
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="C10" s="44" t="n">
+        <x:f>'13-Week Forecast'!F$48</x:f>
+        <x:v>201000</x:v>
+      </x:c>
+      <x:c r="D10" s="38"/>
+      <x:c r="E10" s="42" t="str">
+        <x:f>IF(D10="","",D10-C10)</x:f>
+      </x:c>
+      <x:c r="F10" s="16"/>
+      <x:c r="G10" s="16"/>
+      <x:c r="H10" s="16"/>
+      <x:c r="I10" s="16"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="n">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="B11" s="45" t="n">
+        <x:f>'13-Week Forecast'!G$6</x:f>
+        <x:v>46306</x:v>
+      </x:c>
+      <x:c r="C11" s="44" t="n">
+        <x:f>'13-Week Forecast'!G$48</x:f>
+        <x:v>133000</x:v>
+      </x:c>
+      <x:c r="D11" s="38"/>
+      <x:c r="E11" s="42" t="str">
+        <x:f>IF(D11="","",D11-C11)</x:f>
+      </x:c>
+      <x:c r="F11" s="16"/>
+      <x:c r="G11" s="16"/>
+      <x:c r="H11" s="16"/>
+      <x:c r="I11" s="16"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="n">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="B12" s="45" t="n">
+        <x:f>'13-Week Forecast'!H$6</x:f>
+        <x:v>46313</x:v>
+      </x:c>
+      <x:c r="C12" s="44" t="n">
+        <x:f>'13-Week Forecast'!H$48</x:f>
+        <x:v>217000</x:v>
+      </x:c>
+      <x:c r="D12" s="38"/>
+      <x:c r="E12" s="42" t="str">
+        <x:f>IF(D12="","",D12-C12)</x:f>
+      </x:c>
+      <x:c r="F12" s="16"/>
+      <x:c r="G12" s="16"/>
+      <x:c r="H12" s="16"/>
+      <x:c r="I12" s="16"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="n">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="B13" s="45" t="n">
+        <x:f>'13-Week Forecast'!I$6</x:f>
+        <x:v>46320</x:v>
+      </x:c>
+      <x:c r="C13" s="44" t="n">
+        <x:f>'13-Week Forecast'!I$48</x:f>
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="D13" s="38"/>
+      <x:c r="E13" s="42" t="str">
+        <x:f>IF(D13="","",D13-C13)</x:f>
+      </x:c>
+      <x:c r="F13" s="16"/>
+      <x:c r="G13" s="16"/>
+      <x:c r="H13" s="16"/>
+      <x:c r="I13" s="16"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="n">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="B14" s="45" t="n">
+        <x:f>'13-Week Forecast'!J$6</x:f>
+        <x:v>46327</x:v>
+      </x:c>
+      <x:c r="C14" s="44" t="n">
+        <x:f>'13-Week Forecast'!J$48</x:f>
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="D14" s="38"/>
+      <x:c r="E14" s="42" t="str">
+        <x:f>IF(D14="","",D14-C14)</x:f>
+      </x:c>
+      <x:c r="F14" s="16"/>
+      <x:c r="G14" s="16"/>
+      <x:c r="H14" s="16"/>
+      <x:c r="I14" s="16"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="n">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="B15" s="45" t="n">
+        <x:f>'13-Week Forecast'!K$6</x:f>
+        <x:v>46334</x:v>
+      </x:c>
+      <x:c r="C15" s="44" t="n">
+        <x:f>'13-Week Forecast'!K$48</x:f>
+        <x:v>137000</x:v>
+      </x:c>
+      <x:c r="D15" s="38"/>
+      <x:c r="E15" s="42" t="str">
+        <x:f>IF(D15="","",D15-C15)</x:f>
+      </x:c>
+      <x:c r="F15" s="16"/>
+      <x:c r="G15" s="16"/>
+      <x:c r="H15" s="16"/>
+      <x:c r="I15" s="16"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="n">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="B16" s="45" t="n">
+        <x:f>'13-Week Forecast'!L$6</x:f>
+        <x:v>46341</x:v>
+      </x:c>
+      <x:c r="C16" s="44" t="n">
+        <x:f>'13-Week Forecast'!L$48</x:f>
+        <x:v>99000</x:v>
+      </x:c>
+      <x:c r="D16" s="38"/>
+      <x:c r="E16" s="42" t="str">
+        <x:f>IF(D16="","",D16-C16)</x:f>
+      </x:c>
+      <x:c r="F16" s="16"/>
+      <x:c r="G16" s="16"/>
+      <x:c r="H16" s="16"/>
+      <x:c r="I16" s="16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="n">
         <x:v>12</x:v>
       </x:c>
+      <x:c r="B17" s="45" t="n">
+        <x:f>'13-Week Forecast'!M$6</x:f>
+        <x:v>46348</x:v>
+      </x:c>
+      <x:c r="C17" s="44" t="n">
+        <x:f>'13-Week Forecast'!M$48</x:f>
+        <x:v>82000</x:v>
+      </x:c>
+      <x:c r="D17" s="38"/>
+      <x:c r="E17" s="42" t="str">
+        <x:f>IF(D17="","",D17-C17)</x:f>
+      </x:c>
+      <x:c r="F17" s="16"/>
+      <x:c r="G17" s="16"/>
+      <x:c r="H17" s="16"/>
+      <x:c r="I17" s="16"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="n">
         <x:v>13</x:v>
       </x:c>
+      <x:c r="B18" s="45" t="n">
+        <x:f>'13-Week Forecast'!N$6</x:f>
+        <x:v>46355</x:v>
+      </x:c>
+      <x:c r="C18" s="44" t="n">
+        <x:f>'13-Week Forecast'!N$48</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="D18" s="38"/>
+      <x:c r="E18" s="42" t="str">
+        <x:f>IF(D18="","",D18-C18)</x:f>
+      </x:c>
+      <x:c r="F18" s="16"/>
+      <x:c r="G18" s="16"/>
+      <x:c r="H18" s="16"/>
+      <x:c r="I18" s="16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:N1"/>
-    <x:mergeCell ref="A2:N2"/>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A2:I2"/>
   </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I6:I18">
+      <x:formula1>"Open,In progress,Complete"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -2281,16 +3884,16 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="41" t="str">
+      <x:c r="A6" s="47" t="str">
         <x:v>MODEL STATUS: prepared for formula-driven integrity checks</x:v>
       </x:c>
-      <x:c r="B6" s="41"/>
-      <x:c r="C6" s="41"/>
-      <x:c r="D6" s="41"/>
-      <x:c r="E6" s="41"/>
-      <x:c r="F6" s="41"/>
-      <x:c r="G6" s="41"/>
-      <x:c r="H6" s="41"/>
+      <x:c r="B6" s="47"/>
+      <x:c r="C6" s="47"/>
+      <x:c r="D6" s="47"/>
+      <x:c r="E6" s="47"/>
+      <x:c r="F6" s="47"/>
+      <x:c r="G6" s="47"/>
+      <x:c r="H6" s="47"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
@@ -2313,22 +3916,22 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="43" t="str">
+      <x:c r="A11" s="49" t="str">
         <x:v>Statutory dates and classifications require confirmation for your entity, reporting cycle and agent arrangements.</x:v>
       </x:c>
-      <x:c r="B11" s="43"/>
-      <x:c r="C11" s="43"/>
-      <x:c r="D11" s="43"/>
-      <x:c r="E11" s="43"/>
-      <x:c r="F11" s="43"/>
+      <x:c r="B11" s="49"/>
+      <x:c r="C11" s="49"/>
+      <x:c r="D11" s="49"/>
+      <x:c r="E11" s="49"/>
+      <x:c r="F11" s="49"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="43"/>
-      <x:c r="B12" s="43"/>
-      <x:c r="C12" s="43"/>
-      <x:c r="D12" s="43"/>
-      <x:c r="E12" s="43"/>
-      <x:c r="F12" s="43"/>
+      <x:c r="A12" s="49"/>
+      <x:c r="B12" s="49"/>
+      <x:c r="C12" s="49"/>
+      <x:c r="D12" s="49"/>
+      <x:c r="E12" s="49"/>
+      <x:c r="F12" s="49"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R163eef40803243ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R36a323b4bd524392"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R55e1d91aef2144cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R3a5216492bc244a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R6e15a48bc1404b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R40686c5f31a64d21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R3e53cff34fb3404f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Ra5d9b34592c44d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R02020629f966456b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R9a98a45bf36543f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R4948e13d0d524a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R758b2f2e63254719"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -20,10 +20,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={E28899D8-E974-D419-CBA0-A3EAED613B76}</x:author>
-    <x:author>tc={17D25D66-7DB0-58F0-CE5E-E2EB2DCDA11F}</x:author>
-    <x:author>tc={6D6F189E-71DD-5AB0-A5B5-8089484B0A68}</x:author>
-    <x:author>tc={E870F557-83E1-4DD3-E5B6-7E48039B894E}</x:author>
+    <x:author>tc={75DE23CE-A935-BFA0-98B0-716B59A88F03}</x:author>
+    <x:author>tc={2E978C1C-A140-5B1A-8A5A-5E0CB2034512}</x:author>
+    <x:author>tc={AB4F57D7-7C83-4B35-BCE8-54405C1832F3}</x:author>
+    <x:author>tc={F00DFA9B-E108-DC3D-4302-EF7DC2B4B9ED}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -32,7 +32,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Scenario receipt adjustment applies the selected scenario only to customer receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</x:t>
+    Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -335,7 +335,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}"/>
+  <xltc:person displayName="User" id="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}"/>
 </xltc:personList>
 </file>
 
@@ -532,16 +532,16 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-26T13:22:07.159" personId="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}" id="{E28899D8-E974-D419-CBA0-A3EAED613B76}">
-    <xltc:text>Scenario receipt adjustment applies the selected scenario only to customer receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
+  <xltc:threadedComment ref="B18" dT="2026-08-26T13:28:35.39" personId="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}" id="{75DE23CE-A935-BFA0-98B0-716B59A88F03}">
+    <xltc:text>Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B42" dT="2026-08-26T13:22:07.159" personId="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}" id="{17D25D66-7DB0-58F0-CE5E-E2EB2DCDA11F}">
+  <xltc:threadedComment ref="B42" dT="2026-08-26T13:28:35.391" personId="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}" id="{2E978C1C-A140-5B1A-8A5A-5E0CB2034512}">
     <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B34" dT="2026-08-26T13:22:07.159" personId="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}" id="{6D6F189E-71DD-5AB0-A5B5-8089484B0A68}">
+  <xltc:threadedComment ref="B34" dT="2026-08-26T13:28:35.391" personId="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}" id="{AB4F57D7-7C83-4B35-BCE8-54405C1832F3}">
     <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B35" dT="2026-08-26T13:22:07.159" personId="{D4E71844-CD76-4BEE-BAA9-387BBDF1B51C}" id="{E870F557-83E1-4DD3-E5B6-7E48039B894E}">
+  <xltc:threadedComment ref="B35" dT="2026-08-26T13:28:35.391" personId="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}" id="{F00DFA9B-E108-DC3D-4302-EF7DC2B4B9ED}">
     <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -3458,7 +3458,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4c825058279492f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5578828a6574f7e"/>
 </x:worksheet>
 </file>
 

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R3e53cff34fb3404f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Ra5d9b34592c44d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R02020629f966456b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R9a98a45bf36543f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R4948e13d0d524a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R758b2f2e63254719"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R6365591222b34de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R63a198b070c74297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R3c5e1c3bfbe94158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rbc435d3534754d31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="Raf7ca443aec049a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R6513339d280742ea"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -20,10 +20,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={75DE23CE-A935-BFA0-98B0-716B59A88F03}</x:author>
-    <x:author>tc={2E978C1C-A140-5B1A-8A5A-5E0CB2034512}</x:author>
-    <x:author>tc={AB4F57D7-7C83-4B35-BCE8-54405C1832F3}</x:author>
-    <x:author>tc={F00DFA9B-E108-DC3D-4302-EF7DC2B4B9ED}</x:author>
+    <x:author>tc={98FAA047-B01D-5348-2BF1-D894601FC806}</x:author>
+    <x:author>tc={BE1B932E-612F-4047-F56F-9CDCA82CBB32}</x:author>
+    <x:author>tc={B3C5A793-7724-FDA4-8C59-D102B1FE2C65}</x:author>
+    <x:author>tc={736F7184-3EC3-9C52-7FDB-69574353E070}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -76,10 +76,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="dd mmm yyyy"/>
     <x:numFmt numFmtId="201" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0);-"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
+    <x:numFmt numFmtId="203" formatCode="#,##0;[Red](#,##0);-"/>
   </x:numFmts>
   <x:fonts count="14">
     <x:font>
@@ -135,6 +136,12 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FF04001F"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FF2B2733"/>
       <x:name val="Aptos"/>
@@ -151,14 +158,8 @@
       <x:color rgb="FF000000"/>
       <x:name val="Aptos"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF008000"/>
-      <x:name val="Aptos"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -207,6 +208,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFB1AFAD"/>
       </x:patternFill>
     </x:fill>
@@ -222,7 +228,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="50">
+  <x:cellXfs count="63">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -266,25 +272,60 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -295,7 +336,29 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="18">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:b/>
@@ -329,13 +392,562 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5C2D91"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDED9E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5C2D91"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDED9E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5C2D91"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDED9E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
 
+<file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="900"/>
+              <a:t>Closing cash vs minimum buffer (AUD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Closing cash</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard'!$P$5:$P$17</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard'!$Q$5:$Q$17</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0;[Red]("$"#,##0);-</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Minimum buffer</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard'!$P$5:$P$17</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard'!$R$5:$R$17</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0;[Red]("$"#,##0);-</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="$#,##0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="900"/>
+              <a:t>Weekly receipts vs payments (AUD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Total cash receipts</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard'!$P$22:$P$34</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard'!$Q$22:$Q$34</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0;[Red]("$"#,##0);-</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Total cash payments</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Dashboard'!$P$22:$P$34</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Dashboard'!$R$22:$R$34</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0;[Red]("$"#,##0);-</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="$#,##0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref5028a0a2fe4326"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8ac1622332704bbf"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}"/>
+  <xltc:person displayName="User" id="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}"/>
 </xltc:personList>
 </file>
 
@@ -532,16 +1144,16 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-26T13:28:35.39" personId="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}" id="{75DE23CE-A935-BFA0-98B0-716B59A88F03}">
+  <xltc:threadedComment ref="B18" dT="2026-08-26T13:42:51.005" personId="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}" id="{98FAA047-B01D-5348-2BF1-D894601FC806}">
     <xltc:text>Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B42" dT="2026-08-26T13:28:35.391" personId="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}" id="{2E978C1C-A140-5B1A-8A5A-5E0CB2034512}">
+  <xltc:threadedComment ref="B42" dT="2026-08-26T13:42:51.005" personId="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}" id="{BE1B932E-612F-4047-F56F-9CDCA82CBB32}">
     <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B34" dT="2026-08-26T13:28:35.391" personId="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}" id="{AB4F57D7-7C83-4B35-BCE8-54405C1832F3}">
+  <xltc:threadedComment ref="B34" dT="2026-08-26T13:42:51.005" personId="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}" id="{B3C5A793-7724-FDA4-8C59-D102B1FE2C65}">
     <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B35" dT="2026-08-26T13:28:35.391" personId="{D45FE37B-BE5A-40E8-9106-C3ABA403F384}" id="{F00DFA9B-E108-DC3D-4302-EF7DC2B4B9ED}">
+  <xltc:threadedComment ref="B35" dT="2026-08-26T13:42:51.005" personId="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}" id="{736F7184-3EC3-9C52-7FDB-69574353E070}">
     <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -808,14 +1420,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
@@ -823,6 +1435,9 @@
     <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -843,10 +1458,13 @@
       <x:c r="M1" s="4"/>
       <x:c r="N1" s="4"/>
       <x:c r="O1" s="4"/>
+      <x:c r="P1" s="4"/>
+      <x:c r="Q1" s="4"/>
+      <x:c r="R1" s="4"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Management view. Formula-linked KPI cards, charts and liquidity outlook are added in the dashboard build step.</x:v>
+        <x:v>Management view. Formula-linked KPI cards, weekly liquidity outlook and native charts.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -862,6 +1480,9 @@
       <x:c r="M2" s="8"/>
       <x:c r="N2" s="8"/>
       <x:c r="O2" s="8"/>
+      <x:c r="P2" s="8"/>
+      <x:c r="Q2" s="8"/>
+      <x:c r="R2" s="8"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="25" t="str">
@@ -881,68 +1502,766 @@
       <x:c r="M4" s="25"/>
       <x:c r="N4" s="25"/>
       <x:c r="O4" s="25"/>
+      <x:c r="P4" s="14" t="str">
+        <x:v>Week ending</x:v>
+      </x:c>
+      <x:c r="Q4" s="14" t="str">
+        <x:v>Closing cash</x:v>
+      </x:c>
+      <x:c r="R4" s="14" t="str">
+        <x:v>Minimum buffer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="P5" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
+        <x:v>06 Sep</x:v>
+      </x:c>
+      <x:c r="Q5" s="36" t="n">
+        <x:f>'13-Week Forecast'!B$48</x:f>
+        <x:v>358000</x:v>
+      </x:c>
+      <x:c r="R5" s="36" t="n">
+        <x:f>'13-Week Forecast'!B$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="28" t="str">
+      <x:c r="A6" s="30" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B6" s="28" t="str">
-        <x:v>Week 13 closing cash</x:v>
-      </x:c>
-      <x:c r="C6" s="28" t="str">
+      <x:c r="B6" s="30" t="str">
+        <x:v>Opening cash</x:v>
+      </x:c>
+      <x:c r="C6" s="30" t="str">
         <x:v>Lowest closing cash</x:v>
       </x:c>
-      <x:c r="D6" s="28" t="str">
-        <x:v>Minimum buffer</x:v>
-      </x:c>
-      <x:c r="E6" s="28" t="str">
+      <x:c r="D6" s="30" t="str">
         <x:v>Minimum headroom</x:v>
       </x:c>
-      <x:c r="F6" s="28" t="str">
+      <x:c r="E6" s="30" t="str">
         <x:v>Weeks below buffer</x:v>
       </x:c>
+      <x:c r="F6" s="30" t="str">
+        <x:v>Week of lowest cash</x:v>
+      </x:c>
+      <x:c r="G6" s="30" t="str">
+        <x:v>MODEL STATUS</x:v>
+      </x:c>
+      <x:c r="H6" s="30" t="str">
+        <x:v>LIQUIDITY STATUS</x:v>
+      </x:c>
+      <x:c r="P6" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
+        <x:v>13 Sep</x:v>
+      </x:c>
+      <x:c r="Q6" s="36" t="n">
+        <x:f>'13-Week Forecast'!C$48</x:f>
+        <x:v>349000</x:v>
+      </x:c>
+      <x:c r="R6" s="36" t="n">
+        <x:f>'13-Week Forecast'!C$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>Linked in build 3</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>Linked in build 3</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Linked in build 3</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>Linked in build 3</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>Linked in build 3</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>Linked in build 3</x:v>
+      <x:c r="A7" s="33" t="str">
+        <x:f>'Assumptions'!$B$12</x:f>
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="B7" s="34" t="n">
+        <x:f>'Assumptions'!$B$10</x:f>
+        <x:v>400000</x:v>
+      </x:c>
+      <x:c r="C7" s="34" t="n">
+        <x:f>MIN('13-Week Forecast'!$B$48:$N$48)</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="D7" s="34" t="n">
+        <x:f>MIN('13-Week Forecast'!$B$50:$N$50)</x:f>
+        <x:v>-69000</x:v>
+      </x:c>
+      <x:c r="E7" s="33" t="n">
+        <x:f>COUNTIF('13-Week Forecast'!$B$50:$N$50,"&lt;0")</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F7" s="35" t="n">
+        <x:f>INDEX('13-Week Forecast'!$B$6:$N$6,1,MATCH(C7,'13-Week Forecast'!$B$48:$N$48,0))</x:f>
+        <x:v>46355</x:v>
+      </x:c>
+      <x:c r="G7" s="33" t="str">
+        <x:f>'Checks &amp; Sources'!$B$4</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="H7" s="33" t="str">
+        <x:f>'Checks &amp; Sources'!$E$4</x:f>
+        <x:v>ACTION REQUIRED</x:v>
+      </x:c>
+      <x:c r="P7" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
+        <x:v>20 Sep</x:v>
+      </x:c>
+      <x:c r="Q7" s="36" t="n">
+        <x:f>'13-Week Forecast'!D$48</x:f>
+        <x:v>325000</x:v>
+      </x:c>
+      <x:c r="R7" s="36" t="n">
+        <x:f>'13-Week Forecast'!D$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="P8" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
+        <x:v>27 Sep</x:v>
+      </x:c>
+      <x:c r="Q8" s="36" t="n">
+        <x:f>'13-Week Forecast'!E$48</x:f>
+        <x:v>293000</x:v>
+      </x:c>
+      <x:c r="R8" s="36" t="n">
+        <x:f>'13-Week Forecast'!E$49</x:f>
+        <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="14" t="str">
-        <x:v>Liquidity outlook</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
+      <x:c r="P9" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
+        <x:v>04 Oct</x:v>
+      </x:c>
+      <x:c r="Q9" s="36" t="n">
+        <x:f>'13-Week Forecast'!F$48</x:f>
+        <x:v>201000</x:v>
+      </x:c>
+      <x:c r="R9" s="36" t="n">
+        <x:f>'13-Week Forecast'!F$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="P10" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
+        <x:v>11 Oct</x:v>
+      </x:c>
+      <x:c r="Q10" s="36" t="n">
+        <x:f>'13-Week Forecast'!G$48</x:f>
+        <x:v>133000</x:v>
+      </x:c>
+      <x:c r="R10" s="36" t="n">
+        <x:f>'13-Week Forecast'!G$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>Week</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="str">
+      <x:c r="C11" s="14" t="str">
         <x:v>Closing cash</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="str">
+      <x:c r="D11" s="14" t="str">
         <x:v>Headroom</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>Liquidity status</x:v>
+      </x:c>
+      <x:c r="P11" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
+        <x:v>18 Oct</x:v>
+      </x:c>
+      <x:c r="Q11" s="36" t="n">
+        <x:f>'13-Week Forecast'!H$48</x:f>
+        <x:v>217000</x:v>
+      </x:c>
+      <x:c r="R11" s="36" t="n">
+        <x:f>'13-Week Forecast'!H$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B12" s="37" t="n">
+        <x:f>'13-Week Forecast'!B$6</x:f>
+        <x:v>46271</x:v>
+      </x:c>
+      <x:c r="C12" s="38" t="n">
+        <x:f>'13-Week Forecast'!B$48</x:f>
+        <x:v>358000</x:v>
+      </x:c>
+      <x:c r="D12" s="38" t="n">
+        <x:f>'13-Week Forecast'!B$50</x:f>
+        <x:v>258000</x:v>
+      </x:c>
+      <x:c r="E12" s="12" t="str">
+        <x:f>'13-Week Forecast'!B$51</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="P12" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
+        <x:v>25 Oct</x:v>
+      </x:c>
+      <x:c r="Q12" s="36" t="n">
+        <x:f>'13-Week Forecast'!I$48</x:f>
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="R12" s="36" t="n">
+        <x:f>'13-Week Forecast'!I$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B13" s="37" t="n">
+        <x:f>'13-Week Forecast'!C$6</x:f>
+        <x:v>46278</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="n">
+        <x:f>'13-Week Forecast'!C$48</x:f>
+        <x:v>349000</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
+        <x:f>'13-Week Forecast'!C$50</x:f>
+        <x:v>249000</x:v>
+      </x:c>
+      <x:c r="E13" s="12" t="str">
+        <x:f>'13-Week Forecast'!C$51</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="P13" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
+        <x:v>01 Nov</x:v>
+      </x:c>
+      <x:c r="Q13" s="36" t="n">
+        <x:f>'13-Week Forecast'!J$48</x:f>
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="R13" s="36" t="n">
+        <x:f>'13-Week Forecast'!J$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="37" t="n">
+        <x:f>'13-Week Forecast'!D$6</x:f>
+        <x:v>46285</x:v>
+      </x:c>
+      <x:c r="C14" s="38" t="n">
+        <x:f>'13-Week Forecast'!D$48</x:f>
+        <x:v>325000</x:v>
+      </x:c>
+      <x:c r="D14" s="38" t="n">
+        <x:f>'13-Week Forecast'!D$50</x:f>
+        <x:v>225000</x:v>
+      </x:c>
+      <x:c r="E14" s="12" t="str">
+        <x:f>'13-Week Forecast'!D$51</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="P14" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
+        <x:v>08 Nov</x:v>
+      </x:c>
+      <x:c r="Q14" s="36" t="n">
+        <x:f>'13-Week Forecast'!K$48</x:f>
+        <x:v>137000</x:v>
+      </x:c>
+      <x:c r="R14" s="36" t="n">
+        <x:f>'13-Week Forecast'!K$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B15" s="37" t="n">
+        <x:f>'13-Week Forecast'!E$6</x:f>
+        <x:v>46292</x:v>
+      </x:c>
+      <x:c r="C15" s="38" t="n">
+        <x:f>'13-Week Forecast'!E$48</x:f>
+        <x:v>293000</x:v>
+      </x:c>
+      <x:c r="D15" s="38" t="n">
+        <x:f>'13-Week Forecast'!E$50</x:f>
+        <x:v>193000</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="str">
+        <x:f>'13-Week Forecast'!E$51</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="P15" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
+        <x:v>15 Nov</x:v>
+      </x:c>
+      <x:c r="Q15" s="36" t="n">
+        <x:f>'13-Week Forecast'!L$48</x:f>
+        <x:v>99000</x:v>
+      </x:c>
+      <x:c r="R15" s="36" t="n">
+        <x:f>'13-Week Forecast'!L$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B16" s="37" t="n">
+        <x:f>'13-Week Forecast'!F$6</x:f>
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="C16" s="38" t="n">
+        <x:f>'13-Week Forecast'!F$48</x:f>
+        <x:v>201000</x:v>
+      </x:c>
+      <x:c r="D16" s="38" t="n">
+        <x:f>'13-Week Forecast'!F$50</x:f>
+        <x:v>101000</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="str">
+        <x:f>'13-Week Forecast'!F$51</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="P16" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
+        <x:v>22 Nov</x:v>
+      </x:c>
+      <x:c r="Q16" s="36" t="n">
+        <x:f>'13-Week Forecast'!M$48</x:f>
+        <x:v>82000</x:v>
+      </x:c>
+      <x:c r="R16" s="36" t="n">
+        <x:f>'13-Week Forecast'!M$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B17" s="37" t="n">
+        <x:f>'13-Week Forecast'!G$6</x:f>
+        <x:v>46306</x:v>
+      </x:c>
+      <x:c r="C17" s="38" t="n">
+        <x:f>'13-Week Forecast'!G$48</x:f>
+        <x:v>133000</x:v>
+      </x:c>
+      <x:c r="D17" s="38" t="n">
+        <x:f>'13-Week Forecast'!G$50</x:f>
+        <x:v>33000</x:v>
+      </x:c>
+      <x:c r="E17" s="12" t="str">
+        <x:f>'13-Week Forecast'!G$51</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="P17" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
+        <x:v>29 Nov</x:v>
+      </x:c>
+      <x:c r="Q17" s="36" t="n">
+        <x:f>'13-Week Forecast'!N$48</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="R17" s="36" t="n">
+        <x:f>'13-Week Forecast'!N$49</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B18" s="37" t="n">
+        <x:f>'13-Week Forecast'!H$6</x:f>
+        <x:v>46313</x:v>
+      </x:c>
+      <x:c r="C18" s="38" t="n">
+        <x:f>'13-Week Forecast'!H$48</x:f>
+        <x:v>217000</x:v>
+      </x:c>
+      <x:c r="D18" s="38" t="n">
+        <x:f>'13-Week Forecast'!H$50</x:f>
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="E18" s="12" t="str">
+        <x:f>'13-Week Forecast'!H$51</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B19" s="37" t="n">
+        <x:f>'13-Week Forecast'!I$6</x:f>
+        <x:v>46320</x:v>
+      </x:c>
+      <x:c r="C19" s="38" t="n">
+        <x:f>'13-Week Forecast'!I$48</x:f>
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="D19" s="38" t="n">
+        <x:f>'13-Week Forecast'!I$50</x:f>
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="E19" s="12" t="str">
+        <x:f>'13-Week Forecast'!I$51</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B20" s="37" t="n">
+        <x:f>'13-Week Forecast'!J$6</x:f>
+        <x:v>46327</x:v>
+      </x:c>
+      <x:c r="C20" s="38" t="n">
+        <x:f>'13-Week Forecast'!J$48</x:f>
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="D20" s="38" t="n">
+        <x:f>'13-Week Forecast'!J$50</x:f>
+        <x:v>17000</x:v>
+      </x:c>
+      <x:c r="E20" s="12" t="str">
+        <x:f>'13-Week Forecast'!J$51</x:f>
+        <x:v>WATCH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B21" s="37" t="n">
+        <x:f>'13-Week Forecast'!K$6</x:f>
+        <x:v>46334</x:v>
+      </x:c>
+      <x:c r="C21" s="38" t="n">
+        <x:f>'13-Week Forecast'!K$48</x:f>
+        <x:v>137000</x:v>
+      </x:c>
+      <x:c r="D21" s="38" t="n">
+        <x:f>'13-Week Forecast'!K$50</x:f>
+        <x:v>37000</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="str">
+        <x:f>'13-Week Forecast'!K$51</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="P21" s="14" t="str">
+        <x:v>Week ending</x:v>
+      </x:c>
+      <x:c r="Q21" s="14" t="str">
+        <x:v>Total cash receipts</x:v>
+      </x:c>
+      <x:c r="R21" s="14" t="str">
+        <x:v>Total cash payments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B22" s="37" t="n">
+        <x:f>'13-Week Forecast'!L$6</x:f>
+        <x:v>46341</x:v>
+      </x:c>
+      <x:c r="C22" s="38" t="n">
+        <x:f>'13-Week Forecast'!L$48</x:f>
+        <x:v>99000</x:v>
+      </x:c>
+      <x:c r="D22" s="38" t="n">
+        <x:f>'13-Week Forecast'!L$50</x:f>
+        <x:v>-1000</x:v>
+      </x:c>
+      <x:c r="E22" s="12" t="str">
+        <x:f>'13-Week Forecast'!L$51</x:f>
+        <x:v>BELOW BUFFER</x:v>
+      </x:c>
+      <x:c r="P22" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
+        <x:v>06 Sep</x:v>
+      </x:c>
+      <x:c r="Q22" s="36" t="n">
+        <x:f>'13-Week Forecast'!B$19</x:f>
+        <x:v>170000</x:v>
+      </x:c>
+      <x:c r="R22" s="36" t="n">
+        <x:f>'13-Week Forecast'!B$43</x:f>
+        <x:v>212000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B23" s="37" t="n">
+        <x:f>'13-Week Forecast'!M$6</x:f>
+        <x:v>46348</x:v>
+      </x:c>
+      <x:c r="C23" s="38" t="n">
+        <x:f>'13-Week Forecast'!M$48</x:f>
+        <x:v>82000</x:v>
+      </x:c>
+      <x:c r="D23" s="38" t="n">
+        <x:f>'13-Week Forecast'!M$50</x:f>
+        <x:v>-18000</x:v>
+      </x:c>
+      <x:c r="E23" s="12" t="str">
+        <x:f>'13-Week Forecast'!M$51</x:f>
+        <x:v>BELOW BUFFER</x:v>
+      </x:c>
+      <x:c r="P23" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
+        <x:v>13 Sep</x:v>
+      </x:c>
+      <x:c r="Q23" s="36" t="n">
+        <x:f>'13-Week Forecast'!C$19</x:f>
+        <x:v>169000</x:v>
+      </x:c>
+      <x:c r="R23" s="36" t="n">
+        <x:f>'13-Week Forecast'!C$43</x:f>
+        <x:v>178000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="n">
+        <x:f>ROW()-11</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B24" s="37" t="n">
+        <x:f>'13-Week Forecast'!N$6</x:f>
+        <x:v>46355</x:v>
+      </x:c>
+      <x:c r="C24" s="38" t="n">
+        <x:f>'13-Week Forecast'!N$48</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="D24" s="38" t="n">
+        <x:f>'13-Week Forecast'!N$50</x:f>
+        <x:v>-69000</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="str">
+        <x:f>'13-Week Forecast'!N$51</x:f>
+        <x:v>BELOW BUFFER</x:v>
+      </x:c>
+      <x:c r="P24" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
+        <x:v>20 Sep</x:v>
+      </x:c>
+      <x:c r="Q24" s="36" t="n">
+        <x:f>'13-Week Forecast'!D$19</x:f>
+        <x:v>158000</x:v>
+      </x:c>
+      <x:c r="R24" s="36" t="n">
+        <x:f>'13-Week Forecast'!D$43</x:f>
+        <x:v>182000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="P25" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
+        <x:v>27 Sep</x:v>
+      </x:c>
+      <x:c r="Q25" s="36" t="n">
+        <x:f>'13-Week Forecast'!E$19</x:f>
+        <x:v>147000</x:v>
+      </x:c>
+      <x:c r="R25" s="36" t="n">
+        <x:f>'13-Week Forecast'!E$43</x:f>
+        <x:v>179000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="P26" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
+        <x:v>04 Oct</x:v>
+      </x:c>
+      <x:c r="Q26" s="36" t="n">
+        <x:f>'13-Week Forecast'!F$19</x:f>
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="R26" s="36" t="n">
+        <x:f>'13-Week Forecast'!F$43</x:f>
+        <x:v>232000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="P27" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
+        <x:v>11 Oct</x:v>
+      </x:c>
+      <x:c r="Q27" s="36" t="n">
+        <x:f>'13-Week Forecast'!G$19</x:f>
+        <x:v>141000</x:v>
+      </x:c>
+      <x:c r="R27" s="36" t="n">
+        <x:f>'13-Week Forecast'!G$43</x:f>
+        <x:v>209000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="P28" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
+        <x:v>18 Oct</x:v>
+      </x:c>
+      <x:c r="Q28" s="36" t="n">
+        <x:f>'13-Week Forecast'!H$19</x:f>
+        <x:v>281000</x:v>
+      </x:c>
+      <x:c r="R28" s="36" t="n">
+        <x:f>'13-Week Forecast'!H$43</x:f>
+        <x:v>197000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="P29" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
+        <x:v>25 Oct</x:v>
+      </x:c>
+      <x:c r="Q29" s="36" t="n">
+        <x:f>'13-Week Forecast'!I$19</x:f>
+        <x:v>135000</x:v>
+      </x:c>
+      <x:c r="R29" s="36" t="n">
+        <x:f>'13-Week Forecast'!I$43</x:f>
+        <x:v>192000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="P30" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
+        <x:v>01 Nov</x:v>
+      </x:c>
+      <x:c r="Q30" s="36" t="n">
+        <x:f>'13-Week Forecast'!J$19</x:f>
+        <x:v>264000</x:v>
+      </x:c>
+      <x:c r="R30" s="36" t="n">
+        <x:f>'13-Week Forecast'!J$43</x:f>
+        <x:v>307000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="P31" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
+        <x:v>08 Nov</x:v>
+      </x:c>
+      <x:c r="Q31" s="36" t="n">
+        <x:f>'13-Week Forecast'!K$19</x:f>
+        <x:v>249000</x:v>
+      </x:c>
+      <x:c r="R31" s="36" t="n">
+        <x:f>'13-Week Forecast'!K$43</x:f>
+        <x:v>229000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="P32" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
+        <x:v>15 Nov</x:v>
+      </x:c>
+      <x:c r="Q32" s="36" t="n">
+        <x:f>'13-Week Forecast'!L$19</x:f>
+        <x:v>154000</x:v>
+      </x:c>
+      <x:c r="R32" s="36" t="n">
+        <x:f>'13-Week Forecast'!L$43</x:f>
+        <x:v>192000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="P33" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
+        <x:v>22 Nov</x:v>
+      </x:c>
+      <x:c r="Q33" s="36" t="n">
+        <x:f>'13-Week Forecast'!M$19</x:f>
+        <x:v>162000</x:v>
+      </x:c>
+      <x:c r="R33" s="36" t="n">
+        <x:f>'13-Week Forecast'!M$43</x:f>
+        <x:v>179000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="P34" s="11" t="str">
+        <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
+        <x:v>29 Nov</x:v>
+      </x:c>
+      <x:c r="Q34" s="36" t="n">
+        <x:f>'13-Week Forecast'!N$19</x:f>
+        <x:v>168000</x:v>
+      </x:c>
+      <x:c r="R34" s="36" t="n">
+        <x:f>'13-Week Forecast'!N$43</x:f>
+        <x:v>219000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:O1"/>
-    <x:mergeCell ref="A2:O2"/>
-    <x:mergeCell ref="A4:O4"/>
+    <x:mergeCell ref="A1:R1"/>
+    <x:mergeCell ref="A2:R2"/>
+    <x:mergeCell ref="A4:R4"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="G7:G7">
+    <x:cfRule type="expression" dxfId="0" priority="1">
+      <x:formula>G7="PASS"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="1" priority="2">
+      <x:formula>G7="FAIL"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="H7:H7">
+    <x:cfRule type="expression" dxfId="2" priority="3">
+      <x:formula>H7="ACTION REQUIRED"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="3" priority="4">
+      <x:formula>H7="WATCH"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="4" priority="5">
+      <x:formula>H7="HEALTHY"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="E12:E24">
+    <x:cfRule type="expression" dxfId="5" priority="6">
+      <x:formula>E12="BELOW BUFFER"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="6" priority="7">
+      <x:formula>E12="WATCH"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="7" priority="8">
+      <x:formula>E12="OK"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fce3a2c5625401a"/>
 </x:worksheet>
 </file>
 
@@ -990,7 +2309,7 @@
       <x:c r="A5" t="str">
         <x:v>Business name</x:v>
       </x:c>
-      <x:c r="B5" s="29" t="str">
+      <x:c r="B5" s="40" t="str">
         <x:v>Illustrative Australian business</x:v>
       </x:c>
     </x:row>
@@ -998,7 +2317,7 @@
       <x:c r="A6" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="B6" s="29" t="str">
+      <x:c r="B6" s="40" t="str">
         <x:v>AUD</x:v>
       </x:c>
     </x:row>
@@ -1006,7 +2325,7 @@
       <x:c r="A7" t="str">
         <x:v>Units</x:v>
       </x:c>
-      <x:c r="B7" s="29" t="str">
+      <x:c r="B7" s="40" t="str">
         <x:v>Whole dollars</x:v>
       </x:c>
     </x:row>
@@ -1014,7 +2333,7 @@
       <x:c r="A8" t="str">
         <x:v>Forecast start date</x:v>
       </x:c>
-      <x:c r="B8" s="30" t="n">
+      <x:c r="B8" s="41" t="n">
         <x:v>46265</x:v>
       </x:c>
     </x:row>
@@ -1022,7 +2341,7 @@
       <x:c r="A9" t="str">
         <x:v>As-at date</x:v>
       </x:c>
-      <x:c r="B9" s="30" t="n">
+      <x:c r="B9" s="41" t="n">
         <x:v>46271</x:v>
       </x:c>
     </x:row>
@@ -1030,7 +2349,7 @@
       <x:c r="A10" t="str">
         <x:v>Opening cash</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="n">
+      <x:c r="B10" s="42" t="n">
         <x:v>400000</x:v>
       </x:c>
     </x:row>
@@ -1038,7 +2357,7 @@
       <x:c r="A11" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="n">
+      <x:c r="B11" s="42" t="n">
         <x:v>100000</x:v>
       </x:c>
     </x:row>
@@ -1046,7 +2365,7 @@
       <x:c r="A12" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B12" s="29" t="str">
+      <x:c r="B12" s="40" t="str">
         <x:v>Base</x:v>
       </x:c>
     </x:row>
@@ -1071,10 +2390,10 @@
       <x:c r="B15" s="16" t="str">
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="C15" s="32" t="n">
+      <x:c r="C15" s="43" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="32" t="n">
+      <x:c r="D15" s="43" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="16" t="str">
@@ -1085,10 +2404,10 @@
       <x:c r="B16" s="16" t="str">
         <x:v>Upside</x:v>
       </x:c>
-      <x:c r="C16" s="32" t="n">
+      <x:c r="C16" s="43" t="n">
         <x:v>1.08</x:v>
       </x:c>
-      <x:c r="D16" s="32" t="n">
+      <x:c r="D16" s="43" t="n">
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="E16" s="16" t="str">
@@ -1099,10 +2418,10 @@
       <x:c r="B17" s="16" t="str">
         <x:v>Downside</x:v>
       </x:c>
-      <x:c r="C17" s="32" t="n">
+      <x:c r="C17" s="43" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="D17" s="32" t="n">
+      <x:c r="D17" s="43" t="n">
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
@@ -1224,55 +2543,55 @@
       <x:c r="A5" t="str">
         <x:v>Week commencing</x:v>
       </x:c>
-      <x:c r="B5" s="34" t="n">
+      <x:c r="B5" s="45" t="n">
         <x:f>'Assumptions'!$B$8</x:f>
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="C5" s="34" t="n">
+      <x:c r="C5" s="45" t="n">
         <x:f>B5+7</x:f>
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="D5" s="34" t="n">
+      <x:c r="D5" s="45" t="n">
         <x:f>C5+7</x:f>
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="E5" s="34" t="n">
+      <x:c r="E5" s="45" t="n">
         <x:f>D5+7</x:f>
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="F5" s="34" t="n">
+      <x:c r="F5" s="45" t="n">
         <x:f>E5+7</x:f>
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="G5" s="34" t="n">
+      <x:c r="G5" s="45" t="n">
         <x:f>F5+7</x:f>
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="H5" s="34" t="n">
+      <x:c r="H5" s="45" t="n">
         <x:f>G5+7</x:f>
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="I5" s="34" t="n">
+      <x:c r="I5" s="45" t="n">
         <x:f>H5+7</x:f>
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="J5" s="34" t="n">
+      <x:c r="J5" s="45" t="n">
         <x:f>I5+7</x:f>
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="K5" s="34" t="n">
+      <x:c r="K5" s="45" t="n">
         <x:f>J5+7</x:f>
         <x:v>46328</x:v>
       </x:c>
-      <x:c r="L5" s="34" t="n">
+      <x:c r="L5" s="45" t="n">
         <x:f>K5+7</x:f>
         <x:v>46335</x:v>
       </x:c>
-      <x:c r="M5" s="34" t="n">
+      <x:c r="M5" s="45" t="n">
         <x:f>L5+7</x:f>
         <x:v>46342</x:v>
       </x:c>
-      <x:c r="N5" s="34" t="n">
+      <x:c r="N5" s="45" t="n">
         <x:f>M5+7</x:f>
         <x:v>46349</x:v>
       </x:c>
@@ -1284,55 +2603,55 @@
       <x:c r="A6" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="B6" s="34" t="n">
+      <x:c r="B6" s="45" t="n">
         <x:f>B5+6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C6" s="34" t="n">
+      <x:c r="C6" s="45" t="n">
         <x:f>C5+6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="D6" s="34" t="n">
+      <x:c r="D6" s="45" t="n">
         <x:f>D5+6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="E6" s="34" t="n">
+      <x:c r="E6" s="45" t="n">
         <x:f>E5+6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="F6" s="34" t="n">
+      <x:c r="F6" s="45" t="n">
         <x:f>F5+6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="G6" s="34" t="n">
+      <x:c r="G6" s="45" t="n">
         <x:f>G5+6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="H6" s="34" t="n">
+      <x:c r="H6" s="45" t="n">
         <x:f>H5+6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="I6" s="34" t="n">
+      <x:c r="I6" s="45" t="n">
         <x:f>I5+6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="J6" s="34" t="n">
+      <x:c r="J6" s="45" t="n">
         <x:f>J5+6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="K6" s="34" t="n">
+      <x:c r="K6" s="45" t="n">
         <x:f>K5+6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="L6" s="34" t="n">
+      <x:c r="L6" s="45" t="n">
         <x:f>L5+6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="M6" s="34" t="n">
+      <x:c r="M6" s="45" t="n">
         <x:f>M5+6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="N6" s="34" t="n">
+      <x:c r="N6" s="45" t="n">
         <x:f>N5+6</x:f>
         <x:v>46355</x:v>
       </x:c>
@@ -1344,55 +2663,55 @@
       <x:c r="A7" t="str">
         <x:v>Actual / Forecast</x:v>
       </x:c>
-      <x:c r="B7" s="35" t="str">
+      <x:c r="B7" s="46" t="str">
         <x:f>IF(B6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Actual</x:v>
       </x:c>
-      <x:c r="C7" s="35" t="str">
+      <x:c r="C7" s="46" t="str">
         <x:f>IF(C6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="D7" s="35" t="str">
+      <x:c r="D7" s="46" t="str">
         <x:f>IF(D6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="E7" s="35" t="str">
+      <x:c r="E7" s="46" t="str">
         <x:f>IF(E6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="F7" s="35" t="str">
+      <x:c r="F7" s="46" t="str">
         <x:f>IF(F6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="G7" s="35" t="str">
+      <x:c r="G7" s="46" t="str">
         <x:f>IF(G6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="H7" s="35" t="str">
+      <x:c r="H7" s="46" t="str">
         <x:f>IF(H6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="I7" s="35" t="str">
+      <x:c r="I7" s="46" t="str">
         <x:f>IF(I6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="J7" s="35" t="str">
+      <x:c r="J7" s="46" t="str">
         <x:f>IF(J6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="K7" s="35" t="str">
+      <x:c r="K7" s="46" t="str">
         <x:f>IF(K6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="L7" s="35" t="str">
+      <x:c r="L7" s="46" t="str">
         <x:f>IF(L6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="M7" s="35" t="str">
+      <x:c r="M7" s="46" t="str">
         <x:f>IF(M6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="N7" s="35" t="str">
+      <x:c r="N7" s="46" t="str">
         <x:f>IF(N6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
@@ -1421,46 +2740,46 @@
       <x:c r="A10" t="str">
         <x:v>Customer receipts</x:v>
       </x:c>
-      <x:c r="B10" s="38" t="n">
+      <x:c r="B10" s="49" t="n">
         <x:v>118000</x:v>
       </x:c>
-      <x:c r="C10" s="38" t="n">
+      <x:c r="C10" s="49" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="D10" s="38" t="n">
+      <x:c r="D10" s="49" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="E10" s="38" t="n">
+      <x:c r="E10" s="49" t="n">
         <x:v>115000</x:v>
       </x:c>
-      <x:c r="F10" s="38" t="n">
+      <x:c r="F10" s="49" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="G10" s="38" t="n">
+      <x:c r="G10" s="49" t="n">
         <x:v>112000</x:v>
       </x:c>
-      <x:c r="H10" s="38" t="n">
+      <x:c r="H10" s="49" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="I10" s="38" t="n">
+      <x:c r="I10" s="49" t="n">
         <x:v>108000</x:v>
       </x:c>
-      <x:c r="J10" s="38" t="n">
+      <x:c r="J10" s="49" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="K10" s="38" t="n">
+      <x:c r="K10" s="49" t="n">
         <x:v>116000</x:v>
       </x:c>
-      <x:c r="L10" s="38" t="n">
+      <x:c r="L10" s="49" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="M10" s="38" t="n">
+      <x:c r="M10" s="49" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="N10" s="38" t="n">
+      <x:c r="N10" s="49" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="O10" s="39" t="n">
+      <x:c r="O10" s="36" t="n">
         <x:f>SUM(B10:N10)</x:f>
         <x:v>1514000</x:v>
       </x:c>
@@ -1469,46 +2788,46 @@
       <x:c r="A11" t="str">
         <x:v>Overdue receipts</x:v>
       </x:c>
-      <x:c r="B11" s="38" t="n">
+      <x:c r="B11" s="49" t="n">
         <x:v>30000</x:v>
       </x:c>
-      <x:c r="C11" s="38" t="n">
+      <x:c r="C11" s="49" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="D11" s="38" t="n">
+      <x:c r="D11" s="49" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="E11" s="38" t="n">
+      <x:c r="E11" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F11" s="38" t="n">
+      <x:c r="F11" s="49" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="G11" s="38" t="n">
+      <x:c r="G11" s="49" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="H11" s="38" t="n">
+      <x:c r="H11" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="I11" s="38" t="n">
+      <x:c r="I11" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="J11" s="38" t="n">
+      <x:c r="J11" s="49" t="n">
         <x:v>7000</x:v>
       </x:c>
-      <x:c r="K11" s="38" t="n">
+      <x:c r="K11" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="L11" s="38" t="n">
+      <x:c r="L11" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="M11" s="38" t="n">
+      <x:c r="M11" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="N11" s="38" t="n">
+      <x:c r="N11" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O11" s="39" t="n">
+      <x:c r="O11" s="36" t="n">
         <x:f>SUM(B11:N11)</x:f>
         <x:v>152000</x:v>
       </x:c>
@@ -1517,46 +2836,46 @@
       <x:c r="A12" t="str">
         <x:v>Cash / EFTPOS sales</x:v>
       </x:c>
-      <x:c r="B12" s="38" t="n">
+      <x:c r="B12" s="49" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="C12" s="38" t="n">
+      <x:c r="C12" s="49" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="D12" s="38" t="n">
+      <x:c r="D12" s="49" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="E12" s="38" t="n">
+      <x:c r="E12" s="49" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="F12" s="38" t="n">
+      <x:c r="F12" s="49" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="G12" s="38" t="n">
+      <x:c r="G12" s="49" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="H12" s="38" t="n">
+      <x:c r="H12" s="49" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="I12" s="38" t="n">
+      <x:c r="I12" s="49" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="J12" s="38" t="n">
+      <x:c r="J12" s="49" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="K12" s="38" t="n">
+      <x:c r="K12" s="49" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="L12" s="38" t="n">
+      <x:c r="L12" s="49" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="M12" s="38" t="n">
+      <x:c r="M12" s="49" t="n">
         <x:v>21000</x:v>
       </x:c>
-      <x:c r="N12" s="38" t="n">
+      <x:c r="N12" s="49" t="n">
         <x:v>22000</x:v>
       </x:c>
-      <x:c r="O12" s="39" t="n">
+      <x:c r="O12" s="36" t="n">
         <x:f>SUM(B12:N12)</x:f>
         <x:v>245000</x:v>
       </x:c>
@@ -1565,46 +2884,46 @@
       <x:c r="A13" t="str">
         <x:v>GST refunds / credits</x:v>
       </x:c>
-      <x:c r="B13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O13" s="39" t="n">
+      <x:c r="B13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="36" t="n">
         <x:f>SUM(B13:N13)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1613,46 +2932,46 @@
       <x:c r="A14" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B14" s="38" t="n">
+      <x:c r="B14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="C14" s="38" t="n">
+      <x:c r="C14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="D14" s="38" t="n">
+      <x:c r="D14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="E14" s="38" t="n">
+      <x:c r="E14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="F14" s="38" t="n">
+      <x:c r="F14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G14" s="38" t="n">
+      <x:c r="G14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="H14" s="38" t="n">
+      <x:c r="H14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="I14" s="38" t="n">
+      <x:c r="I14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="J14" s="38" t="n">
+      <x:c r="J14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K14" s="38" t="n">
+      <x:c r="K14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="L14" s="38" t="n">
+      <x:c r="L14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="M14" s="38" t="n">
+      <x:c r="M14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="N14" s="38" t="n">
+      <x:c r="N14" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O14" s="39" t="n">
+      <x:c r="O14" s="36" t="n">
         <x:f>SUM(B14:N14)</x:f>
         <x:v>52000</x:v>
       </x:c>
@@ -1661,46 +2980,46 @@
       <x:c r="A15" t="str">
         <x:v>Asset sale proceeds</x:v>
       </x:c>
-      <x:c r="B15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="38" t="n">
+      <x:c r="B15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="49" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="L15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O15" s="39" t="n">
+      <x:c r="L15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="36" t="n">
         <x:f>SUM(B15:N15)</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1709,46 +3028,46 @@
       <x:c r="A16" t="str">
         <x:v>Equity / owner funding</x:v>
       </x:c>
-      <x:c r="B16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="38" t="n">
+      <x:c r="B16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="49" t="n">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O16" s="39" t="n">
+      <x:c r="I16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="36" t="n">
         <x:f>SUM(B16:N16)</x:f>
         <x:v>150000</x:v>
       </x:c>
@@ -1757,46 +3076,46 @@
       <x:c r="A17" t="str">
         <x:v>Loan proceeds</x:v>
       </x:c>
-      <x:c r="B17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="38" t="n">
+      <x:c r="B17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="49" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="K17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O17" s="39" t="n">
+      <x:c r="K17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="36" t="n">
         <x:f>SUM(B17:N17)</x:f>
         <x:v>125000</x:v>
       </x:c>
@@ -1805,203 +3124,203 @@
       <x:c r="A18" t="str">
         <x:v>Scenario receipt adjustment</x:v>
       </x:c>
-      <x:c r="B18" s="42" t="n">
+      <x:c r="B18" s="52" t="n">
         <x:f>IF(B$7="Actual",0,SUM(B10:B12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C18" s="42" t="n">
+      <x:c r="C18" s="52" t="n">
         <x:f>IF(C$7="Actual",0,SUM(C10:C12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D18" s="42" t="n">
+      <x:c r="D18" s="52" t="n">
         <x:f>IF(D$7="Actual",0,SUM(D10:D12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="42" t="n">
+      <x:c r="E18" s="52" t="n">
         <x:f>IF(E$7="Actual",0,SUM(E10:E12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="42" t="n">
+      <x:c r="F18" s="52" t="n">
         <x:f>IF(F$7="Actual",0,SUM(F10:F12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="42" t="n">
+      <x:c r="G18" s="52" t="n">
         <x:f>IF(G$7="Actual",0,SUM(G10:G12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="42" t="n">
+      <x:c r="H18" s="52" t="n">
         <x:f>IF(H$7="Actual",0,SUM(H10:H12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="42" t="n">
+      <x:c r="I18" s="52" t="n">
         <x:f>IF(I$7="Actual",0,SUM(I10:I12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="42" t="n">
+      <x:c r="J18" s="52" t="n">
         <x:f>IF(J$7="Actual",0,SUM(J10:J12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="42" t="n">
+      <x:c r="K18" s="52" t="n">
         <x:f>IF(K$7="Actual",0,SUM(K10:K12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="42" t="n">
+      <x:c r="L18" s="52" t="n">
         <x:f>IF(L$7="Actual",0,SUM(L10:L12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="42" t="n">
+      <x:c r="M18" s="52" t="n">
         <x:f>IF(M$7="Actual",0,SUM(M10:M12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N18" s="42" t="n">
+      <x:c r="N18" s="52" t="n">
         <x:f>IF(N$7="Actual",0,SUM(N10:N12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="39" t="n">
+      <x:c r="O18" s="36" t="n">
         <x:f>SUM(B18:N18)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="37" t="str">
+      <x:c r="A19" s="48" t="str">
         <x:v>Total cash receipts</x:v>
       </x:c>
-      <x:c r="B19" s="43" t="n">
+      <x:c r="B19" s="53" t="n">
         <x:f>SUM(B10:B18)</x:f>
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="C19" s="43" t="n">
+      <x:c r="C19" s="53" t="n">
         <x:f>SUM(C10:C18)</x:f>
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="D19" s="43" t="n">
+      <x:c r="D19" s="53" t="n">
         <x:f>SUM(D10:D18)</x:f>
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="E19" s="43" t="n">
+      <x:c r="E19" s="53" t="n">
         <x:f>SUM(E10:E18)</x:f>
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="F19" s="43" t="n">
+      <x:c r="F19" s="53" t="n">
         <x:f>SUM(F10:F18)</x:f>
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="G19" s="43" t="n">
+      <x:c r="G19" s="53" t="n">
         <x:f>SUM(G10:G18)</x:f>
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="H19" s="43" t="n">
+      <x:c r="H19" s="53" t="n">
         <x:f>SUM(H10:H18)</x:f>
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="I19" s="43" t="n">
+      <x:c r="I19" s="53" t="n">
         <x:f>SUM(I10:I18)</x:f>
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="J19" s="43" t="n">
+      <x:c r="J19" s="53" t="n">
         <x:f>SUM(J10:J18)</x:f>
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="K19" s="43" t="n">
+      <x:c r="K19" s="53" t="n">
         <x:f>SUM(K10:K18)</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="L19" s="43" t="n">
+      <x:c r="L19" s="53" t="n">
         <x:f>SUM(L10:L18)</x:f>
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="M19" s="43" t="n">
+      <x:c r="M19" s="53" t="n">
         <x:f>SUM(M10:M18)</x:f>
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="N19" s="43" t="n">
+      <x:c r="N19" s="53" t="n">
         <x:f>SUM(N10:N18)</x:f>
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="O19" s="40" t="n">
+      <x:c r="O19" s="50" t="n">
         <x:f>SUM(B19:N19)</x:f>
         <x:v>2338000</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="39"/>
-      <x:c r="C20" s="39"/>
-      <x:c r="D20" s="39"/>
-      <x:c r="E20" s="39"/>
-      <x:c r="F20" s="39"/>
-      <x:c r="G20" s="39"/>
-      <x:c r="H20" s="39"/>
-      <x:c r="I20" s="39"/>
-      <x:c r="J20" s="39"/>
-      <x:c r="K20" s="39"/>
-      <x:c r="L20" s="39"/>
-      <x:c r="M20" s="39"/>
-      <x:c r="N20" s="39"/>
-      <x:c r="O20" s="39"/>
+      <x:c r="B20" s="36"/>
+      <x:c r="C20" s="36"/>
+      <x:c r="D20" s="36"/>
+      <x:c r="E20" s="36"/>
+      <x:c r="F20" s="36"/>
+      <x:c r="G20" s="36"/>
+      <x:c r="H20" s="36"/>
+      <x:c r="I20" s="36"/>
+      <x:c r="J20" s="36"/>
+      <x:c r="K20" s="36"/>
+      <x:c r="L20" s="36"/>
+      <x:c r="M20" s="36"/>
+      <x:c r="N20" s="36"/>
+      <x:c r="O20" s="36"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
         <x:v>CASH PAYMENTS</x:v>
       </x:c>
-      <x:c r="B21" s="41"/>
-      <x:c r="C21" s="41"/>
-      <x:c r="D21" s="41"/>
-      <x:c r="E21" s="41"/>
-      <x:c r="F21" s="41"/>
-      <x:c r="G21" s="41"/>
-      <x:c r="H21" s="41"/>
-      <x:c r="I21" s="41"/>
-      <x:c r="J21" s="41"/>
-      <x:c r="K21" s="41"/>
-      <x:c r="L21" s="41"/>
-      <x:c r="M21" s="41"/>
-      <x:c r="N21" s="41"/>
-      <x:c r="O21" s="41"/>
+      <x:c r="B21" s="51"/>
+      <x:c r="C21" s="51"/>
+      <x:c r="D21" s="51"/>
+      <x:c r="E21" s="51"/>
+      <x:c r="F21" s="51"/>
+      <x:c r="G21" s="51"/>
+      <x:c r="H21" s="51"/>
+      <x:c r="I21" s="51"/>
+      <x:c r="J21" s="51"/>
+      <x:c r="K21" s="51"/>
+      <x:c r="L21" s="51"/>
+      <x:c r="M21" s="51"/>
+      <x:c r="N21" s="51"/>
+      <x:c r="O21" s="51"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
         <x:v>Suppliers and inventory</x:v>
       </x:c>
-      <x:c r="B22" s="38" t="n">
+      <x:c r="B22" s="49" t="n">
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="C22" s="38" t="n">
+      <x:c r="C22" s="49" t="n">
         <x:v>88000</x:v>
       </x:c>
-      <x:c r="D22" s="38" t="n">
+      <x:c r="D22" s="49" t="n">
         <x:v>90000</x:v>
       </x:c>
-      <x:c r="E22" s="38" t="n">
+      <x:c r="E22" s="49" t="n">
         <x:v>95000</x:v>
       </x:c>
-      <x:c r="F22" s="38" t="n">
+      <x:c r="F22" s="49" t="n">
         <x:v>98000</x:v>
       </x:c>
-      <x:c r="G22" s="38" t="n">
+      <x:c r="G22" s="49" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="H22" s="38" t="n">
+      <x:c r="H22" s="49" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="I22" s="38" t="n">
+      <x:c r="I22" s="49" t="n">
         <x:v>108000</x:v>
       </x:c>
-      <x:c r="J22" s="38" t="n">
+      <x:c r="J22" s="49" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="K22" s="38" t="n">
+      <x:c r="K22" s="49" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="L22" s="38" t="n">
+      <x:c r="L22" s="49" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="M22" s="38" t="n">
+      <x:c r="M22" s="49" t="n">
         <x:v>95000</x:v>
       </x:c>
-      <x:c r="N22" s="38" t="n">
+      <x:c r="N22" s="49" t="n">
         <x:v>90000</x:v>
       </x:c>
-      <x:c r="O22" s="39" t="n">
+      <x:c r="O22" s="36" t="n">
         <x:f>SUM(B22:N22)</x:f>
         <x:v>1266000</x:v>
       </x:c>
@@ -2010,46 +3329,46 @@
       <x:c r="A23" t="str">
         <x:v>Net wages</x:v>
       </x:c>
-      <x:c r="B23" s="38" t="n">
+      <x:c r="B23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="C23" s="38" t="n">
+      <x:c r="C23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="D23" s="38" t="n">
+      <x:c r="D23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="E23" s="38" t="n">
+      <x:c r="E23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="F23" s="38" t="n">
+      <x:c r="F23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="G23" s="38" t="n">
+      <x:c r="G23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="H23" s="38" t="n">
+      <x:c r="H23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="I23" s="38" t="n">
+      <x:c r="I23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="J23" s="38" t="n">
+      <x:c r="J23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="K23" s="38" t="n">
+      <x:c r="K23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="L23" s="38" t="n">
+      <x:c r="L23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="M23" s="38" t="n">
+      <x:c r="M23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="N23" s="38" t="n">
+      <x:c r="N23" s="49" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="O23" s="39" t="n">
+      <x:c r="O23" s="36" t="n">
         <x:f>SUM(B23:N23)</x:f>
         <x:v>546000</x:v>
       </x:c>
@@ -2058,46 +3377,46 @@
       <x:c r="A24" t="str">
         <x:v>PAYG withholding</x:v>
       </x:c>
-      <x:c r="B24" s="38" t="n">
+      <x:c r="B24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="C24" s="38" t="n">
+      <x:c r="C24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="D24" s="38" t="n">
+      <x:c r="D24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="E24" s="38" t="n">
+      <x:c r="E24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="F24" s="38" t="n">
+      <x:c r="F24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="G24" s="38" t="n">
+      <x:c r="G24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="H24" s="38" t="n">
+      <x:c r="H24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="I24" s="38" t="n">
+      <x:c r="I24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="J24" s="38" t="n">
+      <x:c r="J24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="K24" s="38" t="n">
+      <x:c r="K24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="L24" s="38" t="n">
+      <x:c r="L24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="M24" s="38" t="n">
+      <x:c r="M24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="N24" s="38" t="n">
+      <x:c r="N24" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O24" s="39" t="n">
+      <x:c r="O24" s="36" t="n">
         <x:f>SUM(B24:N24)</x:f>
         <x:v>156000</x:v>
       </x:c>
@@ -2106,46 +3425,46 @@
       <x:c r="A25" t="str">
         <x:v>Superannuation</x:v>
       </x:c>
-      <x:c r="B25" s="38" t="n">
+      <x:c r="B25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="C25" s="38" t="n">
+      <x:c r="C25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D25" s="38" t="n">
+      <x:c r="D25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="E25" s="38" t="n">
+      <x:c r="E25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="F25" s="38" t="n">
+      <x:c r="F25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="G25" s="38" t="n">
+      <x:c r="G25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="H25" s="38" t="n">
+      <x:c r="H25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="I25" s="38" t="n">
+      <x:c r="I25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="J25" s="38" t="n">
+      <x:c r="J25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="K25" s="38" t="n">
+      <x:c r="K25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="L25" s="38" t="n">
+      <x:c r="L25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="M25" s="38" t="n">
+      <x:c r="M25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="N25" s="38" t="n">
+      <x:c r="N25" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O25" s="39" t="n">
+      <x:c r="O25" s="36" t="n">
         <x:f>SUM(B25:N25)</x:f>
         <x:v>78000</x:v>
       </x:c>
@@ -2154,46 +3473,46 @@
       <x:c r="A26" t="str">
         <x:v>Payroll tax / workers compensation</x:v>
       </x:c>
-      <x:c r="B26" s="38" t="n">
+      <x:c r="B26" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="C26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F26" s="38" t="n">
+      <x:c r="C26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="G26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="38" t="n">
+      <x:c r="G26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="K26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O26" s="39" t="n">
+      <x:c r="K26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" s="36" t="n">
         <x:f>SUM(B26:N26)</x:f>
         <x:v>15000</x:v>
       </x:c>
@@ -2202,46 +3521,46 @@
       <x:c r="A27" t="str">
         <x:v>Rent</x:v>
       </x:c>
-      <x:c r="B27" s="38" t="n">
+      <x:c r="B27" s="49" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="C27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F27" s="38" t="n">
+      <x:c r="C27" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" s="49" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="G27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="38" t="n">
+      <x:c r="G27" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="49" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="K27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N27" s="38" t="n">
+      <x:c r="K27" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="49" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="O27" s="39" t="n">
+      <x:c r="O27" s="36" t="n">
         <x:f>SUM(B27:N27)</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -2250,46 +3569,46 @@
       <x:c r="A28" t="str">
         <x:v>Utilities</x:v>
       </x:c>
-      <x:c r="B28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F28" s="38" t="n">
+      <x:c r="B28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J28" s="38" t="n">
+      <x:c r="G28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N28" s="38" t="n">
+      <x:c r="K28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O28" s="39" t="n">
+      <x:c r="O28" s="36" t="n">
         <x:f>SUM(B28:N28)</x:f>
         <x:v>12000</x:v>
       </x:c>
@@ -2298,46 +3617,46 @@
       <x:c r="A29" t="str">
         <x:v>Insurance</x:v>
       </x:c>
-      <x:c r="B29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="38" t="n">
+      <x:c r="B29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O29" s="39" t="n">
+      <x:c r="D29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" s="36" t="n">
         <x:f>SUM(B29:N29)</x:f>
         <x:v>6000</x:v>
       </x:c>
@@ -2346,46 +3665,46 @@
       <x:c r="A30" t="str">
         <x:v>Software and subscriptions</x:v>
       </x:c>
-      <x:c r="B30" s="38" t="n">
+      <x:c r="B30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="C30" s="38" t="n">
+      <x:c r="C30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="D30" s="38" t="n">
+      <x:c r="D30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="E30" s="38" t="n">
+      <x:c r="E30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="F30" s="38" t="n">
+      <x:c r="F30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="G30" s="38" t="n">
+      <x:c r="G30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="H30" s="38" t="n">
+      <x:c r="H30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="I30" s="38" t="n">
+      <x:c r="I30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="J30" s="38" t="n">
+      <x:c r="J30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="K30" s="38" t="n">
+      <x:c r="K30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="L30" s="38" t="n">
+      <x:c r="L30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="M30" s="38" t="n">
+      <x:c r="M30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="N30" s="38" t="n">
+      <x:c r="N30" s="49" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="O30" s="39" t="n">
+      <x:c r="O30" s="36" t="n">
         <x:f>SUM(B30:N30)</x:f>
         <x:v>39000</x:v>
       </x:c>
@@ -2394,46 +3713,46 @@
       <x:c r="A31" t="str">
         <x:v>Marketing</x:v>
       </x:c>
-      <x:c r="B31" s="38" t="n">
+      <x:c r="B31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="C31" s="38" t="n">
+      <x:c r="C31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D31" s="38" t="n">
+      <x:c r="D31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="E31" s="38" t="n">
+      <x:c r="E31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="F31" s="38" t="n">
+      <x:c r="F31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="G31" s="38" t="n">
+      <x:c r="G31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="H31" s="38" t="n">
+      <x:c r="H31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="I31" s="38" t="n">
+      <x:c r="I31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="J31" s="38" t="n">
+      <x:c r="J31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="K31" s="38" t="n">
+      <x:c r="K31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="L31" s="38" t="n">
+      <x:c r="L31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="M31" s="38" t="n">
+      <x:c r="M31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="N31" s="38" t="n">
+      <x:c r="N31" s="49" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O31" s="39" t="n">
+      <x:c r="O31" s="36" t="n">
         <x:f>SUM(B31:N31)</x:f>
         <x:v>78000</x:v>
       </x:c>
@@ -2442,46 +3761,46 @@
       <x:c r="A32" t="str">
         <x:v>Professional services</x:v>
       </x:c>
-      <x:c r="B32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="38" t="n">
+      <x:c r="B32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="49" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="E32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="38" t="n">
+      <x:c r="E32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="49" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="I32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L32" s="38" t="n">
+      <x:c r="I32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="49" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="M32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O32" s="39" t="n">
+      <x:c r="M32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O32" s="36" t="n">
         <x:f>SUM(B32:N32)</x:f>
         <x:v>24000</x:v>
       </x:c>
@@ -2490,46 +3809,46 @@
       <x:c r="A33" t="str">
         <x:v>Freight, vehicles and travel</x:v>
       </x:c>
-      <x:c r="B33" s="38" t="n">
+      <x:c r="B33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="C33" s="38" t="n">
+      <x:c r="C33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="D33" s="38" t="n">
+      <x:c r="D33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="E33" s="38" t="n">
+      <x:c r="E33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F33" s="38" t="n">
+      <x:c r="F33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="G33" s="38" t="n">
+      <x:c r="G33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H33" s="38" t="n">
+      <x:c r="H33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="I33" s="38" t="n">
+      <x:c r="I33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="J33" s="38" t="n">
+      <x:c r="J33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="K33" s="38" t="n">
+      <x:c r="K33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="L33" s="38" t="n">
+      <x:c r="L33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="M33" s="38" t="n">
+      <x:c r="M33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="N33" s="38" t="n">
+      <x:c r="N33" s="49" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="O33" s="39" t="n">
+      <x:c r="O33" s="36" t="n">
         <x:f>SUM(B33:N33)</x:f>
         <x:v>130000</x:v>
       </x:c>
@@ -2538,46 +3857,46 @@
       <x:c r="A34" t="str">
         <x:v>GST / BAS payments</x:v>
       </x:c>
-      <x:c r="B34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J34" s="38" t="n">
+      <x:c r="B34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="49" t="n">
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="K34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O34" s="39" t="n">
+      <x:c r="K34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N34" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34" s="36" t="n">
         <x:f>SUM(B34:N34)</x:f>
         <x:v>45000</x:v>
       </x:c>
@@ -2586,46 +3905,46 @@
       <x:c r="A35" t="str">
         <x:v>PAYG income tax instalments</x:v>
       </x:c>
-      <x:c r="B35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J35" s="38" t="n">
+      <x:c r="B35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="49" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="K35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O35" s="39" t="n">
+      <x:c r="K35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N35" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O35" s="36" t="n">
         <x:f>SUM(B35:N35)</x:f>
         <x:v>18000</x:v>
       </x:c>
@@ -2634,46 +3953,46 @@
       <x:c r="A36" t="str">
         <x:v>FBT / other tax</x:v>
       </x:c>
-      <x:c r="B36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O36" s="39" t="n">
+      <x:c r="B36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N36" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" s="36" t="n">
         <x:f>SUM(B36:N36)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2682,46 +4001,46 @@
       <x:c r="A37" t="str">
         <x:v>Interest and bank fees</x:v>
       </x:c>
-      <x:c r="B37" s="38" t="n">
+      <x:c r="B37" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="C37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F37" s="38" t="n">
+      <x:c r="C37" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J37" s="38" t="n">
+      <x:c r="G37" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I37" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N37" s="38" t="n">
+      <x:c r="K37" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N37" s="49" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O37" s="39" t="n">
+      <x:c r="O37" s="36" t="n">
         <x:f>SUM(B37:N37)</x:f>
         <x:v>16000</x:v>
       </x:c>
@@ -2730,46 +4049,46 @@
       <x:c r="A38" t="str">
         <x:v>Loan principal</x:v>
       </x:c>
-      <x:c r="B38" s="38" t="n">
+      <x:c r="B38" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="C38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F38" s="38" t="n">
+      <x:c r="C38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F38" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="G38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J38" s="38" t="n">
+      <x:c r="G38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="K38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N38" s="38" t="n">
+      <x:c r="K38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N38" s="49" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O38" s="39" t="n">
+      <x:c r="O38" s="36" t="n">
         <x:f>SUM(B38:N38)</x:f>
         <x:v>48000</x:v>
       </x:c>
@@ -2778,46 +4097,46 @@
       <x:c r="A39" t="str">
         <x:v>Capital expenditure</x:v>
       </x:c>
-      <x:c r="B39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G39" s="38" t="n">
+      <x:c r="B39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G39" s="49" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="H39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K39" s="38" t="n">
+      <x:c r="H39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39" s="49" t="n">
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="L39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O39" s="39" t="n">
+      <x:c r="L39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" s="36" t="n">
         <x:f>SUM(B39:N39)</x:f>
         <x:v>65000</x:v>
       </x:c>
@@ -2826,46 +4145,46 @@
       <x:c r="A40" t="str">
         <x:v>Dividends / distributions</x:v>
       </x:c>
-      <x:c r="B40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O40" s="39" t="n">
+      <x:c r="B40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" s="36" t="n">
         <x:f>SUM(B40:N40)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2874,46 +4193,46 @@
       <x:c r="A41" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B41" s="38" t="n">
+      <x:c r="B41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="C41" s="38" t="n">
+      <x:c r="C41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D41" s="38" t="n">
+      <x:c r="D41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="E41" s="38" t="n">
+      <x:c r="E41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="F41" s="38" t="n">
+      <x:c r="F41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="G41" s="38" t="n">
+      <x:c r="G41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="H41" s="38" t="n">
+      <x:c r="H41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="I41" s="38" t="n">
+      <x:c r="I41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="J41" s="38" t="n">
+      <x:c r="J41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="K41" s="38" t="n">
+      <x:c r="K41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="L41" s="38" t="n">
+      <x:c r="L41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="M41" s="38" t="n">
+      <x:c r="M41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="N41" s="38" t="n">
+      <x:c r="N41" s="49" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="O41" s="39" t="n">
+      <x:c r="O41" s="36" t="n">
         <x:f>SUM(B41:N41)</x:f>
         <x:v>65000</x:v>
       </x:c>
@@ -2922,216 +4241,216 @@
       <x:c r="A42" t="str">
         <x:v>Scenario payment adjustment</x:v>
       </x:c>
-      <x:c r="B42" s="42" t="n">
+      <x:c r="B42" s="52" t="n">
         <x:f>IF(B$7="Actual",0,SUM(B22,B31,B33,B41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C42" s="42" t="n">
+      <x:c r="C42" s="52" t="n">
         <x:f>IF(C$7="Actual",0,SUM(C22,C31,C33,C41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D42" s="42" t="n">
+      <x:c r="D42" s="52" t="n">
         <x:f>IF(D$7="Actual",0,SUM(D22,D31,D33,D41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E42" s="42" t="n">
+      <x:c r="E42" s="52" t="n">
         <x:f>IF(E$7="Actual",0,SUM(E22,E31,E33,E41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F42" s="42" t="n">
+      <x:c r="F42" s="52" t="n">
         <x:f>IF(F$7="Actual",0,SUM(F22,F31,F33,F41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G42" s="42" t="n">
+      <x:c r="G42" s="52" t="n">
         <x:f>IF(G$7="Actual",0,SUM(G22,G31,G33,G41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H42" s="42" t="n">
+      <x:c r="H42" s="52" t="n">
         <x:f>IF(H$7="Actual",0,SUM(H22,H31,H33,H41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I42" s="42" t="n">
+      <x:c r="I42" s="52" t="n">
         <x:f>IF(I$7="Actual",0,SUM(I22,I31,I33,I41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J42" s="42" t="n">
+      <x:c r="J42" s="52" t="n">
         <x:f>IF(J$7="Actual",0,SUM(J22,J31,J33,J41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K42" s="42" t="n">
+      <x:c r="K42" s="52" t="n">
         <x:f>IF(K$7="Actual",0,SUM(K22,K31,K33,K41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L42" s="42" t="n">
+      <x:c r="L42" s="52" t="n">
         <x:f>IF(L$7="Actual",0,SUM(L22,L31,L33,L41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M42" s="42" t="n">
+      <x:c r="M42" s="52" t="n">
         <x:f>IF(M$7="Actual",0,SUM(M22,M31,M33,M41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N42" s="42" t="n">
+      <x:c r="N42" s="52" t="n">
         <x:f>IF(N$7="Actual",0,SUM(N22,N31,N33,N41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O42" s="39" t="n">
+      <x:c r="O42" s="36" t="n">
         <x:f>SUM(B42:N42)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="37" t="str">
+      <x:c r="A43" s="48" t="str">
         <x:v>Total cash payments</x:v>
       </x:c>
-      <x:c r="B43" s="43" t="n">
+      <x:c r="B43" s="53" t="n">
         <x:f>SUM(B22:B42)</x:f>
         <x:v>212000</x:v>
       </x:c>
-      <x:c r="C43" s="43" t="n">
+      <x:c r="C43" s="53" t="n">
         <x:f>SUM(C22:C42)</x:f>
         <x:v>178000</x:v>
       </x:c>
-      <x:c r="D43" s="43" t="n">
+      <x:c r="D43" s="53" t="n">
         <x:f>SUM(D22:D42)</x:f>
         <x:v>182000</x:v>
       </x:c>
-      <x:c r="E43" s="43" t="n">
+      <x:c r="E43" s="53" t="n">
         <x:f>SUM(E22:E42)</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="F43" s="43" t="n">
+      <x:c r="F43" s="53" t="n">
         <x:f>SUM(F22:F42)</x:f>
         <x:v>232000</x:v>
       </x:c>
-      <x:c r="G43" s="43" t="n">
+      <x:c r="G43" s="53" t="n">
         <x:f>SUM(G22:G42)</x:f>
         <x:v>209000</x:v>
       </x:c>
-      <x:c r="H43" s="43" t="n">
+      <x:c r="H43" s="53" t="n">
         <x:f>SUM(H22:H42)</x:f>
         <x:v>197000</x:v>
       </x:c>
-      <x:c r="I43" s="43" t="n">
+      <x:c r="I43" s="53" t="n">
         <x:f>SUM(I22:I42)</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="J43" s="43" t="n">
+      <x:c r="J43" s="53" t="n">
         <x:f>SUM(J22:J42)</x:f>
         <x:v>307000</x:v>
       </x:c>
-      <x:c r="K43" s="43" t="n">
+      <x:c r="K43" s="53" t="n">
         <x:f>SUM(K22:K42)</x:f>
         <x:v>229000</x:v>
       </x:c>
-      <x:c r="L43" s="43" t="n">
+      <x:c r="L43" s="53" t="n">
         <x:f>SUM(L22:L42)</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="M43" s="43" t="n">
+      <x:c r="M43" s="53" t="n">
         <x:f>SUM(M22:M42)</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="N43" s="43" t="n">
+      <x:c r="N43" s="53" t="n">
         <x:f>SUM(N22:N42)</x:f>
         <x:v>219000</x:v>
       </x:c>
-      <x:c r="O43" s="40" t="n">
+      <x:c r="O43" s="50" t="n">
         <x:f>SUM(B43:N43)</x:f>
         <x:v>2707000</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="B44" s="39"/>
-      <x:c r="C44" s="39"/>
-      <x:c r="D44" s="39"/>
-      <x:c r="E44" s="39"/>
-      <x:c r="F44" s="39"/>
-      <x:c r="G44" s="39"/>
-      <x:c r="H44" s="39"/>
-      <x:c r="I44" s="39"/>
-      <x:c r="J44" s="39"/>
-      <x:c r="K44" s="39"/>
-      <x:c r="L44" s="39"/>
-      <x:c r="M44" s="39"/>
-      <x:c r="N44" s="39"/>
-      <x:c r="O44" s="39"/>
+      <x:c r="B44" s="36"/>
+      <x:c r="C44" s="36"/>
+      <x:c r="D44" s="36"/>
+      <x:c r="E44" s="36"/>
+      <x:c r="F44" s="36"/>
+      <x:c r="G44" s="36"/>
+      <x:c r="H44" s="36"/>
+      <x:c r="I44" s="36"/>
+      <x:c r="J44" s="36"/>
+      <x:c r="K44" s="36"/>
+      <x:c r="L44" s="36"/>
+      <x:c r="M44" s="36"/>
+      <x:c r="N44" s="36"/>
+      <x:c r="O44" s="36"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="14" t="str">
         <x:v>CASH POSITION</x:v>
       </x:c>
-      <x:c r="B45" s="41"/>
-      <x:c r="C45" s="41"/>
-      <x:c r="D45" s="41"/>
-      <x:c r="E45" s="41"/>
-      <x:c r="F45" s="41"/>
-      <x:c r="G45" s="41"/>
-      <x:c r="H45" s="41"/>
-      <x:c r="I45" s="41"/>
-      <x:c r="J45" s="41"/>
-      <x:c r="K45" s="41"/>
-      <x:c r="L45" s="41"/>
-      <x:c r="M45" s="41"/>
-      <x:c r="N45" s="41"/>
-      <x:c r="O45" s="41"/>
+      <x:c r="B45" s="51"/>
+      <x:c r="C45" s="51"/>
+      <x:c r="D45" s="51"/>
+      <x:c r="E45" s="51"/>
+      <x:c r="F45" s="51"/>
+      <x:c r="G45" s="51"/>
+      <x:c r="H45" s="51"/>
+      <x:c r="I45" s="51"/>
+      <x:c r="J45" s="51"/>
+      <x:c r="K45" s="51"/>
+      <x:c r="L45" s="51"/>
+      <x:c r="M45" s="51"/>
+      <x:c r="N45" s="51"/>
+      <x:c r="O45" s="51"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
         <x:v>Opening cash balance</x:v>
       </x:c>
-      <x:c r="B46" s="44" t="n">
+      <x:c r="B46" s="38" t="n">
         <x:f>'Assumptions'!$B$10</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="C46" s="44" t="n">
+      <x:c r="C46" s="38" t="n">
         <x:f>B48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="D46" s="44" t="n">
+      <x:c r="D46" s="38" t="n">
         <x:f>C48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="E46" s="44" t="n">
+      <x:c r="E46" s="38" t="n">
         <x:f>D48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="F46" s="44" t="n">
+      <x:c r="F46" s="38" t="n">
         <x:f>E48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="G46" s="44" t="n">
+      <x:c r="G46" s="38" t="n">
         <x:f>F48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="H46" s="44" t="n">
+      <x:c r="H46" s="38" t="n">
         <x:f>G48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="I46" s="44" t="n">
+      <x:c r="I46" s="38" t="n">
         <x:f>H48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="J46" s="44" t="n">
+      <x:c r="J46" s="38" t="n">
         <x:f>I48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="K46" s="44" t="n">
+      <x:c r="K46" s="38" t="n">
         <x:f>J48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="L46" s="44" t="n">
+      <x:c r="L46" s="38" t="n">
         <x:f>K48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="M46" s="44" t="n">
+      <x:c r="M46" s="38" t="n">
         <x:f>L48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="N46" s="44" t="n">
+      <x:c r="N46" s="38" t="n">
         <x:f>M48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="O46" s="39" t="n">
+      <x:c r="O46" s="36" t="n">
         <x:f>N46</x:f>
         <x:v>82000</x:v>
       </x:c>
@@ -3140,120 +4459,120 @@
       <x:c r="A47" t="str">
         <x:v>Net cash movement</x:v>
       </x:c>
-      <x:c r="B47" s="42" t="n">
+      <x:c r="B47" s="52" t="n">
         <x:f>B19-B43</x:f>
         <x:v>-42000</x:v>
       </x:c>
-      <x:c r="C47" s="42" t="n">
+      <x:c r="C47" s="52" t="n">
         <x:f>C19-C43</x:f>
         <x:v>-9000</x:v>
       </x:c>
-      <x:c r="D47" s="42" t="n">
+      <x:c r="D47" s="52" t="n">
         <x:f>D19-D43</x:f>
         <x:v>-24000</x:v>
       </x:c>
-      <x:c r="E47" s="42" t="n">
+      <x:c r="E47" s="52" t="n">
         <x:f>E19-E43</x:f>
         <x:v>-32000</x:v>
       </x:c>
-      <x:c r="F47" s="42" t="n">
+      <x:c r="F47" s="52" t="n">
         <x:f>F19-F43</x:f>
         <x:v>-92000</x:v>
       </x:c>
-      <x:c r="G47" s="42" t="n">
+      <x:c r="G47" s="52" t="n">
         <x:f>G19-G43</x:f>
         <x:v>-68000</x:v>
       </x:c>
-      <x:c r="H47" s="42" t="n">
+      <x:c r="H47" s="52" t="n">
         <x:f>H19-H43</x:f>
         <x:v>84000</x:v>
       </x:c>
-      <x:c r="I47" s="42" t="n">
+      <x:c r="I47" s="52" t="n">
         <x:f>I19-I43</x:f>
         <x:v>-57000</x:v>
       </x:c>
-      <x:c r="J47" s="42" t="n">
+      <x:c r="J47" s="52" t="n">
         <x:f>J19-J43</x:f>
         <x:v>-43000</x:v>
       </x:c>
-      <x:c r="K47" s="42" t="n">
+      <x:c r="K47" s="52" t="n">
         <x:f>K19-K43</x:f>
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="L47" s="42" t="n">
+      <x:c r="L47" s="52" t="n">
         <x:f>L19-L43</x:f>
         <x:v>-38000</x:v>
       </x:c>
-      <x:c r="M47" s="42" t="n">
+      <x:c r="M47" s="52" t="n">
         <x:f>M19-M43</x:f>
         <x:v>-17000</x:v>
       </x:c>
-      <x:c r="N47" s="42" t="n">
+      <x:c r="N47" s="52" t="n">
         <x:f>N19-N43</x:f>
         <x:v>-51000</x:v>
       </x:c>
-      <x:c r="O47" s="39" t="n">
+      <x:c r="O47" s="36" t="n">
         <x:f>N47</x:f>
         <x:v>-51000</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="37" t="str">
+      <x:c r="A48" s="48" t="str">
         <x:v>Closing cash balance</x:v>
       </x:c>
-      <x:c r="B48" s="43" t="n">
+      <x:c r="B48" s="53" t="n">
         <x:f>B46+B47</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="C48" s="43" t="n">
+      <x:c r="C48" s="53" t="n">
         <x:f>C46+C47</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="D48" s="43" t="n">
+      <x:c r="D48" s="53" t="n">
         <x:f>D46+D47</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="E48" s="43" t="n">
+      <x:c r="E48" s="53" t="n">
         <x:f>E46+E47</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="F48" s="43" t="n">
+      <x:c r="F48" s="53" t="n">
         <x:f>F46+F47</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="G48" s="43" t="n">
+      <x:c r="G48" s="53" t="n">
         <x:f>G46+G47</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="H48" s="43" t="n">
+      <x:c r="H48" s="53" t="n">
         <x:f>H46+H47</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="I48" s="43" t="n">
+      <x:c r="I48" s="53" t="n">
         <x:f>I46+I47</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="J48" s="43" t="n">
+      <x:c r="J48" s="53" t="n">
         <x:f>J46+J47</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="K48" s="43" t="n">
+      <x:c r="K48" s="53" t="n">
         <x:f>K46+K47</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="L48" s="43" t="n">
+      <x:c r="L48" s="53" t="n">
         <x:f>L46+L47</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="M48" s="43" t="n">
+      <x:c r="M48" s="53" t="n">
         <x:f>M46+M47</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="N48" s="43" t="n">
+      <x:c r="N48" s="53" t="n">
         <x:f>N46+N47</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="O48" s="40" t="n">
+      <x:c r="O48" s="50" t="n">
         <x:f>N48</x:f>
         <x:v>31000</x:v>
       </x:c>
@@ -3262,120 +4581,120 @@
       <x:c r="A49" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B49" s="44" t="n">
+      <x:c r="B49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="C49" s="44" t="n">
+      <x:c r="C49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="D49" s="44" t="n">
+      <x:c r="D49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="E49" s="44" t="n">
+      <x:c r="E49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="F49" s="44" t="n">
+      <x:c r="F49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="G49" s="44" t="n">
+      <x:c r="G49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="H49" s="44" t="n">
+      <x:c r="H49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="I49" s="44" t="n">
+      <x:c r="I49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="J49" s="44" t="n">
+      <x:c r="J49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="K49" s="44" t="n">
+      <x:c r="K49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="L49" s="44" t="n">
+      <x:c r="L49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="M49" s="44" t="n">
+      <x:c r="M49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="N49" s="44" t="n">
+      <x:c r="N49" s="38" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="O49" s="39" t="n">
+      <x:c r="O49" s="36" t="n">
         <x:f>N49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="37" t="str">
+      <x:c r="A50" s="48" t="str">
         <x:v>Headroom / (gap)</x:v>
       </x:c>
-      <x:c r="B50" s="43" t="n">
+      <x:c r="B50" s="53" t="n">
         <x:f>B48-B49</x:f>
         <x:v>258000</x:v>
       </x:c>
-      <x:c r="C50" s="43" t="n">
+      <x:c r="C50" s="53" t="n">
         <x:f>C48-C49</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="D50" s="43" t="n">
+      <x:c r="D50" s="53" t="n">
         <x:f>D48-D49</x:f>
         <x:v>225000</x:v>
       </x:c>
-      <x:c r="E50" s="43" t="n">
+      <x:c r="E50" s="53" t="n">
         <x:f>E48-E49</x:f>
         <x:v>193000</x:v>
       </x:c>
-      <x:c r="F50" s="43" t="n">
+      <x:c r="F50" s="53" t="n">
         <x:f>F48-F49</x:f>
         <x:v>101000</x:v>
       </x:c>
-      <x:c r="G50" s="43" t="n">
+      <x:c r="G50" s="53" t="n">
         <x:f>G48-G49</x:f>
         <x:v>33000</x:v>
       </x:c>
-      <x:c r="H50" s="43" t="n">
+      <x:c r="H50" s="53" t="n">
         <x:f>H48-H49</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="I50" s="43" t="n">
+      <x:c r="I50" s="53" t="n">
         <x:f>I48-I49</x:f>
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="J50" s="43" t="n">
+      <x:c r="J50" s="53" t="n">
         <x:f>J48-J49</x:f>
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="K50" s="43" t="n">
+      <x:c r="K50" s="53" t="n">
         <x:f>K48-K49</x:f>
         <x:v>37000</x:v>
       </x:c>
-      <x:c r="L50" s="43" t="n">
+      <x:c r="L50" s="53" t="n">
         <x:f>L48-L49</x:f>
         <x:v>-1000</x:v>
       </x:c>
-      <x:c r="M50" s="43" t="n">
+      <x:c r="M50" s="53" t="n">
         <x:f>M48-M49</x:f>
         <x:v>-18000</x:v>
       </x:c>
-      <x:c r="N50" s="43" t="n">
+      <x:c r="N50" s="53" t="n">
         <x:f>N48-N49</x:f>
         <x:v>-69000</x:v>
       </x:c>
-      <x:c r="O50" s="40" t="n">
+      <x:c r="O50" s="50" t="n">
         <x:f>N50</x:f>
         <x:v>-69000</x:v>
       </x:c>
@@ -3447,18 +4766,18 @@
     <x:mergeCell ref="A2:O2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B51:N51">
-    <x:cfRule type="expression" dxfId="0" priority="1">
+    <x:cfRule type="expression" dxfId="8" priority="1">
       <x:formula>B51="BELOW BUFFER"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1" priority="2">
+    <x:cfRule type="expression" dxfId="9" priority="2">
       <x:formula>B51="WATCH"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="2" priority="3">
+    <x:cfRule type="expression" dxfId="10" priority="3">
       <x:formula>B51="OK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5578828a6574f7e"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cebc129644548f1"/>
 </x:worksheet>
 </file>
 
@@ -3536,16 +4855,16 @@
       <x:c r="A6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="45" t="n">
+      <x:c r="B6" s="37" t="n">
         <x:f>'13-Week Forecast'!B$6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C6" s="44" t="n">
+      <x:c r="C6" s="38" t="n">
         <x:f>'13-Week Forecast'!B$48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="D6" s="38"/>
-      <x:c r="E6" s="42" t="str">
+      <x:c r="D6" s="49"/>
+      <x:c r="E6" s="52" t="str">
         <x:f>IF(D6="","",D6-C6)</x:f>
       </x:c>
       <x:c r="F6" s="16"/>
@@ -3557,16 +4876,16 @@
       <x:c r="A7" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="45" t="n">
+      <x:c r="B7" s="37" t="n">
         <x:f>'13-Week Forecast'!C$6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="C7" s="44" t="n">
+      <x:c r="C7" s="38" t="n">
         <x:f>'13-Week Forecast'!C$48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="D7" s="38"/>
-      <x:c r="E7" s="42" t="str">
+      <x:c r="D7" s="49"/>
+      <x:c r="E7" s="52" t="str">
         <x:f>IF(D7="","",D7-C7)</x:f>
       </x:c>
       <x:c r="F7" s="16"/>
@@ -3578,16 +4897,16 @@
       <x:c r="A8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="45" t="n">
+      <x:c r="B8" s="37" t="n">
         <x:f>'13-Week Forecast'!D$6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="C8" s="44" t="n">
+      <x:c r="C8" s="38" t="n">
         <x:f>'13-Week Forecast'!D$48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="D8" s="38"/>
-      <x:c r="E8" s="42" t="str">
+      <x:c r="D8" s="49"/>
+      <x:c r="E8" s="52" t="str">
         <x:f>IF(D8="","",D8-C8)</x:f>
       </x:c>
       <x:c r="F8" s="16"/>
@@ -3599,16 +4918,16 @@
       <x:c r="A9" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="45" t="n">
+      <x:c r="B9" s="37" t="n">
         <x:f>'13-Week Forecast'!E$6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="C9" s="44" t="n">
+      <x:c r="C9" s="38" t="n">
         <x:f>'13-Week Forecast'!E$48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="D9" s="38"/>
-      <x:c r="E9" s="42" t="str">
+      <x:c r="D9" s="49"/>
+      <x:c r="E9" s="52" t="str">
         <x:f>IF(D9="","",D9-C9)</x:f>
       </x:c>
       <x:c r="F9" s="16"/>
@@ -3620,16 +4939,16 @@
       <x:c r="A10" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="45" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>'13-Week Forecast'!F$6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="C10" s="44" t="n">
+      <x:c r="C10" s="38" t="n">
         <x:f>'13-Week Forecast'!F$48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="D10" s="38"/>
-      <x:c r="E10" s="42" t="str">
+      <x:c r="D10" s="49"/>
+      <x:c r="E10" s="52" t="str">
         <x:f>IF(D10="","",D10-C10)</x:f>
       </x:c>
       <x:c r="F10" s="16"/>
@@ -3641,16 +4960,16 @@
       <x:c r="A11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="45" t="n">
+      <x:c r="B11" s="37" t="n">
         <x:f>'13-Week Forecast'!G$6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="C11" s="44" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>'13-Week Forecast'!G$48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="D11" s="38"/>
-      <x:c r="E11" s="42" t="str">
+      <x:c r="D11" s="49"/>
+      <x:c r="E11" s="52" t="str">
         <x:f>IF(D11="","",D11-C11)</x:f>
       </x:c>
       <x:c r="F11" s="16"/>
@@ -3662,16 +4981,16 @@
       <x:c r="A12" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B12" s="45" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>'13-Week Forecast'!H$6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="C12" s="44" t="n">
+      <x:c r="C12" s="38" t="n">
         <x:f>'13-Week Forecast'!H$48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="D12" s="38"/>
-      <x:c r="E12" s="42" t="str">
+      <x:c r="D12" s="49"/>
+      <x:c r="E12" s="52" t="str">
         <x:f>IF(D12="","",D12-C12)</x:f>
       </x:c>
       <x:c r="F12" s="16"/>
@@ -3683,16 +5002,16 @@
       <x:c r="A13" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B13" s="45" t="n">
+      <x:c r="B13" s="37" t="n">
         <x:f>'13-Week Forecast'!I$6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="C13" s="44" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>'13-Week Forecast'!I$48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="D13" s="38"/>
-      <x:c r="E13" s="42" t="str">
+      <x:c r="D13" s="49"/>
+      <x:c r="E13" s="52" t="str">
         <x:f>IF(D13="","",D13-C13)</x:f>
       </x:c>
       <x:c r="F13" s="16"/>
@@ -3704,16 +5023,16 @@
       <x:c r="A14" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B14" s="45" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>'13-Week Forecast'!J$6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="C14" s="44" t="n">
+      <x:c r="C14" s="38" t="n">
         <x:f>'13-Week Forecast'!J$48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="D14" s="38"/>
-      <x:c r="E14" s="42" t="str">
+      <x:c r="D14" s="49"/>
+      <x:c r="E14" s="52" t="str">
         <x:f>IF(D14="","",D14-C14)</x:f>
       </x:c>
       <x:c r="F14" s="16"/>
@@ -3725,16 +5044,16 @@
       <x:c r="A15" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B15" s="45" t="n">
+      <x:c r="B15" s="37" t="n">
         <x:f>'13-Week Forecast'!K$6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="C15" s="44" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>'13-Week Forecast'!K$48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="D15" s="38"/>
-      <x:c r="E15" s="42" t="str">
+      <x:c r="D15" s="49"/>
+      <x:c r="E15" s="52" t="str">
         <x:f>IF(D15="","",D15-C15)</x:f>
       </x:c>
       <x:c r="F15" s="16"/>
@@ -3746,16 +5065,16 @@
       <x:c r="A16" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B16" s="45" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>'13-Week Forecast'!L$6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="C16" s="44" t="n">
+      <x:c r="C16" s="38" t="n">
         <x:f>'13-Week Forecast'!L$48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="D16" s="38"/>
-      <x:c r="E16" s="42" t="str">
+      <x:c r="D16" s="49"/>
+      <x:c r="E16" s="52" t="str">
         <x:f>IF(D16="","",D16-C16)</x:f>
       </x:c>
       <x:c r="F16" s="16"/>
@@ -3767,16 +5086,16 @@
       <x:c r="A17" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B17" s="45" t="n">
+      <x:c r="B17" s="37" t="n">
         <x:f>'13-Week Forecast'!M$6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="C17" s="44" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>'13-Week Forecast'!M$48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="D17" s="38"/>
-      <x:c r="E17" s="42" t="str">
+      <x:c r="D17" s="49"/>
+      <x:c r="E17" s="52" t="str">
         <x:f>IF(D17="","",D17-C17)</x:f>
       </x:c>
       <x:c r="F17" s="16"/>
@@ -3788,16 +5107,16 @@
       <x:c r="A18" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B18" s="45" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>'13-Week Forecast'!N$6</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="C18" s="44" t="n">
+      <x:c r="C18" s="38" t="n">
         <x:f>'13-Week Forecast'!N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D18" s="38"/>
-      <x:c r="E18" s="42" t="str">
+      <x:c r="D18" s="49"/>
+      <x:c r="E18" s="52" t="str">
         <x:f>IF(D18="","",D18-C18)</x:f>
       </x:c>
       <x:c r="F18" s="16"/>
@@ -3824,13 +5143,13 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="54" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -3847,7 +5166,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Structural checks and Australian statutory-source log are added in the controls build step.</x:v>
+        <x:v>Formula-driven integrity controls and official Australian planning sources checked 26 August 2026.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -3858,88 +5177,483 @@
       <x:c r="H2" s="8"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="A4" s="55" t="str">
+        <x:v>MODEL STATUS</x:v>
+      </x:c>
+      <x:c r="B4" s="55" t="str">
+        <x:f>IF(COUNTIF(F8:F16,"PASS")=9,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C4" s="55"/>
+      <x:c r="D4" s="55" t="str">
+        <x:v>LIQUIDITY STATUS</x:v>
+      </x:c>
+      <x:c r="E4" s="55" t="str">
+        <x:f>IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"BELOW BUFFER")&gt;0,"ACTION REQUIRED",IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"WATCH")&gt;0,"WATCH","HEALTHY"))</x:f>
+        <x:v>ACTION REQUIRED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
         <x:v>Check</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="str">
+      <x:c r="B7" s="14" t="str">
         <x:v>Actual</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="str">
+      <x:c r="C7" s="14" t="str">
         <x:v>Expected</x:v>
       </x:c>
-      <x:c r="D4" s="14" t="str">
+      <x:c r="D7" s="14" t="str">
         <x:v>Difference</x:v>
       </x:c>
-      <x:c r="E4" s="14" t="str">
+      <x:c r="E7" s="14" t="str">
         <x:v>Tolerance</x:v>
       </x:c>
-      <x:c r="F4" s="14" t="str">
+      <x:c r="F7" s="14" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="G4" s="14" t="str">
+      <x:c r="G7" s="14" t="str">
         <x:v>Where to fix</x:v>
       </x:c>
-      <x:c r="H4" s="14" t="str">
+      <x:c r="H7" s="14" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="47" t="str">
-        <x:v>MODEL STATUS: prepared for formula-driven integrity checks</x:v>
-      </x:c>
-      <x:c r="B6" s="47"/>
-      <x:c r="C6" s="47"/>
-      <x:c r="D6" s="47"/>
-      <x:c r="E6" s="47"/>
-      <x:c r="F6" s="47"/>
-      <x:c r="G6" s="47"/>
-      <x:c r="H6" s="47"/>
+    <x:row r="8">
+      <x:c r="A8" s="15" t="str">
+        <x:v>Forecast starts Monday</x:v>
+      </x:c>
+      <x:c r="B8" s="56" t="n">
+        <x:f>WEEKDAY('Assumptions'!$B$8,2)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="56" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="56" t="n">
+        <x:f>B8-C8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="str">
+        <x:f>IF(ABS(D8)&lt;=E8,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="str">
+        <x:v>Assumptions!B8</x:v>
+      </x:c>
+      <x:c r="H8" s="15" t="str">
+        <x:v>Forecast start date must be a Monday.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="14" t="str">
+      <x:c r="A9" s="15" t="str">
+        <x:v>As-at date in forecast horizon</x:v>
+      </x:c>
+      <x:c r="B9" s="56" t="n">
+        <x:f>--AND('Assumptions'!$B$9&gt;='13-Week Forecast'!$B$5,'Assumptions'!$B$9&lt;='13-Week Forecast'!$N$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="56" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" s="56" t="n">
+        <x:f>B9-C9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="str">
+        <x:f>IF(ABS(D9)&lt;=E9,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="str">
+        <x:v>Assumptions!B9</x:v>
+      </x:c>
+      <x:c r="H9" s="15" t="str">
+        <x:v>Keep the as-at date inside the displayed 13 weeks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="15" t="str">
+        <x:v>Selected scenario recognised</x:v>
+      </x:c>
+      <x:c r="B10" s="56" t="n">
+        <x:f>COUNTIF('Assumptions'!$B$15:$B$17,'Assumptions'!$B$12)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="56" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="56" t="n">
+        <x:f>B10-C10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="str">
+        <x:f>IF(ABS(D10)&lt;=E10,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="str">
+        <x:v>Assumptions!B12</x:v>
+      </x:c>
+      <x:c r="H10" s="15" t="str">
+        <x:v>Select Base, Upside or Downside.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="15" t="str">
+        <x:v>Week 1 opening cash ties</x:v>
+      </x:c>
+      <x:c r="B11" s="57" t="n">
+        <x:f>'13-Week Forecast'!$B$46</x:f>
+        <x:v>400000</x:v>
+      </x:c>
+      <x:c r="C11" s="57" t="n">
+        <x:f>'Assumptions'!$B$10</x:f>
+        <x:v>400000</x:v>
+      </x:c>
+      <x:c r="D11" s="56" t="n">
+        <x:f>B11-C11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="str">
+        <x:f>IF(ABS(D11)&lt;=E11,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="str">
+        <x:v>13-Week Forecast!B46</x:v>
+      </x:c>
+      <x:c r="H11" s="15" t="str">
+        <x:v>Week 1 opening cash must link to the control panel.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="15" t="str">
+        <x:v>Opening cash roll-forward continuity</x:v>
+      </x:c>
+      <x:c r="B12" s="56" t="n">
+        <x:f>ABS('13-Week Forecast'!$C$46-'13-Week Forecast'!$B$48)+ABS('13-Week Forecast'!$D$46-'13-Week Forecast'!$C$48)+ABS('13-Week Forecast'!$E$46-'13-Week Forecast'!$D$48)+ABS('13-Week Forecast'!$F$46-'13-Week Forecast'!$E$48)+ABS('13-Week Forecast'!$G$46-'13-Week Forecast'!$F$48)+ABS('13-Week Forecast'!$H$46-'13-Week Forecast'!$G$48)+ABS('13-Week Forecast'!$I$46-'13-Week Forecast'!$H$48)+ABS('13-Week Forecast'!$J$46-'13-Week Forecast'!$I$48)+ABS('13-Week Forecast'!$K$46-'13-Week Forecast'!$J$48)+ABS('13-Week Forecast'!$L$46-'13-Week Forecast'!$K$48)+ABS('13-Week Forecast'!$M$46-'13-Week Forecast'!$L$48)+ABS('13-Week Forecast'!$N$46-'13-Week Forecast'!$M$48)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="56" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="56" t="n">
+        <x:f>B12-C12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="str">
+        <x:f>IF(ABS(D12)&lt;=E12,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="str">
+        <x:v>13-Week Forecast!C46:N46</x:v>
+      </x:c>
+      <x:c r="H12" s="15" t="str">
+        <x:v>Each weekly opening cash balance must equal the prior close.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="15" t="str">
+        <x:v>Cash receipt totals reconcile</x:v>
+      </x:c>
+      <x:c r="B13" s="57" t="n">
+        <x:f>SUM('13-Week Forecast'!$B$19:$N$19)</x:f>
+        <x:v>2338000</x:v>
+      </x:c>
+      <x:c r="C13" s="57" t="n">
+        <x:f>SUM('13-Week Forecast'!$B$10:$N$18)</x:f>
+        <x:v>2338000</x:v>
+      </x:c>
+      <x:c r="D13" s="56" t="n">
+        <x:f>B13-C13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="str">
+        <x:f>IF(ABS(D13)&lt;=E13,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="str">
+        <x:v>13-Week Forecast!B19:N19</x:v>
+      </x:c>
+      <x:c r="H13" s="15" t="str">
+        <x:v>Includes the selected-scenario receipt adjustment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="15" t="str">
+        <x:v>Cash payment totals reconcile</x:v>
+      </x:c>
+      <x:c r="B14" s="57" t="n">
+        <x:f>SUM('13-Week Forecast'!$B$43:$N$43)</x:f>
+        <x:v>2707000</x:v>
+      </x:c>
+      <x:c r="C14" s="57" t="n">
+        <x:f>SUM('13-Week Forecast'!$B$22:$N$42)</x:f>
+        <x:v>2707000</x:v>
+      </x:c>
+      <x:c r="D14" s="56" t="n">
+        <x:f>B14-C14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="str">
+        <x:f>IF(ABS(D14)&lt;=E14,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="str">
+        <x:v>13-Week Forecast!B43:N43</x:v>
+      </x:c>
+      <x:c r="H14" s="15" t="str">
+        <x:v>Includes the selected-scenario payment adjustment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="15" t="str">
+        <x:v>Closing cash equation</x:v>
+      </x:c>
+      <x:c r="B15" s="57" t="n">
+        <x:f>'13-Week Forecast'!$N$48</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="C15" s="57" t="n">
+        <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!$B$47:$N$47)</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="D15" s="56" t="n">
+        <x:f>B15-C15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="str">
+        <x:f>IF(ABS(D15)&lt;=E15,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="str">
+        <x:v>13-Week Forecast!N48</x:v>
+      </x:c>
+      <x:c r="H15" s="15" t="str">
+        <x:v>Terminal cash must equal opening cash plus cumulative movement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="15" t="str">
+        <x:v>Weekly Review linkage</x:v>
+      </x:c>
+      <x:c r="B16" s="56" t="n">
+        <x:f>ABS('Weekly Review'!$C$6-'13-Week Forecast'!$B$48)+ABS('Weekly Review'!$C$7-'13-Week Forecast'!$C$48)+ABS('Weekly Review'!$C$8-'13-Week Forecast'!$D$48)+ABS('Weekly Review'!$C$9-'13-Week Forecast'!$E$48)+ABS('Weekly Review'!$C$10-'13-Week Forecast'!$F$48)+ABS('Weekly Review'!$C$11-'13-Week Forecast'!$G$48)+ABS('Weekly Review'!$C$12-'13-Week Forecast'!$H$48)+ABS('Weekly Review'!$C$13-'13-Week Forecast'!$I$48)+ABS('Weekly Review'!$C$14-'13-Week Forecast'!$J$48)+ABS('Weekly Review'!$C$15-'13-Week Forecast'!$K$48)+ABS('Weekly Review'!$C$16-'13-Week Forecast'!$L$48)+ABS('Weekly Review'!$C$17-'13-Week Forecast'!$M$48)+ABS('Weekly Review'!$C$18-'13-Week Forecast'!$N$48)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="56" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="56" t="n">
+        <x:f>B16-C16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="str">
+        <x:f>IF(ABS(D16)&lt;=E16,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="str">
+        <x:v>Weekly Review!C6:C18</x:v>
+      </x:c>
+      <x:c r="H16" s="15" t="str">
+        <x:v>All 13 forecast closing-cash values must link to Weekly Review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="14" t="str">
         <x:v>Source item</x:v>
       </x:c>
-      <x:c r="B9" s="14" t="str">
+      <x:c r="B21" s="14" t="str">
         <x:v>Official URL</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="str">
+      <x:c r="C21" s="14" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="str">
-        <x:v>As-at date</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="str">
+      <x:c r="D21" s="14" t="str">
+        <x:v>Checked</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="str">
-        <x:v>Owner</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="49" t="str">
-        <x:v>Statutory dates and classifications require confirmation for your entity, reporting cycle and agent arrangements.</x:v>
-      </x:c>
-      <x:c r="B11" s="49"/>
-      <x:c r="C11" s="49"/>
-      <x:c r="D11" s="49"/>
-      <x:c r="E11" s="49"/>
-      <x:c r="F11" s="49"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="49"/>
-      <x:c r="B12" s="49"/>
-      <x:c r="C12" s="49"/>
-      <x:c r="D12" s="49"/>
-      <x:c r="E12" s="49"/>
-      <x:c r="F12" s="49"/>
+      <x:c r="F21" s="14" t="str">
+        <x:v>Planning treatment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="59" t="str">
+        <x:v>GST standard rate</x:v>
+      </x:c>
+      <x:c r="B22" s="60" t="str">
+        <x:v>https://www.legislation.gov.au/C2004A00446/latest/text</x:v>
+      </x:c>
+      <x:c r="C22" s="59" t="str">
+        <x:v>GST default: 10% of the value of a taxable supply.</x:v>
+      </x:c>
+      <x:c r="D22" s="59" t="str">
+        <x:v>26 August 2026</x:v>
+      </x:c>
+      <x:c r="E22" s="59" t="str">
+        <x:v>The 10% default does not decide whether a transaction is taxable, GST-free, input taxed or outside the GST system.</x:v>
+      </x:c>
+      <x:c r="F22" s="59" t="str">
+        <x:v>Keep tax classifications user-confirmed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="59" t="str">
+        <x:v>BAS due dates</x:v>
+      </x:c>
+      <x:c r="B23" s="60" t="str">
+        <x:v>https://www.ato.gov.au/businesses-and-organisations/preparing-lodging-and-paying/business-activity-statements-bas/due-dates-for-lodging-and-paying-your-bas</x:v>
+      </x:c>
+      <x:c r="C23" s="59" t="str">
+        <x:v>Monthly BAS planning pattern is generally the 21st day after the taxable period; quarterly dates are planning patterns only.</x:v>
+      </x:c>
+      <x:c r="D23" s="59" t="str">
+        <x:v>26 August 2026</x:v>
+      </x:c>
+      <x:c r="E23" s="59" t="str">
+        <x:v>The issued BAS controls. Online lodgement, registered-agent arrangements, holidays and entity circumstances can change the date.</x:v>
+      </x:c>
+      <x:c r="F23" s="59" t="str">
+        <x:v>Use issued BAS and user-entered dates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="59" t="str">
+        <x:v>Super guarantee</x:v>
+      </x:c>
+      <x:c r="B24" s="60" t="str">
+        <x:v>https://www.ato.gov.au/tax-rates-and-codes/key-superannuation-rates-and-thresholds/super-guarantee</x:v>
+      </x:c>
+      <x:c r="C24" s="59" t="str">
+        <x:v>Default SG rate: 12.0% from 1 July 2025, including 1 July 2026 to 30 June 2027.</x:v>
+      </x:c>
+      <x:c r="D24" s="59" t="str">
+        <x:v>26 August 2026</x:v>
+      </x:c>
+      <x:c r="E24" s="59" t="str">
+        <x:v>Apply only after checking worker eligibility, earnings base and special rules.</x:v>
+      </x:c>
+      <x:c r="F24" s="59" t="str">
+        <x:v>Weekly super is illustrative FP&amp;A input.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="59" t="str">
+        <x:v>Payday Super</x:v>
+      </x:c>
+      <x:c r="B25" s="60" t="str">
+        <x:v>https://softwaredevelopers.ato.gov.au/PaydaySuper</x:v>
+      </x:c>
+      <x:c r="C25" s="59" t="str">
+        <x:v>From 1 July 2026, pay SG with each pay cycle. The fund must generally receive it by the seventh business day after payday.</x:v>
+      </x:c>
+      <x:c r="D25" s="59" t="str">
+        <x:v>26 August 2026</x:v>
+      </x:c>
+      <x:c r="E25" s="59" t="str">
+        <x:v>Fund receipt, not employer submission, is the statutory timing anchor. Allow for eligible longer periods.</x:v>
+      </x:c>
+      <x:c r="F25" s="59" t="str">
+        <x:v>Illustrative forecast starts after the July 2026 transition.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="62" t="str">
+        <x:v>Disclaimer: Illustrative FP&amp;A cash-planning model only. Statutory amounts and dates are indicative assumptions, not tax, BAS, payroll, superannuation or legal advice. Entity-specific lodgement dates and tax classifications must be confirmed by the user or adviser before relying on the model or lodging or paying.</x:v>
+      </x:c>
+      <x:c r="B27" s="62"/>
+      <x:c r="C27" s="62"/>
+      <x:c r="D27" s="62"/>
+      <x:c r="E27" s="62"/>
+      <x:c r="F27" s="62"/>
+      <x:c r="G27" s="62"/>
+      <x:c r="H27" s="62"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="62"/>
+      <x:c r="B28" s="62"/>
+      <x:c r="C28" s="62"/>
+      <x:c r="D28" s="62"/>
+      <x:c r="E28" s="62"/>
+      <x:c r="F28" s="62"/>
+      <x:c r="G28" s="62"/>
+      <x:c r="H28" s="62"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="62"/>
+      <x:c r="B29" s="62"/>
+      <x:c r="C29" s="62"/>
+      <x:c r="D29" s="62"/>
+      <x:c r="E29" s="62"/>
+      <x:c r="F29" s="62"/>
+      <x:c r="G29" s="62"/>
+      <x:c r="H29" s="62"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="A6:H6"/>
-    <x:mergeCell ref="A11:F12"/>
+    <x:mergeCell ref="A27:H29"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="B4:B4">
+    <x:cfRule type="expression" dxfId="11" priority="1">
+      <x:formula>B4="PASS"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="12" priority="2">
+      <x:formula>B4="FAIL"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="E4:E4">
+    <x:cfRule type="expression" dxfId="13" priority="3">
+      <x:formula>E4="ACTION REQUIRED"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="14" priority="4">
+      <x:formula>E4="WATCH"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="15" priority="5">
+      <x:formula>E4="HEALTHY"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F8:F16">
+    <x:cfRule type="expression" dxfId="16" priority="6">
+      <x:formula>F8="PASS"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="17" priority="7">
+      <x:formula>F8="FAIL"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R6365591222b34de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R63a198b070c74297"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R3c5e1c3bfbe94158"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rbc435d3534754d31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="Raf7ca443aec049a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R6513339d280742ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R5f02dd2468644489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Ra885b4ee6f8f4aba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R3af6af053bd54b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rfab8b815b5ca4192"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R872022763bea412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R7e8e625aeb7a449f"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -20,10 +20,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={98FAA047-B01D-5348-2BF1-D894601FC806}</x:author>
-    <x:author>tc={BE1B932E-612F-4047-F56F-9CDCA82CBB32}</x:author>
-    <x:author>tc={B3C5A793-7724-FDA4-8C59-D102B1FE2C65}</x:author>
-    <x:author>tc={736F7184-3EC3-9C52-7FDB-69574353E070}</x:author>
+    <x:author>tc={9630C31D-6C15-3DCD-6FEC-FFF0920387C0}</x:author>
+    <x:author>tc={78DC6C45-5048-5652-71C1-FFC94265B0A0}</x:author>
+    <x:author>tc={CC57C4BB-274F-5D5B-93F2-2C6F5FC0530F}</x:author>
+    <x:author>tc={B28E83DE-AB9D-F6A0-5F2B-175B1910D78A}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -746,6 +746,7 @@
     <c:plotArea>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -906,7 +907,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref5028a0a2fe4326"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2c40855584474044"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -936,7 +937,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8ac1622332704bbf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R41b1b7debcf1437a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -947,7 +948,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}"/>
+  <xltc:person displayName="User" id="{951688C4-7DF6-4493-9F59-4D169F48BCE3}"/>
 </xltc:personList>
 </file>
 
@@ -1144,16 +1145,16 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-26T13:42:51.005" personId="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}" id="{98FAA047-B01D-5348-2BF1-D894601FC806}">
+  <xltc:threadedComment ref="B18" dT="2026-08-26T13:49:48.939" personId="{951688C4-7DF6-4493-9F59-4D169F48BCE3}" id="{9630C31D-6C15-3DCD-6FEC-FFF0920387C0}">
     <xltc:text>Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B42" dT="2026-08-26T13:42:51.005" personId="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}" id="{BE1B932E-612F-4047-F56F-9CDCA82CBB32}">
+  <xltc:threadedComment ref="B42" dT="2026-08-26T13:49:48.939" personId="{951688C4-7DF6-4493-9F59-4D169F48BCE3}" id="{78DC6C45-5048-5652-71C1-FFC94265B0A0}">
     <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B34" dT="2026-08-26T13:42:51.005" personId="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}" id="{B3C5A793-7724-FDA4-8C59-D102B1FE2C65}">
+  <xltc:threadedComment ref="B34" dT="2026-08-26T13:49:48.939" personId="{951688C4-7DF6-4493-9F59-4D169F48BCE3}" id="{CC57C4BB-274F-5D5B-93F2-2C6F5FC0530F}">
     <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B35" dT="2026-08-26T13:42:51.005" personId="{40D6A7C4-057F-4C0F-94B0-D08E14A712BD}" id="{736F7184-3EC3-9C52-7FDB-69574353E070}">
+  <xltc:threadedComment ref="B35" dT="2026-08-26T13:49:48.939" personId="{951688C4-7DF6-4493-9F59-4D169F48BCE3}" id="{B28E83DE-AB9D-F6A0-5F2B-175B1910D78A}">
     <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -2261,7 +2262,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fce3a2c5625401a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R242e8ccac0354ed6"/>
 </x:worksheet>
 </file>
 
@@ -4777,7 +4778,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cebc129644548f1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc4c8ec6ea244832"/>
 </x:worksheet>
 </file>
 
@@ -5543,7 +5544,7 @@
         <x:v>26 August 2026</x:v>
       </x:c>
       <x:c r="E23" s="59" t="str">
-        <x:v>The issued BAS controls. Online lodgement, registered-agent arrangements, holidays and entity circumstances can change the date.</x:v>
+        <x:v>The issued or entity-specific BAS due date controls. Online lodgement, registered-agent arrangements, holidays and entity circumstances can change the date.</x:v>
       </x:c>
       <x:c r="F23" s="59" t="str">
         <x:v>Use issued BAS and user-entered dates.</x:v>

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R5f02dd2468644489"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Ra885b4ee6f8f4aba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R3af6af053bd54b31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rfab8b815b5ca4192"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R872022763bea412f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R7e8e625aeb7a449f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rc6463e792faf46f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Ra5bf1840a7a849d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R569615fbea9c4417"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R8549e76a58c646a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R4b268d1345624768"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R7ad570235965495b"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -20,10 +20,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={9630C31D-6C15-3DCD-6FEC-FFF0920387C0}</x:author>
-    <x:author>tc={78DC6C45-5048-5652-71C1-FFC94265B0A0}</x:author>
-    <x:author>tc={CC57C4BB-274F-5D5B-93F2-2C6F5FC0530F}</x:author>
-    <x:author>tc={B28E83DE-AB9D-F6A0-5F2B-175B1910D78A}</x:author>
+    <x:author>tc={6150C06D-0457-5C86-C3C0-AE0049FE548F}</x:author>
+    <x:author>tc={10FFFD00-D8ED-6C1E-A4F9-A29DB51051D7}</x:author>
+    <x:author>tc={BDF069F6-163C-548D-0C24-D5CD3190C6B0}</x:author>
+    <x:author>tc={31BA30AE-D302-55C2-C616-5D8A9C3C43C7}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -907,7 +907,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2c40855584474044"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0f4d8477e6a94356"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -937,7 +937,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R41b1b7debcf1437a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R496d2c41286a4acb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -948,7 +948,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{951688C4-7DF6-4493-9F59-4D169F48BCE3}"/>
+  <xltc:person displayName="User" id="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}"/>
 </xltc:personList>
 </file>
 
@@ -1145,16 +1145,16 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-26T13:49:48.939" personId="{951688C4-7DF6-4493-9F59-4D169F48BCE3}" id="{9630C31D-6C15-3DCD-6FEC-FFF0920387C0}">
+  <xltc:threadedComment ref="B18" dT="2026-08-26T14:16:10.492" personId="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}" id="{6150C06D-0457-5C86-C3C0-AE0049FE548F}">
     <xltc:text>Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B42" dT="2026-08-26T13:49:48.939" personId="{951688C4-7DF6-4493-9F59-4D169F48BCE3}" id="{78DC6C45-5048-5652-71C1-FFC94265B0A0}">
+  <xltc:threadedComment ref="B42" dT="2026-08-26T14:16:10.492" personId="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}" id="{10FFFD00-D8ED-6C1E-A4F9-A29DB51051D7}">
     <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B34" dT="2026-08-26T13:49:48.939" personId="{951688C4-7DF6-4493-9F59-4D169F48BCE3}" id="{CC57C4BB-274F-5D5B-93F2-2C6F5FC0530F}">
+  <xltc:threadedComment ref="B34" dT="2026-08-26T14:16:10.492" personId="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}" id="{BDF069F6-163C-548D-0C24-D5CD3190C6B0}">
     <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B35" dT="2026-08-26T13:49:48.939" personId="{951688C4-7DF6-4493-9F59-4D169F48BCE3}" id="{B28E83DE-AB9D-F6A0-5F2B-175B1910D78A}">
+  <xltc:threadedComment ref="B35" dT="2026-08-26T14:16:10.492" personId="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}" id="{31BA30AE-D302-55C2-C616-5D8A9C3C43C7}">
     <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -2262,7 +2262,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R242e8ccac0354ed6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64b1483b845a4cf9"/>
 </x:worksheet>
 </file>
 
@@ -2273,7 +2273,7 @@
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
   </x:cols>
@@ -4778,7 +4778,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc4c8ec6ea244832"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03cec6b27bdd4e44"/>
 </x:worksheet>
 </file>
 

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rc6463e792faf46f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Ra5bf1840a7a849d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R569615fbea9c4417"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R8549e76a58c646a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R4b268d1345624768"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R7ad570235965495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Re205b0f6e9714c7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R626c134bb200410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="Rbf718284d1eb44d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rd31ed432d30342c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R3eeb8bd2f859490e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="Rb45787a5c4bf4fa8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -20,10 +20,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={6150C06D-0457-5C86-C3C0-AE0049FE548F}</x:author>
-    <x:author>tc={10FFFD00-D8ED-6C1E-A4F9-A29DB51051D7}</x:author>
-    <x:author>tc={BDF069F6-163C-548D-0C24-D5CD3190C6B0}</x:author>
-    <x:author>tc={31BA30AE-D302-55C2-C616-5D8A9C3C43C7}</x:author>
+    <x:author>tc={69516E80-B86B-5485-9815-F1D6B4F4A1A6}</x:author>
+    <x:author>tc={218FD7FC-83FB-9E7C-4BEE-9EA002F59077}</x:author>
+    <x:author>tc={8121AE60-30EE-0278-CF63-EC455EEFB906}</x:author>
+    <x:author>tc={E5346B2C-4D96-0537-D519-CF76582AE940}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -136,12 +136,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="12"/>
-      <x:color rgb="FF04001F"/>
-      <x:name val="Aptos"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FF2B2733"/>
       <x:name val="Aptos"/>
@@ -156,6 +150,12 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FF04001F"/>
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
@@ -208,12 +208,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFFF"/>
+        <x:fgColor rgb="FFB1AFAD"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFB1AFAD"/>
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -228,7 +228,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="63">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -269,44 +269,28 @@
     <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="202" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -332,11 +316,239 @@
     <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="18">
+  <x:dxfs count="28">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5C2D91"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDED9E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5C2D91"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDED9E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:b/>
@@ -422,116 +634,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFE2F0D9"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFC00000"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFCE4D6"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF5C2D91"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFDED9E8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF008000"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFE2F0D9"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF008000"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFE2F0D9"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFC00000"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFCE4D6"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFC00000"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFCE4D6"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF5C2D91"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFDED9E8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF008000"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFE2F0D9"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FF008000"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFE2F0D9"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFC00000"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -907,7 +1009,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0f4d8477e6a94356"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4cb8a91667d04fd2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -937,7 +1039,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R496d2c41286a4acb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6e1022fa26714d0b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -948,7 +1050,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}"/>
+  <xltc:person displayName="User" id="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}"/>
 </xltc:personList>
 </file>
 
@@ -1145,16 +1247,16 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-26T14:16:10.492" personId="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}" id="{6150C06D-0457-5C86-C3C0-AE0049FE548F}">
+  <xltc:threadedComment ref="B18" dT="2026-08-26T14:43:45.786" personId="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}" id="{69516E80-B86B-5485-9815-F1D6B4F4A1A6}">
     <xltc:text>Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B42" dT="2026-08-26T14:16:10.492" personId="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}" id="{10FFFD00-D8ED-6C1E-A4F9-A29DB51051D7}">
+  <xltc:threadedComment ref="B42" dT="2026-08-26T14:43:45.786" personId="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}" id="{218FD7FC-83FB-9E7C-4BEE-9EA002F59077}">
     <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B34" dT="2026-08-26T14:16:10.492" personId="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}" id="{BDF069F6-163C-548D-0C24-D5CD3190C6B0}">
+  <xltc:threadedComment ref="B34" dT="2026-08-26T14:43:45.786" personId="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}" id="{8121AE60-30EE-0278-CF63-EC455EEFB906}">
     <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B35" dT="2026-08-26T14:16:10.492" personId="{1DA5EA16-2278-4414-9D93-50966BD9A7B8}" id="{31BA30AE-D302-55C2-C616-5D8A9C3C43C7}">
+  <xltc:threadedComment ref="B35" dT="2026-08-26T14:43:45.786" personId="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}" id="{E5346B2C-4D96-0537-D519-CF76582AE940}">
     <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -1215,10 +1317,10 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>1.0 scaffold</x:v>
+        <x:v>Release 1.0</x:v>
       </x:c>
       <x:c r="D6" s="23" t="str">
-        <x:v>Quick links</x:v>
+        <x:v>Workbook sheets</x:v>
       </x:c>
       <x:c r="E6" s="23"/>
       <x:c r="F6" s="23"/>
@@ -1232,9 +1334,8 @@
       <x:c r="B7" s="11" t="n">
         <x:v>46260</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="e">
-        <x:f>HYPERLINK("#'Dashboard'!A1","Dashboard")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=#'Dashboard'!A1, friendlyName=Dashboard</x:v>
+      <x:c r="D7" s="1" t="str">
+        <x:v>Dashboard</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1244,9 +1345,8 @@
       <x:c r="B8" t="str">
         <x:v>AUD</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="e">
-        <x:f>HYPERLINK("#'Assumptions'!A1","Assumptions")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=#'Assumptions'!A1, friendlyName=Assumptions</x:v>
+      <x:c r="D8" s="1" t="str">
+        <x:v>Assumptions</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1256,9 +1356,8 @@
       <x:c r="B9" t="str">
         <x:v>Whole dollars</x:v>
       </x:c>
-      <x:c r="D9" s="12" t="e">
-        <x:f>HYPERLINK("#'13-Week Forecast'!A1","13-Week Forecast")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=#'13-Week Forecast'!A1, friendlyName=13-Week Forecast</x:v>
+      <x:c r="D9" s="1" t="str">
+        <x:v>13-Week Forecast</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1269,15 +1368,13 @@
         <x:f>'Assumptions'!$B$12</x:f>
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="e">
-        <x:f>HYPERLINK("#'Weekly Review'!A1","Weekly Review")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=#'Weekly Review'!A1, friendlyName=Weekly Review</x:v>
+      <x:c r="D10" s="1" t="str">
+        <x:v>Weekly Review</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="D11" s="12" t="e">
-        <x:f>HYPERLINK("#'Checks &amp; Sources'!A1","Checks &amp; Sources")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=#'Checks &amp; Sources'!A1, friendlyName=Checks &amp; Sources</x:v>
+      <x:c r="D11" s="1" t="str">
+        <x:v>Checks &amp; Sources</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1321,7 +1418,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B16" s="15" t="str">
-        <x:v>Record actual results, actions and owners in Weekly Review.</x:v>
+        <x:v>Record actual receipts, payments, closing cash and owner commentary in Weekly Review.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1421,16 +1518,16 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
@@ -1518,83 +1615,97 @@
         <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
         <x:v>06 Sep</x:v>
       </x:c>
-      <x:c r="Q5" s="36" t="n">
+      <x:c r="Q5" s="38" t="n">
         <x:f>'13-Week Forecast'!B$48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="R5" s="36" t="n">
+      <x:c r="R5" s="38" t="n">
         <x:f>'13-Week Forecast'!B$49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="58" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B6" s="30" t="str">
-        <x:v>Opening cash</x:v>
-      </x:c>
-      <x:c r="C6" s="30" t="str">
+      <x:c r="B6" s="58" t="str">
+        <x:v>Week 13 closing cash</x:v>
+      </x:c>
+      <x:c r="C6" s="58" t="str">
         <x:v>Lowest closing cash</x:v>
       </x:c>
-      <x:c r="D6" s="30" t="str">
+      <x:c r="D6" s="58" t="str">
+        <x:v>Minimum cash buffer</x:v>
+      </x:c>
+      <x:c r="E6" s="58" t="str">
         <x:v>Minimum headroom</x:v>
       </x:c>
-      <x:c r="E6" s="30" t="str">
+      <x:c r="F6" s="58" t="str">
         <x:v>Weeks below buffer</x:v>
       </x:c>
-      <x:c r="F6" s="30" t="str">
+      <x:c r="G6" s="58" t="str">
+        <x:v>13-week net cash change</x:v>
+      </x:c>
+      <x:c r="H6" s="58" t="str">
         <x:v>Week of lowest cash</x:v>
       </x:c>
-      <x:c r="G6" s="30" t="str">
+      <x:c r="I6" s="58" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="H6" s="30" t="str">
+      <x:c r="J6" s="58" t="str">
         <x:v>LIQUIDITY STATUS</x:v>
       </x:c>
       <x:c r="P6" s="11" t="str">
         <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
         <x:v>13 Sep</x:v>
       </x:c>
-      <x:c r="Q6" s="36" t="n">
+      <x:c r="Q6" s="38" t="n">
         <x:f>'13-Week Forecast'!C$48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="R6" s="36" t="n">
+      <x:c r="R6" s="38" t="n">
         <x:f>'13-Week Forecast'!C$49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
+      <x:c r="A7" s="61" t="str">
         <x:f>'Assumptions'!$B$12</x:f>
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="B7" s="34" t="n">
-        <x:f>'Assumptions'!$B$10</x:f>
-        <x:v>400000</x:v>
-      </x:c>
-      <x:c r="C7" s="34" t="n">
+      <x:c r="B7" s="62" t="n">
+        <x:f>'13-Week Forecast'!$N$48</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="C7" s="62" t="n">
         <x:f>MIN('13-Week Forecast'!$B$48:$N$48)</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D7" s="34" t="n">
+      <x:c r="D7" s="62" t="n">
+        <x:f>'Assumptions'!$B$11</x:f>
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="E7" s="62" t="n">
         <x:f>MIN('13-Week Forecast'!$B$50:$N$50)</x:f>
         <x:v>-69000</x:v>
       </x:c>
-      <x:c r="E7" s="33" t="n">
+      <x:c r="F7" s="61" t="n">
         <x:f>COUNTIF('13-Week Forecast'!$B$50:$N$50,"&lt;0")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F7" s="35" t="n">
+      <x:c r="G7" s="62" t="n">
+        <x:f>SUM('13-Week Forecast'!$B$47:$N$47)</x:f>
+        <x:v>-369000</x:v>
+      </x:c>
+      <x:c r="H7" s="63" t="n">
         <x:f>INDEX('13-Week Forecast'!$B$6:$N$6,1,MATCH(C7,'13-Week Forecast'!$B$48:$N$48,0))</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="G7" s="33" t="str">
+      <x:c r="I7" s="61" t="str">
         <x:f>'Checks &amp; Sources'!$B$4</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="H7" s="33" t="str">
+      <x:c r="J7" s="61" t="str">
         <x:f>'Checks &amp; Sources'!$E$4</x:f>
         <x:v>ACTION REQUIRED</x:v>
       </x:c>
@@ -1602,11 +1713,11 @@
         <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
         <x:v>20 Sep</x:v>
       </x:c>
-      <x:c r="Q7" s="36" t="n">
+      <x:c r="Q7" s="38" t="n">
         <x:f>'13-Week Forecast'!D$48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="R7" s="36" t="n">
+      <x:c r="R7" s="38" t="n">
         <x:f>'13-Week Forecast'!D$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1616,11 +1727,11 @@
         <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
         <x:v>27 Sep</x:v>
       </x:c>
-      <x:c r="Q8" s="36" t="n">
+      <x:c r="Q8" s="38" t="n">
         <x:f>'13-Week Forecast'!E$48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="R8" s="36" t="n">
+      <x:c r="R8" s="38" t="n">
         <x:f>'13-Week Forecast'!E$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1630,11 +1741,11 @@
         <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
         <x:v>04 Oct</x:v>
       </x:c>
-      <x:c r="Q9" s="36" t="n">
+      <x:c r="Q9" s="38" t="n">
         <x:f>'13-Week Forecast'!F$48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="R9" s="36" t="n">
+      <x:c r="R9" s="38" t="n">
         <x:f>'13-Week Forecast'!F$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1644,11 +1755,11 @@
         <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
         <x:v>11 Oct</x:v>
       </x:c>
-      <x:c r="Q10" s="36" t="n">
+      <x:c r="Q10" s="38" t="n">
         <x:f>'13-Week Forecast'!G$48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="R10" s="36" t="n">
+      <x:c r="R10" s="38" t="n">
         <x:f>'13-Week Forecast'!G$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1673,11 +1784,11 @@
         <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
         <x:v>18 Oct</x:v>
       </x:c>
-      <x:c r="Q11" s="36" t="n">
+      <x:c r="Q11" s="38" t="n">
         <x:f>'13-Week Forecast'!H$48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="R11" s="36" t="n">
+      <x:c r="R11" s="38" t="n">
         <x:f>'13-Week Forecast'!H$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1687,15 +1798,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B12" s="37" t="n">
+      <x:c r="B12" s="46" t="n">
         <x:f>'13-Week Forecast'!B$6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C12" s="38" t="n">
+      <x:c r="C12" s="43" t="n">
         <x:f>'13-Week Forecast'!B$48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="D12" s="38" t="n">
+      <x:c r="D12" s="43" t="n">
         <x:f>'13-Week Forecast'!B$50</x:f>
         <x:v>258000</x:v>
       </x:c>
@@ -1707,11 +1818,11 @@
         <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
         <x:v>25 Oct</x:v>
       </x:c>
-      <x:c r="Q12" s="36" t="n">
+      <x:c r="Q12" s="38" t="n">
         <x:f>'13-Week Forecast'!I$48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="R12" s="36" t="n">
+      <x:c r="R12" s="38" t="n">
         <x:f>'13-Week Forecast'!I$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1721,15 +1832,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B13" s="37" t="n">
+      <x:c r="B13" s="46" t="n">
         <x:f>'13-Week Forecast'!C$6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="C13" s="38" t="n">
+      <x:c r="C13" s="43" t="n">
         <x:f>'13-Week Forecast'!C$48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="D13" s="38" t="n">
+      <x:c r="D13" s="43" t="n">
         <x:f>'13-Week Forecast'!C$50</x:f>
         <x:v>249000</x:v>
       </x:c>
@@ -1741,11 +1852,11 @@
         <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
         <x:v>01 Nov</x:v>
       </x:c>
-      <x:c r="Q13" s="36" t="n">
+      <x:c r="Q13" s="38" t="n">
         <x:f>'13-Week Forecast'!J$48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="R13" s="36" t="n">
+      <x:c r="R13" s="38" t="n">
         <x:f>'13-Week Forecast'!J$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1755,15 +1866,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B14" s="37" t="n">
+      <x:c r="B14" s="46" t="n">
         <x:f>'13-Week Forecast'!D$6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="C14" s="38" t="n">
+      <x:c r="C14" s="43" t="n">
         <x:f>'13-Week Forecast'!D$48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="D14" s="38" t="n">
+      <x:c r="D14" s="43" t="n">
         <x:f>'13-Week Forecast'!D$50</x:f>
         <x:v>225000</x:v>
       </x:c>
@@ -1775,11 +1886,11 @@
         <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
         <x:v>08 Nov</x:v>
       </x:c>
-      <x:c r="Q14" s="36" t="n">
+      <x:c r="Q14" s="38" t="n">
         <x:f>'13-Week Forecast'!K$48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="R14" s="36" t="n">
+      <x:c r="R14" s="38" t="n">
         <x:f>'13-Week Forecast'!K$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1789,15 +1900,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B15" s="37" t="n">
+      <x:c r="B15" s="46" t="n">
         <x:f>'13-Week Forecast'!E$6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="C15" s="38" t="n">
+      <x:c r="C15" s="43" t="n">
         <x:f>'13-Week Forecast'!E$48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="D15" s="38" t="n">
+      <x:c r="D15" s="43" t="n">
         <x:f>'13-Week Forecast'!E$50</x:f>
         <x:v>193000</x:v>
       </x:c>
@@ -1809,11 +1920,11 @@
         <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
         <x:v>15 Nov</x:v>
       </x:c>
-      <x:c r="Q15" s="36" t="n">
+      <x:c r="Q15" s="38" t="n">
         <x:f>'13-Week Forecast'!L$48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="R15" s="36" t="n">
+      <x:c r="R15" s="38" t="n">
         <x:f>'13-Week Forecast'!L$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1823,15 +1934,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B16" s="37" t="n">
+      <x:c r="B16" s="46" t="n">
         <x:f>'13-Week Forecast'!F$6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="C16" s="38" t="n">
+      <x:c r="C16" s="43" t="n">
         <x:f>'13-Week Forecast'!F$48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="D16" s="38" t="n">
+      <x:c r="D16" s="43" t="n">
         <x:f>'13-Week Forecast'!F$50</x:f>
         <x:v>101000</x:v>
       </x:c>
@@ -1843,11 +1954,11 @@
         <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
         <x:v>22 Nov</x:v>
       </x:c>
-      <x:c r="Q16" s="36" t="n">
+      <x:c r="Q16" s="38" t="n">
         <x:f>'13-Week Forecast'!M$48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="R16" s="36" t="n">
+      <x:c r="R16" s="38" t="n">
         <x:f>'13-Week Forecast'!M$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1857,15 +1968,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B17" s="37" t="n">
+      <x:c r="B17" s="46" t="n">
         <x:f>'13-Week Forecast'!G$6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="C17" s="38" t="n">
+      <x:c r="C17" s="43" t="n">
         <x:f>'13-Week Forecast'!G$48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="D17" s="38" t="n">
+      <x:c r="D17" s="43" t="n">
         <x:f>'13-Week Forecast'!G$50</x:f>
         <x:v>33000</x:v>
       </x:c>
@@ -1877,11 +1988,11 @@
         <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
         <x:v>29 Nov</x:v>
       </x:c>
-      <x:c r="Q17" s="36" t="n">
+      <x:c r="Q17" s="38" t="n">
         <x:f>'13-Week Forecast'!N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="R17" s="36" t="n">
+      <x:c r="R17" s="38" t="n">
         <x:f>'13-Week Forecast'!N$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1891,15 +2002,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B18" s="37" t="n">
+      <x:c r="B18" s="46" t="n">
         <x:f>'13-Week Forecast'!H$6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="C18" s="38" t="n">
+      <x:c r="C18" s="43" t="n">
         <x:f>'13-Week Forecast'!H$48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="D18" s="38" t="n">
+      <x:c r="D18" s="43" t="n">
         <x:f>'13-Week Forecast'!H$50</x:f>
         <x:v>117000</x:v>
       </x:c>
@@ -1913,15 +2024,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B19" s="37" t="n">
+      <x:c r="B19" s="46" t="n">
         <x:f>'13-Week Forecast'!I$6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="C19" s="38" t="n">
+      <x:c r="C19" s="43" t="n">
         <x:f>'13-Week Forecast'!I$48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="D19" s="38" t="n">
+      <x:c r="D19" s="43" t="n">
         <x:f>'13-Week Forecast'!I$50</x:f>
         <x:v>60000</x:v>
       </x:c>
@@ -1935,15 +2046,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B20" s="37" t="n">
+      <x:c r="B20" s="46" t="n">
         <x:f>'13-Week Forecast'!J$6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="C20" s="38" t="n">
+      <x:c r="C20" s="43" t="n">
         <x:f>'13-Week Forecast'!J$48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="D20" s="38" t="n">
+      <x:c r="D20" s="43" t="n">
         <x:f>'13-Week Forecast'!J$50</x:f>
         <x:v>17000</x:v>
       </x:c>
@@ -1957,15 +2068,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B21" s="37" t="n">
+      <x:c r="B21" s="46" t="n">
         <x:f>'13-Week Forecast'!K$6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="C21" s="38" t="n">
+      <x:c r="C21" s="43" t="n">
         <x:f>'13-Week Forecast'!K$48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="D21" s="38" t="n">
+      <x:c r="D21" s="43" t="n">
         <x:f>'13-Week Forecast'!K$50</x:f>
         <x:v>37000</x:v>
       </x:c>
@@ -1988,15 +2099,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B22" s="37" t="n">
+      <x:c r="B22" s="46" t="n">
         <x:f>'13-Week Forecast'!L$6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="C22" s="38" t="n">
+      <x:c r="C22" s="43" t="n">
         <x:f>'13-Week Forecast'!L$48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="D22" s="38" t="n">
+      <x:c r="D22" s="43" t="n">
         <x:f>'13-Week Forecast'!L$50</x:f>
         <x:v>-1000</x:v>
       </x:c>
@@ -2008,11 +2119,11 @@
         <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
         <x:v>06 Sep</x:v>
       </x:c>
-      <x:c r="Q22" s="36" t="n">
+      <x:c r="Q22" s="38" t="n">
         <x:f>'13-Week Forecast'!B$19</x:f>
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="R22" s="36" t="n">
+      <x:c r="R22" s="38" t="n">
         <x:f>'13-Week Forecast'!B$43</x:f>
         <x:v>212000</x:v>
       </x:c>
@@ -2022,15 +2133,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B23" s="37" t="n">
+      <x:c r="B23" s="46" t="n">
         <x:f>'13-Week Forecast'!M$6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="C23" s="38" t="n">
+      <x:c r="C23" s="43" t="n">
         <x:f>'13-Week Forecast'!M$48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="D23" s="38" t="n">
+      <x:c r="D23" s="43" t="n">
         <x:f>'13-Week Forecast'!M$50</x:f>
         <x:v>-18000</x:v>
       </x:c>
@@ -2042,11 +2153,11 @@
         <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
         <x:v>13 Sep</x:v>
       </x:c>
-      <x:c r="Q23" s="36" t="n">
+      <x:c r="Q23" s="38" t="n">
         <x:f>'13-Week Forecast'!C$19</x:f>
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="R23" s="36" t="n">
+      <x:c r="R23" s="38" t="n">
         <x:f>'13-Week Forecast'!C$43</x:f>
         <x:v>178000</x:v>
       </x:c>
@@ -2056,15 +2167,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B24" s="37" t="n">
+      <x:c r="B24" s="46" t="n">
         <x:f>'13-Week Forecast'!N$6</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="C24" s="38" t="n">
+      <x:c r="C24" s="43" t="n">
         <x:f>'13-Week Forecast'!N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D24" s="38" t="n">
+      <x:c r="D24" s="43" t="n">
         <x:f>'13-Week Forecast'!N$50</x:f>
         <x:v>-69000</x:v>
       </x:c>
@@ -2076,11 +2187,11 @@
         <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
         <x:v>20 Sep</x:v>
       </x:c>
-      <x:c r="Q24" s="36" t="n">
+      <x:c r="Q24" s="38" t="n">
         <x:f>'13-Week Forecast'!D$19</x:f>
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="R24" s="36" t="n">
+      <x:c r="R24" s="38" t="n">
         <x:f>'13-Week Forecast'!D$43</x:f>
         <x:v>182000</x:v>
       </x:c>
@@ -2090,11 +2201,11 @@
         <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
         <x:v>27 Sep</x:v>
       </x:c>
-      <x:c r="Q25" s="36" t="n">
+      <x:c r="Q25" s="38" t="n">
         <x:f>'13-Week Forecast'!E$19</x:f>
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="R25" s="36" t="n">
+      <x:c r="R25" s="38" t="n">
         <x:f>'13-Week Forecast'!E$43</x:f>
         <x:v>179000</x:v>
       </x:c>
@@ -2104,11 +2215,11 @@
         <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
         <x:v>04 Oct</x:v>
       </x:c>
-      <x:c r="Q26" s="36" t="n">
+      <x:c r="Q26" s="38" t="n">
         <x:f>'13-Week Forecast'!F$19</x:f>
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="R26" s="36" t="n">
+      <x:c r="R26" s="38" t="n">
         <x:f>'13-Week Forecast'!F$43</x:f>
         <x:v>232000</x:v>
       </x:c>
@@ -2118,11 +2229,11 @@
         <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
         <x:v>11 Oct</x:v>
       </x:c>
-      <x:c r="Q27" s="36" t="n">
+      <x:c r="Q27" s="38" t="n">
         <x:f>'13-Week Forecast'!G$19</x:f>
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="R27" s="36" t="n">
+      <x:c r="R27" s="38" t="n">
         <x:f>'13-Week Forecast'!G$43</x:f>
         <x:v>209000</x:v>
       </x:c>
@@ -2132,11 +2243,11 @@
         <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
         <x:v>18 Oct</x:v>
       </x:c>
-      <x:c r="Q28" s="36" t="n">
+      <x:c r="Q28" s="38" t="n">
         <x:f>'13-Week Forecast'!H$19</x:f>
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="R28" s="36" t="n">
+      <x:c r="R28" s="38" t="n">
         <x:f>'13-Week Forecast'!H$43</x:f>
         <x:v>197000</x:v>
       </x:c>
@@ -2146,11 +2257,11 @@
         <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
         <x:v>25 Oct</x:v>
       </x:c>
-      <x:c r="Q29" s="36" t="n">
+      <x:c r="Q29" s="38" t="n">
         <x:f>'13-Week Forecast'!I$19</x:f>
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="R29" s="36" t="n">
+      <x:c r="R29" s="38" t="n">
         <x:f>'13-Week Forecast'!I$43</x:f>
         <x:v>192000</x:v>
       </x:c>
@@ -2160,11 +2271,11 @@
         <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
         <x:v>01 Nov</x:v>
       </x:c>
-      <x:c r="Q30" s="36" t="n">
+      <x:c r="Q30" s="38" t="n">
         <x:f>'13-Week Forecast'!J$19</x:f>
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="R30" s="36" t="n">
+      <x:c r="R30" s="38" t="n">
         <x:f>'13-Week Forecast'!J$43</x:f>
         <x:v>307000</x:v>
       </x:c>
@@ -2174,11 +2285,11 @@
         <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
         <x:v>08 Nov</x:v>
       </x:c>
-      <x:c r="Q31" s="36" t="n">
+      <x:c r="Q31" s="38" t="n">
         <x:f>'13-Week Forecast'!K$19</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="R31" s="36" t="n">
+      <x:c r="R31" s="38" t="n">
         <x:f>'13-Week Forecast'!K$43</x:f>
         <x:v>229000</x:v>
       </x:c>
@@ -2188,11 +2299,11 @@
         <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
         <x:v>15 Nov</x:v>
       </x:c>
-      <x:c r="Q32" s="36" t="n">
+      <x:c r="Q32" s="38" t="n">
         <x:f>'13-Week Forecast'!L$19</x:f>
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="R32" s="36" t="n">
+      <x:c r="R32" s="38" t="n">
         <x:f>'13-Week Forecast'!L$43</x:f>
         <x:v>192000</x:v>
       </x:c>
@@ -2202,11 +2313,11 @@
         <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
         <x:v>22 Nov</x:v>
       </x:c>
-      <x:c r="Q33" s="36" t="n">
+      <x:c r="Q33" s="38" t="n">
         <x:f>'13-Week Forecast'!M$19</x:f>
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="R33" s="36" t="n">
+      <x:c r="R33" s="38" t="n">
         <x:f>'13-Week Forecast'!M$43</x:f>
         <x:v>179000</x:v>
       </x:c>
@@ -2216,11 +2327,11 @@
         <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
         <x:v>29 Nov</x:v>
       </x:c>
-      <x:c r="Q34" s="36" t="n">
+      <x:c r="Q34" s="38" t="n">
         <x:f>'13-Week Forecast'!N$19</x:f>
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="R34" s="36" t="n">
+      <x:c r="R34" s="38" t="n">
         <x:f>'13-Week Forecast'!N$43</x:f>
         <x:v>219000</x:v>
       </x:c>
@@ -2231,38 +2342,38 @@
     <x:mergeCell ref="A2:R2"/>
     <x:mergeCell ref="A4:R4"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="G7:G7">
-    <x:cfRule type="expression" dxfId="0" priority="1">
-      <x:formula>G7="PASS"</x:formula>
+  <x:conditionalFormatting sqref="I7:I7">
+    <x:cfRule type="expression" dxfId="20" priority="1">
+      <x:formula>I7="PASS"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="1" priority="2">
-      <x:formula>G7="FAIL"</x:formula>
+    <x:cfRule type="expression" dxfId="21" priority="2">
+      <x:formula>I7="FAIL"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="H7:H7">
-    <x:cfRule type="expression" dxfId="2" priority="3">
-      <x:formula>H7="ACTION REQUIRED"</x:formula>
+  <x:conditionalFormatting sqref="J7:J7">
+    <x:cfRule type="expression" dxfId="22" priority="3">
+      <x:formula>J7="ACTION REQUIRED"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="3" priority="4">
-      <x:formula>H7="WATCH"</x:formula>
+    <x:cfRule type="expression" dxfId="23" priority="4">
+      <x:formula>J7="WATCH"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="4" priority="5">
-      <x:formula>H7="HEALTHY"</x:formula>
+    <x:cfRule type="expression" dxfId="24" priority="5">
+      <x:formula>J7="OK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E12:E24">
-    <x:cfRule type="expression" dxfId="5" priority="6">
+    <x:cfRule type="expression" dxfId="25" priority="6">
       <x:formula>E12="BELOW BUFFER"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="6" priority="7">
+    <x:cfRule type="expression" dxfId="26" priority="7">
       <x:formula>E12="WATCH"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="7" priority="8">
+    <x:cfRule type="expression" dxfId="27" priority="8">
       <x:formula>E12="OK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64b1483b845a4cf9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d7a0950c2c04bb1"/>
 </x:worksheet>
 </file>
 
@@ -2310,7 +2421,7 @@
       <x:c r="A5" t="str">
         <x:v>Business name</x:v>
       </x:c>
-      <x:c r="B5" s="40" t="str">
+      <x:c r="B5" s="28" t="str">
         <x:v>Illustrative Australian business</x:v>
       </x:c>
     </x:row>
@@ -2318,7 +2429,7 @@
       <x:c r="A6" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="B6" s="40" t="str">
+      <x:c r="B6" s="28" t="str">
         <x:v>AUD</x:v>
       </x:c>
     </x:row>
@@ -2326,7 +2437,7 @@
       <x:c r="A7" t="str">
         <x:v>Units</x:v>
       </x:c>
-      <x:c r="B7" s="40" t="str">
+      <x:c r="B7" s="28" t="str">
         <x:v>Whole dollars</x:v>
       </x:c>
     </x:row>
@@ -2334,7 +2445,7 @@
       <x:c r="A8" t="str">
         <x:v>Forecast start date</x:v>
       </x:c>
-      <x:c r="B8" s="41" t="n">
+      <x:c r="B8" s="29" t="n">
         <x:v>46265</x:v>
       </x:c>
     </x:row>
@@ -2342,7 +2453,7 @@
       <x:c r="A9" t="str">
         <x:v>As-at date</x:v>
       </x:c>
-      <x:c r="B9" s="41" t="n">
+      <x:c r="B9" s="29" t="n">
         <x:v>46271</x:v>
       </x:c>
     </x:row>
@@ -2350,7 +2461,7 @@
       <x:c r="A10" t="str">
         <x:v>Opening cash</x:v>
       </x:c>
-      <x:c r="B10" s="42" t="n">
+      <x:c r="B10" s="30" t="n">
         <x:v>400000</x:v>
       </x:c>
     </x:row>
@@ -2358,7 +2469,7 @@
       <x:c r="A11" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B11" s="42" t="n">
+      <x:c r="B11" s="30" t="n">
         <x:v>100000</x:v>
       </x:c>
     </x:row>
@@ -2366,7 +2477,7 @@
       <x:c r="A12" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B12" s="40" t="str">
+      <x:c r="B12" s="28" t="str">
         <x:v>Base</x:v>
       </x:c>
     </x:row>
@@ -2391,10 +2502,10 @@
       <x:c r="B15" s="16" t="str">
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="C15" s="43" t="n">
+      <x:c r="C15" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="43" t="n">
+      <x:c r="D15" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="16" t="str">
@@ -2405,10 +2516,10 @@
       <x:c r="B16" s="16" t="str">
         <x:v>Upside</x:v>
       </x:c>
-      <x:c r="C16" s="43" t="n">
+      <x:c r="C16" s="31" t="n">
         <x:v>1.08</x:v>
       </x:c>
-      <x:c r="D16" s="43" t="n">
+      <x:c r="D16" s="31" t="n">
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="E16" s="16" t="str">
@@ -2419,10 +2530,10 @@
       <x:c r="B17" s="16" t="str">
         <x:v>Downside</x:v>
       </x:c>
-      <x:c r="C17" s="43" t="n">
+      <x:c r="C17" s="31" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="D17" s="43" t="n">
+      <x:c r="D17" s="31" t="n">
         <x:v>1.05</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
@@ -2544,55 +2655,55 @@
       <x:c r="A5" t="str">
         <x:v>Week commencing</x:v>
       </x:c>
-      <x:c r="B5" s="45" t="n">
+      <x:c r="B5" s="33" t="n">
         <x:f>'Assumptions'!$B$8</x:f>
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="C5" s="45" t="n">
+      <x:c r="C5" s="33" t="n">
         <x:f>B5+7</x:f>
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="D5" s="45" t="n">
+      <x:c r="D5" s="33" t="n">
         <x:f>C5+7</x:f>
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="E5" s="45" t="n">
+      <x:c r="E5" s="33" t="n">
         <x:f>D5+7</x:f>
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="F5" s="45" t="n">
+      <x:c r="F5" s="33" t="n">
         <x:f>E5+7</x:f>
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="G5" s="45" t="n">
+      <x:c r="G5" s="33" t="n">
         <x:f>F5+7</x:f>
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="H5" s="45" t="n">
+      <x:c r="H5" s="33" t="n">
         <x:f>G5+7</x:f>
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="I5" s="45" t="n">
+      <x:c r="I5" s="33" t="n">
         <x:f>H5+7</x:f>
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="J5" s="45" t="n">
+      <x:c r="J5" s="33" t="n">
         <x:f>I5+7</x:f>
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="K5" s="45" t="n">
+      <x:c r="K5" s="33" t="n">
         <x:f>J5+7</x:f>
         <x:v>46328</x:v>
       </x:c>
-      <x:c r="L5" s="45" t="n">
+      <x:c r="L5" s="33" t="n">
         <x:f>K5+7</x:f>
         <x:v>46335</x:v>
       </x:c>
-      <x:c r="M5" s="45" t="n">
+      <x:c r="M5" s="33" t="n">
         <x:f>L5+7</x:f>
         <x:v>46342</x:v>
       </x:c>
-      <x:c r="N5" s="45" t="n">
+      <x:c r="N5" s="33" t="n">
         <x:f>M5+7</x:f>
         <x:v>46349</x:v>
       </x:c>
@@ -2604,55 +2715,55 @@
       <x:c r="A6" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="B6" s="45" t="n">
+      <x:c r="B6" s="33" t="n">
         <x:f>B5+6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C6" s="45" t="n">
+      <x:c r="C6" s="33" t="n">
         <x:f>C5+6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="D6" s="45" t="n">
+      <x:c r="D6" s="33" t="n">
         <x:f>D5+6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="E6" s="45" t="n">
+      <x:c r="E6" s="33" t="n">
         <x:f>E5+6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="F6" s="45" t="n">
+      <x:c r="F6" s="33" t="n">
         <x:f>F5+6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="G6" s="45" t="n">
+      <x:c r="G6" s="33" t="n">
         <x:f>G5+6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="H6" s="45" t="n">
+      <x:c r="H6" s="33" t="n">
         <x:f>H5+6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="I6" s="45" t="n">
+      <x:c r="I6" s="33" t="n">
         <x:f>I5+6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="J6" s="45" t="n">
+      <x:c r="J6" s="33" t="n">
         <x:f>J5+6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="K6" s="45" t="n">
+      <x:c r="K6" s="33" t="n">
         <x:f>K5+6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="L6" s="45" t="n">
+      <x:c r="L6" s="33" t="n">
         <x:f>L5+6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="M6" s="45" t="n">
+      <x:c r="M6" s="33" t="n">
         <x:f>M5+6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="N6" s="45" t="n">
+      <x:c r="N6" s="33" t="n">
         <x:f>N5+6</x:f>
         <x:v>46355</x:v>
       </x:c>
@@ -2664,55 +2775,55 @@
       <x:c r="A7" t="str">
         <x:v>Actual / Forecast</x:v>
       </x:c>
-      <x:c r="B7" s="46" t="str">
+      <x:c r="B7" s="34" t="str">
         <x:f>IF(B6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Actual</x:v>
       </x:c>
-      <x:c r="C7" s="46" t="str">
+      <x:c r="C7" s="34" t="str">
         <x:f>IF(C6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="D7" s="46" t="str">
+      <x:c r="D7" s="34" t="str">
         <x:f>IF(D6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="E7" s="46" t="str">
+      <x:c r="E7" s="34" t="str">
         <x:f>IF(E6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="F7" s="46" t="str">
+      <x:c r="F7" s="34" t="str">
         <x:f>IF(F6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="G7" s="46" t="str">
+      <x:c r="G7" s="34" t="str">
         <x:f>IF(G6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="H7" s="46" t="str">
+      <x:c r="H7" s="34" t="str">
         <x:f>IF(H6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="I7" s="46" t="str">
+      <x:c r="I7" s="34" t="str">
         <x:f>IF(I6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="J7" s="46" t="str">
+      <x:c r="J7" s="34" t="str">
         <x:f>IF(J6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="K7" s="46" t="str">
+      <x:c r="K7" s="34" t="str">
         <x:f>IF(K6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="L7" s="46" t="str">
+      <x:c r="L7" s="34" t="str">
         <x:f>IF(L6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="M7" s="46" t="str">
+      <x:c r="M7" s="34" t="str">
         <x:f>IF(M6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="N7" s="46" t="str">
+      <x:c r="N7" s="34" t="str">
         <x:f>IF(N6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
@@ -2741,46 +2852,46 @@
       <x:c r="A10" t="str">
         <x:v>Customer receipts</x:v>
       </x:c>
-      <x:c r="B10" s="49" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:v>118000</x:v>
       </x:c>
-      <x:c r="C10" s="49" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="D10" s="49" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="E10" s="49" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:v>115000</x:v>
       </x:c>
-      <x:c r="F10" s="49" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="G10" s="49" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:v>112000</x:v>
       </x:c>
-      <x:c r="H10" s="49" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="I10" s="49" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:v>108000</x:v>
       </x:c>
-      <x:c r="J10" s="49" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="K10" s="49" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:v>116000</x:v>
       </x:c>
-      <x:c r="L10" s="49" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="M10" s="49" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="N10" s="49" t="n">
+      <x:c r="N10" s="37" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="O10" s="36" t="n">
+      <x:c r="O10" s="38" t="n">
         <x:f>SUM(B10:N10)</x:f>
         <x:v>1514000</x:v>
       </x:c>
@@ -2789,46 +2900,46 @@
       <x:c r="A11" t="str">
         <x:v>Overdue receipts</x:v>
       </x:c>
-      <x:c r="B11" s="49" t="n">
+      <x:c r="B11" s="37" t="n">
         <x:v>30000</x:v>
       </x:c>
-      <x:c r="C11" s="49" t="n">
+      <x:c r="C11" s="37" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="D11" s="49" t="n">
+      <x:c r="D11" s="37" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="E11" s="49" t="n">
+      <x:c r="E11" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F11" s="49" t="n">
+      <x:c r="F11" s="37" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="G11" s="49" t="n">
+      <x:c r="G11" s="37" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="H11" s="49" t="n">
+      <x:c r="H11" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="I11" s="49" t="n">
+      <x:c r="I11" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="J11" s="49" t="n">
+      <x:c r="J11" s="37" t="n">
         <x:v>7000</x:v>
       </x:c>
-      <x:c r="K11" s="49" t="n">
+      <x:c r="K11" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="L11" s="49" t="n">
+      <x:c r="L11" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="M11" s="49" t="n">
+      <x:c r="M11" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="N11" s="49" t="n">
+      <x:c r="N11" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O11" s="36" t="n">
+      <x:c r="O11" s="38" t="n">
         <x:f>SUM(B11:N11)</x:f>
         <x:v>152000</x:v>
       </x:c>
@@ -2837,46 +2948,46 @@
       <x:c r="A12" t="str">
         <x:v>Cash / EFTPOS sales</x:v>
       </x:c>
-      <x:c r="B12" s="49" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="C12" s="49" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="D12" s="49" t="n">
+      <x:c r="D12" s="37" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="E12" s="49" t="n">
+      <x:c r="E12" s="37" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="F12" s="49" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="G12" s="49" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="H12" s="49" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="I12" s="49" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="J12" s="49" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="K12" s="49" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="L12" s="49" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="M12" s="49" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:v>21000</x:v>
       </x:c>
-      <x:c r="N12" s="49" t="n">
+      <x:c r="N12" s="37" t="n">
         <x:v>22000</x:v>
       </x:c>
-      <x:c r="O12" s="36" t="n">
+      <x:c r="O12" s="38" t="n">
         <x:f>SUM(B12:N12)</x:f>
         <x:v>245000</x:v>
       </x:c>
@@ -2885,46 +2996,46 @@
       <x:c r="A13" t="str">
         <x:v>GST refunds / credits</x:v>
       </x:c>
-      <x:c r="B13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O13" s="36" t="n">
+      <x:c r="B13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="38" t="n">
         <x:f>SUM(B13:N13)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2933,46 +3044,46 @@
       <x:c r="A14" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B14" s="49" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="C14" s="49" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="D14" s="49" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="E14" s="49" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="F14" s="49" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G14" s="49" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="H14" s="49" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="I14" s="49" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="J14" s="49" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K14" s="49" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="L14" s="49" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="M14" s="49" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="N14" s="49" t="n">
+      <x:c r="N14" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O14" s="36" t="n">
+      <x:c r="O14" s="38" t="n">
         <x:f>SUM(B14:N14)</x:f>
         <x:v>52000</x:v>
       </x:c>
@@ -2981,46 +3092,46 @@
       <x:c r="A15" t="str">
         <x:v>Asset sale proceeds</x:v>
       </x:c>
-      <x:c r="B15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="49" t="n">
+      <x:c r="B15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="37" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="L15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O15" s="36" t="n">
+      <x:c r="L15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="38" t="n">
         <x:f>SUM(B15:N15)</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -3029,46 +3140,46 @@
       <x:c r="A16" t="str">
         <x:v>Equity / owner funding</x:v>
       </x:c>
-      <x:c r="B16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="49" t="n">
+      <x:c r="B16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="37" t="n">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O16" s="36" t="n">
+      <x:c r="I16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="38" t="n">
         <x:f>SUM(B16:N16)</x:f>
         <x:v>150000</x:v>
       </x:c>
@@ -3077,46 +3188,46 @@
       <x:c r="A17" t="str">
         <x:v>Loan proceeds</x:v>
       </x:c>
-      <x:c r="B17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="49" t="n">
+      <x:c r="B17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="37" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="K17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O17" s="36" t="n">
+      <x:c r="K17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="38" t="n">
         <x:f>SUM(B17:N17)</x:f>
         <x:v>125000</x:v>
       </x:c>
@@ -3125,203 +3236,203 @@
       <x:c r="A18" t="str">
         <x:v>Scenario receipt adjustment</x:v>
       </x:c>
-      <x:c r="B18" s="52" t="n">
+      <x:c r="B18" s="41" t="n">
         <x:f>IF(B$7="Actual",0,SUM(B10:B12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C18" s="52" t="n">
+      <x:c r="C18" s="41" t="n">
         <x:f>IF(C$7="Actual",0,SUM(C10:C12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D18" s="52" t="n">
+      <x:c r="D18" s="41" t="n">
         <x:f>IF(D$7="Actual",0,SUM(D10:D12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="52" t="n">
+      <x:c r="E18" s="41" t="n">
         <x:f>IF(E$7="Actual",0,SUM(E10:E12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="52" t="n">
+      <x:c r="F18" s="41" t="n">
         <x:f>IF(F$7="Actual",0,SUM(F10:F12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="52" t="n">
+      <x:c r="G18" s="41" t="n">
         <x:f>IF(G$7="Actual",0,SUM(G10:G12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="52" t="n">
+      <x:c r="H18" s="41" t="n">
         <x:f>IF(H$7="Actual",0,SUM(H10:H12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="52" t="n">
+      <x:c r="I18" s="41" t="n">
         <x:f>IF(I$7="Actual",0,SUM(I10:I12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="52" t="n">
+      <x:c r="J18" s="41" t="n">
         <x:f>IF(J$7="Actual",0,SUM(J10:J12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="52" t="n">
+      <x:c r="K18" s="41" t="n">
         <x:f>IF(K$7="Actual",0,SUM(K10:K12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="52" t="n">
+      <x:c r="L18" s="41" t="n">
         <x:f>IF(L$7="Actual",0,SUM(L10:L12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="52" t="n">
+      <x:c r="M18" s="41" t="n">
         <x:f>IF(M$7="Actual",0,SUM(M10:M12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N18" s="52" t="n">
+      <x:c r="N18" s="41" t="n">
         <x:f>IF(N$7="Actual",0,SUM(N10:N12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="36" t="n">
+      <x:c r="O18" s="38" t="n">
         <x:f>SUM(B18:N18)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="48" t="str">
+      <x:c r="A19" s="36" t="str">
         <x:v>Total cash receipts</x:v>
       </x:c>
-      <x:c r="B19" s="53" t="n">
+      <x:c r="B19" s="42" t="n">
         <x:f>SUM(B10:B18)</x:f>
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="C19" s="53" t="n">
+      <x:c r="C19" s="42" t="n">
         <x:f>SUM(C10:C18)</x:f>
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="D19" s="53" t="n">
+      <x:c r="D19" s="42" t="n">
         <x:f>SUM(D10:D18)</x:f>
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="E19" s="53" t="n">
+      <x:c r="E19" s="42" t="n">
         <x:f>SUM(E10:E18)</x:f>
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="F19" s="53" t="n">
+      <x:c r="F19" s="42" t="n">
         <x:f>SUM(F10:F18)</x:f>
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="G19" s="53" t="n">
+      <x:c r="G19" s="42" t="n">
         <x:f>SUM(G10:G18)</x:f>
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="H19" s="53" t="n">
+      <x:c r="H19" s="42" t="n">
         <x:f>SUM(H10:H18)</x:f>
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="I19" s="53" t="n">
+      <x:c r="I19" s="42" t="n">
         <x:f>SUM(I10:I18)</x:f>
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="J19" s="53" t="n">
+      <x:c r="J19" s="42" t="n">
         <x:f>SUM(J10:J18)</x:f>
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="K19" s="53" t="n">
+      <x:c r="K19" s="42" t="n">
         <x:f>SUM(K10:K18)</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="L19" s="53" t="n">
+      <x:c r="L19" s="42" t="n">
         <x:f>SUM(L10:L18)</x:f>
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="M19" s="53" t="n">
+      <x:c r="M19" s="42" t="n">
         <x:f>SUM(M10:M18)</x:f>
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="N19" s="53" t="n">
+      <x:c r="N19" s="42" t="n">
         <x:f>SUM(N10:N18)</x:f>
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="O19" s="50" t="n">
+      <x:c r="O19" s="39" t="n">
         <x:f>SUM(B19:N19)</x:f>
         <x:v>2338000</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="36"/>
-      <x:c r="C20" s="36"/>
-      <x:c r="D20" s="36"/>
-      <x:c r="E20" s="36"/>
-      <x:c r="F20" s="36"/>
-      <x:c r="G20" s="36"/>
-      <x:c r="H20" s="36"/>
-      <x:c r="I20" s="36"/>
-      <x:c r="J20" s="36"/>
-      <x:c r="K20" s="36"/>
-      <x:c r="L20" s="36"/>
-      <x:c r="M20" s="36"/>
-      <x:c r="N20" s="36"/>
-      <x:c r="O20" s="36"/>
+      <x:c r="B20" s="38"/>
+      <x:c r="C20" s="38"/>
+      <x:c r="D20" s="38"/>
+      <x:c r="E20" s="38"/>
+      <x:c r="F20" s="38"/>
+      <x:c r="G20" s="38"/>
+      <x:c r="H20" s="38"/>
+      <x:c r="I20" s="38"/>
+      <x:c r="J20" s="38"/>
+      <x:c r="K20" s="38"/>
+      <x:c r="L20" s="38"/>
+      <x:c r="M20" s="38"/>
+      <x:c r="N20" s="38"/>
+      <x:c r="O20" s="38"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
         <x:v>CASH PAYMENTS</x:v>
       </x:c>
-      <x:c r="B21" s="51"/>
-      <x:c r="C21" s="51"/>
-      <x:c r="D21" s="51"/>
-      <x:c r="E21" s="51"/>
-      <x:c r="F21" s="51"/>
-      <x:c r="G21" s="51"/>
-      <x:c r="H21" s="51"/>
-      <x:c r="I21" s="51"/>
-      <x:c r="J21" s="51"/>
-      <x:c r="K21" s="51"/>
-      <x:c r="L21" s="51"/>
-      <x:c r="M21" s="51"/>
-      <x:c r="N21" s="51"/>
-      <x:c r="O21" s="51"/>
+      <x:c r="B21" s="40"/>
+      <x:c r="C21" s="40"/>
+      <x:c r="D21" s="40"/>
+      <x:c r="E21" s="40"/>
+      <x:c r="F21" s="40"/>
+      <x:c r="G21" s="40"/>
+      <x:c r="H21" s="40"/>
+      <x:c r="I21" s="40"/>
+      <x:c r="J21" s="40"/>
+      <x:c r="K21" s="40"/>
+      <x:c r="L21" s="40"/>
+      <x:c r="M21" s="40"/>
+      <x:c r="N21" s="40"/>
+      <x:c r="O21" s="40"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
         <x:v>Suppliers and inventory</x:v>
       </x:c>
-      <x:c r="B22" s="49" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="C22" s="49" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:v>88000</x:v>
       </x:c>
-      <x:c r="D22" s="49" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:v>90000</x:v>
       </x:c>
-      <x:c r="E22" s="49" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:v>95000</x:v>
       </x:c>
-      <x:c r="F22" s="49" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:v>98000</x:v>
       </x:c>
-      <x:c r="G22" s="49" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="H22" s="49" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="I22" s="49" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:v>108000</x:v>
       </x:c>
-      <x:c r="J22" s="49" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="K22" s="49" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="L22" s="49" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="M22" s="49" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:v>95000</x:v>
       </x:c>
-      <x:c r="N22" s="49" t="n">
+      <x:c r="N22" s="37" t="n">
         <x:v>90000</x:v>
       </x:c>
-      <x:c r="O22" s="36" t="n">
+      <x:c r="O22" s="38" t="n">
         <x:f>SUM(B22:N22)</x:f>
         <x:v>1266000</x:v>
       </x:c>
@@ -3330,46 +3441,46 @@
       <x:c r="A23" t="str">
         <x:v>Net wages</x:v>
       </x:c>
-      <x:c r="B23" s="49" t="n">
+      <x:c r="B23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="C23" s="49" t="n">
+      <x:c r="C23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="D23" s="49" t="n">
+      <x:c r="D23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="E23" s="49" t="n">
+      <x:c r="E23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="F23" s="49" t="n">
+      <x:c r="F23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="G23" s="49" t="n">
+      <x:c r="G23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="H23" s="49" t="n">
+      <x:c r="H23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="I23" s="49" t="n">
+      <x:c r="I23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="J23" s="49" t="n">
+      <x:c r="J23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="K23" s="49" t="n">
+      <x:c r="K23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="L23" s="49" t="n">
+      <x:c r="L23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="M23" s="49" t="n">
+      <x:c r="M23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="N23" s="49" t="n">
+      <x:c r="N23" s="37" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="O23" s="36" t="n">
+      <x:c r="O23" s="38" t="n">
         <x:f>SUM(B23:N23)</x:f>
         <x:v>546000</x:v>
       </x:c>
@@ -3378,46 +3489,46 @@
       <x:c r="A24" t="str">
         <x:v>PAYG withholding</x:v>
       </x:c>
-      <x:c r="B24" s="49" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="C24" s="49" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="D24" s="49" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="E24" s="49" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="F24" s="49" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="G24" s="49" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="H24" s="49" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="I24" s="49" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="J24" s="49" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="K24" s="49" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="L24" s="49" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="M24" s="49" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="N24" s="49" t="n">
+      <x:c r="N24" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O24" s="36" t="n">
+      <x:c r="O24" s="38" t="n">
         <x:f>SUM(B24:N24)</x:f>
         <x:v>156000</x:v>
       </x:c>
@@ -3426,46 +3537,46 @@
       <x:c r="A25" t="str">
         <x:v>Superannuation</x:v>
       </x:c>
-      <x:c r="B25" s="49" t="n">
+      <x:c r="B25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="C25" s="49" t="n">
+      <x:c r="C25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D25" s="49" t="n">
+      <x:c r="D25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="E25" s="49" t="n">
+      <x:c r="E25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="F25" s="49" t="n">
+      <x:c r="F25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="G25" s="49" t="n">
+      <x:c r="G25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="H25" s="49" t="n">
+      <x:c r="H25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="I25" s="49" t="n">
+      <x:c r="I25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="J25" s="49" t="n">
+      <x:c r="J25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="K25" s="49" t="n">
+      <x:c r="K25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="L25" s="49" t="n">
+      <x:c r="L25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="M25" s="49" t="n">
+      <x:c r="M25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="N25" s="49" t="n">
+      <x:c r="N25" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O25" s="36" t="n">
+      <x:c r="O25" s="38" t="n">
         <x:f>SUM(B25:N25)</x:f>
         <x:v>78000</x:v>
       </x:c>
@@ -3474,46 +3585,46 @@
       <x:c r="A26" t="str">
         <x:v>Payroll tax / workers compensation</x:v>
       </x:c>
-      <x:c r="B26" s="49" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="C26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F26" s="49" t="n">
+      <x:c r="C26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="G26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="49" t="n">
+      <x:c r="G26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="K26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N26" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O26" s="36" t="n">
+      <x:c r="K26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" s="38" t="n">
         <x:f>SUM(B26:N26)</x:f>
         <x:v>15000</x:v>
       </x:c>
@@ -3522,46 +3633,46 @@
       <x:c r="A27" t="str">
         <x:v>Rent</x:v>
       </x:c>
-      <x:c r="B27" s="49" t="n">
+      <x:c r="B27" s="37" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="C27" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E27" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F27" s="49" t="n">
+      <x:c r="C27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" s="37" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="G27" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I27" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="49" t="n">
+      <x:c r="G27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="37" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="K27" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L27" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M27" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N27" s="49" t="n">
+      <x:c r="K27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="37" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="O27" s="36" t="n">
+      <x:c r="O27" s="38" t="n">
         <x:f>SUM(B27:N27)</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -3570,46 +3681,46 @@
       <x:c r="A28" t="str">
         <x:v>Utilities</x:v>
       </x:c>
-      <x:c r="B28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F28" s="49" t="n">
+      <x:c r="B28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J28" s="49" t="n">
+      <x:c r="G28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M28" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N28" s="49" t="n">
+      <x:c r="K28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O28" s="36" t="n">
+      <x:c r="O28" s="38" t="n">
         <x:f>SUM(B28:N28)</x:f>
         <x:v>12000</x:v>
       </x:c>
@@ -3618,46 +3729,46 @@
       <x:c r="A29" t="str">
         <x:v>Insurance</x:v>
       </x:c>
-      <x:c r="B29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="49" t="n">
+      <x:c r="B29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N29" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O29" s="36" t="n">
+      <x:c r="D29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" s="38" t="n">
         <x:f>SUM(B29:N29)</x:f>
         <x:v>6000</x:v>
       </x:c>
@@ -3666,46 +3777,46 @@
       <x:c r="A30" t="str">
         <x:v>Software and subscriptions</x:v>
       </x:c>
-      <x:c r="B30" s="49" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="C30" s="49" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="D30" s="49" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="E30" s="49" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="F30" s="49" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="G30" s="49" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="H30" s="49" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="I30" s="49" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="J30" s="49" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="K30" s="49" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="L30" s="49" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="M30" s="49" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="N30" s="49" t="n">
+      <x:c r="N30" s="37" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="O30" s="36" t="n">
+      <x:c r="O30" s="38" t="n">
         <x:f>SUM(B30:N30)</x:f>
         <x:v>39000</x:v>
       </x:c>
@@ -3714,46 +3825,46 @@
       <x:c r="A31" t="str">
         <x:v>Marketing</x:v>
       </x:c>
-      <x:c r="B31" s="49" t="n">
+      <x:c r="B31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="C31" s="49" t="n">
+      <x:c r="C31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D31" s="49" t="n">
+      <x:c r="D31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="E31" s="49" t="n">
+      <x:c r="E31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="F31" s="49" t="n">
+      <x:c r="F31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="G31" s="49" t="n">
+      <x:c r="G31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="H31" s="49" t="n">
+      <x:c r="H31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="I31" s="49" t="n">
+      <x:c r="I31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="J31" s="49" t="n">
+      <x:c r="J31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="K31" s="49" t="n">
+      <x:c r="K31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="L31" s="49" t="n">
+      <x:c r="L31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="M31" s="49" t="n">
+      <x:c r="M31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="N31" s="49" t="n">
+      <x:c r="N31" s="37" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O31" s="36" t="n">
+      <x:c r="O31" s="38" t="n">
         <x:f>SUM(B31:N31)</x:f>
         <x:v>78000</x:v>
       </x:c>
@@ -3762,46 +3873,46 @@
       <x:c r="A32" t="str">
         <x:v>Professional services</x:v>
       </x:c>
-      <x:c r="B32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="49" t="n">
+      <x:c r="B32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="37" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="E32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="49" t="n">
+      <x:c r="E32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="37" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="I32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L32" s="49" t="n">
+      <x:c r="I32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="37" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="M32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N32" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O32" s="36" t="n">
+      <x:c r="M32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O32" s="38" t="n">
         <x:f>SUM(B32:N32)</x:f>
         <x:v>24000</x:v>
       </x:c>
@@ -3810,46 +3921,46 @@
       <x:c r="A33" t="str">
         <x:v>Freight, vehicles and travel</x:v>
       </x:c>
-      <x:c r="B33" s="49" t="n">
+      <x:c r="B33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="C33" s="49" t="n">
+      <x:c r="C33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="D33" s="49" t="n">
+      <x:c r="D33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="E33" s="49" t="n">
+      <x:c r="E33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F33" s="49" t="n">
+      <x:c r="F33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="G33" s="49" t="n">
+      <x:c r="G33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H33" s="49" t="n">
+      <x:c r="H33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="I33" s="49" t="n">
+      <x:c r="I33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="J33" s="49" t="n">
+      <x:c r="J33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="K33" s="49" t="n">
+      <x:c r="K33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="L33" s="49" t="n">
+      <x:c r="L33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="M33" s="49" t="n">
+      <x:c r="M33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="N33" s="49" t="n">
+      <x:c r="N33" s="37" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="O33" s="36" t="n">
+      <x:c r="O33" s="38" t="n">
         <x:f>SUM(B33:N33)</x:f>
         <x:v>130000</x:v>
       </x:c>
@@ -3858,46 +3969,46 @@
       <x:c r="A34" t="str">
         <x:v>GST / BAS payments</x:v>
       </x:c>
-      <x:c r="B34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J34" s="49" t="n">
+      <x:c r="B34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="37" t="n">
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="K34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N34" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O34" s="36" t="n">
+      <x:c r="K34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34" s="38" t="n">
         <x:f>SUM(B34:N34)</x:f>
         <x:v>45000</x:v>
       </x:c>
@@ -3906,46 +4017,46 @@
       <x:c r="A35" t="str">
         <x:v>PAYG income tax instalments</x:v>
       </x:c>
-      <x:c r="B35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J35" s="49" t="n">
+      <x:c r="B35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="37" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="K35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N35" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O35" s="36" t="n">
+      <x:c r="K35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O35" s="38" t="n">
         <x:f>SUM(B35:N35)</x:f>
         <x:v>18000</x:v>
       </x:c>
@@ -3954,46 +4065,46 @@
       <x:c r="A36" t="str">
         <x:v>FBT / other tax</x:v>
       </x:c>
-      <x:c r="B36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N36" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O36" s="36" t="n">
+      <x:c r="B36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" s="38" t="n">
         <x:f>SUM(B36:N36)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4002,46 +4113,46 @@
       <x:c r="A37" t="str">
         <x:v>Interest and bank fees</x:v>
       </x:c>
-      <x:c r="B37" s="49" t="n">
+      <x:c r="B37" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="C37" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F37" s="49" t="n">
+      <x:c r="C37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G37" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I37" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J37" s="49" t="n">
+      <x:c r="G37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K37" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L37" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M37" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N37" s="49" t="n">
+      <x:c r="K37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N37" s="37" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O37" s="36" t="n">
+      <x:c r="O37" s="38" t="n">
         <x:f>SUM(B37:N37)</x:f>
         <x:v>16000</x:v>
       </x:c>
@@ -4050,46 +4161,46 @@
       <x:c r="A38" t="str">
         <x:v>Loan principal</x:v>
       </x:c>
-      <x:c r="B38" s="49" t="n">
+      <x:c r="B38" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="C38" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E38" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F38" s="49" t="n">
+      <x:c r="C38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F38" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="G38" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I38" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J38" s="49" t="n">
+      <x:c r="G38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="K38" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L38" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M38" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N38" s="49" t="n">
+      <x:c r="K38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N38" s="37" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O38" s="36" t="n">
+      <x:c r="O38" s="38" t="n">
         <x:f>SUM(B38:N38)</x:f>
         <x:v>48000</x:v>
       </x:c>
@@ -4098,46 +4209,46 @@
       <x:c r="A39" t="str">
         <x:v>Capital expenditure</x:v>
       </x:c>
-      <x:c r="B39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G39" s="49" t="n">
+      <x:c r="B39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G39" s="37" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="H39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K39" s="49" t="n">
+      <x:c r="H39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39" s="37" t="n">
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="L39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N39" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O39" s="36" t="n">
+      <x:c r="L39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" s="38" t="n">
         <x:f>SUM(B39:N39)</x:f>
         <x:v>65000</x:v>
       </x:c>
@@ -4146,46 +4257,46 @@
       <x:c r="A40" t="str">
         <x:v>Dividends / distributions</x:v>
       </x:c>
-      <x:c r="B40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O40" s="36" t="n">
+      <x:c r="B40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" s="38" t="n">
         <x:f>SUM(B40:N40)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4194,46 +4305,46 @@
       <x:c r="A41" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B41" s="49" t="n">
+      <x:c r="B41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="C41" s="49" t="n">
+      <x:c r="C41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D41" s="49" t="n">
+      <x:c r="D41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="E41" s="49" t="n">
+      <x:c r="E41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="F41" s="49" t="n">
+      <x:c r="F41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="G41" s="49" t="n">
+      <x:c r="G41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="H41" s="49" t="n">
+      <x:c r="H41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="I41" s="49" t="n">
+      <x:c r="I41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="J41" s="49" t="n">
+      <x:c r="J41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="K41" s="49" t="n">
+      <x:c r="K41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="L41" s="49" t="n">
+      <x:c r="L41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="M41" s="49" t="n">
+      <x:c r="M41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="N41" s="49" t="n">
+      <x:c r="N41" s="37" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="O41" s="36" t="n">
+      <x:c r="O41" s="38" t="n">
         <x:f>SUM(B41:N41)</x:f>
         <x:v>65000</x:v>
       </x:c>
@@ -4242,216 +4353,216 @@
       <x:c r="A42" t="str">
         <x:v>Scenario payment adjustment</x:v>
       </x:c>
-      <x:c r="B42" s="52" t="n">
+      <x:c r="B42" s="41" t="n">
         <x:f>IF(B$7="Actual",0,SUM(B22,B31,B33,B41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C42" s="52" t="n">
+      <x:c r="C42" s="41" t="n">
         <x:f>IF(C$7="Actual",0,SUM(C22,C31,C33,C41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D42" s="52" t="n">
+      <x:c r="D42" s="41" t="n">
         <x:f>IF(D$7="Actual",0,SUM(D22,D31,D33,D41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E42" s="52" t="n">
+      <x:c r="E42" s="41" t="n">
         <x:f>IF(E$7="Actual",0,SUM(E22,E31,E33,E41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F42" s="52" t="n">
+      <x:c r="F42" s="41" t="n">
         <x:f>IF(F$7="Actual",0,SUM(F22,F31,F33,F41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G42" s="52" t="n">
+      <x:c r="G42" s="41" t="n">
         <x:f>IF(G$7="Actual",0,SUM(G22,G31,G33,G41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H42" s="52" t="n">
+      <x:c r="H42" s="41" t="n">
         <x:f>IF(H$7="Actual",0,SUM(H22,H31,H33,H41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I42" s="52" t="n">
+      <x:c r="I42" s="41" t="n">
         <x:f>IF(I$7="Actual",0,SUM(I22,I31,I33,I41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J42" s="52" t="n">
+      <x:c r="J42" s="41" t="n">
         <x:f>IF(J$7="Actual",0,SUM(J22,J31,J33,J41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K42" s="52" t="n">
+      <x:c r="K42" s="41" t="n">
         <x:f>IF(K$7="Actual",0,SUM(K22,K31,K33,K41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L42" s="52" t="n">
+      <x:c r="L42" s="41" t="n">
         <x:f>IF(L$7="Actual",0,SUM(L22,L31,L33,L41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M42" s="52" t="n">
+      <x:c r="M42" s="41" t="n">
         <x:f>IF(M$7="Actual",0,SUM(M22,M31,M33,M41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N42" s="52" t="n">
+      <x:c r="N42" s="41" t="n">
         <x:f>IF(N$7="Actual",0,SUM(N22,N31,N33,N41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O42" s="36" t="n">
+      <x:c r="O42" s="38" t="n">
         <x:f>SUM(B42:N42)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="48" t="str">
+      <x:c r="A43" s="36" t="str">
         <x:v>Total cash payments</x:v>
       </x:c>
-      <x:c r="B43" s="53" t="n">
+      <x:c r="B43" s="42" t="n">
         <x:f>SUM(B22:B42)</x:f>
         <x:v>212000</x:v>
       </x:c>
-      <x:c r="C43" s="53" t="n">
+      <x:c r="C43" s="42" t="n">
         <x:f>SUM(C22:C42)</x:f>
         <x:v>178000</x:v>
       </x:c>
-      <x:c r="D43" s="53" t="n">
+      <x:c r="D43" s="42" t="n">
         <x:f>SUM(D22:D42)</x:f>
         <x:v>182000</x:v>
       </x:c>
-      <x:c r="E43" s="53" t="n">
+      <x:c r="E43" s="42" t="n">
         <x:f>SUM(E22:E42)</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="F43" s="53" t="n">
+      <x:c r="F43" s="42" t="n">
         <x:f>SUM(F22:F42)</x:f>
         <x:v>232000</x:v>
       </x:c>
-      <x:c r="G43" s="53" t="n">
+      <x:c r="G43" s="42" t="n">
         <x:f>SUM(G22:G42)</x:f>
         <x:v>209000</x:v>
       </x:c>
-      <x:c r="H43" s="53" t="n">
+      <x:c r="H43" s="42" t="n">
         <x:f>SUM(H22:H42)</x:f>
         <x:v>197000</x:v>
       </x:c>
-      <x:c r="I43" s="53" t="n">
+      <x:c r="I43" s="42" t="n">
         <x:f>SUM(I22:I42)</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="J43" s="53" t="n">
+      <x:c r="J43" s="42" t="n">
         <x:f>SUM(J22:J42)</x:f>
         <x:v>307000</x:v>
       </x:c>
-      <x:c r="K43" s="53" t="n">
+      <x:c r="K43" s="42" t="n">
         <x:f>SUM(K22:K42)</x:f>
         <x:v>229000</x:v>
       </x:c>
-      <x:c r="L43" s="53" t="n">
+      <x:c r="L43" s="42" t="n">
         <x:f>SUM(L22:L42)</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="M43" s="53" t="n">
+      <x:c r="M43" s="42" t="n">
         <x:f>SUM(M22:M42)</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="N43" s="53" t="n">
+      <x:c r="N43" s="42" t="n">
         <x:f>SUM(N22:N42)</x:f>
         <x:v>219000</x:v>
       </x:c>
-      <x:c r="O43" s="50" t="n">
+      <x:c r="O43" s="39" t="n">
         <x:f>SUM(B43:N43)</x:f>
         <x:v>2707000</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="B44" s="36"/>
-      <x:c r="C44" s="36"/>
-      <x:c r="D44" s="36"/>
-      <x:c r="E44" s="36"/>
-      <x:c r="F44" s="36"/>
-      <x:c r="G44" s="36"/>
-      <x:c r="H44" s="36"/>
-      <x:c r="I44" s="36"/>
-      <x:c r="J44" s="36"/>
-      <x:c r="K44" s="36"/>
-      <x:c r="L44" s="36"/>
-      <x:c r="M44" s="36"/>
-      <x:c r="N44" s="36"/>
-      <x:c r="O44" s="36"/>
+      <x:c r="B44" s="38"/>
+      <x:c r="C44" s="38"/>
+      <x:c r="D44" s="38"/>
+      <x:c r="E44" s="38"/>
+      <x:c r="F44" s="38"/>
+      <x:c r="G44" s="38"/>
+      <x:c r="H44" s="38"/>
+      <x:c r="I44" s="38"/>
+      <x:c r="J44" s="38"/>
+      <x:c r="K44" s="38"/>
+      <x:c r="L44" s="38"/>
+      <x:c r="M44" s="38"/>
+      <x:c r="N44" s="38"/>
+      <x:c r="O44" s="38"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="14" t="str">
         <x:v>CASH POSITION</x:v>
       </x:c>
-      <x:c r="B45" s="51"/>
-      <x:c r="C45" s="51"/>
-      <x:c r="D45" s="51"/>
-      <x:c r="E45" s="51"/>
-      <x:c r="F45" s="51"/>
-      <x:c r="G45" s="51"/>
-      <x:c r="H45" s="51"/>
-      <x:c r="I45" s="51"/>
-      <x:c r="J45" s="51"/>
-      <x:c r="K45" s="51"/>
-      <x:c r="L45" s="51"/>
-      <x:c r="M45" s="51"/>
-      <x:c r="N45" s="51"/>
-      <x:c r="O45" s="51"/>
+      <x:c r="B45" s="40"/>
+      <x:c r="C45" s="40"/>
+      <x:c r="D45" s="40"/>
+      <x:c r="E45" s="40"/>
+      <x:c r="F45" s="40"/>
+      <x:c r="G45" s="40"/>
+      <x:c r="H45" s="40"/>
+      <x:c r="I45" s="40"/>
+      <x:c r="J45" s="40"/>
+      <x:c r="K45" s="40"/>
+      <x:c r="L45" s="40"/>
+      <x:c r="M45" s="40"/>
+      <x:c r="N45" s="40"/>
+      <x:c r="O45" s="40"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
         <x:v>Opening cash balance</x:v>
       </x:c>
-      <x:c r="B46" s="38" t="n">
+      <x:c r="B46" s="43" t="n">
         <x:f>'Assumptions'!$B$10</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="C46" s="38" t="n">
+      <x:c r="C46" s="43" t="n">
         <x:f>B48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="D46" s="38" t="n">
+      <x:c r="D46" s="43" t="n">
         <x:f>C48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="E46" s="38" t="n">
+      <x:c r="E46" s="43" t="n">
         <x:f>D48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="F46" s="38" t="n">
+      <x:c r="F46" s="43" t="n">
         <x:f>E48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="G46" s="38" t="n">
+      <x:c r="G46" s="43" t="n">
         <x:f>F48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="H46" s="38" t="n">
+      <x:c r="H46" s="43" t="n">
         <x:f>G48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="I46" s="38" t="n">
+      <x:c r="I46" s="43" t="n">
         <x:f>H48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="J46" s="38" t="n">
+      <x:c r="J46" s="43" t="n">
         <x:f>I48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="K46" s="38" t="n">
+      <x:c r="K46" s="43" t="n">
         <x:f>J48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="L46" s="38" t="n">
+      <x:c r="L46" s="43" t="n">
         <x:f>K48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="M46" s="38" t="n">
+      <x:c r="M46" s="43" t="n">
         <x:f>L48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="N46" s="38" t="n">
+      <x:c r="N46" s="43" t="n">
         <x:f>M48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="O46" s="36" t="n">
+      <x:c r="O46" s="38" t="n">
         <x:f>N46</x:f>
         <x:v>82000</x:v>
       </x:c>
@@ -4460,120 +4571,120 @@
       <x:c r="A47" t="str">
         <x:v>Net cash movement</x:v>
       </x:c>
-      <x:c r="B47" s="52" t="n">
+      <x:c r="B47" s="41" t="n">
         <x:f>B19-B43</x:f>
         <x:v>-42000</x:v>
       </x:c>
-      <x:c r="C47" s="52" t="n">
+      <x:c r="C47" s="41" t="n">
         <x:f>C19-C43</x:f>
         <x:v>-9000</x:v>
       </x:c>
-      <x:c r="D47" s="52" t="n">
+      <x:c r="D47" s="41" t="n">
         <x:f>D19-D43</x:f>
         <x:v>-24000</x:v>
       </x:c>
-      <x:c r="E47" s="52" t="n">
+      <x:c r="E47" s="41" t="n">
         <x:f>E19-E43</x:f>
         <x:v>-32000</x:v>
       </x:c>
-      <x:c r="F47" s="52" t="n">
+      <x:c r="F47" s="41" t="n">
         <x:f>F19-F43</x:f>
         <x:v>-92000</x:v>
       </x:c>
-      <x:c r="G47" s="52" t="n">
+      <x:c r="G47" s="41" t="n">
         <x:f>G19-G43</x:f>
         <x:v>-68000</x:v>
       </x:c>
-      <x:c r="H47" s="52" t="n">
+      <x:c r="H47" s="41" t="n">
         <x:f>H19-H43</x:f>
         <x:v>84000</x:v>
       </x:c>
-      <x:c r="I47" s="52" t="n">
+      <x:c r="I47" s="41" t="n">
         <x:f>I19-I43</x:f>
         <x:v>-57000</x:v>
       </x:c>
-      <x:c r="J47" s="52" t="n">
+      <x:c r="J47" s="41" t="n">
         <x:f>J19-J43</x:f>
         <x:v>-43000</x:v>
       </x:c>
-      <x:c r="K47" s="52" t="n">
+      <x:c r="K47" s="41" t="n">
         <x:f>K19-K43</x:f>
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="L47" s="52" t="n">
+      <x:c r="L47" s="41" t="n">
         <x:f>L19-L43</x:f>
         <x:v>-38000</x:v>
       </x:c>
-      <x:c r="M47" s="52" t="n">
+      <x:c r="M47" s="41" t="n">
         <x:f>M19-M43</x:f>
         <x:v>-17000</x:v>
       </x:c>
-      <x:c r="N47" s="52" t="n">
+      <x:c r="N47" s="41" t="n">
         <x:f>N19-N43</x:f>
         <x:v>-51000</x:v>
       </x:c>
-      <x:c r="O47" s="36" t="n">
-        <x:f>N47</x:f>
-        <x:v>-51000</x:v>
+      <x:c r="O47" s="38" t="n">
+        <x:f>SUM(B47:N47)</x:f>
+        <x:v>-369000</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="48" t="str">
+      <x:c r="A48" s="36" t="str">
         <x:v>Closing cash balance</x:v>
       </x:c>
-      <x:c r="B48" s="53" t="n">
+      <x:c r="B48" s="42" t="n">
         <x:f>B46+B47</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="C48" s="53" t="n">
+      <x:c r="C48" s="42" t="n">
         <x:f>C46+C47</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="D48" s="53" t="n">
+      <x:c r="D48" s="42" t="n">
         <x:f>D46+D47</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="E48" s="53" t="n">
+      <x:c r="E48" s="42" t="n">
         <x:f>E46+E47</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="F48" s="53" t="n">
+      <x:c r="F48" s="42" t="n">
         <x:f>F46+F47</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="G48" s="53" t="n">
+      <x:c r="G48" s="42" t="n">
         <x:f>G46+G47</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="H48" s="53" t="n">
+      <x:c r="H48" s="42" t="n">
         <x:f>H46+H47</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="I48" s="53" t="n">
+      <x:c r="I48" s="42" t="n">
         <x:f>I46+I47</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="J48" s="53" t="n">
+      <x:c r="J48" s="42" t="n">
         <x:f>J46+J47</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="K48" s="53" t="n">
+      <x:c r="K48" s="42" t="n">
         <x:f>K46+K47</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="L48" s="53" t="n">
+      <x:c r="L48" s="42" t="n">
         <x:f>L46+L47</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="M48" s="53" t="n">
+      <x:c r="M48" s="42" t="n">
         <x:f>M46+M47</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="N48" s="53" t="n">
+      <x:c r="N48" s="42" t="n">
         <x:f>N46+N47</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="O48" s="50" t="n">
+      <x:c r="O48" s="39" t="n">
         <x:f>N48</x:f>
         <x:v>31000</x:v>
       </x:c>
@@ -4582,120 +4693,120 @@
       <x:c r="A49" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B49" s="38" t="n">
+      <x:c r="B49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="C49" s="38" t="n">
+      <x:c r="C49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="D49" s="38" t="n">
+      <x:c r="D49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="E49" s="38" t="n">
+      <x:c r="E49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="F49" s="38" t="n">
+      <x:c r="F49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="G49" s="38" t="n">
+      <x:c r="G49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="H49" s="38" t="n">
+      <x:c r="H49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="I49" s="38" t="n">
+      <x:c r="I49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="J49" s="38" t="n">
+      <x:c r="J49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="K49" s="38" t="n">
+      <x:c r="K49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="L49" s="38" t="n">
+      <x:c r="L49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="M49" s="38" t="n">
+      <x:c r="M49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="N49" s="38" t="n">
+      <x:c r="N49" s="43" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="O49" s="36" t="n">
+      <x:c r="O49" s="38" t="n">
         <x:f>N49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="48" t="str">
+      <x:c r="A50" s="36" t="str">
         <x:v>Headroom / (gap)</x:v>
       </x:c>
-      <x:c r="B50" s="53" t="n">
+      <x:c r="B50" s="42" t="n">
         <x:f>B48-B49</x:f>
         <x:v>258000</x:v>
       </x:c>
-      <x:c r="C50" s="53" t="n">
+      <x:c r="C50" s="42" t="n">
         <x:f>C48-C49</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="D50" s="53" t="n">
+      <x:c r="D50" s="42" t="n">
         <x:f>D48-D49</x:f>
         <x:v>225000</x:v>
       </x:c>
-      <x:c r="E50" s="53" t="n">
+      <x:c r="E50" s="42" t="n">
         <x:f>E48-E49</x:f>
         <x:v>193000</x:v>
       </x:c>
-      <x:c r="F50" s="53" t="n">
+      <x:c r="F50" s="42" t="n">
         <x:f>F48-F49</x:f>
         <x:v>101000</x:v>
       </x:c>
-      <x:c r="G50" s="53" t="n">
+      <x:c r="G50" s="42" t="n">
         <x:f>G48-G49</x:f>
         <x:v>33000</x:v>
       </x:c>
-      <x:c r="H50" s="53" t="n">
+      <x:c r="H50" s="42" t="n">
         <x:f>H48-H49</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="I50" s="53" t="n">
+      <x:c r="I50" s="42" t="n">
         <x:f>I48-I49</x:f>
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="J50" s="53" t="n">
+      <x:c r="J50" s="42" t="n">
         <x:f>J48-J49</x:f>
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="K50" s="53" t="n">
+      <x:c r="K50" s="42" t="n">
         <x:f>K48-K49</x:f>
         <x:v>37000</x:v>
       </x:c>
-      <x:c r="L50" s="53" t="n">
+      <x:c r="L50" s="42" t="n">
         <x:f>L48-L49</x:f>
         <x:v>-1000</x:v>
       </x:c>
-      <x:c r="M50" s="53" t="n">
+      <x:c r="M50" s="42" t="n">
         <x:f>M48-M49</x:f>
         <x:v>-18000</x:v>
       </x:c>
-      <x:c r="N50" s="53" t="n">
+      <x:c r="N50" s="42" t="n">
         <x:f>N48-N49</x:f>
         <x:v>-69000</x:v>
       </x:c>
-      <x:c r="O50" s="50" t="n">
+      <x:c r="O50" s="39" t="n">
         <x:f>N50</x:f>
         <x:v>-69000</x:v>
       </x:c>
@@ -4767,18 +4878,18 @@
     <x:mergeCell ref="A2:O2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B51:N51">
-    <x:cfRule type="expression" dxfId="8" priority="1">
+    <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>B51="BELOW BUFFER"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="9" priority="2">
+    <x:cfRule type="expression" dxfId="1" priority="2">
       <x:formula>B51="WATCH"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="10" priority="3">
+    <x:cfRule type="expression" dxfId="2" priority="3">
       <x:formula>B51="OK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03cec6b27bdd4e44"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39f6cd30e8d746ad"/>
 </x:worksheet>
 </file>
 
@@ -4786,15 +4897,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="19" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="19" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="19" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="19" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -4809,10 +4925,15 @@
       <x:c r="G1" s="4"/>
       <x:c r="H1" s="4"/>
       <x:c r="I1" s="4"/>
+      <x:c r="J1" s="4"/>
+      <x:c r="K1" s="4"/>
+      <x:c r="L1" s="4"/>
+      <x:c r="M1" s="4"/>
+      <x:c r="N1" s="4"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Record actual closing cash, actions and ownership each week. Variance remains blank until an actual is entered.</x:v>
+        <x:v>Compare forecast and actual receipts, payments and closing cash. Variances remain blank until the related actual is entered.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -4822,319 +4943,634 @@
       <x:c r="G2" s="8"/>
       <x:c r="H2" s="8"/>
       <x:c r="I2" s="8"/>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="28" t="str">
-        <x:v>Week</x:v>
-      </x:c>
-      <x:c r="B5" s="28" t="str">
-        <x:v>Week ending</x:v>
-      </x:c>
-      <x:c r="C5" s="28" t="str">
+      <x:c r="J2" s="8"/>
+      <x:c r="K2" s="8"/>
+      <x:c r="L2" s="8"/>
+      <x:c r="M2" s="8"/>
+      <x:c r="N2" s="8"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="44" t="str">
+        <x:v>Week start</x:v>
+      </x:c>
+      <x:c r="B5" s="44" t="str">
+        <x:v>Week end</x:v>
+      </x:c>
+      <x:c r="C5" s="44" t="str">
+        <x:v>Forecast receipts</x:v>
+      </x:c>
+      <x:c r="D5" s="44" t="str">
+        <x:v>Actual receipts</x:v>
+      </x:c>
+      <x:c r="E5" s="44" t="str">
+        <x:v>Receipt variance $</x:v>
+      </x:c>
+      <x:c r="F5" s="44" t="str">
+        <x:v>Receipt variance %</x:v>
+      </x:c>
+      <x:c r="G5" s="44" t="str">
+        <x:v>Forecast payments</x:v>
+      </x:c>
+      <x:c r="H5" s="44" t="str">
+        <x:v>Actual payments</x:v>
+      </x:c>
+      <x:c r="I5" s="44" t="str">
+        <x:v>Payment variance $</x:v>
+      </x:c>
+      <x:c r="J5" s="44" t="str">
+        <x:v>Payment variance %</x:v>
+      </x:c>
+      <x:c r="K5" s="44" t="str">
         <x:v>Forecast closing cash</x:v>
       </x:c>
-      <x:c r="D5" s="28" t="str">
+      <x:c r="L5" s="44" t="str">
         <x:v>Actual closing cash</x:v>
       </x:c>
-      <x:c r="E5" s="28" t="str">
-        <x:v>Variance</x:v>
-      </x:c>
-      <x:c r="F5" s="28" t="str">
-        <x:v>Rolling forecast note</x:v>
-      </x:c>
-      <x:c r="G5" s="28" t="str">
-        <x:v>Owner</x:v>
-      </x:c>
-      <x:c r="H5" s="28" t="str">
-        <x:v>Action</x:v>
-      </x:c>
-      <x:c r="I5" s="28" t="str">
-        <x:v>Status</x:v>
+      <x:c r="M5" s="44" t="str">
+        <x:v>Closing-cash variance</x:v>
+      </x:c>
+      <x:c r="N5" s="44" t="str">
+        <x:v>Owner commentary</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B6" s="37" t="n">
+      <x:c r="A6" s="46" t="n">
+        <x:f>'13-Week Forecast'!B$5</x:f>
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="B6" s="46" t="n">
         <x:f>'13-Week Forecast'!B$6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C6" s="38" t="n">
+      <x:c r="C6" s="43" t="n">
+        <x:f>'13-Week Forecast'!B$19</x:f>
+        <x:v>170000</x:v>
+      </x:c>
+      <x:c r="D6" s="37"/>
+      <x:c r="E6" s="41" t="str">
+        <x:f>IF(D6="","",D6-C6)</x:f>
+      </x:c>
+      <x:c r="F6" s="47" t="str">
+        <x:f>IF(OR(D6="",C6=0),"",(D6-C6)/C6)</x:f>
+      </x:c>
+      <x:c r="G6" s="43" t="n">
+        <x:f>'13-Week Forecast'!B$43</x:f>
+        <x:v>212000</x:v>
+      </x:c>
+      <x:c r="H6" s="37"/>
+      <x:c r="I6" s="41" t="str">
+        <x:f>IF(H6="","",G6-H6)</x:f>
+      </x:c>
+      <x:c r="J6" s="47" t="str">
+        <x:f>IF(OR(H6="",G6=0),"",(G6-H6)/G6)</x:f>
+      </x:c>
+      <x:c r="K6" s="43" t="n">
         <x:f>'13-Week Forecast'!B$48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="D6" s="49"/>
-      <x:c r="E6" s="52" t="str">
-        <x:f>IF(D6="","",D6-C6)</x:f>
-      </x:c>
-      <x:c r="F6" s="16"/>
-      <x:c r="G6" s="16"/>
-      <x:c r="H6" s="16"/>
-      <x:c r="I6" s="16"/>
+      <x:c r="L6" s="37"/>
+      <x:c r="M6" s="41" t="str">
+        <x:f>IF(L6="","",L6-K6)</x:f>
+      </x:c>
+      <x:c r="N6" s="16"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B7" s="37" t="n">
+      <x:c r="A7" s="46" t="n">
+        <x:f>'13-Week Forecast'!C$5</x:f>
+        <x:v>46272</x:v>
+      </x:c>
+      <x:c r="B7" s="46" t="n">
         <x:f>'13-Week Forecast'!C$6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="C7" s="38" t="n">
+      <x:c r="C7" s="43" t="n">
+        <x:f>'13-Week Forecast'!C$19</x:f>
+        <x:v>169000</x:v>
+      </x:c>
+      <x:c r="D7" s="37"/>
+      <x:c r="E7" s="41" t="str">
+        <x:f>IF(D7="","",D7-C7)</x:f>
+      </x:c>
+      <x:c r="F7" s="47" t="str">
+        <x:f>IF(OR(D7="",C7=0),"",(D7-C7)/C7)</x:f>
+      </x:c>
+      <x:c r="G7" s="43" t="n">
+        <x:f>'13-Week Forecast'!C$43</x:f>
+        <x:v>178000</x:v>
+      </x:c>
+      <x:c r="H7" s="37"/>
+      <x:c r="I7" s="41" t="str">
+        <x:f>IF(H7="","",G7-H7)</x:f>
+      </x:c>
+      <x:c r="J7" s="47" t="str">
+        <x:f>IF(OR(H7="",G7=0),"",(G7-H7)/G7)</x:f>
+      </x:c>
+      <x:c r="K7" s="43" t="n">
         <x:f>'13-Week Forecast'!C$48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="D7" s="49"/>
-      <x:c r="E7" s="52" t="str">
-        <x:f>IF(D7="","",D7-C7)</x:f>
-      </x:c>
-      <x:c r="F7" s="16"/>
-      <x:c r="G7" s="16"/>
-      <x:c r="H7" s="16"/>
-      <x:c r="I7" s="16"/>
+      <x:c r="L7" s="37"/>
+      <x:c r="M7" s="41" t="str">
+        <x:f>IF(L7="","",L7-K7)</x:f>
+      </x:c>
+      <x:c r="N7" s="16"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="37" t="n">
+      <x:c r="A8" s="46" t="n">
+        <x:f>'13-Week Forecast'!D$5</x:f>
+        <x:v>46279</x:v>
+      </x:c>
+      <x:c r="B8" s="46" t="n">
         <x:f>'13-Week Forecast'!D$6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="C8" s="38" t="n">
+      <x:c r="C8" s="43" t="n">
+        <x:f>'13-Week Forecast'!D$19</x:f>
+        <x:v>158000</x:v>
+      </x:c>
+      <x:c r="D8" s="37"/>
+      <x:c r="E8" s="41" t="str">
+        <x:f>IF(D8="","",D8-C8)</x:f>
+      </x:c>
+      <x:c r="F8" s="47" t="str">
+        <x:f>IF(OR(D8="",C8=0),"",(D8-C8)/C8)</x:f>
+      </x:c>
+      <x:c r="G8" s="43" t="n">
+        <x:f>'13-Week Forecast'!D$43</x:f>
+        <x:v>182000</x:v>
+      </x:c>
+      <x:c r="H8" s="37"/>
+      <x:c r="I8" s="41" t="str">
+        <x:f>IF(H8="","",G8-H8)</x:f>
+      </x:c>
+      <x:c r="J8" s="47" t="str">
+        <x:f>IF(OR(H8="",G8=0),"",(G8-H8)/G8)</x:f>
+      </x:c>
+      <x:c r="K8" s="43" t="n">
         <x:f>'13-Week Forecast'!D$48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="D8" s="49"/>
-      <x:c r="E8" s="52" t="str">
-        <x:f>IF(D8="","",D8-C8)</x:f>
-      </x:c>
-      <x:c r="F8" s="16"/>
-      <x:c r="G8" s="16"/>
-      <x:c r="H8" s="16"/>
-      <x:c r="I8" s="16"/>
+      <x:c r="L8" s="37"/>
+      <x:c r="M8" s="41" t="str">
+        <x:f>IF(L8="","",L8-K8)</x:f>
+      </x:c>
+      <x:c r="N8" s="16"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B9" s="37" t="n">
+      <x:c r="A9" s="46" t="n">
+        <x:f>'13-Week Forecast'!E$5</x:f>
+        <x:v>46286</x:v>
+      </x:c>
+      <x:c r="B9" s="46" t="n">
         <x:f>'13-Week Forecast'!E$6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="C9" s="38" t="n">
+      <x:c r="C9" s="43" t="n">
+        <x:f>'13-Week Forecast'!E$19</x:f>
+        <x:v>147000</x:v>
+      </x:c>
+      <x:c r="D9" s="37"/>
+      <x:c r="E9" s="41" t="str">
+        <x:f>IF(D9="","",D9-C9)</x:f>
+      </x:c>
+      <x:c r="F9" s="47" t="str">
+        <x:f>IF(OR(D9="",C9=0),"",(D9-C9)/C9)</x:f>
+      </x:c>
+      <x:c r="G9" s="43" t="n">
+        <x:f>'13-Week Forecast'!E$43</x:f>
+        <x:v>179000</x:v>
+      </x:c>
+      <x:c r="H9" s="37"/>
+      <x:c r="I9" s="41" t="str">
+        <x:f>IF(H9="","",G9-H9)</x:f>
+      </x:c>
+      <x:c r="J9" s="47" t="str">
+        <x:f>IF(OR(H9="",G9=0),"",(G9-H9)/G9)</x:f>
+      </x:c>
+      <x:c r="K9" s="43" t="n">
         <x:f>'13-Week Forecast'!E$48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="D9" s="49"/>
-      <x:c r="E9" s="52" t="str">
-        <x:f>IF(D9="","",D9-C9)</x:f>
-      </x:c>
-      <x:c r="F9" s="16"/>
-      <x:c r="G9" s="16"/>
-      <x:c r="H9" s="16"/>
-      <x:c r="I9" s="16"/>
+      <x:c r="L9" s="37"/>
+      <x:c r="M9" s="41" t="str">
+        <x:f>IF(L9="","",L9-K9)</x:f>
+      </x:c>
+      <x:c r="N9" s="16"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="37" t="n">
+      <x:c r="A10" s="46" t="n">
+        <x:f>'13-Week Forecast'!F$5</x:f>
+        <x:v>46293</x:v>
+      </x:c>
+      <x:c r="B10" s="46" t="n">
         <x:f>'13-Week Forecast'!F$6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="C10" s="38" t="n">
+      <x:c r="C10" s="43" t="n">
+        <x:f>'13-Week Forecast'!F$19</x:f>
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="D10" s="37"/>
+      <x:c r="E10" s="41" t="str">
+        <x:f>IF(D10="","",D10-C10)</x:f>
+      </x:c>
+      <x:c r="F10" s="47" t="str">
+        <x:f>IF(OR(D10="",C10=0),"",(D10-C10)/C10)</x:f>
+      </x:c>
+      <x:c r="G10" s="43" t="n">
+        <x:f>'13-Week Forecast'!F$43</x:f>
+        <x:v>232000</x:v>
+      </x:c>
+      <x:c r="H10" s="37"/>
+      <x:c r="I10" s="41" t="str">
+        <x:f>IF(H10="","",G10-H10)</x:f>
+      </x:c>
+      <x:c r="J10" s="47" t="str">
+        <x:f>IF(OR(H10="",G10=0),"",(G10-H10)/G10)</x:f>
+      </x:c>
+      <x:c r="K10" s="43" t="n">
         <x:f>'13-Week Forecast'!F$48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="D10" s="49"/>
-      <x:c r="E10" s="52" t="str">
-        <x:f>IF(D10="","",D10-C10)</x:f>
-      </x:c>
-      <x:c r="F10" s="16"/>
-      <x:c r="G10" s="16"/>
-      <x:c r="H10" s="16"/>
-      <x:c r="I10" s="16"/>
+      <x:c r="L10" s="37"/>
+      <x:c r="M10" s="41" t="str">
+        <x:f>IF(L10="","",L10-K10)</x:f>
+      </x:c>
+      <x:c r="N10" s="16"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B11" s="37" t="n">
+      <x:c r="A11" s="46" t="n">
+        <x:f>'13-Week Forecast'!G$5</x:f>
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="B11" s="46" t="n">
         <x:f>'13-Week Forecast'!G$6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="C11" s="38" t="n">
+      <x:c r="C11" s="43" t="n">
+        <x:f>'13-Week Forecast'!G$19</x:f>
+        <x:v>141000</x:v>
+      </x:c>
+      <x:c r="D11" s="37"/>
+      <x:c r="E11" s="41" t="str">
+        <x:f>IF(D11="","",D11-C11)</x:f>
+      </x:c>
+      <x:c r="F11" s="47" t="str">
+        <x:f>IF(OR(D11="",C11=0),"",(D11-C11)/C11)</x:f>
+      </x:c>
+      <x:c r="G11" s="43" t="n">
+        <x:f>'13-Week Forecast'!G$43</x:f>
+        <x:v>209000</x:v>
+      </x:c>
+      <x:c r="H11" s="37"/>
+      <x:c r="I11" s="41" t="str">
+        <x:f>IF(H11="","",G11-H11)</x:f>
+      </x:c>
+      <x:c r="J11" s="47" t="str">
+        <x:f>IF(OR(H11="",G11=0),"",(G11-H11)/G11)</x:f>
+      </x:c>
+      <x:c r="K11" s="43" t="n">
         <x:f>'13-Week Forecast'!G$48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="D11" s="49"/>
-      <x:c r="E11" s="52" t="str">
-        <x:f>IF(D11="","",D11-C11)</x:f>
-      </x:c>
-      <x:c r="F11" s="16"/>
-      <x:c r="G11" s="16"/>
-      <x:c r="H11" s="16"/>
-      <x:c r="I11" s="16"/>
+      <x:c r="L11" s="37"/>
+      <x:c r="M11" s="41" t="str">
+        <x:f>IF(L11="","",L11-K11)</x:f>
+      </x:c>
+      <x:c r="N11" s="16"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B12" s="37" t="n">
+      <x:c r="A12" s="46" t="n">
+        <x:f>'13-Week Forecast'!H$5</x:f>
+        <x:v>46307</x:v>
+      </x:c>
+      <x:c r="B12" s="46" t="n">
         <x:f>'13-Week Forecast'!H$6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="C12" s="38" t="n">
+      <x:c r="C12" s="43" t="n">
+        <x:f>'13-Week Forecast'!H$19</x:f>
+        <x:v>281000</x:v>
+      </x:c>
+      <x:c r="D12" s="37"/>
+      <x:c r="E12" s="41" t="str">
+        <x:f>IF(D12="","",D12-C12)</x:f>
+      </x:c>
+      <x:c r="F12" s="47" t="str">
+        <x:f>IF(OR(D12="",C12=0),"",(D12-C12)/C12)</x:f>
+      </x:c>
+      <x:c r="G12" s="43" t="n">
+        <x:f>'13-Week Forecast'!H$43</x:f>
+        <x:v>197000</x:v>
+      </x:c>
+      <x:c r="H12" s="37"/>
+      <x:c r="I12" s="41" t="str">
+        <x:f>IF(H12="","",G12-H12)</x:f>
+      </x:c>
+      <x:c r="J12" s="47" t="str">
+        <x:f>IF(OR(H12="",G12=0),"",(G12-H12)/G12)</x:f>
+      </x:c>
+      <x:c r="K12" s="43" t="n">
         <x:f>'13-Week Forecast'!H$48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="D12" s="49"/>
-      <x:c r="E12" s="52" t="str">
-        <x:f>IF(D12="","",D12-C12)</x:f>
-      </x:c>
-      <x:c r="F12" s="16"/>
-      <x:c r="G12" s="16"/>
-      <x:c r="H12" s="16"/>
-      <x:c r="I12" s="16"/>
+      <x:c r="L12" s="37"/>
+      <x:c r="M12" s="41" t="str">
+        <x:f>IF(L12="","",L12-K12)</x:f>
+      </x:c>
+      <x:c r="N12" s="16"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B13" s="37" t="n">
+      <x:c r="A13" s="46" t="n">
+        <x:f>'13-Week Forecast'!I$5</x:f>
+        <x:v>46314</x:v>
+      </x:c>
+      <x:c r="B13" s="46" t="n">
         <x:f>'13-Week Forecast'!I$6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="C13" s="38" t="n">
+      <x:c r="C13" s="43" t="n">
+        <x:f>'13-Week Forecast'!I$19</x:f>
+        <x:v>135000</x:v>
+      </x:c>
+      <x:c r="D13" s="37"/>
+      <x:c r="E13" s="41" t="str">
+        <x:f>IF(D13="","",D13-C13)</x:f>
+      </x:c>
+      <x:c r="F13" s="47" t="str">
+        <x:f>IF(OR(D13="",C13=0),"",(D13-C13)/C13)</x:f>
+      </x:c>
+      <x:c r="G13" s="43" t="n">
+        <x:f>'13-Week Forecast'!I$43</x:f>
+        <x:v>192000</x:v>
+      </x:c>
+      <x:c r="H13" s="37"/>
+      <x:c r="I13" s="41" t="str">
+        <x:f>IF(H13="","",G13-H13)</x:f>
+      </x:c>
+      <x:c r="J13" s="47" t="str">
+        <x:f>IF(OR(H13="",G13=0),"",(G13-H13)/G13)</x:f>
+      </x:c>
+      <x:c r="K13" s="43" t="n">
         <x:f>'13-Week Forecast'!I$48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="D13" s="49"/>
-      <x:c r="E13" s="52" t="str">
-        <x:f>IF(D13="","",D13-C13)</x:f>
-      </x:c>
-      <x:c r="F13" s="16"/>
-      <x:c r="G13" s="16"/>
-      <x:c r="H13" s="16"/>
-      <x:c r="I13" s="16"/>
+      <x:c r="L13" s="37"/>
+      <x:c r="M13" s="41" t="str">
+        <x:f>IF(L13="","",L13-K13)</x:f>
+      </x:c>
+      <x:c r="N13" s="16"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B14" s="37" t="n">
+      <x:c r="A14" s="46" t="n">
+        <x:f>'13-Week Forecast'!J$5</x:f>
+        <x:v>46321</x:v>
+      </x:c>
+      <x:c r="B14" s="46" t="n">
         <x:f>'13-Week Forecast'!J$6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="C14" s="38" t="n">
+      <x:c r="C14" s="43" t="n">
+        <x:f>'13-Week Forecast'!J$19</x:f>
+        <x:v>264000</x:v>
+      </x:c>
+      <x:c r="D14" s="37"/>
+      <x:c r="E14" s="41" t="str">
+        <x:f>IF(D14="","",D14-C14)</x:f>
+      </x:c>
+      <x:c r="F14" s="47" t="str">
+        <x:f>IF(OR(D14="",C14=0),"",(D14-C14)/C14)</x:f>
+      </x:c>
+      <x:c r="G14" s="43" t="n">
+        <x:f>'13-Week Forecast'!J$43</x:f>
+        <x:v>307000</x:v>
+      </x:c>
+      <x:c r="H14" s="37"/>
+      <x:c r="I14" s="41" t="str">
+        <x:f>IF(H14="","",G14-H14)</x:f>
+      </x:c>
+      <x:c r="J14" s="47" t="str">
+        <x:f>IF(OR(H14="",G14=0),"",(G14-H14)/G14)</x:f>
+      </x:c>
+      <x:c r="K14" s="43" t="n">
         <x:f>'13-Week Forecast'!J$48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="D14" s="49"/>
-      <x:c r="E14" s="52" t="str">
-        <x:f>IF(D14="","",D14-C14)</x:f>
-      </x:c>
-      <x:c r="F14" s="16"/>
-      <x:c r="G14" s="16"/>
-      <x:c r="H14" s="16"/>
-      <x:c r="I14" s="16"/>
+      <x:c r="L14" s="37"/>
+      <x:c r="M14" s="41" t="str">
+        <x:f>IF(L14="","",L14-K14)</x:f>
+      </x:c>
+      <x:c r="N14" s="16"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B15" s="37" t="n">
+      <x:c r="A15" s="46" t="n">
+        <x:f>'13-Week Forecast'!K$5</x:f>
+        <x:v>46328</x:v>
+      </x:c>
+      <x:c r="B15" s="46" t="n">
         <x:f>'13-Week Forecast'!K$6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="C15" s="38" t="n">
+      <x:c r="C15" s="43" t="n">
+        <x:f>'13-Week Forecast'!K$19</x:f>
+        <x:v>249000</x:v>
+      </x:c>
+      <x:c r="D15" s="37"/>
+      <x:c r="E15" s="41" t="str">
+        <x:f>IF(D15="","",D15-C15)</x:f>
+      </x:c>
+      <x:c r="F15" s="47" t="str">
+        <x:f>IF(OR(D15="",C15=0),"",(D15-C15)/C15)</x:f>
+      </x:c>
+      <x:c r="G15" s="43" t="n">
+        <x:f>'13-Week Forecast'!K$43</x:f>
+        <x:v>229000</x:v>
+      </x:c>
+      <x:c r="H15" s="37"/>
+      <x:c r="I15" s="41" t="str">
+        <x:f>IF(H15="","",G15-H15)</x:f>
+      </x:c>
+      <x:c r="J15" s="47" t="str">
+        <x:f>IF(OR(H15="",G15=0),"",(G15-H15)/G15)</x:f>
+      </x:c>
+      <x:c r="K15" s="43" t="n">
         <x:f>'13-Week Forecast'!K$48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="D15" s="49"/>
-      <x:c r="E15" s="52" t="str">
-        <x:f>IF(D15="","",D15-C15)</x:f>
-      </x:c>
-      <x:c r="F15" s="16"/>
-      <x:c r="G15" s="16"/>
-      <x:c r="H15" s="16"/>
-      <x:c r="I15" s="16"/>
+      <x:c r="L15" s="37"/>
+      <x:c r="M15" s="41" t="str">
+        <x:f>IF(L15="","",L15-K15)</x:f>
+      </x:c>
+      <x:c r="N15" s="16"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B16" s="37" t="n">
+      <x:c r="A16" s="46" t="n">
+        <x:f>'13-Week Forecast'!L$5</x:f>
+        <x:v>46335</x:v>
+      </x:c>
+      <x:c r="B16" s="46" t="n">
         <x:f>'13-Week Forecast'!L$6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="C16" s="38" t="n">
+      <x:c r="C16" s="43" t="n">
+        <x:f>'13-Week Forecast'!L$19</x:f>
+        <x:v>154000</x:v>
+      </x:c>
+      <x:c r="D16" s="37"/>
+      <x:c r="E16" s="41" t="str">
+        <x:f>IF(D16="","",D16-C16)</x:f>
+      </x:c>
+      <x:c r="F16" s="47" t="str">
+        <x:f>IF(OR(D16="",C16=0),"",(D16-C16)/C16)</x:f>
+      </x:c>
+      <x:c r="G16" s="43" t="n">
+        <x:f>'13-Week Forecast'!L$43</x:f>
+        <x:v>192000</x:v>
+      </x:c>
+      <x:c r="H16" s="37"/>
+      <x:c r="I16" s="41" t="str">
+        <x:f>IF(H16="","",G16-H16)</x:f>
+      </x:c>
+      <x:c r="J16" s="47" t="str">
+        <x:f>IF(OR(H16="",G16=0),"",(G16-H16)/G16)</x:f>
+      </x:c>
+      <x:c r="K16" s="43" t="n">
         <x:f>'13-Week Forecast'!L$48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="D16" s="49"/>
-      <x:c r="E16" s="52" t="str">
-        <x:f>IF(D16="","",D16-C16)</x:f>
-      </x:c>
-      <x:c r="F16" s="16"/>
-      <x:c r="G16" s="16"/>
-      <x:c r="H16" s="16"/>
-      <x:c r="I16" s="16"/>
+      <x:c r="L16" s="37"/>
+      <x:c r="M16" s="41" t="str">
+        <x:f>IF(L16="","",L16-K16)</x:f>
+      </x:c>
+      <x:c r="N16" s="16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B17" s="37" t="n">
+      <x:c r="A17" s="46" t="n">
+        <x:f>'13-Week Forecast'!M$5</x:f>
+        <x:v>46342</x:v>
+      </x:c>
+      <x:c r="B17" s="46" t="n">
         <x:f>'13-Week Forecast'!M$6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="C17" s="38" t="n">
+      <x:c r="C17" s="43" t="n">
+        <x:f>'13-Week Forecast'!M$19</x:f>
+        <x:v>162000</x:v>
+      </x:c>
+      <x:c r="D17" s="37"/>
+      <x:c r="E17" s="41" t="str">
+        <x:f>IF(D17="","",D17-C17)</x:f>
+      </x:c>
+      <x:c r="F17" s="47" t="str">
+        <x:f>IF(OR(D17="",C17=0),"",(D17-C17)/C17)</x:f>
+      </x:c>
+      <x:c r="G17" s="43" t="n">
+        <x:f>'13-Week Forecast'!M$43</x:f>
+        <x:v>179000</x:v>
+      </x:c>
+      <x:c r="H17" s="37"/>
+      <x:c r="I17" s="41" t="str">
+        <x:f>IF(H17="","",G17-H17)</x:f>
+      </x:c>
+      <x:c r="J17" s="47" t="str">
+        <x:f>IF(OR(H17="",G17=0),"",(G17-H17)/G17)</x:f>
+      </x:c>
+      <x:c r="K17" s="43" t="n">
         <x:f>'13-Week Forecast'!M$48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="D17" s="49"/>
-      <x:c r="E17" s="52" t="str">
-        <x:f>IF(D17="","",D17-C17)</x:f>
-      </x:c>
-      <x:c r="F17" s="16"/>
-      <x:c r="G17" s="16"/>
-      <x:c r="H17" s="16"/>
-      <x:c r="I17" s="16"/>
+      <x:c r="L17" s="37"/>
+      <x:c r="M17" s="41" t="str">
+        <x:f>IF(L17="","",L17-K17)</x:f>
+      </x:c>
+      <x:c r="N17" s="16"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B18" s="37" t="n">
+      <x:c r="A18" s="46" t="n">
+        <x:f>'13-Week Forecast'!N$5</x:f>
+        <x:v>46349</x:v>
+      </x:c>
+      <x:c r="B18" s="46" t="n">
         <x:f>'13-Week Forecast'!N$6</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="C18" s="38" t="n">
+      <x:c r="C18" s="43" t="n">
+        <x:f>'13-Week Forecast'!N$19</x:f>
+        <x:v>168000</x:v>
+      </x:c>
+      <x:c r="D18" s="37"/>
+      <x:c r="E18" s="41" t="str">
+        <x:f>IF(D18="","",D18-C18)</x:f>
+      </x:c>
+      <x:c r="F18" s="47" t="str">
+        <x:f>IF(OR(D18="",C18=0),"",(D18-C18)/C18)</x:f>
+      </x:c>
+      <x:c r="G18" s="43" t="n">
+        <x:f>'13-Week Forecast'!N$43</x:f>
+        <x:v>219000</x:v>
+      </x:c>
+      <x:c r="H18" s="37"/>
+      <x:c r="I18" s="41" t="str">
+        <x:f>IF(H18="","",G18-H18)</x:f>
+      </x:c>
+      <x:c r="J18" s="47" t="str">
+        <x:f>IF(OR(H18="",G18=0),"",(G18-H18)/G18)</x:f>
+      </x:c>
+      <x:c r="K18" s="43" t="n">
         <x:f>'13-Week Forecast'!N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D18" s="49"/>
-      <x:c r="E18" s="52" t="str">
-        <x:f>IF(D18="","",D18-C18)</x:f>
-      </x:c>
-      <x:c r="F18" s="16"/>
-      <x:c r="G18" s="16"/>
-      <x:c r="H18" s="16"/>
-      <x:c r="I18" s="16"/>
+      <x:c r="L18" s="37"/>
+      <x:c r="M18" s="41" t="str">
+        <x:f>IF(L18="","",L18-K18)</x:f>
+      </x:c>
+      <x:c r="N18" s="16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:I1"/>
-    <x:mergeCell ref="A2:I2"/>
+    <x:mergeCell ref="A1:N1"/>
+    <x:mergeCell ref="A2:N2"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="I6:I18">
-      <x:formula1>"Open,In progress,Complete"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
+  <x:conditionalFormatting sqref="E6:E18">
+    <x:cfRule type="expression" dxfId="3" priority="1">
+      <x:formula>E6&gt;0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="4" priority="2">
+      <x:formula>E6&lt;0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="I6:I18">
+    <x:cfRule type="expression" dxfId="5" priority="3">
+      <x:formula>I6&gt;0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="6" priority="4">
+      <x:formula>I6&lt;0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="M6:M18">
+    <x:cfRule type="expression" dxfId="7" priority="5">
+      <x:formula>M6&gt;0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="8" priority="6">
+      <x:formula>M6&lt;0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F6:F18">
+    <x:cfRule type="expression" dxfId="9" priority="7">
+      <x:formula>F6&gt;0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="10" priority="8">
+      <x:formula>F6&lt;0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="J6:J18">
+    <x:cfRule type="expression" dxfId="11" priority="9">
+      <x:formula>J6&gt;0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="12" priority="10">
+      <x:formula>J6&lt;0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -5178,19 +5614,19 @@
       <x:c r="H2" s="8"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="55" t="str">
+      <x:c r="A4" s="49" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="B4" s="55" t="str">
+      <x:c r="B4" s="49" t="str">
         <x:f>IF(COUNTIF(F8:F16,"PASS")=9,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C4" s="55"/>
-      <x:c r="D4" s="55" t="str">
+      <x:c r="C4" s="49"/>
+      <x:c r="D4" s="49" t="str">
         <x:v>LIQUIDITY STATUS</x:v>
       </x:c>
-      <x:c r="E4" s="55" t="str">
-        <x:f>IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"BELOW BUFFER")&gt;0,"ACTION REQUIRED",IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"WATCH")&gt;0,"WATCH","HEALTHY"))</x:f>
+      <x:c r="E4" s="49" t="str">
+        <x:f>IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"BELOW BUFFER")&gt;0,"ACTION REQUIRED",IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"WATCH")&gt;0,"WATCH","OK"))</x:f>
         <x:v>ACTION REQUIRED</x:v>
       </x:c>
     </x:row>
@@ -5222,21 +5658,21 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="15" t="str">
-        <x:v>Forecast starts Monday</x:v>
-      </x:c>
-      <x:c r="B8" s="56" t="n">
-        <x:f>WEEKDAY('Assumptions'!$B$8,2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="56" t="n">
-        <x:f>1</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="56" t="n">
+        <x:v>Exactly 13 forecast weeks</x:v>
+      </x:c>
+      <x:c r="B8" s="50" t="n">
+        <x:f>COLUMNS('13-Week Forecast'!$B$5:$N$5)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="50" t="n">
+        <x:f>13</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D8" s="50" t="n">
         <x:f>B8-C8</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E8" s="56" t="n">
+      <x:c r="E8" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="15" t="str">
@@ -5244,29 +5680,29 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="15" t="str">
-        <x:v>Assumptions!B8</x:v>
+        <x:v>13-Week Forecast!B5:N5</x:v>
       </x:c>
       <x:c r="H8" s="15" t="str">
-        <x:v>Forecast start date must be a Monday.</x:v>
+        <x:v>The weekly horizon must contain exactly 13 columns.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="15" t="str">
-        <x:v>As-at date in forecast horizon</x:v>
-      </x:c>
-      <x:c r="B9" s="56" t="n">
-        <x:f>--AND('Assumptions'!$B$9&gt;='13-Week Forecast'!$B$5,'Assumptions'!$B$9&lt;='13-Week Forecast'!$N$6)</x:f>
+        <x:v>Forecast starts Monday</x:v>
+      </x:c>
+      <x:c r="B9" s="50" t="n">
+        <x:f>WEEKDAY('Assumptions'!$B$8,2)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C9" s="56" t="n">
+      <x:c r="C9" s="50" t="n">
         <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D9" s="56" t="n">
+      <x:c r="D9" s="50" t="n">
         <x:f>B9-C9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E9" s="56" t="n">
+      <x:c r="E9" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="15" t="str">
@@ -5274,29 +5710,29 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G9" s="15" t="str">
-        <x:v>Assumptions!B9</x:v>
+        <x:v>Assumptions!B8</x:v>
       </x:c>
       <x:c r="H9" s="15" t="str">
-        <x:v>Keep the as-at date inside the displayed 13 weeks.</x:v>
+        <x:v>Forecast start date must be a Monday.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="15" t="str">
         <x:v>Selected scenario recognised</x:v>
       </x:c>
-      <x:c r="B10" s="56" t="n">
+      <x:c r="B10" s="50" t="n">
         <x:f>COUNTIF('Assumptions'!$B$15:$B$17,'Assumptions'!$B$12)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="56" t="n">
+      <x:c r="C10" s="50" t="n">
         <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D10" s="56" t="n">
+      <x:c r="D10" s="50" t="n">
         <x:f>B10-C10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="56" t="n">
+      <x:c r="E10" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str">
@@ -5314,19 +5750,19 @@
       <x:c r="A11" s="15" t="str">
         <x:v>Week 1 opening cash ties</x:v>
       </x:c>
-      <x:c r="B11" s="57" t="n">
+      <x:c r="B11" s="51" t="n">
         <x:f>'13-Week Forecast'!$B$46</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="C11" s="57" t="n">
+      <x:c r="C11" s="51" t="n">
         <x:f>'Assumptions'!$B$10</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="D11" s="56" t="n">
+      <x:c r="D11" s="50" t="n">
         <x:f>B11-C11</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="56" t="n">
+      <x:c r="E11" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="15" t="str">
@@ -5342,21 +5778,21 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="15" t="str">
-        <x:v>Opening cash roll-forward continuity</x:v>
-      </x:c>
-      <x:c r="B12" s="56" t="n">
-        <x:f>ABS('13-Week Forecast'!$C$46-'13-Week Forecast'!$B$48)+ABS('13-Week Forecast'!$D$46-'13-Week Forecast'!$C$48)+ABS('13-Week Forecast'!$E$46-'13-Week Forecast'!$D$48)+ABS('13-Week Forecast'!$F$46-'13-Week Forecast'!$E$48)+ABS('13-Week Forecast'!$G$46-'13-Week Forecast'!$F$48)+ABS('13-Week Forecast'!$H$46-'13-Week Forecast'!$G$48)+ABS('13-Week Forecast'!$I$46-'13-Week Forecast'!$H$48)+ABS('13-Week Forecast'!$J$46-'13-Week Forecast'!$I$48)+ABS('13-Week Forecast'!$K$46-'13-Week Forecast'!$J$48)+ABS('13-Week Forecast'!$L$46-'13-Week Forecast'!$K$48)+ABS('13-Week Forecast'!$M$46-'13-Week Forecast'!$L$48)+ABS('13-Week Forecast'!$N$46-'13-Week Forecast'!$M$48)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="56" t="n">
+        <x:v>Weekly cash roll-forward equations</x:v>
+      </x:c>
+      <x:c r="B12" s="50" t="n">
+        <x:f>MAX(ABS('13-Week Forecast'!$B$48-'13-Week Forecast'!$B$46-'13-Week Forecast'!$B$47),ABS('13-Week Forecast'!$C$48-'13-Week Forecast'!$C$46-'13-Week Forecast'!$C$47),ABS('13-Week Forecast'!$D$48-'13-Week Forecast'!$D$46-'13-Week Forecast'!$D$47),ABS('13-Week Forecast'!$E$48-'13-Week Forecast'!$E$46-'13-Week Forecast'!$E$47),ABS('13-Week Forecast'!$F$48-'13-Week Forecast'!$F$46-'13-Week Forecast'!$F$47),ABS('13-Week Forecast'!$G$48-'13-Week Forecast'!$G$46-'13-Week Forecast'!$G$47),ABS('13-Week Forecast'!$H$48-'13-Week Forecast'!$H$46-'13-Week Forecast'!$H$47),ABS('13-Week Forecast'!$I$48-'13-Week Forecast'!$I$46-'13-Week Forecast'!$I$47),ABS('13-Week Forecast'!$J$48-'13-Week Forecast'!$J$46-'13-Week Forecast'!$J$47),ABS('13-Week Forecast'!$K$48-'13-Week Forecast'!$K$46-'13-Week Forecast'!$K$47),ABS('13-Week Forecast'!$L$48-'13-Week Forecast'!$L$46-'13-Week Forecast'!$L$47),ABS('13-Week Forecast'!$M$48-'13-Week Forecast'!$M$46-'13-Week Forecast'!$M$47),ABS('13-Week Forecast'!$N$48-'13-Week Forecast'!$N$46-'13-Week Forecast'!$N$47),ABS('13-Week Forecast'!$C$46-'13-Week Forecast'!$B$48),ABS('13-Week Forecast'!$D$46-'13-Week Forecast'!$C$48),ABS('13-Week Forecast'!$E$46-'13-Week Forecast'!$D$48),ABS('13-Week Forecast'!$F$46-'13-Week Forecast'!$E$48),ABS('13-Week Forecast'!$G$46-'13-Week Forecast'!$F$48),ABS('13-Week Forecast'!$H$46-'13-Week Forecast'!$G$48),ABS('13-Week Forecast'!$I$46-'13-Week Forecast'!$H$48),ABS('13-Week Forecast'!$J$46-'13-Week Forecast'!$I$48),ABS('13-Week Forecast'!$K$46-'13-Week Forecast'!$J$48),ABS('13-Week Forecast'!$L$46-'13-Week Forecast'!$K$48),ABS('13-Week Forecast'!$M$46-'13-Week Forecast'!$L$48),ABS('13-Week Forecast'!$N$46-'13-Week Forecast'!$M$48))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="50" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="56" t="n">
+      <x:c r="D12" s="50" t="n">
         <x:f>B12-C12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="56" t="n">
+      <x:c r="E12" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F12" s="15" t="str">
@@ -5364,29 +5800,29 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G12" s="15" t="str">
-        <x:v>13-Week Forecast!C46:N46</x:v>
+        <x:v>13-Week Forecast!B46:N48</x:v>
       </x:c>
       <x:c r="H12" s="15" t="str">
-        <x:v>Each weekly opening cash balance must equal the prior close.</x:v>
+        <x:v>Each close must equal opening plus net movement; each opening after Week 1 must equal the prior close.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="15" t="str">
         <x:v>Cash receipt totals reconcile</x:v>
       </x:c>
-      <x:c r="B13" s="57" t="n">
-        <x:f>SUM('13-Week Forecast'!$B$19:$N$19)</x:f>
-        <x:v>2338000</x:v>
-      </x:c>
-      <x:c r="C13" s="57" t="n">
-        <x:f>SUM('13-Week Forecast'!$B$10:$N$18)</x:f>
-        <x:v>2338000</x:v>
-      </x:c>
-      <x:c r="D13" s="56" t="n">
+      <x:c r="B13" s="50" t="n">
+        <x:f>MAX(ABS('13-Week Forecast'!$B$19-SUM('13-Week Forecast'!$B$10:$B$18)),ABS('13-Week Forecast'!$C$19-SUM('13-Week Forecast'!$C$10:$C$18)),ABS('13-Week Forecast'!$D$19-SUM('13-Week Forecast'!$D$10:$D$18)),ABS('13-Week Forecast'!$E$19-SUM('13-Week Forecast'!$E$10:$E$18)),ABS('13-Week Forecast'!$F$19-SUM('13-Week Forecast'!$F$10:$F$18)),ABS('13-Week Forecast'!$G$19-SUM('13-Week Forecast'!$G$10:$G$18)),ABS('13-Week Forecast'!$H$19-SUM('13-Week Forecast'!$H$10:$H$18)),ABS('13-Week Forecast'!$I$19-SUM('13-Week Forecast'!$I$10:$I$18)),ABS('13-Week Forecast'!$J$19-SUM('13-Week Forecast'!$J$10:$J$18)),ABS('13-Week Forecast'!$K$19-SUM('13-Week Forecast'!$K$10:$K$18)),ABS('13-Week Forecast'!$L$19-SUM('13-Week Forecast'!$L$10:$L$18)),ABS('13-Week Forecast'!$M$19-SUM('13-Week Forecast'!$M$10:$M$18)),ABS('13-Week Forecast'!$N$19-SUM('13-Week Forecast'!$N$10:$N$18)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="50" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="50" t="n">
         <x:f>B13-C13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="56" t="n">
+      <x:c r="E13" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F13" s="15" t="str">
@@ -5397,26 +5833,26 @@
         <x:v>13-Week Forecast!B19:N19</x:v>
       </x:c>
       <x:c r="H13" s="15" t="str">
-        <x:v>Includes the selected-scenario receipt adjustment.</x:v>
+        <x:v>Maximum weekly difference; includes the selected-scenario receipt adjustment.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="15" t="str">
         <x:v>Cash payment totals reconcile</x:v>
       </x:c>
-      <x:c r="B14" s="57" t="n">
-        <x:f>SUM('13-Week Forecast'!$B$43:$N$43)</x:f>
-        <x:v>2707000</x:v>
-      </x:c>
-      <x:c r="C14" s="57" t="n">
-        <x:f>SUM('13-Week Forecast'!$B$22:$N$42)</x:f>
-        <x:v>2707000</x:v>
-      </x:c>
-      <x:c r="D14" s="56" t="n">
+      <x:c r="B14" s="50" t="n">
+        <x:f>MAX(ABS('13-Week Forecast'!$B$43-SUM('13-Week Forecast'!$B$22:$B$42)),ABS('13-Week Forecast'!$C$43-SUM('13-Week Forecast'!$C$22:$C$42)),ABS('13-Week Forecast'!$D$43-SUM('13-Week Forecast'!$D$22:$D$42)),ABS('13-Week Forecast'!$E$43-SUM('13-Week Forecast'!$E$22:$E$42)),ABS('13-Week Forecast'!$F$43-SUM('13-Week Forecast'!$F$22:$F$42)),ABS('13-Week Forecast'!$G$43-SUM('13-Week Forecast'!$G$22:$G$42)),ABS('13-Week Forecast'!$H$43-SUM('13-Week Forecast'!$H$22:$H$42)),ABS('13-Week Forecast'!$I$43-SUM('13-Week Forecast'!$I$22:$I$42)),ABS('13-Week Forecast'!$J$43-SUM('13-Week Forecast'!$J$22:$J$42)),ABS('13-Week Forecast'!$K$43-SUM('13-Week Forecast'!$K$22:$K$42)),ABS('13-Week Forecast'!$L$43-SUM('13-Week Forecast'!$L$22:$L$42)),ABS('13-Week Forecast'!$M$43-SUM('13-Week Forecast'!$M$22:$M$42)),ABS('13-Week Forecast'!$N$43-SUM('13-Week Forecast'!$N$22:$N$42)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="50" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="50" t="n">
         <x:f>B14-C14</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="56" t="n">
+      <x:c r="E14" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="15" t="str">
@@ -5427,26 +5863,26 @@
         <x:v>13-Week Forecast!B43:N43</x:v>
       </x:c>
       <x:c r="H14" s="15" t="str">
-        <x:v>Includes the selected-scenario payment adjustment.</x:v>
+        <x:v>Maximum weekly difference; includes the selected-scenario payment adjustment.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="15" t="str">
-        <x:v>Closing cash equation</x:v>
-      </x:c>
-      <x:c r="B15" s="57" t="n">
+        <x:v>Week 13 closing cash equation</x:v>
+      </x:c>
+      <x:c r="B15" s="51" t="n">
         <x:f>'13-Week Forecast'!$N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="C15" s="57" t="n">
+      <x:c r="C15" s="51" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!$B$47:$N$47)</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D15" s="56" t="n">
+      <x:c r="D15" s="50" t="n">
         <x:f>B15-C15</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="56" t="n">
+      <x:c r="E15" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F15" s="15" t="str">
@@ -5457,26 +5893,26 @@
         <x:v>13-Week Forecast!N48</x:v>
       </x:c>
       <x:c r="H15" s="15" t="str">
-        <x:v>Terminal cash must equal opening cash plus cumulative movement.</x:v>
+        <x:v>Week 13 close must equal opening cash plus cumulative net movement.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="15" t="str">
-        <x:v>Weekly Review linkage</x:v>
-      </x:c>
-      <x:c r="B16" s="56" t="n">
-        <x:f>ABS('Weekly Review'!$C$6-'13-Week Forecast'!$B$48)+ABS('Weekly Review'!$C$7-'13-Week Forecast'!$C$48)+ABS('Weekly Review'!$C$8-'13-Week Forecast'!$D$48)+ABS('Weekly Review'!$C$9-'13-Week Forecast'!$E$48)+ABS('Weekly Review'!$C$10-'13-Week Forecast'!$F$48)+ABS('Weekly Review'!$C$11-'13-Week Forecast'!$G$48)+ABS('Weekly Review'!$C$12-'13-Week Forecast'!$H$48)+ABS('Weekly Review'!$C$13-'13-Week Forecast'!$I$48)+ABS('Weekly Review'!$C$14-'13-Week Forecast'!$J$48)+ABS('Weekly Review'!$C$15-'13-Week Forecast'!$K$48)+ABS('Weekly Review'!$C$16-'13-Week Forecast'!$L$48)+ABS('Weekly Review'!$C$17-'13-Week Forecast'!$M$48)+ABS('Weekly Review'!$C$18-'13-Week Forecast'!$N$48)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="56" t="n">
+        <x:v>Formula-error count</x:v>
+      </x:c>
+      <x:c r="B16" s="50" t="n">
+        <x:f>SUMPRODUCT(--ISERROR('Assumptions'!$B$5:$D$17))+SUMPRODUCT(--ISERROR('13-Week Forecast'!$B$5:$O$51))+SUMPRODUCT(--ISERROR('Weekly Review'!$A$5:$N$18))+SUMPRODUCT(--ISERROR('Dashboard'!$A$6:$J$24))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="50" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="56" t="n">
+      <x:c r="D16" s="50" t="n">
         <x:f>B16-C16</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="56" t="n">
+      <x:c r="E16" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="15" t="str">
@@ -5484,10 +5920,10 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G16" s="15" t="str">
-        <x:v>Weekly Review!C6:C18</x:v>
+        <x:v>Assumptions, Forecast, Weekly Review and Dashboard</x:v>
       </x:c>
       <x:c r="H16" s="15" t="str">
-        <x:v>All 13 forecast closing-cash values must link to Weekly Review.</x:v>
+        <x:v>Any formula error in the model ranges fails this check.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -5511,147 +5947,167 @@
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="59" t="str">
+      <x:c r="A22" s="53" t="str">
         <x:v>GST standard rate</x:v>
       </x:c>
-      <x:c r="B22" s="60" t="str">
+      <x:c r="B22" s="54" t="str">
         <x:v>https://www.legislation.gov.au/C2004A00446/latest/text</x:v>
       </x:c>
-      <x:c r="C22" s="59" t="str">
+      <x:c r="C22" s="53" t="str">
         <x:v>GST default: 10% of the value of a taxable supply.</x:v>
       </x:c>
-      <x:c r="D22" s="59" t="str">
+      <x:c r="D22" s="53" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E22" s="59" t="str">
+      <x:c r="E22" s="53" t="str">
         <x:v>The 10% default does not decide whether a transaction is taxable, GST-free, input taxed or outside the GST system.</x:v>
       </x:c>
-      <x:c r="F22" s="59" t="str">
+      <x:c r="F22" s="53" t="str">
         <x:v>Keep tax classifications user-confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="59" t="str">
+      <x:c r="A23" s="53" t="str">
         <x:v>BAS due dates</x:v>
       </x:c>
-      <x:c r="B23" s="60" t="str">
+      <x:c r="B23" s="54" t="str">
         <x:v>https://www.ato.gov.au/businesses-and-organisations/preparing-lodging-and-paying/business-activity-statements-bas/due-dates-for-lodging-and-paying-your-bas</x:v>
       </x:c>
-      <x:c r="C23" s="59" t="str">
+      <x:c r="C23" s="53" t="str">
         <x:v>Monthly BAS planning pattern is generally the 21st day after the taxable period; quarterly dates are planning patterns only.</x:v>
       </x:c>
-      <x:c r="D23" s="59" t="str">
+      <x:c r="D23" s="53" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E23" s="59" t="str">
+      <x:c r="E23" s="53" t="str">
         <x:v>The issued or entity-specific BAS due date controls. Online lodgement, registered-agent arrangements, holidays and entity circumstances can change the date.</x:v>
       </x:c>
-      <x:c r="F23" s="59" t="str">
+      <x:c r="F23" s="53" t="str">
         <x:v>Use issued BAS and user-entered dates.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="59" t="str">
+      <x:c r="A24" s="53" t="str">
+        <x:v>PAYG withholding</x:v>
+      </x:c>
+      <x:c r="B24" s="54" t="str">
+        <x:v>https://www.ato.gov.au/businesses-and-organisations/hiring-and-paying-your-workers/payg-withholding</x:v>
+      </x:c>
+      <x:c r="C24" s="53" t="str">
+        <x:v>PAYG withholding payment and reporting due dates vary with business size and circumstances.</x:v>
+      </x:c>
+      <x:c r="D24" s="53" t="str">
+        <x:v>26 August 2026</x:v>
+      </x:c>
+      <x:c r="E24" s="53" t="str">
+        <x:v>Confirm the applicable due date for the entity and reporting cycle.</x:v>
+      </x:c>
+      <x:c r="F24" s="53" t="str">
+        <x:v>Keep payment dates user-entered and confirmed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="53" t="str">
         <x:v>Super guarantee</x:v>
       </x:c>
-      <x:c r="B24" s="60" t="str">
+      <x:c r="B25" s="54" t="str">
         <x:v>https://www.ato.gov.au/tax-rates-and-codes/key-superannuation-rates-and-thresholds/super-guarantee</x:v>
       </x:c>
-      <x:c r="C24" s="59" t="str">
+      <x:c r="C25" s="53" t="str">
         <x:v>Default SG rate: 12.0% from 1 July 2025, including 1 July 2026 to 30 June 2027.</x:v>
       </x:c>
-      <x:c r="D24" s="59" t="str">
+      <x:c r="D25" s="53" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E24" s="59" t="str">
+      <x:c r="E25" s="53" t="str">
         <x:v>Apply only after checking worker eligibility, earnings base and special rules.</x:v>
       </x:c>
-      <x:c r="F24" s="59" t="str">
+      <x:c r="F25" s="53" t="str">
         <x:v>Weekly super is illustrative FP&amp;A input.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="59" t="str">
+    <x:row r="26">
+      <x:c r="A26" s="53" t="str">
         <x:v>Payday Super</x:v>
       </x:c>
-      <x:c r="B25" s="60" t="str">
+      <x:c r="B26" s="54" t="str">
         <x:v>https://softwaredevelopers.ato.gov.au/PaydaySuper</x:v>
       </x:c>
-      <x:c r="C25" s="59" t="str">
+      <x:c r="C26" s="53" t="str">
         <x:v>From 1 July 2026, pay SG with each pay cycle. The fund must generally receive it by the seventh business day after payday.</x:v>
       </x:c>
-      <x:c r="D25" s="59" t="str">
+      <x:c r="D26" s="53" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E25" s="59" t="str">
+      <x:c r="E26" s="53" t="str">
         <x:v>Fund receipt, not employer submission, is the statutory timing anchor. Allow for eligible longer periods.</x:v>
       </x:c>
-      <x:c r="F25" s="59" t="str">
+      <x:c r="F26" s="53" t="str">
         <x:v>Illustrative forecast starts after the July 2026 transition.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="62" t="str">
+    <x:row r="28">
+      <x:c r="A28" s="56" t="str">
         <x:v>Disclaimer: Illustrative FP&amp;A cash-planning model only. Statutory amounts and dates are indicative assumptions, not tax, BAS, payroll, superannuation or legal advice. Entity-specific lodgement dates and tax classifications must be confirmed by the user or adviser before relying on the model or lodging or paying.</x:v>
       </x:c>
-      <x:c r="B27" s="62"/>
-      <x:c r="C27" s="62"/>
-      <x:c r="D27" s="62"/>
-      <x:c r="E27" s="62"/>
-      <x:c r="F27" s="62"/>
-      <x:c r="G27" s="62"/>
-      <x:c r="H27" s="62"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="62"/>
-      <x:c r="B28" s="62"/>
-      <x:c r="C28" s="62"/>
-      <x:c r="D28" s="62"/>
-      <x:c r="E28" s="62"/>
-      <x:c r="F28" s="62"/>
-      <x:c r="G28" s="62"/>
-      <x:c r="H28" s="62"/>
+      <x:c r="B28" s="56"/>
+      <x:c r="C28" s="56"/>
+      <x:c r="D28" s="56"/>
+      <x:c r="E28" s="56"/>
+      <x:c r="F28" s="56"/>
+      <x:c r="G28" s="56"/>
+      <x:c r="H28" s="56"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="62"/>
-      <x:c r="B29" s="62"/>
-      <x:c r="C29" s="62"/>
-      <x:c r="D29" s="62"/>
-      <x:c r="E29" s="62"/>
-      <x:c r="F29" s="62"/>
-      <x:c r="G29" s="62"/>
-      <x:c r="H29" s="62"/>
+      <x:c r="A29" s="56"/>
+      <x:c r="B29" s="56"/>
+      <x:c r="C29" s="56"/>
+      <x:c r="D29" s="56"/>
+      <x:c r="E29" s="56"/>
+      <x:c r="F29" s="56"/>
+      <x:c r="G29" s="56"/>
+      <x:c r="H29" s="56"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="56"/>
+      <x:c r="B30" s="56"/>
+      <x:c r="C30" s="56"/>
+      <x:c r="D30" s="56"/>
+      <x:c r="E30" s="56"/>
+      <x:c r="F30" s="56"/>
+      <x:c r="G30" s="56"/>
+      <x:c r="H30" s="56"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="A27:H29"/>
+    <x:mergeCell ref="A28:H30"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B4:B4">
-    <x:cfRule type="expression" dxfId="11" priority="1">
+    <x:cfRule type="expression" dxfId="13" priority="1">
       <x:formula>B4="PASS"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="12" priority="2">
+    <x:cfRule type="expression" dxfId="14" priority="2">
       <x:formula>B4="FAIL"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E4:E4">
-    <x:cfRule type="expression" dxfId="13" priority="3">
+    <x:cfRule type="expression" dxfId="15" priority="3">
       <x:formula>E4="ACTION REQUIRED"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="14" priority="4">
+    <x:cfRule type="expression" dxfId="16" priority="4">
       <x:formula>E4="WATCH"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="15" priority="5">
-      <x:formula>E4="HEALTHY"</x:formula>
+    <x:cfRule type="expression" dxfId="17" priority="5">
+      <x:formula>E4="OK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F8:F16">
-    <x:cfRule type="expression" dxfId="16" priority="6">
+    <x:cfRule type="expression" dxfId="18" priority="6">
       <x:formula>F8="PASS"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="17" priority="7">
+    <x:cfRule type="expression" dxfId="19" priority="7">
       <x:formula>F8="FAIL"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Re205b0f6e9714c7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R626c134bb200410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="Rbf718284d1eb44d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rd31ed432d30342c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R3eeb8bd2f859490e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="Rb45787a5c4bf4fa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R0aced715edfa470c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R6bce5e00559047c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="Ree0ec750fe2a4a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R4367c1a2476249bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="Rcc34dbc9481e43f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="Rcd66832414704385"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -20,10 +20,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={69516E80-B86B-5485-9815-F1D6B4F4A1A6}</x:author>
-    <x:author>tc={218FD7FC-83FB-9E7C-4BEE-9EA002F59077}</x:author>
-    <x:author>tc={8121AE60-30EE-0278-CF63-EC455EEFB906}</x:author>
-    <x:author>tc={E5346B2C-4D96-0537-D519-CF76582AE940}</x:author>
+    <x:author>tc={7258B81E-8D3B-6CE0-FD35-E742545C19CE}</x:author>
+    <x:author>tc={4B221FE6-B027-FA2F-C6F9-1EE0264D0247}</x:author>
+    <x:author>tc={93A359DE-A609-AD0C-0920-C48C5D95F28D}</x:author>
+    <x:author>tc={57C27267-3D72-7DA2-C807-8DC3D2110E18}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -1009,7 +1009,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4cb8a91667d04fd2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra179688aa6fa4295"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1039,7 +1039,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6e1022fa26714d0b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5cdac9e588944447"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1050,7 +1050,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}"/>
+  <xltc:person displayName="User" id="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}"/>
 </xltc:personList>
 </file>
 
@@ -1247,16 +1247,16 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-26T14:43:45.786" personId="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}" id="{69516E80-B86B-5485-9815-F1D6B4F4A1A6}">
+  <xltc:threadedComment ref="B18" dT="2026-08-26T14:58:01.498" personId="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}" id="{7258B81E-8D3B-6CE0-FD35-E742545C19CE}">
     <xltc:text>Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B42" dT="2026-08-26T14:43:45.786" personId="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}" id="{218FD7FC-83FB-9E7C-4BEE-9EA002F59077}">
+  <xltc:threadedComment ref="B42" dT="2026-08-26T14:58:01.498" personId="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}" id="{4B221FE6-B027-FA2F-C6F9-1EE0264D0247}">
     <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B34" dT="2026-08-26T14:43:45.786" personId="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}" id="{8121AE60-30EE-0278-CF63-EC455EEFB906}">
+  <xltc:threadedComment ref="B34" dT="2026-08-26T14:58:01.498" personId="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}" id="{93A359DE-A609-AD0C-0920-C48C5D95F28D}">
     <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B35" dT="2026-08-26T14:43:45.786" personId="{347AE2E5-ED2C-41D2-9AA6-47721B3B961B}" id="{E5346B2C-4D96-0537-D519-CF76582AE940}">
+  <xltc:threadedComment ref="B35" dT="2026-08-26T14:58:01.498" personId="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}" id="{57C27267-3D72-7DA2-C807-8DC3D2110E18}">
     <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -2373,7 +2373,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d7a0950c2c04bb1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd417ac4cdfee42a8"/>
 </x:worksheet>
 </file>
 
@@ -4889,7 +4889,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39f6cd30e8d746ad"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R993fc6886ca7468d"/>
 </x:worksheet>
 </file>
 
@@ -5901,7 +5901,7 @@
         <x:v>Formula-error count</x:v>
       </x:c>
       <x:c r="B16" s="50" t="n">
-        <x:f>SUMPRODUCT(--ISERROR('Assumptions'!$B$5:$D$17))+SUMPRODUCT(--ISERROR('13-Week Forecast'!$B$5:$O$51))+SUMPRODUCT(--ISERROR('Weekly Review'!$A$5:$N$18))+SUMPRODUCT(--ISERROR('Dashboard'!$A$6:$J$24))</x:f>
+        <x:f>SUMPRODUCT(--ISERROR('Assumptions'!$B$5:$D$17))+SUMPRODUCT(--ISERROR('13-Week Forecast'!$B$5:$O$51))+SUMPRODUCT(--ISERROR('Weekly Review'!$A$5:$N$18))+SUMPRODUCT(--ISERROR('Dashboard'!$A$6:$J$24))+SUMPRODUCT(--ISERROR('Dashboard'!$P$4:$R$34))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="50" t="n">

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R0aced715edfa470c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R6bce5e00559047c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="Ree0ec750fe2a4a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R4367c1a2476249bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="Rcc34dbc9481e43f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="Rcd66832414704385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R4d44442af84142eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R6fecb1a629ca4327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R91bf2385bb964313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rd2cfaf2133b94566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R906f3a99a7484e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="Ra98aead422a1451b"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -20,10 +20,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={7258B81E-8D3B-6CE0-FD35-E742545C19CE}</x:author>
-    <x:author>tc={4B221FE6-B027-FA2F-C6F9-1EE0264D0247}</x:author>
-    <x:author>tc={93A359DE-A609-AD0C-0920-C48C5D95F28D}</x:author>
-    <x:author>tc={57C27267-3D72-7DA2-C807-8DC3D2110E18}</x:author>
+    <x:author>tc={911808D7-7490-7273-81DF-52B18E6A0026}</x:author>
+    <x:author>tc={3CE89642-A655-41DD-1FA6-DE53C860A290}</x:author>
+    <x:author>tc={39CDC10E-89CD-355E-05E8-C2A4AA6F0BB9}</x:author>
+    <x:author>tc={1C0A15C3-71DD-065B-05EE-065A18D44E19}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -76,11 +76,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="dd mmm yyyy"/>
     <x:numFmt numFmtId="201" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0);-"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0;[Red](#,##0);-"/>
+    <x:numFmt numFmtId="203" formatCode="0"/>
+    <x:numFmt numFmtId="204" formatCode="#,##0;[Red](#,##0);-"/>
   </x:numFmts>
   <x:fonts count="14">
     <x:font>
@@ -228,7 +229,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="71">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -273,6 +274,7 @@
     <x:xf numFmtId="200" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -289,13 +291,14 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -333,7 +336,17 @@
     <x:xf numFmtId="200" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1009,7 +1022,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra179688aa6fa4295"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdb280384cd224945"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1039,7 +1052,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5cdac9e588944447"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R67d1bcb11ae843fc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1050,7 +1063,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}"/>
+  <xltc:person displayName="User" id="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}"/>
 </xltc:personList>
 </file>
 
@@ -1247,16 +1260,16 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-26T14:58:01.498" personId="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}" id="{7258B81E-8D3B-6CE0-FD35-E742545C19CE}">
+  <xltc:threadedComment ref="B18" dT="2026-08-26T16:49:11.841" personId="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}" id="{911808D7-7490-7273-81DF-52B18E6A0026}">
     <xltc:text>Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B42" dT="2026-08-26T14:58:01.498" personId="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}" id="{4B221FE6-B027-FA2F-C6F9-1EE0264D0247}">
+  <xltc:threadedComment ref="B42" dT="2026-08-26T16:49:11.842" personId="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}" id="{3CE89642-A655-41DD-1FA6-DE53C860A290}">
     <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B34" dT="2026-08-26T14:58:01.498" personId="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}" id="{93A359DE-A609-AD0C-0920-C48C5D95F28D}">
+  <xltc:threadedComment ref="B34" dT="2026-08-26T16:49:11.842" personId="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}" id="{39CDC10E-89CD-355E-05E8-C2A4AA6F0BB9}">
     <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B35" dT="2026-08-26T14:58:01.498" personId="{1F1C2A46-2A2C-47F8-83D6-8D7E7B6B5F2A}" id="{57C27267-3D72-7DA2-C807-8DC3D2110E18}">
+  <xltc:threadedComment ref="B35" dT="2026-08-26T16:49:11.842" personId="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}" id="{1C0A15C3-71DD-065B-05EE-065A18D44E19}">
     <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -1317,7 +1330,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>Release 1.0</x:v>
+        <x:v>Release 1.1</x:v>
       </x:c>
       <x:c r="D6" s="23" t="str">
         <x:v>Workbook sheets</x:v>
@@ -1418,7 +1431,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B16" s="15" t="str">
-        <x:v>Record actual receipts, payments, closing cash and owner commentary in Weekly Review.</x:v>
+        <x:v>Snapshot the original forecast as values, then record actuals and owner commentary in Weekly Review.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1536,6 +1549,7 @@
     <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1559,6 +1573,7 @@
       <x:c r="P1" s="4"/>
       <x:c r="Q1" s="4"/>
       <x:c r="R1" s="4"/>
+      <x:c r="S1" s="4"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
@@ -1581,6 +1596,7 @@
       <x:c r="P2" s="8"/>
       <x:c r="Q2" s="8"/>
       <x:c r="R2" s="8"/>
+      <x:c r="S2" s="8"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="25" t="str">
@@ -1615,97 +1631,97 @@
         <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
         <x:v>06 Sep</x:v>
       </x:c>
-      <x:c r="Q5" s="38" t="n">
+      <x:c r="Q5" s="39" t="n">
         <x:f>'13-Week Forecast'!B$48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="R5" s="38" t="n">
+      <x:c r="R5" s="39" t="n">
         <x:f>'13-Week Forecast'!B$49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
-      <x:c r="A6" s="58" t="str">
+      <x:c r="A6" s="60" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B6" s="58" t="str">
+      <x:c r="B6" s="60" t="str">
         <x:v>Week 13 closing cash</x:v>
       </x:c>
-      <x:c r="C6" s="58" t="str">
+      <x:c r="C6" s="60" t="str">
         <x:v>Lowest closing cash</x:v>
       </x:c>
-      <x:c r="D6" s="58" t="str">
+      <x:c r="D6" s="60" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="E6" s="58" t="str">
+      <x:c r="E6" s="60" t="str">
         <x:v>Minimum headroom</x:v>
       </x:c>
-      <x:c r="F6" s="58" t="str">
+      <x:c r="F6" s="60" t="str">
         <x:v>Weeks below buffer</x:v>
       </x:c>
-      <x:c r="G6" s="58" t="str">
+      <x:c r="G6" s="60" t="str">
         <x:v>13-week net cash change</x:v>
       </x:c>
-      <x:c r="H6" s="58" t="str">
+      <x:c r="H6" s="60" t="str">
         <x:v>Week of lowest cash</x:v>
       </x:c>
-      <x:c r="I6" s="58" t="str">
+      <x:c r="I6" s="60" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="J6" s="58" t="str">
+      <x:c r="J6" s="60" t="str">
         <x:v>LIQUIDITY STATUS</x:v>
       </x:c>
       <x:c r="P6" s="11" t="str">
         <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
         <x:v>13 Sep</x:v>
       </x:c>
-      <x:c r="Q6" s="38" t="n">
+      <x:c r="Q6" s="39" t="n">
         <x:f>'13-Week Forecast'!C$48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="R6" s="38" t="n">
+      <x:c r="R6" s="39" t="n">
         <x:f>'13-Week Forecast'!C$49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="61" t="str">
+      <x:c r="A7" s="63" t="str">
         <x:f>'Assumptions'!$B$12</x:f>
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="B7" s="62" t="n">
+      <x:c r="B7" s="64" t="n">
         <x:f>'13-Week Forecast'!$N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="C7" s="62" t="n">
+      <x:c r="C7" s="64" t="n">
         <x:f>MIN('13-Week Forecast'!$B$48:$N$48)</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D7" s="62" t="n">
+      <x:c r="D7" s="64" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="E7" s="62" t="n">
+      <x:c r="E7" s="64" t="n">
         <x:f>MIN('13-Week Forecast'!$B$50:$N$50)</x:f>
         <x:v>-69000</x:v>
       </x:c>
-      <x:c r="F7" s="61" t="n">
+      <x:c r="F7" s="63" t="n">
         <x:f>COUNTIF('13-Week Forecast'!$B$50:$N$50,"&lt;0")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G7" s="62" t="n">
+      <x:c r="G7" s="64" t="n">
         <x:f>SUM('13-Week Forecast'!$B$47:$N$47)</x:f>
         <x:v>-369000</x:v>
       </x:c>
-      <x:c r="H7" s="63" t="n">
+      <x:c r="H7" s="65" t="n">
         <x:f>INDEX('13-Week Forecast'!$B$6:$N$6,1,MATCH(C7,'13-Week Forecast'!$B$48:$N$48,0))</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="I7" s="61" t="str">
+      <x:c r="I7" s="63" t="str">
         <x:f>'Checks &amp; Sources'!$B$4</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="J7" s="61" t="str">
+      <x:c r="J7" s="63" t="str">
         <x:f>'Checks &amp; Sources'!$E$4</x:f>
         <x:v>ACTION REQUIRED</x:v>
       </x:c>
@@ -1713,11 +1729,11 @@
         <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
         <x:v>20 Sep</x:v>
       </x:c>
-      <x:c r="Q7" s="38" t="n">
+      <x:c r="Q7" s="39" t="n">
         <x:f>'13-Week Forecast'!D$48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="R7" s="38" t="n">
+      <x:c r="R7" s="39" t="n">
         <x:f>'13-Week Forecast'!D$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1727,39 +1743,67 @@
         <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
         <x:v>27 Sep</x:v>
       </x:c>
-      <x:c r="Q8" s="38" t="n">
+      <x:c r="Q8" s="39" t="n">
         <x:f>'13-Week Forecast'!E$48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="R8" s="38" t="n">
+      <x:c r="R8" s="39" t="n">
         <x:f>'13-Week Forecast'!E$49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
+      <x:c r="A9" s="59" t="str">
+        <x:v>First buffer breach</x:v>
+      </x:c>
+      <x:c r="B9" s="59" t="str">
+        <x:v>Weeks until breach</x:v>
+      </x:c>
+      <x:c r="C9" s="59" t="str">
+        <x:v>Funding required</x:v>
+      </x:c>
+      <x:c r="D9" s="59" t="str">
+        <x:v>Action deadline</x:v>
+      </x:c>
       <x:c r="P9" s="11" t="str">
         <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
         <x:v>04 Oct</x:v>
       </x:c>
-      <x:c r="Q9" s="38" t="n">
+      <x:c r="Q9" s="39" t="n">
         <x:f>'13-Week Forecast'!F$48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="R9" s="38" t="n">
+      <x:c r="R9" s="39" t="n">
         <x:f>'13-Week Forecast'!F$49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
+      <x:c r="A10" s="68" t="n">
+        <x:f>IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"BELOW BUFFER")=0,"None",INDEX('13-Week Forecast'!$B$6:$N$6,1,MATCH("BELOW BUFFER",'13-Week Forecast'!$B$51:$N$51,0)))</x:f>
+        <x:v>46341</x:v>
+      </x:c>
+      <x:c r="B10" s="67" t="n">
+        <x:f>IF(A10="None","13+",MAX(0,ROUNDUP((A10-'Assumptions'!$B$9)/7,0)))</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="69" t="n">
+        <x:f>MAX(0,-MIN('13-Week Forecast'!$B$50:$N$50))</x:f>
+        <x:v>69000</x:v>
+      </x:c>
+      <x:c r="D10" s="68" t="n">
+        <x:f>IF(A10="None","None",A10-7*'Assumptions'!$B$19)</x:f>
+        <x:v>46327</x:v>
+      </x:c>
       <x:c r="P10" s="11" t="str">
         <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
         <x:v>11 Oct</x:v>
       </x:c>
-      <x:c r="Q10" s="38" t="n">
+      <x:c r="Q10" s="39" t="n">
         <x:f>'13-Week Forecast'!G$48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="R10" s="38" t="n">
+      <x:c r="R10" s="39" t="n">
         <x:f>'13-Week Forecast'!G$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1784,11 +1828,11 @@
         <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
         <x:v>18 Oct</x:v>
       </x:c>
-      <x:c r="Q11" s="38" t="n">
+      <x:c r="Q11" s="39" t="n">
         <x:f>'13-Week Forecast'!H$48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="R11" s="38" t="n">
+      <x:c r="R11" s="39" t="n">
         <x:f>'13-Week Forecast'!H$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1798,15 +1842,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B12" s="46" t="n">
+      <x:c r="B12" s="70" t="n">
         <x:f>'13-Week Forecast'!B$6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C12" s="43" t="n">
+      <x:c r="C12" s="44" t="n">
         <x:f>'13-Week Forecast'!B$48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="D12" s="43" t="n">
+      <x:c r="D12" s="44" t="n">
         <x:f>'13-Week Forecast'!B$50</x:f>
         <x:v>258000</x:v>
       </x:c>
@@ -1818,11 +1862,11 @@
         <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
         <x:v>25 Oct</x:v>
       </x:c>
-      <x:c r="Q12" s="38" t="n">
+      <x:c r="Q12" s="39" t="n">
         <x:f>'13-Week Forecast'!I$48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="R12" s="38" t="n">
+      <x:c r="R12" s="39" t="n">
         <x:f>'13-Week Forecast'!I$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1832,15 +1876,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B13" s="46" t="n">
+      <x:c r="B13" s="70" t="n">
         <x:f>'13-Week Forecast'!C$6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="C13" s="43" t="n">
+      <x:c r="C13" s="44" t="n">
         <x:f>'13-Week Forecast'!C$48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="D13" s="43" t="n">
+      <x:c r="D13" s="44" t="n">
         <x:f>'13-Week Forecast'!C$50</x:f>
         <x:v>249000</x:v>
       </x:c>
@@ -1852,11 +1896,11 @@
         <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
         <x:v>01 Nov</x:v>
       </x:c>
-      <x:c r="Q13" s="38" t="n">
+      <x:c r="Q13" s="39" t="n">
         <x:f>'13-Week Forecast'!J$48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="R13" s="38" t="n">
+      <x:c r="R13" s="39" t="n">
         <x:f>'13-Week Forecast'!J$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1866,15 +1910,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B14" s="46" t="n">
+      <x:c r="B14" s="70" t="n">
         <x:f>'13-Week Forecast'!D$6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="C14" s="43" t="n">
+      <x:c r="C14" s="44" t="n">
         <x:f>'13-Week Forecast'!D$48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="D14" s="43" t="n">
+      <x:c r="D14" s="44" t="n">
         <x:f>'13-Week Forecast'!D$50</x:f>
         <x:v>225000</x:v>
       </x:c>
@@ -1886,11 +1930,11 @@
         <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
         <x:v>08 Nov</x:v>
       </x:c>
-      <x:c r="Q14" s="38" t="n">
+      <x:c r="Q14" s="39" t="n">
         <x:f>'13-Week Forecast'!K$48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="R14" s="38" t="n">
+      <x:c r="R14" s="39" t="n">
         <x:f>'13-Week Forecast'!K$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1900,15 +1944,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B15" s="46" t="n">
+      <x:c r="B15" s="70" t="n">
         <x:f>'13-Week Forecast'!E$6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="C15" s="43" t="n">
+      <x:c r="C15" s="44" t="n">
         <x:f>'13-Week Forecast'!E$48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="D15" s="43" t="n">
+      <x:c r="D15" s="44" t="n">
         <x:f>'13-Week Forecast'!E$50</x:f>
         <x:v>193000</x:v>
       </x:c>
@@ -1920,11 +1964,11 @@
         <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
         <x:v>15 Nov</x:v>
       </x:c>
-      <x:c r="Q15" s="38" t="n">
+      <x:c r="Q15" s="39" t="n">
         <x:f>'13-Week Forecast'!L$48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="R15" s="38" t="n">
+      <x:c r="R15" s="39" t="n">
         <x:f>'13-Week Forecast'!L$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1934,15 +1978,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B16" s="46" t="n">
+      <x:c r="B16" s="70" t="n">
         <x:f>'13-Week Forecast'!F$6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="C16" s="43" t="n">
+      <x:c r="C16" s="44" t="n">
         <x:f>'13-Week Forecast'!F$48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="D16" s="43" t="n">
+      <x:c r="D16" s="44" t="n">
         <x:f>'13-Week Forecast'!F$50</x:f>
         <x:v>101000</x:v>
       </x:c>
@@ -1954,11 +1998,11 @@
         <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
         <x:v>22 Nov</x:v>
       </x:c>
-      <x:c r="Q16" s="38" t="n">
+      <x:c r="Q16" s="39" t="n">
         <x:f>'13-Week Forecast'!M$48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="R16" s="38" t="n">
+      <x:c r="R16" s="39" t="n">
         <x:f>'13-Week Forecast'!M$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -1968,15 +2012,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B17" s="46" t="n">
+      <x:c r="B17" s="70" t="n">
         <x:f>'13-Week Forecast'!G$6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="C17" s="43" t="n">
+      <x:c r="C17" s="44" t="n">
         <x:f>'13-Week Forecast'!G$48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="D17" s="43" t="n">
+      <x:c r="D17" s="44" t="n">
         <x:f>'13-Week Forecast'!G$50</x:f>
         <x:v>33000</x:v>
       </x:c>
@@ -1988,11 +2032,11 @@
         <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
         <x:v>29 Nov</x:v>
       </x:c>
-      <x:c r="Q17" s="38" t="n">
+      <x:c r="Q17" s="39" t="n">
         <x:f>'13-Week Forecast'!N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="R17" s="38" t="n">
+      <x:c r="R17" s="39" t="n">
         <x:f>'13-Week Forecast'!N$49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -2002,15 +2046,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B18" s="46" t="n">
+      <x:c r="B18" s="70" t="n">
         <x:f>'13-Week Forecast'!H$6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="C18" s="43" t="n">
+      <x:c r="C18" s="44" t="n">
         <x:f>'13-Week Forecast'!H$48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="D18" s="43" t="n">
+      <x:c r="D18" s="44" t="n">
         <x:f>'13-Week Forecast'!H$50</x:f>
         <x:v>117000</x:v>
       </x:c>
@@ -2024,15 +2068,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B19" s="46" t="n">
+      <x:c r="B19" s="70" t="n">
         <x:f>'13-Week Forecast'!I$6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="C19" s="43" t="n">
+      <x:c r="C19" s="44" t="n">
         <x:f>'13-Week Forecast'!I$48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="D19" s="43" t="n">
+      <x:c r="D19" s="44" t="n">
         <x:f>'13-Week Forecast'!I$50</x:f>
         <x:v>60000</x:v>
       </x:c>
@@ -2046,15 +2090,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B20" s="46" t="n">
+      <x:c r="B20" s="70" t="n">
         <x:f>'13-Week Forecast'!J$6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="C20" s="43" t="n">
+      <x:c r="C20" s="44" t="n">
         <x:f>'13-Week Forecast'!J$48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="D20" s="43" t="n">
+      <x:c r="D20" s="44" t="n">
         <x:f>'13-Week Forecast'!J$50</x:f>
         <x:v>17000</x:v>
       </x:c>
@@ -2068,15 +2112,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B21" s="46" t="n">
+      <x:c r="B21" s="70" t="n">
         <x:f>'13-Week Forecast'!K$6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="C21" s="43" t="n">
+      <x:c r="C21" s="44" t="n">
         <x:f>'13-Week Forecast'!K$48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="D21" s="43" t="n">
+      <x:c r="D21" s="44" t="n">
         <x:f>'13-Week Forecast'!K$50</x:f>
         <x:v>37000</x:v>
       </x:c>
@@ -2099,15 +2143,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B22" s="46" t="n">
+      <x:c r="B22" s="70" t="n">
         <x:f>'13-Week Forecast'!L$6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="C22" s="43" t="n">
+      <x:c r="C22" s="44" t="n">
         <x:f>'13-Week Forecast'!L$48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="D22" s="43" t="n">
+      <x:c r="D22" s="44" t="n">
         <x:f>'13-Week Forecast'!L$50</x:f>
         <x:v>-1000</x:v>
       </x:c>
@@ -2119,11 +2163,11 @@
         <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
         <x:v>06 Sep</x:v>
       </x:c>
-      <x:c r="Q22" s="38" t="n">
+      <x:c r="Q22" s="39" t="n">
         <x:f>'13-Week Forecast'!B$19</x:f>
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="R22" s="38" t="n">
+      <x:c r="R22" s="39" t="n">
         <x:f>'13-Week Forecast'!B$43</x:f>
         <x:v>212000</x:v>
       </x:c>
@@ -2133,15 +2177,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B23" s="46" t="n">
+      <x:c r="B23" s="70" t="n">
         <x:f>'13-Week Forecast'!M$6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="C23" s="43" t="n">
+      <x:c r="C23" s="44" t="n">
         <x:f>'13-Week Forecast'!M$48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="D23" s="43" t="n">
+      <x:c r="D23" s="44" t="n">
         <x:f>'13-Week Forecast'!M$50</x:f>
         <x:v>-18000</x:v>
       </x:c>
@@ -2153,11 +2197,11 @@
         <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
         <x:v>13 Sep</x:v>
       </x:c>
-      <x:c r="Q23" s="38" t="n">
+      <x:c r="Q23" s="39" t="n">
         <x:f>'13-Week Forecast'!C$19</x:f>
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="R23" s="38" t="n">
+      <x:c r="R23" s="39" t="n">
         <x:f>'13-Week Forecast'!C$43</x:f>
         <x:v>178000</x:v>
       </x:c>
@@ -2167,15 +2211,15 @@
         <x:f>ROW()-11</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B24" s="46" t="n">
+      <x:c r="B24" s="70" t="n">
         <x:f>'13-Week Forecast'!N$6</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="C24" s="43" t="n">
+      <x:c r="C24" s="44" t="n">
         <x:f>'13-Week Forecast'!N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D24" s="43" t="n">
+      <x:c r="D24" s="44" t="n">
         <x:f>'13-Week Forecast'!N$50</x:f>
         <x:v>-69000</x:v>
       </x:c>
@@ -2187,11 +2231,11 @@
         <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
         <x:v>20 Sep</x:v>
       </x:c>
-      <x:c r="Q24" s="38" t="n">
+      <x:c r="Q24" s="39" t="n">
         <x:f>'13-Week Forecast'!D$19</x:f>
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="R24" s="38" t="n">
+      <x:c r="R24" s="39" t="n">
         <x:f>'13-Week Forecast'!D$43</x:f>
         <x:v>182000</x:v>
       </x:c>
@@ -2201,11 +2245,11 @@
         <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
         <x:v>27 Sep</x:v>
       </x:c>
-      <x:c r="Q25" s="38" t="n">
+      <x:c r="Q25" s="39" t="n">
         <x:f>'13-Week Forecast'!E$19</x:f>
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="R25" s="38" t="n">
+      <x:c r="R25" s="39" t="n">
         <x:f>'13-Week Forecast'!E$43</x:f>
         <x:v>179000</x:v>
       </x:c>
@@ -2215,67 +2259,142 @@
         <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
         <x:v>04 Oct</x:v>
       </x:c>
-      <x:c r="Q26" s="38" t="n">
+      <x:c r="Q26" s="39" t="n">
         <x:f>'13-Week Forecast'!F$19</x:f>
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="R26" s="38" t="n">
+      <x:c r="R26" s="39" t="n">
         <x:f>'13-Week Forecast'!F$43</x:f>
         <x:v>232000</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
+      <x:c r="A27" s="45" t="str">
+        <x:v>Scenario</x:v>
+      </x:c>
+      <x:c r="B27" s="45" t="str">
+        <x:v>Week 13 cash</x:v>
+      </x:c>
+      <x:c r="C27" s="45" t="str">
+        <x:v>Minimum cash</x:v>
+      </x:c>
+      <x:c r="D27" s="45" t="str">
+        <x:v>First buffer breach</x:v>
+      </x:c>
+      <x:c r="E27" s="45" t="str">
+        <x:v>Funding required</x:v>
+      </x:c>
       <x:c r="P27" s="11" t="str">
         <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
         <x:v>11 Oct</x:v>
       </x:c>
-      <x:c r="Q27" s="38" t="n">
+      <x:c r="Q27" s="39" t="n">
         <x:f>'13-Week Forecast'!G$19</x:f>
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="R27" s="38" t="n">
+      <x:c r="R27" s="39" t="n">
         <x:f>'13-Week Forecast'!G$43</x:f>
         <x:v>209000</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
+      <x:c r="A28" s="12" t="str">
+        <x:f>'Assumptions'!$B$15</x:f>
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="B28" s="39" t="n">
+        <x:f>Q49</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="C28" s="39" t="n">
+        <x:f>MIN(Q37:Q49)</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="n">
+        <x:f>IF(Q37&lt;'Assumptions'!$B$11,P37,IF(Q38&lt;'Assumptions'!$B$11,P38,IF(Q39&lt;'Assumptions'!$B$11,P39,IF(Q40&lt;'Assumptions'!$B$11,P40,IF(Q41&lt;'Assumptions'!$B$11,P41,IF(Q42&lt;'Assumptions'!$B$11,P42,IF(Q43&lt;'Assumptions'!$B$11,P43,IF(Q44&lt;'Assumptions'!$B$11,P44,IF(Q45&lt;'Assumptions'!$B$11,P45,IF(Q46&lt;'Assumptions'!$B$11,P46,IF(Q47&lt;'Assumptions'!$B$11,P47,IF(Q48&lt;'Assumptions'!$B$11,P48,IF(Q49&lt;'Assumptions'!$B$11,P49,"None")))))))))))))</x:f>
+        <x:v>46341</x:v>
+      </x:c>
+      <x:c r="E28" s="39" t="n">
+        <x:f>MAX(0,'Assumptions'!$B$11-MIN(Q37:Q49))</x:f>
+        <x:v>69000</x:v>
+      </x:c>
       <x:c r="P28" s="11" t="str">
         <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
         <x:v>18 Oct</x:v>
       </x:c>
-      <x:c r="Q28" s="38" t="n">
+      <x:c r="Q28" s="39" t="n">
         <x:f>'13-Week Forecast'!H$19</x:f>
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="R28" s="38" t="n">
+      <x:c r="R28" s="39" t="n">
         <x:f>'13-Week Forecast'!H$43</x:f>
         <x:v>197000</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
+      <x:c r="A29" s="12" t="str">
+        <x:f>'Assumptions'!$B$16</x:f>
+        <x:v>Upside</x:v>
+      </x:c>
+      <x:c r="B29" s="39" t="n">
+        <x:f>R49</x:f>
+        <x:v>199320</x:v>
+      </x:c>
+      <x:c r="C29" s="39" t="n">
+        <x:f>MIN(R37:R49)</x:f>
+        <x:v>199320</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:f>IF(R37&lt;'Assumptions'!$B$11,P37,IF(R38&lt;'Assumptions'!$B$11,P38,IF(R39&lt;'Assumptions'!$B$11,P39,IF(R40&lt;'Assumptions'!$B$11,P40,IF(R41&lt;'Assumptions'!$B$11,P41,IF(R42&lt;'Assumptions'!$B$11,P42,IF(R43&lt;'Assumptions'!$B$11,P43,IF(R44&lt;'Assumptions'!$B$11,P44,IF(R45&lt;'Assumptions'!$B$11,P45,IF(R46&lt;'Assumptions'!$B$11,P46,IF(R47&lt;'Assumptions'!$B$11,P47,IF(R48&lt;'Assumptions'!$B$11,P48,IF(R49&lt;'Assumptions'!$B$11,P49,"None")))))))))))))</x:f>
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="E29" s="39" t="n">
+        <x:f>MAX(0,'Assumptions'!$B$11-MIN(R37:R49))</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="P29" s="11" t="str">
         <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
         <x:v>25 Oct</x:v>
       </x:c>
-      <x:c r="Q29" s="38" t="n">
+      <x:c r="Q29" s="39" t="n">
         <x:f>'13-Week Forecast'!I$19</x:f>
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="R29" s="38" t="n">
+      <x:c r="R29" s="39" t="n">
         <x:f>'13-Week Forecast'!I$43</x:f>
         <x:v>192000</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
+      <x:c r="A30" s="12" t="str">
+        <x:f>'Assumptions'!$B$17</x:f>
+        <x:v>Downside</x:v>
+      </x:c>
+      <x:c r="B30" s="39" t="n">
+        <x:f>S49</x:f>
+        <x:v>-302550</x:v>
+      </x:c>
+      <x:c r="C30" s="39" t="n">
+        <x:f>MIN(S37:S49)</x:f>
+        <x:v>-302550</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="n">
+        <x:f>IF(S37&lt;'Assumptions'!$B$11,P37,IF(S38&lt;'Assumptions'!$B$11,P38,IF(S39&lt;'Assumptions'!$B$11,P39,IF(S40&lt;'Assumptions'!$B$11,P40,IF(S41&lt;'Assumptions'!$B$11,P41,IF(S42&lt;'Assumptions'!$B$11,P42,IF(S43&lt;'Assumptions'!$B$11,P43,IF(S44&lt;'Assumptions'!$B$11,P44,IF(S45&lt;'Assumptions'!$B$11,P45,IF(S46&lt;'Assumptions'!$B$11,P46,IF(S47&lt;'Assumptions'!$B$11,P47,IF(S48&lt;'Assumptions'!$B$11,P48,IF(S49&lt;'Assumptions'!$B$11,P49,"None")))))))))))))</x:f>
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="E30" s="39" t="n">
+        <x:f>MAX(0,'Assumptions'!$B$11-MIN(S37:S49))</x:f>
+        <x:v>402550</x:v>
+      </x:c>
       <x:c r="P30" s="11" t="str">
         <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
         <x:v>01 Nov</x:v>
       </x:c>
-      <x:c r="Q30" s="38" t="n">
+      <x:c r="Q30" s="39" t="n">
         <x:f>'13-Week Forecast'!J$19</x:f>
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="R30" s="38" t="n">
+      <x:c r="R30" s="39" t="n">
         <x:f>'13-Week Forecast'!J$43</x:f>
         <x:v>307000</x:v>
       </x:c>
@@ -2285,11 +2404,11 @@
         <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
         <x:v>08 Nov</x:v>
       </x:c>
-      <x:c r="Q31" s="38" t="n">
+      <x:c r="Q31" s="39" t="n">
         <x:f>'13-Week Forecast'!K$19</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="R31" s="38" t="n">
+      <x:c r="R31" s="39" t="n">
         <x:f>'13-Week Forecast'!K$43</x:f>
         <x:v>229000</x:v>
       </x:c>
@@ -2299,11 +2418,11 @@
         <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
         <x:v>15 Nov</x:v>
       </x:c>
-      <x:c r="Q32" s="38" t="n">
+      <x:c r="Q32" s="39" t="n">
         <x:f>'13-Week Forecast'!L$19</x:f>
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="R32" s="38" t="n">
+      <x:c r="R32" s="39" t="n">
         <x:f>'13-Week Forecast'!L$43</x:f>
         <x:v>192000</x:v>
       </x:c>
@@ -2313,11 +2432,11 @@
         <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
         <x:v>22 Nov</x:v>
       </x:c>
-      <x:c r="Q33" s="38" t="n">
+      <x:c r="Q33" s="39" t="n">
         <x:f>'13-Week Forecast'!M$19</x:f>
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="R33" s="38" t="n">
+      <x:c r="R33" s="39" t="n">
         <x:f>'13-Week Forecast'!M$43</x:f>
         <x:v>179000</x:v>
       </x:c>
@@ -2327,20 +2446,268 @@
         <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
         <x:v>29 Nov</x:v>
       </x:c>
-      <x:c r="Q34" s="38" t="n">
+      <x:c r="Q34" s="39" t="n">
         <x:f>'13-Week Forecast'!N$19</x:f>
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="R34" s="38" t="n">
+      <x:c r="R34" s="39" t="n">
         <x:f>'13-Week Forecast'!N$43</x:f>
         <x:v>219000</x:v>
       </x:c>
     </x:row>
+    <x:row r="36">
+      <x:c r="P36" s="14" t="str">
+        <x:v>Week ending</x:v>
+      </x:c>
+      <x:c r="Q36" s="14" t="str">
+        <x:v>Base closing cash</x:v>
+      </x:c>
+      <x:c r="R36" s="14" t="str">
+        <x:v>Upside closing cash</x:v>
+      </x:c>
+      <x:c r="S36" s="14" t="str">
+        <x:v>Downside closing cash</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="P37" s="11" t="n">
+        <x:f>'13-Week Forecast'!B$6</x:f>
+        <x:v>46271</x:v>
+      </x:c>
+      <x:c r="Q37" s="39" t="n">
+        <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!B10:B17)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B10:B12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!B22:B41)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B22,'13-Week Forecast'!B31,'13-Week Forecast'!B33,'13-Week Forecast'!B41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>358000</x:v>
+      </x:c>
+      <x:c r="R37" s="39" t="n">
+        <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!B10:B17)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B10:B12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!B22:B41)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B22,'13-Week Forecast'!B31,'13-Week Forecast'!B33,'13-Week Forecast'!B41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>358000</x:v>
+      </x:c>
+      <x:c r="S37" s="39" t="n">
+        <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!B10:B17)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B10:B12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!B22:B41)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B22,'13-Week Forecast'!B31,'13-Week Forecast'!B33,'13-Week Forecast'!B41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>358000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="P38" s="11" t="n">
+        <x:f>'13-Week Forecast'!C$6</x:f>
+        <x:v>46278</x:v>
+      </x:c>
+      <x:c r="Q38" s="39" t="n">
+        <x:f>Q37+SUM('13-Week Forecast'!C10:C17)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C10:C12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!C22:C41)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C22,'13-Week Forecast'!C31,'13-Week Forecast'!C33,'13-Week Forecast'!C41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>349000</x:v>
+      </x:c>
+      <x:c r="R38" s="39" t="n">
+        <x:f>R37+SUM('13-Week Forecast'!C10:C17)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C10:C12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!C22:C41)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C22,'13-Week Forecast'!C31,'13-Week Forecast'!C33,'13-Week Forecast'!C41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>364380</x:v>
+      </x:c>
+      <x:c r="S38" s="39" t="n">
+        <x:f>S37+SUM('13-Week Forecast'!C10:C17)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C10:C12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!C22:C41)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C22,'13-Week Forecast'!C31,'13-Week Forecast'!C33,'13-Week Forecast'!C41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>318800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="P39" s="11" t="n">
+        <x:f>'13-Week Forecast'!D$6</x:f>
+        <x:v>46285</x:v>
+      </x:c>
+      <x:c r="Q39" s="39" t="n">
+        <x:f>Q38+SUM('13-Week Forecast'!D10:D17)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D10:D12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!D22:D41)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D22,'13-Week Forecast'!D31,'13-Week Forecast'!D33,'13-Week Forecast'!D41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>325000</x:v>
+      </x:c>
+      <x:c r="R39" s="39" t="n">
+        <x:f>R38+SUM('13-Week Forecast'!D10:D17)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D10:D12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!D22:D41)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D22,'13-Week Forecast'!D31,'13-Week Forecast'!D33,'13-Week Forecast'!D41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>354920</x:v>
+      </x:c>
+      <x:c r="S39" s="39" t="n">
+        <x:f>S38+SUM('13-Week Forecast'!D10:D17)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D10:D12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!D22:D41)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D22,'13-Week Forecast'!D31,'13-Week Forecast'!D33,'13-Week Forecast'!D41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>266150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="P40" s="11" t="n">
+        <x:f>'13-Week Forecast'!E$6</x:f>
+        <x:v>46292</x:v>
+      </x:c>
+      <x:c r="Q40" s="39" t="n">
+        <x:f>Q39+SUM('13-Week Forecast'!E10:E17)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E10:E12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!E22:E41)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E22,'13-Week Forecast'!E31,'13-Week Forecast'!E33,'13-Week Forecast'!E41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>293000</x:v>
+      </x:c>
+      <x:c r="R40" s="39" t="n">
+        <x:f>R39+SUM('13-Week Forecast'!E10:E17)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E10:E12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!E22:E41)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E22,'13-Week Forecast'!E31,'13-Week Forecast'!E33,'13-Week Forecast'!E41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>336680</x:v>
+      </x:c>
+      <x:c r="S40" s="39" t="n">
+        <x:f>S39+SUM('13-Week Forecast'!E10:E17)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E10:E12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!E22:E41)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E22,'13-Week Forecast'!E31,'13-Week Forecast'!E33,'13-Week Forecast'!E41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>206900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="P41" s="11" t="n">
+        <x:f>'13-Week Forecast'!F$6</x:f>
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="Q41" s="39" t="n">
+        <x:f>Q40+SUM('13-Week Forecast'!F10:F17)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F10:F12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!F22:F41)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F22,'13-Week Forecast'!F31,'13-Week Forecast'!F33,'13-Week Forecast'!F41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>201000</x:v>
+      </x:c>
+      <x:c r="R41" s="39" t="n">
+        <x:f>R40+SUM('13-Week Forecast'!F10:F17)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F10:F12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!F22:F41)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F22,'13-Week Forecast'!F31,'13-Week Forecast'!F33,'13-Week Forecast'!F41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>257940</x:v>
+      </x:c>
+      <x:c r="S41" s="39" t="n">
+        <x:f>S40+SUM('13-Week Forecast'!F10:F17)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F10:F12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!F22:F41)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F22,'13-Week Forecast'!F31,'13-Week Forecast'!F33,'13-Week Forecast'!F41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>88550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="P42" s="11" t="n">
+        <x:f>'13-Week Forecast'!G$6</x:f>
+        <x:v>46306</x:v>
+      </x:c>
+      <x:c r="Q42" s="39" t="n">
+        <x:f>Q41+SUM('13-Week Forecast'!G10:G17)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G10:G12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!G22:G41)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G22,'13-Week Forecast'!G31,'13-Week Forecast'!G33,'13-Week Forecast'!G41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>133000</x:v>
+      </x:c>
+      <x:c r="R42" s="39" t="n">
+        <x:f>R41+SUM('13-Week Forecast'!G10:G17)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G10:G12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!G22:G41)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G22,'13-Week Forecast'!G31,'13-Week Forecast'!G33,'13-Week Forecast'!G41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>203320</x:v>
+      </x:c>
+      <x:c r="S42" s="39" t="n">
+        <x:f>S41+SUM('13-Week Forecast'!G10:G17)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G10:G12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!G22:G41)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G22,'13-Week Forecast'!G31,'13-Week Forecast'!G33,'13-Week Forecast'!G41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>-6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="P43" s="11" t="n">
+        <x:f>'13-Week Forecast'!H$6</x:f>
+        <x:v>46313</x:v>
+      </x:c>
+      <x:c r="Q43" s="39" t="n">
+        <x:f>Q42+SUM('13-Week Forecast'!H10:H17)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H10:H12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!H22:H41)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H22,'13-Week Forecast'!H31,'13-Week Forecast'!H33,'13-Week Forecast'!H41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>217000</x:v>
+      </x:c>
+      <x:c r="R43" s="39" t="n">
+        <x:f>R42+SUM('13-Week Forecast'!H10:H17)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H10:H12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!H22:H41)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H22,'13-Week Forecast'!H31,'13-Week Forecast'!H33,'13-Week Forecast'!H41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="S43" s="39" t="n">
+        <x:f>S42+SUM('13-Week Forecast'!H10:H17)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H10:H12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!H22:H41)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H22,'13-Week Forecast'!H31,'13-Week Forecast'!H33,'13-Week Forecast'!H41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>52600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="P44" s="11" t="n">
+        <x:f>'13-Week Forecast'!I$6</x:f>
+        <x:v>46320</x:v>
+      </x:c>
+      <x:c r="Q44" s="39" t="n">
+        <x:f>Q43+SUM('13-Week Forecast'!I10:I17)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I10:I12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!I22:I41)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I22,'13-Week Forecast'!I31,'13-Week Forecast'!I33,'13-Week Forecast'!I41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>160000</x:v>
+      </x:c>
+      <x:c r="R44" s="39" t="n">
+        <x:f>R43+SUM('13-Week Forecast'!I10:I17)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I10:I12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!I22:I41)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I22,'13-Week Forecast'!I31,'13-Week Forecast'!I33,'13-Week Forecast'!I41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>256060</x:v>
+      </x:c>
+      <x:c r="S44" s="39" t="n">
+        <x:f>S43+SUM('13-Week Forecast'!I10:I17)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I10:I12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!I22:I41)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I22,'13-Week Forecast'!I31,'13-Week Forecast'!I33,'13-Week Forecast'!I41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>-30500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="P45" s="11" t="n">
+        <x:f>'13-Week Forecast'!J$6</x:f>
+        <x:v>46327</x:v>
+      </x:c>
+      <x:c r="Q45" s="39" t="n">
+        <x:f>Q44+SUM('13-Week Forecast'!J10:J17)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J10:J12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!J22:J41)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J22,'13-Week Forecast'!J31,'13-Week Forecast'!J33,'13-Week Forecast'!J41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="R45" s="39" t="n">
+        <x:f>R44+SUM('13-Week Forecast'!J10:J17)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J10:J12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!J22:J41)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J22,'13-Week Forecast'!J31,'13-Week Forecast'!J33,'13-Week Forecast'!J41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>226480</x:v>
+      </x:c>
+      <x:c r="S45" s="39" t="n">
+        <x:f>S44+SUM('13-Week Forecast'!J10:J17)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J10:J12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!J22:J41)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J22,'13-Week Forecast'!J31,'13-Week Forecast'!J33,'13-Week Forecast'!J41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>-100300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="P46" s="11" t="n">
+        <x:f>'13-Week Forecast'!K$6</x:f>
+        <x:v>46334</x:v>
+      </x:c>
+      <x:c r="Q46" s="39" t="n">
+        <x:f>Q45+SUM('13-Week Forecast'!K10:K17)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K10:K12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!K22:K41)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K22,'13-Week Forecast'!K31,'13-Week Forecast'!K33,'13-Week Forecast'!K41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>137000</x:v>
+      </x:c>
+      <x:c r="R46" s="39" t="n">
+        <x:f>R45+SUM('13-Week Forecast'!K10:K17)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K10:K12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!K22:K41)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K22,'13-Week Forecast'!K31,'13-Week Forecast'!K33,'13-Week Forecast'!K41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>260600</x:v>
+      </x:c>
+      <x:c r="S46" s="39" t="n">
+        <x:f>S45+SUM('13-Week Forecast'!K10:K17)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K10:K12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!K22:K41)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K22,'13-Week Forecast'!K31,'13-Week Forecast'!K33,'13-Week Forecast'!K41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>-108350</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="P47" s="11" t="n">
+        <x:f>'13-Week Forecast'!L$6</x:f>
+        <x:v>46341</x:v>
+      </x:c>
+      <x:c r="Q47" s="39" t="n">
+        <x:f>Q46+SUM('13-Week Forecast'!L10:L17)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L10:L12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!L22:L41)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L22,'13-Week Forecast'!L31,'13-Week Forecast'!L33,'13-Week Forecast'!L41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>99000</x:v>
+      </x:c>
+      <x:c r="R47" s="39" t="n">
+        <x:f>R46+SUM('13-Week Forecast'!L10:L17)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L10:L12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!L22:L41)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L22,'13-Week Forecast'!L31,'13-Week Forecast'!L33,'13-Week Forecast'!L41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>237020</x:v>
+      </x:c>
+      <x:c r="S47" s="39" t="n">
+        <x:f>S46+SUM('13-Week Forecast'!L10:L17)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L10:L12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!L22:L41)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L22,'13-Week Forecast'!L31,'13-Week Forecast'!L33,'13-Week Forecast'!L41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>-174900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="P48" s="11" t="n">
+        <x:f>'13-Week Forecast'!M$6</x:f>
+        <x:v>46348</x:v>
+      </x:c>
+      <x:c r="Q48" s="39" t="n">
+        <x:f>Q47+SUM('13-Week Forecast'!M10:M17)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M10:M12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!M22:M41)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M22,'13-Week Forecast'!M31,'13-Week Forecast'!M33,'13-Week Forecast'!M41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>82000</x:v>
+      </x:c>
+      <x:c r="R48" s="39" t="n">
+        <x:f>R47+SUM('13-Week Forecast'!M10:M17)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M10:M12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!M22:M41)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M22,'13-Week Forecast'!M31,'13-Week Forecast'!M33,'13-Week Forecast'!M41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>234980</x:v>
+      </x:c>
+      <x:c r="S48" s="39" t="n">
+        <x:f>S47+SUM('13-Week Forecast'!M10:M17)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M10:M12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!M22:M41)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M22,'13-Week Forecast'!M31,'13-Week Forecast'!M33,'13-Week Forecast'!M41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>-221400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="P49" s="11" t="n">
+        <x:f>'13-Week Forecast'!N$6</x:f>
+        <x:v>46355</x:v>
+      </x:c>
+      <x:c r="Q49" s="39" t="n">
+        <x:f>Q48+SUM('13-Week Forecast'!N10:N17)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N10:N12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!N22:N41)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N22,'13-Week Forecast'!N31,'13-Week Forecast'!N33,'13-Week Forecast'!N41)*('Assumptions'!$D$15-1)))</x:f>
+        <x:v>31000</x:v>
+      </x:c>
+      <x:c r="R49" s="39" t="n">
+        <x:f>R48+SUM('13-Week Forecast'!N10:N17)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N10:N12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!N22:N41)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N22,'13-Week Forecast'!N31,'13-Week Forecast'!N33,'13-Week Forecast'!N41)*('Assumptions'!$D$16-1)))</x:f>
+        <x:v>199320</x:v>
+      </x:c>
+      <x:c r="S49" s="39" t="n">
+        <x:f>S48+SUM('13-Week Forecast'!N10:N17)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N10:N12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!N22:N41)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N22,'13-Week Forecast'!N31,'13-Week Forecast'!N33,'13-Week Forecast'!N41)*('Assumptions'!$D$17-1)))</x:f>
+        <x:v>-302550</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:R1"/>
-    <x:mergeCell ref="A2:R2"/>
-    <x:mergeCell ref="A4:R4"/>
+    <x:mergeCell ref="A1:S1"/>
+    <x:mergeCell ref="A2:S2"/>
+    <x:mergeCell ref="A4:O4"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="I7:I7">
     <x:cfRule type="expression" dxfId="20" priority="1">
@@ -2373,7 +2740,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd417ac4cdfee42a8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfed8bbef86874f97"/>
 </x:worksheet>
 </file>
 
@@ -2540,6 +2907,14 @@
         <x:v>Softer receipts and higher selected variable payments</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Liquidity action lead time (weeks)</x:v>
+      </x:c>
+      <x:c r="B19" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
         <x:v>Data-quality notes</x:v>
@@ -2583,9 +2958,13 @@
     <x:mergeCell ref="A20:F20"/>
     <x:mergeCell ref="A21:F23"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="B12">
       <x:formula1>CashFlowScenarioList</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B19">
+      <x:formula1>0</x:formula1>
+      <x:formula2>13</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2655,55 +3034,55 @@
       <x:c r="A5" t="str">
         <x:v>Week commencing</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:f>'Assumptions'!$B$8</x:f>
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="n">
+      <x:c r="C5" s="34" t="n">
         <x:f>B5+7</x:f>
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="D5" s="33" t="n">
+      <x:c r="D5" s="34" t="n">
         <x:f>C5+7</x:f>
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="34" t="n">
         <x:f>D5+7</x:f>
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="F5" s="33" t="n">
+      <x:c r="F5" s="34" t="n">
         <x:f>E5+7</x:f>
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="G5" s="33" t="n">
+      <x:c r="G5" s="34" t="n">
         <x:f>F5+7</x:f>
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="34" t="n">
         <x:f>G5+7</x:f>
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="I5" s="33" t="n">
+      <x:c r="I5" s="34" t="n">
         <x:f>H5+7</x:f>
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="J5" s="33" t="n">
+      <x:c r="J5" s="34" t="n">
         <x:f>I5+7</x:f>
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="34" t="n">
         <x:f>J5+7</x:f>
         <x:v>46328</x:v>
       </x:c>
-      <x:c r="L5" s="33" t="n">
+      <x:c r="L5" s="34" t="n">
         <x:f>K5+7</x:f>
         <x:v>46335</x:v>
       </x:c>
-      <x:c r="M5" s="33" t="n">
+      <x:c r="M5" s="34" t="n">
         <x:f>L5+7</x:f>
         <x:v>46342</x:v>
       </x:c>
-      <x:c r="N5" s="33" t="n">
+      <x:c r="N5" s="34" t="n">
         <x:f>M5+7</x:f>
         <x:v>46349</x:v>
       </x:c>
@@ -2715,55 +3094,55 @@
       <x:c r="A6" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
+      <x:c r="B6" s="34" t="n">
         <x:f>B5+6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C6" s="33" t="n">
+      <x:c r="C6" s="34" t="n">
         <x:f>C5+6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="D6" s="33" t="n">
+      <x:c r="D6" s="34" t="n">
         <x:f>D5+6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="E6" s="33" t="n">
+      <x:c r="E6" s="34" t="n">
         <x:f>E5+6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="F6" s="33" t="n">
+      <x:c r="F6" s="34" t="n">
         <x:f>F5+6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="G6" s="33" t="n">
+      <x:c r="G6" s="34" t="n">
         <x:f>G5+6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="H6" s="33" t="n">
+      <x:c r="H6" s="34" t="n">
         <x:f>H5+6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="I6" s="33" t="n">
+      <x:c r="I6" s="34" t="n">
         <x:f>I5+6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="J6" s="33" t="n">
+      <x:c r="J6" s="34" t="n">
         <x:f>J5+6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="K6" s="33" t="n">
+      <x:c r="K6" s="34" t="n">
         <x:f>K5+6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="L6" s="33" t="n">
+      <x:c r="L6" s="34" t="n">
         <x:f>L5+6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="M6" s="33" t="n">
+      <x:c r="M6" s="34" t="n">
         <x:f>M5+6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="N6" s="33" t="n">
+      <x:c r="N6" s="34" t="n">
         <x:f>N5+6</x:f>
         <x:v>46355</x:v>
       </x:c>
@@ -2775,55 +3154,55 @@
       <x:c r="A7" t="str">
         <x:v>Actual / Forecast</x:v>
       </x:c>
-      <x:c r="B7" s="34" t="str">
+      <x:c r="B7" s="35" t="str">
         <x:f>IF(B6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Actual</x:v>
       </x:c>
-      <x:c r="C7" s="34" t="str">
+      <x:c r="C7" s="35" t="str">
         <x:f>IF(C6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="D7" s="34" t="str">
+      <x:c r="D7" s="35" t="str">
         <x:f>IF(D6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="E7" s="34" t="str">
+      <x:c r="E7" s="35" t="str">
         <x:f>IF(E6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="F7" s="34" t="str">
+      <x:c r="F7" s="35" t="str">
         <x:f>IF(F6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="G7" s="34" t="str">
+      <x:c r="G7" s="35" t="str">
         <x:f>IF(G6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="H7" s="34" t="str">
+      <x:c r="H7" s="35" t="str">
         <x:f>IF(H6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="I7" s="34" t="str">
+      <x:c r="I7" s="35" t="str">
         <x:f>IF(I6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="J7" s="34" t="str">
+      <x:c r="J7" s="35" t="str">
         <x:f>IF(J6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="K7" s="34" t="str">
+      <x:c r="K7" s="35" t="str">
         <x:f>IF(K6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="L7" s="34" t="str">
+      <x:c r="L7" s="35" t="str">
         <x:f>IF(L6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="M7" s="34" t="str">
+      <x:c r="M7" s="35" t="str">
         <x:f>IF(M6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="N7" s="34" t="str">
+      <x:c r="N7" s="35" t="str">
         <x:f>IF(N6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
@@ -2852,46 +3231,46 @@
       <x:c r="A10" t="str">
         <x:v>Customer receipts</x:v>
       </x:c>
-      <x:c r="B10" s="37" t="n">
+      <x:c r="B10" s="38" t="n">
         <x:v>118000</x:v>
       </x:c>
-      <x:c r="C10" s="37" t="n">
+      <x:c r="C10" s="38" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="D10" s="37" t="n">
+      <x:c r="D10" s="38" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="E10" s="37" t="n">
+      <x:c r="E10" s="38" t="n">
         <x:v>115000</x:v>
       </x:c>
-      <x:c r="F10" s="37" t="n">
+      <x:c r="F10" s="38" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="G10" s="37" t="n">
+      <x:c r="G10" s="38" t="n">
         <x:v>112000</x:v>
       </x:c>
-      <x:c r="H10" s="37" t="n">
+      <x:c r="H10" s="38" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="I10" s="37" t="n">
+      <x:c r="I10" s="38" t="n">
         <x:v>108000</x:v>
       </x:c>
-      <x:c r="J10" s="37" t="n">
+      <x:c r="J10" s="38" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="K10" s="37" t="n">
+      <x:c r="K10" s="38" t="n">
         <x:v>116000</x:v>
       </x:c>
-      <x:c r="L10" s="37" t="n">
+      <x:c r="L10" s="38" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="M10" s="37" t="n">
+      <x:c r="M10" s="38" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="N10" s="37" t="n">
+      <x:c r="N10" s="38" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="O10" s="38" t="n">
+      <x:c r="O10" s="39" t="n">
         <x:f>SUM(B10:N10)</x:f>
         <x:v>1514000</x:v>
       </x:c>
@@ -2900,46 +3279,46 @@
       <x:c r="A11" t="str">
         <x:v>Overdue receipts</x:v>
       </x:c>
-      <x:c r="B11" s="37" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:v>30000</x:v>
       </x:c>
-      <x:c r="C11" s="37" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="D11" s="37" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="E11" s="37" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F11" s="37" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="G11" s="37" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="H11" s="37" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="I11" s="37" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="J11" s="37" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:v>7000</x:v>
       </x:c>
-      <x:c r="K11" s="37" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="L11" s="37" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="M11" s="37" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="N11" s="37" t="n">
+      <x:c r="N11" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O11" s="38" t="n">
+      <x:c r="O11" s="39" t="n">
         <x:f>SUM(B11:N11)</x:f>
         <x:v>152000</x:v>
       </x:c>
@@ -2948,46 +3327,46 @@
       <x:c r="A12" t="str">
         <x:v>Cash / EFTPOS sales</x:v>
       </x:c>
-      <x:c r="B12" s="37" t="n">
+      <x:c r="B12" s="38" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="C12" s="37" t="n">
+      <x:c r="C12" s="38" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="D12" s="37" t="n">
+      <x:c r="D12" s="38" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="E12" s="37" t="n">
+      <x:c r="E12" s="38" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="F12" s="37" t="n">
+      <x:c r="F12" s="38" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="G12" s="37" t="n">
+      <x:c r="G12" s="38" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="H12" s="37" t="n">
+      <x:c r="H12" s="38" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="I12" s="37" t="n">
+      <x:c r="I12" s="38" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="J12" s="37" t="n">
+      <x:c r="J12" s="38" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="K12" s="37" t="n">
+      <x:c r="K12" s="38" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="L12" s="37" t="n">
+      <x:c r="L12" s="38" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="M12" s="37" t="n">
+      <x:c r="M12" s="38" t="n">
         <x:v>21000</x:v>
       </x:c>
-      <x:c r="N12" s="37" t="n">
+      <x:c r="N12" s="38" t="n">
         <x:v>22000</x:v>
       </x:c>
-      <x:c r="O12" s="38" t="n">
+      <x:c r="O12" s="39" t="n">
         <x:f>SUM(B12:N12)</x:f>
         <x:v>245000</x:v>
       </x:c>
@@ -2996,46 +3375,46 @@
       <x:c r="A13" t="str">
         <x:v>GST refunds / credits</x:v>
       </x:c>
-      <x:c r="B13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O13" s="38" t="n">
+      <x:c r="B13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="39" t="n">
         <x:f>SUM(B13:N13)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3044,46 +3423,46 @@
       <x:c r="A14" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B14" s="37" t="n">
+      <x:c r="B14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="C14" s="37" t="n">
+      <x:c r="C14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="D14" s="37" t="n">
+      <x:c r="D14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="E14" s="37" t="n">
+      <x:c r="E14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="F14" s="37" t="n">
+      <x:c r="F14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G14" s="37" t="n">
+      <x:c r="G14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="H14" s="37" t="n">
+      <x:c r="H14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="I14" s="37" t="n">
+      <x:c r="I14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="J14" s="37" t="n">
+      <x:c r="J14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K14" s="37" t="n">
+      <x:c r="K14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="L14" s="37" t="n">
+      <x:c r="L14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="M14" s="37" t="n">
+      <x:c r="M14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="N14" s="37" t="n">
+      <x:c r="N14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O14" s="38" t="n">
+      <x:c r="O14" s="39" t="n">
         <x:f>SUM(B14:N14)</x:f>
         <x:v>52000</x:v>
       </x:c>
@@ -3092,46 +3471,46 @@
       <x:c r="A15" t="str">
         <x:v>Asset sale proceeds</x:v>
       </x:c>
-      <x:c r="B15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="37" t="n">
+      <x:c r="B15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="38" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="L15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O15" s="38" t="n">
+      <x:c r="L15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="39" t="n">
         <x:f>SUM(B15:N15)</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -3140,46 +3519,46 @@
       <x:c r="A16" t="str">
         <x:v>Equity / owner funding</x:v>
       </x:c>
-      <x:c r="B16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="37" t="n">
+      <x:c r="B16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="38" t="n">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O16" s="38" t="n">
+      <x:c r="I16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="39" t="n">
         <x:f>SUM(B16:N16)</x:f>
         <x:v>150000</x:v>
       </x:c>
@@ -3188,46 +3567,46 @@
       <x:c r="A17" t="str">
         <x:v>Loan proceeds</x:v>
       </x:c>
-      <x:c r="B17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="37" t="n">
+      <x:c r="B17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="38" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="K17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O17" s="38" t="n">
+      <x:c r="K17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="39" t="n">
         <x:f>SUM(B17:N17)</x:f>
         <x:v>125000</x:v>
       </x:c>
@@ -3236,203 +3615,203 @@
       <x:c r="A18" t="str">
         <x:v>Scenario receipt adjustment</x:v>
       </x:c>
-      <x:c r="B18" s="41" t="n">
+      <x:c r="B18" s="42" t="n">
         <x:f>IF(B$7="Actual",0,SUM(B10:B12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C18" s="41" t="n">
+      <x:c r="C18" s="42" t="n">
         <x:f>IF(C$7="Actual",0,SUM(C10:C12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D18" s="41" t="n">
+      <x:c r="D18" s="42" t="n">
         <x:f>IF(D$7="Actual",0,SUM(D10:D12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="41" t="n">
+      <x:c r="E18" s="42" t="n">
         <x:f>IF(E$7="Actual",0,SUM(E10:E12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="41" t="n">
+      <x:c r="F18" s="42" t="n">
         <x:f>IF(F$7="Actual",0,SUM(F10:F12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="41" t="n">
+      <x:c r="G18" s="42" t="n">
         <x:f>IF(G$7="Actual",0,SUM(G10:G12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="41" t="n">
+      <x:c r="H18" s="42" t="n">
         <x:f>IF(H$7="Actual",0,SUM(H10:H12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="41" t="n">
+      <x:c r="I18" s="42" t="n">
         <x:f>IF(I$7="Actual",0,SUM(I10:I12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="41" t="n">
+      <x:c r="J18" s="42" t="n">
         <x:f>IF(J$7="Actual",0,SUM(J10:J12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="41" t="n">
+      <x:c r="K18" s="42" t="n">
         <x:f>IF(K$7="Actual",0,SUM(K10:K12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="41" t="n">
+      <x:c r="L18" s="42" t="n">
         <x:f>IF(L$7="Actual",0,SUM(L10:L12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="41" t="n">
+      <x:c r="M18" s="42" t="n">
         <x:f>IF(M$7="Actual",0,SUM(M10:M12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N18" s="41" t="n">
+      <x:c r="N18" s="42" t="n">
         <x:f>IF(N$7="Actual",0,SUM(N10:N12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="38" t="n">
+      <x:c r="O18" s="39" t="n">
         <x:f>SUM(B18:N18)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="36" t="str">
+      <x:c r="A19" s="37" t="str">
         <x:v>Total cash receipts</x:v>
       </x:c>
-      <x:c r="B19" s="42" t="n">
+      <x:c r="B19" s="43" t="n">
         <x:f>SUM(B10:B18)</x:f>
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="C19" s="42" t="n">
+      <x:c r="C19" s="43" t="n">
         <x:f>SUM(C10:C18)</x:f>
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="D19" s="42" t="n">
+      <x:c r="D19" s="43" t="n">
         <x:f>SUM(D10:D18)</x:f>
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="E19" s="42" t="n">
+      <x:c r="E19" s="43" t="n">
         <x:f>SUM(E10:E18)</x:f>
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="F19" s="42" t="n">
+      <x:c r="F19" s="43" t="n">
         <x:f>SUM(F10:F18)</x:f>
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="G19" s="42" t="n">
+      <x:c r="G19" s="43" t="n">
         <x:f>SUM(G10:G18)</x:f>
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="H19" s="42" t="n">
+      <x:c r="H19" s="43" t="n">
         <x:f>SUM(H10:H18)</x:f>
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="I19" s="42" t="n">
+      <x:c r="I19" s="43" t="n">
         <x:f>SUM(I10:I18)</x:f>
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="J19" s="42" t="n">
+      <x:c r="J19" s="43" t="n">
         <x:f>SUM(J10:J18)</x:f>
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="K19" s="42" t="n">
+      <x:c r="K19" s="43" t="n">
         <x:f>SUM(K10:K18)</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="L19" s="42" t="n">
+      <x:c r="L19" s="43" t="n">
         <x:f>SUM(L10:L18)</x:f>
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="M19" s="42" t="n">
+      <x:c r="M19" s="43" t="n">
         <x:f>SUM(M10:M18)</x:f>
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="N19" s="42" t="n">
+      <x:c r="N19" s="43" t="n">
         <x:f>SUM(N10:N18)</x:f>
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="O19" s="39" t="n">
+      <x:c r="O19" s="40" t="n">
         <x:f>SUM(B19:N19)</x:f>
         <x:v>2338000</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="38"/>
-      <x:c r="C20" s="38"/>
-      <x:c r="D20" s="38"/>
-      <x:c r="E20" s="38"/>
-      <x:c r="F20" s="38"/>
-      <x:c r="G20" s="38"/>
-      <x:c r="H20" s="38"/>
-      <x:c r="I20" s="38"/>
-      <x:c r="J20" s="38"/>
-      <x:c r="K20" s="38"/>
-      <x:c r="L20" s="38"/>
-      <x:c r="M20" s="38"/>
-      <x:c r="N20" s="38"/>
-      <x:c r="O20" s="38"/>
+      <x:c r="B20" s="39"/>
+      <x:c r="C20" s="39"/>
+      <x:c r="D20" s="39"/>
+      <x:c r="E20" s="39"/>
+      <x:c r="F20" s="39"/>
+      <x:c r="G20" s="39"/>
+      <x:c r="H20" s="39"/>
+      <x:c r="I20" s="39"/>
+      <x:c r="J20" s="39"/>
+      <x:c r="K20" s="39"/>
+      <x:c r="L20" s="39"/>
+      <x:c r="M20" s="39"/>
+      <x:c r="N20" s="39"/>
+      <x:c r="O20" s="39"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
         <x:v>CASH PAYMENTS</x:v>
       </x:c>
-      <x:c r="B21" s="40"/>
-      <x:c r="C21" s="40"/>
-      <x:c r="D21" s="40"/>
-      <x:c r="E21" s="40"/>
-      <x:c r="F21" s="40"/>
-      <x:c r="G21" s="40"/>
-      <x:c r="H21" s="40"/>
-      <x:c r="I21" s="40"/>
-      <x:c r="J21" s="40"/>
-      <x:c r="K21" s="40"/>
-      <x:c r="L21" s="40"/>
-      <x:c r="M21" s="40"/>
-      <x:c r="N21" s="40"/>
-      <x:c r="O21" s="40"/>
+      <x:c r="B21" s="41"/>
+      <x:c r="C21" s="41"/>
+      <x:c r="D21" s="41"/>
+      <x:c r="E21" s="41"/>
+      <x:c r="F21" s="41"/>
+      <x:c r="G21" s="41"/>
+      <x:c r="H21" s="41"/>
+      <x:c r="I21" s="41"/>
+      <x:c r="J21" s="41"/>
+      <x:c r="K21" s="41"/>
+      <x:c r="L21" s="41"/>
+      <x:c r="M21" s="41"/>
+      <x:c r="N21" s="41"/>
+      <x:c r="O21" s="41"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
         <x:v>Suppliers and inventory</x:v>
       </x:c>
-      <x:c r="B22" s="37" t="n">
+      <x:c r="B22" s="38" t="n">
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="C22" s="37" t="n">
+      <x:c r="C22" s="38" t="n">
         <x:v>88000</x:v>
       </x:c>
-      <x:c r="D22" s="37" t="n">
+      <x:c r="D22" s="38" t="n">
         <x:v>90000</x:v>
       </x:c>
-      <x:c r="E22" s="37" t="n">
+      <x:c r="E22" s="38" t="n">
         <x:v>95000</x:v>
       </x:c>
-      <x:c r="F22" s="37" t="n">
+      <x:c r="F22" s="38" t="n">
         <x:v>98000</x:v>
       </x:c>
-      <x:c r="G22" s="37" t="n">
+      <x:c r="G22" s="38" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="H22" s="37" t="n">
+      <x:c r="H22" s="38" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="I22" s="37" t="n">
+      <x:c r="I22" s="38" t="n">
         <x:v>108000</x:v>
       </x:c>
-      <x:c r="J22" s="37" t="n">
+      <x:c r="J22" s="38" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="K22" s="37" t="n">
+      <x:c r="K22" s="38" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="L22" s="37" t="n">
+      <x:c r="L22" s="38" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="M22" s="37" t="n">
+      <x:c r="M22" s="38" t="n">
         <x:v>95000</x:v>
       </x:c>
-      <x:c r="N22" s="37" t="n">
+      <x:c r="N22" s="38" t="n">
         <x:v>90000</x:v>
       </x:c>
-      <x:c r="O22" s="38" t="n">
+      <x:c r="O22" s="39" t="n">
         <x:f>SUM(B22:N22)</x:f>
         <x:v>1266000</x:v>
       </x:c>
@@ -3441,46 +3820,46 @@
       <x:c r="A23" t="str">
         <x:v>Net wages</x:v>
       </x:c>
-      <x:c r="B23" s="37" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="C23" s="37" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="D23" s="37" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="E23" s="37" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="F23" s="37" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="G23" s="37" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="H23" s="37" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="I23" s="37" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="J23" s="37" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="K23" s="37" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="L23" s="37" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="M23" s="37" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="N23" s="37" t="n">
+      <x:c r="N23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="O23" s="38" t="n">
+      <x:c r="O23" s="39" t="n">
         <x:f>SUM(B23:N23)</x:f>
         <x:v>546000</x:v>
       </x:c>
@@ -3489,46 +3868,46 @@
       <x:c r="A24" t="str">
         <x:v>PAYG withholding</x:v>
       </x:c>
-      <x:c r="B24" s="37" t="n">
+      <x:c r="B24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="C24" s="37" t="n">
+      <x:c r="C24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="D24" s="37" t="n">
+      <x:c r="D24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="E24" s="37" t="n">
+      <x:c r="E24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="F24" s="37" t="n">
+      <x:c r="F24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="G24" s="37" t="n">
+      <x:c r="G24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="H24" s="37" t="n">
+      <x:c r="H24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="I24" s="37" t="n">
+      <x:c r="I24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="J24" s="37" t="n">
+      <x:c r="J24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="K24" s="37" t="n">
+      <x:c r="K24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="L24" s="37" t="n">
+      <x:c r="L24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="M24" s="37" t="n">
+      <x:c r="M24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="N24" s="37" t="n">
+      <x:c r="N24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O24" s="38" t="n">
+      <x:c r="O24" s="39" t="n">
         <x:f>SUM(B24:N24)</x:f>
         <x:v>156000</x:v>
       </x:c>
@@ -3537,46 +3916,46 @@
       <x:c r="A25" t="str">
         <x:v>Superannuation</x:v>
       </x:c>
-      <x:c r="B25" s="37" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="C25" s="37" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D25" s="37" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="E25" s="37" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="F25" s="37" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="G25" s="37" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="H25" s="37" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="I25" s="37" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="J25" s="37" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="K25" s="37" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="L25" s="37" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="M25" s="37" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="N25" s="37" t="n">
+      <x:c r="N25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O25" s="38" t="n">
+      <x:c r="O25" s="39" t="n">
         <x:f>SUM(B25:N25)</x:f>
         <x:v>78000</x:v>
       </x:c>
@@ -3585,46 +3964,46 @@
       <x:c r="A26" t="str">
         <x:v>Payroll tax / workers compensation</x:v>
       </x:c>
-      <x:c r="B26" s="37" t="n">
+      <x:c r="B26" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="C26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F26" s="37" t="n">
+      <x:c r="C26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="G26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="37" t="n">
+      <x:c r="G26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="K26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N26" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O26" s="38" t="n">
+      <x:c r="K26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" s="39" t="n">
         <x:f>SUM(B26:N26)</x:f>
         <x:v>15000</x:v>
       </x:c>
@@ -3633,46 +4012,46 @@
       <x:c r="A27" t="str">
         <x:v>Rent</x:v>
       </x:c>
-      <x:c r="B27" s="37" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="C27" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E27" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F27" s="37" t="n">
+      <x:c r="C27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" s="38" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="G27" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I27" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="37" t="n">
+      <x:c r="G27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="38" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="K27" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L27" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M27" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N27" s="37" t="n">
+      <x:c r="K27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="38" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="O27" s="38" t="n">
+      <x:c r="O27" s="39" t="n">
         <x:f>SUM(B27:N27)</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -3681,46 +4060,46 @@
       <x:c r="A28" t="str">
         <x:v>Utilities</x:v>
       </x:c>
-      <x:c r="B28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F28" s="37" t="n">
+      <x:c r="B28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J28" s="37" t="n">
+      <x:c r="G28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M28" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N28" s="37" t="n">
+      <x:c r="K28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O28" s="38" t="n">
+      <x:c r="O28" s="39" t="n">
         <x:f>SUM(B28:N28)</x:f>
         <x:v>12000</x:v>
       </x:c>
@@ -3729,46 +4108,46 @@
       <x:c r="A29" t="str">
         <x:v>Insurance</x:v>
       </x:c>
-      <x:c r="B29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="37" t="n">
+      <x:c r="B29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N29" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O29" s="38" t="n">
+      <x:c r="D29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" s="39" t="n">
         <x:f>SUM(B29:N29)</x:f>
         <x:v>6000</x:v>
       </x:c>
@@ -3777,46 +4156,46 @@
       <x:c r="A30" t="str">
         <x:v>Software and subscriptions</x:v>
       </x:c>
-      <x:c r="B30" s="37" t="n">
+      <x:c r="B30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="C30" s="37" t="n">
+      <x:c r="C30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="D30" s="37" t="n">
+      <x:c r="D30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="E30" s="37" t="n">
+      <x:c r="E30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="F30" s="37" t="n">
+      <x:c r="F30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="G30" s="37" t="n">
+      <x:c r="G30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="H30" s="37" t="n">
+      <x:c r="H30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="I30" s="37" t="n">
+      <x:c r="I30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="J30" s="37" t="n">
+      <x:c r="J30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="K30" s="37" t="n">
+      <x:c r="K30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="L30" s="37" t="n">
+      <x:c r="L30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="M30" s="37" t="n">
+      <x:c r="M30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="N30" s="37" t="n">
+      <x:c r="N30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="O30" s="38" t="n">
+      <x:c r="O30" s="39" t="n">
         <x:f>SUM(B30:N30)</x:f>
         <x:v>39000</x:v>
       </x:c>
@@ -3825,46 +4204,46 @@
       <x:c r="A31" t="str">
         <x:v>Marketing</x:v>
       </x:c>
-      <x:c r="B31" s="37" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="C31" s="37" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D31" s="37" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="E31" s="37" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="F31" s="37" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="G31" s="37" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="H31" s="37" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="I31" s="37" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="J31" s="37" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="K31" s="37" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="L31" s="37" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="M31" s="37" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="N31" s="37" t="n">
+      <x:c r="N31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O31" s="38" t="n">
+      <x:c r="O31" s="39" t="n">
         <x:f>SUM(B31:N31)</x:f>
         <x:v>78000</x:v>
       </x:c>
@@ -3873,46 +4252,46 @@
       <x:c r="A32" t="str">
         <x:v>Professional services</x:v>
       </x:c>
-      <x:c r="B32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="37" t="n">
+      <x:c r="B32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="38" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="E32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="37" t="n">
+      <x:c r="E32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="38" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="I32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L32" s="37" t="n">
+      <x:c r="I32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="38" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="M32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N32" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O32" s="38" t="n">
+      <x:c r="M32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O32" s="39" t="n">
         <x:f>SUM(B32:N32)</x:f>
         <x:v>24000</x:v>
       </x:c>
@@ -3921,46 +4300,46 @@
       <x:c r="A33" t="str">
         <x:v>Freight, vehicles and travel</x:v>
       </x:c>
-      <x:c r="B33" s="37" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="C33" s="37" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="D33" s="37" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="E33" s="37" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F33" s="37" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="G33" s="37" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H33" s="37" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="I33" s="37" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="J33" s="37" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="K33" s="37" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="L33" s="37" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="M33" s="37" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="N33" s="37" t="n">
+      <x:c r="N33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="O33" s="38" t="n">
+      <x:c r="O33" s="39" t="n">
         <x:f>SUM(B33:N33)</x:f>
         <x:v>130000</x:v>
       </x:c>
@@ -3969,46 +4348,46 @@
       <x:c r="A34" t="str">
         <x:v>GST / BAS payments</x:v>
       </x:c>
-      <x:c r="B34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J34" s="37" t="n">
+      <x:c r="B34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="38" t="n">
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="K34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N34" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O34" s="38" t="n">
+      <x:c r="K34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N34" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34" s="39" t="n">
         <x:f>SUM(B34:N34)</x:f>
         <x:v>45000</x:v>
       </x:c>
@@ -4017,46 +4396,46 @@
       <x:c r="A35" t="str">
         <x:v>PAYG income tax instalments</x:v>
       </x:c>
-      <x:c r="B35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J35" s="37" t="n">
+      <x:c r="B35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="38" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="K35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N35" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O35" s="38" t="n">
+      <x:c r="K35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N35" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O35" s="39" t="n">
         <x:f>SUM(B35:N35)</x:f>
         <x:v>18000</x:v>
       </x:c>
@@ -4065,46 +4444,46 @@
       <x:c r="A36" t="str">
         <x:v>FBT / other tax</x:v>
       </x:c>
-      <x:c r="B36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N36" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O36" s="38" t="n">
+      <x:c r="B36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N36" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" s="39" t="n">
         <x:f>SUM(B36:N36)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4113,46 +4492,46 @@
       <x:c r="A37" t="str">
         <x:v>Interest and bank fees</x:v>
       </x:c>
-      <x:c r="B37" s="37" t="n">
+      <x:c r="B37" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="C37" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F37" s="37" t="n">
+      <x:c r="C37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G37" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I37" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J37" s="37" t="n">
+      <x:c r="G37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K37" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L37" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M37" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N37" s="37" t="n">
+      <x:c r="K37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N37" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O37" s="38" t="n">
+      <x:c r="O37" s="39" t="n">
         <x:f>SUM(B37:N37)</x:f>
         <x:v>16000</x:v>
       </x:c>
@@ -4161,46 +4540,46 @@
       <x:c r="A38" t="str">
         <x:v>Loan principal</x:v>
       </x:c>
-      <x:c r="B38" s="37" t="n">
+      <x:c r="B38" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="C38" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E38" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F38" s="37" t="n">
+      <x:c r="C38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F38" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="G38" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I38" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J38" s="37" t="n">
+      <x:c r="G38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="K38" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L38" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M38" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N38" s="37" t="n">
+      <x:c r="K38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N38" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O38" s="38" t="n">
+      <x:c r="O38" s="39" t="n">
         <x:f>SUM(B38:N38)</x:f>
         <x:v>48000</x:v>
       </x:c>
@@ -4209,46 +4588,46 @@
       <x:c r="A39" t="str">
         <x:v>Capital expenditure</x:v>
       </x:c>
-      <x:c r="B39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G39" s="37" t="n">
+      <x:c r="B39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G39" s="38" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="H39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K39" s="37" t="n">
+      <x:c r="H39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39" s="38" t="n">
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="L39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N39" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O39" s="38" t="n">
+      <x:c r="L39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" s="39" t="n">
         <x:f>SUM(B39:N39)</x:f>
         <x:v>65000</x:v>
       </x:c>
@@ -4257,46 +4636,46 @@
       <x:c r="A40" t="str">
         <x:v>Dividends / distributions</x:v>
       </x:c>
-      <x:c r="B40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N40" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O40" s="38" t="n">
+      <x:c r="B40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" s="39" t="n">
         <x:f>SUM(B40:N40)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4305,46 +4684,46 @@
       <x:c r="A41" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B41" s="37" t="n">
+      <x:c r="B41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="C41" s="37" t="n">
+      <x:c r="C41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D41" s="37" t="n">
+      <x:c r="D41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="E41" s="37" t="n">
+      <x:c r="E41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="F41" s="37" t="n">
+      <x:c r="F41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="G41" s="37" t="n">
+      <x:c r="G41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="H41" s="37" t="n">
+      <x:c r="H41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="I41" s="37" t="n">
+      <x:c r="I41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="J41" s="37" t="n">
+      <x:c r="J41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="K41" s="37" t="n">
+      <x:c r="K41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="L41" s="37" t="n">
+      <x:c r="L41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="M41" s="37" t="n">
+      <x:c r="M41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="N41" s="37" t="n">
+      <x:c r="N41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="O41" s="38" t="n">
+      <x:c r="O41" s="39" t="n">
         <x:f>SUM(B41:N41)</x:f>
         <x:v>65000</x:v>
       </x:c>
@@ -4353,216 +4732,216 @@
       <x:c r="A42" t="str">
         <x:v>Scenario payment adjustment</x:v>
       </x:c>
-      <x:c r="B42" s="41" t="n">
+      <x:c r="B42" s="42" t="n">
         <x:f>IF(B$7="Actual",0,SUM(B22,B31,B33,B41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C42" s="41" t="n">
+      <x:c r="C42" s="42" t="n">
         <x:f>IF(C$7="Actual",0,SUM(C22,C31,C33,C41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D42" s="41" t="n">
+      <x:c r="D42" s="42" t="n">
         <x:f>IF(D$7="Actual",0,SUM(D22,D31,D33,D41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E42" s="41" t="n">
+      <x:c r="E42" s="42" t="n">
         <x:f>IF(E$7="Actual",0,SUM(E22,E31,E33,E41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F42" s="41" t="n">
+      <x:c r="F42" s="42" t="n">
         <x:f>IF(F$7="Actual",0,SUM(F22,F31,F33,F41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G42" s="41" t="n">
+      <x:c r="G42" s="42" t="n">
         <x:f>IF(G$7="Actual",0,SUM(G22,G31,G33,G41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H42" s="41" t="n">
+      <x:c r="H42" s="42" t="n">
         <x:f>IF(H$7="Actual",0,SUM(H22,H31,H33,H41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I42" s="41" t="n">
+      <x:c r="I42" s="42" t="n">
         <x:f>IF(I$7="Actual",0,SUM(I22,I31,I33,I41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J42" s="41" t="n">
+      <x:c r="J42" s="42" t="n">
         <x:f>IF(J$7="Actual",0,SUM(J22,J31,J33,J41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K42" s="41" t="n">
+      <x:c r="K42" s="42" t="n">
         <x:f>IF(K$7="Actual",0,SUM(K22,K31,K33,K41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L42" s="41" t="n">
+      <x:c r="L42" s="42" t="n">
         <x:f>IF(L$7="Actual",0,SUM(L22,L31,L33,L41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M42" s="41" t="n">
+      <x:c r="M42" s="42" t="n">
         <x:f>IF(M$7="Actual",0,SUM(M22,M31,M33,M41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N42" s="41" t="n">
+      <x:c r="N42" s="42" t="n">
         <x:f>IF(N$7="Actual",0,SUM(N22,N31,N33,N41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O42" s="38" t="n">
+      <x:c r="O42" s="39" t="n">
         <x:f>SUM(B42:N42)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="36" t="str">
+      <x:c r="A43" s="37" t="str">
         <x:v>Total cash payments</x:v>
       </x:c>
-      <x:c r="B43" s="42" t="n">
+      <x:c r="B43" s="43" t="n">
         <x:f>SUM(B22:B42)</x:f>
         <x:v>212000</x:v>
       </x:c>
-      <x:c r="C43" s="42" t="n">
+      <x:c r="C43" s="43" t="n">
         <x:f>SUM(C22:C42)</x:f>
         <x:v>178000</x:v>
       </x:c>
-      <x:c r="D43" s="42" t="n">
+      <x:c r="D43" s="43" t="n">
         <x:f>SUM(D22:D42)</x:f>
         <x:v>182000</x:v>
       </x:c>
-      <x:c r="E43" s="42" t="n">
+      <x:c r="E43" s="43" t="n">
         <x:f>SUM(E22:E42)</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="F43" s="42" t="n">
+      <x:c r="F43" s="43" t="n">
         <x:f>SUM(F22:F42)</x:f>
         <x:v>232000</x:v>
       </x:c>
-      <x:c r="G43" s="42" t="n">
+      <x:c r="G43" s="43" t="n">
         <x:f>SUM(G22:G42)</x:f>
         <x:v>209000</x:v>
       </x:c>
-      <x:c r="H43" s="42" t="n">
+      <x:c r="H43" s="43" t="n">
         <x:f>SUM(H22:H42)</x:f>
         <x:v>197000</x:v>
       </x:c>
-      <x:c r="I43" s="42" t="n">
+      <x:c r="I43" s="43" t="n">
         <x:f>SUM(I22:I42)</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="J43" s="42" t="n">
+      <x:c r="J43" s="43" t="n">
         <x:f>SUM(J22:J42)</x:f>
         <x:v>307000</x:v>
       </x:c>
-      <x:c r="K43" s="42" t="n">
+      <x:c r="K43" s="43" t="n">
         <x:f>SUM(K22:K42)</x:f>
         <x:v>229000</x:v>
       </x:c>
-      <x:c r="L43" s="42" t="n">
+      <x:c r="L43" s="43" t="n">
         <x:f>SUM(L22:L42)</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="M43" s="42" t="n">
+      <x:c r="M43" s="43" t="n">
         <x:f>SUM(M22:M42)</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="N43" s="42" t="n">
+      <x:c r="N43" s="43" t="n">
         <x:f>SUM(N22:N42)</x:f>
         <x:v>219000</x:v>
       </x:c>
-      <x:c r="O43" s="39" t="n">
+      <x:c r="O43" s="40" t="n">
         <x:f>SUM(B43:N43)</x:f>
         <x:v>2707000</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="B44" s="38"/>
-      <x:c r="C44" s="38"/>
-      <x:c r="D44" s="38"/>
-      <x:c r="E44" s="38"/>
-      <x:c r="F44" s="38"/>
-      <x:c r="G44" s="38"/>
-      <x:c r="H44" s="38"/>
-      <x:c r="I44" s="38"/>
-      <x:c r="J44" s="38"/>
-      <x:c r="K44" s="38"/>
-      <x:c r="L44" s="38"/>
-      <x:c r="M44" s="38"/>
-      <x:c r="N44" s="38"/>
-      <x:c r="O44" s="38"/>
+      <x:c r="B44" s="39"/>
+      <x:c r="C44" s="39"/>
+      <x:c r="D44" s="39"/>
+      <x:c r="E44" s="39"/>
+      <x:c r="F44" s="39"/>
+      <x:c r="G44" s="39"/>
+      <x:c r="H44" s="39"/>
+      <x:c r="I44" s="39"/>
+      <x:c r="J44" s="39"/>
+      <x:c r="K44" s="39"/>
+      <x:c r="L44" s="39"/>
+      <x:c r="M44" s="39"/>
+      <x:c r="N44" s="39"/>
+      <x:c r="O44" s="39"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="14" t="str">
         <x:v>CASH POSITION</x:v>
       </x:c>
-      <x:c r="B45" s="40"/>
-      <x:c r="C45" s="40"/>
-      <x:c r="D45" s="40"/>
-      <x:c r="E45" s="40"/>
-      <x:c r="F45" s="40"/>
-      <x:c r="G45" s="40"/>
-      <x:c r="H45" s="40"/>
-      <x:c r="I45" s="40"/>
-      <x:c r="J45" s="40"/>
-      <x:c r="K45" s="40"/>
-      <x:c r="L45" s="40"/>
-      <x:c r="M45" s="40"/>
-      <x:c r="N45" s="40"/>
-      <x:c r="O45" s="40"/>
+      <x:c r="B45" s="41"/>
+      <x:c r="C45" s="41"/>
+      <x:c r="D45" s="41"/>
+      <x:c r="E45" s="41"/>
+      <x:c r="F45" s="41"/>
+      <x:c r="G45" s="41"/>
+      <x:c r="H45" s="41"/>
+      <x:c r="I45" s="41"/>
+      <x:c r="J45" s="41"/>
+      <x:c r="K45" s="41"/>
+      <x:c r="L45" s="41"/>
+      <x:c r="M45" s="41"/>
+      <x:c r="N45" s="41"/>
+      <x:c r="O45" s="41"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
         <x:v>Opening cash balance</x:v>
       </x:c>
-      <x:c r="B46" s="43" t="n">
+      <x:c r="B46" s="44" t="n">
         <x:f>'Assumptions'!$B$10</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="C46" s="43" t="n">
+      <x:c r="C46" s="44" t="n">
         <x:f>B48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="D46" s="43" t="n">
+      <x:c r="D46" s="44" t="n">
         <x:f>C48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="E46" s="43" t="n">
+      <x:c r="E46" s="44" t="n">
         <x:f>D48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="F46" s="43" t="n">
+      <x:c r="F46" s="44" t="n">
         <x:f>E48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="G46" s="43" t="n">
+      <x:c r="G46" s="44" t="n">
         <x:f>F48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="H46" s="43" t="n">
+      <x:c r="H46" s="44" t="n">
         <x:f>G48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="I46" s="43" t="n">
+      <x:c r="I46" s="44" t="n">
         <x:f>H48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="J46" s="43" t="n">
+      <x:c r="J46" s="44" t="n">
         <x:f>I48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="K46" s="43" t="n">
+      <x:c r="K46" s="44" t="n">
         <x:f>J48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="L46" s="43" t="n">
+      <x:c r="L46" s="44" t="n">
         <x:f>K48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="M46" s="43" t="n">
+      <x:c r="M46" s="44" t="n">
         <x:f>L48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="N46" s="43" t="n">
+      <x:c r="N46" s="44" t="n">
         <x:f>M48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="O46" s="38" t="n">
+      <x:c r="O46" s="39" t="n">
         <x:f>N46</x:f>
         <x:v>82000</x:v>
       </x:c>
@@ -4571,120 +4950,120 @@
       <x:c r="A47" t="str">
         <x:v>Net cash movement</x:v>
       </x:c>
-      <x:c r="B47" s="41" t="n">
+      <x:c r="B47" s="42" t="n">
         <x:f>B19-B43</x:f>
         <x:v>-42000</x:v>
       </x:c>
-      <x:c r="C47" s="41" t="n">
+      <x:c r="C47" s="42" t="n">
         <x:f>C19-C43</x:f>
         <x:v>-9000</x:v>
       </x:c>
-      <x:c r="D47" s="41" t="n">
+      <x:c r="D47" s="42" t="n">
         <x:f>D19-D43</x:f>
         <x:v>-24000</x:v>
       </x:c>
-      <x:c r="E47" s="41" t="n">
+      <x:c r="E47" s="42" t="n">
         <x:f>E19-E43</x:f>
         <x:v>-32000</x:v>
       </x:c>
-      <x:c r="F47" s="41" t="n">
+      <x:c r="F47" s="42" t="n">
         <x:f>F19-F43</x:f>
         <x:v>-92000</x:v>
       </x:c>
-      <x:c r="G47" s="41" t="n">
+      <x:c r="G47" s="42" t="n">
         <x:f>G19-G43</x:f>
         <x:v>-68000</x:v>
       </x:c>
-      <x:c r="H47" s="41" t="n">
+      <x:c r="H47" s="42" t="n">
         <x:f>H19-H43</x:f>
         <x:v>84000</x:v>
       </x:c>
-      <x:c r="I47" s="41" t="n">
+      <x:c r="I47" s="42" t="n">
         <x:f>I19-I43</x:f>
         <x:v>-57000</x:v>
       </x:c>
-      <x:c r="J47" s="41" t="n">
+      <x:c r="J47" s="42" t="n">
         <x:f>J19-J43</x:f>
         <x:v>-43000</x:v>
       </x:c>
-      <x:c r="K47" s="41" t="n">
+      <x:c r="K47" s="42" t="n">
         <x:f>K19-K43</x:f>
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="L47" s="41" t="n">
+      <x:c r="L47" s="42" t="n">
         <x:f>L19-L43</x:f>
         <x:v>-38000</x:v>
       </x:c>
-      <x:c r="M47" s="41" t="n">
+      <x:c r="M47" s="42" t="n">
         <x:f>M19-M43</x:f>
         <x:v>-17000</x:v>
       </x:c>
-      <x:c r="N47" s="41" t="n">
+      <x:c r="N47" s="42" t="n">
         <x:f>N19-N43</x:f>
         <x:v>-51000</x:v>
       </x:c>
-      <x:c r="O47" s="38" t="n">
+      <x:c r="O47" s="39" t="n">
         <x:f>SUM(B47:N47)</x:f>
         <x:v>-369000</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="36" t="str">
+      <x:c r="A48" s="37" t="str">
         <x:v>Closing cash balance</x:v>
       </x:c>
-      <x:c r="B48" s="42" t="n">
+      <x:c r="B48" s="43" t="n">
         <x:f>B46+B47</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="C48" s="42" t="n">
+      <x:c r="C48" s="43" t="n">
         <x:f>C46+C47</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="D48" s="42" t="n">
+      <x:c r="D48" s="43" t="n">
         <x:f>D46+D47</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="E48" s="42" t="n">
+      <x:c r="E48" s="43" t="n">
         <x:f>E46+E47</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="F48" s="42" t="n">
+      <x:c r="F48" s="43" t="n">
         <x:f>F46+F47</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="G48" s="42" t="n">
+      <x:c r="G48" s="43" t="n">
         <x:f>G46+G47</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="H48" s="42" t="n">
+      <x:c r="H48" s="43" t="n">
         <x:f>H46+H47</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="I48" s="42" t="n">
+      <x:c r="I48" s="43" t="n">
         <x:f>I46+I47</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="J48" s="42" t="n">
+      <x:c r="J48" s="43" t="n">
         <x:f>J46+J47</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="K48" s="42" t="n">
+      <x:c r="K48" s="43" t="n">
         <x:f>K46+K47</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="L48" s="42" t="n">
+      <x:c r="L48" s="43" t="n">
         <x:f>L46+L47</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="M48" s="42" t="n">
+      <x:c r="M48" s="43" t="n">
         <x:f>M46+M47</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="N48" s="42" t="n">
+      <x:c r="N48" s="43" t="n">
         <x:f>N46+N47</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="O48" s="39" t="n">
+      <x:c r="O48" s="40" t="n">
         <x:f>N48</x:f>
         <x:v>31000</x:v>
       </x:c>
@@ -4693,120 +5072,120 @@
       <x:c r="A49" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B49" s="43" t="n">
+      <x:c r="B49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="C49" s="43" t="n">
+      <x:c r="C49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="D49" s="43" t="n">
+      <x:c r="D49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="E49" s="43" t="n">
+      <x:c r="E49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="F49" s="43" t="n">
+      <x:c r="F49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="G49" s="43" t="n">
+      <x:c r="G49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="H49" s="43" t="n">
+      <x:c r="H49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="I49" s="43" t="n">
+      <x:c r="I49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="J49" s="43" t="n">
+      <x:c r="J49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="K49" s="43" t="n">
+      <x:c r="K49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="L49" s="43" t="n">
+      <x:c r="L49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="M49" s="43" t="n">
+      <x:c r="M49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="N49" s="43" t="n">
+      <x:c r="N49" s="44" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="O49" s="38" t="n">
+      <x:c r="O49" s="39" t="n">
         <x:f>N49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="36" t="str">
+      <x:c r="A50" s="37" t="str">
         <x:v>Headroom / (gap)</x:v>
       </x:c>
-      <x:c r="B50" s="42" t="n">
+      <x:c r="B50" s="43" t="n">
         <x:f>B48-B49</x:f>
         <x:v>258000</x:v>
       </x:c>
-      <x:c r="C50" s="42" t="n">
+      <x:c r="C50" s="43" t="n">
         <x:f>C48-C49</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="D50" s="42" t="n">
+      <x:c r="D50" s="43" t="n">
         <x:f>D48-D49</x:f>
         <x:v>225000</x:v>
       </x:c>
-      <x:c r="E50" s="42" t="n">
+      <x:c r="E50" s="43" t="n">
         <x:f>E48-E49</x:f>
         <x:v>193000</x:v>
       </x:c>
-      <x:c r="F50" s="42" t="n">
+      <x:c r="F50" s="43" t="n">
         <x:f>F48-F49</x:f>
         <x:v>101000</x:v>
       </x:c>
-      <x:c r="G50" s="42" t="n">
+      <x:c r="G50" s="43" t="n">
         <x:f>G48-G49</x:f>
         <x:v>33000</x:v>
       </x:c>
-      <x:c r="H50" s="42" t="n">
+      <x:c r="H50" s="43" t="n">
         <x:f>H48-H49</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="I50" s="42" t="n">
+      <x:c r="I50" s="43" t="n">
         <x:f>I48-I49</x:f>
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="J50" s="42" t="n">
+      <x:c r="J50" s="43" t="n">
         <x:f>J48-J49</x:f>
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="K50" s="42" t="n">
+      <x:c r="K50" s="43" t="n">
         <x:f>K48-K49</x:f>
         <x:v>37000</x:v>
       </x:c>
-      <x:c r="L50" s="42" t="n">
+      <x:c r="L50" s="43" t="n">
         <x:f>L48-L49</x:f>
         <x:v>-1000</x:v>
       </x:c>
-      <x:c r="M50" s="42" t="n">
+      <x:c r="M50" s="43" t="n">
         <x:f>M48-M49</x:f>
         <x:v>-18000</x:v>
       </x:c>
-      <x:c r="N50" s="42" t="n">
+      <x:c r="N50" s="43" t="n">
         <x:f>N48-N49</x:f>
         <x:v>-69000</x:v>
       </x:c>
-      <x:c r="O50" s="39" t="n">
+      <x:c r="O50" s="40" t="n">
         <x:f>N50</x:f>
         <x:v>-69000</x:v>
       </x:c>
@@ -4889,7 +5268,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R993fc6886ca7468d"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb3415d0a01b41c9"/>
 </x:worksheet>
 </file>
 
@@ -4933,7 +5312,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Compare forecast and actual receipts, payments and closing cash. Variances remain blank until the related actual is entered.</x:v>
+        <x:v>Preserve the original forecast as values, then compare it with actual receipts, payments and closing cash.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -4949,579 +5328,532 @@
       <x:c r="M2" s="8"/>
       <x:c r="N2" s="8"/>
     </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="27" t="str">
+        <x:v>Before updating the live forecast, paste the week's original period dates, receipts, payments and closing cash here as values. Snapshot cells must not link back to the live forecast.</x:v>
+      </x:c>
+      <x:c r="B4" s="27"/>
+      <x:c r="C4" s="27"/>
+      <x:c r="D4" s="27"/>
+      <x:c r="E4" s="27"/>
+      <x:c r="F4" s="27"/>
+      <x:c r="G4" s="27"/>
+      <x:c r="H4" s="27"/>
+      <x:c r="I4" s="27"/>
+      <x:c r="J4" s="27"/>
+      <x:c r="K4" s="27"/>
+      <x:c r="L4" s="27"/>
+      <x:c r="M4" s="27"/>
+      <x:c r="N4" s="27"/>
+    </x:row>
     <x:row r="5" ht="42" customHeight="1">
-      <x:c r="A5" s="44" t="str">
-        <x:v>Week start</x:v>
-      </x:c>
-      <x:c r="B5" s="44" t="str">
-        <x:v>Week end</x:v>
-      </x:c>
-      <x:c r="C5" s="44" t="str">
-        <x:v>Forecast receipts</x:v>
-      </x:c>
-      <x:c r="D5" s="44" t="str">
+      <x:c r="A5" s="45" t="str">
+        <x:v>Snapshot week start</x:v>
+      </x:c>
+      <x:c r="B5" s="45" t="str">
+        <x:v>Snapshot week end</x:v>
+      </x:c>
+      <x:c r="C5" s="45" t="str">
+        <x:v>Forecast snapshot receipts</x:v>
+      </x:c>
+      <x:c r="D5" s="45" t="str">
         <x:v>Actual receipts</x:v>
       </x:c>
-      <x:c r="E5" s="44" t="str">
+      <x:c r="E5" s="45" t="str">
         <x:v>Receipt variance $</x:v>
       </x:c>
-      <x:c r="F5" s="44" t="str">
+      <x:c r="F5" s="45" t="str">
         <x:v>Receipt variance %</x:v>
       </x:c>
-      <x:c r="G5" s="44" t="str">
-        <x:v>Forecast payments</x:v>
-      </x:c>
-      <x:c r="H5" s="44" t="str">
+      <x:c r="G5" s="45" t="str">
+        <x:v>Forecast snapshot payments</x:v>
+      </x:c>
+      <x:c r="H5" s="45" t="str">
         <x:v>Actual payments</x:v>
       </x:c>
-      <x:c r="I5" s="44" t="str">
+      <x:c r="I5" s="45" t="str">
         <x:v>Payment variance $</x:v>
       </x:c>
-      <x:c r="J5" s="44" t="str">
+      <x:c r="J5" s="45" t="str">
         <x:v>Payment variance %</x:v>
       </x:c>
-      <x:c r="K5" s="44" t="str">
-        <x:v>Forecast closing cash</x:v>
-      </x:c>
-      <x:c r="L5" s="44" t="str">
+      <x:c r="K5" s="45" t="str">
+        <x:v>Forecast snapshot closing cash</x:v>
+      </x:c>
+      <x:c r="L5" s="45" t="str">
         <x:v>Actual closing cash</x:v>
       </x:c>
-      <x:c r="M5" s="44" t="str">
+      <x:c r="M5" s="45" t="str">
         <x:v>Closing-cash variance</x:v>
       </x:c>
-      <x:c r="N5" s="44" t="str">
+      <x:c r="N5" s="45" t="str">
         <x:v>Owner commentary</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="46" t="n">
-        <x:f>'13-Week Forecast'!B$5</x:f>
+      <x:c r="A6" s="49" t="n">
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="B6" s="46" t="n">
-        <x:f>'13-Week Forecast'!B$6</x:f>
+      <x:c r="B6" s="49" t="n">
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C6" s="43" t="n">
-        <x:f>'13-Week Forecast'!B$19</x:f>
+      <x:c r="C6" s="38" t="n">
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="D6" s="37"/>
-      <x:c r="E6" s="41" t="str">
+      <x:c r="D6" s="38"/>
+      <x:c r="E6" s="42" t="str">
         <x:f>IF(D6="","",D6-C6)</x:f>
       </x:c>
-      <x:c r="F6" s="47" t="str">
+      <x:c r="F6" s="50" t="str">
         <x:f>IF(OR(D6="",C6=0),"",(D6-C6)/C6)</x:f>
       </x:c>
-      <x:c r="G6" s="43" t="n">
-        <x:f>'13-Week Forecast'!B$43</x:f>
+      <x:c r="G6" s="38" t="n">
         <x:v>212000</x:v>
       </x:c>
-      <x:c r="H6" s="37"/>
-      <x:c r="I6" s="41" t="str">
+      <x:c r="H6" s="38"/>
+      <x:c r="I6" s="42" t="str">
         <x:f>IF(H6="","",G6-H6)</x:f>
       </x:c>
-      <x:c r="J6" s="47" t="str">
+      <x:c r="J6" s="50" t="str">
         <x:f>IF(OR(H6="",G6=0),"",(G6-H6)/G6)</x:f>
       </x:c>
-      <x:c r="K6" s="43" t="n">
-        <x:f>'13-Week Forecast'!B$48</x:f>
+      <x:c r="K6" s="38" t="n">
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="L6" s="37"/>
-      <x:c r="M6" s="41" t="str">
+      <x:c r="L6" s="38"/>
+      <x:c r="M6" s="42" t="str">
         <x:f>IF(L6="","",L6-K6)</x:f>
       </x:c>
       <x:c r="N6" s="16"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="46" t="n">
-        <x:f>'13-Week Forecast'!C$5</x:f>
+      <x:c r="A7" s="49" t="n">
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="B7" s="46" t="n">
-        <x:f>'13-Week Forecast'!C$6</x:f>
+      <x:c r="B7" s="49" t="n">
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="C7" s="43" t="n">
-        <x:f>'13-Week Forecast'!C$19</x:f>
+      <x:c r="C7" s="38" t="n">
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="D7" s="37"/>
-      <x:c r="E7" s="41" t="str">
+      <x:c r="D7" s="38"/>
+      <x:c r="E7" s="42" t="str">
         <x:f>IF(D7="","",D7-C7)</x:f>
       </x:c>
-      <x:c r="F7" s="47" t="str">
+      <x:c r="F7" s="50" t="str">
         <x:f>IF(OR(D7="",C7=0),"",(D7-C7)/C7)</x:f>
       </x:c>
-      <x:c r="G7" s="43" t="n">
-        <x:f>'13-Week Forecast'!C$43</x:f>
+      <x:c r="G7" s="38" t="n">
         <x:v>178000</x:v>
       </x:c>
-      <x:c r="H7" s="37"/>
-      <x:c r="I7" s="41" t="str">
+      <x:c r="H7" s="38"/>
+      <x:c r="I7" s="42" t="str">
         <x:f>IF(H7="","",G7-H7)</x:f>
       </x:c>
-      <x:c r="J7" s="47" t="str">
+      <x:c r="J7" s="50" t="str">
         <x:f>IF(OR(H7="",G7=0),"",(G7-H7)/G7)</x:f>
       </x:c>
-      <x:c r="K7" s="43" t="n">
-        <x:f>'13-Week Forecast'!C$48</x:f>
+      <x:c r="K7" s="38" t="n">
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="L7" s="37"/>
-      <x:c r="M7" s="41" t="str">
+      <x:c r="L7" s="38"/>
+      <x:c r="M7" s="42" t="str">
         <x:f>IF(L7="","",L7-K7)</x:f>
       </x:c>
       <x:c r="N7" s="16"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="46" t="n">
-        <x:f>'13-Week Forecast'!D$5</x:f>
+      <x:c r="A8" s="49" t="n">
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="B8" s="46" t="n">
-        <x:f>'13-Week Forecast'!D$6</x:f>
+      <x:c r="B8" s="49" t="n">
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="C8" s="43" t="n">
-        <x:f>'13-Week Forecast'!D$19</x:f>
+      <x:c r="C8" s="38" t="n">
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="D8" s="37"/>
-      <x:c r="E8" s="41" t="str">
+      <x:c r="D8" s="38"/>
+      <x:c r="E8" s="42" t="str">
         <x:f>IF(D8="","",D8-C8)</x:f>
       </x:c>
-      <x:c r="F8" s="47" t="str">
+      <x:c r="F8" s="50" t="str">
         <x:f>IF(OR(D8="",C8=0),"",(D8-C8)/C8)</x:f>
       </x:c>
-      <x:c r="G8" s="43" t="n">
-        <x:f>'13-Week Forecast'!D$43</x:f>
+      <x:c r="G8" s="38" t="n">
         <x:v>182000</x:v>
       </x:c>
-      <x:c r="H8" s="37"/>
-      <x:c r="I8" s="41" t="str">
+      <x:c r="H8" s="38"/>
+      <x:c r="I8" s="42" t="str">
         <x:f>IF(H8="","",G8-H8)</x:f>
       </x:c>
-      <x:c r="J8" s="47" t="str">
+      <x:c r="J8" s="50" t="str">
         <x:f>IF(OR(H8="",G8=0),"",(G8-H8)/G8)</x:f>
       </x:c>
-      <x:c r="K8" s="43" t="n">
-        <x:f>'13-Week Forecast'!D$48</x:f>
+      <x:c r="K8" s="38" t="n">
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="L8" s="37"/>
-      <x:c r="M8" s="41" t="str">
+      <x:c r="L8" s="38"/>
+      <x:c r="M8" s="42" t="str">
         <x:f>IF(L8="","",L8-K8)</x:f>
       </x:c>
       <x:c r="N8" s="16"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="46" t="n">
-        <x:f>'13-Week Forecast'!E$5</x:f>
+      <x:c r="A9" s="49" t="n">
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="B9" s="46" t="n">
-        <x:f>'13-Week Forecast'!E$6</x:f>
+      <x:c r="B9" s="49" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="C9" s="43" t="n">
-        <x:f>'13-Week Forecast'!E$19</x:f>
+      <x:c r="C9" s="38" t="n">
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="D9" s="37"/>
-      <x:c r="E9" s="41" t="str">
+      <x:c r="D9" s="38"/>
+      <x:c r="E9" s="42" t="str">
         <x:f>IF(D9="","",D9-C9)</x:f>
       </x:c>
-      <x:c r="F9" s="47" t="str">
+      <x:c r="F9" s="50" t="str">
         <x:f>IF(OR(D9="",C9=0),"",(D9-C9)/C9)</x:f>
       </x:c>
-      <x:c r="G9" s="43" t="n">
-        <x:f>'13-Week Forecast'!E$43</x:f>
+      <x:c r="G9" s="38" t="n">
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="H9" s="37"/>
-      <x:c r="I9" s="41" t="str">
+      <x:c r="H9" s="38"/>
+      <x:c r="I9" s="42" t="str">
         <x:f>IF(H9="","",G9-H9)</x:f>
       </x:c>
-      <x:c r="J9" s="47" t="str">
+      <x:c r="J9" s="50" t="str">
         <x:f>IF(OR(H9="",G9=0),"",(G9-H9)/G9)</x:f>
       </x:c>
-      <x:c r="K9" s="43" t="n">
-        <x:f>'13-Week Forecast'!E$48</x:f>
+      <x:c r="K9" s="38" t="n">
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="L9" s="37"/>
-      <x:c r="M9" s="41" t="str">
+      <x:c r="L9" s="38"/>
+      <x:c r="M9" s="42" t="str">
         <x:f>IF(L9="","",L9-K9)</x:f>
       </x:c>
       <x:c r="N9" s="16"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="46" t="n">
-        <x:f>'13-Week Forecast'!F$5</x:f>
+      <x:c r="A10" s="49" t="n">
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="B10" s="46" t="n">
-        <x:f>'13-Week Forecast'!F$6</x:f>
+      <x:c r="B10" s="49" t="n">
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="C10" s="43" t="n">
-        <x:f>'13-Week Forecast'!F$19</x:f>
+      <x:c r="C10" s="38" t="n">
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="D10" s="37"/>
-      <x:c r="E10" s="41" t="str">
+      <x:c r="D10" s="38"/>
+      <x:c r="E10" s="42" t="str">
         <x:f>IF(D10="","",D10-C10)</x:f>
       </x:c>
-      <x:c r="F10" s="47" t="str">
+      <x:c r="F10" s="50" t="str">
         <x:f>IF(OR(D10="",C10=0),"",(D10-C10)/C10)</x:f>
       </x:c>
-      <x:c r="G10" s="43" t="n">
-        <x:f>'13-Week Forecast'!F$43</x:f>
+      <x:c r="G10" s="38" t="n">
         <x:v>232000</x:v>
       </x:c>
-      <x:c r="H10" s="37"/>
-      <x:c r="I10" s="41" t="str">
+      <x:c r="H10" s="38"/>
+      <x:c r="I10" s="42" t="str">
         <x:f>IF(H10="","",G10-H10)</x:f>
       </x:c>
-      <x:c r="J10" s="47" t="str">
+      <x:c r="J10" s="50" t="str">
         <x:f>IF(OR(H10="",G10=0),"",(G10-H10)/G10)</x:f>
       </x:c>
-      <x:c r="K10" s="43" t="n">
-        <x:f>'13-Week Forecast'!F$48</x:f>
+      <x:c r="K10" s="38" t="n">
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="L10" s="37"/>
-      <x:c r="M10" s="41" t="str">
+      <x:c r="L10" s="38"/>
+      <x:c r="M10" s="42" t="str">
         <x:f>IF(L10="","",L10-K10)</x:f>
       </x:c>
       <x:c r="N10" s="16"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="46" t="n">
-        <x:f>'13-Week Forecast'!G$5</x:f>
+      <x:c r="A11" s="49" t="n">
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="B11" s="46" t="n">
-        <x:f>'13-Week Forecast'!G$6</x:f>
+      <x:c r="B11" s="49" t="n">
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="C11" s="43" t="n">
-        <x:f>'13-Week Forecast'!G$19</x:f>
+      <x:c r="C11" s="38" t="n">
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="D11" s="37"/>
-      <x:c r="E11" s="41" t="str">
+      <x:c r="D11" s="38"/>
+      <x:c r="E11" s="42" t="str">
         <x:f>IF(D11="","",D11-C11)</x:f>
       </x:c>
-      <x:c r="F11" s="47" t="str">
+      <x:c r="F11" s="50" t="str">
         <x:f>IF(OR(D11="",C11=0),"",(D11-C11)/C11)</x:f>
       </x:c>
-      <x:c r="G11" s="43" t="n">
-        <x:f>'13-Week Forecast'!G$43</x:f>
+      <x:c r="G11" s="38" t="n">
         <x:v>209000</x:v>
       </x:c>
-      <x:c r="H11" s="37"/>
-      <x:c r="I11" s="41" t="str">
+      <x:c r="H11" s="38"/>
+      <x:c r="I11" s="42" t="str">
         <x:f>IF(H11="","",G11-H11)</x:f>
       </x:c>
-      <x:c r="J11" s="47" t="str">
+      <x:c r="J11" s="50" t="str">
         <x:f>IF(OR(H11="",G11=0),"",(G11-H11)/G11)</x:f>
       </x:c>
-      <x:c r="K11" s="43" t="n">
-        <x:f>'13-Week Forecast'!G$48</x:f>
+      <x:c r="K11" s="38" t="n">
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="L11" s="37"/>
-      <x:c r="M11" s="41" t="str">
+      <x:c r="L11" s="38"/>
+      <x:c r="M11" s="42" t="str">
         <x:f>IF(L11="","",L11-K11)</x:f>
       </x:c>
       <x:c r="N11" s="16"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="46" t="n">
-        <x:f>'13-Week Forecast'!H$5</x:f>
+      <x:c r="A12" s="49" t="n">
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="B12" s="46" t="n">
-        <x:f>'13-Week Forecast'!H$6</x:f>
+      <x:c r="B12" s="49" t="n">
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="C12" s="43" t="n">
-        <x:f>'13-Week Forecast'!H$19</x:f>
+      <x:c r="C12" s="38" t="n">
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="D12" s="37"/>
-      <x:c r="E12" s="41" t="str">
+      <x:c r="D12" s="38"/>
+      <x:c r="E12" s="42" t="str">
         <x:f>IF(D12="","",D12-C12)</x:f>
       </x:c>
-      <x:c r="F12" s="47" t="str">
+      <x:c r="F12" s="50" t="str">
         <x:f>IF(OR(D12="",C12=0),"",(D12-C12)/C12)</x:f>
       </x:c>
-      <x:c r="G12" s="43" t="n">
-        <x:f>'13-Week Forecast'!H$43</x:f>
+      <x:c r="G12" s="38" t="n">
         <x:v>197000</x:v>
       </x:c>
-      <x:c r="H12" s="37"/>
-      <x:c r="I12" s="41" t="str">
+      <x:c r="H12" s="38"/>
+      <x:c r="I12" s="42" t="str">
         <x:f>IF(H12="","",G12-H12)</x:f>
       </x:c>
-      <x:c r="J12" s="47" t="str">
+      <x:c r="J12" s="50" t="str">
         <x:f>IF(OR(H12="",G12=0),"",(G12-H12)/G12)</x:f>
       </x:c>
-      <x:c r="K12" s="43" t="n">
-        <x:f>'13-Week Forecast'!H$48</x:f>
+      <x:c r="K12" s="38" t="n">
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="L12" s="37"/>
-      <x:c r="M12" s="41" t="str">
+      <x:c r="L12" s="38"/>
+      <x:c r="M12" s="42" t="str">
         <x:f>IF(L12="","",L12-K12)</x:f>
       </x:c>
       <x:c r="N12" s="16"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="46" t="n">
-        <x:f>'13-Week Forecast'!I$5</x:f>
+      <x:c r="A13" s="49" t="n">
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="B13" s="46" t="n">
-        <x:f>'13-Week Forecast'!I$6</x:f>
+      <x:c r="B13" s="49" t="n">
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="C13" s="43" t="n">
-        <x:f>'13-Week Forecast'!I$19</x:f>
+      <x:c r="C13" s="38" t="n">
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="D13" s="37"/>
-      <x:c r="E13" s="41" t="str">
+      <x:c r="D13" s="38"/>
+      <x:c r="E13" s="42" t="str">
         <x:f>IF(D13="","",D13-C13)</x:f>
       </x:c>
-      <x:c r="F13" s="47" t="str">
+      <x:c r="F13" s="50" t="str">
         <x:f>IF(OR(D13="",C13=0),"",(D13-C13)/C13)</x:f>
       </x:c>
-      <x:c r="G13" s="43" t="n">
-        <x:f>'13-Week Forecast'!I$43</x:f>
+      <x:c r="G13" s="38" t="n">
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="H13" s="37"/>
-      <x:c r="I13" s="41" t="str">
+      <x:c r="H13" s="38"/>
+      <x:c r="I13" s="42" t="str">
         <x:f>IF(H13="","",G13-H13)</x:f>
       </x:c>
-      <x:c r="J13" s="47" t="str">
+      <x:c r="J13" s="50" t="str">
         <x:f>IF(OR(H13="",G13=0),"",(G13-H13)/G13)</x:f>
       </x:c>
-      <x:c r="K13" s="43" t="n">
-        <x:f>'13-Week Forecast'!I$48</x:f>
+      <x:c r="K13" s="38" t="n">
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="L13" s="37"/>
-      <x:c r="M13" s="41" t="str">
+      <x:c r="L13" s="38"/>
+      <x:c r="M13" s="42" t="str">
         <x:f>IF(L13="","",L13-K13)</x:f>
       </x:c>
       <x:c r="N13" s="16"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="46" t="n">
-        <x:f>'13-Week Forecast'!J$5</x:f>
+      <x:c r="A14" s="49" t="n">
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="B14" s="46" t="n">
-        <x:f>'13-Week Forecast'!J$6</x:f>
+      <x:c r="B14" s="49" t="n">
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="C14" s="43" t="n">
-        <x:f>'13-Week Forecast'!J$19</x:f>
+      <x:c r="C14" s="38" t="n">
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="D14" s="37"/>
-      <x:c r="E14" s="41" t="str">
+      <x:c r="D14" s="38"/>
+      <x:c r="E14" s="42" t="str">
         <x:f>IF(D14="","",D14-C14)</x:f>
       </x:c>
-      <x:c r="F14" s="47" t="str">
+      <x:c r="F14" s="50" t="str">
         <x:f>IF(OR(D14="",C14=0),"",(D14-C14)/C14)</x:f>
       </x:c>
-      <x:c r="G14" s="43" t="n">
-        <x:f>'13-Week Forecast'!J$43</x:f>
+      <x:c r="G14" s="38" t="n">
         <x:v>307000</x:v>
       </x:c>
-      <x:c r="H14" s="37"/>
-      <x:c r="I14" s="41" t="str">
+      <x:c r="H14" s="38"/>
+      <x:c r="I14" s="42" t="str">
         <x:f>IF(H14="","",G14-H14)</x:f>
       </x:c>
-      <x:c r="J14" s="47" t="str">
+      <x:c r="J14" s="50" t="str">
         <x:f>IF(OR(H14="",G14=0),"",(G14-H14)/G14)</x:f>
       </x:c>
-      <x:c r="K14" s="43" t="n">
-        <x:f>'13-Week Forecast'!J$48</x:f>
+      <x:c r="K14" s="38" t="n">
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="L14" s="37"/>
-      <x:c r="M14" s="41" t="str">
+      <x:c r="L14" s="38"/>
+      <x:c r="M14" s="42" t="str">
         <x:f>IF(L14="","",L14-K14)</x:f>
       </x:c>
       <x:c r="N14" s="16"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="46" t="n">
-        <x:f>'13-Week Forecast'!K$5</x:f>
+      <x:c r="A15" s="49" t="n">
         <x:v>46328</x:v>
       </x:c>
-      <x:c r="B15" s="46" t="n">
-        <x:f>'13-Week Forecast'!K$6</x:f>
+      <x:c r="B15" s="49" t="n">
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="C15" s="43" t="n">
-        <x:f>'13-Week Forecast'!K$19</x:f>
+      <x:c r="C15" s="38" t="n">
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="D15" s="37"/>
-      <x:c r="E15" s="41" t="str">
+      <x:c r="D15" s="38"/>
+      <x:c r="E15" s="42" t="str">
         <x:f>IF(D15="","",D15-C15)</x:f>
       </x:c>
-      <x:c r="F15" s="47" t="str">
+      <x:c r="F15" s="50" t="str">
         <x:f>IF(OR(D15="",C15=0),"",(D15-C15)/C15)</x:f>
       </x:c>
-      <x:c r="G15" s="43" t="n">
-        <x:f>'13-Week Forecast'!K$43</x:f>
+      <x:c r="G15" s="38" t="n">
         <x:v>229000</x:v>
       </x:c>
-      <x:c r="H15" s="37"/>
-      <x:c r="I15" s="41" t="str">
+      <x:c r="H15" s="38"/>
+      <x:c r="I15" s="42" t="str">
         <x:f>IF(H15="","",G15-H15)</x:f>
       </x:c>
-      <x:c r="J15" s="47" t="str">
+      <x:c r="J15" s="50" t="str">
         <x:f>IF(OR(H15="",G15=0),"",(G15-H15)/G15)</x:f>
       </x:c>
-      <x:c r="K15" s="43" t="n">
-        <x:f>'13-Week Forecast'!K$48</x:f>
+      <x:c r="K15" s="38" t="n">
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="L15" s="37"/>
-      <x:c r="M15" s="41" t="str">
+      <x:c r="L15" s="38"/>
+      <x:c r="M15" s="42" t="str">
         <x:f>IF(L15="","",L15-K15)</x:f>
       </x:c>
       <x:c r="N15" s="16"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="46" t="n">
-        <x:f>'13-Week Forecast'!L$5</x:f>
+      <x:c r="A16" s="49" t="n">
         <x:v>46335</x:v>
       </x:c>
-      <x:c r="B16" s="46" t="n">
-        <x:f>'13-Week Forecast'!L$6</x:f>
+      <x:c r="B16" s="49" t="n">
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="C16" s="43" t="n">
-        <x:f>'13-Week Forecast'!L$19</x:f>
+      <x:c r="C16" s="38" t="n">
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="D16" s="37"/>
-      <x:c r="E16" s="41" t="str">
+      <x:c r="D16" s="38"/>
+      <x:c r="E16" s="42" t="str">
         <x:f>IF(D16="","",D16-C16)</x:f>
       </x:c>
-      <x:c r="F16" s="47" t="str">
+      <x:c r="F16" s="50" t="str">
         <x:f>IF(OR(D16="",C16=0),"",(D16-C16)/C16)</x:f>
       </x:c>
-      <x:c r="G16" s="43" t="n">
-        <x:f>'13-Week Forecast'!L$43</x:f>
+      <x:c r="G16" s="38" t="n">
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="H16" s="37"/>
-      <x:c r="I16" s="41" t="str">
+      <x:c r="H16" s="38"/>
+      <x:c r="I16" s="42" t="str">
         <x:f>IF(H16="","",G16-H16)</x:f>
       </x:c>
-      <x:c r="J16" s="47" t="str">
+      <x:c r="J16" s="50" t="str">
         <x:f>IF(OR(H16="",G16=0),"",(G16-H16)/G16)</x:f>
       </x:c>
-      <x:c r="K16" s="43" t="n">
-        <x:f>'13-Week Forecast'!L$48</x:f>
+      <x:c r="K16" s="38" t="n">
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="L16" s="37"/>
-      <x:c r="M16" s="41" t="str">
+      <x:c r="L16" s="38"/>
+      <x:c r="M16" s="42" t="str">
         <x:f>IF(L16="","",L16-K16)</x:f>
       </x:c>
       <x:c r="N16" s="16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="46" t="n">
-        <x:f>'13-Week Forecast'!M$5</x:f>
+      <x:c r="A17" s="49" t="n">
         <x:v>46342</x:v>
       </x:c>
-      <x:c r="B17" s="46" t="n">
-        <x:f>'13-Week Forecast'!M$6</x:f>
+      <x:c r="B17" s="49" t="n">
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="C17" s="43" t="n">
-        <x:f>'13-Week Forecast'!M$19</x:f>
+      <x:c r="C17" s="38" t="n">
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="D17" s="37"/>
-      <x:c r="E17" s="41" t="str">
+      <x:c r="D17" s="38"/>
+      <x:c r="E17" s="42" t="str">
         <x:f>IF(D17="","",D17-C17)</x:f>
       </x:c>
-      <x:c r="F17" s="47" t="str">
+      <x:c r="F17" s="50" t="str">
         <x:f>IF(OR(D17="",C17=0),"",(D17-C17)/C17)</x:f>
       </x:c>
-      <x:c r="G17" s="43" t="n">
-        <x:f>'13-Week Forecast'!M$43</x:f>
+      <x:c r="G17" s="38" t="n">
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="H17" s="37"/>
-      <x:c r="I17" s="41" t="str">
+      <x:c r="H17" s="38"/>
+      <x:c r="I17" s="42" t="str">
         <x:f>IF(H17="","",G17-H17)</x:f>
       </x:c>
-      <x:c r="J17" s="47" t="str">
+      <x:c r="J17" s="50" t="str">
         <x:f>IF(OR(H17="",G17=0),"",(G17-H17)/G17)</x:f>
       </x:c>
-      <x:c r="K17" s="43" t="n">
-        <x:f>'13-Week Forecast'!M$48</x:f>
+      <x:c r="K17" s="38" t="n">
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="L17" s="37"/>
-      <x:c r="M17" s="41" t="str">
+      <x:c r="L17" s="38"/>
+      <x:c r="M17" s="42" t="str">
         <x:f>IF(L17="","",L17-K17)</x:f>
       </x:c>
       <x:c r="N17" s="16"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="46" t="n">
-        <x:f>'13-Week Forecast'!N$5</x:f>
+      <x:c r="A18" s="49" t="n">
         <x:v>46349</x:v>
       </x:c>
-      <x:c r="B18" s="46" t="n">
-        <x:f>'13-Week Forecast'!N$6</x:f>
+      <x:c r="B18" s="49" t="n">
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="C18" s="43" t="n">
-        <x:f>'13-Week Forecast'!N$19</x:f>
+      <x:c r="C18" s="38" t="n">
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="D18" s="37"/>
-      <x:c r="E18" s="41" t="str">
+      <x:c r="D18" s="38"/>
+      <x:c r="E18" s="42" t="str">
         <x:f>IF(D18="","",D18-C18)</x:f>
       </x:c>
-      <x:c r="F18" s="47" t="str">
+      <x:c r="F18" s="50" t="str">
         <x:f>IF(OR(D18="",C18=0),"",(D18-C18)/C18)</x:f>
       </x:c>
-      <x:c r="G18" s="43" t="n">
-        <x:f>'13-Week Forecast'!N$43</x:f>
+      <x:c r="G18" s="38" t="n">
         <x:v>219000</x:v>
       </x:c>
-      <x:c r="H18" s="37"/>
-      <x:c r="I18" s="41" t="str">
+      <x:c r="H18" s="38"/>
+      <x:c r="I18" s="42" t="str">
         <x:f>IF(H18="","",G18-H18)</x:f>
       </x:c>
-      <x:c r="J18" s="47" t="str">
+      <x:c r="J18" s="50" t="str">
         <x:f>IF(OR(H18="",G18=0),"",(G18-H18)/G18)</x:f>
       </x:c>
-      <x:c r="K18" s="43" t="n">
-        <x:f>'13-Week Forecast'!N$48</x:f>
+      <x:c r="K18" s="38" t="n">
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="L18" s="37"/>
-      <x:c r="M18" s="41" t="str">
+      <x:c r="L18" s="38"/>
+      <x:c r="M18" s="42" t="str">
         <x:f>IF(L18="","",L18-K18)</x:f>
       </x:c>
       <x:c r="N18" s="16"/>
@@ -5530,6 +5862,7 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:N1"/>
     <x:mergeCell ref="A2:N2"/>
+    <x:mergeCell ref="A4:N4"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="E6:E18">
     <x:cfRule type="expression" dxfId="3" priority="1">
@@ -5614,18 +5947,18 @@
       <x:c r="H2" s="8"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="49" t="str">
+      <x:c r="A4" s="51" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="B4" s="49" t="str">
+      <x:c r="B4" s="51" t="str">
         <x:f>IF(COUNTIF(F8:F16,"PASS")=9,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C4" s="49"/>
-      <x:c r="D4" s="49" t="str">
+      <x:c r="C4" s="51"/>
+      <x:c r="D4" s="51" t="str">
         <x:v>LIQUIDITY STATUS</x:v>
       </x:c>
-      <x:c r="E4" s="49" t="str">
+      <x:c r="E4" s="51" t="str">
         <x:f>IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"BELOW BUFFER")&gt;0,"ACTION REQUIRED",IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"WATCH")&gt;0,"WATCH","OK"))</x:f>
         <x:v>ACTION REQUIRED</x:v>
       </x:c>
@@ -5660,19 +5993,19 @@
       <x:c r="A8" s="15" t="str">
         <x:v>Exactly 13 forecast weeks</x:v>
       </x:c>
-      <x:c r="B8" s="50" t="n">
+      <x:c r="B8" s="52" t="n">
         <x:f>COLUMNS('13-Week Forecast'!$B$5:$N$5)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="50" t="n">
+      <x:c r="C8" s="52" t="n">
         <x:f>13</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D8" s="50" t="n">
+      <x:c r="D8" s="52" t="n">
         <x:f>B8-C8</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E8" s="50" t="n">
+      <x:c r="E8" s="52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="15" t="str">
@@ -5690,19 +6023,19 @@
       <x:c r="A9" s="15" t="str">
         <x:v>Forecast starts Monday</x:v>
       </x:c>
-      <x:c r="B9" s="50" t="n">
+      <x:c r="B9" s="52" t="n">
         <x:f>WEEKDAY('Assumptions'!$B$8,2)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C9" s="50" t="n">
+      <x:c r="C9" s="52" t="n">
         <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D9" s="50" t="n">
+      <x:c r="D9" s="52" t="n">
         <x:f>B9-C9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E9" s="50" t="n">
+      <x:c r="E9" s="52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="15" t="str">
@@ -5720,19 +6053,19 @@
       <x:c r="A10" s="15" t="str">
         <x:v>Selected scenario recognised</x:v>
       </x:c>
-      <x:c r="B10" s="50" t="n">
+      <x:c r="B10" s="52" t="n">
         <x:f>COUNTIF('Assumptions'!$B$15:$B$17,'Assumptions'!$B$12)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="50" t="n">
+      <x:c r="C10" s="52" t="n">
         <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D10" s="50" t="n">
+      <x:c r="D10" s="52" t="n">
         <x:f>B10-C10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="50" t="n">
+      <x:c r="E10" s="52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str">
@@ -5750,19 +6083,19 @@
       <x:c r="A11" s="15" t="str">
         <x:v>Week 1 opening cash ties</x:v>
       </x:c>
-      <x:c r="B11" s="51" t="n">
+      <x:c r="B11" s="53" t="n">
         <x:f>'13-Week Forecast'!$B$46</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="C11" s="51" t="n">
+      <x:c r="C11" s="53" t="n">
         <x:f>'Assumptions'!$B$10</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="D11" s="50" t="n">
+      <x:c r="D11" s="52" t="n">
         <x:f>B11-C11</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="50" t="n">
+      <x:c r="E11" s="52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="15" t="str">
@@ -5780,19 +6113,19 @@
       <x:c r="A12" s="15" t="str">
         <x:v>Weekly cash roll-forward equations</x:v>
       </x:c>
-      <x:c r="B12" s="50" t="n">
+      <x:c r="B12" s="52" t="n">
         <x:f>MAX(ABS('13-Week Forecast'!$B$48-'13-Week Forecast'!$B$46-'13-Week Forecast'!$B$47),ABS('13-Week Forecast'!$C$48-'13-Week Forecast'!$C$46-'13-Week Forecast'!$C$47),ABS('13-Week Forecast'!$D$48-'13-Week Forecast'!$D$46-'13-Week Forecast'!$D$47),ABS('13-Week Forecast'!$E$48-'13-Week Forecast'!$E$46-'13-Week Forecast'!$E$47),ABS('13-Week Forecast'!$F$48-'13-Week Forecast'!$F$46-'13-Week Forecast'!$F$47),ABS('13-Week Forecast'!$G$48-'13-Week Forecast'!$G$46-'13-Week Forecast'!$G$47),ABS('13-Week Forecast'!$H$48-'13-Week Forecast'!$H$46-'13-Week Forecast'!$H$47),ABS('13-Week Forecast'!$I$48-'13-Week Forecast'!$I$46-'13-Week Forecast'!$I$47),ABS('13-Week Forecast'!$J$48-'13-Week Forecast'!$J$46-'13-Week Forecast'!$J$47),ABS('13-Week Forecast'!$K$48-'13-Week Forecast'!$K$46-'13-Week Forecast'!$K$47),ABS('13-Week Forecast'!$L$48-'13-Week Forecast'!$L$46-'13-Week Forecast'!$L$47),ABS('13-Week Forecast'!$M$48-'13-Week Forecast'!$M$46-'13-Week Forecast'!$M$47),ABS('13-Week Forecast'!$N$48-'13-Week Forecast'!$N$46-'13-Week Forecast'!$N$47),ABS('13-Week Forecast'!$C$46-'13-Week Forecast'!$B$48),ABS('13-Week Forecast'!$D$46-'13-Week Forecast'!$C$48),ABS('13-Week Forecast'!$E$46-'13-Week Forecast'!$D$48),ABS('13-Week Forecast'!$F$46-'13-Week Forecast'!$E$48),ABS('13-Week Forecast'!$G$46-'13-Week Forecast'!$F$48),ABS('13-Week Forecast'!$H$46-'13-Week Forecast'!$G$48),ABS('13-Week Forecast'!$I$46-'13-Week Forecast'!$H$48),ABS('13-Week Forecast'!$J$46-'13-Week Forecast'!$I$48),ABS('13-Week Forecast'!$K$46-'13-Week Forecast'!$J$48),ABS('13-Week Forecast'!$L$46-'13-Week Forecast'!$K$48),ABS('13-Week Forecast'!$M$46-'13-Week Forecast'!$L$48),ABS('13-Week Forecast'!$N$46-'13-Week Forecast'!$M$48))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C12" s="50" t="n">
+      <x:c r="C12" s="52" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="50" t="n">
+      <x:c r="D12" s="52" t="n">
         <x:f>B12-C12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="50" t="n">
+      <x:c r="E12" s="52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F12" s="15" t="str">
@@ -5810,19 +6143,19 @@
       <x:c r="A13" s="15" t="str">
         <x:v>Cash receipt totals reconcile</x:v>
       </x:c>
-      <x:c r="B13" s="50" t="n">
+      <x:c r="B13" s="52" t="n">
         <x:f>MAX(ABS('13-Week Forecast'!$B$19-SUM('13-Week Forecast'!$B$10:$B$18)),ABS('13-Week Forecast'!$C$19-SUM('13-Week Forecast'!$C$10:$C$18)),ABS('13-Week Forecast'!$D$19-SUM('13-Week Forecast'!$D$10:$D$18)),ABS('13-Week Forecast'!$E$19-SUM('13-Week Forecast'!$E$10:$E$18)),ABS('13-Week Forecast'!$F$19-SUM('13-Week Forecast'!$F$10:$F$18)),ABS('13-Week Forecast'!$G$19-SUM('13-Week Forecast'!$G$10:$G$18)),ABS('13-Week Forecast'!$H$19-SUM('13-Week Forecast'!$H$10:$H$18)),ABS('13-Week Forecast'!$I$19-SUM('13-Week Forecast'!$I$10:$I$18)),ABS('13-Week Forecast'!$J$19-SUM('13-Week Forecast'!$J$10:$J$18)),ABS('13-Week Forecast'!$K$19-SUM('13-Week Forecast'!$K$10:$K$18)),ABS('13-Week Forecast'!$L$19-SUM('13-Week Forecast'!$L$10:$L$18)),ABS('13-Week Forecast'!$M$19-SUM('13-Week Forecast'!$M$10:$M$18)),ABS('13-Week Forecast'!$N$19-SUM('13-Week Forecast'!$N$10:$N$18)))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C13" s="50" t="n">
+      <x:c r="C13" s="52" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="50" t="n">
+      <x:c r="D13" s="52" t="n">
         <x:f>B13-C13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="50" t="n">
+      <x:c r="E13" s="52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F13" s="15" t="str">
@@ -5840,19 +6173,19 @@
       <x:c r="A14" s="15" t="str">
         <x:v>Cash payment totals reconcile</x:v>
       </x:c>
-      <x:c r="B14" s="50" t="n">
+      <x:c r="B14" s="52" t="n">
         <x:f>MAX(ABS('13-Week Forecast'!$B$43-SUM('13-Week Forecast'!$B$22:$B$42)),ABS('13-Week Forecast'!$C$43-SUM('13-Week Forecast'!$C$22:$C$42)),ABS('13-Week Forecast'!$D$43-SUM('13-Week Forecast'!$D$22:$D$42)),ABS('13-Week Forecast'!$E$43-SUM('13-Week Forecast'!$E$22:$E$42)),ABS('13-Week Forecast'!$F$43-SUM('13-Week Forecast'!$F$22:$F$42)),ABS('13-Week Forecast'!$G$43-SUM('13-Week Forecast'!$G$22:$G$42)),ABS('13-Week Forecast'!$H$43-SUM('13-Week Forecast'!$H$22:$H$42)),ABS('13-Week Forecast'!$I$43-SUM('13-Week Forecast'!$I$22:$I$42)),ABS('13-Week Forecast'!$J$43-SUM('13-Week Forecast'!$J$22:$J$42)),ABS('13-Week Forecast'!$K$43-SUM('13-Week Forecast'!$K$22:$K$42)),ABS('13-Week Forecast'!$L$43-SUM('13-Week Forecast'!$L$22:$L$42)),ABS('13-Week Forecast'!$M$43-SUM('13-Week Forecast'!$M$22:$M$42)),ABS('13-Week Forecast'!$N$43-SUM('13-Week Forecast'!$N$22:$N$42)))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C14" s="50" t="n">
+      <x:c r="C14" s="52" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="50" t="n">
+      <x:c r="D14" s="52" t="n">
         <x:f>B14-C14</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="50" t="n">
+      <x:c r="E14" s="52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="15" t="str">
@@ -5870,19 +6203,19 @@
       <x:c r="A15" s="15" t="str">
         <x:v>Week 13 closing cash equation</x:v>
       </x:c>
-      <x:c r="B15" s="51" t="n">
+      <x:c r="B15" s="53" t="n">
         <x:f>'13-Week Forecast'!$N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="C15" s="51" t="n">
+      <x:c r="C15" s="53" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!$B$47:$N$47)</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D15" s="50" t="n">
+      <x:c r="D15" s="52" t="n">
         <x:f>B15-C15</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="50" t="n">
+      <x:c r="E15" s="52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F15" s="15" t="str">
@@ -5900,19 +6233,19 @@
       <x:c r="A16" s="15" t="str">
         <x:v>Formula-error count</x:v>
       </x:c>
-      <x:c r="B16" s="50" t="n">
-        <x:f>SUMPRODUCT(--ISERROR('Assumptions'!$B$5:$D$17))+SUMPRODUCT(--ISERROR('13-Week Forecast'!$B$5:$O$51))+SUMPRODUCT(--ISERROR('Weekly Review'!$A$5:$N$18))+SUMPRODUCT(--ISERROR('Dashboard'!$A$6:$J$24))+SUMPRODUCT(--ISERROR('Dashboard'!$P$4:$R$34))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="50" t="n">
+      <x:c r="B16" s="52" t="n">
+        <x:f>SUMPRODUCT(--ISERROR('Assumptions'!$B$5:$E$19))+SUMPRODUCT(--ISERROR('13-Week Forecast'!$B$5:$O$51))+SUMPRODUCT(--ISERROR('Weekly Review'!$A$4:$N$18))+SUMPRODUCT(--ISERROR('Dashboard'!$A$6:$J$30))+SUMPRODUCT(--ISERROR('Dashboard'!$P$4:$S$49))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="52" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="50" t="n">
+      <x:c r="D16" s="52" t="n">
         <x:f>B16-C16</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="50" t="n">
+      <x:c r="E16" s="52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="15" t="str">
@@ -5947,136 +6280,136 @@
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="53" t="str">
+      <x:c r="A22" s="55" t="str">
         <x:v>GST standard rate</x:v>
       </x:c>
-      <x:c r="B22" s="54" t="str">
+      <x:c r="B22" s="56" t="str">
         <x:v>https://www.legislation.gov.au/C2004A00446/latest/text</x:v>
       </x:c>
-      <x:c r="C22" s="53" t="str">
+      <x:c r="C22" s="55" t="str">
         <x:v>GST default: 10% of the value of a taxable supply.</x:v>
       </x:c>
-      <x:c r="D22" s="53" t="str">
+      <x:c r="D22" s="55" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E22" s="53" t="str">
+      <x:c r="E22" s="55" t="str">
         <x:v>The 10% default does not decide whether a transaction is taxable, GST-free, input taxed or outside the GST system.</x:v>
       </x:c>
-      <x:c r="F22" s="53" t="str">
+      <x:c r="F22" s="55" t="str">
         <x:v>Keep tax classifications user-confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="53" t="str">
+      <x:c r="A23" s="55" t="str">
         <x:v>BAS due dates</x:v>
       </x:c>
-      <x:c r="B23" s="54" t="str">
+      <x:c r="B23" s="56" t="str">
         <x:v>https://www.ato.gov.au/businesses-and-organisations/preparing-lodging-and-paying/business-activity-statements-bas/due-dates-for-lodging-and-paying-your-bas</x:v>
       </x:c>
-      <x:c r="C23" s="53" t="str">
+      <x:c r="C23" s="55" t="str">
         <x:v>Monthly BAS planning pattern is generally the 21st day after the taxable period; quarterly dates are planning patterns only.</x:v>
       </x:c>
-      <x:c r="D23" s="53" t="str">
+      <x:c r="D23" s="55" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E23" s="53" t="str">
+      <x:c r="E23" s="55" t="str">
         <x:v>The issued or entity-specific BAS due date controls. Online lodgement, registered-agent arrangements, holidays and entity circumstances can change the date.</x:v>
       </x:c>
-      <x:c r="F23" s="53" t="str">
+      <x:c r="F23" s="55" t="str">
         <x:v>Use issued BAS and user-entered dates.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="53" t="str">
+      <x:c r="A24" s="55" t="str">
         <x:v>PAYG withholding</x:v>
       </x:c>
-      <x:c r="B24" s="54" t="str">
+      <x:c r="B24" s="56" t="str">
         <x:v>https://www.ato.gov.au/businesses-and-organisations/hiring-and-paying-your-workers/payg-withholding</x:v>
       </x:c>
-      <x:c r="C24" s="53" t="str">
+      <x:c r="C24" s="55" t="str">
         <x:v>PAYG withholding payment and reporting due dates vary with business size and circumstances.</x:v>
       </x:c>
-      <x:c r="D24" s="53" t="str">
+      <x:c r="D24" s="55" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E24" s="53" t="str">
+      <x:c r="E24" s="55" t="str">
         <x:v>Confirm the applicable due date for the entity and reporting cycle.</x:v>
       </x:c>
-      <x:c r="F24" s="53" t="str">
+      <x:c r="F24" s="55" t="str">
         <x:v>Keep payment dates user-entered and confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="53" t="str">
+      <x:c r="A25" s="55" t="str">
         <x:v>Super guarantee</x:v>
       </x:c>
-      <x:c r="B25" s="54" t="str">
+      <x:c r="B25" s="56" t="str">
         <x:v>https://www.ato.gov.au/tax-rates-and-codes/key-superannuation-rates-and-thresholds/super-guarantee</x:v>
       </x:c>
-      <x:c r="C25" s="53" t="str">
+      <x:c r="C25" s="55" t="str">
         <x:v>Default SG rate: 12.0% from 1 July 2025, including 1 July 2026 to 30 June 2027.</x:v>
       </x:c>
-      <x:c r="D25" s="53" t="str">
+      <x:c r="D25" s="55" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E25" s="53" t="str">
+      <x:c r="E25" s="55" t="str">
         <x:v>Apply only after checking worker eligibility, earnings base and special rules.</x:v>
       </x:c>
-      <x:c r="F25" s="53" t="str">
+      <x:c r="F25" s="55" t="str">
         <x:v>Weekly super is illustrative FP&amp;A input.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="53" t="str">
+      <x:c r="A26" s="55" t="str">
         <x:v>Payday Super</x:v>
       </x:c>
-      <x:c r="B26" s="54" t="str">
+      <x:c r="B26" s="56" t="str">
         <x:v>https://softwaredevelopers.ato.gov.au/PaydaySuper</x:v>
       </x:c>
-      <x:c r="C26" s="53" t="str">
+      <x:c r="C26" s="55" t="str">
         <x:v>From 1 July 2026, pay SG with each pay cycle. The fund must generally receive it by the seventh business day after payday.</x:v>
       </x:c>
-      <x:c r="D26" s="53" t="str">
+      <x:c r="D26" s="55" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E26" s="53" t="str">
+      <x:c r="E26" s="55" t="str">
         <x:v>Fund receipt, not employer submission, is the statutory timing anchor. Allow for eligible longer periods.</x:v>
       </x:c>
-      <x:c r="F26" s="53" t="str">
+      <x:c r="F26" s="55" t="str">
         <x:v>Illustrative forecast starts after the July 2026 transition.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="56" t="str">
+      <x:c r="A28" s="58" t="str">
         <x:v>Disclaimer: Illustrative FP&amp;A cash-planning model only. Statutory amounts and dates are indicative assumptions, not tax, BAS, payroll, superannuation or legal advice. Entity-specific lodgement dates and tax classifications must be confirmed by the user or adviser before relying on the model or lodging or paying.</x:v>
       </x:c>
-      <x:c r="B28" s="56"/>
-      <x:c r="C28" s="56"/>
-      <x:c r="D28" s="56"/>
-      <x:c r="E28" s="56"/>
-      <x:c r="F28" s="56"/>
-      <x:c r="G28" s="56"/>
-      <x:c r="H28" s="56"/>
+      <x:c r="B28" s="58"/>
+      <x:c r="C28" s="58"/>
+      <x:c r="D28" s="58"/>
+      <x:c r="E28" s="58"/>
+      <x:c r="F28" s="58"/>
+      <x:c r="G28" s="58"/>
+      <x:c r="H28" s="58"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="56"/>
-      <x:c r="B29" s="56"/>
-      <x:c r="C29" s="56"/>
-      <x:c r="D29" s="56"/>
-      <x:c r="E29" s="56"/>
-      <x:c r="F29" s="56"/>
-      <x:c r="G29" s="56"/>
-      <x:c r="H29" s="56"/>
+      <x:c r="A29" s="58"/>
+      <x:c r="B29" s="58"/>
+      <x:c r="C29" s="58"/>
+      <x:c r="D29" s="58"/>
+      <x:c r="E29" s="58"/>
+      <x:c r="F29" s="58"/>
+      <x:c r="G29" s="58"/>
+      <x:c r="H29" s="58"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="56"/>
-      <x:c r="B30" s="56"/>
-      <x:c r="C30" s="56"/>
-      <x:c r="D30" s="56"/>
-      <x:c r="E30" s="56"/>
-      <x:c r="F30" s="56"/>
-      <x:c r="G30" s="56"/>
-      <x:c r="H30" s="56"/>
+      <x:c r="A30" s="58"/>
+      <x:c r="B30" s="58"/>
+      <x:c r="C30" s="58"/>
+      <x:c r="D30" s="58"/>
+      <x:c r="E30" s="58"/>
+      <x:c r="F30" s="58"/>
+      <x:c r="G30" s="58"/>
+      <x:c r="H30" s="58"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R4d44442af84142eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R6fecb1a629ca4327"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R91bf2385bb964313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rd2cfaf2133b94566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R906f3a99a7484e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="Ra98aead422a1451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rb46856e0cd274e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Rf51f7fc7c7ac4703"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R09e2d2a5fbda4d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rdff7daedb25c448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="Rda7868aea9f24915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R3349cf15cb6b4e86"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -20,10 +20,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={911808D7-7490-7273-81DF-52B18E6A0026}</x:author>
-    <x:author>tc={3CE89642-A655-41DD-1FA6-DE53C860A290}</x:author>
-    <x:author>tc={39CDC10E-89CD-355E-05E8-C2A4AA6F0BB9}</x:author>
-    <x:author>tc={1C0A15C3-71DD-065B-05EE-065A18D44E19}</x:author>
+    <x:author>tc={84D266F6-19BA-B47D-5D1E-5574E3244C5E}</x:author>
+    <x:author>tc={EB8A6292-8349-BCED-0B6A-820E09C1CE7C}</x:author>
+    <x:author>tc={F2C7C3A4-FBBA-3A12-EE58-6838DD9AE503}</x:author>
+    <x:author>tc={72F653C9-5555-6279-61F6-5B5AB1783FF8}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -83,7 +83,7 @@
     <x:numFmt numFmtId="203" formatCode="0"/>
     <x:numFmt numFmtId="204" formatCode="#,##0;[Red](#,##0);-"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -97,7 +97,7 @@
       <x:b/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Aptos Display"/>
+      <x:name val="Aptos"/>
     </x:font>
     <x:font>
       <x:sz val="10"/>
@@ -157,6 +157,10 @@
       <x:b/>
       <x:sz val="12"/>
       <x:color rgb="FF04001F"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
@@ -229,7 +233,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="71">
+  <x:cellXfs count="77">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -347,6 +351,18 @@
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1022,7 +1038,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdb280384cd224945"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8d359760a76540fd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1052,7 +1068,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R67d1bcb11ae843fc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R85f1f962974a472b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1063,7 +1079,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}"/>
+  <xltc:person displayName="User" id="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}"/>
 </xltc:personList>
 </file>
 
@@ -1260,16 +1276,16 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-26T16:49:11.841" personId="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}" id="{911808D7-7490-7273-81DF-52B18E6A0026}">
+  <xltc:threadedComment ref="B18" dT="2026-08-26T17:04:38.821" personId="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}" id="{84D266F6-19BA-B47D-5D1E-5574E3244C5E}">
     <xltc:text>Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B42" dT="2026-08-26T16:49:11.842" personId="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}" id="{3CE89642-A655-41DD-1FA6-DE53C860A290}">
+  <xltc:threadedComment ref="B42" dT="2026-08-26T17:04:38.821" personId="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}" id="{EB8A6292-8349-BCED-0B6A-820E09C1CE7C}">
     <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B34" dT="2026-08-26T16:49:11.842" personId="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}" id="{39CDC10E-89CD-355E-05E8-C2A4AA6F0BB9}">
+  <xltc:threadedComment ref="B34" dT="2026-08-26T17:04:38.821" personId="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}" id="{F2C7C3A4-FBBA-3A12-EE58-6838DD9AE503}">
     <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B35" dT="2026-08-26T16:49:11.842" personId="{4E5C786D-4D85-4AFA-B2CD-21FAF79CB976}" id="{1C0A15C3-71DD-065B-05EE-065A18D44E19}">
+  <xltc:threadedComment ref="B35" dT="2026-08-26T17:04:38.821" personId="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}" id="{72F653C9-5555-6279-61F6-5B5AB1783FF8}">
     <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -1313,6 +1329,16 @@
       <x:c r="G2" s="8"/>
       <x:c r="H2" s="8"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="71"/>
+      <x:c r="B3" s="71"/>
+      <x:c r="C3" s="71"/>
+      <x:c r="D3" s="71"/>
+      <x:c r="E3" s="71"/>
+      <x:c r="F3" s="71"/>
+      <x:c r="G3" s="71"/>
+      <x:c r="H3" s="71"/>
+    </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="str">
         <x:v>ILLUSTRATIVE DATA | Replace every blue input with your organisation's current cash-flow assumptions.</x:v>
@@ -1325,13 +1351,24 @@
       <x:c r="G4" s="10"/>
       <x:c r="H4" s="10"/>
     </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="71"/>
+      <x:c r="B5" s="71"/>
+      <x:c r="C5" s="71"/>
+      <x:c r="D5" s="71"/>
+      <x:c r="E5" s="71"/>
+      <x:c r="F5" s="71"/>
+      <x:c r="G5" s="71"/>
+      <x:c r="H5" s="71"/>
+    </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
+      <x:c r="A6" s="71" t="str">
         <x:v>Version</x:v>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="B6" s="71" t="str">
         <x:v>Release 1.1</x:v>
       </x:c>
+      <x:c r="C6" s="71"/>
       <x:c r="D6" s="23" t="str">
         <x:v>Workbook sheets</x:v>
       </x:c>
@@ -1341,54 +1378,81 @@
       <x:c r="H6" s="23"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
+      <x:c r="A7" s="71" t="str">
         <x:v>Prepared date</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="n">
+      <x:c r="B7" s="72" t="n">
         <x:v>46260</x:v>
       </x:c>
+      <x:c r="C7" s="71"/>
       <x:c r="D7" s="1" t="str">
         <x:v>Dashboard</x:v>
       </x:c>
+      <x:c r="E7" s="71"/>
+      <x:c r="F7" s="71"/>
+      <x:c r="G7" s="71"/>
+      <x:c r="H7" s="71"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
+      <x:c r="A8" s="71" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="B8" s="71" t="str">
         <x:v>AUD</x:v>
       </x:c>
+      <x:c r="C8" s="71"/>
       <x:c r="D8" s="1" t="str">
         <x:v>Assumptions</x:v>
       </x:c>
+      <x:c r="E8" s="71"/>
+      <x:c r="F8" s="71"/>
+      <x:c r="G8" s="71"/>
+      <x:c r="H8" s="71"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
+      <x:c r="A9" s="71" t="str">
         <x:v>Units</x:v>
       </x:c>
-      <x:c r="B9" t="str">
+      <x:c r="B9" s="71" t="str">
         <x:v>Whole dollars</x:v>
       </x:c>
+      <x:c r="C9" s="71"/>
       <x:c r="D9" s="1" t="str">
         <x:v>13-Week Forecast</x:v>
       </x:c>
+      <x:c r="E9" s="71"/>
+      <x:c r="F9" s="71"/>
+      <x:c r="G9" s="71"/>
+      <x:c r="H9" s="71"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
+      <x:c r="A10" s="71" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
         <x:f>'Assumptions'!$B$12</x:f>
         <x:v>Base</x:v>
       </x:c>
+      <x:c r="C10" s="71"/>
       <x:c r="D10" s="1" t="str">
         <x:v>Weekly Review</x:v>
       </x:c>
+      <x:c r="E10" s="71"/>
+      <x:c r="F10" s="71"/>
+      <x:c r="G10" s="71"/>
+      <x:c r="H10" s="71"/>
     </x:row>
     <x:row r="11">
+      <x:c r="A11" s="71"/>
+      <x:c r="B11" s="71"/>
+      <x:c r="C11" s="71"/>
       <x:c r="D11" s="1" t="str">
         <x:v>Checks &amp; Sources</x:v>
       </x:c>
+      <x:c r="E11" s="71"/>
+      <x:c r="F11" s="71"/>
+      <x:c r="G11" s="71"/>
+      <x:c r="H11" s="71"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
@@ -1403,44 +1467,84 @@
       <x:c r="H12" s="14"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="str">
+      <x:c r="A13" s="71" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B13" s="15" t="str">
+      <x:c r="B13" s="73" t="str">
         <x:v>Update the Assumptions control panel and selected scenario.</x:v>
       </x:c>
+      <x:c r="C13" s="71"/>
+      <x:c r="D13" s="71"/>
+      <x:c r="E13" s="71"/>
+      <x:c r="F13" s="71"/>
+      <x:c r="G13" s="71"/>
+      <x:c r="H13" s="71"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="str">
+      <x:c r="A14" s="71" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B14" s="15" t="str">
+      <x:c r="B14" s="73" t="str">
         <x:v>Replace blue cash-receipt and cash-payment inputs with the latest weekly view.</x:v>
       </x:c>
+      <x:c r="C14" s="71"/>
+      <x:c r="D14" s="71"/>
+      <x:c r="E14" s="71"/>
+      <x:c r="F14" s="71"/>
+      <x:c r="G14" s="71"/>
+      <x:c r="H14" s="71"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="str">
+      <x:c r="A15" s="71" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B15" s="15" t="str">
+      <x:c r="B15" s="73" t="str">
         <x:v>Review closing cash, headroom and liquidity status in the 13-Week Forecast.</x:v>
       </x:c>
+      <x:c r="C15" s="71"/>
+      <x:c r="D15" s="71"/>
+      <x:c r="E15" s="71"/>
+      <x:c r="F15" s="71"/>
+      <x:c r="G15" s="71"/>
+      <x:c r="H15" s="71"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="str">
+      <x:c r="A16" s="71" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B16" s="15" t="str">
+      <x:c r="B16" s="73" t="str">
         <x:v>Snapshot the original forecast as values, then record actuals and owner commentary in Weekly Review.</x:v>
       </x:c>
+      <x:c r="C16" s="71"/>
+      <x:c r="D16" s="71"/>
+      <x:c r="E16" s="71"/>
+      <x:c r="F16" s="71"/>
+      <x:c r="G16" s="71"/>
+      <x:c r="H16" s="71"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
+      <x:c r="A17" s="71" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B17" s="15" t="str">
+      <x:c r="B17" s="73" t="str">
         <x:v>Resolve any control failure in Checks &amp; Sources before management review.</x:v>
       </x:c>
+      <x:c r="C17" s="71"/>
+      <x:c r="D17" s="71"/>
+      <x:c r="E17" s="71"/>
+      <x:c r="F17" s="71"/>
+      <x:c r="G17" s="71"/>
+      <x:c r="H17" s="71"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="71"/>
+      <x:c r="B18" s="71"/>
+      <x:c r="C18" s="71"/>
+      <x:c r="D18" s="71"/>
+      <x:c r="E18" s="71"/>
+      <x:c r="F18" s="71"/>
+      <x:c r="G18" s="71"/>
+      <x:c r="H18" s="71"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14" t="str">
@@ -1458,41 +1562,91 @@
       <x:c r="A20" s="16" t="str">
         <x:v>Blue text / lavender fill</x:v>
       </x:c>
-      <x:c r="B20" t="str">
+      <x:c r="B20" s="71" t="str">
         <x:v>Editable user input</x:v>
       </x:c>
+      <x:c r="C20" s="71"/>
+      <x:c r="D20" s="71"/>
+      <x:c r="E20" s="71"/>
+      <x:c r="F20" s="71"/>
+      <x:c r="G20" s="71"/>
+      <x:c r="H20" s="71"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="17" t="str">
         <x:v>Black text</x:v>
       </x:c>
-      <x:c r="B21" t="str">
+      <x:c r="B21" s="71" t="str">
         <x:v>Formula or calculation</x:v>
       </x:c>
+      <x:c r="C21" s="71"/>
+      <x:c r="D21" s="71"/>
+      <x:c r="E21" s="71"/>
+      <x:c r="F21" s="71"/>
+      <x:c r="G21" s="71"/>
+      <x:c r="H21" s="71"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="12" t="str">
         <x:v>Green text</x:v>
       </x:c>
-      <x:c r="B22" t="str">
+      <x:c r="B22" s="71" t="str">
         <x:v>Cross-sheet link</x:v>
       </x:c>
+      <x:c r="C22" s="71"/>
+      <x:c r="D22" s="71"/>
+      <x:c r="E22" s="71"/>
+      <x:c r="F22" s="71"/>
+      <x:c r="G22" s="71"/>
+      <x:c r="H22" s="71"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="19" t="str">
         <x:v>Red text / pale-red fill</x:v>
       </x:c>
-      <x:c r="B23" t="str">
+      <x:c r="B23" s="71" t="str">
         <x:v>Warning or exception</x:v>
       </x:c>
+      <x:c r="C23" s="71"/>
+      <x:c r="D23" s="71"/>
+      <x:c r="E23" s="71"/>
+      <x:c r="F23" s="71"/>
+      <x:c r="G23" s="71"/>
+      <x:c r="H23" s="71"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21" t="str">
         <x:v>Dark green / pale-green fill</x:v>
       </x:c>
-      <x:c r="B24" t="str">
+      <x:c r="B24" s="71" t="str">
         <x:v>Passing check</x:v>
       </x:c>
+      <x:c r="C24" s="71"/>
+      <x:c r="D24" s="71"/>
+      <x:c r="E24" s="71"/>
+      <x:c r="F24" s="71"/>
+      <x:c r="G24" s="71"/>
+      <x:c r="H24" s="71"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="71"/>
+      <x:c r="B25" s="71"/>
+      <x:c r="C25" s="71"/>
+      <x:c r="D25" s="71"/>
+      <x:c r="E25" s="71"/>
+      <x:c r="F25" s="71"/>
+      <x:c r="G25" s="71"/>
+      <x:c r="H25" s="71"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="71"/>
+      <x:c r="B26" s="71"/>
+      <x:c r="C26" s="71"/>
+      <x:c r="D26" s="71"/>
+      <x:c r="E26" s="71"/>
+      <x:c r="F26" s="71"/>
+      <x:c r="G26" s="71"/>
+      <x:c r="H26" s="71"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="27" t="str">
@@ -1598,6 +1752,27 @@
       <x:c r="R2" s="8"/>
       <x:c r="S2" s="8"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="71"/>
+      <x:c r="B3" s="71"/>
+      <x:c r="C3" s="71"/>
+      <x:c r="D3" s="71"/>
+      <x:c r="E3" s="71"/>
+      <x:c r="F3" s="71"/>
+      <x:c r="G3" s="71"/>
+      <x:c r="H3" s="71"/>
+      <x:c r="I3" s="71"/>
+      <x:c r="J3" s="71"/>
+      <x:c r="K3" s="71"/>
+      <x:c r="L3" s="71"/>
+      <x:c r="M3" s="71"/>
+      <x:c r="N3" s="71"/>
+      <x:c r="O3" s="71"/>
+      <x:c r="P3" s="71"/>
+      <x:c r="Q3" s="71"/>
+      <x:c r="R3" s="71"/>
+      <x:c r="S3" s="71"/>
+    </x:row>
     <x:row r="4">
       <x:c r="A4" s="25" t="str">
         <x:v>No cash-flow inputs belong on this sheet. Update Assumptions and the 13-Week Forecast instead.</x:v>
@@ -1625,20 +1800,37 @@
       <x:c r="R4" s="14" t="str">
         <x:v>Minimum buffer</x:v>
       </x:c>
+      <x:c r="S4" s="71"/>
     </x:row>
     <x:row r="5">
-      <x:c r="P5" s="11" t="str">
+      <x:c r="A5" s="71"/>
+      <x:c r="B5" s="71"/>
+      <x:c r="C5" s="71"/>
+      <x:c r="D5" s="71"/>
+      <x:c r="E5" s="71"/>
+      <x:c r="F5" s="71"/>
+      <x:c r="G5" s="71"/>
+      <x:c r="H5" s="71"/>
+      <x:c r="I5" s="71"/>
+      <x:c r="J5" s="71"/>
+      <x:c r="K5" s="71"/>
+      <x:c r="L5" s="71"/>
+      <x:c r="M5" s="71"/>
+      <x:c r="N5" s="71"/>
+      <x:c r="O5" s="71"/>
+      <x:c r="P5" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
         <x:v>06 Sep</x:v>
       </x:c>
-      <x:c r="Q5" s="39" t="n">
+      <x:c r="Q5" s="74" t="n">
         <x:f>'13-Week Forecast'!B$48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="R5" s="39" t="n">
+      <x:c r="R5" s="74" t="n">
         <x:f>'13-Week Forecast'!B$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S5" s="71"/>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="60" t="str">
@@ -1671,18 +1863,24 @@
       <x:c r="J6" s="60" t="str">
         <x:v>LIQUIDITY STATUS</x:v>
       </x:c>
-      <x:c r="P6" s="11" t="str">
+      <x:c r="K6" s="71"/>
+      <x:c r="L6" s="71"/>
+      <x:c r="M6" s="71"/>
+      <x:c r="N6" s="71"/>
+      <x:c r="O6" s="71"/>
+      <x:c r="P6" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
         <x:v>13 Sep</x:v>
       </x:c>
-      <x:c r="Q6" s="39" t="n">
+      <x:c r="Q6" s="74" t="n">
         <x:f>'13-Week Forecast'!C$48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="R6" s="39" t="n">
+      <x:c r="R6" s="74" t="n">
         <x:f>'13-Week Forecast'!C$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S6" s="71"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="63" t="str">
@@ -1725,32 +1923,54 @@
         <x:f>'Checks &amp; Sources'!$E$4</x:f>
         <x:v>ACTION REQUIRED</x:v>
       </x:c>
-      <x:c r="P7" s="11" t="str">
+      <x:c r="K7" s="71"/>
+      <x:c r="L7" s="71"/>
+      <x:c r="M7" s="71"/>
+      <x:c r="N7" s="71"/>
+      <x:c r="O7" s="71"/>
+      <x:c r="P7" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
         <x:v>20 Sep</x:v>
       </x:c>
-      <x:c r="Q7" s="39" t="n">
+      <x:c r="Q7" s="74" t="n">
         <x:f>'13-Week Forecast'!D$48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="R7" s="39" t="n">
+      <x:c r="R7" s="74" t="n">
         <x:f>'13-Week Forecast'!D$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S7" s="71"/>
     </x:row>
     <x:row r="8">
-      <x:c r="P8" s="11" t="str">
+      <x:c r="A8" s="71"/>
+      <x:c r="B8" s="71"/>
+      <x:c r="C8" s="71"/>
+      <x:c r="D8" s="71"/>
+      <x:c r="E8" s="71"/>
+      <x:c r="F8" s="71"/>
+      <x:c r="G8" s="71"/>
+      <x:c r="H8" s="71"/>
+      <x:c r="I8" s="71"/>
+      <x:c r="J8" s="71"/>
+      <x:c r="K8" s="71"/>
+      <x:c r="L8" s="71"/>
+      <x:c r="M8" s="71"/>
+      <x:c r="N8" s="71"/>
+      <x:c r="O8" s="71"/>
+      <x:c r="P8" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
         <x:v>27 Sep</x:v>
       </x:c>
-      <x:c r="Q8" s="39" t="n">
+      <x:c r="Q8" s="74" t="n">
         <x:f>'13-Week Forecast'!E$48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="R8" s="39" t="n">
+      <x:c r="R8" s="74" t="n">
         <x:f>'13-Week Forecast'!E$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S8" s="71"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="59" t="str">
@@ -1765,18 +1985,30 @@
       <x:c r="D9" s="59" t="str">
         <x:v>Action deadline</x:v>
       </x:c>
-      <x:c r="P9" s="11" t="str">
+      <x:c r="E9" s="71"/>
+      <x:c r="F9" s="71"/>
+      <x:c r="G9" s="71"/>
+      <x:c r="H9" s="71"/>
+      <x:c r="I9" s="71"/>
+      <x:c r="J9" s="71"/>
+      <x:c r="K9" s="71"/>
+      <x:c r="L9" s="71"/>
+      <x:c r="M9" s="71"/>
+      <x:c r="N9" s="71"/>
+      <x:c r="O9" s="71"/>
+      <x:c r="P9" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
         <x:v>04 Oct</x:v>
       </x:c>
-      <x:c r="Q9" s="39" t="n">
+      <x:c r="Q9" s="74" t="n">
         <x:f>'13-Week Forecast'!F$48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="R9" s="39" t="n">
+      <x:c r="R9" s="74" t="n">
         <x:f>'13-Week Forecast'!F$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S9" s="71"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="68" t="n">
@@ -1795,18 +2027,30 @@
         <x:f>IF(A10="None","None",A10-7*'Assumptions'!$B$19)</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="P10" s="11" t="str">
+      <x:c r="E10" s="71"/>
+      <x:c r="F10" s="71"/>
+      <x:c r="G10" s="71"/>
+      <x:c r="H10" s="71"/>
+      <x:c r="I10" s="71"/>
+      <x:c r="J10" s="71"/>
+      <x:c r="K10" s="71"/>
+      <x:c r="L10" s="71"/>
+      <x:c r="M10" s="71"/>
+      <x:c r="N10" s="71"/>
+      <x:c r="O10" s="71"/>
+      <x:c r="P10" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
         <x:v>11 Oct</x:v>
       </x:c>
-      <x:c r="Q10" s="39" t="n">
+      <x:c r="Q10" s="74" t="n">
         <x:f>'13-Week Forecast'!G$48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="R10" s="39" t="n">
+      <x:c r="R10" s="74" t="n">
         <x:f>'13-Week Forecast'!G$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S10" s="71"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
@@ -1824,21 +2068,32 @@
       <x:c r="E11" s="14" t="str">
         <x:v>Liquidity status</x:v>
       </x:c>
-      <x:c r="P11" s="11" t="str">
+      <x:c r="F11" s="71"/>
+      <x:c r="G11" s="71"/>
+      <x:c r="H11" s="71"/>
+      <x:c r="I11" s="71"/>
+      <x:c r="J11" s="71"/>
+      <x:c r="K11" s="71"/>
+      <x:c r="L11" s="71"/>
+      <x:c r="M11" s="71"/>
+      <x:c r="N11" s="71"/>
+      <x:c r="O11" s="71"/>
+      <x:c r="P11" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
         <x:v>18 Oct</x:v>
       </x:c>
-      <x:c r="Q11" s="39" t="n">
+      <x:c r="Q11" s="74" t="n">
         <x:f>'13-Week Forecast'!H$48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="R11" s="39" t="n">
+      <x:c r="R11" s="74" t="n">
         <x:f>'13-Week Forecast'!H$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S11" s="71"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="n">
+      <x:c r="A12" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -1858,21 +2113,32 @@
         <x:f>'13-Week Forecast'!B$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="P12" s="11" t="str">
+      <x:c r="F12" s="71"/>
+      <x:c r="G12" s="71"/>
+      <x:c r="H12" s="71"/>
+      <x:c r="I12" s="71"/>
+      <x:c r="J12" s="71"/>
+      <x:c r="K12" s="71"/>
+      <x:c r="L12" s="71"/>
+      <x:c r="M12" s="71"/>
+      <x:c r="N12" s="71"/>
+      <x:c r="O12" s="71"/>
+      <x:c r="P12" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
         <x:v>25 Oct</x:v>
       </x:c>
-      <x:c r="Q12" s="39" t="n">
+      <x:c r="Q12" s="74" t="n">
         <x:f>'13-Week Forecast'!I$48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="R12" s="39" t="n">
+      <x:c r="R12" s="74" t="n">
         <x:f>'13-Week Forecast'!I$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S12" s="71"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="n">
+      <x:c r="A13" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>2</x:v>
       </x:c>
@@ -1892,21 +2158,32 @@
         <x:f>'13-Week Forecast'!C$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="P13" s="11" t="str">
+      <x:c r="F13" s="71"/>
+      <x:c r="G13" s="71"/>
+      <x:c r="H13" s="71"/>
+      <x:c r="I13" s="71"/>
+      <x:c r="J13" s="71"/>
+      <x:c r="K13" s="71"/>
+      <x:c r="L13" s="71"/>
+      <x:c r="M13" s="71"/>
+      <x:c r="N13" s="71"/>
+      <x:c r="O13" s="71"/>
+      <x:c r="P13" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
         <x:v>01 Nov</x:v>
       </x:c>
-      <x:c r="Q13" s="39" t="n">
+      <x:c r="Q13" s="74" t="n">
         <x:f>'13-Week Forecast'!J$48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="R13" s="39" t="n">
+      <x:c r="R13" s="74" t="n">
         <x:f>'13-Week Forecast'!J$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S13" s="71"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="n">
+      <x:c r="A14" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -1926,21 +2203,32 @@
         <x:f>'13-Week Forecast'!D$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="P14" s="11" t="str">
+      <x:c r="F14" s="71"/>
+      <x:c r="G14" s="71"/>
+      <x:c r="H14" s="71"/>
+      <x:c r="I14" s="71"/>
+      <x:c r="J14" s="71"/>
+      <x:c r="K14" s="71"/>
+      <x:c r="L14" s="71"/>
+      <x:c r="M14" s="71"/>
+      <x:c r="N14" s="71"/>
+      <x:c r="O14" s="71"/>
+      <x:c r="P14" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
         <x:v>08 Nov</x:v>
       </x:c>
-      <x:c r="Q14" s="39" t="n">
+      <x:c r="Q14" s="74" t="n">
         <x:f>'13-Week Forecast'!K$48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="R14" s="39" t="n">
+      <x:c r="R14" s="74" t="n">
         <x:f>'13-Week Forecast'!K$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S14" s="71"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="n">
+      <x:c r="A15" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>4</x:v>
       </x:c>
@@ -1960,21 +2248,32 @@
         <x:f>'13-Week Forecast'!E$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="P15" s="11" t="str">
+      <x:c r="F15" s="71"/>
+      <x:c r="G15" s="71"/>
+      <x:c r="H15" s="71"/>
+      <x:c r="I15" s="71"/>
+      <x:c r="J15" s="71"/>
+      <x:c r="K15" s="71"/>
+      <x:c r="L15" s="71"/>
+      <x:c r="M15" s="71"/>
+      <x:c r="N15" s="71"/>
+      <x:c r="O15" s="71"/>
+      <x:c r="P15" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
         <x:v>15 Nov</x:v>
       </x:c>
-      <x:c r="Q15" s="39" t="n">
+      <x:c r="Q15" s="74" t="n">
         <x:f>'13-Week Forecast'!L$48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="R15" s="39" t="n">
+      <x:c r="R15" s="74" t="n">
         <x:f>'13-Week Forecast'!L$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S15" s="71"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="n">
+      <x:c r="A16" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>5</x:v>
       </x:c>
@@ -1994,21 +2293,32 @@
         <x:f>'13-Week Forecast'!F$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="P16" s="11" t="str">
+      <x:c r="F16" s="71"/>
+      <x:c r="G16" s="71"/>
+      <x:c r="H16" s="71"/>
+      <x:c r="I16" s="71"/>
+      <x:c r="J16" s="71"/>
+      <x:c r="K16" s="71"/>
+      <x:c r="L16" s="71"/>
+      <x:c r="M16" s="71"/>
+      <x:c r="N16" s="71"/>
+      <x:c r="O16" s="71"/>
+      <x:c r="P16" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
         <x:v>22 Nov</x:v>
       </x:c>
-      <x:c r="Q16" s="39" t="n">
+      <x:c r="Q16" s="74" t="n">
         <x:f>'13-Week Forecast'!M$48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="R16" s="39" t="n">
+      <x:c r="R16" s="74" t="n">
         <x:f>'13-Week Forecast'!M$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S16" s="71"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="n">
+      <x:c r="A17" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>6</x:v>
       </x:c>
@@ -2028,21 +2338,32 @@
         <x:f>'13-Week Forecast'!G$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="P17" s="11" t="str">
+      <x:c r="F17" s="71"/>
+      <x:c r="G17" s="71"/>
+      <x:c r="H17" s="71"/>
+      <x:c r="I17" s="71"/>
+      <x:c r="J17" s="71"/>
+      <x:c r="K17" s="71"/>
+      <x:c r="L17" s="71"/>
+      <x:c r="M17" s="71"/>
+      <x:c r="N17" s="71"/>
+      <x:c r="O17" s="71"/>
+      <x:c r="P17" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
         <x:v>29 Nov</x:v>
       </x:c>
-      <x:c r="Q17" s="39" t="n">
+      <x:c r="Q17" s="74" t="n">
         <x:f>'13-Week Forecast'!N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="R17" s="39" t="n">
+      <x:c r="R17" s="74" t="n">
         <x:f>'13-Week Forecast'!N$49</x:f>
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="S17" s="71"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="n">
+      <x:c r="A18" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>7</x:v>
       </x:c>
@@ -2062,9 +2383,23 @@
         <x:f>'13-Week Forecast'!H$51</x:f>
         <x:v>OK</x:v>
       </x:c>
+      <x:c r="F18" s="71"/>
+      <x:c r="G18" s="71"/>
+      <x:c r="H18" s="71"/>
+      <x:c r="I18" s="71"/>
+      <x:c r="J18" s="71"/>
+      <x:c r="K18" s="71"/>
+      <x:c r="L18" s="71"/>
+      <x:c r="M18" s="71"/>
+      <x:c r="N18" s="71"/>
+      <x:c r="O18" s="71"/>
+      <x:c r="P18" s="71"/>
+      <x:c r="Q18" s="71"/>
+      <x:c r="R18" s="71"/>
+      <x:c r="S18" s="71"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" t="n">
+      <x:c r="A19" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>8</x:v>
       </x:c>
@@ -2084,9 +2419,23 @@
         <x:f>'13-Week Forecast'!I$51</x:f>
         <x:v>OK</x:v>
       </x:c>
+      <x:c r="F19" s="71"/>
+      <x:c r="G19" s="71"/>
+      <x:c r="H19" s="71"/>
+      <x:c r="I19" s="71"/>
+      <x:c r="J19" s="71"/>
+      <x:c r="K19" s="71"/>
+      <x:c r="L19" s="71"/>
+      <x:c r="M19" s="71"/>
+      <x:c r="N19" s="71"/>
+      <x:c r="O19" s="71"/>
+      <x:c r="P19" s="71"/>
+      <x:c r="Q19" s="71"/>
+      <x:c r="R19" s="71"/>
+      <x:c r="S19" s="71"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" t="n">
+      <x:c r="A20" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>9</x:v>
       </x:c>
@@ -2106,9 +2455,23 @@
         <x:f>'13-Week Forecast'!J$51</x:f>
         <x:v>WATCH</x:v>
       </x:c>
+      <x:c r="F20" s="71"/>
+      <x:c r="G20" s="71"/>
+      <x:c r="H20" s="71"/>
+      <x:c r="I20" s="71"/>
+      <x:c r="J20" s="71"/>
+      <x:c r="K20" s="71"/>
+      <x:c r="L20" s="71"/>
+      <x:c r="M20" s="71"/>
+      <x:c r="N20" s="71"/>
+      <x:c r="O20" s="71"/>
+      <x:c r="P20" s="71"/>
+      <x:c r="Q20" s="71"/>
+      <x:c r="R20" s="71"/>
+      <x:c r="S20" s="71"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" t="n">
+      <x:c r="A21" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>10</x:v>
       </x:c>
@@ -2128,6 +2491,16 @@
         <x:f>'13-Week Forecast'!K$51</x:f>
         <x:v>OK</x:v>
       </x:c>
+      <x:c r="F21" s="71"/>
+      <x:c r="G21" s="71"/>
+      <x:c r="H21" s="71"/>
+      <x:c r="I21" s="71"/>
+      <x:c r="J21" s="71"/>
+      <x:c r="K21" s="71"/>
+      <x:c r="L21" s="71"/>
+      <x:c r="M21" s="71"/>
+      <x:c r="N21" s="71"/>
+      <x:c r="O21" s="71"/>
       <x:c r="P21" s="14" t="str">
         <x:v>Week ending</x:v>
       </x:c>
@@ -2137,9 +2510,10 @@
       <x:c r="R21" s="14" t="str">
         <x:v>Total cash payments</x:v>
       </x:c>
+      <x:c r="S21" s="71"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" t="n">
+      <x:c r="A22" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>11</x:v>
       </x:c>
@@ -2159,21 +2533,32 @@
         <x:f>'13-Week Forecast'!L$51</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="P22" s="11" t="str">
+      <x:c r="F22" s="71"/>
+      <x:c r="G22" s="71"/>
+      <x:c r="H22" s="71"/>
+      <x:c r="I22" s="71"/>
+      <x:c r="J22" s="71"/>
+      <x:c r="K22" s="71"/>
+      <x:c r="L22" s="71"/>
+      <x:c r="M22" s="71"/>
+      <x:c r="N22" s="71"/>
+      <x:c r="O22" s="71"/>
+      <x:c r="P22" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
         <x:v>06 Sep</x:v>
       </x:c>
-      <x:c r="Q22" s="39" t="n">
+      <x:c r="Q22" s="74" t="n">
         <x:f>'13-Week Forecast'!B$19</x:f>
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="R22" s="39" t="n">
+      <x:c r="R22" s="74" t="n">
         <x:f>'13-Week Forecast'!B$43</x:f>
         <x:v>212000</x:v>
       </x:c>
+      <x:c r="S22" s="71"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" t="n">
+      <x:c r="A23" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>12</x:v>
       </x:c>
@@ -2193,21 +2578,32 @@
         <x:f>'13-Week Forecast'!M$51</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="P23" s="11" t="str">
+      <x:c r="F23" s="71"/>
+      <x:c r="G23" s="71"/>
+      <x:c r="H23" s="71"/>
+      <x:c r="I23" s="71"/>
+      <x:c r="J23" s="71"/>
+      <x:c r="K23" s="71"/>
+      <x:c r="L23" s="71"/>
+      <x:c r="M23" s="71"/>
+      <x:c r="N23" s="71"/>
+      <x:c r="O23" s="71"/>
+      <x:c r="P23" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
         <x:v>13 Sep</x:v>
       </x:c>
-      <x:c r="Q23" s="39" t="n">
+      <x:c r="Q23" s="74" t="n">
         <x:f>'13-Week Forecast'!C$19</x:f>
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="R23" s="39" t="n">
+      <x:c r="R23" s="74" t="n">
         <x:f>'13-Week Forecast'!C$43</x:f>
         <x:v>178000</x:v>
       </x:c>
+      <x:c r="S23" s="71"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" t="n">
+      <x:c r="A24" s="71" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>13</x:v>
       </x:c>
@@ -2227,46 +2623,89 @@
         <x:f>'13-Week Forecast'!N$51</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="P24" s="11" t="str">
+      <x:c r="F24" s="71"/>
+      <x:c r="G24" s="71"/>
+      <x:c r="H24" s="71"/>
+      <x:c r="I24" s="71"/>
+      <x:c r="J24" s="71"/>
+      <x:c r="K24" s="71"/>
+      <x:c r="L24" s="71"/>
+      <x:c r="M24" s="71"/>
+      <x:c r="N24" s="71"/>
+      <x:c r="O24" s="71"/>
+      <x:c r="P24" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
         <x:v>20 Sep</x:v>
       </x:c>
-      <x:c r="Q24" s="39" t="n">
+      <x:c r="Q24" s="74" t="n">
         <x:f>'13-Week Forecast'!D$19</x:f>
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="R24" s="39" t="n">
+      <x:c r="R24" s="74" t="n">
         <x:f>'13-Week Forecast'!D$43</x:f>
         <x:v>182000</x:v>
       </x:c>
+      <x:c r="S24" s="71"/>
     </x:row>
     <x:row r="25">
-      <x:c r="P25" s="11" t="str">
+      <x:c r="A25" s="71"/>
+      <x:c r="B25" s="71"/>
+      <x:c r="C25" s="71"/>
+      <x:c r="D25" s="71"/>
+      <x:c r="E25" s="71"/>
+      <x:c r="F25" s="71"/>
+      <x:c r="G25" s="71"/>
+      <x:c r="H25" s="71"/>
+      <x:c r="I25" s="71"/>
+      <x:c r="J25" s="71"/>
+      <x:c r="K25" s="71"/>
+      <x:c r="L25" s="71"/>
+      <x:c r="M25" s="71"/>
+      <x:c r="N25" s="71"/>
+      <x:c r="O25" s="71"/>
+      <x:c r="P25" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
         <x:v>27 Sep</x:v>
       </x:c>
-      <x:c r="Q25" s="39" t="n">
+      <x:c r="Q25" s="74" t="n">
         <x:f>'13-Week Forecast'!E$19</x:f>
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="R25" s="39" t="n">
+      <x:c r="R25" s="74" t="n">
         <x:f>'13-Week Forecast'!E$43</x:f>
         <x:v>179000</x:v>
       </x:c>
+      <x:c r="S25" s="71"/>
     </x:row>
     <x:row r="26">
-      <x:c r="P26" s="11" t="str">
+      <x:c r="A26" s="71"/>
+      <x:c r="B26" s="71"/>
+      <x:c r="C26" s="71"/>
+      <x:c r="D26" s="71"/>
+      <x:c r="E26" s="71"/>
+      <x:c r="F26" s="71"/>
+      <x:c r="G26" s="71"/>
+      <x:c r="H26" s="71"/>
+      <x:c r="I26" s="71"/>
+      <x:c r="J26" s="71"/>
+      <x:c r="K26" s="71"/>
+      <x:c r="L26" s="71"/>
+      <x:c r="M26" s="71"/>
+      <x:c r="N26" s="71"/>
+      <x:c r="O26" s="71"/>
+      <x:c r="P26" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
         <x:v>04 Oct</x:v>
       </x:c>
-      <x:c r="Q26" s="39" t="n">
+      <x:c r="Q26" s="74" t="n">
         <x:f>'13-Week Forecast'!F$19</x:f>
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="R26" s="39" t="n">
+      <x:c r="R26" s="74" t="n">
         <x:f>'13-Week Forecast'!F$43</x:f>
         <x:v>232000</x:v>
       </x:c>
+      <x:c r="S26" s="71"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="45" t="str">
@@ -2284,178 +2723,322 @@
       <x:c r="E27" s="45" t="str">
         <x:v>Funding required</x:v>
       </x:c>
-      <x:c r="P27" s="11" t="str">
+      <x:c r="F27" s="71"/>
+      <x:c r="G27" s="71"/>
+      <x:c r="H27" s="71"/>
+      <x:c r="I27" s="71"/>
+      <x:c r="J27" s="71"/>
+      <x:c r="K27" s="71"/>
+      <x:c r="L27" s="71"/>
+      <x:c r="M27" s="71"/>
+      <x:c r="N27" s="71"/>
+      <x:c r="O27" s="71"/>
+      <x:c r="P27" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
         <x:v>11 Oct</x:v>
       </x:c>
-      <x:c r="Q27" s="39" t="n">
+      <x:c r="Q27" s="74" t="n">
         <x:f>'13-Week Forecast'!G$19</x:f>
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="R27" s="39" t="n">
+      <x:c r="R27" s="74" t="n">
         <x:f>'13-Week Forecast'!G$43</x:f>
         <x:v>209000</x:v>
       </x:c>
+      <x:c r="S27" s="71"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="12" t="str">
         <x:f>'Assumptions'!$B$15</x:f>
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="74" t="n">
         <x:f>Q49</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="74" t="n">
         <x:f>MIN(Q37:Q49)</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D28" s="11" t="n">
+      <x:c r="D28" s="72" t="n">
         <x:f>IF(Q37&lt;'Assumptions'!$B$11,P37,IF(Q38&lt;'Assumptions'!$B$11,P38,IF(Q39&lt;'Assumptions'!$B$11,P39,IF(Q40&lt;'Assumptions'!$B$11,P40,IF(Q41&lt;'Assumptions'!$B$11,P41,IF(Q42&lt;'Assumptions'!$B$11,P42,IF(Q43&lt;'Assumptions'!$B$11,P43,IF(Q44&lt;'Assumptions'!$B$11,P44,IF(Q45&lt;'Assumptions'!$B$11,P45,IF(Q46&lt;'Assumptions'!$B$11,P46,IF(Q47&lt;'Assumptions'!$B$11,P47,IF(Q48&lt;'Assumptions'!$B$11,P48,IF(Q49&lt;'Assumptions'!$B$11,P49,"None")))))))))))))</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="74" t="n">
         <x:f>MAX(0,'Assumptions'!$B$11-MIN(Q37:Q49))</x:f>
         <x:v>69000</x:v>
       </x:c>
-      <x:c r="P28" s="11" t="str">
+      <x:c r="F28" s="71"/>
+      <x:c r="G28" s="71"/>
+      <x:c r="H28" s="71"/>
+      <x:c r="I28" s="71"/>
+      <x:c r="J28" s="71"/>
+      <x:c r="K28" s="71"/>
+      <x:c r="L28" s="71"/>
+      <x:c r="M28" s="71"/>
+      <x:c r="N28" s="71"/>
+      <x:c r="O28" s="71"/>
+      <x:c r="P28" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
         <x:v>18 Oct</x:v>
       </x:c>
-      <x:c r="Q28" s="39" t="n">
+      <x:c r="Q28" s="74" t="n">
         <x:f>'13-Week Forecast'!H$19</x:f>
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="R28" s="39" t="n">
+      <x:c r="R28" s="74" t="n">
         <x:f>'13-Week Forecast'!H$43</x:f>
         <x:v>197000</x:v>
       </x:c>
+      <x:c r="S28" s="71"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="12" t="str">
         <x:f>'Assumptions'!$B$16</x:f>
         <x:v>Upside</x:v>
       </x:c>
-      <x:c r="B29" s="39" t="n">
+      <x:c r="B29" s="74" t="n">
         <x:f>R49</x:f>
         <x:v>199320</x:v>
       </x:c>
-      <x:c r="C29" s="39" t="n">
+      <x:c r="C29" s="74" t="n">
         <x:f>MIN(R37:R49)</x:f>
         <x:v>199320</x:v>
       </x:c>
-      <x:c r="D29" s="11" t="str">
+      <x:c r="D29" s="72" t="str">
         <x:f>IF(R37&lt;'Assumptions'!$B$11,P37,IF(R38&lt;'Assumptions'!$B$11,P38,IF(R39&lt;'Assumptions'!$B$11,P39,IF(R40&lt;'Assumptions'!$B$11,P40,IF(R41&lt;'Assumptions'!$B$11,P41,IF(R42&lt;'Assumptions'!$B$11,P42,IF(R43&lt;'Assumptions'!$B$11,P43,IF(R44&lt;'Assumptions'!$B$11,P44,IF(R45&lt;'Assumptions'!$B$11,P45,IF(R46&lt;'Assumptions'!$B$11,P46,IF(R47&lt;'Assumptions'!$B$11,P47,IF(R48&lt;'Assumptions'!$B$11,P48,IF(R49&lt;'Assumptions'!$B$11,P49,"None")))))))))))))</x:f>
         <x:v>None</x:v>
       </x:c>
-      <x:c r="E29" s="39" t="n">
+      <x:c r="E29" s="74" t="n">
         <x:f>MAX(0,'Assumptions'!$B$11-MIN(R37:R49))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P29" s="11" t="str">
+      <x:c r="F29" s="71"/>
+      <x:c r="G29" s="71"/>
+      <x:c r="H29" s="71"/>
+      <x:c r="I29" s="71"/>
+      <x:c r="J29" s="71"/>
+      <x:c r="K29" s="71"/>
+      <x:c r="L29" s="71"/>
+      <x:c r="M29" s="71"/>
+      <x:c r="N29" s="71"/>
+      <x:c r="O29" s="71"/>
+      <x:c r="P29" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
         <x:v>25 Oct</x:v>
       </x:c>
-      <x:c r="Q29" s="39" t="n">
+      <x:c r="Q29" s="74" t="n">
         <x:f>'13-Week Forecast'!I$19</x:f>
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="R29" s="39" t="n">
+      <x:c r="R29" s="74" t="n">
         <x:f>'13-Week Forecast'!I$43</x:f>
         <x:v>192000</x:v>
       </x:c>
+      <x:c r="S29" s="71"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="12" t="str">
         <x:f>'Assumptions'!$B$17</x:f>
         <x:v>Downside</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="74" t="n">
         <x:f>S49</x:f>
         <x:v>-302550</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="74" t="n">
         <x:f>MIN(S37:S49)</x:f>
         <x:v>-302550</x:v>
       </x:c>
-      <x:c r="D30" s="11" t="n">
+      <x:c r="D30" s="72" t="n">
         <x:f>IF(S37&lt;'Assumptions'!$B$11,P37,IF(S38&lt;'Assumptions'!$B$11,P38,IF(S39&lt;'Assumptions'!$B$11,P39,IF(S40&lt;'Assumptions'!$B$11,P40,IF(S41&lt;'Assumptions'!$B$11,P41,IF(S42&lt;'Assumptions'!$B$11,P42,IF(S43&lt;'Assumptions'!$B$11,P43,IF(S44&lt;'Assumptions'!$B$11,P44,IF(S45&lt;'Assumptions'!$B$11,P45,IF(S46&lt;'Assumptions'!$B$11,P46,IF(S47&lt;'Assumptions'!$B$11,P47,IF(S48&lt;'Assumptions'!$B$11,P48,IF(S49&lt;'Assumptions'!$B$11,P49,"None")))))))))))))</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="74" t="n">
         <x:f>MAX(0,'Assumptions'!$B$11-MIN(S37:S49))</x:f>
         <x:v>402550</x:v>
       </x:c>
-      <x:c r="P30" s="11" t="str">
+      <x:c r="F30" s="71"/>
+      <x:c r="G30" s="71"/>
+      <x:c r="H30" s="71"/>
+      <x:c r="I30" s="71"/>
+      <x:c r="J30" s="71"/>
+      <x:c r="K30" s="71"/>
+      <x:c r="L30" s="71"/>
+      <x:c r="M30" s="71"/>
+      <x:c r="N30" s="71"/>
+      <x:c r="O30" s="71"/>
+      <x:c r="P30" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
         <x:v>01 Nov</x:v>
       </x:c>
-      <x:c r="Q30" s="39" t="n">
+      <x:c r="Q30" s="74" t="n">
         <x:f>'13-Week Forecast'!J$19</x:f>
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="R30" s="39" t="n">
+      <x:c r="R30" s="74" t="n">
         <x:f>'13-Week Forecast'!J$43</x:f>
         <x:v>307000</x:v>
       </x:c>
+      <x:c r="S30" s="71"/>
     </x:row>
     <x:row r="31">
-      <x:c r="P31" s="11" t="str">
+      <x:c r="A31" s="71"/>
+      <x:c r="B31" s="71"/>
+      <x:c r="C31" s="71"/>
+      <x:c r="D31" s="71"/>
+      <x:c r="E31" s="71"/>
+      <x:c r="F31" s="71"/>
+      <x:c r="G31" s="71"/>
+      <x:c r="H31" s="71"/>
+      <x:c r="I31" s="71"/>
+      <x:c r="J31" s="71"/>
+      <x:c r="K31" s="71"/>
+      <x:c r="L31" s="71"/>
+      <x:c r="M31" s="71"/>
+      <x:c r="N31" s="71"/>
+      <x:c r="O31" s="71"/>
+      <x:c r="P31" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
         <x:v>08 Nov</x:v>
       </x:c>
-      <x:c r="Q31" s="39" t="n">
+      <x:c r="Q31" s="74" t="n">
         <x:f>'13-Week Forecast'!K$19</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="R31" s="39" t="n">
+      <x:c r="R31" s="74" t="n">
         <x:f>'13-Week Forecast'!K$43</x:f>
         <x:v>229000</x:v>
       </x:c>
+      <x:c r="S31" s="71"/>
     </x:row>
     <x:row r="32">
-      <x:c r="P32" s="11" t="str">
+      <x:c r="A32" s="71"/>
+      <x:c r="B32" s="71"/>
+      <x:c r="C32" s="71"/>
+      <x:c r="D32" s="71"/>
+      <x:c r="E32" s="71"/>
+      <x:c r="F32" s="71"/>
+      <x:c r="G32" s="71"/>
+      <x:c r="H32" s="71"/>
+      <x:c r="I32" s="71"/>
+      <x:c r="J32" s="71"/>
+      <x:c r="K32" s="71"/>
+      <x:c r="L32" s="71"/>
+      <x:c r="M32" s="71"/>
+      <x:c r="N32" s="71"/>
+      <x:c r="O32" s="71"/>
+      <x:c r="P32" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
         <x:v>15 Nov</x:v>
       </x:c>
-      <x:c r="Q32" s="39" t="n">
+      <x:c r="Q32" s="74" t="n">
         <x:f>'13-Week Forecast'!L$19</x:f>
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="R32" s="39" t="n">
+      <x:c r="R32" s="74" t="n">
         <x:f>'13-Week Forecast'!L$43</x:f>
         <x:v>192000</x:v>
       </x:c>
+      <x:c r="S32" s="71"/>
     </x:row>
     <x:row r="33">
-      <x:c r="P33" s="11" t="str">
+      <x:c r="A33" s="71"/>
+      <x:c r="B33" s="71"/>
+      <x:c r="C33" s="71"/>
+      <x:c r="D33" s="71"/>
+      <x:c r="E33" s="71"/>
+      <x:c r="F33" s="71"/>
+      <x:c r="G33" s="71"/>
+      <x:c r="H33" s="71"/>
+      <x:c r="I33" s="71"/>
+      <x:c r="J33" s="71"/>
+      <x:c r="K33" s="71"/>
+      <x:c r="L33" s="71"/>
+      <x:c r="M33" s="71"/>
+      <x:c r="N33" s="71"/>
+      <x:c r="O33" s="71"/>
+      <x:c r="P33" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
         <x:v>22 Nov</x:v>
       </x:c>
-      <x:c r="Q33" s="39" t="n">
+      <x:c r="Q33" s="74" t="n">
         <x:f>'13-Week Forecast'!M$19</x:f>
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="R33" s="39" t="n">
+      <x:c r="R33" s="74" t="n">
         <x:f>'13-Week Forecast'!M$43</x:f>
         <x:v>179000</x:v>
       </x:c>
+      <x:c r="S33" s="71"/>
     </x:row>
     <x:row r="34">
-      <x:c r="P34" s="11" t="str">
+      <x:c r="A34" s="71"/>
+      <x:c r="B34" s="71"/>
+      <x:c r="C34" s="71"/>
+      <x:c r="D34" s="71"/>
+      <x:c r="E34" s="71"/>
+      <x:c r="F34" s="71"/>
+      <x:c r="G34" s="71"/>
+      <x:c r="H34" s="71"/>
+      <x:c r="I34" s="71"/>
+      <x:c r="J34" s="71"/>
+      <x:c r="K34" s="71"/>
+      <x:c r="L34" s="71"/>
+      <x:c r="M34" s="71"/>
+      <x:c r="N34" s="71"/>
+      <x:c r="O34" s="71"/>
+      <x:c r="P34" s="72" t="str">
         <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
         <x:v>29 Nov</x:v>
       </x:c>
-      <x:c r="Q34" s="39" t="n">
+      <x:c r="Q34" s="74" t="n">
         <x:f>'13-Week Forecast'!N$19</x:f>
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="R34" s="39" t="n">
+      <x:c r="R34" s="74" t="n">
         <x:f>'13-Week Forecast'!N$43</x:f>
         <x:v>219000</x:v>
       </x:c>
+      <x:c r="S34" s="71"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="71"/>
+      <x:c r="B35" s="71"/>
+      <x:c r="C35" s="71"/>
+      <x:c r="D35" s="71"/>
+      <x:c r="E35" s="71"/>
+      <x:c r="F35" s="71"/>
+      <x:c r="G35" s="71"/>
+      <x:c r="H35" s="71"/>
+      <x:c r="I35" s="71"/>
+      <x:c r="J35" s="71"/>
+      <x:c r="K35" s="71"/>
+      <x:c r="L35" s="71"/>
+      <x:c r="M35" s="71"/>
+      <x:c r="N35" s="71"/>
+      <x:c r="O35" s="71"/>
+      <x:c r="P35" s="71"/>
+      <x:c r="Q35" s="71"/>
+      <x:c r="R35" s="71"/>
+      <x:c r="S35" s="71"/>
     </x:row>
     <x:row r="36">
+      <x:c r="A36" s="71"/>
+      <x:c r="B36" s="71"/>
+      <x:c r="C36" s="71"/>
+      <x:c r="D36" s="71"/>
+      <x:c r="E36" s="71"/>
+      <x:c r="F36" s="71"/>
+      <x:c r="G36" s="71"/>
+      <x:c r="H36" s="71"/>
+      <x:c r="I36" s="71"/>
+      <x:c r="J36" s="71"/>
+      <x:c r="K36" s="71"/>
+      <x:c r="L36" s="71"/>
+      <x:c r="M36" s="71"/>
+      <x:c r="N36" s="71"/>
+      <x:c r="O36" s="71"/>
       <x:c r="P36" s="14" t="str">
         <x:v>Week ending</x:v>
       </x:c>
@@ -2470,235 +3053,430 @@
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="P37" s="11" t="n">
+      <x:c r="A37" s="71"/>
+      <x:c r="B37" s="71"/>
+      <x:c r="C37" s="71"/>
+      <x:c r="D37" s="71"/>
+      <x:c r="E37" s="71"/>
+      <x:c r="F37" s="71"/>
+      <x:c r="G37" s="71"/>
+      <x:c r="H37" s="71"/>
+      <x:c r="I37" s="71"/>
+      <x:c r="J37" s="71"/>
+      <x:c r="K37" s="71"/>
+      <x:c r="L37" s="71"/>
+      <x:c r="M37" s="71"/>
+      <x:c r="N37" s="71"/>
+      <x:c r="O37" s="71"/>
+      <x:c r="P37" s="72" t="n">
         <x:f>'13-Week Forecast'!B$6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="Q37" s="39" t="n">
+      <x:c r="Q37" s="74" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!B10:B17)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B10:B12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!B22:B41)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B22,'13-Week Forecast'!B31,'13-Week Forecast'!B33,'13-Week Forecast'!B41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="R37" s="39" t="n">
+      <x:c r="R37" s="74" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!B10:B17)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B10:B12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!B22:B41)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B22,'13-Week Forecast'!B31,'13-Week Forecast'!B33,'13-Week Forecast'!B41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="S37" s="39" t="n">
+      <x:c r="S37" s="74" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!B10:B17)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B10:B12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!B22:B41)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B22,'13-Week Forecast'!B31,'13-Week Forecast'!B33,'13-Week Forecast'!B41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>358000</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="P38" s="11" t="n">
+      <x:c r="A38" s="71"/>
+      <x:c r="B38" s="71"/>
+      <x:c r="C38" s="71"/>
+      <x:c r="D38" s="71"/>
+      <x:c r="E38" s="71"/>
+      <x:c r="F38" s="71"/>
+      <x:c r="G38" s="71"/>
+      <x:c r="H38" s="71"/>
+      <x:c r="I38" s="71"/>
+      <x:c r="J38" s="71"/>
+      <x:c r="K38" s="71"/>
+      <x:c r="L38" s="71"/>
+      <x:c r="M38" s="71"/>
+      <x:c r="N38" s="71"/>
+      <x:c r="O38" s="71"/>
+      <x:c r="P38" s="72" t="n">
         <x:f>'13-Week Forecast'!C$6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="Q38" s="39" t="n">
+      <x:c r="Q38" s="74" t="n">
         <x:f>Q37+SUM('13-Week Forecast'!C10:C17)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C10:C12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!C22:C41)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C22,'13-Week Forecast'!C31,'13-Week Forecast'!C33,'13-Week Forecast'!C41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="R38" s="39" t="n">
+      <x:c r="R38" s="74" t="n">
         <x:f>R37+SUM('13-Week Forecast'!C10:C17)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C10:C12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!C22:C41)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C22,'13-Week Forecast'!C31,'13-Week Forecast'!C33,'13-Week Forecast'!C41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>364380</x:v>
       </x:c>
-      <x:c r="S38" s="39" t="n">
+      <x:c r="S38" s="74" t="n">
         <x:f>S37+SUM('13-Week Forecast'!C10:C17)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C10:C12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!C22:C41)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C22,'13-Week Forecast'!C31,'13-Week Forecast'!C33,'13-Week Forecast'!C41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>318800</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="P39" s="11" t="n">
+      <x:c r="A39" s="71"/>
+      <x:c r="B39" s="71"/>
+      <x:c r="C39" s="71"/>
+      <x:c r="D39" s="71"/>
+      <x:c r="E39" s="71"/>
+      <x:c r="F39" s="71"/>
+      <x:c r="G39" s="71"/>
+      <x:c r="H39" s="71"/>
+      <x:c r="I39" s="71"/>
+      <x:c r="J39" s="71"/>
+      <x:c r="K39" s="71"/>
+      <x:c r="L39" s="71"/>
+      <x:c r="M39" s="71"/>
+      <x:c r="N39" s="71"/>
+      <x:c r="O39" s="71"/>
+      <x:c r="P39" s="72" t="n">
         <x:f>'13-Week Forecast'!D$6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="Q39" s="39" t="n">
+      <x:c r="Q39" s="74" t="n">
         <x:f>Q38+SUM('13-Week Forecast'!D10:D17)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D10:D12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!D22:D41)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D22,'13-Week Forecast'!D31,'13-Week Forecast'!D33,'13-Week Forecast'!D41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="R39" s="39" t="n">
+      <x:c r="R39" s="74" t="n">
         <x:f>R38+SUM('13-Week Forecast'!D10:D17)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D10:D12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!D22:D41)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D22,'13-Week Forecast'!D31,'13-Week Forecast'!D33,'13-Week Forecast'!D41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>354920</x:v>
       </x:c>
-      <x:c r="S39" s="39" t="n">
+      <x:c r="S39" s="74" t="n">
         <x:f>S38+SUM('13-Week Forecast'!D10:D17)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D10:D12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!D22:D41)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D22,'13-Week Forecast'!D31,'13-Week Forecast'!D33,'13-Week Forecast'!D41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>266150</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="P40" s="11" t="n">
+      <x:c r="A40" s="71"/>
+      <x:c r="B40" s="71"/>
+      <x:c r="C40" s="71"/>
+      <x:c r="D40" s="71"/>
+      <x:c r="E40" s="71"/>
+      <x:c r="F40" s="71"/>
+      <x:c r="G40" s="71"/>
+      <x:c r="H40" s="71"/>
+      <x:c r="I40" s="71"/>
+      <x:c r="J40" s="71"/>
+      <x:c r="K40" s="71"/>
+      <x:c r="L40" s="71"/>
+      <x:c r="M40" s="71"/>
+      <x:c r="N40" s="71"/>
+      <x:c r="O40" s="71"/>
+      <x:c r="P40" s="72" t="n">
         <x:f>'13-Week Forecast'!E$6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="Q40" s="39" t="n">
+      <x:c r="Q40" s="74" t="n">
         <x:f>Q39+SUM('13-Week Forecast'!E10:E17)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E10:E12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!E22:E41)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E22,'13-Week Forecast'!E31,'13-Week Forecast'!E33,'13-Week Forecast'!E41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="R40" s="39" t="n">
+      <x:c r="R40" s="74" t="n">
         <x:f>R39+SUM('13-Week Forecast'!E10:E17)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E10:E12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!E22:E41)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E22,'13-Week Forecast'!E31,'13-Week Forecast'!E33,'13-Week Forecast'!E41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>336680</x:v>
       </x:c>
-      <x:c r="S40" s="39" t="n">
+      <x:c r="S40" s="74" t="n">
         <x:f>S39+SUM('13-Week Forecast'!E10:E17)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E10:E12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!E22:E41)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E22,'13-Week Forecast'!E31,'13-Week Forecast'!E33,'13-Week Forecast'!E41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>206900</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="P41" s="11" t="n">
+      <x:c r="A41" s="71"/>
+      <x:c r="B41" s="71"/>
+      <x:c r="C41" s="71"/>
+      <x:c r="D41" s="71"/>
+      <x:c r="E41" s="71"/>
+      <x:c r="F41" s="71"/>
+      <x:c r="G41" s="71"/>
+      <x:c r="H41" s="71"/>
+      <x:c r="I41" s="71"/>
+      <x:c r="J41" s="71"/>
+      <x:c r="K41" s="71"/>
+      <x:c r="L41" s="71"/>
+      <x:c r="M41" s="71"/>
+      <x:c r="N41" s="71"/>
+      <x:c r="O41" s="71"/>
+      <x:c r="P41" s="72" t="n">
         <x:f>'13-Week Forecast'!F$6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="Q41" s="39" t="n">
+      <x:c r="Q41" s="74" t="n">
         <x:f>Q40+SUM('13-Week Forecast'!F10:F17)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F10:F12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!F22:F41)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F22,'13-Week Forecast'!F31,'13-Week Forecast'!F33,'13-Week Forecast'!F41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="R41" s="39" t="n">
+      <x:c r="R41" s="74" t="n">
         <x:f>R40+SUM('13-Week Forecast'!F10:F17)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F10:F12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!F22:F41)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F22,'13-Week Forecast'!F31,'13-Week Forecast'!F33,'13-Week Forecast'!F41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>257940</x:v>
       </x:c>
-      <x:c r="S41" s="39" t="n">
+      <x:c r="S41" s="74" t="n">
         <x:f>S40+SUM('13-Week Forecast'!F10:F17)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F10:F12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!F22:F41)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F22,'13-Week Forecast'!F31,'13-Week Forecast'!F33,'13-Week Forecast'!F41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>88550</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="P42" s="11" t="n">
+      <x:c r="A42" s="71"/>
+      <x:c r="B42" s="71"/>
+      <x:c r="C42" s="71"/>
+      <x:c r="D42" s="71"/>
+      <x:c r="E42" s="71"/>
+      <x:c r="F42" s="71"/>
+      <x:c r="G42" s="71"/>
+      <x:c r="H42" s="71"/>
+      <x:c r="I42" s="71"/>
+      <x:c r="J42" s="71"/>
+      <x:c r="K42" s="71"/>
+      <x:c r="L42" s="71"/>
+      <x:c r="M42" s="71"/>
+      <x:c r="N42" s="71"/>
+      <x:c r="O42" s="71"/>
+      <x:c r="P42" s="72" t="n">
         <x:f>'13-Week Forecast'!G$6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="Q42" s="39" t="n">
+      <x:c r="Q42" s="74" t="n">
         <x:f>Q41+SUM('13-Week Forecast'!G10:G17)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G10:G12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!G22:G41)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G22,'13-Week Forecast'!G31,'13-Week Forecast'!G33,'13-Week Forecast'!G41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="R42" s="39" t="n">
+      <x:c r="R42" s="74" t="n">
         <x:f>R41+SUM('13-Week Forecast'!G10:G17)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G10:G12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!G22:G41)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G22,'13-Week Forecast'!G31,'13-Week Forecast'!G33,'13-Week Forecast'!G41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>203320</x:v>
       </x:c>
-      <x:c r="S42" s="39" t="n">
+      <x:c r="S42" s="74" t="n">
         <x:f>S41+SUM('13-Week Forecast'!G10:G17)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G10:G12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!G22:G41)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G22,'13-Week Forecast'!G31,'13-Week Forecast'!G33,'13-Week Forecast'!G41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-6050</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="P43" s="11" t="n">
+      <x:c r="A43" s="71"/>
+      <x:c r="B43" s="71"/>
+      <x:c r="C43" s="71"/>
+      <x:c r="D43" s="71"/>
+      <x:c r="E43" s="71"/>
+      <x:c r="F43" s="71"/>
+      <x:c r="G43" s="71"/>
+      <x:c r="H43" s="71"/>
+      <x:c r="I43" s="71"/>
+      <x:c r="J43" s="71"/>
+      <x:c r="K43" s="71"/>
+      <x:c r="L43" s="71"/>
+      <x:c r="M43" s="71"/>
+      <x:c r="N43" s="71"/>
+      <x:c r="O43" s="71"/>
+      <x:c r="P43" s="72" t="n">
         <x:f>'13-Week Forecast'!H$6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="Q43" s="39" t="n">
+      <x:c r="Q43" s="74" t="n">
         <x:f>Q42+SUM('13-Week Forecast'!H10:H17)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H10:H12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!H22:H41)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H22,'13-Week Forecast'!H31,'13-Week Forecast'!H33,'13-Week Forecast'!H41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="R43" s="39" t="n">
+      <x:c r="R43" s="74" t="n">
         <x:f>R42+SUM('13-Week Forecast'!H10:H17)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H10:H12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!H22:H41)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H22,'13-Week Forecast'!H31,'13-Week Forecast'!H33,'13-Week Forecast'!H41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>300000</x:v>
       </x:c>
-      <x:c r="S43" s="39" t="n">
+      <x:c r="S43" s="74" t="n">
         <x:f>S42+SUM('13-Week Forecast'!H10:H17)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H10:H12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!H22:H41)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H22,'13-Week Forecast'!H31,'13-Week Forecast'!H33,'13-Week Forecast'!H41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>52600</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="P44" s="11" t="n">
+      <x:c r="A44" s="71"/>
+      <x:c r="B44" s="71"/>
+      <x:c r="C44" s="71"/>
+      <x:c r="D44" s="71"/>
+      <x:c r="E44" s="71"/>
+      <x:c r="F44" s="71"/>
+      <x:c r="G44" s="71"/>
+      <x:c r="H44" s="71"/>
+      <x:c r="I44" s="71"/>
+      <x:c r="J44" s="71"/>
+      <x:c r="K44" s="71"/>
+      <x:c r="L44" s="71"/>
+      <x:c r="M44" s="71"/>
+      <x:c r="N44" s="71"/>
+      <x:c r="O44" s="71"/>
+      <x:c r="P44" s="72" t="n">
         <x:f>'13-Week Forecast'!I$6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="Q44" s="39" t="n">
+      <x:c r="Q44" s="74" t="n">
         <x:f>Q43+SUM('13-Week Forecast'!I10:I17)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I10:I12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!I22:I41)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I22,'13-Week Forecast'!I31,'13-Week Forecast'!I33,'13-Week Forecast'!I41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="R44" s="39" t="n">
+      <x:c r="R44" s="74" t="n">
         <x:f>R43+SUM('13-Week Forecast'!I10:I17)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I10:I12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!I22:I41)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I22,'13-Week Forecast'!I31,'13-Week Forecast'!I33,'13-Week Forecast'!I41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>256060</x:v>
       </x:c>
-      <x:c r="S44" s="39" t="n">
+      <x:c r="S44" s="74" t="n">
         <x:f>S43+SUM('13-Week Forecast'!I10:I17)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I10:I12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!I22:I41)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I22,'13-Week Forecast'!I31,'13-Week Forecast'!I33,'13-Week Forecast'!I41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-30500</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="P45" s="11" t="n">
+      <x:c r="A45" s="71"/>
+      <x:c r="B45" s="71"/>
+      <x:c r="C45" s="71"/>
+      <x:c r="D45" s="71"/>
+      <x:c r="E45" s="71"/>
+      <x:c r="F45" s="71"/>
+      <x:c r="G45" s="71"/>
+      <x:c r="H45" s="71"/>
+      <x:c r="I45" s="71"/>
+      <x:c r="J45" s="71"/>
+      <x:c r="K45" s="71"/>
+      <x:c r="L45" s="71"/>
+      <x:c r="M45" s="71"/>
+      <x:c r="N45" s="71"/>
+      <x:c r="O45" s="71"/>
+      <x:c r="P45" s="72" t="n">
         <x:f>'13-Week Forecast'!J$6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="Q45" s="39" t="n">
+      <x:c r="Q45" s="74" t="n">
         <x:f>Q44+SUM('13-Week Forecast'!J10:J17)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J10:J12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!J22:J41)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J22,'13-Week Forecast'!J31,'13-Week Forecast'!J33,'13-Week Forecast'!J41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="R45" s="39" t="n">
+      <x:c r="R45" s="74" t="n">
         <x:f>R44+SUM('13-Week Forecast'!J10:J17)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J10:J12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!J22:J41)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J22,'13-Week Forecast'!J31,'13-Week Forecast'!J33,'13-Week Forecast'!J41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>226480</x:v>
       </x:c>
-      <x:c r="S45" s="39" t="n">
+      <x:c r="S45" s="74" t="n">
         <x:f>S44+SUM('13-Week Forecast'!J10:J17)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J10:J12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!J22:J41)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J22,'13-Week Forecast'!J31,'13-Week Forecast'!J33,'13-Week Forecast'!J41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-100300</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="P46" s="11" t="n">
+      <x:c r="A46" s="71"/>
+      <x:c r="B46" s="71"/>
+      <x:c r="C46" s="71"/>
+      <x:c r="D46" s="71"/>
+      <x:c r="E46" s="71"/>
+      <x:c r="F46" s="71"/>
+      <x:c r="G46" s="71"/>
+      <x:c r="H46" s="71"/>
+      <x:c r="I46" s="71"/>
+      <x:c r="J46" s="71"/>
+      <x:c r="K46" s="71"/>
+      <x:c r="L46" s="71"/>
+      <x:c r="M46" s="71"/>
+      <x:c r="N46" s="71"/>
+      <x:c r="O46" s="71"/>
+      <x:c r="P46" s="72" t="n">
         <x:f>'13-Week Forecast'!K$6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="Q46" s="39" t="n">
+      <x:c r="Q46" s="74" t="n">
         <x:f>Q45+SUM('13-Week Forecast'!K10:K17)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K10:K12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!K22:K41)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K22,'13-Week Forecast'!K31,'13-Week Forecast'!K33,'13-Week Forecast'!K41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="R46" s="39" t="n">
+      <x:c r="R46" s="74" t="n">
         <x:f>R45+SUM('13-Week Forecast'!K10:K17)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K10:K12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!K22:K41)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K22,'13-Week Forecast'!K31,'13-Week Forecast'!K33,'13-Week Forecast'!K41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>260600</x:v>
       </x:c>
-      <x:c r="S46" s="39" t="n">
+      <x:c r="S46" s="74" t="n">
         <x:f>S45+SUM('13-Week Forecast'!K10:K17)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K10:K12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!K22:K41)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K22,'13-Week Forecast'!K31,'13-Week Forecast'!K33,'13-Week Forecast'!K41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-108350</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="P47" s="11" t="n">
+      <x:c r="A47" s="71"/>
+      <x:c r="B47" s="71"/>
+      <x:c r="C47" s="71"/>
+      <x:c r="D47" s="71"/>
+      <x:c r="E47" s="71"/>
+      <x:c r="F47" s="71"/>
+      <x:c r="G47" s="71"/>
+      <x:c r="H47" s="71"/>
+      <x:c r="I47" s="71"/>
+      <x:c r="J47" s="71"/>
+      <x:c r="K47" s="71"/>
+      <x:c r="L47" s="71"/>
+      <x:c r="M47" s="71"/>
+      <x:c r="N47" s="71"/>
+      <x:c r="O47" s="71"/>
+      <x:c r="P47" s="72" t="n">
         <x:f>'13-Week Forecast'!L$6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="Q47" s="39" t="n">
+      <x:c r="Q47" s="74" t="n">
         <x:f>Q46+SUM('13-Week Forecast'!L10:L17)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L10:L12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!L22:L41)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L22,'13-Week Forecast'!L31,'13-Week Forecast'!L33,'13-Week Forecast'!L41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="R47" s="39" t="n">
+      <x:c r="R47" s="74" t="n">
         <x:f>R46+SUM('13-Week Forecast'!L10:L17)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L10:L12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!L22:L41)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L22,'13-Week Forecast'!L31,'13-Week Forecast'!L33,'13-Week Forecast'!L41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>237020</x:v>
       </x:c>
-      <x:c r="S47" s="39" t="n">
+      <x:c r="S47" s="74" t="n">
         <x:f>S46+SUM('13-Week Forecast'!L10:L17)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L10:L12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!L22:L41)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L22,'13-Week Forecast'!L31,'13-Week Forecast'!L33,'13-Week Forecast'!L41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-174900</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="P48" s="11" t="n">
+      <x:c r="A48" s="71"/>
+      <x:c r="B48" s="71"/>
+      <x:c r="C48" s="71"/>
+      <x:c r="D48" s="71"/>
+      <x:c r="E48" s="71"/>
+      <x:c r="F48" s="71"/>
+      <x:c r="G48" s="71"/>
+      <x:c r="H48" s="71"/>
+      <x:c r="I48" s="71"/>
+      <x:c r="J48" s="71"/>
+      <x:c r="K48" s="71"/>
+      <x:c r="L48" s="71"/>
+      <x:c r="M48" s="71"/>
+      <x:c r="N48" s="71"/>
+      <x:c r="O48" s="71"/>
+      <x:c r="P48" s="72" t="n">
         <x:f>'13-Week Forecast'!M$6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="Q48" s="39" t="n">
+      <x:c r="Q48" s="74" t="n">
         <x:f>Q47+SUM('13-Week Forecast'!M10:M17)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M10:M12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!M22:M41)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M22,'13-Week Forecast'!M31,'13-Week Forecast'!M33,'13-Week Forecast'!M41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="R48" s="39" t="n">
+      <x:c r="R48" s="74" t="n">
         <x:f>R47+SUM('13-Week Forecast'!M10:M17)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M10:M12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!M22:M41)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M22,'13-Week Forecast'!M31,'13-Week Forecast'!M33,'13-Week Forecast'!M41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>234980</x:v>
       </x:c>
-      <x:c r="S48" s="39" t="n">
+      <x:c r="S48" s="74" t="n">
         <x:f>S47+SUM('13-Week Forecast'!M10:M17)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M10:M12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!M22:M41)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M22,'13-Week Forecast'!M31,'13-Week Forecast'!M33,'13-Week Forecast'!M41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-221400</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="P49" s="11" t="n">
+      <x:c r="A49" s="71"/>
+      <x:c r="B49" s="71"/>
+      <x:c r="C49" s="71"/>
+      <x:c r="D49" s="71"/>
+      <x:c r="E49" s="71"/>
+      <x:c r="F49" s="71"/>
+      <x:c r="G49" s="71"/>
+      <x:c r="H49" s="71"/>
+      <x:c r="I49" s="71"/>
+      <x:c r="J49" s="71"/>
+      <x:c r="K49" s="71"/>
+      <x:c r="L49" s="71"/>
+      <x:c r="M49" s="71"/>
+      <x:c r="N49" s="71"/>
+      <x:c r="O49" s="71"/>
+      <x:c r="P49" s="72" t="n">
         <x:f>'13-Week Forecast'!N$6</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="Q49" s="39" t="n">
+      <x:c r="Q49" s="74" t="n">
         <x:f>Q48+SUM('13-Week Forecast'!N10:N17)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N10:N12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!N22:N41)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N22,'13-Week Forecast'!N31,'13-Week Forecast'!N33,'13-Week Forecast'!N41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="R49" s="39" t="n">
+      <x:c r="R49" s="74" t="n">
         <x:f>R48+SUM('13-Week Forecast'!N10:N17)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N10:N12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!N22:N41)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N22,'13-Week Forecast'!N31,'13-Week Forecast'!N33,'13-Week Forecast'!N41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>199320</x:v>
       </x:c>
-      <x:c r="S49" s="39" t="n">
+      <x:c r="S49" s="74" t="n">
         <x:f>S48+SUM('13-Week Forecast'!N10:N17)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N10:N12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!N22:N41)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N22,'13-Week Forecast'!N31,'13-Week Forecast'!N33,'13-Week Forecast'!N41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-302550</x:v>
       </x:c>
@@ -2740,7 +3518,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfed8bbef86874f97"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca6d148ad5dd4b41"/>
 </x:worksheet>
 </file>
 
@@ -2776,6 +3554,14 @@
       <x:c r="E2" s="8"/>
       <x:c r="F2" s="8"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="71"/>
+      <x:c r="B3" s="71"/>
+      <x:c r="C3" s="71"/>
+      <x:c r="D3" s="71"/>
+      <x:c r="E3" s="71"/>
+      <x:c r="F3" s="71"/>
+    </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
         <x:v>Core controls</x:v>
@@ -2783,70 +3569,114 @@
       <x:c r="B4" s="14" t="str">
         <x:v>Value</x:v>
       </x:c>
+      <x:c r="C4" s="71"/>
+      <x:c r="D4" s="71"/>
+      <x:c r="E4" s="71"/>
+      <x:c r="F4" s="71"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
+      <x:c r="A5" s="71" t="str">
         <x:v>Business name</x:v>
       </x:c>
       <x:c r="B5" s="28" t="str">
         <x:v>Illustrative Australian business</x:v>
       </x:c>
+      <x:c r="C5" s="71"/>
+      <x:c r="D5" s="71"/>
+      <x:c r="E5" s="71"/>
+      <x:c r="F5" s="71"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
+      <x:c r="A6" s="71" t="str">
         <x:v>Currency</x:v>
       </x:c>
       <x:c r="B6" s="28" t="str">
         <x:v>AUD</x:v>
       </x:c>
+      <x:c r="C6" s="71"/>
+      <x:c r="D6" s="71"/>
+      <x:c r="E6" s="71"/>
+      <x:c r="F6" s="71"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
+      <x:c r="A7" s="71" t="str">
         <x:v>Units</x:v>
       </x:c>
       <x:c r="B7" s="28" t="str">
         <x:v>Whole dollars</x:v>
       </x:c>
+      <x:c r="C7" s="71"/>
+      <x:c r="D7" s="71"/>
+      <x:c r="E7" s="71"/>
+      <x:c r="F7" s="71"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
+      <x:c r="A8" s="71" t="str">
         <x:v>Forecast start date</x:v>
       </x:c>
       <x:c r="B8" s="29" t="n">
         <x:v>46265</x:v>
       </x:c>
+      <x:c r="C8" s="71"/>
+      <x:c r="D8" s="71"/>
+      <x:c r="E8" s="71"/>
+      <x:c r="F8" s="71"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
+      <x:c r="A9" s="71" t="str">
         <x:v>As-at date</x:v>
       </x:c>
       <x:c r="B9" s="29" t="n">
         <x:v>46271</x:v>
       </x:c>
+      <x:c r="C9" s="71"/>
+      <x:c r="D9" s="71"/>
+      <x:c r="E9" s="71"/>
+      <x:c r="F9" s="71"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
+      <x:c r="A10" s="71" t="str">
         <x:v>Opening cash</x:v>
       </x:c>
       <x:c r="B10" s="30" t="n">
         <x:v>400000</x:v>
       </x:c>
+      <x:c r="C10" s="71"/>
+      <x:c r="D10" s="71"/>
+      <x:c r="E10" s="71"/>
+      <x:c r="F10" s="71"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
+      <x:c r="A11" s="71" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
       <x:c r="B11" s="30" t="n">
         <x:v>100000</x:v>
       </x:c>
+      <x:c r="C11" s="71"/>
+      <x:c r="D11" s="71"/>
+      <x:c r="E11" s="71"/>
+      <x:c r="F11" s="71"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
+      <x:c r="A12" s="71" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
       <x:c r="B12" s="28" t="str">
         <x:v>Base</x:v>
       </x:c>
+      <x:c r="C12" s="71"/>
+      <x:c r="D12" s="71"/>
+      <x:c r="E12" s="71"/>
+      <x:c r="F12" s="71"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="71"/>
+      <x:c r="B13" s="71"/>
+      <x:c r="C13" s="71"/>
+      <x:c r="D13" s="71"/>
+      <x:c r="E13" s="71"/>
+      <x:c r="F13" s="71"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
@@ -2864,8 +3694,10 @@
       <x:c r="E14" s="14" t="str">
         <x:v>Description</x:v>
       </x:c>
+      <x:c r="F14" s="71"/>
     </x:row>
     <x:row r="15">
+      <x:c r="A15" s="71"/>
       <x:c r="B15" s="16" t="str">
         <x:v>Base</x:v>
       </x:c>
@@ -2878,8 +3710,10 @@
       <x:c r="E15" s="16" t="str">
         <x:v>Current operating expectation</x:v>
       </x:c>
+      <x:c r="F15" s="71"/>
     </x:row>
     <x:row r="16">
+      <x:c r="A16" s="71"/>
       <x:c r="B16" s="16" t="str">
         <x:v>Upside</x:v>
       </x:c>
@@ -2892,8 +3726,10 @@
       <x:c r="E16" s="16" t="str">
         <x:v>Stronger receipts and lower selected variable payments</x:v>
       </x:c>
+      <x:c r="F16" s="71"/>
     </x:row>
     <x:row r="17">
+      <x:c r="A17" s="71"/>
       <x:c r="B17" s="16" t="str">
         <x:v>Downside</x:v>
       </x:c>
@@ -2906,14 +3742,27 @@
       <x:c r="E17" s="16" t="str">
         <x:v>Softer receipts and higher selected variable payments</x:v>
       </x:c>
+      <x:c r="F17" s="71"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="71"/>
+      <x:c r="B18" s="71"/>
+      <x:c r="C18" s="71"/>
+      <x:c r="D18" s="71"/>
+      <x:c r="E18" s="71"/>
+      <x:c r="F18" s="71"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" t="str">
+      <x:c r="A19" s="71" t="str">
         <x:v>Liquidity action lead time (weeks)</x:v>
       </x:c>
       <x:c r="B19" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="C19" s="71"/>
+      <x:c r="D19" s="71"/>
+      <x:c r="E19" s="71"/>
+      <x:c r="F19" s="71"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
@@ -3030,8 +3879,42 @@
       <x:c r="N2" s="8"/>
       <x:c r="O2" s="8"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="71"/>
+      <x:c r="B3" s="71"/>
+      <x:c r="C3" s="71"/>
+      <x:c r="D3" s="71"/>
+      <x:c r="E3" s="71"/>
+      <x:c r="F3" s="71"/>
+      <x:c r="G3" s="71"/>
+      <x:c r="H3" s="71"/>
+      <x:c r="I3" s="71"/>
+      <x:c r="J3" s="71"/>
+      <x:c r="K3" s="71"/>
+      <x:c r="L3" s="71"/>
+      <x:c r="M3" s="71"/>
+      <x:c r="N3" s="71"/>
+      <x:c r="O3" s="71"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="71"/>
+      <x:c r="B4" s="71"/>
+      <x:c r="C4" s="71"/>
+      <x:c r="D4" s="71"/>
+      <x:c r="E4" s="71"/>
+      <x:c r="F4" s="71"/>
+      <x:c r="G4" s="71"/>
+      <x:c r="H4" s="71"/>
+      <x:c r="I4" s="71"/>
+      <x:c r="J4" s="71"/>
+      <x:c r="K4" s="71"/>
+      <x:c r="L4" s="71"/>
+      <x:c r="M4" s="71"/>
+      <x:c r="N4" s="71"/>
+      <x:c r="O4" s="71"/>
+    </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
+      <x:c r="A5" s="71" t="str">
         <x:v>Week commencing</x:v>
       </x:c>
       <x:c r="B5" s="34" t="n">
@@ -3086,12 +3969,12 @@
         <x:f>M5+7</x:f>
         <x:v>46349</x:v>
       </x:c>
-      <x:c r="O5" t="str">
+      <x:c r="O5" s="71" t="str">
         <x:v>13-week total / terminal</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
+      <x:c r="A6" s="71" t="str">
         <x:v>Week ending</x:v>
       </x:c>
       <x:c r="B6" s="34" t="n">
@@ -3146,12 +4029,12 @@
         <x:f>N5+6</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="O6" t="str">
+      <x:c r="O6" s="71" t="str">
         <x:v>Week 13 value</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
+      <x:c r="A7" s="71" t="str">
         <x:v>Actual / Forecast</x:v>
       </x:c>
       <x:c r="B7" s="35" t="str">
@@ -3206,7 +4089,24 @@
         <x:f>IF(N6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="O7" t="str"/>
+      <x:c r="O7" s="71" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="71"/>
+      <x:c r="B8" s="71"/>
+      <x:c r="C8" s="71"/>
+      <x:c r="D8" s="71"/>
+      <x:c r="E8" s="71"/>
+      <x:c r="F8" s="71"/>
+      <x:c r="G8" s="71"/>
+      <x:c r="H8" s="71"/>
+      <x:c r="I8" s="71"/>
+      <x:c r="J8" s="71"/>
+      <x:c r="K8" s="71"/>
+      <x:c r="L8" s="71"/>
+      <x:c r="M8" s="71"/>
+      <x:c r="N8" s="71"/>
+      <x:c r="O8" s="71"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
@@ -3228,7 +4128,7 @@
       <x:c r="O9" s="14"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
+      <x:c r="A10" s="71" t="str">
         <x:v>Customer receipts</x:v>
       </x:c>
       <x:c r="B10" s="38" t="n">
@@ -3270,13 +4170,13 @@
       <x:c r="N10" s="38" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="O10" s="39" t="n">
+      <x:c r="O10" s="74" t="n">
         <x:f>SUM(B10:N10)</x:f>
         <x:v>1514000</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
+      <x:c r="A11" s="71" t="str">
         <x:v>Overdue receipts</x:v>
       </x:c>
       <x:c r="B11" s="38" t="n">
@@ -3318,13 +4218,13 @@
       <x:c r="N11" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O11" s="39" t="n">
+      <x:c r="O11" s="74" t="n">
         <x:f>SUM(B11:N11)</x:f>
         <x:v>152000</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
+      <x:c r="A12" s="71" t="str">
         <x:v>Cash / EFTPOS sales</x:v>
       </x:c>
       <x:c r="B12" s="38" t="n">
@@ -3366,13 +4266,13 @@
       <x:c r="N12" s="38" t="n">
         <x:v>22000</x:v>
       </x:c>
-      <x:c r="O12" s="39" t="n">
+      <x:c r="O12" s="74" t="n">
         <x:f>SUM(B12:N12)</x:f>
         <x:v>245000</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="str">
+      <x:c r="A13" s="71" t="str">
         <x:v>GST refunds / credits</x:v>
       </x:c>
       <x:c r="B13" s="38" t="n">
@@ -3414,13 +4314,13 @@
       <x:c r="N13" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O13" s="39" t="n">
+      <x:c r="O13" s="74" t="n">
         <x:f>SUM(B13:N13)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="str">
+      <x:c r="A14" s="71" t="str">
         <x:v>Other operating</x:v>
       </x:c>
       <x:c r="B14" s="38" t="n">
@@ -3462,13 +4362,13 @@
       <x:c r="N14" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O14" s="39" t="n">
+      <x:c r="O14" s="74" t="n">
         <x:f>SUM(B14:N14)</x:f>
         <x:v>52000</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="str">
+      <x:c r="A15" s="71" t="str">
         <x:v>Asset sale proceeds</x:v>
       </x:c>
       <x:c r="B15" s="38" t="n">
@@ -3510,13 +4410,13 @@
       <x:c r="N15" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O15" s="39" t="n">
+      <x:c r="O15" s="74" t="n">
         <x:f>SUM(B15:N15)</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="str">
+      <x:c r="A16" s="71" t="str">
         <x:v>Equity / owner funding</x:v>
       </x:c>
       <x:c r="B16" s="38" t="n">
@@ -3558,13 +4458,13 @@
       <x:c r="N16" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O16" s="39" t="n">
+      <x:c r="O16" s="74" t="n">
         <x:f>SUM(B16:N16)</x:f>
         <x:v>150000</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
+      <x:c r="A17" s="71" t="str">
         <x:v>Loan proceeds</x:v>
       </x:c>
       <x:c r="B17" s="38" t="n">
@@ -3606,13 +4506,13 @@
       <x:c r="N17" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O17" s="39" t="n">
+      <x:c r="O17" s="74" t="n">
         <x:f>SUM(B17:N17)</x:f>
         <x:v>125000</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="str">
+      <x:c r="A18" s="71" t="str">
         <x:v>Scenario receipt adjustment</x:v>
       </x:c>
       <x:c r="B18" s="42" t="n">
@@ -3667,7 +4567,7 @@
         <x:f>IF(N$7="Actual",0,SUM(N10:N12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="39" t="n">
+      <x:c r="O18" s="74" t="n">
         <x:f>SUM(B18:N18)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3734,20 +4634,21 @@
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="39"/>
-      <x:c r="C20" s="39"/>
-      <x:c r="D20" s="39"/>
-      <x:c r="E20" s="39"/>
-      <x:c r="F20" s="39"/>
-      <x:c r="G20" s="39"/>
-      <x:c r="H20" s="39"/>
-      <x:c r="I20" s="39"/>
-      <x:c r="J20" s="39"/>
-      <x:c r="K20" s="39"/>
-      <x:c r="L20" s="39"/>
-      <x:c r="M20" s="39"/>
-      <x:c r="N20" s="39"/>
-      <x:c r="O20" s="39"/>
+      <x:c r="A20" s="71"/>
+      <x:c r="B20" s="74"/>
+      <x:c r="C20" s="74"/>
+      <x:c r="D20" s="74"/>
+      <x:c r="E20" s="74"/>
+      <x:c r="F20" s="74"/>
+      <x:c r="G20" s="74"/>
+      <x:c r="H20" s="74"/>
+      <x:c r="I20" s="74"/>
+      <x:c r="J20" s="74"/>
+      <x:c r="K20" s="74"/>
+      <x:c r="L20" s="74"/>
+      <x:c r="M20" s="74"/>
+      <x:c r="N20" s="74"/>
+      <x:c r="O20" s="74"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
@@ -3769,7 +4670,7 @@
       <x:c r="O21" s="41"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" t="str">
+      <x:c r="A22" s="71" t="str">
         <x:v>Suppliers and inventory</x:v>
       </x:c>
       <x:c r="B22" s="38" t="n">
@@ -3811,13 +4712,13 @@
       <x:c r="N22" s="38" t="n">
         <x:v>90000</x:v>
       </x:c>
-      <x:c r="O22" s="39" t="n">
+      <x:c r="O22" s="74" t="n">
         <x:f>SUM(B22:N22)</x:f>
         <x:v>1266000</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" t="str">
+      <x:c r="A23" s="71" t="str">
         <x:v>Net wages</x:v>
       </x:c>
       <x:c r="B23" s="38" t="n">
@@ -3859,13 +4760,13 @@
       <x:c r="N23" s="38" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="O23" s="39" t="n">
+      <x:c r="O23" s="74" t="n">
         <x:f>SUM(B23:N23)</x:f>
         <x:v>546000</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" t="str">
+      <x:c r="A24" s="71" t="str">
         <x:v>PAYG withholding</x:v>
       </x:c>
       <x:c r="B24" s="38" t="n">
@@ -3907,13 +4808,13 @@
       <x:c r="N24" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O24" s="39" t="n">
+      <x:c r="O24" s="74" t="n">
         <x:f>SUM(B24:N24)</x:f>
         <x:v>156000</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" t="str">
+      <x:c r="A25" s="71" t="str">
         <x:v>Superannuation</x:v>
       </x:c>
       <x:c r="B25" s="38" t="n">
@@ -3955,13 +4856,13 @@
       <x:c r="N25" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O25" s="39" t="n">
+      <x:c r="O25" s="74" t="n">
         <x:f>SUM(B25:N25)</x:f>
         <x:v>78000</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" t="str">
+      <x:c r="A26" s="71" t="str">
         <x:v>Payroll tax / workers compensation</x:v>
       </x:c>
       <x:c r="B26" s="38" t="n">
@@ -4003,13 +4904,13 @@
       <x:c r="N26" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O26" s="39" t="n">
+      <x:c r="O26" s="74" t="n">
         <x:f>SUM(B26:N26)</x:f>
         <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" t="str">
+      <x:c r="A27" s="71" t="str">
         <x:v>Rent</x:v>
       </x:c>
       <x:c r="B27" s="38" t="n">
@@ -4051,13 +4952,13 @@
       <x:c r="N27" s="38" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="O27" s="39" t="n">
+      <x:c r="O27" s="74" t="n">
         <x:f>SUM(B27:N27)</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" t="str">
+      <x:c r="A28" s="71" t="str">
         <x:v>Utilities</x:v>
       </x:c>
       <x:c r="B28" s="38" t="n">
@@ -4099,13 +5000,13 @@
       <x:c r="N28" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O28" s="39" t="n">
+      <x:c r="O28" s="74" t="n">
         <x:f>SUM(B28:N28)</x:f>
         <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="str">
+      <x:c r="A29" s="71" t="str">
         <x:v>Insurance</x:v>
       </x:c>
       <x:c r="B29" s="38" t="n">
@@ -4147,13 +5048,13 @@
       <x:c r="N29" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O29" s="39" t="n">
+      <x:c r="O29" s="74" t="n">
         <x:f>SUM(B29:N29)</x:f>
         <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" t="str">
+      <x:c r="A30" s="71" t="str">
         <x:v>Software and subscriptions</x:v>
       </x:c>
       <x:c r="B30" s="38" t="n">
@@ -4195,13 +5096,13 @@
       <x:c r="N30" s="38" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="O30" s="39" t="n">
+      <x:c r="O30" s="74" t="n">
         <x:f>SUM(B30:N30)</x:f>
         <x:v>39000</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" t="str">
+      <x:c r="A31" s="71" t="str">
         <x:v>Marketing</x:v>
       </x:c>
       <x:c r="B31" s="38" t="n">
@@ -4243,13 +5144,13 @@
       <x:c r="N31" s="38" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O31" s="39" t="n">
+      <x:c r="O31" s="74" t="n">
         <x:f>SUM(B31:N31)</x:f>
         <x:v>78000</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" t="str">
+      <x:c r="A32" s="71" t="str">
         <x:v>Professional services</x:v>
       </x:c>
       <x:c r="B32" s="38" t="n">
@@ -4291,13 +5192,13 @@
       <x:c r="N32" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O32" s="39" t="n">
+      <x:c r="O32" s="74" t="n">
         <x:f>SUM(B32:N32)</x:f>
         <x:v>24000</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" t="str">
+      <x:c r="A33" s="71" t="str">
         <x:v>Freight, vehicles and travel</x:v>
       </x:c>
       <x:c r="B33" s="38" t="n">
@@ -4339,13 +5240,13 @@
       <x:c r="N33" s="38" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="O33" s="39" t="n">
+      <x:c r="O33" s="74" t="n">
         <x:f>SUM(B33:N33)</x:f>
         <x:v>130000</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" t="str">
+      <x:c r="A34" s="71" t="str">
         <x:v>GST / BAS payments</x:v>
       </x:c>
       <x:c r="B34" s="38" t="n">
@@ -4387,13 +5288,13 @@
       <x:c r="N34" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O34" s="39" t="n">
+      <x:c r="O34" s="74" t="n">
         <x:f>SUM(B34:N34)</x:f>
         <x:v>45000</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" t="str">
+      <x:c r="A35" s="71" t="str">
         <x:v>PAYG income tax instalments</x:v>
       </x:c>
       <x:c r="B35" s="38" t="n">
@@ -4435,13 +5336,13 @@
       <x:c r="N35" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O35" s="39" t="n">
+      <x:c r="O35" s="74" t="n">
         <x:f>SUM(B35:N35)</x:f>
         <x:v>18000</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" t="str">
+      <x:c r="A36" s="71" t="str">
         <x:v>FBT / other tax</x:v>
       </x:c>
       <x:c r="B36" s="38" t="n">
@@ -4483,13 +5384,13 @@
       <x:c r="N36" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O36" s="39" t="n">
+      <x:c r="O36" s="74" t="n">
         <x:f>SUM(B36:N36)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" t="str">
+      <x:c r="A37" s="71" t="str">
         <x:v>Interest and bank fees</x:v>
       </x:c>
       <x:c r="B37" s="38" t="n">
@@ -4531,13 +5432,13 @@
       <x:c r="N37" s="38" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O37" s="39" t="n">
+      <x:c r="O37" s="74" t="n">
         <x:f>SUM(B37:N37)</x:f>
         <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" t="str">
+      <x:c r="A38" s="71" t="str">
         <x:v>Loan principal</x:v>
       </x:c>
       <x:c r="B38" s="38" t="n">
@@ -4579,13 +5480,13 @@
       <x:c r="N38" s="38" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O38" s="39" t="n">
+      <x:c r="O38" s="74" t="n">
         <x:f>SUM(B38:N38)</x:f>
         <x:v>48000</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" t="str">
+      <x:c r="A39" s="71" t="str">
         <x:v>Capital expenditure</x:v>
       </x:c>
       <x:c r="B39" s="38" t="n">
@@ -4627,13 +5528,13 @@
       <x:c r="N39" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O39" s="39" t="n">
+      <x:c r="O39" s="74" t="n">
         <x:f>SUM(B39:N39)</x:f>
         <x:v>65000</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" t="str">
+      <x:c r="A40" s="71" t="str">
         <x:v>Dividends / distributions</x:v>
       </x:c>
       <x:c r="B40" s="38" t="n">
@@ -4675,13 +5576,13 @@
       <x:c r="N40" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O40" s="39" t="n">
+      <x:c r="O40" s="74" t="n">
         <x:f>SUM(B40:N40)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" t="str">
+      <x:c r="A41" s="71" t="str">
         <x:v>Other operating</x:v>
       </x:c>
       <x:c r="B41" s="38" t="n">
@@ -4723,13 +5624,13 @@
       <x:c r="N41" s="38" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="O41" s="39" t="n">
+      <x:c r="O41" s="74" t="n">
         <x:f>SUM(B41:N41)</x:f>
         <x:v>65000</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" t="str">
+      <x:c r="A42" s="71" t="str">
         <x:v>Scenario payment adjustment</x:v>
       </x:c>
       <x:c r="B42" s="42" t="n">
@@ -4784,7 +5685,7 @@
         <x:f>IF(N$7="Actual",0,SUM(N22,N31,N33,N41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O42" s="39" t="n">
+      <x:c r="O42" s="74" t="n">
         <x:f>SUM(B42:N42)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -4851,20 +5752,21 @@
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="B44" s="39"/>
-      <x:c r="C44" s="39"/>
-      <x:c r="D44" s="39"/>
-      <x:c r="E44" s="39"/>
-      <x:c r="F44" s="39"/>
-      <x:c r="G44" s="39"/>
-      <x:c r="H44" s="39"/>
-      <x:c r="I44" s="39"/>
-      <x:c r="J44" s="39"/>
-      <x:c r="K44" s="39"/>
-      <x:c r="L44" s="39"/>
-      <x:c r="M44" s="39"/>
-      <x:c r="N44" s="39"/>
-      <x:c r="O44" s="39"/>
+      <x:c r="A44" s="71"/>
+      <x:c r="B44" s="74"/>
+      <x:c r="C44" s="74"/>
+      <x:c r="D44" s="74"/>
+      <x:c r="E44" s="74"/>
+      <x:c r="F44" s="74"/>
+      <x:c r="G44" s="74"/>
+      <x:c r="H44" s="74"/>
+      <x:c r="I44" s="74"/>
+      <x:c r="J44" s="74"/>
+      <x:c r="K44" s="74"/>
+      <x:c r="L44" s="74"/>
+      <x:c r="M44" s="74"/>
+      <x:c r="N44" s="74"/>
+      <x:c r="O44" s="74"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="14" t="str">
@@ -4886,7 +5788,7 @@
       <x:c r="O45" s="41"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" t="str">
+      <x:c r="A46" s="71" t="str">
         <x:v>Opening cash balance</x:v>
       </x:c>
       <x:c r="B46" s="44" t="n">
@@ -4941,13 +5843,13 @@
         <x:f>M48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="O46" s="39" t="n">
+      <x:c r="O46" s="74" t="n">
         <x:f>N46</x:f>
         <x:v>82000</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" t="str">
+      <x:c r="A47" s="71" t="str">
         <x:v>Net cash movement</x:v>
       </x:c>
       <x:c r="B47" s="42" t="n">
@@ -5002,7 +5904,7 @@
         <x:f>N19-N43</x:f>
         <x:v>-51000</x:v>
       </x:c>
-      <x:c r="O47" s="39" t="n">
+      <x:c r="O47" s="74" t="n">
         <x:f>SUM(B47:N47)</x:f>
         <x:v>-369000</x:v>
       </x:c>
@@ -5069,7 +5971,7 @@
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" t="str">
+      <x:c r="A49" s="71" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
       <x:c r="B49" s="44" t="n">
@@ -5124,7 +6026,7 @@
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="O49" s="39" t="n">
+      <x:c r="O49" s="74" t="n">
         <x:f>N49</x:f>
         <x:v>100000</x:v>
       </x:c>
@@ -5191,7 +6093,7 @@
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" t="str">
+      <x:c r="A51" s="71" t="str">
         <x:v>Liquidity status</x:v>
       </x:c>
       <x:c r="B51" s="17" t="str">
@@ -5246,7 +6148,7 @@
         <x:f>IF(N48&lt;N49,"BELOW BUFFER",IF(N48&lt;=N49*1.25,"WATCH","OK"))</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="O51" t="str">
+      <x:c r="O51" s="71" t="str">
         <x:f>N51</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
@@ -5268,7 +6170,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb3415d0a01b41c9"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62ee5fc974354fc5"/>
 </x:worksheet>
 </file>
 
@@ -5327,6 +6229,22 @@
       <x:c r="L2" s="8"/>
       <x:c r="M2" s="8"/>
       <x:c r="N2" s="8"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="71"/>
+      <x:c r="B3" s="71"/>
+      <x:c r="C3" s="71"/>
+      <x:c r="D3" s="71"/>
+      <x:c r="E3" s="71"/>
+      <x:c r="F3" s="71"/>
+      <x:c r="G3" s="71"/>
+      <x:c r="H3" s="71"/>
+      <x:c r="I3" s="71"/>
+      <x:c r="J3" s="71"/>
+      <x:c r="K3" s="71"/>
+      <x:c r="L3" s="71"/>
+      <x:c r="M3" s="71"/>
+      <x:c r="N3" s="71"/>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
       <x:c r="A4" s="27" t="str">
@@ -5946,6 +6864,16 @@
       <x:c r="G2" s="8"/>
       <x:c r="H2" s="8"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="71"/>
+      <x:c r="B3" s="71"/>
+      <x:c r="C3" s="71"/>
+      <x:c r="D3" s="71"/>
+      <x:c r="E3" s="71"/>
+      <x:c r="F3" s="71"/>
+      <x:c r="G3" s="71"/>
+      <x:c r="H3" s="71"/>
+    </x:row>
     <x:row r="4">
       <x:c r="A4" s="51" t="str">
         <x:v>MODEL STATUS</x:v>
@@ -5962,6 +6890,29 @@
         <x:f>IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"BELOW BUFFER")&gt;0,"ACTION REQUIRED",IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"WATCH")&gt;0,"WATCH","OK"))</x:f>
         <x:v>ACTION REQUIRED</x:v>
       </x:c>
+      <x:c r="F4" s="71"/>
+      <x:c r="G4" s="71"/>
+      <x:c r="H4" s="71"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="71"/>
+      <x:c r="B5" s="71"/>
+      <x:c r="C5" s="71"/>
+      <x:c r="D5" s="71"/>
+      <x:c r="E5" s="71"/>
+      <x:c r="F5" s="71"/>
+      <x:c r="G5" s="71"/>
+      <x:c r="H5" s="71"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="71"/>
+      <x:c r="B6" s="71"/>
+      <x:c r="C6" s="71"/>
+      <x:c r="D6" s="71"/>
+      <x:c r="E6" s="71"/>
+      <x:c r="F6" s="71"/>
+      <x:c r="G6" s="71"/>
+      <x:c r="H6" s="71"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
@@ -5990,274 +6941,314 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="15" t="str">
+      <x:c r="A8" s="73" t="str">
         <x:v>Exactly 13 forecast weeks</x:v>
       </x:c>
-      <x:c r="B8" s="52" t="n">
+      <x:c r="B8" s="75" t="n">
         <x:f>COLUMNS('13-Week Forecast'!$B$5:$N$5)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="52" t="n">
+      <x:c r="C8" s="75" t="n">
         <x:f>13</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D8" s="52" t="n">
+      <x:c r="D8" s="75" t="n">
         <x:f>B8-C8</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E8" s="52" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="str">
+      <x:c r="E8" s="75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="73" t="str">
         <x:f>IF(ABS(D8)&lt;=E8,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="str">
+      <x:c r="G8" s="73" t="str">
         <x:v>13-Week Forecast!B5:N5</x:v>
       </x:c>
-      <x:c r="H8" s="15" t="str">
+      <x:c r="H8" s="73" t="str">
         <x:v>The weekly horizon must contain exactly 13 columns.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="15" t="str">
+      <x:c r="A9" s="73" t="str">
         <x:v>Forecast starts Monday</x:v>
       </x:c>
-      <x:c r="B9" s="52" t="n">
+      <x:c r="B9" s="75" t="n">
         <x:f>WEEKDAY('Assumptions'!$B$8,2)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C9" s="52" t="n">
+      <x:c r="C9" s="75" t="n">
         <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D9" s="52" t="n">
+      <x:c r="D9" s="75" t="n">
         <x:f>B9-C9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E9" s="52" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="str">
+      <x:c r="E9" s="75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="73" t="str">
         <x:f>IF(ABS(D9)&lt;=E9,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="str">
+      <x:c r="G9" s="73" t="str">
         <x:v>Assumptions!B8</x:v>
       </x:c>
-      <x:c r="H9" s="15" t="str">
+      <x:c r="H9" s="73" t="str">
         <x:v>Forecast start date must be a Monday.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="15" t="str">
+      <x:c r="A10" s="73" t="str">
         <x:v>Selected scenario recognised</x:v>
       </x:c>
-      <x:c r="B10" s="52" t="n">
+      <x:c r="B10" s="75" t="n">
         <x:f>COUNTIF('Assumptions'!$B$15:$B$17,'Assumptions'!$B$12)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="52" t="n">
+      <x:c r="C10" s="75" t="n">
         <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D10" s="52" t="n">
+      <x:c r="D10" s="75" t="n">
         <x:f>B10-C10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="52" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="str">
+      <x:c r="E10" s="75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="73" t="str">
         <x:f>IF(ABS(D10)&lt;=E10,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="str">
+      <x:c r="G10" s="73" t="str">
         <x:v>Assumptions!B12</x:v>
       </x:c>
-      <x:c r="H10" s="15" t="str">
+      <x:c r="H10" s="73" t="str">
         <x:v>Select Base, Upside or Downside.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="15" t="str">
+      <x:c r="A11" s="73" t="str">
         <x:v>Week 1 opening cash ties</x:v>
       </x:c>
-      <x:c r="B11" s="53" t="n">
+      <x:c r="B11" s="76" t="n">
         <x:f>'13-Week Forecast'!$B$46</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="C11" s="53" t="n">
+      <x:c r="C11" s="76" t="n">
         <x:f>'Assumptions'!$B$10</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="D11" s="52" t="n">
+      <x:c r="D11" s="75" t="n">
         <x:f>B11-C11</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="52" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="str">
+      <x:c r="E11" s="75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="73" t="str">
         <x:f>IF(ABS(D11)&lt;=E11,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="str">
+      <x:c r="G11" s="73" t="str">
         <x:v>13-Week Forecast!B46</x:v>
       </x:c>
-      <x:c r="H11" s="15" t="str">
+      <x:c r="H11" s="73" t="str">
         <x:v>Week 1 opening cash must link to the control panel.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="15" t="str">
+      <x:c r="A12" s="73" t="str">
         <x:v>Weekly cash roll-forward equations</x:v>
       </x:c>
-      <x:c r="B12" s="52" t="n">
+      <x:c r="B12" s="75" t="n">
         <x:f>MAX(ABS('13-Week Forecast'!$B$48-'13-Week Forecast'!$B$46-'13-Week Forecast'!$B$47),ABS('13-Week Forecast'!$C$48-'13-Week Forecast'!$C$46-'13-Week Forecast'!$C$47),ABS('13-Week Forecast'!$D$48-'13-Week Forecast'!$D$46-'13-Week Forecast'!$D$47),ABS('13-Week Forecast'!$E$48-'13-Week Forecast'!$E$46-'13-Week Forecast'!$E$47),ABS('13-Week Forecast'!$F$48-'13-Week Forecast'!$F$46-'13-Week Forecast'!$F$47),ABS('13-Week Forecast'!$G$48-'13-Week Forecast'!$G$46-'13-Week Forecast'!$G$47),ABS('13-Week Forecast'!$H$48-'13-Week Forecast'!$H$46-'13-Week Forecast'!$H$47),ABS('13-Week Forecast'!$I$48-'13-Week Forecast'!$I$46-'13-Week Forecast'!$I$47),ABS('13-Week Forecast'!$J$48-'13-Week Forecast'!$J$46-'13-Week Forecast'!$J$47),ABS('13-Week Forecast'!$K$48-'13-Week Forecast'!$K$46-'13-Week Forecast'!$K$47),ABS('13-Week Forecast'!$L$48-'13-Week Forecast'!$L$46-'13-Week Forecast'!$L$47),ABS('13-Week Forecast'!$M$48-'13-Week Forecast'!$M$46-'13-Week Forecast'!$M$47),ABS('13-Week Forecast'!$N$48-'13-Week Forecast'!$N$46-'13-Week Forecast'!$N$47),ABS('13-Week Forecast'!$C$46-'13-Week Forecast'!$B$48),ABS('13-Week Forecast'!$D$46-'13-Week Forecast'!$C$48),ABS('13-Week Forecast'!$E$46-'13-Week Forecast'!$D$48),ABS('13-Week Forecast'!$F$46-'13-Week Forecast'!$E$48),ABS('13-Week Forecast'!$G$46-'13-Week Forecast'!$F$48),ABS('13-Week Forecast'!$H$46-'13-Week Forecast'!$G$48),ABS('13-Week Forecast'!$I$46-'13-Week Forecast'!$H$48),ABS('13-Week Forecast'!$J$46-'13-Week Forecast'!$I$48),ABS('13-Week Forecast'!$K$46-'13-Week Forecast'!$J$48),ABS('13-Week Forecast'!$L$46-'13-Week Forecast'!$K$48),ABS('13-Week Forecast'!$M$46-'13-Week Forecast'!$L$48),ABS('13-Week Forecast'!$N$46-'13-Week Forecast'!$M$48))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C12" s="52" t="n">
+      <x:c r="C12" s="75" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="52" t="n">
+      <x:c r="D12" s="75" t="n">
         <x:f>B12-C12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="52" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="str">
+      <x:c r="E12" s="75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="73" t="str">
         <x:f>IF(ABS(D12)&lt;=E12,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="str">
+      <x:c r="G12" s="73" t="str">
         <x:v>13-Week Forecast!B46:N48</x:v>
       </x:c>
-      <x:c r="H12" s="15" t="str">
+      <x:c r="H12" s="73" t="str">
         <x:v>Each close must equal opening plus net movement; each opening after Week 1 must equal the prior close.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="15" t="str">
+      <x:c r="A13" s="73" t="str">
         <x:v>Cash receipt totals reconcile</x:v>
       </x:c>
-      <x:c r="B13" s="52" t="n">
+      <x:c r="B13" s="75" t="n">
         <x:f>MAX(ABS('13-Week Forecast'!$B$19-SUM('13-Week Forecast'!$B$10:$B$18)),ABS('13-Week Forecast'!$C$19-SUM('13-Week Forecast'!$C$10:$C$18)),ABS('13-Week Forecast'!$D$19-SUM('13-Week Forecast'!$D$10:$D$18)),ABS('13-Week Forecast'!$E$19-SUM('13-Week Forecast'!$E$10:$E$18)),ABS('13-Week Forecast'!$F$19-SUM('13-Week Forecast'!$F$10:$F$18)),ABS('13-Week Forecast'!$G$19-SUM('13-Week Forecast'!$G$10:$G$18)),ABS('13-Week Forecast'!$H$19-SUM('13-Week Forecast'!$H$10:$H$18)),ABS('13-Week Forecast'!$I$19-SUM('13-Week Forecast'!$I$10:$I$18)),ABS('13-Week Forecast'!$J$19-SUM('13-Week Forecast'!$J$10:$J$18)),ABS('13-Week Forecast'!$K$19-SUM('13-Week Forecast'!$K$10:$K$18)),ABS('13-Week Forecast'!$L$19-SUM('13-Week Forecast'!$L$10:$L$18)),ABS('13-Week Forecast'!$M$19-SUM('13-Week Forecast'!$M$10:$M$18)),ABS('13-Week Forecast'!$N$19-SUM('13-Week Forecast'!$N$10:$N$18)))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C13" s="52" t="n">
+      <x:c r="C13" s="75" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="52" t="n">
+      <x:c r="D13" s="75" t="n">
         <x:f>B13-C13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="52" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="str">
+      <x:c r="E13" s="75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="73" t="str">
         <x:f>IF(ABS(D13)&lt;=E13,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="str">
+      <x:c r="G13" s="73" t="str">
         <x:v>13-Week Forecast!B19:N19</x:v>
       </x:c>
-      <x:c r="H13" s="15" t="str">
+      <x:c r="H13" s="73" t="str">
         <x:v>Maximum weekly difference; includes the selected-scenario receipt adjustment.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="15" t="str">
+      <x:c r="A14" s="73" t="str">
         <x:v>Cash payment totals reconcile</x:v>
       </x:c>
-      <x:c r="B14" s="52" t="n">
+      <x:c r="B14" s="75" t="n">
         <x:f>MAX(ABS('13-Week Forecast'!$B$43-SUM('13-Week Forecast'!$B$22:$B$42)),ABS('13-Week Forecast'!$C$43-SUM('13-Week Forecast'!$C$22:$C$42)),ABS('13-Week Forecast'!$D$43-SUM('13-Week Forecast'!$D$22:$D$42)),ABS('13-Week Forecast'!$E$43-SUM('13-Week Forecast'!$E$22:$E$42)),ABS('13-Week Forecast'!$F$43-SUM('13-Week Forecast'!$F$22:$F$42)),ABS('13-Week Forecast'!$G$43-SUM('13-Week Forecast'!$G$22:$G$42)),ABS('13-Week Forecast'!$H$43-SUM('13-Week Forecast'!$H$22:$H$42)),ABS('13-Week Forecast'!$I$43-SUM('13-Week Forecast'!$I$22:$I$42)),ABS('13-Week Forecast'!$J$43-SUM('13-Week Forecast'!$J$22:$J$42)),ABS('13-Week Forecast'!$K$43-SUM('13-Week Forecast'!$K$22:$K$42)),ABS('13-Week Forecast'!$L$43-SUM('13-Week Forecast'!$L$22:$L$42)),ABS('13-Week Forecast'!$M$43-SUM('13-Week Forecast'!$M$22:$M$42)),ABS('13-Week Forecast'!$N$43-SUM('13-Week Forecast'!$N$22:$N$42)))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C14" s="52" t="n">
+      <x:c r="C14" s="75" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="52" t="n">
+      <x:c r="D14" s="75" t="n">
         <x:f>B14-C14</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="52" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="str">
+      <x:c r="E14" s="75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="73" t="str">
         <x:f>IF(ABS(D14)&lt;=E14,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="str">
+      <x:c r="G14" s="73" t="str">
         <x:v>13-Week Forecast!B43:N43</x:v>
       </x:c>
-      <x:c r="H14" s="15" t="str">
+      <x:c r="H14" s="73" t="str">
         <x:v>Maximum weekly difference; includes the selected-scenario payment adjustment.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="15" t="str">
+      <x:c r="A15" s="73" t="str">
         <x:v>Week 13 closing cash equation</x:v>
       </x:c>
-      <x:c r="B15" s="53" t="n">
+      <x:c r="B15" s="76" t="n">
         <x:f>'13-Week Forecast'!$N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="C15" s="53" t="n">
+      <x:c r="C15" s="76" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!$B$47:$N$47)</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D15" s="52" t="n">
+      <x:c r="D15" s="75" t="n">
         <x:f>B15-C15</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="52" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="str">
+      <x:c r="E15" s="75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="73" t="str">
         <x:f>IF(ABS(D15)&lt;=E15,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="str">
+      <x:c r="G15" s="73" t="str">
         <x:v>13-Week Forecast!N48</x:v>
       </x:c>
-      <x:c r="H15" s="15" t="str">
+      <x:c r="H15" s="73" t="str">
         <x:v>Week 13 close must equal opening cash plus cumulative net movement.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="15" t="str">
+      <x:c r="A16" s="73" t="str">
         <x:v>Formula-error count</x:v>
       </x:c>
-      <x:c r="B16" s="52" t="n">
+      <x:c r="B16" s="75" t="n">
         <x:f>SUMPRODUCT(--ISERROR('Assumptions'!$B$5:$E$19))+SUMPRODUCT(--ISERROR('13-Week Forecast'!$B$5:$O$51))+SUMPRODUCT(--ISERROR('Weekly Review'!$A$4:$N$18))+SUMPRODUCT(--ISERROR('Dashboard'!$A$6:$J$30))+SUMPRODUCT(--ISERROR('Dashboard'!$P$4:$S$49))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C16" s="52" t="n">
+      <x:c r="C16" s="75" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="52" t="n">
+      <x:c r="D16" s="75" t="n">
         <x:f>B16-C16</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="52" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="str">
+      <x:c r="E16" s="75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="73" t="str">
         <x:f>IF(ABS(D16)&lt;=E16,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="str">
+      <x:c r="G16" s="73" t="str">
         <x:v>Assumptions, Forecast, Weekly Review and Dashboard</x:v>
       </x:c>
-      <x:c r="H16" s="15" t="str">
+      <x:c r="H16" s="73" t="str">
         <x:v>Any formula error in the model ranges fails this check.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="71"/>
+      <x:c r="B17" s="71"/>
+      <x:c r="C17" s="71"/>
+      <x:c r="D17" s="71"/>
+      <x:c r="E17" s="71"/>
+      <x:c r="F17" s="71"/>
+      <x:c r="G17" s="71"/>
+      <x:c r="H17" s="71"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="71"/>
+      <x:c r="B18" s="71"/>
+      <x:c r="C18" s="71"/>
+      <x:c r="D18" s="71"/>
+      <x:c r="E18" s="71"/>
+      <x:c r="F18" s="71"/>
+      <x:c r="G18" s="71"/>
+      <x:c r="H18" s="71"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="71"/>
+      <x:c r="B19" s="71"/>
+      <x:c r="C19" s="71"/>
+      <x:c r="D19" s="71"/>
+      <x:c r="E19" s="71"/>
+      <x:c r="F19" s="71"/>
+      <x:c r="G19" s="71"/>
+      <x:c r="H19" s="71"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="71"/>
+      <x:c r="B20" s="71"/>
+      <x:c r="C20" s="71"/>
+      <x:c r="D20" s="71"/>
+      <x:c r="E20" s="71"/>
+      <x:c r="F20" s="71"/>
+      <x:c r="G20" s="71"/>
+      <x:c r="H20" s="71"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
@@ -6278,6 +7269,8 @@
       <x:c r="F21" s="14" t="str">
         <x:v>Planning treatment</x:v>
       </x:c>
+      <x:c r="G21" s="71"/>
+      <x:c r="H21" s="71"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="55" t="str">
@@ -6298,6 +7291,8 @@
       <x:c r="F22" s="55" t="str">
         <x:v>Keep tax classifications user-confirmed.</x:v>
       </x:c>
+      <x:c r="G22" s="71"/>
+      <x:c r="H22" s="71"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="55" t="str">
@@ -6318,6 +7313,8 @@
       <x:c r="F23" s="55" t="str">
         <x:v>Use issued BAS and user-entered dates.</x:v>
       </x:c>
+      <x:c r="G23" s="71"/>
+      <x:c r="H23" s="71"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="55" t="str">
@@ -6338,6 +7335,8 @@
       <x:c r="F24" s="55" t="str">
         <x:v>Keep payment dates user-entered and confirmed.</x:v>
       </x:c>
+      <x:c r="G24" s="71"/>
+      <x:c r="H24" s="71"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="55" t="str">
@@ -6358,6 +7357,8 @@
       <x:c r="F25" s="55" t="str">
         <x:v>Weekly super is illustrative FP&amp;A input.</x:v>
       </x:c>
+      <x:c r="G25" s="71"/>
+      <x:c r="H25" s="71"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="55" t="str">
@@ -6378,6 +7379,18 @@
       <x:c r="F26" s="55" t="str">
         <x:v>Illustrative forecast starts after the July 2026 transition.</x:v>
       </x:c>
+      <x:c r="G26" s="71"/>
+      <x:c r="H26" s="71"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="71"/>
+      <x:c r="B27" s="71"/>
+      <x:c r="C27" s="71"/>
+      <x:c r="D27" s="71"/>
+      <x:c r="E27" s="71"/>
+      <x:c r="F27" s="71"/>
+      <x:c r="G27" s="71"/>
+      <x:c r="H27" s="71"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="58" t="str">

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rb46856e0cd274e1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="Rf51f7fc7c7ac4703"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="R09e2d2a5fbda4d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="Rdff7daedb25c448a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="Rda7868aea9f24915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R3349cf15cb6b4e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R684e3a83283d4fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" r:id="R7800141f1d67452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" r:id="Rd14f3bcb9f50434c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-Week Forecast" sheetId="4" r:id="R678c6243fa8c4a62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Review" sheetId="5" r:id="R9058f1779f6646a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks &amp; Sources" sheetId="6" r:id="R79c588e19c574c44"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="CashFlowScenario">'Assumptions'!$B$12</x:definedName>
@@ -20,10 +20,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={84D266F6-19BA-B47D-5D1E-5574E3244C5E}</x:author>
-    <x:author>tc={EB8A6292-8349-BCED-0B6A-820E09C1CE7C}</x:author>
-    <x:author>tc={F2C7C3A4-FBBA-3A12-EE58-6838DD9AE503}</x:author>
-    <x:author>tc={72F653C9-5555-6279-61F6-5B5AB1783FF8}</x:author>
+    <x:author>tc={1CA3A93B-3ADC-827F-8CEE-A811705E1D1F}</x:author>
+    <x:author>tc={C97139E3-0479-A622-290F-CDB6923A5A0F}</x:author>
+    <x:author>tc={D5F90669-03C7-33D3-694B-C09DFC28185D}</x:author>
+    <x:author>tc={DBEFEBE9-FE43-5AD0-8C78-F63EFF1E6BF6}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -233,7 +233,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="77">
+  <x:cellXfs count="81">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -253,6 +253,7 @@
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -279,6 +280,7 @@
     <x:xf numFmtId="201" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="203" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -297,7 +299,6 @@
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -350,7 +351,16 @@
     <x:xf numFmtId="201" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -367,7 +377,7 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="28">
+  <x:dxfs count="34">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -498,6 +508,39 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5C2D91"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDED9E8"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -663,6 +706,39 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF008000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC00000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF5C2D91"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDED9E8"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -1038,7 +1114,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8d359760a76540fd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4724ee4aaee4ff7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1068,7 +1144,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R85f1f962974a472b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd9a64b3d55294531"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1079,7 +1155,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}"/>
+  <xltc:person displayName="User" id="{D4177B1A-E9BC-42BA-BE25-E272547D6545}"/>
 </xltc:personList>
 </file>
 
@@ -1276,16 +1352,16 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-26T17:04:38.821" personId="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}" id="{84D266F6-19BA-B47D-5D1E-5574E3244C5E}">
+  <xltc:threadedComment ref="B18" dT="2026-08-26T17:21:27.47" personId="{D4177B1A-E9BC-42BA-BE25-E272547D6545}" id="{1CA3A93B-3ADC-827F-8CEE-A811705E1D1F}">
     <xltc:text>Scenario receipt adjustment applies the selected scenario only to current customer receipts, overdue receipts and cash / EFTPOS sales. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B42" dT="2026-08-26T17:04:38.821" personId="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}" id="{EB8A6292-8349-BCED-0B6A-820E09C1CE7C}">
+  <xltc:threadedComment ref="B42" dT="2026-08-26T17:21:27.47" personId="{D4177B1A-E9BC-42BA-BE25-E272547D6545}" id="{C97139E3-0479-A622-290F-CDB6923A5A0F}">
     <xltc:text>Scenario payment adjustment applies the selected scenario only to suppliers, marketing, freight / vehicles / travel and other operating payments. Week 1 is Actual, so the adjustment is zero.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B34" dT="2026-08-26T17:04:38.821" personId="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}" id="{F2C7C3A4-FBBA-3A12-EE58-6838DD9AE503}">
+  <xltc:threadedComment ref="B34" dT="2026-08-26T17:21:27.47" personId="{D4177B1A-E9BC-42BA-BE25-E272547D6545}" id="{D5F90669-03C7-33D3-694B-C09DFC28185D}">
     <xltc:text>GST / BAS cash timing is illustrative. Confirm your entity's reporting cycle, due date and payment arrangement before relying on this forecast.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B35" dT="2026-08-26T17:04:38.821" personId="{602EEDB7-EB17-4906-A8BC-ABFEC588047C}" id="{72F653C9-5555-6279-61F6-5B5AB1783FF8}">
+  <xltc:threadedComment ref="B35" dT="2026-08-26T17:21:27.47" personId="{D4177B1A-E9BC-42BA-BE25-E272547D6545}" id="{DBEFEBE9-FE43-5AD0-8C78-F63EFF1E6BF6}">
     <xltc:text>PAYG income-tax instalment timing and amount are illustrative. Confirm the applicable ATO notice and adviser instructions.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -1330,14 +1406,14 @@
       <x:c r="H2" s="8"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="71"/>
-      <x:c r="B3" s="71"/>
-      <x:c r="C3" s="71"/>
-      <x:c r="D3" s="71"/>
-      <x:c r="E3" s="71"/>
-      <x:c r="F3" s="71"/>
-      <x:c r="G3" s="71"/>
-      <x:c r="H3" s="71"/>
+      <x:c r="A3" s="75"/>
+      <x:c r="B3" s="75"/>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+      <x:c r="F3" s="75"/>
+      <x:c r="G3" s="75"/>
+      <x:c r="H3" s="75"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="str">
@@ -1352,330 +1428,390 @@
       <x:c r="H4" s="10"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="71"/>
-      <x:c r="B5" s="71"/>
-      <x:c r="C5" s="71"/>
-      <x:c r="D5" s="71"/>
-      <x:c r="E5" s="71"/>
-      <x:c r="F5" s="71"/>
-      <x:c r="G5" s="71"/>
-      <x:c r="H5" s="71"/>
+      <x:c r="A5" s="75"/>
+      <x:c r="B5" s="75"/>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="75"/>
+      <x:c r="E5" s="75"/>
+      <x:c r="F5" s="75"/>
+      <x:c r="G5" s="75"/>
+      <x:c r="H5" s="75"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="71" t="str">
+      <x:c r="A6" s="75" t="str">
         <x:v>Version</x:v>
       </x:c>
-      <x:c r="B6" s="71" t="str">
-        <x:v>Release 1.1</x:v>
-      </x:c>
-      <x:c r="C6" s="71"/>
-      <x:c r="D6" s="23" t="str">
+      <x:c r="B6" s="75" t="str">
+        <x:v>Release 1.2</x:v>
+      </x:c>
+      <x:c r="C6" s="75"/>
+      <x:c r="D6" s="24" t="str">
         <x:v>Workbook sheets</x:v>
       </x:c>
-      <x:c r="E6" s="23"/>
-      <x:c r="F6" s="23"/>
-      <x:c r="G6" s="23"/>
-      <x:c r="H6" s="23"/>
+      <x:c r="E6" s="24"/>
+      <x:c r="F6" s="24"/>
+      <x:c r="G6" s="24"/>
+      <x:c r="H6" s="24"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="71" t="str">
+      <x:c r="A7" s="75" t="str">
         <x:v>Prepared date</x:v>
       </x:c>
-      <x:c r="B7" s="72" t="n">
-        <x:v>46260</x:v>
-      </x:c>
-      <x:c r="C7" s="71"/>
+      <x:c r="B7" s="76" t="n">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C7" s="75"/>
       <x:c r="D7" s="1" t="str">
         <x:v>Dashboard</x:v>
       </x:c>
-      <x:c r="E7" s="71"/>
-      <x:c r="F7" s="71"/>
-      <x:c r="G7" s="71"/>
-      <x:c r="H7" s="71"/>
+      <x:c r="E7" s="75"/>
+      <x:c r="F7" s="75"/>
+      <x:c r="G7" s="75"/>
+      <x:c r="H7" s="75"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="71" t="str">
-        <x:v>Currency</x:v>
-      </x:c>
-      <x:c r="B8" s="71" t="str">
-        <x:v>AUD</x:v>
-      </x:c>
-      <x:c r="C8" s="71"/>
+      <x:c r="A8" s="75" t="str">
+        <x:v>Prepared by</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:f>'Assumptions'!$B$21</x:f>
+        <x:v>Finance Manager</x:v>
+      </x:c>
+      <x:c r="C8" s="75"/>
       <x:c r="D8" s="1" t="str">
         <x:v>Assumptions</x:v>
       </x:c>
-      <x:c r="E8" s="71"/>
-      <x:c r="F8" s="71"/>
-      <x:c r="G8" s="71"/>
-      <x:c r="H8" s="71"/>
+      <x:c r="E8" s="75"/>
+      <x:c r="F8" s="75"/>
+      <x:c r="G8" s="75"/>
+      <x:c r="H8" s="75"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="71" t="str">
-        <x:v>Units</x:v>
-      </x:c>
-      <x:c r="B9" s="71" t="str">
-        <x:v>Whole dollars</x:v>
-      </x:c>
-      <x:c r="C9" s="71"/>
+      <x:c r="A9" s="75" t="str">
+        <x:v>Reviewed by</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:f>'Assumptions'!$B$22</x:f>
+        <x:v>CFO / Business Owner</x:v>
+      </x:c>
+      <x:c r="C9" s="75"/>
       <x:c r="D9" s="1" t="str">
         <x:v>13-Week Forecast</x:v>
       </x:c>
-      <x:c r="E9" s="71"/>
-      <x:c r="F9" s="71"/>
-      <x:c r="G9" s="71"/>
-      <x:c r="H9" s="71"/>
+      <x:c r="E9" s="75"/>
+      <x:c r="F9" s="75"/>
+      <x:c r="G9" s="75"/>
+      <x:c r="H9" s="75"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="71" t="str">
+      <x:c r="A10" s="75" t="str">
+        <x:v>Forecast owner</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:f>'Assumptions'!$B$23</x:f>
+        <x:v>Finance Manager</x:v>
+      </x:c>
+      <x:c r="C10" s="75"/>
+      <x:c r="D10" s="1" t="str">
+        <x:v>Weekly Review</x:v>
+      </x:c>
+      <x:c r="E10" s="75"/>
+      <x:c r="F10" s="75"/>
+      <x:c r="G10" s="75"/>
+      <x:c r="H10" s="75"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="75" t="str">
+        <x:v>Next review date</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="n">
+        <x:f>'Assumptions'!$B$24</x:f>
+        <x:v>46278</x:v>
+      </x:c>
+      <x:c r="C11" s="75"/>
+      <x:c r="D11" s="1" t="str">
+        <x:v>Checks &amp; Sources</x:v>
+      </x:c>
+      <x:c r="E11" s="75"/>
+      <x:c r="F11" s="75"/>
+      <x:c r="G11" s="75"/>
+      <x:c r="H11" s="75"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="75" t="str">
+        <x:v>Currency</x:v>
+      </x:c>
+      <x:c r="B12" s="75" t="str">
+        <x:v>AUD</x:v>
+      </x:c>
+      <x:c r="C12" s="75"/>
+      <x:c r="D12" s="75"/>
+      <x:c r="E12" s="75"/>
+      <x:c r="F12" s="75"/>
+      <x:c r="G12" s="75"/>
+      <x:c r="H12" s="75"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="75" t="str">
+        <x:v>Units</x:v>
+      </x:c>
+      <x:c r="B13" s="75" t="str">
+        <x:v>Whole dollars</x:v>
+      </x:c>
+      <x:c r="C13" s="75"/>
+      <x:c r="D13" s="75"/>
+      <x:c r="E13" s="75"/>
+      <x:c r="F13" s="75"/>
+      <x:c r="G13" s="75"/>
+      <x:c r="H13" s="75"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="75" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="str">
+      <x:c r="B14" s="12" t="str">
         <x:f>'Assumptions'!$B$12</x:f>
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="C10" s="71"/>
-      <x:c r="D10" s="1" t="str">
-        <x:v>Weekly Review</x:v>
-      </x:c>
-      <x:c r="E10" s="71"/>
-      <x:c r="F10" s="71"/>
-      <x:c r="G10" s="71"/>
-      <x:c r="H10" s="71"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="71"/>
-      <x:c r="B11" s="71"/>
-      <x:c r="C11" s="71"/>
-      <x:c r="D11" s="1" t="str">
-        <x:v>Checks &amp; Sources</x:v>
-      </x:c>
-      <x:c r="E11" s="71"/>
-      <x:c r="F11" s="71"/>
-      <x:c r="G11" s="71"/>
-      <x:c r="H11" s="71"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="14" t="str">
+      <x:c r="C14" s="75"/>
+      <x:c r="D14" s="75"/>
+      <x:c r="E14" s="75"/>
+      <x:c r="F14" s="75"/>
+      <x:c r="G14" s="75"/>
+      <x:c r="H14" s="75"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="75"/>
+      <x:c r="B15" s="75"/>
+      <x:c r="C15" s="75"/>
+      <x:c r="D15" s="75"/>
+      <x:c r="E15" s="75"/>
+      <x:c r="F15" s="75"/>
+      <x:c r="G15" s="75"/>
+      <x:c r="H15" s="75"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="15" t="str">
         <x:v>Five-step weekly update process</x:v>
       </x:c>
-      <x:c r="B12" s="14"/>
-      <x:c r="C12" s="14"/>
-      <x:c r="D12" s="14"/>
-      <x:c r="E12" s="14"/>
-      <x:c r="F12" s="14"/>
-      <x:c r="G12" s="14"/>
-      <x:c r="H12" s="14"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="71" t="str">
+      <x:c r="B16" s="15"/>
+      <x:c r="C16" s="15"/>
+      <x:c r="D16" s="15"/>
+      <x:c r="E16" s="15"/>
+      <x:c r="F16" s="15"/>
+      <x:c r="G16" s="15"/>
+      <x:c r="H16" s="15"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="75" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B13" s="73" t="str">
+      <x:c r="B17" s="77" t="str">
         <x:v>Update the Assumptions control panel and selected scenario.</x:v>
       </x:c>
-      <x:c r="C13" s="71"/>
-      <x:c r="D13" s="71"/>
-      <x:c r="E13" s="71"/>
-      <x:c r="F13" s="71"/>
-      <x:c r="G13" s="71"/>
-      <x:c r="H13" s="71"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="71" t="str">
+      <x:c r="C17" s="75"/>
+      <x:c r="D17" s="75"/>
+      <x:c r="E17" s="75"/>
+      <x:c r="F17" s="75"/>
+      <x:c r="G17" s="75"/>
+      <x:c r="H17" s="75"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="75" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B14" s="73" t="str">
+      <x:c r="B18" s="77" t="str">
         <x:v>Replace blue cash-receipt and cash-payment inputs with the latest weekly view.</x:v>
       </x:c>
-      <x:c r="C14" s="71"/>
-      <x:c r="D14" s="71"/>
-      <x:c r="E14" s="71"/>
-      <x:c r="F14" s="71"/>
-      <x:c r="G14" s="71"/>
-      <x:c r="H14" s="71"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="71" t="str">
+      <x:c r="C18" s="75"/>
+      <x:c r="D18" s="75"/>
+      <x:c r="E18" s="75"/>
+      <x:c r="F18" s="75"/>
+      <x:c r="G18" s="75"/>
+      <x:c r="H18" s="75"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="75" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B15" s="73" t="str">
+      <x:c r="B19" s="77" t="str">
         <x:v>Review closing cash, headroom and liquidity status in the 13-Week Forecast.</x:v>
       </x:c>
-      <x:c r="C15" s="71"/>
-      <x:c r="D15" s="71"/>
-      <x:c r="E15" s="71"/>
-      <x:c r="F15" s="71"/>
-      <x:c r="G15" s="71"/>
-      <x:c r="H15" s="71"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="71" t="str">
+      <x:c r="C19" s="75"/>
+      <x:c r="D19" s="75"/>
+      <x:c r="E19" s="75"/>
+      <x:c r="F19" s="75"/>
+      <x:c r="G19" s="75"/>
+      <x:c r="H19" s="75"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="75" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B16" s="73" t="str">
+      <x:c r="B20" s="77" t="str">
         <x:v>Snapshot the original forecast as values, then record actuals and owner commentary in Weekly Review.</x:v>
       </x:c>
-      <x:c r="C16" s="71"/>
-      <x:c r="D16" s="71"/>
-      <x:c r="E16" s="71"/>
-      <x:c r="F16" s="71"/>
-      <x:c r="G16" s="71"/>
-      <x:c r="H16" s="71"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="71" t="str">
+      <x:c r="C20" s="75"/>
+      <x:c r="D20" s="75"/>
+      <x:c r="E20" s="75"/>
+      <x:c r="F20" s="75"/>
+      <x:c r="G20" s="75"/>
+      <x:c r="H20" s="75"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="75" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B17" s="73" t="str">
+      <x:c r="B21" s="77" t="str">
         <x:v>Resolve any control failure in Checks &amp; Sources before management review.</x:v>
       </x:c>
-      <x:c r="C17" s="71"/>
-      <x:c r="D17" s="71"/>
-      <x:c r="E17" s="71"/>
-      <x:c r="F17" s="71"/>
-      <x:c r="G17" s="71"/>
-      <x:c r="H17" s="71"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="71"/>
-      <x:c r="B18" s="71"/>
-      <x:c r="C18" s="71"/>
-      <x:c r="D18" s="71"/>
-      <x:c r="E18" s="71"/>
-      <x:c r="F18" s="71"/>
-      <x:c r="G18" s="71"/>
-      <x:c r="H18" s="71"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="14" t="str">
+      <x:c r="C21" s="75"/>
+      <x:c r="D21" s="75"/>
+      <x:c r="E21" s="75"/>
+      <x:c r="F21" s="75"/>
+      <x:c r="G21" s="75"/>
+      <x:c r="H21" s="75"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="75"/>
+      <x:c r="B22" s="75"/>
+      <x:c r="C22" s="75"/>
+      <x:c r="D22" s="75"/>
+      <x:c r="E22" s="75"/>
+      <x:c r="F22" s="75"/>
+      <x:c r="G22" s="75"/>
+      <x:c r="H22" s="75"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="15" t="str">
         <x:v>Colour legend</x:v>
       </x:c>
-      <x:c r="B19" s="14"/>
-      <x:c r="C19" s="14"/>
-      <x:c r="D19" s="14"/>
-      <x:c r="E19" s="14"/>
-      <x:c r="F19" s="14"/>
-      <x:c r="G19" s="14"/>
-      <x:c r="H19" s="14"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="16" t="str">
+      <x:c r="B23" s="15"/>
+      <x:c r="C23" s="15"/>
+      <x:c r="D23" s="15"/>
+      <x:c r="E23" s="15"/>
+      <x:c r="F23" s="15"/>
+      <x:c r="G23" s="15"/>
+      <x:c r="H23" s="15"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="17" t="str">
         <x:v>Blue text / lavender fill</x:v>
       </x:c>
-      <x:c r="B20" s="71" t="str">
+      <x:c r="B24" s="75" t="str">
         <x:v>Editable user input</x:v>
       </x:c>
-      <x:c r="C20" s="71"/>
-      <x:c r="D20" s="71"/>
-      <x:c r="E20" s="71"/>
-      <x:c r="F20" s="71"/>
-      <x:c r="G20" s="71"/>
-      <x:c r="H20" s="71"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="17" t="str">
+      <x:c r="C24" s="75"/>
+      <x:c r="D24" s="75"/>
+      <x:c r="E24" s="75"/>
+      <x:c r="F24" s="75"/>
+      <x:c r="G24" s="75"/>
+      <x:c r="H24" s="75"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="18" t="str">
         <x:v>Black text</x:v>
       </x:c>
-      <x:c r="B21" s="71" t="str">
+      <x:c r="B25" s="75" t="str">
         <x:v>Formula or calculation</x:v>
       </x:c>
-      <x:c r="C21" s="71"/>
-      <x:c r="D21" s="71"/>
-      <x:c r="E21" s="71"/>
-      <x:c r="F21" s="71"/>
-      <x:c r="G21" s="71"/>
-      <x:c r="H21" s="71"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="12" t="str">
+      <x:c r="C25" s="75"/>
+      <x:c r="D25" s="75"/>
+      <x:c r="E25" s="75"/>
+      <x:c r="F25" s="75"/>
+      <x:c r="G25" s="75"/>
+      <x:c r="H25" s="75"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="12" t="str">
         <x:v>Green text</x:v>
       </x:c>
-      <x:c r="B22" s="71" t="str">
+      <x:c r="B26" s="75" t="str">
         <x:v>Cross-sheet link</x:v>
       </x:c>
-      <x:c r="C22" s="71"/>
-      <x:c r="D22" s="71"/>
-      <x:c r="E22" s="71"/>
-      <x:c r="F22" s="71"/>
-      <x:c r="G22" s="71"/>
-      <x:c r="H22" s="71"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="19" t="str">
+      <x:c r="C26" s="75"/>
+      <x:c r="D26" s="75"/>
+      <x:c r="E26" s="75"/>
+      <x:c r="F26" s="75"/>
+      <x:c r="G26" s="75"/>
+      <x:c r="H26" s="75"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="20" t="str">
         <x:v>Red text / pale-red fill</x:v>
       </x:c>
-      <x:c r="B23" s="71" t="str">
+      <x:c r="B27" s="75" t="str">
         <x:v>Warning or exception</x:v>
       </x:c>
-      <x:c r="C23" s="71"/>
-      <x:c r="D23" s="71"/>
-      <x:c r="E23" s="71"/>
-      <x:c r="F23" s="71"/>
-      <x:c r="G23" s="71"/>
-      <x:c r="H23" s="71"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="21" t="str">
+      <x:c r="C27" s="75"/>
+      <x:c r="D27" s="75"/>
+      <x:c r="E27" s="75"/>
+      <x:c r="F27" s="75"/>
+      <x:c r="G27" s="75"/>
+      <x:c r="H27" s="75"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="22" t="str">
         <x:v>Dark green / pale-green fill</x:v>
       </x:c>
-      <x:c r="B24" s="71" t="str">
+      <x:c r="B28" s="75" t="str">
         <x:v>Passing check</x:v>
       </x:c>
-      <x:c r="C24" s="71"/>
-      <x:c r="D24" s="71"/>
-      <x:c r="E24" s="71"/>
-      <x:c r="F24" s="71"/>
-      <x:c r="G24" s="71"/>
-      <x:c r="H24" s="71"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="71"/>
-      <x:c r="B25" s="71"/>
-      <x:c r="C25" s="71"/>
-      <x:c r="D25" s="71"/>
-      <x:c r="E25" s="71"/>
-      <x:c r="F25" s="71"/>
-      <x:c r="G25" s="71"/>
-      <x:c r="H25" s="71"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="71"/>
-      <x:c r="B26" s="71"/>
-      <x:c r="C26" s="71"/>
-      <x:c r="D26" s="71"/>
-      <x:c r="E26" s="71"/>
-      <x:c r="F26" s="71"/>
-      <x:c r="G26" s="71"/>
-      <x:c r="H26" s="71"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="27" t="str">
+      <x:c r="C28" s="75"/>
+      <x:c r="D28" s="75"/>
+      <x:c r="E28" s="75"/>
+      <x:c r="F28" s="75"/>
+      <x:c r="G28" s="75"/>
+      <x:c r="H28" s="75"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="75"/>
+      <x:c r="B29" s="75"/>
+      <x:c r="C29" s="75"/>
+      <x:c r="D29" s="75"/>
+      <x:c r="E29" s="75"/>
+      <x:c r="F29" s="75"/>
+      <x:c r="G29" s="75"/>
+      <x:c r="H29" s="75"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="75"/>
+      <x:c r="B30" s="75"/>
+      <x:c r="C30" s="75"/>
+      <x:c r="D30" s="75"/>
+      <x:c r="E30" s="75"/>
+      <x:c r="F30" s="75"/>
+      <x:c r="G30" s="75"/>
+      <x:c r="H30" s="75"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="28" t="str">
         <x:v>Scope limit: this workbook supports short-term cash planning. It is illustrative only and is not tax, payroll, legal or financial advice. Confirm statutory dates and classifications with your adviser.</x:v>
       </x:c>
-      <x:c r="B27" s="27"/>
-      <x:c r="C27" s="27"/>
-      <x:c r="D27" s="27"/>
-      <x:c r="E27" s="27"/>
-      <x:c r="F27" s="27"/>
-      <x:c r="G27" s="27"/>
-      <x:c r="H27" s="27"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="27"/>
-      <x:c r="B28" s="27"/>
-      <x:c r="C28" s="27"/>
-      <x:c r="D28" s="27"/>
-      <x:c r="E28" s="27"/>
-      <x:c r="F28" s="27"/>
-      <x:c r="G28" s="27"/>
-      <x:c r="H28" s="27"/>
+      <x:c r="B31" s="28"/>
+      <x:c r="C31" s="28"/>
+      <x:c r="D31" s="28"/>
+      <x:c r="E31" s="28"/>
+      <x:c r="F31" s="28"/>
+      <x:c r="G31" s="28"/>
+      <x:c r="H31" s="28"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="28"/>
+      <x:c r="B32" s="28"/>
+      <x:c r="C32" s="28"/>
+      <x:c r="D32" s="28"/>
+      <x:c r="E32" s="28"/>
+      <x:c r="F32" s="28"/>
+      <x:c r="G32" s="28"/>
+      <x:c r="H32" s="28"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
     <x:mergeCell ref="A4:H4"/>
-    <x:mergeCell ref="A27:H28"/>
+    <x:mergeCell ref="A31:H32"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1753,359 +1889,359 @@
       <x:c r="S2" s="8"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="71"/>
-      <x:c r="B3" s="71"/>
-      <x:c r="C3" s="71"/>
-      <x:c r="D3" s="71"/>
-      <x:c r="E3" s="71"/>
-      <x:c r="F3" s="71"/>
-      <x:c r="G3" s="71"/>
-      <x:c r="H3" s="71"/>
-      <x:c r="I3" s="71"/>
-      <x:c r="J3" s="71"/>
-      <x:c r="K3" s="71"/>
-      <x:c r="L3" s="71"/>
-      <x:c r="M3" s="71"/>
-      <x:c r="N3" s="71"/>
-      <x:c r="O3" s="71"/>
-      <x:c r="P3" s="71"/>
-      <x:c r="Q3" s="71"/>
-      <x:c r="R3" s="71"/>
-      <x:c r="S3" s="71"/>
+      <x:c r="A3" s="75"/>
+      <x:c r="B3" s="75"/>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+      <x:c r="F3" s="75"/>
+      <x:c r="G3" s="75"/>
+      <x:c r="H3" s="75"/>
+      <x:c r="I3" s="75"/>
+      <x:c r="J3" s="75"/>
+      <x:c r="K3" s="75"/>
+      <x:c r="L3" s="75"/>
+      <x:c r="M3" s="75"/>
+      <x:c r="N3" s="75"/>
+      <x:c r="O3" s="75"/>
+      <x:c r="P3" s="75"/>
+      <x:c r="Q3" s="75"/>
+      <x:c r="R3" s="75"/>
+      <x:c r="S3" s="75"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="25" t="str">
+      <x:c r="A4" s="26" t="str">
         <x:v>No cash-flow inputs belong on this sheet. Update Assumptions and the 13-Week Forecast instead.</x:v>
       </x:c>
-      <x:c r="B4" s="25"/>
-      <x:c r="C4" s="25"/>
-      <x:c r="D4" s="25"/>
-      <x:c r="E4" s="25"/>
-      <x:c r="F4" s="25"/>
-      <x:c r="G4" s="25"/>
-      <x:c r="H4" s="25"/>
-      <x:c r="I4" s="25"/>
-      <x:c r="J4" s="25"/>
-      <x:c r="K4" s="25"/>
-      <x:c r="L4" s="25"/>
-      <x:c r="M4" s="25"/>
-      <x:c r="N4" s="25"/>
-      <x:c r="O4" s="25"/>
-      <x:c r="P4" s="14" t="str">
+      <x:c r="B4" s="26"/>
+      <x:c r="C4" s="26"/>
+      <x:c r="D4" s="26"/>
+      <x:c r="E4" s="26"/>
+      <x:c r="F4" s="26"/>
+      <x:c r="G4" s="26"/>
+      <x:c r="H4" s="26"/>
+      <x:c r="I4" s="26"/>
+      <x:c r="J4" s="26"/>
+      <x:c r="K4" s="26"/>
+      <x:c r="L4" s="26"/>
+      <x:c r="M4" s="26"/>
+      <x:c r="N4" s="26"/>
+      <x:c r="O4" s="26"/>
+      <x:c r="P4" s="15" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="Q4" s="14" t="str">
+      <x:c r="Q4" s="15" t="str">
         <x:v>Closing cash</x:v>
       </x:c>
-      <x:c r="R4" s="14" t="str">
+      <x:c r="R4" s="15" t="str">
         <x:v>Minimum buffer</x:v>
       </x:c>
-      <x:c r="S4" s="71"/>
+      <x:c r="S4" s="75"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="71"/>
-      <x:c r="B5" s="71"/>
-      <x:c r="C5" s="71"/>
-      <x:c r="D5" s="71"/>
-      <x:c r="E5" s="71"/>
-      <x:c r="F5" s="71"/>
-      <x:c r="G5" s="71"/>
-      <x:c r="H5" s="71"/>
-      <x:c r="I5" s="71"/>
-      <x:c r="J5" s="71"/>
-      <x:c r="K5" s="71"/>
-      <x:c r="L5" s="71"/>
-      <x:c r="M5" s="71"/>
-      <x:c r="N5" s="71"/>
-      <x:c r="O5" s="71"/>
-      <x:c r="P5" s="72" t="str">
+      <x:c r="A5" s="75"/>
+      <x:c r="B5" s="75"/>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="75"/>
+      <x:c r="E5" s="75"/>
+      <x:c r="F5" s="75"/>
+      <x:c r="G5" s="75"/>
+      <x:c r="H5" s="75"/>
+      <x:c r="I5" s="75"/>
+      <x:c r="J5" s="75"/>
+      <x:c r="K5" s="75"/>
+      <x:c r="L5" s="75"/>
+      <x:c r="M5" s="75"/>
+      <x:c r="N5" s="75"/>
+      <x:c r="O5" s="75"/>
+      <x:c r="P5" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
         <x:v>06 Sep</x:v>
       </x:c>
-      <x:c r="Q5" s="74" t="n">
+      <x:c r="Q5" s="78" t="n">
         <x:f>'13-Week Forecast'!B$48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="R5" s="74" t="n">
+      <x:c r="R5" s="78" t="n">
         <x:f>'13-Week Forecast'!B$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S5" s="71"/>
+      <x:c r="S5" s="75"/>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
-      <x:c r="A6" s="60" t="str">
+      <x:c r="A6" s="61" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B6" s="60" t="str">
+      <x:c r="B6" s="61" t="str">
         <x:v>Week 13 closing cash</x:v>
       </x:c>
-      <x:c r="C6" s="60" t="str">
+      <x:c r="C6" s="61" t="str">
         <x:v>Lowest closing cash</x:v>
       </x:c>
-      <x:c r="D6" s="60" t="str">
+      <x:c r="D6" s="61" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="E6" s="60" t="str">
+      <x:c r="E6" s="61" t="str">
         <x:v>Minimum headroom</x:v>
       </x:c>
-      <x:c r="F6" s="60" t="str">
+      <x:c r="F6" s="61" t="str">
         <x:v>Weeks below buffer</x:v>
       </x:c>
-      <x:c r="G6" s="60" t="str">
+      <x:c r="G6" s="61" t="str">
         <x:v>13-week net cash change</x:v>
       </x:c>
-      <x:c r="H6" s="60" t="str">
+      <x:c r="H6" s="61" t="str">
         <x:v>Week of lowest cash</x:v>
       </x:c>
-      <x:c r="I6" s="60" t="str">
+      <x:c r="I6" s="61" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="J6" s="60" t="str">
+      <x:c r="J6" s="61" t="str">
         <x:v>LIQUIDITY STATUS</x:v>
       </x:c>
-      <x:c r="K6" s="71"/>
-      <x:c r="L6" s="71"/>
-      <x:c r="M6" s="71"/>
-      <x:c r="N6" s="71"/>
-      <x:c r="O6" s="71"/>
-      <x:c r="P6" s="72" t="str">
+      <x:c r="K6" s="75"/>
+      <x:c r="L6" s="75"/>
+      <x:c r="M6" s="75"/>
+      <x:c r="N6" s="75"/>
+      <x:c r="O6" s="75"/>
+      <x:c r="P6" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
         <x:v>13 Sep</x:v>
       </x:c>
-      <x:c r="Q6" s="74" t="n">
+      <x:c r="Q6" s="78" t="n">
         <x:f>'13-Week Forecast'!C$48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="R6" s="74" t="n">
+      <x:c r="R6" s="78" t="n">
         <x:f>'13-Week Forecast'!C$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S6" s="71"/>
+      <x:c r="S6" s="75"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="63" t="str">
+      <x:c r="A7" s="64" t="str">
         <x:f>'Assumptions'!$B$12</x:f>
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="B7" s="64" t="n">
+      <x:c r="B7" s="65" t="n">
         <x:f>'13-Week Forecast'!$N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="C7" s="64" t="n">
+      <x:c r="C7" s="65" t="n">
         <x:f>MIN('13-Week Forecast'!$B$48:$N$48)</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D7" s="64" t="n">
+      <x:c r="D7" s="65" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="E7" s="64" t="n">
+      <x:c r="E7" s="65" t="n">
         <x:f>MIN('13-Week Forecast'!$B$50:$N$50)</x:f>
         <x:v>-69000</x:v>
       </x:c>
-      <x:c r="F7" s="63" t="n">
+      <x:c r="F7" s="64" t="n">
         <x:f>COUNTIF('13-Week Forecast'!$B$50:$N$50,"&lt;0")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G7" s="64" t="n">
+      <x:c r="G7" s="65" t="n">
         <x:f>SUM('13-Week Forecast'!$B$47:$N$47)</x:f>
         <x:v>-369000</x:v>
       </x:c>
-      <x:c r="H7" s="65" t="n">
+      <x:c r="H7" s="66" t="n">
         <x:f>INDEX('13-Week Forecast'!$B$6:$N$6,1,MATCH(C7,'13-Week Forecast'!$B$48:$N$48,0))</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="I7" s="63" t="str">
+      <x:c r="I7" s="64" t="str">
         <x:f>'Checks &amp; Sources'!$B$4</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="J7" s="63" t="str">
+      <x:c r="J7" s="64" t="str">
         <x:f>'Checks &amp; Sources'!$E$4</x:f>
         <x:v>ACTION REQUIRED</x:v>
       </x:c>
-      <x:c r="K7" s="71"/>
-      <x:c r="L7" s="71"/>
-      <x:c r="M7" s="71"/>
-      <x:c r="N7" s="71"/>
-      <x:c r="O7" s="71"/>
-      <x:c r="P7" s="72" t="str">
+      <x:c r="K7" s="75"/>
+      <x:c r="L7" s="75"/>
+      <x:c r="M7" s="75"/>
+      <x:c r="N7" s="75"/>
+      <x:c r="O7" s="75"/>
+      <x:c r="P7" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
         <x:v>20 Sep</x:v>
       </x:c>
-      <x:c r="Q7" s="74" t="n">
+      <x:c r="Q7" s="78" t="n">
         <x:f>'13-Week Forecast'!D$48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="R7" s="74" t="n">
+      <x:c r="R7" s="78" t="n">
         <x:f>'13-Week Forecast'!D$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S7" s="71"/>
+      <x:c r="S7" s="75"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="71"/>
-      <x:c r="B8" s="71"/>
-      <x:c r="C8" s="71"/>
-      <x:c r="D8" s="71"/>
-      <x:c r="E8" s="71"/>
-      <x:c r="F8" s="71"/>
-      <x:c r="G8" s="71"/>
-      <x:c r="H8" s="71"/>
-      <x:c r="I8" s="71"/>
-      <x:c r="J8" s="71"/>
-      <x:c r="K8" s="71"/>
-      <x:c r="L8" s="71"/>
-      <x:c r="M8" s="71"/>
-      <x:c r="N8" s="71"/>
-      <x:c r="O8" s="71"/>
-      <x:c r="P8" s="72" t="str">
+      <x:c r="A8" s="75"/>
+      <x:c r="B8" s="75"/>
+      <x:c r="C8" s="75"/>
+      <x:c r="D8" s="75"/>
+      <x:c r="E8" s="75"/>
+      <x:c r="F8" s="75"/>
+      <x:c r="G8" s="75"/>
+      <x:c r="H8" s="75"/>
+      <x:c r="I8" s="75"/>
+      <x:c r="J8" s="75"/>
+      <x:c r="K8" s="75"/>
+      <x:c r="L8" s="75"/>
+      <x:c r="M8" s="75"/>
+      <x:c r="N8" s="75"/>
+      <x:c r="O8" s="75"/>
+      <x:c r="P8" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
         <x:v>27 Sep</x:v>
       </x:c>
-      <x:c r="Q8" s="74" t="n">
+      <x:c r="Q8" s="78" t="n">
         <x:f>'13-Week Forecast'!E$48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="R8" s="74" t="n">
+      <x:c r="R8" s="78" t="n">
         <x:f>'13-Week Forecast'!E$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S8" s="71"/>
+      <x:c r="S8" s="75"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="59" t="str">
+      <x:c r="A9" s="60" t="str">
         <x:v>First buffer breach</x:v>
       </x:c>
-      <x:c r="B9" s="59" t="str">
+      <x:c r="B9" s="60" t="str">
         <x:v>Weeks until breach</x:v>
       </x:c>
-      <x:c r="C9" s="59" t="str">
+      <x:c r="C9" s="60" t="str">
         <x:v>Funding required</x:v>
       </x:c>
-      <x:c r="D9" s="59" t="str">
+      <x:c r="D9" s="60" t="str">
         <x:v>Action deadline</x:v>
       </x:c>
-      <x:c r="E9" s="71"/>
-      <x:c r="F9" s="71"/>
-      <x:c r="G9" s="71"/>
-      <x:c r="H9" s="71"/>
-      <x:c r="I9" s="71"/>
-      <x:c r="J9" s="71"/>
-      <x:c r="K9" s="71"/>
-      <x:c r="L9" s="71"/>
-      <x:c r="M9" s="71"/>
-      <x:c r="N9" s="71"/>
-      <x:c r="O9" s="71"/>
-      <x:c r="P9" s="72" t="str">
+      <x:c r="E9" s="75"/>
+      <x:c r="F9" s="75"/>
+      <x:c r="G9" s="75"/>
+      <x:c r="H9" s="75"/>
+      <x:c r="I9" s="75"/>
+      <x:c r="J9" s="75"/>
+      <x:c r="K9" s="75"/>
+      <x:c r="L9" s="75"/>
+      <x:c r="M9" s="75"/>
+      <x:c r="N9" s="75"/>
+      <x:c r="O9" s="75"/>
+      <x:c r="P9" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
         <x:v>04 Oct</x:v>
       </x:c>
-      <x:c r="Q9" s="74" t="n">
+      <x:c r="Q9" s="78" t="n">
         <x:f>'13-Week Forecast'!F$48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="R9" s="74" t="n">
+      <x:c r="R9" s="78" t="n">
         <x:f>'13-Week Forecast'!F$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S9" s="71"/>
+      <x:c r="S9" s="75"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="68" t="n">
+      <x:c r="A10" s="69" t="n">
         <x:f>IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"BELOW BUFFER")=0,"None",INDEX('13-Week Forecast'!$B$6:$N$6,1,MATCH("BELOW BUFFER",'13-Week Forecast'!$B$51:$N$51,0)))</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="B10" s="67" t="n">
+      <x:c r="B10" s="68" t="n">
         <x:f>IF(A10="None","13+",MAX(0,ROUNDUP((A10-'Assumptions'!$B$9)/7,0)))</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="69" t="n">
+      <x:c r="C10" s="70" t="n">
         <x:f>MAX(0,-MIN('13-Week Forecast'!$B$50:$N$50))</x:f>
         <x:v>69000</x:v>
       </x:c>
-      <x:c r="D10" s="68" t="n">
+      <x:c r="D10" s="69" t="n">
         <x:f>IF(A10="None","None",A10-7*'Assumptions'!$B$19)</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="E10" s="71"/>
-      <x:c r="F10" s="71"/>
-      <x:c r="G10" s="71"/>
-      <x:c r="H10" s="71"/>
-      <x:c r="I10" s="71"/>
-      <x:c r="J10" s="71"/>
-      <x:c r="K10" s="71"/>
-      <x:c r="L10" s="71"/>
-      <x:c r="M10" s="71"/>
-      <x:c r="N10" s="71"/>
-      <x:c r="O10" s="71"/>
-      <x:c r="P10" s="72" t="str">
+      <x:c r="E10" s="75"/>
+      <x:c r="F10" s="75"/>
+      <x:c r="G10" s="75"/>
+      <x:c r="H10" s="75"/>
+      <x:c r="I10" s="75"/>
+      <x:c r="J10" s="75"/>
+      <x:c r="K10" s="75"/>
+      <x:c r="L10" s="75"/>
+      <x:c r="M10" s="75"/>
+      <x:c r="N10" s="75"/>
+      <x:c r="O10" s="75"/>
+      <x:c r="P10" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
         <x:v>11 Oct</x:v>
       </x:c>
-      <x:c r="Q10" s="74" t="n">
+      <x:c r="Q10" s="78" t="n">
         <x:f>'13-Week Forecast'!G$48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="R10" s="74" t="n">
+      <x:c r="R10" s="78" t="n">
         <x:f>'13-Week Forecast'!G$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S10" s="71"/>
+      <x:c r="S10" s="75"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="14" t="str">
+      <x:c r="A11" s="15" t="str">
         <x:v>Week</x:v>
       </x:c>
-      <x:c r="B11" s="14" t="str">
+      <x:c r="B11" s="15" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="str">
+      <x:c r="C11" s="15" t="str">
         <x:v>Closing cash</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="str">
+      <x:c r="D11" s="15" t="str">
         <x:v>Headroom</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="str">
+      <x:c r="E11" s="15" t="str">
         <x:v>Liquidity status</x:v>
       </x:c>
-      <x:c r="F11" s="71"/>
-      <x:c r="G11" s="71"/>
-      <x:c r="H11" s="71"/>
-      <x:c r="I11" s="71"/>
-      <x:c r="J11" s="71"/>
-      <x:c r="K11" s="71"/>
-      <x:c r="L11" s="71"/>
-      <x:c r="M11" s="71"/>
-      <x:c r="N11" s="71"/>
-      <x:c r="O11" s="71"/>
-      <x:c r="P11" s="72" t="str">
+      <x:c r="F11" s="75"/>
+      <x:c r="G11" s="75"/>
+      <x:c r="H11" s="75"/>
+      <x:c r="I11" s="75"/>
+      <x:c r="J11" s="75"/>
+      <x:c r="K11" s="75"/>
+      <x:c r="L11" s="75"/>
+      <x:c r="M11" s="75"/>
+      <x:c r="N11" s="75"/>
+      <x:c r="O11" s="75"/>
+      <x:c r="P11" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
         <x:v>18 Oct</x:v>
       </x:c>
-      <x:c r="Q11" s="74" t="n">
+      <x:c r="Q11" s="78" t="n">
         <x:f>'13-Week Forecast'!H$48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="R11" s="74" t="n">
+      <x:c r="R11" s="78" t="n">
         <x:f>'13-Week Forecast'!H$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S11" s="71"/>
+      <x:c r="S11" s="75"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="71" t="n">
+      <x:c r="A12" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B12" s="70" t="n">
+      <x:c r="B12" s="13" t="n">
         <x:f>'13-Week Forecast'!B$6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C12" s="44" t="n">
+      <x:c r="C12" s="46" t="n">
         <x:f>'13-Week Forecast'!B$48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="D12" s="44" t="n">
+      <x:c r="D12" s="46" t="n">
         <x:f>'13-Week Forecast'!B$50</x:f>
         <x:v>258000</x:v>
       </x:c>
@@ -2113,44 +2249,44 @@
         <x:f>'13-Week Forecast'!B$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F12" s="71"/>
-      <x:c r="G12" s="71"/>
-      <x:c r="H12" s="71"/>
-      <x:c r="I12" s="71"/>
-      <x:c r="J12" s="71"/>
-      <x:c r="K12" s="71"/>
-      <x:c r="L12" s="71"/>
-      <x:c r="M12" s="71"/>
-      <x:c r="N12" s="71"/>
-      <x:c r="O12" s="71"/>
-      <x:c r="P12" s="72" t="str">
+      <x:c r="F12" s="75"/>
+      <x:c r="G12" s="75"/>
+      <x:c r="H12" s="75"/>
+      <x:c r="I12" s="75"/>
+      <x:c r="J12" s="75"/>
+      <x:c r="K12" s="75"/>
+      <x:c r="L12" s="75"/>
+      <x:c r="M12" s="75"/>
+      <x:c r="N12" s="75"/>
+      <x:c r="O12" s="75"/>
+      <x:c r="P12" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
         <x:v>25 Oct</x:v>
       </x:c>
-      <x:c r="Q12" s="74" t="n">
+      <x:c r="Q12" s="78" t="n">
         <x:f>'13-Week Forecast'!I$48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="R12" s="74" t="n">
+      <x:c r="R12" s="78" t="n">
         <x:f>'13-Week Forecast'!I$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S12" s="71"/>
+      <x:c r="S12" s="75"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="71" t="n">
+      <x:c r="A13" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B13" s="70" t="n">
+      <x:c r="B13" s="13" t="n">
         <x:f>'13-Week Forecast'!C$6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="C13" s="44" t="n">
+      <x:c r="C13" s="46" t="n">
         <x:f>'13-Week Forecast'!C$48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="D13" s="44" t="n">
+      <x:c r="D13" s="46" t="n">
         <x:f>'13-Week Forecast'!C$50</x:f>
         <x:v>249000</x:v>
       </x:c>
@@ -2158,44 +2294,44 @@
         <x:f>'13-Week Forecast'!C$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F13" s="71"/>
-      <x:c r="G13" s="71"/>
-      <x:c r="H13" s="71"/>
-      <x:c r="I13" s="71"/>
-      <x:c r="J13" s="71"/>
-      <x:c r="K13" s="71"/>
-      <x:c r="L13" s="71"/>
-      <x:c r="M13" s="71"/>
-      <x:c r="N13" s="71"/>
-      <x:c r="O13" s="71"/>
-      <x:c r="P13" s="72" t="str">
+      <x:c r="F13" s="75"/>
+      <x:c r="G13" s="75"/>
+      <x:c r="H13" s="75"/>
+      <x:c r="I13" s="75"/>
+      <x:c r="J13" s="75"/>
+      <x:c r="K13" s="75"/>
+      <x:c r="L13" s="75"/>
+      <x:c r="M13" s="75"/>
+      <x:c r="N13" s="75"/>
+      <x:c r="O13" s="75"/>
+      <x:c r="P13" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
         <x:v>01 Nov</x:v>
       </x:c>
-      <x:c r="Q13" s="74" t="n">
+      <x:c r="Q13" s="78" t="n">
         <x:f>'13-Week Forecast'!J$48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="R13" s="74" t="n">
+      <x:c r="R13" s="78" t="n">
         <x:f>'13-Week Forecast'!J$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S13" s="71"/>
+      <x:c r="S13" s="75"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="71" t="n">
+      <x:c r="A14" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B14" s="70" t="n">
+      <x:c r="B14" s="13" t="n">
         <x:f>'13-Week Forecast'!D$6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="C14" s="44" t="n">
+      <x:c r="C14" s="46" t="n">
         <x:f>'13-Week Forecast'!D$48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="D14" s="44" t="n">
+      <x:c r="D14" s="46" t="n">
         <x:f>'13-Week Forecast'!D$50</x:f>
         <x:v>225000</x:v>
       </x:c>
@@ -2203,44 +2339,44 @@
         <x:f>'13-Week Forecast'!D$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F14" s="71"/>
-      <x:c r="G14" s="71"/>
-      <x:c r="H14" s="71"/>
-      <x:c r="I14" s="71"/>
-      <x:c r="J14" s="71"/>
-      <x:c r="K14" s="71"/>
-      <x:c r="L14" s="71"/>
-      <x:c r="M14" s="71"/>
-      <x:c r="N14" s="71"/>
-      <x:c r="O14" s="71"/>
-      <x:c r="P14" s="72" t="str">
+      <x:c r="F14" s="75"/>
+      <x:c r="G14" s="75"/>
+      <x:c r="H14" s="75"/>
+      <x:c r="I14" s="75"/>
+      <x:c r="J14" s="75"/>
+      <x:c r="K14" s="75"/>
+      <x:c r="L14" s="75"/>
+      <x:c r="M14" s="75"/>
+      <x:c r="N14" s="75"/>
+      <x:c r="O14" s="75"/>
+      <x:c r="P14" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
         <x:v>08 Nov</x:v>
       </x:c>
-      <x:c r="Q14" s="74" t="n">
+      <x:c r="Q14" s="78" t="n">
         <x:f>'13-Week Forecast'!K$48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="R14" s="74" t="n">
+      <x:c r="R14" s="78" t="n">
         <x:f>'13-Week Forecast'!K$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S14" s="71"/>
+      <x:c r="S14" s="75"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="71" t="n">
+      <x:c r="A15" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B15" s="70" t="n">
+      <x:c r="B15" s="13" t="n">
         <x:f>'13-Week Forecast'!E$6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="C15" s="44" t="n">
+      <x:c r="C15" s="46" t="n">
         <x:f>'13-Week Forecast'!E$48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="D15" s="44" t="n">
+      <x:c r="D15" s="46" t="n">
         <x:f>'13-Week Forecast'!E$50</x:f>
         <x:v>193000</x:v>
       </x:c>
@@ -2248,44 +2384,44 @@
         <x:f>'13-Week Forecast'!E$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F15" s="71"/>
-      <x:c r="G15" s="71"/>
-      <x:c r="H15" s="71"/>
-      <x:c r="I15" s="71"/>
-      <x:c r="J15" s="71"/>
-      <x:c r="K15" s="71"/>
-      <x:c r="L15" s="71"/>
-      <x:c r="M15" s="71"/>
-      <x:c r="N15" s="71"/>
-      <x:c r="O15" s="71"/>
-      <x:c r="P15" s="72" t="str">
+      <x:c r="F15" s="75"/>
+      <x:c r="G15" s="75"/>
+      <x:c r="H15" s="75"/>
+      <x:c r="I15" s="75"/>
+      <x:c r="J15" s="75"/>
+      <x:c r="K15" s="75"/>
+      <x:c r="L15" s="75"/>
+      <x:c r="M15" s="75"/>
+      <x:c r="N15" s="75"/>
+      <x:c r="O15" s="75"/>
+      <x:c r="P15" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
         <x:v>15 Nov</x:v>
       </x:c>
-      <x:c r="Q15" s="74" t="n">
+      <x:c r="Q15" s="78" t="n">
         <x:f>'13-Week Forecast'!L$48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="R15" s="74" t="n">
+      <x:c r="R15" s="78" t="n">
         <x:f>'13-Week Forecast'!L$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S15" s="71"/>
+      <x:c r="S15" s="75"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="71" t="n">
+      <x:c r="A16" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B16" s="70" t="n">
+      <x:c r="B16" s="13" t="n">
         <x:f>'13-Week Forecast'!F$6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="C16" s="44" t="n">
+      <x:c r="C16" s="46" t="n">
         <x:f>'13-Week Forecast'!F$48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="D16" s="44" t="n">
+      <x:c r="D16" s="46" t="n">
         <x:f>'13-Week Forecast'!F$50</x:f>
         <x:v>101000</x:v>
       </x:c>
@@ -2293,44 +2429,44 @@
         <x:f>'13-Week Forecast'!F$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F16" s="71"/>
-      <x:c r="G16" s="71"/>
-      <x:c r="H16" s="71"/>
-      <x:c r="I16" s="71"/>
-      <x:c r="J16" s="71"/>
-      <x:c r="K16" s="71"/>
-      <x:c r="L16" s="71"/>
-      <x:c r="M16" s="71"/>
-      <x:c r="N16" s="71"/>
-      <x:c r="O16" s="71"/>
-      <x:c r="P16" s="72" t="str">
+      <x:c r="F16" s="75"/>
+      <x:c r="G16" s="75"/>
+      <x:c r="H16" s="75"/>
+      <x:c r="I16" s="75"/>
+      <x:c r="J16" s="75"/>
+      <x:c r="K16" s="75"/>
+      <x:c r="L16" s="75"/>
+      <x:c r="M16" s="75"/>
+      <x:c r="N16" s="75"/>
+      <x:c r="O16" s="75"/>
+      <x:c r="P16" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
         <x:v>22 Nov</x:v>
       </x:c>
-      <x:c r="Q16" s="74" t="n">
+      <x:c r="Q16" s="78" t="n">
         <x:f>'13-Week Forecast'!M$48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="R16" s="74" t="n">
+      <x:c r="R16" s="78" t="n">
         <x:f>'13-Week Forecast'!M$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S16" s="71"/>
+      <x:c r="S16" s="75"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="71" t="n">
+      <x:c r="A17" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B17" s="70" t="n">
+      <x:c r="B17" s="13" t="n">
         <x:f>'13-Week Forecast'!G$6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="C17" s="44" t="n">
+      <x:c r="C17" s="46" t="n">
         <x:f>'13-Week Forecast'!G$48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="D17" s="44" t="n">
+      <x:c r="D17" s="46" t="n">
         <x:f>'13-Week Forecast'!G$50</x:f>
         <x:v>33000</x:v>
       </x:c>
@@ -2338,44 +2474,44 @@
         <x:f>'13-Week Forecast'!G$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F17" s="71"/>
-      <x:c r="G17" s="71"/>
-      <x:c r="H17" s="71"/>
-      <x:c r="I17" s="71"/>
-      <x:c r="J17" s="71"/>
-      <x:c r="K17" s="71"/>
-      <x:c r="L17" s="71"/>
-      <x:c r="M17" s="71"/>
-      <x:c r="N17" s="71"/>
-      <x:c r="O17" s="71"/>
-      <x:c r="P17" s="72" t="str">
+      <x:c r="F17" s="75"/>
+      <x:c r="G17" s="75"/>
+      <x:c r="H17" s="75"/>
+      <x:c r="I17" s="75"/>
+      <x:c r="J17" s="75"/>
+      <x:c r="K17" s="75"/>
+      <x:c r="L17" s="75"/>
+      <x:c r="M17" s="75"/>
+      <x:c r="N17" s="75"/>
+      <x:c r="O17" s="75"/>
+      <x:c r="P17" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
         <x:v>29 Nov</x:v>
       </x:c>
-      <x:c r="Q17" s="74" t="n">
+      <x:c r="Q17" s="78" t="n">
         <x:f>'13-Week Forecast'!N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="R17" s="74" t="n">
+      <x:c r="R17" s="78" t="n">
         <x:f>'13-Week Forecast'!N$49</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="S17" s="71"/>
+      <x:c r="S17" s="75"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="71" t="n">
+      <x:c r="A18" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B18" s="70" t="n">
+      <x:c r="B18" s="13" t="n">
         <x:f>'13-Week Forecast'!H$6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="C18" s="44" t="n">
+      <x:c r="C18" s="46" t="n">
         <x:f>'13-Week Forecast'!H$48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="D18" s="44" t="n">
+      <x:c r="D18" s="46" t="n">
         <x:f>'13-Week Forecast'!H$50</x:f>
         <x:v>117000</x:v>
       </x:c>
@@ -2383,35 +2519,35 @@
         <x:f>'13-Week Forecast'!H$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F18" s="71"/>
-      <x:c r="G18" s="71"/>
-      <x:c r="H18" s="71"/>
-      <x:c r="I18" s="71"/>
-      <x:c r="J18" s="71"/>
-      <x:c r="K18" s="71"/>
-      <x:c r="L18" s="71"/>
-      <x:c r="M18" s="71"/>
-      <x:c r="N18" s="71"/>
-      <x:c r="O18" s="71"/>
-      <x:c r="P18" s="71"/>
-      <x:c r="Q18" s="71"/>
-      <x:c r="R18" s="71"/>
-      <x:c r="S18" s="71"/>
+      <x:c r="F18" s="75"/>
+      <x:c r="G18" s="75"/>
+      <x:c r="H18" s="75"/>
+      <x:c r="I18" s="75"/>
+      <x:c r="J18" s="75"/>
+      <x:c r="K18" s="75"/>
+      <x:c r="L18" s="75"/>
+      <x:c r="M18" s="75"/>
+      <x:c r="N18" s="75"/>
+      <x:c r="O18" s="75"/>
+      <x:c r="P18" s="75"/>
+      <x:c r="Q18" s="75"/>
+      <x:c r="R18" s="75"/>
+      <x:c r="S18" s="75"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="71" t="n">
+      <x:c r="A19" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B19" s="70" t="n">
+      <x:c r="B19" s="13" t="n">
         <x:f>'13-Week Forecast'!I$6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="C19" s="44" t="n">
+      <x:c r="C19" s="46" t="n">
         <x:f>'13-Week Forecast'!I$48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="D19" s="44" t="n">
+      <x:c r="D19" s="46" t="n">
         <x:f>'13-Week Forecast'!I$50</x:f>
         <x:v>60000</x:v>
       </x:c>
@@ -2419,35 +2555,35 @@
         <x:f>'13-Week Forecast'!I$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F19" s="71"/>
-      <x:c r="G19" s="71"/>
-      <x:c r="H19" s="71"/>
-      <x:c r="I19" s="71"/>
-      <x:c r="J19" s="71"/>
-      <x:c r="K19" s="71"/>
-      <x:c r="L19" s="71"/>
-      <x:c r="M19" s="71"/>
-      <x:c r="N19" s="71"/>
-      <x:c r="O19" s="71"/>
-      <x:c r="P19" s="71"/>
-      <x:c r="Q19" s="71"/>
-      <x:c r="R19" s="71"/>
-      <x:c r="S19" s="71"/>
+      <x:c r="F19" s="75"/>
+      <x:c r="G19" s="75"/>
+      <x:c r="H19" s="75"/>
+      <x:c r="I19" s="75"/>
+      <x:c r="J19" s="75"/>
+      <x:c r="K19" s="75"/>
+      <x:c r="L19" s="75"/>
+      <x:c r="M19" s="75"/>
+      <x:c r="N19" s="75"/>
+      <x:c r="O19" s="75"/>
+      <x:c r="P19" s="75"/>
+      <x:c r="Q19" s="75"/>
+      <x:c r="R19" s="75"/>
+      <x:c r="S19" s="75"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="71" t="n">
+      <x:c r="A20" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B20" s="70" t="n">
+      <x:c r="B20" s="13" t="n">
         <x:f>'13-Week Forecast'!J$6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="C20" s="44" t="n">
+      <x:c r="C20" s="46" t="n">
         <x:f>'13-Week Forecast'!J$48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="D20" s="44" t="n">
+      <x:c r="D20" s="46" t="n">
         <x:f>'13-Week Forecast'!J$50</x:f>
         <x:v>17000</x:v>
       </x:c>
@@ -2455,35 +2591,35 @@
         <x:f>'13-Week Forecast'!J$51</x:f>
         <x:v>WATCH</x:v>
       </x:c>
-      <x:c r="F20" s="71"/>
-      <x:c r="G20" s="71"/>
-      <x:c r="H20" s="71"/>
-      <x:c r="I20" s="71"/>
-      <x:c r="J20" s="71"/>
-      <x:c r="K20" s="71"/>
-      <x:c r="L20" s="71"/>
-      <x:c r="M20" s="71"/>
-      <x:c r="N20" s="71"/>
-      <x:c r="O20" s="71"/>
-      <x:c r="P20" s="71"/>
-      <x:c r="Q20" s="71"/>
-      <x:c r="R20" s="71"/>
-      <x:c r="S20" s="71"/>
+      <x:c r="F20" s="75"/>
+      <x:c r="G20" s="75"/>
+      <x:c r="H20" s="75"/>
+      <x:c r="I20" s="75"/>
+      <x:c r="J20" s="75"/>
+      <x:c r="K20" s="75"/>
+      <x:c r="L20" s="75"/>
+      <x:c r="M20" s="75"/>
+      <x:c r="N20" s="75"/>
+      <x:c r="O20" s="75"/>
+      <x:c r="P20" s="75"/>
+      <x:c r="Q20" s="75"/>
+      <x:c r="R20" s="75"/>
+      <x:c r="S20" s="75"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="71" t="n">
+      <x:c r="A21" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B21" s="70" t="n">
+      <x:c r="B21" s="13" t="n">
         <x:f>'13-Week Forecast'!K$6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="C21" s="44" t="n">
+      <x:c r="C21" s="46" t="n">
         <x:f>'13-Week Forecast'!K$48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="D21" s="44" t="n">
+      <x:c r="D21" s="46" t="n">
         <x:f>'13-Week Forecast'!K$50</x:f>
         <x:v>37000</x:v>
       </x:c>
@@ -2491,41 +2627,41 @@
         <x:f>'13-Week Forecast'!K$51</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F21" s="71"/>
-      <x:c r="G21" s="71"/>
-      <x:c r="H21" s="71"/>
-      <x:c r="I21" s="71"/>
-      <x:c r="J21" s="71"/>
-      <x:c r="K21" s="71"/>
-      <x:c r="L21" s="71"/>
-      <x:c r="M21" s="71"/>
-      <x:c r="N21" s="71"/>
-      <x:c r="O21" s="71"/>
-      <x:c r="P21" s="14" t="str">
+      <x:c r="F21" s="75"/>
+      <x:c r="G21" s="75"/>
+      <x:c r="H21" s="75"/>
+      <x:c r="I21" s="75"/>
+      <x:c r="J21" s="75"/>
+      <x:c r="K21" s="75"/>
+      <x:c r="L21" s="75"/>
+      <x:c r="M21" s="75"/>
+      <x:c r="N21" s="75"/>
+      <x:c r="O21" s="75"/>
+      <x:c r="P21" s="15" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="Q21" s="14" t="str">
+      <x:c r="Q21" s="15" t="str">
         <x:v>Total cash receipts</x:v>
       </x:c>
-      <x:c r="R21" s="14" t="str">
+      <x:c r="R21" s="15" t="str">
         <x:v>Total cash payments</x:v>
       </x:c>
-      <x:c r="S21" s="71"/>
+      <x:c r="S21" s="75"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="71" t="n">
+      <x:c r="A22" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B22" s="70" t="n">
+      <x:c r="B22" s="13" t="n">
         <x:f>'13-Week Forecast'!L$6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="C22" s="44" t="n">
+      <x:c r="C22" s="46" t="n">
         <x:f>'13-Week Forecast'!L$48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="D22" s="44" t="n">
+      <x:c r="D22" s="46" t="n">
         <x:f>'13-Week Forecast'!L$50</x:f>
         <x:v>-1000</x:v>
       </x:c>
@@ -2533,44 +2669,44 @@
         <x:f>'13-Week Forecast'!L$51</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="F22" s="71"/>
-      <x:c r="G22" s="71"/>
-      <x:c r="H22" s="71"/>
-      <x:c r="I22" s="71"/>
-      <x:c r="J22" s="71"/>
-      <x:c r="K22" s="71"/>
-      <x:c r="L22" s="71"/>
-      <x:c r="M22" s="71"/>
-      <x:c r="N22" s="71"/>
-      <x:c r="O22" s="71"/>
-      <x:c r="P22" s="72" t="str">
+      <x:c r="F22" s="75"/>
+      <x:c r="G22" s="75"/>
+      <x:c r="H22" s="75"/>
+      <x:c r="I22" s="75"/>
+      <x:c r="J22" s="75"/>
+      <x:c r="K22" s="75"/>
+      <x:c r="L22" s="75"/>
+      <x:c r="M22" s="75"/>
+      <x:c r="N22" s="75"/>
+      <x:c r="O22" s="75"/>
+      <x:c r="P22" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!B$6,"dd mmm")</x:f>
         <x:v>06 Sep</x:v>
       </x:c>
-      <x:c r="Q22" s="74" t="n">
+      <x:c r="Q22" s="78" t="n">
         <x:f>'13-Week Forecast'!B$19</x:f>
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="R22" s="74" t="n">
+      <x:c r="R22" s="78" t="n">
         <x:f>'13-Week Forecast'!B$43</x:f>
         <x:v>212000</x:v>
       </x:c>
-      <x:c r="S22" s="71"/>
+      <x:c r="S22" s="75"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="71" t="n">
+      <x:c r="A23" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B23" s="70" t="n">
+      <x:c r="B23" s="13" t="n">
         <x:f>'13-Week Forecast'!M$6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="C23" s="44" t="n">
+      <x:c r="C23" s="46" t="n">
         <x:f>'13-Week Forecast'!M$48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="D23" s="44" t="n">
+      <x:c r="D23" s="46" t="n">
         <x:f>'13-Week Forecast'!M$50</x:f>
         <x:v>-18000</x:v>
       </x:c>
@@ -2578,44 +2714,44 @@
         <x:f>'13-Week Forecast'!M$51</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="F23" s="71"/>
-      <x:c r="G23" s="71"/>
-      <x:c r="H23" s="71"/>
-      <x:c r="I23" s="71"/>
-      <x:c r="J23" s="71"/>
-      <x:c r="K23" s="71"/>
-      <x:c r="L23" s="71"/>
-      <x:c r="M23" s="71"/>
-      <x:c r="N23" s="71"/>
-      <x:c r="O23" s="71"/>
-      <x:c r="P23" s="72" t="str">
+      <x:c r="F23" s="75"/>
+      <x:c r="G23" s="75"/>
+      <x:c r="H23" s="75"/>
+      <x:c r="I23" s="75"/>
+      <x:c r="J23" s="75"/>
+      <x:c r="K23" s="75"/>
+      <x:c r="L23" s="75"/>
+      <x:c r="M23" s="75"/>
+      <x:c r="N23" s="75"/>
+      <x:c r="O23" s="75"/>
+      <x:c r="P23" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!C$6,"dd mmm")</x:f>
         <x:v>13 Sep</x:v>
       </x:c>
-      <x:c r="Q23" s="74" t="n">
+      <x:c r="Q23" s="78" t="n">
         <x:f>'13-Week Forecast'!C$19</x:f>
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="R23" s="74" t="n">
+      <x:c r="R23" s="78" t="n">
         <x:f>'13-Week Forecast'!C$43</x:f>
         <x:v>178000</x:v>
       </x:c>
-      <x:c r="S23" s="71"/>
+      <x:c r="S23" s="75"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="71" t="n">
+      <x:c r="A24" s="75" t="n">
         <x:f>ROW()-11</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B24" s="70" t="n">
+      <x:c r="B24" s="13" t="n">
         <x:f>'13-Week Forecast'!N$6</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="C24" s="44" t="n">
+      <x:c r="C24" s="46" t="n">
         <x:f>'13-Week Forecast'!N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D24" s="44" t="n">
+      <x:c r="D24" s="46" t="n">
         <x:f>'13-Week Forecast'!N$50</x:f>
         <x:v>-69000</x:v>
       </x:c>
@@ -2623,860 +2759,884 @@
         <x:f>'13-Week Forecast'!N$51</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="F24" s="71"/>
-      <x:c r="G24" s="71"/>
-      <x:c r="H24" s="71"/>
-      <x:c r="I24" s="71"/>
-      <x:c r="J24" s="71"/>
-      <x:c r="K24" s="71"/>
-      <x:c r="L24" s="71"/>
-      <x:c r="M24" s="71"/>
-      <x:c r="N24" s="71"/>
-      <x:c r="O24" s="71"/>
-      <x:c r="P24" s="72" t="str">
+      <x:c r="F24" s="75"/>
+      <x:c r="G24" s="75"/>
+      <x:c r="H24" s="75"/>
+      <x:c r="I24" s="75"/>
+      <x:c r="J24" s="75"/>
+      <x:c r="K24" s="75"/>
+      <x:c r="L24" s="75"/>
+      <x:c r="M24" s="75"/>
+      <x:c r="N24" s="75"/>
+      <x:c r="O24" s="75"/>
+      <x:c r="P24" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!D$6,"dd mmm")</x:f>
         <x:v>20 Sep</x:v>
       </x:c>
-      <x:c r="Q24" s="74" t="n">
+      <x:c r="Q24" s="78" t="n">
         <x:f>'13-Week Forecast'!D$19</x:f>
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="R24" s="74" t="n">
+      <x:c r="R24" s="78" t="n">
         <x:f>'13-Week Forecast'!D$43</x:f>
         <x:v>182000</x:v>
       </x:c>
-      <x:c r="S24" s="71"/>
+      <x:c r="S24" s="75"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="71"/>
-      <x:c r="B25" s="71"/>
-      <x:c r="C25" s="71"/>
-      <x:c r="D25" s="71"/>
-      <x:c r="E25" s="71"/>
-      <x:c r="F25" s="71"/>
-      <x:c r="G25" s="71"/>
-      <x:c r="H25" s="71"/>
-      <x:c r="I25" s="71"/>
-      <x:c r="J25" s="71"/>
-      <x:c r="K25" s="71"/>
-      <x:c r="L25" s="71"/>
-      <x:c r="M25" s="71"/>
-      <x:c r="N25" s="71"/>
-      <x:c r="O25" s="71"/>
-      <x:c r="P25" s="72" t="str">
+      <x:c r="A25" s="75"/>
+      <x:c r="B25" s="75"/>
+      <x:c r="C25" s="75"/>
+      <x:c r="D25" s="75"/>
+      <x:c r="E25" s="75"/>
+      <x:c r="F25" s="75"/>
+      <x:c r="G25" s="75"/>
+      <x:c r="H25" s="75"/>
+      <x:c r="I25" s="75"/>
+      <x:c r="J25" s="75"/>
+      <x:c r="K25" s="75"/>
+      <x:c r="L25" s="75"/>
+      <x:c r="M25" s="75"/>
+      <x:c r="N25" s="75"/>
+      <x:c r="O25" s="75"/>
+      <x:c r="P25" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!E$6,"dd mmm")</x:f>
         <x:v>27 Sep</x:v>
       </x:c>
-      <x:c r="Q25" s="74" t="n">
+      <x:c r="Q25" s="78" t="n">
         <x:f>'13-Week Forecast'!E$19</x:f>
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="R25" s="74" t="n">
+      <x:c r="R25" s="78" t="n">
         <x:f>'13-Week Forecast'!E$43</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="S25" s="71"/>
+      <x:c r="S25" s="75"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="71"/>
-      <x:c r="B26" s="71"/>
-      <x:c r="C26" s="71"/>
-      <x:c r="D26" s="71"/>
-      <x:c r="E26" s="71"/>
-      <x:c r="F26" s="71"/>
-      <x:c r="G26" s="71"/>
-      <x:c r="H26" s="71"/>
-      <x:c r="I26" s="71"/>
-      <x:c r="J26" s="71"/>
-      <x:c r="K26" s="71"/>
-      <x:c r="L26" s="71"/>
-      <x:c r="M26" s="71"/>
-      <x:c r="N26" s="71"/>
-      <x:c r="O26" s="71"/>
-      <x:c r="P26" s="72" t="str">
+      <x:c r="A26" s="75"/>
+      <x:c r="B26" s="75"/>
+      <x:c r="C26" s="75"/>
+      <x:c r="D26" s="75"/>
+      <x:c r="E26" s="75"/>
+      <x:c r="F26" s="75"/>
+      <x:c r="G26" s="75"/>
+      <x:c r="H26" s="75"/>
+      <x:c r="I26" s="75"/>
+      <x:c r="J26" s="75"/>
+      <x:c r="K26" s="75"/>
+      <x:c r="L26" s="75"/>
+      <x:c r="M26" s="75"/>
+      <x:c r="N26" s="75"/>
+      <x:c r="O26" s="75"/>
+      <x:c r="P26" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!F$6,"dd mmm")</x:f>
         <x:v>04 Oct</x:v>
       </x:c>
-      <x:c r="Q26" s="74" t="n">
+      <x:c r="Q26" s="78" t="n">
         <x:f>'13-Week Forecast'!F$19</x:f>
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="R26" s="74" t="n">
+      <x:c r="R26" s="78" t="n">
         <x:f>'13-Week Forecast'!F$43</x:f>
         <x:v>232000</x:v>
       </x:c>
-      <x:c r="S26" s="71"/>
+      <x:c r="S26" s="75"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="45" t="str">
+      <x:c r="A27" s="47" t="str">
         <x:v>Scenario</x:v>
       </x:c>
-      <x:c r="B27" s="45" t="str">
+      <x:c r="B27" s="47" t="str">
         <x:v>Week 13 cash</x:v>
       </x:c>
-      <x:c r="C27" s="45" t="str">
+      <x:c r="C27" s="47" t="str">
         <x:v>Minimum cash</x:v>
       </x:c>
-      <x:c r="D27" s="45" t="str">
+      <x:c r="D27" s="47" t="str">
         <x:v>First buffer breach</x:v>
       </x:c>
-      <x:c r="E27" s="45" t="str">
+      <x:c r="E27" s="47" t="str">
         <x:v>Funding required</x:v>
       </x:c>
-      <x:c r="F27" s="71"/>
-      <x:c r="G27" s="71"/>
-      <x:c r="H27" s="71"/>
-      <x:c r="I27" s="71"/>
-      <x:c r="J27" s="71"/>
-      <x:c r="K27" s="71"/>
-      <x:c r="L27" s="71"/>
-      <x:c r="M27" s="71"/>
-      <x:c r="N27" s="71"/>
-      <x:c r="O27" s="71"/>
-      <x:c r="P27" s="72" t="str">
+      <x:c r="F27" s="75"/>
+      <x:c r="G27" s="75"/>
+      <x:c r="H27" s="75"/>
+      <x:c r="I27" s="75"/>
+      <x:c r="J27" s="75"/>
+      <x:c r="K27" s="75"/>
+      <x:c r="L27" s="75"/>
+      <x:c r="M27" s="75"/>
+      <x:c r="N27" s="75"/>
+      <x:c r="O27" s="75"/>
+      <x:c r="P27" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!G$6,"dd mmm")</x:f>
         <x:v>11 Oct</x:v>
       </x:c>
-      <x:c r="Q27" s="74" t="n">
+      <x:c r="Q27" s="78" t="n">
         <x:f>'13-Week Forecast'!G$19</x:f>
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="R27" s="74" t="n">
+      <x:c r="R27" s="78" t="n">
         <x:f>'13-Week Forecast'!G$43</x:f>
         <x:v>209000</x:v>
       </x:c>
-      <x:c r="S27" s="71"/>
+      <x:c r="S27" s="75"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="12" t="str">
         <x:f>'Assumptions'!$B$15</x:f>
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="B28" s="74" t="n">
+      <x:c r="B28" s="78" t="n">
         <x:f>Q49</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="C28" s="74" t="n">
+      <x:c r="C28" s="78" t="n">
         <x:f>MIN(Q37:Q49)</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D28" s="72" t="n">
+      <x:c r="D28" s="76" t="n">
         <x:f>IF(Q37&lt;'Assumptions'!$B$11,P37,IF(Q38&lt;'Assumptions'!$B$11,P38,IF(Q39&lt;'Assumptions'!$B$11,P39,IF(Q40&lt;'Assumptions'!$B$11,P40,IF(Q41&lt;'Assumptions'!$B$11,P41,IF(Q42&lt;'Assumptions'!$B$11,P42,IF(Q43&lt;'Assumptions'!$B$11,P43,IF(Q44&lt;'Assumptions'!$B$11,P44,IF(Q45&lt;'Assumptions'!$B$11,P45,IF(Q46&lt;'Assumptions'!$B$11,P46,IF(Q47&lt;'Assumptions'!$B$11,P47,IF(Q48&lt;'Assumptions'!$B$11,P48,IF(Q49&lt;'Assumptions'!$B$11,P49,"None")))))))))))))</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="E28" s="74" t="n">
+      <x:c r="E28" s="78" t="n">
         <x:f>MAX(0,'Assumptions'!$B$11-MIN(Q37:Q49))</x:f>
         <x:v>69000</x:v>
       </x:c>
-      <x:c r="F28" s="71"/>
-      <x:c r="G28" s="71"/>
-      <x:c r="H28" s="71"/>
-      <x:c r="I28" s="71"/>
-      <x:c r="J28" s="71"/>
-      <x:c r="K28" s="71"/>
-      <x:c r="L28" s="71"/>
-      <x:c r="M28" s="71"/>
-      <x:c r="N28" s="71"/>
-      <x:c r="O28" s="71"/>
-      <x:c r="P28" s="72" t="str">
+      <x:c r="F28" s="75"/>
+      <x:c r="G28" s="75"/>
+      <x:c r="H28" s="75"/>
+      <x:c r="I28" s="75"/>
+      <x:c r="J28" s="75"/>
+      <x:c r="K28" s="75"/>
+      <x:c r="L28" s="75"/>
+      <x:c r="M28" s="75"/>
+      <x:c r="N28" s="75"/>
+      <x:c r="O28" s="75"/>
+      <x:c r="P28" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!H$6,"dd mmm")</x:f>
         <x:v>18 Oct</x:v>
       </x:c>
-      <x:c r="Q28" s="74" t="n">
+      <x:c r="Q28" s="78" t="n">
         <x:f>'13-Week Forecast'!H$19</x:f>
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="R28" s="74" t="n">
+      <x:c r="R28" s="78" t="n">
         <x:f>'13-Week Forecast'!H$43</x:f>
         <x:v>197000</x:v>
       </x:c>
-      <x:c r="S28" s="71"/>
+      <x:c r="S28" s="75"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="12" t="str">
         <x:f>'Assumptions'!$B$16</x:f>
         <x:v>Upside</x:v>
       </x:c>
-      <x:c r="B29" s="74" t="n">
+      <x:c r="B29" s="78" t="n">
         <x:f>R49</x:f>
         <x:v>199320</x:v>
       </x:c>
-      <x:c r="C29" s="74" t="n">
+      <x:c r="C29" s="78" t="n">
         <x:f>MIN(R37:R49)</x:f>
         <x:v>199320</x:v>
       </x:c>
-      <x:c r="D29" s="72" t="str">
+      <x:c r="D29" s="76" t="str">
         <x:f>IF(R37&lt;'Assumptions'!$B$11,P37,IF(R38&lt;'Assumptions'!$B$11,P38,IF(R39&lt;'Assumptions'!$B$11,P39,IF(R40&lt;'Assumptions'!$B$11,P40,IF(R41&lt;'Assumptions'!$B$11,P41,IF(R42&lt;'Assumptions'!$B$11,P42,IF(R43&lt;'Assumptions'!$B$11,P43,IF(R44&lt;'Assumptions'!$B$11,P44,IF(R45&lt;'Assumptions'!$B$11,P45,IF(R46&lt;'Assumptions'!$B$11,P46,IF(R47&lt;'Assumptions'!$B$11,P47,IF(R48&lt;'Assumptions'!$B$11,P48,IF(R49&lt;'Assumptions'!$B$11,P49,"None")))))))))))))</x:f>
         <x:v>None</x:v>
       </x:c>
-      <x:c r="E29" s="74" t="n">
+      <x:c r="E29" s="78" t="n">
         <x:f>MAX(0,'Assumptions'!$B$11-MIN(R37:R49))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="71"/>
-      <x:c r="G29" s="71"/>
-      <x:c r="H29" s="71"/>
-      <x:c r="I29" s="71"/>
-      <x:c r="J29" s="71"/>
-      <x:c r="K29" s="71"/>
-      <x:c r="L29" s="71"/>
-      <x:c r="M29" s="71"/>
-      <x:c r="N29" s="71"/>
-      <x:c r="O29" s="71"/>
-      <x:c r="P29" s="72" t="str">
+      <x:c r="F29" s="75"/>
+      <x:c r="G29" s="75"/>
+      <x:c r="H29" s="75"/>
+      <x:c r="I29" s="75"/>
+      <x:c r="J29" s="75"/>
+      <x:c r="K29" s="75"/>
+      <x:c r="L29" s="75"/>
+      <x:c r="M29" s="75"/>
+      <x:c r="N29" s="75"/>
+      <x:c r="O29" s="75"/>
+      <x:c r="P29" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!I$6,"dd mmm")</x:f>
         <x:v>25 Oct</x:v>
       </x:c>
-      <x:c r="Q29" s="74" t="n">
+      <x:c r="Q29" s="78" t="n">
         <x:f>'13-Week Forecast'!I$19</x:f>
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="R29" s="74" t="n">
+      <x:c r="R29" s="78" t="n">
         <x:f>'13-Week Forecast'!I$43</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="S29" s="71"/>
+      <x:c r="S29" s="75"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="12" t="str">
         <x:f>'Assumptions'!$B$17</x:f>
         <x:v>Downside</x:v>
       </x:c>
-      <x:c r="B30" s="74" t="n">
+      <x:c r="B30" s="78" t="n">
         <x:f>S49</x:f>
         <x:v>-302550</x:v>
       </x:c>
-      <x:c r="C30" s="74" t="n">
+      <x:c r="C30" s="78" t="n">
         <x:f>MIN(S37:S49)</x:f>
         <x:v>-302550</x:v>
       </x:c>
-      <x:c r="D30" s="72" t="n">
+      <x:c r="D30" s="76" t="n">
         <x:f>IF(S37&lt;'Assumptions'!$B$11,P37,IF(S38&lt;'Assumptions'!$B$11,P38,IF(S39&lt;'Assumptions'!$B$11,P39,IF(S40&lt;'Assumptions'!$B$11,P40,IF(S41&lt;'Assumptions'!$B$11,P41,IF(S42&lt;'Assumptions'!$B$11,P42,IF(S43&lt;'Assumptions'!$B$11,P43,IF(S44&lt;'Assumptions'!$B$11,P44,IF(S45&lt;'Assumptions'!$B$11,P45,IF(S46&lt;'Assumptions'!$B$11,P46,IF(S47&lt;'Assumptions'!$B$11,P47,IF(S48&lt;'Assumptions'!$B$11,P48,IF(S49&lt;'Assumptions'!$B$11,P49,"None")))))))))))))</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="E30" s="74" t="n">
+      <x:c r="E30" s="78" t="n">
         <x:f>MAX(0,'Assumptions'!$B$11-MIN(S37:S49))</x:f>
         <x:v>402550</x:v>
       </x:c>
-      <x:c r="F30" s="71"/>
-      <x:c r="G30" s="71"/>
-      <x:c r="H30" s="71"/>
-      <x:c r="I30" s="71"/>
-      <x:c r="J30" s="71"/>
-      <x:c r="K30" s="71"/>
-      <x:c r="L30" s="71"/>
-      <x:c r="M30" s="71"/>
-      <x:c r="N30" s="71"/>
-      <x:c r="O30" s="71"/>
-      <x:c r="P30" s="72" t="str">
+      <x:c r="F30" s="75"/>
+      <x:c r="G30" s="75"/>
+      <x:c r="H30" s="75"/>
+      <x:c r="I30" s="75"/>
+      <x:c r="J30" s="75"/>
+      <x:c r="K30" s="75"/>
+      <x:c r="L30" s="75"/>
+      <x:c r="M30" s="75"/>
+      <x:c r="N30" s="75"/>
+      <x:c r="O30" s="75"/>
+      <x:c r="P30" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!J$6,"dd mmm")</x:f>
         <x:v>01 Nov</x:v>
       </x:c>
-      <x:c r="Q30" s="74" t="n">
+      <x:c r="Q30" s="78" t="n">
         <x:f>'13-Week Forecast'!J$19</x:f>
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="R30" s="74" t="n">
+      <x:c r="R30" s="78" t="n">
         <x:f>'13-Week Forecast'!J$43</x:f>
         <x:v>307000</x:v>
       </x:c>
-      <x:c r="S30" s="71"/>
+      <x:c r="S30" s="75"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="71"/>
-      <x:c r="B31" s="71"/>
-      <x:c r="C31" s="71"/>
-      <x:c r="D31" s="71"/>
-      <x:c r="E31" s="71"/>
-      <x:c r="F31" s="71"/>
-      <x:c r="G31" s="71"/>
-      <x:c r="H31" s="71"/>
-      <x:c r="I31" s="71"/>
-      <x:c r="J31" s="71"/>
-      <x:c r="K31" s="71"/>
-      <x:c r="L31" s="71"/>
-      <x:c r="M31" s="71"/>
-      <x:c r="N31" s="71"/>
-      <x:c r="O31" s="71"/>
-      <x:c r="P31" s="72" t="str">
+      <x:c r="A31" s="75"/>
+      <x:c r="B31" s="75"/>
+      <x:c r="C31" s="75"/>
+      <x:c r="D31" s="75"/>
+      <x:c r="E31" s="75"/>
+      <x:c r="F31" s="75"/>
+      <x:c r="G31" s="75"/>
+      <x:c r="H31" s="75"/>
+      <x:c r="I31" s="75"/>
+      <x:c r="J31" s="75"/>
+      <x:c r="K31" s="75"/>
+      <x:c r="L31" s="75"/>
+      <x:c r="M31" s="75"/>
+      <x:c r="N31" s="75"/>
+      <x:c r="O31" s="75"/>
+      <x:c r="P31" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!K$6,"dd mmm")</x:f>
         <x:v>08 Nov</x:v>
       </x:c>
-      <x:c r="Q31" s="74" t="n">
+      <x:c r="Q31" s="78" t="n">
         <x:f>'13-Week Forecast'!K$19</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="R31" s="74" t="n">
+      <x:c r="R31" s="78" t="n">
         <x:f>'13-Week Forecast'!K$43</x:f>
         <x:v>229000</x:v>
       </x:c>
-      <x:c r="S31" s="71"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="71"/>
-      <x:c r="B32" s="71"/>
-      <x:c r="C32" s="71"/>
-      <x:c r="D32" s="71"/>
-      <x:c r="E32" s="71"/>
-      <x:c r="F32" s="71"/>
-      <x:c r="G32" s="71"/>
-      <x:c r="H32" s="71"/>
-      <x:c r="I32" s="71"/>
-      <x:c r="J32" s="71"/>
-      <x:c r="K32" s="71"/>
-      <x:c r="L32" s="71"/>
-      <x:c r="M32" s="71"/>
-      <x:c r="N32" s="71"/>
-      <x:c r="O32" s="71"/>
-      <x:c r="P32" s="72" t="str">
+      <x:c r="S31" s="75"/>
+    </x:row>
+    <x:row r="32" ht="34" customHeight="1">
+      <x:c r="A32" s="61" t="str">
+        <x:v>Weeks actualised</x:v>
+      </x:c>
+      <x:c r="B32" s="61" t="str">
+        <x:v>Receipt variance %</x:v>
+      </x:c>
+      <x:c r="C32" s="61" t="str">
+        <x:v>Payment variance %</x:v>
+      </x:c>
+      <x:c r="D32" s="61" t="str">
+        <x:v>Closing-cash bias</x:v>
+      </x:c>
+      <x:c r="E32" s="61" t="str">
+        <x:v>Review completeness</x:v>
+      </x:c>
+      <x:c r="F32" s="75"/>
+      <x:c r="G32" s="75"/>
+      <x:c r="H32" s="75"/>
+      <x:c r="I32" s="75"/>
+      <x:c r="J32" s="75"/>
+      <x:c r="K32" s="75"/>
+      <x:c r="L32" s="75"/>
+      <x:c r="M32" s="75"/>
+      <x:c r="N32" s="75"/>
+      <x:c r="O32" s="75"/>
+      <x:c r="P32" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!L$6,"dd mmm")</x:f>
         <x:v>15 Nov</x:v>
       </x:c>
-      <x:c r="Q32" s="74" t="n">
+      <x:c r="Q32" s="78" t="n">
         <x:f>'13-Week Forecast'!L$19</x:f>
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="R32" s="74" t="n">
+      <x:c r="R32" s="78" t="n">
         <x:f>'13-Week Forecast'!L$43</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="S32" s="71"/>
+      <x:c r="S32" s="75"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="71"/>
-      <x:c r="B33" s="71"/>
-      <x:c r="C33" s="71"/>
-      <x:c r="D33" s="71"/>
-      <x:c r="E33" s="71"/>
-      <x:c r="F33" s="71"/>
-      <x:c r="G33" s="71"/>
-      <x:c r="H33" s="71"/>
-      <x:c r="I33" s="71"/>
-      <x:c r="J33" s="71"/>
-      <x:c r="K33" s="71"/>
-      <x:c r="L33" s="71"/>
-      <x:c r="M33" s="71"/>
-      <x:c r="N33" s="71"/>
-      <x:c r="O33" s="71"/>
-      <x:c r="P33" s="72" t="str">
+      <x:c r="A33" s="68" t="n">
+        <x:f>COUNTIFS('Weekly Review'!$D$6:$D$18,"&lt;&gt;",'Weekly Review'!$H$6:$H$18,"&lt;&gt;",'Weekly Review'!$L$6:$L$18,"&lt;&gt;")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B33" s="71" t="str">
+        <x:f>IF(A33=0,"",IF(SUMIF('Weekly Review'!$D$6:$D$18,"&lt;&gt;",'Weekly Review'!$C$6:$C$18)=0,"",SUM('Weekly Review'!$E$6:$E$18)/SUMIF('Weekly Review'!$D$6:$D$18,"&lt;&gt;",'Weekly Review'!$C$6:$C$18)))</x:f>
+      </x:c>
+      <x:c r="C33" s="71" t="str">
+        <x:f>IF(A33=0,"",IF(SUMIF('Weekly Review'!$H$6:$H$18,"&lt;&gt;",'Weekly Review'!$G$6:$G$18)=0,"",SUM('Weekly Review'!$I$6:$I$18)/SUMIF('Weekly Review'!$H$6:$H$18,"&lt;&gt;",'Weekly Review'!$G$6:$G$18)))</x:f>
+      </x:c>
+      <x:c r="D33" s="70" t="str">
+        <x:f>IF(A33=0,"",SUM('Weekly Review'!$M$6:$M$18)/A33)</x:f>
+      </x:c>
+      <x:c r="E33" s="68" t="str">
+        <x:f>IF(COUNTIF('Weekly Review'!$O$6:$O$18,"INCOMPLETE")&gt;0,"INCOMPLETE",IF(COUNTIF('Weekly Review'!$O$6:$O$18,"COMPLETE")&gt;0,"COMPLETE","NOT STARTED"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
+      <x:c r="F33" s="75"/>
+      <x:c r="G33" s="75"/>
+      <x:c r="H33" s="75"/>
+      <x:c r="I33" s="75"/>
+      <x:c r="J33" s="75"/>
+      <x:c r="K33" s="75"/>
+      <x:c r="L33" s="75"/>
+      <x:c r="M33" s="75"/>
+      <x:c r="N33" s="75"/>
+      <x:c r="O33" s="75"/>
+      <x:c r="P33" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!M$6,"dd mmm")</x:f>
         <x:v>22 Nov</x:v>
       </x:c>
-      <x:c r="Q33" s="74" t="n">
+      <x:c r="Q33" s="78" t="n">
         <x:f>'13-Week Forecast'!M$19</x:f>
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="R33" s="74" t="n">
+      <x:c r="R33" s="78" t="n">
         <x:f>'13-Week Forecast'!M$43</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="S33" s="71"/>
+      <x:c r="S33" s="75"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="71"/>
-      <x:c r="B34" s="71"/>
-      <x:c r="C34" s="71"/>
-      <x:c r="D34" s="71"/>
-      <x:c r="E34" s="71"/>
-      <x:c r="F34" s="71"/>
-      <x:c r="G34" s="71"/>
-      <x:c r="H34" s="71"/>
-      <x:c r="I34" s="71"/>
-      <x:c r="J34" s="71"/>
-      <x:c r="K34" s="71"/>
-      <x:c r="L34" s="71"/>
-      <x:c r="M34" s="71"/>
-      <x:c r="N34" s="71"/>
-      <x:c r="O34" s="71"/>
-      <x:c r="P34" s="72" t="str">
+      <x:c r="A34" s="75"/>
+      <x:c r="B34" s="75"/>
+      <x:c r="C34" s="75"/>
+      <x:c r="D34" s="75"/>
+      <x:c r="E34" s="75"/>
+      <x:c r="F34" s="75"/>
+      <x:c r="G34" s="75"/>
+      <x:c r="H34" s="75"/>
+      <x:c r="I34" s="75"/>
+      <x:c r="J34" s="75"/>
+      <x:c r="K34" s="75"/>
+      <x:c r="L34" s="75"/>
+      <x:c r="M34" s="75"/>
+      <x:c r="N34" s="75"/>
+      <x:c r="O34" s="75"/>
+      <x:c r="P34" s="76" t="str">
         <x:f>TEXT('13-Week Forecast'!N$6,"dd mmm")</x:f>
         <x:v>29 Nov</x:v>
       </x:c>
-      <x:c r="Q34" s="74" t="n">
+      <x:c r="Q34" s="78" t="n">
         <x:f>'13-Week Forecast'!N$19</x:f>
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="R34" s="74" t="n">
+      <x:c r="R34" s="78" t="n">
         <x:f>'13-Week Forecast'!N$43</x:f>
         <x:v>219000</x:v>
       </x:c>
-      <x:c r="S34" s="71"/>
+      <x:c r="S34" s="75"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="71"/>
-      <x:c r="B35" s="71"/>
-      <x:c r="C35" s="71"/>
-      <x:c r="D35" s="71"/>
-      <x:c r="E35" s="71"/>
-      <x:c r="F35" s="71"/>
-      <x:c r="G35" s="71"/>
-      <x:c r="H35" s="71"/>
-      <x:c r="I35" s="71"/>
-      <x:c r="J35" s="71"/>
-      <x:c r="K35" s="71"/>
-      <x:c r="L35" s="71"/>
-      <x:c r="M35" s="71"/>
-      <x:c r="N35" s="71"/>
-      <x:c r="O35" s="71"/>
-      <x:c r="P35" s="71"/>
-      <x:c r="Q35" s="71"/>
-      <x:c r="R35" s="71"/>
-      <x:c r="S35" s="71"/>
+      <x:c r="A35" s="74" t="str">
+        <x:v>Accuracy measures remain blank until actuals are entered. Positive receipt and payment variance is favourable; positive closing-cash bias means actual cash exceeded forecast.</x:v>
+      </x:c>
+      <x:c r="B35" s="74"/>
+      <x:c r="C35" s="74"/>
+      <x:c r="D35" s="74"/>
+      <x:c r="E35" s="74"/>
+      <x:c r="F35" s="75"/>
+      <x:c r="G35" s="75"/>
+      <x:c r="H35" s="75"/>
+      <x:c r="I35" s="75"/>
+      <x:c r="J35" s="75"/>
+      <x:c r="K35" s="75"/>
+      <x:c r="L35" s="75"/>
+      <x:c r="M35" s="75"/>
+      <x:c r="N35" s="75"/>
+      <x:c r="O35" s="75"/>
+      <x:c r="P35" s="75"/>
+      <x:c r="Q35" s="75"/>
+      <x:c r="R35" s="75"/>
+      <x:c r="S35" s="75"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="71"/>
-      <x:c r="B36" s="71"/>
-      <x:c r="C36" s="71"/>
-      <x:c r="D36" s="71"/>
-      <x:c r="E36" s="71"/>
-      <x:c r="F36" s="71"/>
-      <x:c r="G36" s="71"/>
-      <x:c r="H36" s="71"/>
-      <x:c r="I36" s="71"/>
-      <x:c r="J36" s="71"/>
-      <x:c r="K36" s="71"/>
-      <x:c r="L36" s="71"/>
-      <x:c r="M36" s="71"/>
-      <x:c r="N36" s="71"/>
-      <x:c r="O36" s="71"/>
-      <x:c r="P36" s="14" t="str">
+      <x:c r="A36" s="74"/>
+      <x:c r="B36" s="74"/>
+      <x:c r="C36" s="74"/>
+      <x:c r="D36" s="74"/>
+      <x:c r="E36" s="74"/>
+      <x:c r="F36" s="75"/>
+      <x:c r="G36" s="75"/>
+      <x:c r="H36" s="75"/>
+      <x:c r="I36" s="75"/>
+      <x:c r="J36" s="75"/>
+      <x:c r="K36" s="75"/>
+      <x:c r="L36" s="75"/>
+      <x:c r="M36" s="75"/>
+      <x:c r="N36" s="75"/>
+      <x:c r="O36" s="75"/>
+      <x:c r="P36" s="15" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="Q36" s="14" t="str">
+      <x:c r="Q36" s="15" t="str">
         <x:v>Base closing cash</x:v>
       </x:c>
-      <x:c r="R36" s="14" t="str">
+      <x:c r="R36" s="15" t="str">
         <x:v>Upside closing cash</x:v>
       </x:c>
-      <x:c r="S36" s="14" t="str">
+      <x:c r="S36" s="15" t="str">
         <x:v>Downside closing cash</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="71"/>
-      <x:c r="B37" s="71"/>
-      <x:c r="C37" s="71"/>
-      <x:c r="D37" s="71"/>
-      <x:c r="E37" s="71"/>
-      <x:c r="F37" s="71"/>
-      <x:c r="G37" s="71"/>
-      <x:c r="H37" s="71"/>
-      <x:c r="I37" s="71"/>
-      <x:c r="J37" s="71"/>
-      <x:c r="K37" s="71"/>
-      <x:c r="L37" s="71"/>
-      <x:c r="M37" s="71"/>
-      <x:c r="N37" s="71"/>
-      <x:c r="O37" s="71"/>
-      <x:c r="P37" s="72" t="n">
+      <x:c r="A37" s="75"/>
+      <x:c r="B37" s="75"/>
+      <x:c r="C37" s="75"/>
+      <x:c r="D37" s="75"/>
+      <x:c r="E37" s="75"/>
+      <x:c r="F37" s="75"/>
+      <x:c r="G37" s="75"/>
+      <x:c r="H37" s="75"/>
+      <x:c r="I37" s="75"/>
+      <x:c r="J37" s="75"/>
+      <x:c r="K37" s="75"/>
+      <x:c r="L37" s="75"/>
+      <x:c r="M37" s="75"/>
+      <x:c r="N37" s="75"/>
+      <x:c r="O37" s="75"/>
+      <x:c r="P37" s="76" t="n">
         <x:f>'13-Week Forecast'!B$6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="Q37" s="74" t="n">
+      <x:c r="Q37" s="78" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!B10:B17)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B10:B12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!B22:B41)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B22,'13-Week Forecast'!B31,'13-Week Forecast'!B33,'13-Week Forecast'!B41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="R37" s="74" t="n">
+      <x:c r="R37" s="78" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!B10:B17)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B10:B12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!B22:B41)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B22,'13-Week Forecast'!B31,'13-Week Forecast'!B33,'13-Week Forecast'!B41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="S37" s="74" t="n">
+      <x:c r="S37" s="78" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!B10:B17)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B10:B12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!B22:B41)+IF('13-Week Forecast'!B$7="Actual",0,SUM('13-Week Forecast'!B22,'13-Week Forecast'!B31,'13-Week Forecast'!B33,'13-Week Forecast'!B41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>358000</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="71"/>
-      <x:c r="B38" s="71"/>
-      <x:c r="C38" s="71"/>
-      <x:c r="D38" s="71"/>
-      <x:c r="E38" s="71"/>
-      <x:c r="F38" s="71"/>
-      <x:c r="G38" s="71"/>
-      <x:c r="H38" s="71"/>
-      <x:c r="I38" s="71"/>
-      <x:c r="J38" s="71"/>
-      <x:c r="K38" s="71"/>
-      <x:c r="L38" s="71"/>
-      <x:c r="M38" s="71"/>
-      <x:c r="N38" s="71"/>
-      <x:c r="O38" s="71"/>
-      <x:c r="P38" s="72" t="n">
+      <x:c r="A38" s="75"/>
+      <x:c r="B38" s="75"/>
+      <x:c r="C38" s="75"/>
+      <x:c r="D38" s="75"/>
+      <x:c r="E38" s="75"/>
+      <x:c r="F38" s="75"/>
+      <x:c r="G38" s="75"/>
+      <x:c r="H38" s="75"/>
+      <x:c r="I38" s="75"/>
+      <x:c r="J38" s="75"/>
+      <x:c r="K38" s="75"/>
+      <x:c r="L38" s="75"/>
+      <x:c r="M38" s="75"/>
+      <x:c r="N38" s="75"/>
+      <x:c r="O38" s="75"/>
+      <x:c r="P38" s="76" t="n">
         <x:f>'13-Week Forecast'!C$6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="Q38" s="74" t="n">
+      <x:c r="Q38" s="78" t="n">
         <x:f>Q37+SUM('13-Week Forecast'!C10:C17)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C10:C12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!C22:C41)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C22,'13-Week Forecast'!C31,'13-Week Forecast'!C33,'13-Week Forecast'!C41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="R38" s="74" t="n">
+      <x:c r="R38" s="78" t="n">
         <x:f>R37+SUM('13-Week Forecast'!C10:C17)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C10:C12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!C22:C41)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C22,'13-Week Forecast'!C31,'13-Week Forecast'!C33,'13-Week Forecast'!C41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>364380</x:v>
       </x:c>
-      <x:c r="S38" s="74" t="n">
+      <x:c r="S38" s="78" t="n">
         <x:f>S37+SUM('13-Week Forecast'!C10:C17)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C10:C12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!C22:C41)+IF('13-Week Forecast'!C$7="Actual",0,SUM('13-Week Forecast'!C22,'13-Week Forecast'!C31,'13-Week Forecast'!C33,'13-Week Forecast'!C41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>318800</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="71"/>
-      <x:c r="B39" s="71"/>
-      <x:c r="C39" s="71"/>
-      <x:c r="D39" s="71"/>
-      <x:c r="E39" s="71"/>
-      <x:c r="F39" s="71"/>
-      <x:c r="G39" s="71"/>
-      <x:c r="H39" s="71"/>
-      <x:c r="I39" s="71"/>
-      <x:c r="J39" s="71"/>
-      <x:c r="K39" s="71"/>
-      <x:c r="L39" s="71"/>
-      <x:c r="M39" s="71"/>
-      <x:c r="N39" s="71"/>
-      <x:c r="O39" s="71"/>
-      <x:c r="P39" s="72" t="n">
+      <x:c r="A39" s="75"/>
+      <x:c r="B39" s="75"/>
+      <x:c r="C39" s="75"/>
+      <x:c r="D39" s="75"/>
+      <x:c r="E39" s="75"/>
+      <x:c r="F39" s="75"/>
+      <x:c r="G39" s="75"/>
+      <x:c r="H39" s="75"/>
+      <x:c r="I39" s="75"/>
+      <x:c r="J39" s="75"/>
+      <x:c r="K39" s="75"/>
+      <x:c r="L39" s="75"/>
+      <x:c r="M39" s="75"/>
+      <x:c r="N39" s="75"/>
+      <x:c r="O39" s="75"/>
+      <x:c r="P39" s="76" t="n">
         <x:f>'13-Week Forecast'!D$6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="Q39" s="74" t="n">
+      <x:c r="Q39" s="78" t="n">
         <x:f>Q38+SUM('13-Week Forecast'!D10:D17)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D10:D12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!D22:D41)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D22,'13-Week Forecast'!D31,'13-Week Forecast'!D33,'13-Week Forecast'!D41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="R39" s="74" t="n">
+      <x:c r="R39" s="78" t="n">
         <x:f>R38+SUM('13-Week Forecast'!D10:D17)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D10:D12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!D22:D41)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D22,'13-Week Forecast'!D31,'13-Week Forecast'!D33,'13-Week Forecast'!D41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>354920</x:v>
       </x:c>
-      <x:c r="S39" s="74" t="n">
+      <x:c r="S39" s="78" t="n">
         <x:f>S38+SUM('13-Week Forecast'!D10:D17)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D10:D12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!D22:D41)+IF('13-Week Forecast'!D$7="Actual",0,SUM('13-Week Forecast'!D22,'13-Week Forecast'!D31,'13-Week Forecast'!D33,'13-Week Forecast'!D41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>266150</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="71"/>
-      <x:c r="B40" s="71"/>
-      <x:c r="C40" s="71"/>
-      <x:c r="D40" s="71"/>
-      <x:c r="E40" s="71"/>
-      <x:c r="F40" s="71"/>
-      <x:c r="G40" s="71"/>
-      <x:c r="H40" s="71"/>
-      <x:c r="I40" s="71"/>
-      <x:c r="J40" s="71"/>
-      <x:c r="K40" s="71"/>
-      <x:c r="L40" s="71"/>
-      <x:c r="M40" s="71"/>
-      <x:c r="N40" s="71"/>
-      <x:c r="O40" s="71"/>
-      <x:c r="P40" s="72" t="n">
+      <x:c r="A40" s="75"/>
+      <x:c r="B40" s="75"/>
+      <x:c r="C40" s="75"/>
+      <x:c r="D40" s="75"/>
+      <x:c r="E40" s="75"/>
+      <x:c r="F40" s="75"/>
+      <x:c r="G40" s="75"/>
+      <x:c r="H40" s="75"/>
+      <x:c r="I40" s="75"/>
+      <x:c r="J40" s="75"/>
+      <x:c r="K40" s="75"/>
+      <x:c r="L40" s="75"/>
+      <x:c r="M40" s="75"/>
+      <x:c r="N40" s="75"/>
+      <x:c r="O40" s="75"/>
+      <x:c r="P40" s="76" t="n">
         <x:f>'13-Week Forecast'!E$6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="Q40" s="74" t="n">
+      <x:c r="Q40" s="78" t="n">
         <x:f>Q39+SUM('13-Week Forecast'!E10:E17)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E10:E12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!E22:E41)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E22,'13-Week Forecast'!E31,'13-Week Forecast'!E33,'13-Week Forecast'!E41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="R40" s="74" t="n">
+      <x:c r="R40" s="78" t="n">
         <x:f>R39+SUM('13-Week Forecast'!E10:E17)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E10:E12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!E22:E41)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E22,'13-Week Forecast'!E31,'13-Week Forecast'!E33,'13-Week Forecast'!E41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>336680</x:v>
       </x:c>
-      <x:c r="S40" s="74" t="n">
+      <x:c r="S40" s="78" t="n">
         <x:f>S39+SUM('13-Week Forecast'!E10:E17)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E10:E12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!E22:E41)+IF('13-Week Forecast'!E$7="Actual",0,SUM('13-Week Forecast'!E22,'13-Week Forecast'!E31,'13-Week Forecast'!E33,'13-Week Forecast'!E41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>206900</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="71"/>
-      <x:c r="B41" s="71"/>
-      <x:c r="C41" s="71"/>
-      <x:c r="D41" s="71"/>
-      <x:c r="E41" s="71"/>
-      <x:c r="F41" s="71"/>
-      <x:c r="G41" s="71"/>
-      <x:c r="H41" s="71"/>
-      <x:c r="I41" s="71"/>
-      <x:c r="J41" s="71"/>
-      <x:c r="K41" s="71"/>
-      <x:c r="L41" s="71"/>
-      <x:c r="M41" s="71"/>
-      <x:c r="N41" s="71"/>
-      <x:c r="O41" s="71"/>
-      <x:c r="P41" s="72" t="n">
+      <x:c r="A41" s="75"/>
+      <x:c r="B41" s="75"/>
+      <x:c r="C41" s="75"/>
+      <x:c r="D41" s="75"/>
+      <x:c r="E41" s="75"/>
+      <x:c r="F41" s="75"/>
+      <x:c r="G41" s="75"/>
+      <x:c r="H41" s="75"/>
+      <x:c r="I41" s="75"/>
+      <x:c r="J41" s="75"/>
+      <x:c r="K41" s="75"/>
+      <x:c r="L41" s="75"/>
+      <x:c r="M41" s="75"/>
+      <x:c r="N41" s="75"/>
+      <x:c r="O41" s="75"/>
+      <x:c r="P41" s="76" t="n">
         <x:f>'13-Week Forecast'!F$6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="Q41" s="74" t="n">
+      <x:c r="Q41" s="78" t="n">
         <x:f>Q40+SUM('13-Week Forecast'!F10:F17)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F10:F12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!F22:F41)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F22,'13-Week Forecast'!F31,'13-Week Forecast'!F33,'13-Week Forecast'!F41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="R41" s="74" t="n">
+      <x:c r="R41" s="78" t="n">
         <x:f>R40+SUM('13-Week Forecast'!F10:F17)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F10:F12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!F22:F41)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F22,'13-Week Forecast'!F31,'13-Week Forecast'!F33,'13-Week Forecast'!F41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>257940</x:v>
       </x:c>
-      <x:c r="S41" s="74" t="n">
+      <x:c r="S41" s="78" t="n">
         <x:f>S40+SUM('13-Week Forecast'!F10:F17)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F10:F12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!F22:F41)+IF('13-Week Forecast'!F$7="Actual",0,SUM('13-Week Forecast'!F22,'13-Week Forecast'!F31,'13-Week Forecast'!F33,'13-Week Forecast'!F41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>88550</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="71"/>
-      <x:c r="B42" s="71"/>
-      <x:c r="C42" s="71"/>
-      <x:c r="D42" s="71"/>
-      <x:c r="E42" s="71"/>
-      <x:c r="F42" s="71"/>
-      <x:c r="G42" s="71"/>
-      <x:c r="H42" s="71"/>
-      <x:c r="I42" s="71"/>
-      <x:c r="J42" s="71"/>
-      <x:c r="K42" s="71"/>
-      <x:c r="L42" s="71"/>
-      <x:c r="M42" s="71"/>
-      <x:c r="N42" s="71"/>
-      <x:c r="O42" s="71"/>
-      <x:c r="P42" s="72" t="n">
+      <x:c r="A42" s="75"/>
+      <x:c r="B42" s="75"/>
+      <x:c r="C42" s="75"/>
+      <x:c r="D42" s="75"/>
+      <x:c r="E42" s="75"/>
+      <x:c r="F42" s="75"/>
+      <x:c r="G42" s="75"/>
+      <x:c r="H42" s="75"/>
+      <x:c r="I42" s="75"/>
+      <x:c r="J42" s="75"/>
+      <x:c r="K42" s="75"/>
+      <x:c r="L42" s="75"/>
+      <x:c r="M42" s="75"/>
+      <x:c r="N42" s="75"/>
+      <x:c r="O42" s="75"/>
+      <x:c r="P42" s="76" t="n">
         <x:f>'13-Week Forecast'!G$6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="Q42" s="74" t="n">
+      <x:c r="Q42" s="78" t="n">
         <x:f>Q41+SUM('13-Week Forecast'!G10:G17)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G10:G12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!G22:G41)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G22,'13-Week Forecast'!G31,'13-Week Forecast'!G33,'13-Week Forecast'!G41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="R42" s="74" t="n">
+      <x:c r="R42" s="78" t="n">
         <x:f>R41+SUM('13-Week Forecast'!G10:G17)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G10:G12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!G22:G41)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G22,'13-Week Forecast'!G31,'13-Week Forecast'!G33,'13-Week Forecast'!G41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>203320</x:v>
       </x:c>
-      <x:c r="S42" s="74" t="n">
+      <x:c r="S42" s="78" t="n">
         <x:f>S41+SUM('13-Week Forecast'!G10:G17)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G10:G12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!G22:G41)+IF('13-Week Forecast'!G$7="Actual",0,SUM('13-Week Forecast'!G22,'13-Week Forecast'!G31,'13-Week Forecast'!G33,'13-Week Forecast'!G41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-6050</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="71"/>
-      <x:c r="B43" s="71"/>
-      <x:c r="C43" s="71"/>
-      <x:c r="D43" s="71"/>
-      <x:c r="E43" s="71"/>
-      <x:c r="F43" s="71"/>
-      <x:c r="G43" s="71"/>
-      <x:c r="H43" s="71"/>
-      <x:c r="I43" s="71"/>
-      <x:c r="J43" s="71"/>
-      <x:c r="K43" s="71"/>
-      <x:c r="L43" s="71"/>
-      <x:c r="M43" s="71"/>
-      <x:c r="N43" s="71"/>
-      <x:c r="O43" s="71"/>
-      <x:c r="P43" s="72" t="n">
+      <x:c r="A43" s="75"/>
+      <x:c r="B43" s="75"/>
+      <x:c r="C43" s="75"/>
+      <x:c r="D43" s="75"/>
+      <x:c r="E43" s="75"/>
+      <x:c r="F43" s="75"/>
+      <x:c r="G43" s="75"/>
+      <x:c r="H43" s="75"/>
+      <x:c r="I43" s="75"/>
+      <x:c r="J43" s="75"/>
+      <x:c r="K43" s="75"/>
+      <x:c r="L43" s="75"/>
+      <x:c r="M43" s="75"/>
+      <x:c r="N43" s="75"/>
+      <x:c r="O43" s="75"/>
+      <x:c r="P43" s="76" t="n">
         <x:f>'13-Week Forecast'!H$6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="Q43" s="74" t="n">
+      <x:c r="Q43" s="78" t="n">
         <x:f>Q42+SUM('13-Week Forecast'!H10:H17)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H10:H12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!H22:H41)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H22,'13-Week Forecast'!H31,'13-Week Forecast'!H33,'13-Week Forecast'!H41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="R43" s="74" t="n">
+      <x:c r="R43" s="78" t="n">
         <x:f>R42+SUM('13-Week Forecast'!H10:H17)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H10:H12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!H22:H41)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H22,'13-Week Forecast'!H31,'13-Week Forecast'!H33,'13-Week Forecast'!H41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>300000</x:v>
       </x:c>
-      <x:c r="S43" s="74" t="n">
+      <x:c r="S43" s="78" t="n">
         <x:f>S42+SUM('13-Week Forecast'!H10:H17)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H10:H12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!H22:H41)+IF('13-Week Forecast'!H$7="Actual",0,SUM('13-Week Forecast'!H22,'13-Week Forecast'!H31,'13-Week Forecast'!H33,'13-Week Forecast'!H41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>52600</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="71"/>
-      <x:c r="B44" s="71"/>
-      <x:c r="C44" s="71"/>
-      <x:c r="D44" s="71"/>
-      <x:c r="E44" s="71"/>
-      <x:c r="F44" s="71"/>
-      <x:c r="G44" s="71"/>
-      <x:c r="H44" s="71"/>
-      <x:c r="I44" s="71"/>
-      <x:c r="J44" s="71"/>
-      <x:c r="K44" s="71"/>
-      <x:c r="L44" s="71"/>
-      <x:c r="M44" s="71"/>
-      <x:c r="N44" s="71"/>
-      <x:c r="O44" s="71"/>
-      <x:c r="P44" s="72" t="n">
+      <x:c r="A44" s="75"/>
+      <x:c r="B44" s="75"/>
+      <x:c r="C44" s="75"/>
+      <x:c r="D44" s="75"/>
+      <x:c r="E44" s="75"/>
+      <x:c r="F44" s="75"/>
+      <x:c r="G44" s="75"/>
+      <x:c r="H44" s="75"/>
+      <x:c r="I44" s="75"/>
+      <x:c r="J44" s="75"/>
+      <x:c r="K44" s="75"/>
+      <x:c r="L44" s="75"/>
+      <x:c r="M44" s="75"/>
+      <x:c r="N44" s="75"/>
+      <x:c r="O44" s="75"/>
+      <x:c r="P44" s="76" t="n">
         <x:f>'13-Week Forecast'!I$6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="Q44" s="74" t="n">
+      <x:c r="Q44" s="78" t="n">
         <x:f>Q43+SUM('13-Week Forecast'!I10:I17)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I10:I12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!I22:I41)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I22,'13-Week Forecast'!I31,'13-Week Forecast'!I33,'13-Week Forecast'!I41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="R44" s="74" t="n">
+      <x:c r="R44" s="78" t="n">
         <x:f>R43+SUM('13-Week Forecast'!I10:I17)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I10:I12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!I22:I41)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I22,'13-Week Forecast'!I31,'13-Week Forecast'!I33,'13-Week Forecast'!I41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>256060</x:v>
       </x:c>
-      <x:c r="S44" s="74" t="n">
+      <x:c r="S44" s="78" t="n">
         <x:f>S43+SUM('13-Week Forecast'!I10:I17)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I10:I12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!I22:I41)+IF('13-Week Forecast'!I$7="Actual",0,SUM('13-Week Forecast'!I22,'13-Week Forecast'!I31,'13-Week Forecast'!I33,'13-Week Forecast'!I41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-30500</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="71"/>
-      <x:c r="B45" s="71"/>
-      <x:c r="C45" s="71"/>
-      <x:c r="D45" s="71"/>
-      <x:c r="E45" s="71"/>
-      <x:c r="F45" s="71"/>
-      <x:c r="G45" s="71"/>
-      <x:c r="H45" s="71"/>
-      <x:c r="I45" s="71"/>
-      <x:c r="J45" s="71"/>
-      <x:c r="K45" s="71"/>
-      <x:c r="L45" s="71"/>
-      <x:c r="M45" s="71"/>
-      <x:c r="N45" s="71"/>
-      <x:c r="O45" s="71"/>
-      <x:c r="P45" s="72" t="n">
+      <x:c r="A45" s="75"/>
+      <x:c r="B45" s="75"/>
+      <x:c r="C45" s="75"/>
+      <x:c r="D45" s="75"/>
+      <x:c r="E45" s="75"/>
+      <x:c r="F45" s="75"/>
+      <x:c r="G45" s="75"/>
+      <x:c r="H45" s="75"/>
+      <x:c r="I45" s="75"/>
+      <x:c r="J45" s="75"/>
+      <x:c r="K45" s="75"/>
+      <x:c r="L45" s="75"/>
+      <x:c r="M45" s="75"/>
+      <x:c r="N45" s="75"/>
+      <x:c r="O45" s="75"/>
+      <x:c r="P45" s="76" t="n">
         <x:f>'13-Week Forecast'!J$6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="Q45" s="74" t="n">
+      <x:c r="Q45" s="78" t="n">
         <x:f>Q44+SUM('13-Week Forecast'!J10:J17)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J10:J12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!J22:J41)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J22,'13-Week Forecast'!J31,'13-Week Forecast'!J33,'13-Week Forecast'!J41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="R45" s="74" t="n">
+      <x:c r="R45" s="78" t="n">
         <x:f>R44+SUM('13-Week Forecast'!J10:J17)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J10:J12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!J22:J41)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J22,'13-Week Forecast'!J31,'13-Week Forecast'!J33,'13-Week Forecast'!J41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>226480</x:v>
       </x:c>
-      <x:c r="S45" s="74" t="n">
+      <x:c r="S45" s="78" t="n">
         <x:f>S44+SUM('13-Week Forecast'!J10:J17)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J10:J12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!J22:J41)+IF('13-Week Forecast'!J$7="Actual",0,SUM('13-Week Forecast'!J22,'13-Week Forecast'!J31,'13-Week Forecast'!J33,'13-Week Forecast'!J41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-100300</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="71"/>
-      <x:c r="B46" s="71"/>
-      <x:c r="C46" s="71"/>
-      <x:c r="D46" s="71"/>
-      <x:c r="E46" s="71"/>
-      <x:c r="F46" s="71"/>
-      <x:c r="G46" s="71"/>
-      <x:c r="H46" s="71"/>
-      <x:c r="I46" s="71"/>
-      <x:c r="J46" s="71"/>
-      <x:c r="K46" s="71"/>
-      <x:c r="L46" s="71"/>
-      <x:c r="M46" s="71"/>
-      <x:c r="N46" s="71"/>
-      <x:c r="O46" s="71"/>
-      <x:c r="P46" s="72" t="n">
+      <x:c r="A46" s="75"/>
+      <x:c r="B46" s="75"/>
+      <x:c r="C46" s="75"/>
+      <x:c r="D46" s="75"/>
+      <x:c r="E46" s="75"/>
+      <x:c r="F46" s="75"/>
+      <x:c r="G46" s="75"/>
+      <x:c r="H46" s="75"/>
+      <x:c r="I46" s="75"/>
+      <x:c r="J46" s="75"/>
+      <x:c r="K46" s="75"/>
+      <x:c r="L46" s="75"/>
+      <x:c r="M46" s="75"/>
+      <x:c r="N46" s="75"/>
+      <x:c r="O46" s="75"/>
+      <x:c r="P46" s="76" t="n">
         <x:f>'13-Week Forecast'!K$6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="Q46" s="74" t="n">
+      <x:c r="Q46" s="78" t="n">
         <x:f>Q45+SUM('13-Week Forecast'!K10:K17)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K10:K12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!K22:K41)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K22,'13-Week Forecast'!K31,'13-Week Forecast'!K33,'13-Week Forecast'!K41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="R46" s="74" t="n">
+      <x:c r="R46" s="78" t="n">
         <x:f>R45+SUM('13-Week Forecast'!K10:K17)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K10:K12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!K22:K41)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K22,'13-Week Forecast'!K31,'13-Week Forecast'!K33,'13-Week Forecast'!K41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>260600</x:v>
       </x:c>
-      <x:c r="S46" s="74" t="n">
+      <x:c r="S46" s="78" t="n">
         <x:f>S45+SUM('13-Week Forecast'!K10:K17)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K10:K12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!K22:K41)+IF('13-Week Forecast'!K$7="Actual",0,SUM('13-Week Forecast'!K22,'13-Week Forecast'!K31,'13-Week Forecast'!K33,'13-Week Forecast'!K41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-108350</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="71"/>
-      <x:c r="B47" s="71"/>
-      <x:c r="C47" s="71"/>
-      <x:c r="D47" s="71"/>
-      <x:c r="E47" s="71"/>
-      <x:c r="F47" s="71"/>
-      <x:c r="G47" s="71"/>
-      <x:c r="H47" s="71"/>
-      <x:c r="I47" s="71"/>
-      <x:c r="J47" s="71"/>
-      <x:c r="K47" s="71"/>
-      <x:c r="L47" s="71"/>
-      <x:c r="M47" s="71"/>
-      <x:c r="N47" s="71"/>
-      <x:c r="O47" s="71"/>
-      <x:c r="P47" s="72" t="n">
+      <x:c r="A47" s="75"/>
+      <x:c r="B47" s="75"/>
+      <x:c r="C47" s="75"/>
+      <x:c r="D47" s="75"/>
+      <x:c r="E47" s="75"/>
+      <x:c r="F47" s="75"/>
+      <x:c r="G47" s="75"/>
+      <x:c r="H47" s="75"/>
+      <x:c r="I47" s="75"/>
+      <x:c r="J47" s="75"/>
+      <x:c r="K47" s="75"/>
+      <x:c r="L47" s="75"/>
+      <x:c r="M47" s="75"/>
+      <x:c r="N47" s="75"/>
+      <x:c r="O47" s="75"/>
+      <x:c r="P47" s="76" t="n">
         <x:f>'13-Week Forecast'!L$6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="Q47" s="74" t="n">
+      <x:c r="Q47" s="78" t="n">
         <x:f>Q46+SUM('13-Week Forecast'!L10:L17)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L10:L12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!L22:L41)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L22,'13-Week Forecast'!L31,'13-Week Forecast'!L33,'13-Week Forecast'!L41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="R47" s="74" t="n">
+      <x:c r="R47" s="78" t="n">
         <x:f>R46+SUM('13-Week Forecast'!L10:L17)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L10:L12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!L22:L41)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L22,'13-Week Forecast'!L31,'13-Week Forecast'!L33,'13-Week Forecast'!L41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>237020</x:v>
       </x:c>
-      <x:c r="S47" s="74" t="n">
+      <x:c r="S47" s="78" t="n">
         <x:f>S46+SUM('13-Week Forecast'!L10:L17)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L10:L12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!L22:L41)+IF('13-Week Forecast'!L$7="Actual",0,SUM('13-Week Forecast'!L22,'13-Week Forecast'!L31,'13-Week Forecast'!L33,'13-Week Forecast'!L41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-174900</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="71"/>
-      <x:c r="B48" s="71"/>
-      <x:c r="C48" s="71"/>
-      <x:c r="D48" s="71"/>
-      <x:c r="E48" s="71"/>
-      <x:c r="F48" s="71"/>
-      <x:c r="G48" s="71"/>
-      <x:c r="H48" s="71"/>
-      <x:c r="I48" s="71"/>
-      <x:c r="J48" s="71"/>
-      <x:c r="K48" s="71"/>
-      <x:c r="L48" s="71"/>
-      <x:c r="M48" s="71"/>
-      <x:c r="N48" s="71"/>
-      <x:c r="O48" s="71"/>
-      <x:c r="P48" s="72" t="n">
+      <x:c r="A48" s="75"/>
+      <x:c r="B48" s="75"/>
+      <x:c r="C48" s="75"/>
+      <x:c r="D48" s="75"/>
+      <x:c r="E48" s="75"/>
+      <x:c r="F48" s="75"/>
+      <x:c r="G48" s="75"/>
+      <x:c r="H48" s="75"/>
+      <x:c r="I48" s="75"/>
+      <x:c r="J48" s="75"/>
+      <x:c r="K48" s="75"/>
+      <x:c r="L48" s="75"/>
+      <x:c r="M48" s="75"/>
+      <x:c r="N48" s="75"/>
+      <x:c r="O48" s="75"/>
+      <x:c r="P48" s="76" t="n">
         <x:f>'13-Week Forecast'!M$6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="Q48" s="74" t="n">
+      <x:c r="Q48" s="78" t="n">
         <x:f>Q47+SUM('13-Week Forecast'!M10:M17)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M10:M12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!M22:M41)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M22,'13-Week Forecast'!M31,'13-Week Forecast'!M33,'13-Week Forecast'!M41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="R48" s="74" t="n">
+      <x:c r="R48" s="78" t="n">
         <x:f>R47+SUM('13-Week Forecast'!M10:M17)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M10:M12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!M22:M41)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M22,'13-Week Forecast'!M31,'13-Week Forecast'!M33,'13-Week Forecast'!M41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>234980</x:v>
       </x:c>
-      <x:c r="S48" s="74" t="n">
+      <x:c r="S48" s="78" t="n">
         <x:f>S47+SUM('13-Week Forecast'!M10:M17)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M10:M12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!M22:M41)+IF('13-Week Forecast'!M$7="Actual",0,SUM('13-Week Forecast'!M22,'13-Week Forecast'!M31,'13-Week Forecast'!M33,'13-Week Forecast'!M41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-221400</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="71"/>
-      <x:c r="B49" s="71"/>
-      <x:c r="C49" s="71"/>
-      <x:c r="D49" s="71"/>
-      <x:c r="E49" s="71"/>
-      <x:c r="F49" s="71"/>
-      <x:c r="G49" s="71"/>
-      <x:c r="H49" s="71"/>
-      <x:c r="I49" s="71"/>
-      <x:c r="J49" s="71"/>
-      <x:c r="K49" s="71"/>
-      <x:c r="L49" s="71"/>
-      <x:c r="M49" s="71"/>
-      <x:c r="N49" s="71"/>
-      <x:c r="O49" s="71"/>
-      <x:c r="P49" s="72" t="n">
+      <x:c r="A49" s="75"/>
+      <x:c r="B49" s="75"/>
+      <x:c r="C49" s="75"/>
+      <x:c r="D49" s="75"/>
+      <x:c r="E49" s="75"/>
+      <x:c r="F49" s="75"/>
+      <x:c r="G49" s="75"/>
+      <x:c r="H49" s="75"/>
+      <x:c r="I49" s="75"/>
+      <x:c r="J49" s="75"/>
+      <x:c r="K49" s="75"/>
+      <x:c r="L49" s="75"/>
+      <x:c r="M49" s="75"/>
+      <x:c r="N49" s="75"/>
+      <x:c r="O49" s="75"/>
+      <x:c r="P49" s="76" t="n">
         <x:f>'13-Week Forecast'!N$6</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="Q49" s="74" t="n">
+      <x:c r="Q49" s="78" t="n">
         <x:f>Q48+SUM('13-Week Forecast'!N10:N17)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N10:N12)*('Assumptions'!$C$15-1))-(SUM('13-Week Forecast'!N22:N41)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N22,'13-Week Forecast'!N31,'13-Week Forecast'!N33,'13-Week Forecast'!N41)*('Assumptions'!$D$15-1)))</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="R49" s="74" t="n">
+      <x:c r="R49" s="78" t="n">
         <x:f>R48+SUM('13-Week Forecast'!N10:N17)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N10:N12)*('Assumptions'!$C$16-1))-(SUM('13-Week Forecast'!N22:N41)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N22,'13-Week Forecast'!N31,'13-Week Forecast'!N33,'13-Week Forecast'!N41)*('Assumptions'!$D$16-1)))</x:f>
         <x:v>199320</x:v>
       </x:c>
-      <x:c r="S49" s="74" t="n">
+      <x:c r="S49" s="78" t="n">
         <x:f>S48+SUM('13-Week Forecast'!N10:N17)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N10:N12)*('Assumptions'!$C$17-1))-(SUM('13-Week Forecast'!N22:N41)+IF('13-Week Forecast'!N$7="Actual",0,SUM('13-Week Forecast'!N22,'13-Week Forecast'!N31,'13-Week Forecast'!N33,'13-Week Forecast'!N41)*('Assumptions'!$D$17-1)))</x:f>
         <x:v>-302550</x:v>
       </x:c>
@@ -3486,39 +3646,51 @@
     <x:mergeCell ref="A1:S1"/>
     <x:mergeCell ref="A2:S2"/>
     <x:mergeCell ref="A4:O4"/>
+    <x:mergeCell ref="A35:E36"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="I7:I7">
-    <x:cfRule type="expression" dxfId="20" priority="1">
+    <x:cfRule type="expression" dxfId="23" priority="1">
       <x:formula>I7="PASS"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="21" priority="2">
+    <x:cfRule type="expression" dxfId="24" priority="2">
       <x:formula>I7="FAIL"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="J7:J7">
-    <x:cfRule type="expression" dxfId="22" priority="3">
+    <x:cfRule type="expression" dxfId="25" priority="3">
       <x:formula>J7="ACTION REQUIRED"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="23" priority="4">
+    <x:cfRule type="expression" dxfId="26" priority="4">
       <x:formula>J7="WATCH"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="24" priority="5">
+    <x:cfRule type="expression" dxfId="27" priority="5">
       <x:formula>J7="OK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E12:E24">
-    <x:cfRule type="expression" dxfId="25" priority="6">
+    <x:cfRule type="expression" dxfId="28" priority="6">
       <x:formula>E12="BELOW BUFFER"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="26" priority="7">
+    <x:cfRule type="expression" dxfId="29" priority="7">
       <x:formula>E12="WATCH"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="27" priority="8">
+    <x:cfRule type="expression" dxfId="30" priority="8">
       <x:formula>E12="OK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="E33:E33">
+    <x:cfRule type="expression" dxfId="31" priority="9">
+      <x:formula>E33="COMPLETE"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="32" priority="10">
+      <x:formula>E33="INCOMPLETE"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="33" priority="11">
+      <x:formula>E33="NOT STARTED"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca6d148ad5dd4b41"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce5aa11df1394a67"/>
 </x:worksheet>
 </file>
 
@@ -3527,7 +3699,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
@@ -3555,257 +3727,324 @@
       <x:c r="F2" s="8"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="71"/>
-      <x:c r="B3" s="71"/>
-      <x:c r="C3" s="71"/>
-      <x:c r="D3" s="71"/>
-      <x:c r="E3" s="71"/>
-      <x:c r="F3" s="71"/>
+      <x:c r="A3" s="75"/>
+      <x:c r="B3" s="75"/>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+      <x:c r="F3" s="75"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="A4" s="15" t="str">
         <x:v>Core controls</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="str">
+      <x:c r="B4" s="15" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C4" s="71"/>
-      <x:c r="D4" s="71"/>
-      <x:c r="E4" s="71"/>
-      <x:c r="F4" s="71"/>
+      <x:c r="C4" s="75"/>
+      <x:c r="D4" s="75"/>
+      <x:c r="E4" s="75"/>
+      <x:c r="F4" s="75"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="71" t="str">
+      <x:c r="A5" s="75" t="str">
         <x:v>Business name</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="str">
+      <x:c r="B5" s="29" t="str">
         <x:v>Illustrative Australian business</x:v>
       </x:c>
-      <x:c r="C5" s="71"/>
-      <x:c r="D5" s="71"/>
-      <x:c r="E5" s="71"/>
-      <x:c r="F5" s="71"/>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="75"/>
+      <x:c r="E5" s="75"/>
+      <x:c r="F5" s="75"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="71" t="str">
+      <x:c r="A6" s="75" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="B6" s="28" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>AUD</x:v>
       </x:c>
-      <x:c r="C6" s="71"/>
-      <x:c r="D6" s="71"/>
-      <x:c r="E6" s="71"/>
-      <x:c r="F6" s="71"/>
+      <x:c r="C6" s="75"/>
+      <x:c r="D6" s="75"/>
+      <x:c r="E6" s="75"/>
+      <x:c r="F6" s="75"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="71" t="str">
+      <x:c r="A7" s="75" t="str">
         <x:v>Units</x:v>
       </x:c>
-      <x:c r="B7" s="28" t="str">
+      <x:c r="B7" s="29" t="str">
         <x:v>Whole dollars</x:v>
       </x:c>
-      <x:c r="C7" s="71"/>
-      <x:c r="D7" s="71"/>
-      <x:c r="E7" s="71"/>
-      <x:c r="F7" s="71"/>
+      <x:c r="C7" s="75"/>
+      <x:c r="D7" s="75"/>
+      <x:c r="E7" s="75"/>
+      <x:c r="F7" s="75"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="71" t="str">
+      <x:c r="A8" s="75" t="str">
         <x:v>Forecast start date</x:v>
       </x:c>
-      <x:c r="B8" s="29" t="n">
+      <x:c r="B8" s="30" t="n">
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="C8" s="71"/>
-      <x:c r="D8" s="71"/>
-      <x:c r="E8" s="71"/>
-      <x:c r="F8" s="71"/>
+      <x:c r="C8" s="75"/>
+      <x:c r="D8" s="75"/>
+      <x:c r="E8" s="75"/>
+      <x:c r="F8" s="75"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="71" t="str">
+      <x:c r="A9" s="75" t="str">
         <x:v>As-at date</x:v>
       </x:c>
-      <x:c r="B9" s="29" t="n">
+      <x:c r="B9" s="30" t="n">
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C9" s="71"/>
-      <x:c r="D9" s="71"/>
-      <x:c r="E9" s="71"/>
-      <x:c r="F9" s="71"/>
+      <x:c r="C9" s="75"/>
+      <x:c r="D9" s="75"/>
+      <x:c r="E9" s="75"/>
+      <x:c r="F9" s="75"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="71" t="str">
+      <x:c r="A10" s="75" t="str">
         <x:v>Opening cash</x:v>
       </x:c>
-      <x:c r="B10" s="30" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="C10" s="71"/>
-      <x:c r="D10" s="71"/>
-      <x:c r="E10" s="71"/>
-      <x:c r="F10" s="71"/>
+      <x:c r="C10" s="75"/>
+      <x:c r="D10" s="75"/>
+      <x:c r="E10" s="75"/>
+      <x:c r="F10" s="75"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="71" t="str">
+      <x:c r="A11" s="75" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B11" s="30" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="C11" s="71"/>
-      <x:c r="D11" s="71"/>
-      <x:c r="E11" s="71"/>
-      <x:c r="F11" s="71"/>
+      <x:c r="C11" s="75"/>
+      <x:c r="D11" s="75"/>
+      <x:c r="E11" s="75"/>
+      <x:c r="F11" s="75"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="71" t="str">
+      <x:c r="A12" s="75" t="str">
         <x:v>Selected scenario</x:v>
       </x:c>
-      <x:c r="B12" s="28" t="str">
+      <x:c r="B12" s="29" t="str">
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="C12" s="71"/>
-      <x:c r="D12" s="71"/>
-      <x:c r="E12" s="71"/>
-      <x:c r="F12" s="71"/>
+      <x:c r="C12" s="75"/>
+      <x:c r="D12" s="75"/>
+      <x:c r="E12" s="75"/>
+      <x:c r="F12" s="75"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="71"/>
-      <x:c r="B13" s="71"/>
-      <x:c r="C13" s="71"/>
-      <x:c r="D13" s="71"/>
-      <x:c r="E13" s="71"/>
-      <x:c r="F13" s="71"/>
+      <x:c r="A13" s="75"/>
+      <x:c r="B13" s="75"/>
+      <x:c r="C13" s="75"/>
+      <x:c r="D13" s="75"/>
+      <x:c r="E13" s="75"/>
+      <x:c r="F13" s="75"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="14" t="str">
+      <x:c r="A14" s="15" t="str">
         <x:v>Scenario controls</x:v>
       </x:c>
-      <x:c r="B14" s="14" t="str">
+      <x:c r="B14" s="15" t="str">
         <x:v>Scenario</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="str">
+      <x:c r="C14" s="15" t="str">
         <x:v>Receipt factor</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="str">
+      <x:c r="D14" s="15" t="str">
         <x:v>Variable-payment factor</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="str">
+      <x:c r="E14" s="15" t="str">
         <x:v>Description</x:v>
       </x:c>
-      <x:c r="F14" s="71"/>
+      <x:c r="F14" s="75"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="71"/>
-      <x:c r="B15" s="16" t="str">
+      <x:c r="A15" s="75"/>
+      <x:c r="B15" s="17" t="str">
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="C15" s="31" t="n">
+      <x:c r="C15" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="D15" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E15" s="16" t="str">
+      <x:c r="E15" s="17" t="str">
         <x:v>Current operating expectation</x:v>
       </x:c>
-      <x:c r="F15" s="71"/>
+      <x:c r="F15" s="75"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="71"/>
-      <x:c r="B16" s="16" t="str">
+      <x:c r="A16" s="75"/>
+      <x:c r="B16" s="17" t="str">
         <x:v>Upside</x:v>
       </x:c>
-      <x:c r="C16" s="31" t="n">
+      <x:c r="C16" s="32" t="n">
         <x:v>1.08</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="D16" s="32" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="str">
+      <x:c r="E16" s="17" t="str">
         <x:v>Stronger receipts and lower selected variable payments</x:v>
       </x:c>
-      <x:c r="F16" s="71"/>
+      <x:c r="F16" s="75"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="71"/>
-      <x:c r="B17" s="16" t="str">
+      <x:c r="A17" s="75"/>
+      <x:c r="B17" s="17" t="str">
         <x:v>Downside</x:v>
       </x:c>
-      <x:c r="C17" s="31" t="n">
+      <x:c r="C17" s="32" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="D17" s="32" t="n">
         <x:v>1.05</x:v>
       </x:c>
-      <x:c r="E17" s="16" t="str">
+      <x:c r="E17" s="17" t="str">
         <x:v>Softer receipts and higher selected variable payments</x:v>
       </x:c>
-      <x:c r="F17" s="71"/>
+      <x:c r="F17" s="75"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="71"/>
-      <x:c r="B18" s="71"/>
-      <x:c r="C18" s="71"/>
-      <x:c r="D18" s="71"/>
-      <x:c r="E18" s="71"/>
-      <x:c r="F18" s="71"/>
+      <x:c r="A18" s="75"/>
+      <x:c r="B18" s="75"/>
+      <x:c r="C18" s="75"/>
+      <x:c r="D18" s="75"/>
+      <x:c r="E18" s="75"/>
+      <x:c r="F18" s="75"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="71" t="str">
+      <x:c r="A19" s="75" t="str">
         <x:v>Liquidity action lead time (weeks)</x:v>
       </x:c>
-      <x:c r="B19" s="32" t="n">
+      <x:c r="B19" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C19" s="71"/>
-      <x:c r="D19" s="71"/>
-      <x:c r="E19" s="71"/>
-      <x:c r="F19" s="71"/>
+      <x:c r="C19" s="75"/>
+      <x:c r="D19" s="75"/>
+      <x:c r="E19" s="75"/>
+      <x:c r="F19" s="75"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="14" t="str">
+      <x:c r="A20" s="15" t="str">
+        <x:v>Forecast governance</x:v>
+      </x:c>
+      <x:c r="B20" s="15"/>
+      <x:c r="C20" s="15"/>
+      <x:c r="D20" s="15"/>
+      <x:c r="E20" s="15"/>
+      <x:c r="F20" s="15"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="75" t="str">
+        <x:v>Prepared by</x:v>
+      </x:c>
+      <x:c r="B21" s="17" t="str">
+        <x:v>Finance Manager</x:v>
+      </x:c>
+      <x:c r="C21" s="75"/>
+      <x:c r="D21" s="75"/>
+      <x:c r="E21" s="75"/>
+      <x:c r="F21" s="75"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="75" t="str">
+        <x:v>Reviewed by</x:v>
+      </x:c>
+      <x:c r="B22" s="17" t="str">
+        <x:v>CFO / Business Owner</x:v>
+      </x:c>
+      <x:c r="C22" s="75"/>
+      <x:c r="D22" s="75"/>
+      <x:c r="E22" s="75"/>
+      <x:c r="F22" s="75"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="75" t="str">
+        <x:v>Forecast owner</x:v>
+      </x:c>
+      <x:c r="B23" s="17" t="str">
+        <x:v>Finance Manager</x:v>
+      </x:c>
+      <x:c r="C23" s="75"/>
+      <x:c r="D23" s="75"/>
+      <x:c r="E23" s="75"/>
+      <x:c r="F23" s="75"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="75" t="str">
+        <x:v>Next review date</x:v>
+      </x:c>
+      <x:c r="B24" s="34" t="n">
+        <x:v>46278</x:v>
+      </x:c>
+      <x:c r="C24" s="75"/>
+      <x:c r="D24" s="75"/>
+      <x:c r="E24" s="75"/>
+      <x:c r="F24" s="75"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="75"/>
+      <x:c r="B25" s="75"/>
+      <x:c r="C25" s="75"/>
+      <x:c r="D25" s="75"/>
+      <x:c r="E25" s="75"/>
+      <x:c r="F25" s="75"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="15" t="str">
         <x:v>Data-quality notes</x:v>
       </x:c>
-      <x:c r="B20" s="14"/>
-      <x:c r="C20" s="14"/>
-      <x:c r="D20" s="14"/>
-      <x:c r="E20" s="14"/>
-      <x:c r="F20" s="14"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="27" t="str">
+      <x:c r="B26" s="15"/>
+      <x:c r="C26" s="15"/>
+      <x:c r="D26" s="15"/>
+      <x:c r="E26" s="15"/>
+      <x:c r="F26" s="15"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="28" t="str">
         <x:v>Use a Monday forecast start. Keep the as-at date inside the 13-week horizon. Replace illustrative inputs before using this workbook for a decision. Statutory cash dates depend on your reporting cycle, agent concessions and entity circumstances.</x:v>
       </x:c>
-      <x:c r="B21" s="27"/>
-      <x:c r="C21" s="27"/>
-      <x:c r="D21" s="27"/>
-      <x:c r="E21" s="27"/>
-      <x:c r="F21" s="27"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="27"/>
-      <x:c r="B22" s="27"/>
-      <x:c r="C22" s="27"/>
-      <x:c r="D22" s="27"/>
-      <x:c r="E22" s="27"/>
-      <x:c r="F22" s="27"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="27"/>
-      <x:c r="B23" s="27"/>
-      <x:c r="C23" s="27"/>
-      <x:c r="D23" s="27"/>
-      <x:c r="E23" s="27"/>
-      <x:c r="F23" s="27"/>
+      <x:c r="B27" s="28"/>
+      <x:c r="C27" s="28"/>
+      <x:c r="D27" s="28"/>
+      <x:c r="E27" s="28"/>
+      <x:c r="F27" s="28"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="28"/>
+      <x:c r="B28" s="28"/>
+      <x:c r="C28" s="28"/>
+      <x:c r="D28" s="28"/>
+      <x:c r="E28" s="28"/>
+      <x:c r="F28" s="28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="28"/>
+      <x:c r="B29" s="28"/>
+      <x:c r="C29" s="28"/>
+      <x:c r="D29" s="28"/>
+      <x:c r="E29" s="28"/>
+      <x:c r="F29" s="28"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
     <x:mergeCell ref="A20:F20"/>
-    <x:mergeCell ref="A21:F23"/>
+    <x:mergeCell ref="A26:F26"/>
+    <x:mergeCell ref="A27:F29"/>
   </x:mergeCells>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="B12">
@@ -3880,2275 +4119,2275 @@
       <x:c r="O2" s="8"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="71"/>
-      <x:c r="B3" s="71"/>
-      <x:c r="C3" s="71"/>
-      <x:c r="D3" s="71"/>
-      <x:c r="E3" s="71"/>
-      <x:c r="F3" s="71"/>
-      <x:c r="G3" s="71"/>
-      <x:c r="H3" s="71"/>
-      <x:c r="I3" s="71"/>
-      <x:c r="J3" s="71"/>
-      <x:c r="K3" s="71"/>
-      <x:c r="L3" s="71"/>
-      <x:c r="M3" s="71"/>
-      <x:c r="N3" s="71"/>
-      <x:c r="O3" s="71"/>
+      <x:c r="A3" s="75"/>
+      <x:c r="B3" s="75"/>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+      <x:c r="F3" s="75"/>
+      <x:c r="G3" s="75"/>
+      <x:c r="H3" s="75"/>
+      <x:c r="I3" s="75"/>
+      <x:c r="J3" s="75"/>
+      <x:c r="K3" s="75"/>
+      <x:c r="L3" s="75"/>
+      <x:c r="M3" s="75"/>
+      <x:c r="N3" s="75"/>
+      <x:c r="O3" s="75"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="71"/>
-      <x:c r="B4" s="71"/>
-      <x:c r="C4" s="71"/>
-      <x:c r="D4" s="71"/>
-      <x:c r="E4" s="71"/>
-      <x:c r="F4" s="71"/>
-      <x:c r="G4" s="71"/>
-      <x:c r="H4" s="71"/>
-      <x:c r="I4" s="71"/>
-      <x:c r="J4" s="71"/>
-      <x:c r="K4" s="71"/>
-      <x:c r="L4" s="71"/>
-      <x:c r="M4" s="71"/>
-      <x:c r="N4" s="71"/>
-      <x:c r="O4" s="71"/>
+      <x:c r="A4" s="75"/>
+      <x:c r="B4" s="75"/>
+      <x:c r="C4" s="75"/>
+      <x:c r="D4" s="75"/>
+      <x:c r="E4" s="75"/>
+      <x:c r="F4" s="75"/>
+      <x:c r="G4" s="75"/>
+      <x:c r="H4" s="75"/>
+      <x:c r="I4" s="75"/>
+      <x:c r="J4" s="75"/>
+      <x:c r="K4" s="75"/>
+      <x:c r="L4" s="75"/>
+      <x:c r="M4" s="75"/>
+      <x:c r="N4" s="75"/>
+      <x:c r="O4" s="75"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="71" t="str">
+      <x:c r="A5" s="75" t="str">
         <x:v>Week commencing</x:v>
       </x:c>
-      <x:c r="B5" s="34" t="n">
+      <x:c r="B5" s="36" t="n">
         <x:f>'Assumptions'!$B$8</x:f>
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="C5" s="34" t="n">
+      <x:c r="C5" s="36" t="n">
         <x:f>B5+7</x:f>
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="D5" s="34" t="n">
+      <x:c r="D5" s="36" t="n">
         <x:f>C5+7</x:f>
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="E5" s="34" t="n">
+      <x:c r="E5" s="36" t="n">
         <x:f>D5+7</x:f>
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="F5" s="34" t="n">
+      <x:c r="F5" s="36" t="n">
         <x:f>E5+7</x:f>
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="G5" s="34" t="n">
+      <x:c r="G5" s="36" t="n">
         <x:f>F5+7</x:f>
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="H5" s="34" t="n">
+      <x:c r="H5" s="36" t="n">
         <x:f>G5+7</x:f>
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="I5" s="34" t="n">
+      <x:c r="I5" s="36" t="n">
         <x:f>H5+7</x:f>
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="J5" s="34" t="n">
+      <x:c r="J5" s="36" t="n">
         <x:f>I5+7</x:f>
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="K5" s="34" t="n">
+      <x:c r="K5" s="36" t="n">
         <x:f>J5+7</x:f>
         <x:v>46328</x:v>
       </x:c>
-      <x:c r="L5" s="34" t="n">
+      <x:c r="L5" s="36" t="n">
         <x:f>K5+7</x:f>
         <x:v>46335</x:v>
       </x:c>
-      <x:c r="M5" s="34" t="n">
+      <x:c r="M5" s="36" t="n">
         <x:f>L5+7</x:f>
         <x:v>46342</x:v>
       </x:c>
-      <x:c r="N5" s="34" t="n">
+      <x:c r="N5" s="36" t="n">
         <x:f>M5+7</x:f>
         <x:v>46349</x:v>
       </x:c>
-      <x:c r="O5" s="71" t="str">
+      <x:c r="O5" s="75" t="str">
         <x:v>13-week total / terminal</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="71" t="str">
+      <x:c r="A6" s="75" t="str">
         <x:v>Week ending</x:v>
       </x:c>
-      <x:c r="B6" s="34" t="n">
+      <x:c r="B6" s="36" t="n">
         <x:f>B5+6</x:f>
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C6" s="34" t="n">
+      <x:c r="C6" s="36" t="n">
         <x:f>C5+6</x:f>
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="D6" s="34" t="n">
+      <x:c r="D6" s="36" t="n">
         <x:f>D5+6</x:f>
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="E6" s="34" t="n">
+      <x:c r="E6" s="36" t="n">
         <x:f>E5+6</x:f>
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="F6" s="34" t="n">
+      <x:c r="F6" s="36" t="n">
         <x:f>F5+6</x:f>
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="G6" s="34" t="n">
+      <x:c r="G6" s="36" t="n">
         <x:f>G5+6</x:f>
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="H6" s="34" t="n">
+      <x:c r="H6" s="36" t="n">
         <x:f>H5+6</x:f>
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="I6" s="34" t="n">
+      <x:c r="I6" s="36" t="n">
         <x:f>I5+6</x:f>
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="J6" s="34" t="n">
+      <x:c r="J6" s="36" t="n">
         <x:f>J5+6</x:f>
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="K6" s="34" t="n">
+      <x:c r="K6" s="36" t="n">
         <x:f>K5+6</x:f>
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="L6" s="34" t="n">
+      <x:c r="L6" s="36" t="n">
         <x:f>L5+6</x:f>
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="M6" s="34" t="n">
+      <x:c r="M6" s="36" t="n">
         <x:f>M5+6</x:f>
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="N6" s="34" t="n">
+      <x:c r="N6" s="36" t="n">
         <x:f>N5+6</x:f>
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="O6" s="71" t="str">
+      <x:c r="O6" s="75" t="str">
         <x:v>Week 13 value</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="71" t="str">
+      <x:c r="A7" s="75" t="str">
         <x:v>Actual / Forecast</x:v>
       </x:c>
-      <x:c r="B7" s="35" t="str">
+      <x:c r="B7" s="37" t="str">
         <x:f>IF(B6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Actual</x:v>
       </x:c>
-      <x:c r="C7" s="35" t="str">
+      <x:c r="C7" s="37" t="str">
         <x:f>IF(C6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="D7" s="35" t="str">
+      <x:c r="D7" s="37" t="str">
         <x:f>IF(D6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="E7" s="35" t="str">
+      <x:c r="E7" s="37" t="str">
         <x:f>IF(E6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="F7" s="35" t="str">
+      <x:c r="F7" s="37" t="str">
         <x:f>IF(F6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="G7" s="35" t="str">
+      <x:c r="G7" s="37" t="str">
         <x:f>IF(G6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="H7" s="35" t="str">
+      <x:c r="H7" s="37" t="str">
         <x:f>IF(H6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="I7" s="35" t="str">
+      <x:c r="I7" s="37" t="str">
         <x:f>IF(I6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="J7" s="35" t="str">
+      <x:c r="J7" s="37" t="str">
         <x:f>IF(J6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="K7" s="35" t="str">
+      <x:c r="K7" s="37" t="str">
         <x:f>IF(K6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="L7" s="35" t="str">
+      <x:c r="L7" s="37" t="str">
         <x:f>IF(L6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="M7" s="35" t="str">
+      <x:c r="M7" s="37" t="str">
         <x:f>IF(M6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="N7" s="35" t="str">
+      <x:c r="N7" s="37" t="str">
         <x:f>IF(N6&lt;='Assumptions'!$B$9,"Actual","Forecast")</x:f>
         <x:v>Forecast</x:v>
       </x:c>
-      <x:c r="O7" s="71" t="str"/>
+      <x:c r="O7" s="75" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="71"/>
-      <x:c r="B8" s="71"/>
-      <x:c r="C8" s="71"/>
-      <x:c r="D8" s="71"/>
-      <x:c r="E8" s="71"/>
-      <x:c r="F8" s="71"/>
-      <x:c r="G8" s="71"/>
-      <x:c r="H8" s="71"/>
-      <x:c r="I8" s="71"/>
-      <x:c r="J8" s="71"/>
-      <x:c r="K8" s="71"/>
-      <x:c r="L8" s="71"/>
-      <x:c r="M8" s="71"/>
-      <x:c r="N8" s="71"/>
-      <x:c r="O8" s="71"/>
+      <x:c r="A8" s="75"/>
+      <x:c r="B8" s="75"/>
+      <x:c r="C8" s="75"/>
+      <x:c r="D8" s="75"/>
+      <x:c r="E8" s="75"/>
+      <x:c r="F8" s="75"/>
+      <x:c r="G8" s="75"/>
+      <x:c r="H8" s="75"/>
+      <x:c r="I8" s="75"/>
+      <x:c r="J8" s="75"/>
+      <x:c r="K8" s="75"/>
+      <x:c r="L8" s="75"/>
+      <x:c r="M8" s="75"/>
+      <x:c r="N8" s="75"/>
+      <x:c r="O8" s="75"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="14" t="str">
+      <x:c r="A9" s="15" t="str">
         <x:v>CASH RECEIPTS</x:v>
       </x:c>
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="14"/>
-      <x:c r="D9" s="14"/>
-      <x:c r="E9" s="14"/>
-      <x:c r="F9" s="14"/>
-      <x:c r="G9" s="14"/>
-      <x:c r="H9" s="14"/>
-      <x:c r="I9" s="14"/>
-      <x:c r="J9" s="14"/>
-      <x:c r="K9" s="14"/>
-      <x:c r="L9" s="14"/>
-      <x:c r="M9" s="14"/>
-      <x:c r="N9" s="14"/>
-      <x:c r="O9" s="14"/>
+      <x:c r="B9" s="15"/>
+      <x:c r="C9" s="15"/>
+      <x:c r="D9" s="15"/>
+      <x:c r="E9" s="15"/>
+      <x:c r="F9" s="15"/>
+      <x:c r="G9" s="15"/>
+      <x:c r="H9" s="15"/>
+      <x:c r="I9" s="15"/>
+      <x:c r="J9" s="15"/>
+      <x:c r="K9" s="15"/>
+      <x:c r="L9" s="15"/>
+      <x:c r="M9" s="15"/>
+      <x:c r="N9" s="15"/>
+      <x:c r="O9" s="15"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="71" t="str">
+      <x:c r="A10" s="75" t="str">
         <x:v>Customer receipts</x:v>
       </x:c>
-      <x:c r="B10" s="38" t="n">
+      <x:c r="B10" s="40" t="n">
         <x:v>118000</x:v>
       </x:c>
-      <x:c r="C10" s="38" t="n">
+      <x:c r="C10" s="40" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="D10" s="38" t="n">
+      <x:c r="D10" s="40" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="E10" s="38" t="n">
+      <x:c r="E10" s="40" t="n">
         <x:v>115000</x:v>
       </x:c>
-      <x:c r="F10" s="38" t="n">
+      <x:c r="F10" s="40" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="G10" s="38" t="n">
+      <x:c r="G10" s="40" t="n">
         <x:v>112000</x:v>
       </x:c>
-      <x:c r="H10" s="38" t="n">
+      <x:c r="H10" s="40" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="I10" s="38" t="n">
+      <x:c r="I10" s="40" t="n">
         <x:v>108000</x:v>
       </x:c>
-      <x:c r="J10" s="38" t="n">
+      <x:c r="J10" s="40" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="K10" s="38" t="n">
+      <x:c r="K10" s="40" t="n">
         <x:v>116000</x:v>
       </x:c>
-      <x:c r="L10" s="38" t="n">
+      <x:c r="L10" s="40" t="n">
         <x:v>120000</x:v>
       </x:c>
-      <x:c r="M10" s="38" t="n">
+      <x:c r="M10" s="40" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="N10" s="38" t="n">
+      <x:c r="N10" s="40" t="n">
         <x:v>130000</x:v>
       </x:c>
-      <x:c r="O10" s="74" t="n">
+      <x:c r="O10" s="78" t="n">
         <x:f>SUM(B10:N10)</x:f>
         <x:v>1514000</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="71" t="str">
+      <x:c r="A11" s="75" t="str">
         <x:v>Overdue receipts</x:v>
       </x:c>
-      <x:c r="B11" s="38" t="n">
+      <x:c r="B11" s="40" t="n">
         <x:v>30000</x:v>
       </x:c>
-      <x:c r="C11" s="38" t="n">
+      <x:c r="C11" s="40" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="D11" s="38" t="n">
+      <x:c r="D11" s="40" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="E11" s="38" t="n">
+      <x:c r="E11" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F11" s="38" t="n">
+      <x:c r="F11" s="40" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="G11" s="38" t="n">
+      <x:c r="G11" s="40" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="H11" s="38" t="n">
+      <x:c r="H11" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="I11" s="38" t="n">
+      <x:c r="I11" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="J11" s="38" t="n">
+      <x:c r="J11" s="40" t="n">
         <x:v>7000</x:v>
       </x:c>
-      <x:c r="K11" s="38" t="n">
+      <x:c r="K11" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="L11" s="38" t="n">
+      <x:c r="L11" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="M11" s="38" t="n">
+      <x:c r="M11" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="N11" s="38" t="n">
+      <x:c r="N11" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O11" s="74" t="n">
+      <x:c r="O11" s="78" t="n">
         <x:f>SUM(B11:N11)</x:f>
         <x:v>152000</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="71" t="str">
+      <x:c r="A12" s="75" t="str">
         <x:v>Cash / EFTPOS sales</x:v>
       </x:c>
-      <x:c r="B12" s="38" t="n">
+      <x:c r="B12" s="40" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="C12" s="38" t="n">
+      <x:c r="C12" s="40" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="D12" s="38" t="n">
+      <x:c r="D12" s="40" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="E12" s="38" t="n">
+      <x:c r="E12" s="40" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="F12" s="38" t="n">
+      <x:c r="F12" s="40" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="G12" s="38" t="n">
+      <x:c r="G12" s="40" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="H12" s="38" t="n">
+      <x:c r="H12" s="40" t="n">
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="I12" s="38" t="n">
+      <x:c r="I12" s="40" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="J12" s="38" t="n">
+      <x:c r="J12" s="40" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="K12" s="38" t="n">
+      <x:c r="K12" s="40" t="n">
         <x:v>19000</x:v>
       </x:c>
-      <x:c r="L12" s="38" t="n">
+      <x:c r="L12" s="40" t="n">
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="M12" s="38" t="n">
+      <x:c r="M12" s="40" t="n">
         <x:v>21000</x:v>
       </x:c>
-      <x:c r="N12" s="38" t="n">
+      <x:c r="N12" s="40" t="n">
         <x:v>22000</x:v>
       </x:c>
-      <x:c r="O12" s="74" t="n">
+      <x:c r="O12" s="78" t="n">
         <x:f>SUM(B12:N12)</x:f>
         <x:v>245000</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="71" t="str">
+      <x:c r="A13" s="75" t="str">
         <x:v>GST refunds / credits</x:v>
       </x:c>
-      <x:c r="B13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O13" s="74" t="n">
+      <x:c r="B13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="78" t="n">
         <x:f>SUM(B13:N13)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="71" t="str">
+      <x:c r="A14" s="75" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B14" s="38" t="n">
+      <x:c r="B14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="C14" s="38" t="n">
+      <x:c r="C14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="D14" s="38" t="n">
+      <x:c r="D14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="E14" s="38" t="n">
+      <x:c r="E14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="F14" s="38" t="n">
+      <x:c r="F14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G14" s="38" t="n">
+      <x:c r="G14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="H14" s="38" t="n">
+      <x:c r="H14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="I14" s="38" t="n">
+      <x:c r="I14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="J14" s="38" t="n">
+      <x:c r="J14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K14" s="38" t="n">
+      <x:c r="K14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="L14" s="38" t="n">
+      <x:c r="L14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="M14" s="38" t="n">
+      <x:c r="M14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="N14" s="38" t="n">
+      <x:c r="N14" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O14" s="74" t="n">
+      <x:c r="O14" s="78" t="n">
         <x:f>SUM(B14:N14)</x:f>
         <x:v>52000</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="71" t="str">
+      <x:c r="A15" s="75" t="str">
         <x:v>Asset sale proceeds</x:v>
       </x:c>
-      <x:c r="B15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="38" t="n">
+      <x:c r="B15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="40" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="L15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O15" s="74" t="n">
+      <x:c r="L15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="78" t="n">
         <x:f>SUM(B15:N15)</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="71" t="str">
+      <x:c r="A16" s="75" t="str">
         <x:v>Equity / owner funding</x:v>
       </x:c>
-      <x:c r="B16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="38" t="n">
+      <x:c r="B16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="40" t="n">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="I16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O16" s="74" t="n">
+      <x:c r="I16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="78" t="n">
         <x:f>SUM(B16:N16)</x:f>
         <x:v>150000</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="71" t="str">
+      <x:c r="A17" s="75" t="str">
         <x:v>Loan proceeds</x:v>
       </x:c>
-      <x:c r="B17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="38" t="n">
+      <x:c r="B17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="40" t="n">
         <x:v>125000</x:v>
       </x:c>
-      <x:c r="K17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O17" s="74" t="n">
+      <x:c r="K17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="78" t="n">
         <x:f>SUM(B17:N17)</x:f>
         <x:v>125000</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="71" t="str">
+      <x:c r="A18" s="75" t="str">
         <x:v>Scenario receipt adjustment</x:v>
       </x:c>
-      <x:c r="B18" s="42" t="n">
+      <x:c r="B18" s="44" t="n">
         <x:f>IF(B$7="Actual",0,SUM(B10:B12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C18" s="42" t="n">
+      <x:c r="C18" s="44" t="n">
         <x:f>IF(C$7="Actual",0,SUM(C10:C12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D18" s="42" t="n">
+      <x:c r="D18" s="44" t="n">
         <x:f>IF(D$7="Actual",0,SUM(D10:D12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="42" t="n">
+      <x:c r="E18" s="44" t="n">
         <x:f>IF(E$7="Actual",0,SUM(E10:E12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="42" t="n">
+      <x:c r="F18" s="44" t="n">
         <x:f>IF(F$7="Actual",0,SUM(F10:F12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="42" t="n">
+      <x:c r="G18" s="44" t="n">
         <x:f>IF(G$7="Actual",0,SUM(G10:G12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="42" t="n">
+      <x:c r="H18" s="44" t="n">
         <x:f>IF(H$7="Actual",0,SUM(H10:H12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="42" t="n">
+      <x:c r="I18" s="44" t="n">
         <x:f>IF(I$7="Actual",0,SUM(I10:I12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="42" t="n">
+      <x:c r="J18" s="44" t="n">
         <x:f>IF(J$7="Actual",0,SUM(J10:J12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="42" t="n">
+      <x:c r="K18" s="44" t="n">
         <x:f>IF(K$7="Actual",0,SUM(K10:K12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="42" t="n">
+      <x:c r="L18" s="44" t="n">
         <x:f>IF(L$7="Actual",0,SUM(L10:L12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="42" t="n">
+      <x:c r="M18" s="44" t="n">
         <x:f>IF(M$7="Actual",0,SUM(M10:M12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N18" s="42" t="n">
+      <x:c r="N18" s="44" t="n">
         <x:f>IF(N$7="Actual",0,SUM(N10:N12)*(INDEX(Assumptions!$C$15:$C$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="74" t="n">
+      <x:c r="O18" s="78" t="n">
         <x:f>SUM(B18:N18)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="37" t="str">
+      <x:c r="A19" s="39" t="str">
         <x:v>Total cash receipts</x:v>
       </x:c>
-      <x:c r="B19" s="43" t="n">
+      <x:c r="B19" s="45" t="n">
         <x:f>SUM(B10:B18)</x:f>
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="C19" s="43" t="n">
+      <x:c r="C19" s="45" t="n">
         <x:f>SUM(C10:C18)</x:f>
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="D19" s="43" t="n">
+      <x:c r="D19" s="45" t="n">
         <x:f>SUM(D10:D18)</x:f>
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="E19" s="43" t="n">
+      <x:c r="E19" s="45" t="n">
         <x:f>SUM(E10:E18)</x:f>
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="F19" s="43" t="n">
+      <x:c r="F19" s="45" t="n">
         <x:f>SUM(F10:F18)</x:f>
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="G19" s="43" t="n">
+      <x:c r="G19" s="45" t="n">
         <x:f>SUM(G10:G18)</x:f>
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="H19" s="43" t="n">
+      <x:c r="H19" s="45" t="n">
         <x:f>SUM(H10:H18)</x:f>
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="I19" s="43" t="n">
+      <x:c r="I19" s="45" t="n">
         <x:f>SUM(I10:I18)</x:f>
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="J19" s="43" t="n">
+      <x:c r="J19" s="45" t="n">
         <x:f>SUM(J10:J18)</x:f>
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="K19" s="43" t="n">
+      <x:c r="K19" s="45" t="n">
         <x:f>SUM(K10:K18)</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="L19" s="43" t="n">
+      <x:c r="L19" s="45" t="n">
         <x:f>SUM(L10:L18)</x:f>
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="M19" s="43" t="n">
+      <x:c r="M19" s="45" t="n">
         <x:f>SUM(M10:M18)</x:f>
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="N19" s="43" t="n">
+      <x:c r="N19" s="45" t="n">
         <x:f>SUM(N10:N18)</x:f>
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="O19" s="40" t="n">
+      <x:c r="O19" s="42" t="n">
         <x:f>SUM(B19:N19)</x:f>
         <x:v>2338000</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="71"/>
-      <x:c r="B20" s="74"/>
-      <x:c r="C20" s="74"/>
-      <x:c r="D20" s="74"/>
-      <x:c r="E20" s="74"/>
-      <x:c r="F20" s="74"/>
-      <x:c r="G20" s="74"/>
-      <x:c r="H20" s="74"/>
-      <x:c r="I20" s="74"/>
-      <x:c r="J20" s="74"/>
-      <x:c r="K20" s="74"/>
-      <x:c r="L20" s="74"/>
-      <x:c r="M20" s="74"/>
-      <x:c r="N20" s="74"/>
-      <x:c r="O20" s="74"/>
+      <x:c r="A20" s="75"/>
+      <x:c r="B20" s="78"/>
+      <x:c r="C20" s="78"/>
+      <x:c r="D20" s="78"/>
+      <x:c r="E20" s="78"/>
+      <x:c r="F20" s="78"/>
+      <x:c r="G20" s="78"/>
+      <x:c r="H20" s="78"/>
+      <x:c r="I20" s="78"/>
+      <x:c r="J20" s="78"/>
+      <x:c r="K20" s="78"/>
+      <x:c r="L20" s="78"/>
+      <x:c r="M20" s="78"/>
+      <x:c r="N20" s="78"/>
+      <x:c r="O20" s="78"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="14" t="str">
+      <x:c r="A21" s="15" t="str">
         <x:v>CASH PAYMENTS</x:v>
       </x:c>
-      <x:c r="B21" s="41"/>
-      <x:c r="C21" s="41"/>
-      <x:c r="D21" s="41"/>
-      <x:c r="E21" s="41"/>
-      <x:c r="F21" s="41"/>
-      <x:c r="G21" s="41"/>
-      <x:c r="H21" s="41"/>
-      <x:c r="I21" s="41"/>
-      <x:c r="J21" s="41"/>
-      <x:c r="K21" s="41"/>
-      <x:c r="L21" s="41"/>
-      <x:c r="M21" s="41"/>
-      <x:c r="N21" s="41"/>
-      <x:c r="O21" s="41"/>
+      <x:c r="B21" s="43"/>
+      <x:c r="C21" s="43"/>
+      <x:c r="D21" s="43"/>
+      <x:c r="E21" s="43"/>
+      <x:c r="F21" s="43"/>
+      <x:c r="G21" s="43"/>
+      <x:c r="H21" s="43"/>
+      <x:c r="I21" s="43"/>
+      <x:c r="J21" s="43"/>
+      <x:c r="K21" s="43"/>
+      <x:c r="L21" s="43"/>
+      <x:c r="M21" s="43"/>
+      <x:c r="N21" s="43"/>
+      <x:c r="O21" s="43"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="71" t="str">
+      <x:c r="A22" s="75" t="str">
         <x:v>Suppliers and inventory</x:v>
       </x:c>
-      <x:c r="B22" s="38" t="n">
+      <x:c r="B22" s="40" t="n">
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="C22" s="38" t="n">
+      <x:c r="C22" s="40" t="n">
         <x:v>88000</x:v>
       </x:c>
-      <x:c r="D22" s="38" t="n">
+      <x:c r="D22" s="40" t="n">
         <x:v>90000</x:v>
       </x:c>
-      <x:c r="E22" s="38" t="n">
+      <x:c r="E22" s="40" t="n">
         <x:v>95000</x:v>
       </x:c>
-      <x:c r="F22" s="38" t="n">
+      <x:c r="F22" s="40" t="n">
         <x:v>98000</x:v>
       </x:c>
-      <x:c r="G22" s="38" t="n">
+      <x:c r="G22" s="40" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="H22" s="38" t="n">
+      <x:c r="H22" s="40" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="I22" s="38" t="n">
+      <x:c r="I22" s="40" t="n">
         <x:v>108000</x:v>
       </x:c>
-      <x:c r="J22" s="38" t="n">
+      <x:c r="J22" s="40" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="K22" s="38" t="n">
+      <x:c r="K22" s="40" t="n">
         <x:v>105000</x:v>
       </x:c>
-      <x:c r="L22" s="38" t="n">
+      <x:c r="L22" s="40" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="M22" s="38" t="n">
+      <x:c r="M22" s="40" t="n">
         <x:v>95000</x:v>
       </x:c>
-      <x:c r="N22" s="38" t="n">
+      <x:c r="N22" s="40" t="n">
         <x:v>90000</x:v>
       </x:c>
-      <x:c r="O22" s="74" t="n">
+      <x:c r="O22" s="78" t="n">
         <x:f>SUM(B22:N22)</x:f>
         <x:v>1266000</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="71" t="str">
+      <x:c r="A23" s="75" t="str">
         <x:v>Net wages</x:v>
       </x:c>
-      <x:c r="B23" s="38" t="n">
+      <x:c r="B23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="C23" s="38" t="n">
+      <x:c r="C23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="D23" s="38" t="n">
+      <x:c r="D23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="E23" s="38" t="n">
+      <x:c r="E23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="F23" s="38" t="n">
+      <x:c r="F23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="G23" s="38" t="n">
+      <x:c r="G23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="H23" s="38" t="n">
+      <x:c r="H23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="I23" s="38" t="n">
+      <x:c r="I23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="J23" s="38" t="n">
+      <x:c r="J23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="K23" s="38" t="n">
+      <x:c r="K23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="L23" s="38" t="n">
+      <x:c r="L23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="M23" s="38" t="n">
+      <x:c r="M23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="N23" s="38" t="n">
+      <x:c r="N23" s="40" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="O23" s="74" t="n">
+      <x:c r="O23" s="78" t="n">
         <x:f>SUM(B23:N23)</x:f>
         <x:v>546000</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="71" t="str">
+      <x:c r="A24" s="75" t="str">
         <x:v>PAYG withholding</x:v>
       </x:c>
-      <x:c r="B24" s="38" t="n">
+      <x:c r="B24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="C24" s="38" t="n">
+      <x:c r="C24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="D24" s="38" t="n">
+      <x:c r="D24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="E24" s="38" t="n">
+      <x:c r="E24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="F24" s="38" t="n">
+      <x:c r="F24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="G24" s="38" t="n">
+      <x:c r="G24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="H24" s="38" t="n">
+      <x:c r="H24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="I24" s="38" t="n">
+      <x:c r="I24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="J24" s="38" t="n">
+      <x:c r="J24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="K24" s="38" t="n">
+      <x:c r="K24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="L24" s="38" t="n">
+      <x:c r="L24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="M24" s="38" t="n">
+      <x:c r="M24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="N24" s="38" t="n">
+      <x:c r="N24" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O24" s="74" t="n">
+      <x:c r="O24" s="78" t="n">
         <x:f>SUM(B24:N24)</x:f>
         <x:v>156000</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="71" t="str">
+      <x:c r="A25" s="75" t="str">
         <x:v>Superannuation</x:v>
       </x:c>
-      <x:c r="B25" s="38" t="n">
+      <x:c r="B25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="C25" s="38" t="n">
+      <x:c r="C25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D25" s="38" t="n">
+      <x:c r="D25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="E25" s="38" t="n">
+      <x:c r="E25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="F25" s="38" t="n">
+      <x:c r="F25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="G25" s="38" t="n">
+      <x:c r="G25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="H25" s="38" t="n">
+      <x:c r="H25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="I25" s="38" t="n">
+      <x:c r="I25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="J25" s="38" t="n">
+      <x:c r="J25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="K25" s="38" t="n">
+      <x:c r="K25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="L25" s="38" t="n">
+      <x:c r="L25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="M25" s="38" t="n">
+      <x:c r="M25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="N25" s="38" t="n">
+      <x:c r="N25" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O25" s="74" t="n">
+      <x:c r="O25" s="78" t="n">
         <x:f>SUM(B25:N25)</x:f>
         <x:v>78000</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="71" t="str">
+      <x:c r="A26" s="75" t="str">
         <x:v>Payroll tax / workers compensation</x:v>
       </x:c>
-      <x:c r="B26" s="38" t="n">
+      <x:c r="B26" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="C26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F26" s="38" t="n">
+      <x:c r="C26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="G26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="38" t="n">
+      <x:c r="G26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="K26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N26" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O26" s="74" t="n">
+      <x:c r="K26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" s="78" t="n">
         <x:f>SUM(B26:N26)</x:f>
         <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="71" t="str">
+      <x:c r="A27" s="75" t="str">
         <x:v>Rent</x:v>
       </x:c>
-      <x:c r="B27" s="38" t="n">
+      <x:c r="B27" s="40" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="C27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F27" s="38" t="n">
+      <x:c r="C27" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" s="40" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="G27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="38" t="n">
+      <x:c r="G27" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="40" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="K27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M27" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N27" s="38" t="n">
+      <x:c r="K27" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="40" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="O27" s="74" t="n">
+      <x:c r="O27" s="78" t="n">
         <x:f>SUM(B27:N27)</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="71" t="str">
+      <x:c r="A28" s="75" t="str">
         <x:v>Utilities</x:v>
       </x:c>
-      <x:c r="B28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F28" s="38" t="n">
+      <x:c r="B28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J28" s="38" t="n">
+      <x:c r="G28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M28" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N28" s="38" t="n">
+      <x:c r="K28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O28" s="74" t="n">
+      <x:c r="O28" s="78" t="n">
         <x:f>SUM(B28:N28)</x:f>
         <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="71" t="str">
+      <x:c r="A29" s="75" t="str">
         <x:v>Insurance</x:v>
       </x:c>
-      <x:c r="B29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="38" t="n">
+      <x:c r="B29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N29" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O29" s="74" t="n">
+      <x:c r="D29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" s="78" t="n">
         <x:f>SUM(B29:N29)</x:f>
         <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="71" t="str">
+      <x:c r="A30" s="75" t="str">
         <x:v>Software and subscriptions</x:v>
       </x:c>
-      <x:c r="B30" s="38" t="n">
+      <x:c r="B30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="C30" s="38" t="n">
+      <x:c r="C30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="D30" s="38" t="n">
+      <x:c r="D30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="E30" s="38" t="n">
+      <x:c r="E30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="F30" s="38" t="n">
+      <x:c r="F30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="G30" s="38" t="n">
+      <x:c r="G30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="H30" s="38" t="n">
+      <x:c r="H30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="I30" s="38" t="n">
+      <x:c r="I30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="J30" s="38" t="n">
+      <x:c r="J30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="K30" s="38" t="n">
+      <x:c r="K30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="L30" s="38" t="n">
+      <x:c r="L30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="M30" s="38" t="n">
+      <x:c r="M30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="N30" s="38" t="n">
+      <x:c r="N30" s="40" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="O30" s="74" t="n">
+      <x:c r="O30" s="78" t="n">
         <x:f>SUM(B30:N30)</x:f>
         <x:v>39000</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="71" t="str">
+      <x:c r="A31" s="75" t="str">
         <x:v>Marketing</x:v>
       </x:c>
-      <x:c r="B31" s="38" t="n">
+      <x:c r="B31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="C31" s="38" t="n">
+      <x:c r="C31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="D31" s="38" t="n">
+      <x:c r="D31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="E31" s="38" t="n">
+      <x:c r="E31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="F31" s="38" t="n">
+      <x:c r="F31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="G31" s="38" t="n">
+      <x:c r="G31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="H31" s="38" t="n">
+      <x:c r="H31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="I31" s="38" t="n">
+      <x:c r="I31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="J31" s="38" t="n">
+      <x:c r="J31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="K31" s="38" t="n">
+      <x:c r="K31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="L31" s="38" t="n">
+      <x:c r="L31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="M31" s="38" t="n">
+      <x:c r="M31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="N31" s="38" t="n">
+      <x:c r="N31" s="40" t="n">
         <x:v>6000</x:v>
       </x:c>
-      <x:c r="O31" s="74" t="n">
+      <x:c r="O31" s="78" t="n">
         <x:f>SUM(B31:N31)</x:f>
         <x:v>78000</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="71" t="str">
+      <x:c r="A32" s="75" t="str">
         <x:v>Professional services</x:v>
       </x:c>
-      <x:c r="B32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="38" t="n">
+      <x:c r="B32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="40" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="E32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="38" t="n">
+      <x:c r="E32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="40" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="I32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L32" s="38" t="n">
+      <x:c r="I32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="40" t="n">
         <x:v>8000</x:v>
       </x:c>
-      <x:c r="M32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N32" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O32" s="74" t="n">
+      <x:c r="M32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O32" s="78" t="n">
         <x:f>SUM(B32:N32)</x:f>
         <x:v>24000</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="71" t="str">
+      <x:c r="A33" s="75" t="str">
         <x:v>Freight, vehicles and travel</x:v>
       </x:c>
-      <x:c r="B33" s="38" t="n">
+      <x:c r="B33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="C33" s="38" t="n">
+      <x:c r="C33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="D33" s="38" t="n">
+      <x:c r="D33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="E33" s="38" t="n">
+      <x:c r="E33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="F33" s="38" t="n">
+      <x:c r="F33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="G33" s="38" t="n">
+      <x:c r="G33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H33" s="38" t="n">
+      <x:c r="H33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="I33" s="38" t="n">
+      <x:c r="I33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="J33" s="38" t="n">
+      <x:c r="J33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="K33" s="38" t="n">
+      <x:c r="K33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="L33" s="38" t="n">
+      <x:c r="L33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="M33" s="38" t="n">
+      <x:c r="M33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="N33" s="38" t="n">
+      <x:c r="N33" s="40" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="O33" s="74" t="n">
+      <x:c r="O33" s="78" t="n">
         <x:f>SUM(B33:N33)</x:f>
         <x:v>130000</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="71" t="str">
+      <x:c r="A34" s="75" t="str">
         <x:v>GST / BAS payments</x:v>
       </x:c>
-      <x:c r="B34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J34" s="38" t="n">
+      <x:c r="B34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="40" t="n">
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="K34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N34" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O34" s="74" t="n">
+      <x:c r="K34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N34" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34" s="78" t="n">
         <x:f>SUM(B34:N34)</x:f>
         <x:v>45000</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="71" t="str">
+      <x:c r="A35" s="75" t="str">
         <x:v>PAYG income tax instalments</x:v>
       </x:c>
-      <x:c r="B35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J35" s="38" t="n">
+      <x:c r="B35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="40" t="n">
         <x:v>18000</x:v>
       </x:c>
-      <x:c r="K35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N35" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O35" s="74" t="n">
+      <x:c r="K35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N35" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O35" s="78" t="n">
         <x:f>SUM(B35:N35)</x:f>
         <x:v>18000</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="71" t="str">
+      <x:c r="A36" s="75" t="str">
         <x:v>FBT / other tax</x:v>
       </x:c>
-      <x:c r="B36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N36" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O36" s="74" t="n">
+      <x:c r="B36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N36" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" s="78" t="n">
         <x:f>SUM(B36:N36)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="71" t="str">
+      <x:c r="A37" s="75" t="str">
         <x:v>Interest and bank fees</x:v>
       </x:c>
-      <x:c r="B37" s="38" t="n">
+      <x:c r="B37" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="C37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F37" s="38" t="n">
+      <x:c r="C37" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="G37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J37" s="38" t="n">
+      <x:c r="G37" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I37" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="K37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M37" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N37" s="38" t="n">
+      <x:c r="K37" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N37" s="40" t="n">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="O37" s="74" t="n">
+      <x:c r="O37" s="78" t="n">
         <x:f>SUM(B37:N37)</x:f>
         <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="71" t="str">
+      <x:c r="A38" s="75" t="str">
         <x:v>Loan principal</x:v>
       </x:c>
-      <x:c r="B38" s="38" t="n">
+      <x:c r="B38" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="C38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F38" s="38" t="n">
+      <x:c r="C38" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F38" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="G38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J38" s="38" t="n">
+      <x:c r="G38" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="K38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M38" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N38" s="38" t="n">
+      <x:c r="K38" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N38" s="40" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="O38" s="74" t="n">
+      <x:c r="O38" s="78" t="n">
         <x:f>SUM(B38:N38)</x:f>
         <x:v>48000</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="71" t="str">
+      <x:c r="A39" s="75" t="str">
         <x:v>Capital expenditure</x:v>
       </x:c>
-      <x:c r="B39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G39" s="38" t="n">
+      <x:c r="B39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G39" s="40" t="n">
         <x:v>25000</x:v>
       </x:c>
-      <x:c r="H39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K39" s="38" t="n">
+      <x:c r="H39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39" s="40" t="n">
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="L39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N39" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O39" s="74" t="n">
+      <x:c r="L39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" s="78" t="n">
         <x:f>SUM(B39:N39)</x:f>
         <x:v>65000</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="71" t="str">
+      <x:c r="A40" s="75" t="str">
         <x:v>Dividends / distributions</x:v>
       </x:c>
-      <x:c r="B40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N40" s="38" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O40" s="74" t="n">
+      <x:c r="B40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" s="78" t="n">
         <x:f>SUM(B40:N40)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="71" t="str">
+      <x:c r="A41" s="75" t="str">
         <x:v>Other operating</x:v>
       </x:c>
-      <x:c r="B41" s="38" t="n">
+      <x:c r="B41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="C41" s="38" t="n">
+      <x:c r="C41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D41" s="38" t="n">
+      <x:c r="D41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="E41" s="38" t="n">
+      <x:c r="E41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="F41" s="38" t="n">
+      <x:c r="F41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="G41" s="38" t="n">
+      <x:c r="G41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="H41" s="38" t="n">
+      <x:c r="H41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="I41" s="38" t="n">
+      <x:c r="I41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="J41" s="38" t="n">
+      <x:c r="J41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="K41" s="38" t="n">
+      <x:c r="K41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="L41" s="38" t="n">
+      <x:c r="L41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="M41" s="38" t="n">
+      <x:c r="M41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="N41" s="38" t="n">
+      <x:c r="N41" s="40" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="O41" s="74" t="n">
+      <x:c r="O41" s="78" t="n">
         <x:f>SUM(B41:N41)</x:f>
         <x:v>65000</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="71" t="str">
+      <x:c r="A42" s="75" t="str">
         <x:v>Scenario payment adjustment</x:v>
       </x:c>
-      <x:c r="B42" s="42" t="n">
+      <x:c r="B42" s="44" t="n">
         <x:f>IF(B$7="Actual",0,SUM(B22,B31,B33,B41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C42" s="42" t="n">
+      <x:c r="C42" s="44" t="n">
         <x:f>IF(C$7="Actual",0,SUM(C22,C31,C33,C41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D42" s="42" t="n">
+      <x:c r="D42" s="44" t="n">
         <x:f>IF(D$7="Actual",0,SUM(D22,D31,D33,D41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E42" s="42" t="n">
+      <x:c r="E42" s="44" t="n">
         <x:f>IF(E$7="Actual",0,SUM(E22,E31,E33,E41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F42" s="42" t="n">
+      <x:c r="F42" s="44" t="n">
         <x:f>IF(F$7="Actual",0,SUM(F22,F31,F33,F41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G42" s="42" t="n">
+      <x:c r="G42" s="44" t="n">
         <x:f>IF(G$7="Actual",0,SUM(G22,G31,G33,G41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H42" s="42" t="n">
+      <x:c r="H42" s="44" t="n">
         <x:f>IF(H$7="Actual",0,SUM(H22,H31,H33,H41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I42" s="42" t="n">
+      <x:c r="I42" s="44" t="n">
         <x:f>IF(I$7="Actual",0,SUM(I22,I31,I33,I41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J42" s="42" t="n">
+      <x:c r="J42" s="44" t="n">
         <x:f>IF(J$7="Actual",0,SUM(J22,J31,J33,J41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K42" s="42" t="n">
+      <x:c r="K42" s="44" t="n">
         <x:f>IF(K$7="Actual",0,SUM(K22,K31,K33,K41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L42" s="42" t="n">
+      <x:c r="L42" s="44" t="n">
         <x:f>IF(L$7="Actual",0,SUM(L22,L31,L33,L41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M42" s="42" t="n">
+      <x:c r="M42" s="44" t="n">
         <x:f>IF(M$7="Actual",0,SUM(M22,M31,M33,M41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N42" s="42" t="n">
+      <x:c r="N42" s="44" t="n">
         <x:f>IF(N$7="Actual",0,SUM(N22,N31,N33,N41)*(INDEX(Assumptions!$D$15:$D$17,MATCH(Assumptions!$B$12,Assumptions!$B$15:$B$17,0))-1))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O42" s="74" t="n">
+      <x:c r="O42" s="78" t="n">
         <x:f>SUM(B42:N42)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="37" t="str">
+      <x:c r="A43" s="39" t="str">
         <x:v>Total cash payments</x:v>
       </x:c>
-      <x:c r="B43" s="43" t="n">
+      <x:c r="B43" s="45" t="n">
         <x:f>SUM(B22:B42)</x:f>
         <x:v>212000</x:v>
       </x:c>
-      <x:c r="C43" s="43" t="n">
+      <x:c r="C43" s="45" t="n">
         <x:f>SUM(C22:C42)</x:f>
         <x:v>178000</x:v>
       </x:c>
-      <x:c r="D43" s="43" t="n">
+      <x:c r="D43" s="45" t="n">
         <x:f>SUM(D22:D42)</x:f>
         <x:v>182000</x:v>
       </x:c>
-      <x:c r="E43" s="43" t="n">
+      <x:c r="E43" s="45" t="n">
         <x:f>SUM(E22:E42)</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="F43" s="43" t="n">
+      <x:c r="F43" s="45" t="n">
         <x:f>SUM(F22:F42)</x:f>
         <x:v>232000</x:v>
       </x:c>
-      <x:c r="G43" s="43" t="n">
+      <x:c r="G43" s="45" t="n">
         <x:f>SUM(G22:G42)</x:f>
         <x:v>209000</x:v>
       </x:c>
-      <x:c r="H43" s="43" t="n">
+      <x:c r="H43" s="45" t="n">
         <x:f>SUM(H22:H42)</x:f>
         <x:v>197000</x:v>
       </x:c>
-      <x:c r="I43" s="43" t="n">
+      <x:c r="I43" s="45" t="n">
         <x:f>SUM(I22:I42)</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="J43" s="43" t="n">
+      <x:c r="J43" s="45" t="n">
         <x:f>SUM(J22:J42)</x:f>
         <x:v>307000</x:v>
       </x:c>
-      <x:c r="K43" s="43" t="n">
+      <x:c r="K43" s="45" t="n">
         <x:f>SUM(K22:K42)</x:f>
         <x:v>229000</x:v>
       </x:c>
-      <x:c r="L43" s="43" t="n">
+      <x:c r="L43" s="45" t="n">
         <x:f>SUM(L22:L42)</x:f>
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="M43" s="43" t="n">
+      <x:c r="M43" s="45" t="n">
         <x:f>SUM(M22:M42)</x:f>
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="N43" s="43" t="n">
+      <x:c r="N43" s="45" t="n">
         <x:f>SUM(N22:N42)</x:f>
         <x:v>219000</x:v>
       </x:c>
-      <x:c r="O43" s="40" t="n">
+      <x:c r="O43" s="42" t="n">
         <x:f>SUM(B43:N43)</x:f>
         <x:v>2707000</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="71"/>
-      <x:c r="B44" s="74"/>
-      <x:c r="C44" s="74"/>
-      <x:c r="D44" s="74"/>
-      <x:c r="E44" s="74"/>
-      <x:c r="F44" s="74"/>
-      <x:c r="G44" s="74"/>
-      <x:c r="H44" s="74"/>
-      <x:c r="I44" s="74"/>
-      <x:c r="J44" s="74"/>
-      <x:c r="K44" s="74"/>
-      <x:c r="L44" s="74"/>
-      <x:c r="M44" s="74"/>
-      <x:c r="N44" s="74"/>
-      <x:c r="O44" s="74"/>
+      <x:c r="A44" s="75"/>
+      <x:c r="B44" s="78"/>
+      <x:c r="C44" s="78"/>
+      <x:c r="D44" s="78"/>
+      <x:c r="E44" s="78"/>
+      <x:c r="F44" s="78"/>
+      <x:c r="G44" s="78"/>
+      <x:c r="H44" s="78"/>
+      <x:c r="I44" s="78"/>
+      <x:c r="J44" s="78"/>
+      <x:c r="K44" s="78"/>
+      <x:c r="L44" s="78"/>
+      <x:c r="M44" s="78"/>
+      <x:c r="N44" s="78"/>
+      <x:c r="O44" s="78"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="14" t="str">
+      <x:c r="A45" s="15" t="str">
         <x:v>CASH POSITION</x:v>
       </x:c>
-      <x:c r="B45" s="41"/>
-      <x:c r="C45" s="41"/>
-      <x:c r="D45" s="41"/>
-      <x:c r="E45" s="41"/>
-      <x:c r="F45" s="41"/>
-      <x:c r="G45" s="41"/>
-      <x:c r="H45" s="41"/>
-      <x:c r="I45" s="41"/>
-      <x:c r="J45" s="41"/>
-      <x:c r="K45" s="41"/>
-      <x:c r="L45" s="41"/>
-      <x:c r="M45" s="41"/>
-      <x:c r="N45" s="41"/>
-      <x:c r="O45" s="41"/>
+      <x:c r="B45" s="43"/>
+      <x:c r="C45" s="43"/>
+      <x:c r="D45" s="43"/>
+      <x:c r="E45" s="43"/>
+      <x:c r="F45" s="43"/>
+      <x:c r="G45" s="43"/>
+      <x:c r="H45" s="43"/>
+      <x:c r="I45" s="43"/>
+      <x:c r="J45" s="43"/>
+      <x:c r="K45" s="43"/>
+      <x:c r="L45" s="43"/>
+      <x:c r="M45" s="43"/>
+      <x:c r="N45" s="43"/>
+      <x:c r="O45" s="43"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="71" t="str">
+      <x:c r="A46" s="75" t="str">
         <x:v>Opening cash balance</x:v>
       </x:c>
-      <x:c r="B46" s="44" t="n">
+      <x:c r="B46" s="46" t="n">
         <x:f>'Assumptions'!$B$10</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="C46" s="44" t="n">
+      <x:c r="C46" s="46" t="n">
         <x:f>B48</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="D46" s="44" t="n">
+      <x:c r="D46" s="46" t="n">
         <x:f>C48</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="E46" s="44" t="n">
+      <x:c r="E46" s="46" t="n">
         <x:f>D48</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="F46" s="44" t="n">
+      <x:c r="F46" s="46" t="n">
         <x:f>E48</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="G46" s="44" t="n">
+      <x:c r="G46" s="46" t="n">
         <x:f>F48</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="H46" s="44" t="n">
+      <x:c r="H46" s="46" t="n">
         <x:f>G48</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="I46" s="44" t="n">
+      <x:c r="I46" s="46" t="n">
         <x:f>H48</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="J46" s="44" t="n">
+      <x:c r="J46" s="46" t="n">
         <x:f>I48</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="K46" s="44" t="n">
+      <x:c r="K46" s="46" t="n">
         <x:f>J48</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="L46" s="44" t="n">
+      <x:c r="L46" s="46" t="n">
         <x:f>K48</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="M46" s="44" t="n">
+      <x:c r="M46" s="46" t="n">
         <x:f>L48</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="N46" s="44" t="n">
+      <x:c r="N46" s="46" t="n">
         <x:f>M48</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="O46" s="74" t="n">
+      <x:c r="O46" s="78" t="n">
         <x:f>N46</x:f>
         <x:v>82000</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="71" t="str">
+      <x:c r="A47" s="75" t="str">
         <x:v>Net cash movement</x:v>
       </x:c>
-      <x:c r="B47" s="42" t="n">
+      <x:c r="B47" s="44" t="n">
         <x:f>B19-B43</x:f>
         <x:v>-42000</x:v>
       </x:c>
-      <x:c r="C47" s="42" t="n">
+      <x:c r="C47" s="44" t="n">
         <x:f>C19-C43</x:f>
         <x:v>-9000</x:v>
       </x:c>
-      <x:c r="D47" s="42" t="n">
+      <x:c r="D47" s="44" t="n">
         <x:f>D19-D43</x:f>
         <x:v>-24000</x:v>
       </x:c>
-      <x:c r="E47" s="42" t="n">
+      <x:c r="E47" s="44" t="n">
         <x:f>E19-E43</x:f>
         <x:v>-32000</x:v>
       </x:c>
-      <x:c r="F47" s="42" t="n">
+      <x:c r="F47" s="44" t="n">
         <x:f>F19-F43</x:f>
         <x:v>-92000</x:v>
       </x:c>
-      <x:c r="G47" s="42" t="n">
+      <x:c r="G47" s="44" t="n">
         <x:f>G19-G43</x:f>
         <x:v>-68000</x:v>
       </x:c>
-      <x:c r="H47" s="42" t="n">
+      <x:c r="H47" s="44" t="n">
         <x:f>H19-H43</x:f>
         <x:v>84000</x:v>
       </x:c>
-      <x:c r="I47" s="42" t="n">
+      <x:c r="I47" s="44" t="n">
         <x:f>I19-I43</x:f>
         <x:v>-57000</x:v>
       </x:c>
-      <x:c r="J47" s="42" t="n">
+      <x:c r="J47" s="44" t="n">
         <x:f>J19-J43</x:f>
         <x:v>-43000</x:v>
       </x:c>
-      <x:c r="K47" s="42" t="n">
+      <x:c r="K47" s="44" t="n">
         <x:f>K19-K43</x:f>
         <x:v>20000</x:v>
       </x:c>
-      <x:c r="L47" s="42" t="n">
+      <x:c r="L47" s="44" t="n">
         <x:f>L19-L43</x:f>
         <x:v>-38000</x:v>
       </x:c>
-      <x:c r="M47" s="42" t="n">
+      <x:c r="M47" s="44" t="n">
         <x:f>M19-M43</x:f>
         <x:v>-17000</x:v>
       </x:c>
-      <x:c r="N47" s="42" t="n">
+      <x:c r="N47" s="44" t="n">
         <x:f>N19-N43</x:f>
         <x:v>-51000</x:v>
       </x:c>
-      <x:c r="O47" s="74" t="n">
+      <x:c r="O47" s="78" t="n">
         <x:f>SUM(B47:N47)</x:f>
         <x:v>-369000</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="37" t="str">
+      <x:c r="A48" s="39" t="str">
         <x:v>Closing cash balance</x:v>
       </x:c>
-      <x:c r="B48" s="43" t="n">
+      <x:c r="B48" s="45" t="n">
         <x:f>B46+B47</x:f>
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="C48" s="43" t="n">
+      <x:c r="C48" s="45" t="n">
         <x:f>C46+C47</x:f>
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="D48" s="43" t="n">
+      <x:c r="D48" s="45" t="n">
         <x:f>D46+D47</x:f>
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="E48" s="43" t="n">
+      <x:c r="E48" s="45" t="n">
         <x:f>E46+E47</x:f>
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="F48" s="43" t="n">
+      <x:c r="F48" s="45" t="n">
         <x:f>F46+F47</x:f>
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="G48" s="43" t="n">
+      <x:c r="G48" s="45" t="n">
         <x:f>G46+G47</x:f>
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="H48" s="43" t="n">
+      <x:c r="H48" s="45" t="n">
         <x:f>H46+H47</x:f>
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="I48" s="43" t="n">
+      <x:c r="I48" s="45" t="n">
         <x:f>I46+I47</x:f>
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="J48" s="43" t="n">
+      <x:c r="J48" s="45" t="n">
         <x:f>J46+J47</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="K48" s="43" t="n">
+      <x:c r="K48" s="45" t="n">
         <x:f>K46+K47</x:f>
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="L48" s="43" t="n">
+      <x:c r="L48" s="45" t="n">
         <x:f>L46+L47</x:f>
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="M48" s="43" t="n">
+      <x:c r="M48" s="45" t="n">
         <x:f>M46+M47</x:f>
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="N48" s="43" t="n">
+      <x:c r="N48" s="45" t="n">
         <x:f>N46+N47</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="O48" s="40" t="n">
+      <x:c r="O48" s="42" t="n">
         <x:f>N48</x:f>
         <x:v>31000</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="71" t="str">
+      <x:c r="A49" s="75" t="str">
         <x:v>Minimum cash buffer</x:v>
       </x:c>
-      <x:c r="B49" s="44" t="n">
+      <x:c r="B49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="C49" s="44" t="n">
+      <x:c r="C49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="D49" s="44" t="n">
+      <x:c r="D49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="E49" s="44" t="n">
+      <x:c r="E49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="F49" s="44" t="n">
+      <x:c r="F49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="G49" s="44" t="n">
+      <x:c r="G49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="H49" s="44" t="n">
+      <x:c r="H49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="I49" s="44" t="n">
+      <x:c r="I49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="J49" s="44" t="n">
+      <x:c r="J49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="K49" s="44" t="n">
+      <x:c r="K49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="L49" s="44" t="n">
+      <x:c r="L49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="M49" s="44" t="n">
+      <x:c r="M49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="N49" s="44" t="n">
+      <x:c r="N49" s="46" t="n">
         <x:f>'Assumptions'!$B$11</x:f>
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="O49" s="74" t="n">
+      <x:c r="O49" s="78" t="n">
         <x:f>N49</x:f>
         <x:v>100000</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="37" t="str">
+      <x:c r="A50" s="39" t="str">
         <x:v>Headroom / (gap)</x:v>
       </x:c>
-      <x:c r="B50" s="43" t="n">
+      <x:c r="B50" s="45" t="n">
         <x:f>B48-B49</x:f>
         <x:v>258000</x:v>
       </x:c>
-      <x:c r="C50" s="43" t="n">
+      <x:c r="C50" s="45" t="n">
         <x:f>C48-C49</x:f>
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="D50" s="43" t="n">
+      <x:c r="D50" s="45" t="n">
         <x:f>D48-D49</x:f>
         <x:v>225000</x:v>
       </x:c>
-      <x:c r="E50" s="43" t="n">
+      <x:c r="E50" s="45" t="n">
         <x:f>E48-E49</x:f>
         <x:v>193000</x:v>
       </x:c>
-      <x:c r="F50" s="43" t="n">
+      <x:c r="F50" s="45" t="n">
         <x:f>F48-F49</x:f>
         <x:v>101000</x:v>
       </x:c>
-      <x:c r="G50" s="43" t="n">
+      <x:c r="G50" s="45" t="n">
         <x:f>G48-G49</x:f>
         <x:v>33000</x:v>
       </x:c>
-      <x:c r="H50" s="43" t="n">
+      <x:c r="H50" s="45" t="n">
         <x:f>H48-H49</x:f>
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="I50" s="43" t="n">
+      <x:c r="I50" s="45" t="n">
         <x:f>I48-I49</x:f>
         <x:v>60000</x:v>
       </x:c>
-      <x:c r="J50" s="43" t="n">
+      <x:c r="J50" s="45" t="n">
         <x:f>J48-J49</x:f>
         <x:v>17000</x:v>
       </x:c>
-      <x:c r="K50" s="43" t="n">
+      <x:c r="K50" s="45" t="n">
         <x:f>K48-K49</x:f>
         <x:v>37000</x:v>
       </x:c>
-      <x:c r="L50" s="43" t="n">
+      <x:c r="L50" s="45" t="n">
         <x:f>L48-L49</x:f>
         <x:v>-1000</x:v>
       </x:c>
-      <x:c r="M50" s="43" t="n">
+      <x:c r="M50" s="45" t="n">
         <x:f>M48-M49</x:f>
         <x:v>-18000</x:v>
       </x:c>
-      <x:c r="N50" s="43" t="n">
+      <x:c r="N50" s="45" t="n">
         <x:f>N48-N49</x:f>
         <x:v>-69000</x:v>
       </x:c>
-      <x:c r="O50" s="40" t="n">
+      <x:c r="O50" s="42" t="n">
         <x:f>N50</x:f>
         <x:v>-69000</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="71" t="str">
+      <x:c r="A51" s="75" t="str">
         <x:v>Liquidity status</x:v>
       </x:c>
-      <x:c r="B51" s="17" t="str">
+      <x:c r="B51" s="18" t="str">
         <x:f>IF(B48&lt;B49,"BELOW BUFFER",IF(B48&lt;=B49*1.25,"WATCH","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="C51" s="17" t="str">
+      <x:c r="C51" s="18" t="str">
         <x:f>IF(C48&lt;C49,"BELOW BUFFER",IF(C48&lt;=C49*1.25,"WATCH","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="D51" s="17" t="str">
+      <x:c r="D51" s="18" t="str">
         <x:f>IF(D48&lt;D49,"BELOW BUFFER",IF(D48&lt;=D49*1.25,"WATCH","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="E51" s="17" t="str">
+      <x:c r="E51" s="18" t="str">
         <x:f>IF(E48&lt;E49,"BELOW BUFFER",IF(E48&lt;=E49*1.25,"WATCH","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="F51" s="17" t="str">
+      <x:c r="F51" s="18" t="str">
         <x:f>IF(F48&lt;F49,"BELOW BUFFER",IF(F48&lt;=F49*1.25,"WATCH","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="G51" s="17" t="str">
+      <x:c r="G51" s="18" t="str">
         <x:f>IF(G48&lt;G49,"BELOW BUFFER",IF(G48&lt;=G49*1.25,"WATCH","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="H51" s="17" t="str">
+      <x:c r="H51" s="18" t="str">
         <x:f>IF(H48&lt;H49,"BELOW BUFFER",IF(H48&lt;=H49*1.25,"WATCH","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="I51" s="17" t="str">
+      <x:c r="I51" s="18" t="str">
         <x:f>IF(I48&lt;I49,"BELOW BUFFER",IF(I48&lt;=I49*1.25,"WATCH","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="J51" s="17" t="str">
+      <x:c r="J51" s="18" t="str">
         <x:f>IF(J48&lt;J49,"BELOW BUFFER",IF(J48&lt;=J49*1.25,"WATCH","OK"))</x:f>
         <x:v>WATCH</x:v>
       </x:c>
-      <x:c r="K51" s="17" t="str">
+      <x:c r="K51" s="18" t="str">
         <x:f>IF(K48&lt;K49,"BELOW BUFFER",IF(K48&lt;=K49*1.25,"WATCH","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
-      <x:c r="L51" s="17" t="str">
+      <x:c r="L51" s="18" t="str">
         <x:f>IF(L48&lt;L49,"BELOW BUFFER",IF(L48&lt;=L49*1.25,"WATCH","OK"))</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="M51" s="17" t="str">
+      <x:c r="M51" s="18" t="str">
         <x:f>IF(M48&lt;M49,"BELOW BUFFER",IF(M48&lt;=M49*1.25,"WATCH","OK"))</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="N51" s="17" t="str">
+      <x:c r="N51" s="18" t="str">
         <x:f>IF(N48&lt;N49,"BELOW BUFFER",IF(N48&lt;=N49*1.25,"WATCH","OK"))</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
-      <x:c r="O51" s="71" t="str">
+      <x:c r="O51" s="75" t="str">
         <x:f>N51</x:f>
         <x:v>BELOW BUFFER</x:v>
       </x:c>
@@ -6170,7 +6409,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62ee5fc974354fc5"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa10216ceddb4f7b"/>
 </x:worksheet>
 </file>
 
@@ -6192,6 +6431,7 @@
     <x:col min="12" max="12" width="19" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="19" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="34" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -6211,6 +6451,7 @@
       <x:c r="L1" s="4"/>
       <x:c r="M1" s="4"/>
       <x:c r="N1" s="4"/>
+      <x:c r="O1" s="4"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
@@ -6229,558 +6470,616 @@
       <x:c r="L2" s="8"/>
       <x:c r="M2" s="8"/>
       <x:c r="N2" s="8"/>
+      <x:c r="O2" s="8"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="71"/>
-      <x:c r="B3" s="71"/>
-      <x:c r="C3" s="71"/>
-      <x:c r="D3" s="71"/>
-      <x:c r="E3" s="71"/>
-      <x:c r="F3" s="71"/>
-      <x:c r="G3" s="71"/>
-      <x:c r="H3" s="71"/>
-      <x:c r="I3" s="71"/>
-      <x:c r="J3" s="71"/>
-      <x:c r="K3" s="71"/>
-      <x:c r="L3" s="71"/>
-      <x:c r="M3" s="71"/>
-      <x:c r="N3" s="71"/>
+      <x:c r="A3" s="75"/>
+      <x:c r="B3" s="75"/>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+      <x:c r="F3" s="75"/>
+      <x:c r="G3" s="75"/>
+      <x:c r="H3" s="75"/>
+      <x:c r="I3" s="75"/>
+      <x:c r="J3" s="75"/>
+      <x:c r="K3" s="75"/>
+      <x:c r="L3" s="75"/>
+      <x:c r="M3" s="75"/>
+      <x:c r="N3" s="75"/>
+      <x:c r="O3" s="75"/>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="27" t="str">
+      <x:c r="A4" s="28" t="str">
         <x:v>Before updating the live forecast, paste the week's original period dates, receipts, payments and closing cash here as values. Snapshot cells must not link back to the live forecast.</x:v>
       </x:c>
-      <x:c r="B4" s="27"/>
-      <x:c r="C4" s="27"/>
-      <x:c r="D4" s="27"/>
-      <x:c r="E4" s="27"/>
-      <x:c r="F4" s="27"/>
-      <x:c r="G4" s="27"/>
-      <x:c r="H4" s="27"/>
-      <x:c r="I4" s="27"/>
-      <x:c r="J4" s="27"/>
-      <x:c r="K4" s="27"/>
-      <x:c r="L4" s="27"/>
-      <x:c r="M4" s="27"/>
-      <x:c r="N4" s="27"/>
+      <x:c r="B4" s="28"/>
+      <x:c r="C4" s="28"/>
+      <x:c r="D4" s="28"/>
+      <x:c r="E4" s="28"/>
+      <x:c r="F4" s="28"/>
+      <x:c r="G4" s="28"/>
+      <x:c r="H4" s="28"/>
+      <x:c r="I4" s="28"/>
+      <x:c r="J4" s="28"/>
+      <x:c r="K4" s="28"/>
+      <x:c r="L4" s="28"/>
+      <x:c r="M4" s="28"/>
+      <x:c r="N4" s="28"/>
+      <x:c r="O4" s="28"/>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
-      <x:c r="A5" s="45" t="str">
+      <x:c r="A5" s="47" t="str">
         <x:v>Snapshot week start</x:v>
       </x:c>
-      <x:c r="B5" s="45" t="str">
+      <x:c r="B5" s="47" t="str">
         <x:v>Snapshot week end</x:v>
       </x:c>
-      <x:c r="C5" s="45" t="str">
+      <x:c r="C5" s="47" t="str">
         <x:v>Forecast snapshot receipts</x:v>
       </x:c>
-      <x:c r="D5" s="45" t="str">
+      <x:c r="D5" s="47" t="str">
         <x:v>Actual receipts</x:v>
       </x:c>
-      <x:c r="E5" s="45" t="str">
+      <x:c r="E5" s="47" t="str">
         <x:v>Receipt variance $</x:v>
       </x:c>
-      <x:c r="F5" s="45" t="str">
+      <x:c r="F5" s="47" t="str">
         <x:v>Receipt variance %</x:v>
       </x:c>
-      <x:c r="G5" s="45" t="str">
+      <x:c r="G5" s="47" t="str">
         <x:v>Forecast snapshot payments</x:v>
       </x:c>
-      <x:c r="H5" s="45" t="str">
+      <x:c r="H5" s="47" t="str">
         <x:v>Actual payments</x:v>
       </x:c>
-      <x:c r="I5" s="45" t="str">
+      <x:c r="I5" s="47" t="str">
         <x:v>Payment variance $</x:v>
       </x:c>
-      <x:c r="J5" s="45" t="str">
+      <x:c r="J5" s="47" t="str">
         <x:v>Payment variance %</x:v>
       </x:c>
-      <x:c r="K5" s="45" t="str">
+      <x:c r="K5" s="47" t="str">
         <x:v>Forecast snapshot closing cash</x:v>
       </x:c>
-      <x:c r="L5" s="45" t="str">
+      <x:c r="L5" s="47" t="str">
         <x:v>Actual closing cash</x:v>
       </x:c>
-      <x:c r="M5" s="45" t="str">
+      <x:c r="M5" s="47" t="str">
         <x:v>Closing-cash variance</x:v>
       </x:c>
-      <x:c r="N5" s="45" t="str">
+      <x:c r="N5" s="47" t="str">
         <x:v>Owner commentary</x:v>
       </x:c>
+      <x:c r="O5" s="47" t="str">
+        <x:v>Review status</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="49" t="n">
+      <x:c r="A6" s="34" t="n">
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="B6" s="49" t="n">
+      <x:c r="B6" s="34" t="n">
         <x:v>46271</x:v>
       </x:c>
-      <x:c r="C6" s="38" t="n">
+      <x:c r="C6" s="40" t="n">
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="D6" s="38"/>
-      <x:c r="E6" s="42" t="str">
+      <x:c r="D6" s="40"/>
+      <x:c r="E6" s="44" t="str">
         <x:f>IF(D6="","",D6-C6)</x:f>
       </x:c>
-      <x:c r="F6" s="50" t="str">
+      <x:c r="F6" s="51" t="str">
         <x:f>IF(OR(D6="",C6=0),"",(D6-C6)/C6)</x:f>
       </x:c>
-      <x:c r="G6" s="38" t="n">
+      <x:c r="G6" s="40" t="n">
         <x:v>212000</x:v>
       </x:c>
-      <x:c r="H6" s="38"/>
-      <x:c r="I6" s="42" t="str">
+      <x:c r="H6" s="40"/>
+      <x:c r="I6" s="44" t="str">
         <x:f>IF(H6="","",G6-H6)</x:f>
       </x:c>
-      <x:c r="J6" s="50" t="str">
+      <x:c r="J6" s="51" t="str">
         <x:f>IF(OR(H6="",G6=0),"",(G6-H6)/G6)</x:f>
       </x:c>
-      <x:c r="K6" s="38" t="n">
+      <x:c r="K6" s="40" t="n">
         <x:v>358000</x:v>
       </x:c>
-      <x:c r="L6" s="38"/>
-      <x:c r="M6" s="42" t="str">
+      <x:c r="L6" s="40"/>
+      <x:c r="M6" s="44" t="str">
         <x:f>IF(L6="","",L6-K6)</x:f>
       </x:c>
-      <x:c r="N6" s="16"/>
+      <x:c r="N6" s="17"/>
+      <x:c r="O6" s="75" t="str">
+        <x:f>IF(COUNTA(D6,H6,L6,N6)=0,"NOT STARTED",IF(AND(A6&lt;&gt;"",B6&lt;&gt;"",C6&lt;&gt;"",D6&lt;&gt;"",G6&lt;&gt;"",H6&lt;&gt;"",K6&lt;&gt;"",L6&lt;&gt;"",N6&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="49" t="n">
+      <x:c r="A7" s="34" t="n">
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="B7" s="49" t="n">
+      <x:c r="B7" s="34" t="n">
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="C7" s="38" t="n">
+      <x:c r="C7" s="40" t="n">
         <x:v>169000</x:v>
       </x:c>
-      <x:c r="D7" s="38"/>
-      <x:c r="E7" s="42" t="str">
+      <x:c r="D7" s="40"/>
+      <x:c r="E7" s="44" t="str">
         <x:f>IF(D7="","",D7-C7)</x:f>
       </x:c>
-      <x:c r="F7" s="50" t="str">
+      <x:c r="F7" s="51" t="str">
         <x:f>IF(OR(D7="",C7=0),"",(D7-C7)/C7)</x:f>
       </x:c>
-      <x:c r="G7" s="38" t="n">
+      <x:c r="G7" s="40" t="n">
         <x:v>178000</x:v>
       </x:c>
-      <x:c r="H7" s="38"/>
-      <x:c r="I7" s="42" t="str">
+      <x:c r="H7" s="40"/>
+      <x:c r="I7" s="44" t="str">
         <x:f>IF(H7="","",G7-H7)</x:f>
       </x:c>
-      <x:c r="J7" s="50" t="str">
+      <x:c r="J7" s="51" t="str">
         <x:f>IF(OR(H7="",G7=0),"",(G7-H7)/G7)</x:f>
       </x:c>
-      <x:c r="K7" s="38" t="n">
+      <x:c r="K7" s="40" t="n">
         <x:v>349000</x:v>
       </x:c>
-      <x:c r="L7" s="38"/>
-      <x:c r="M7" s="42" t="str">
+      <x:c r="L7" s="40"/>
+      <x:c r="M7" s="44" t="str">
         <x:f>IF(L7="","",L7-K7)</x:f>
       </x:c>
-      <x:c r="N7" s="16"/>
+      <x:c r="N7" s="17"/>
+      <x:c r="O7" s="75" t="str">
+        <x:f>IF(COUNTA(D7,H7,L7,N7)=0,"NOT STARTED",IF(AND(A7&lt;&gt;"",B7&lt;&gt;"",C7&lt;&gt;"",D7&lt;&gt;"",G7&lt;&gt;"",H7&lt;&gt;"",K7&lt;&gt;"",L7&lt;&gt;"",N7&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="49" t="n">
+      <x:c r="A8" s="34" t="n">
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="B8" s="49" t="n">
+      <x:c r="B8" s="34" t="n">
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="C8" s="38" t="n">
+      <x:c r="C8" s="40" t="n">
         <x:v>158000</x:v>
       </x:c>
-      <x:c r="D8" s="38"/>
-      <x:c r="E8" s="42" t="str">
+      <x:c r="D8" s="40"/>
+      <x:c r="E8" s="44" t="str">
         <x:f>IF(D8="","",D8-C8)</x:f>
       </x:c>
-      <x:c r="F8" s="50" t="str">
+      <x:c r="F8" s="51" t="str">
         <x:f>IF(OR(D8="",C8=0),"",(D8-C8)/C8)</x:f>
       </x:c>
-      <x:c r="G8" s="38" t="n">
+      <x:c r="G8" s="40" t="n">
         <x:v>182000</x:v>
       </x:c>
-      <x:c r="H8" s="38"/>
-      <x:c r="I8" s="42" t="str">
+      <x:c r="H8" s="40"/>
+      <x:c r="I8" s="44" t="str">
         <x:f>IF(H8="","",G8-H8)</x:f>
       </x:c>
-      <x:c r="J8" s="50" t="str">
+      <x:c r="J8" s="51" t="str">
         <x:f>IF(OR(H8="",G8=0),"",(G8-H8)/G8)</x:f>
       </x:c>
-      <x:c r="K8" s="38" t="n">
+      <x:c r="K8" s="40" t="n">
         <x:v>325000</x:v>
       </x:c>
-      <x:c r="L8" s="38"/>
-      <x:c r="M8" s="42" t="str">
+      <x:c r="L8" s="40"/>
+      <x:c r="M8" s="44" t="str">
         <x:f>IF(L8="","",L8-K8)</x:f>
       </x:c>
-      <x:c r="N8" s="16"/>
+      <x:c r="N8" s="17"/>
+      <x:c r="O8" s="75" t="str">
+        <x:f>IF(COUNTA(D8,H8,L8,N8)=0,"NOT STARTED",IF(AND(A8&lt;&gt;"",B8&lt;&gt;"",C8&lt;&gt;"",D8&lt;&gt;"",G8&lt;&gt;"",H8&lt;&gt;"",K8&lt;&gt;"",L8&lt;&gt;"",N8&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="49" t="n">
+      <x:c r="A9" s="34" t="n">
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="B9" s="49" t="n">
+      <x:c r="B9" s="34" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="C9" s="38" t="n">
+      <x:c r="C9" s="40" t="n">
         <x:v>147000</x:v>
       </x:c>
-      <x:c r="D9" s="38"/>
-      <x:c r="E9" s="42" t="str">
+      <x:c r="D9" s="40"/>
+      <x:c r="E9" s="44" t="str">
         <x:f>IF(D9="","",D9-C9)</x:f>
       </x:c>
-      <x:c r="F9" s="50" t="str">
+      <x:c r="F9" s="51" t="str">
         <x:f>IF(OR(D9="",C9=0),"",(D9-C9)/C9)</x:f>
       </x:c>
-      <x:c r="G9" s="38" t="n">
+      <x:c r="G9" s="40" t="n">
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="H9" s="38"/>
-      <x:c r="I9" s="42" t="str">
+      <x:c r="H9" s="40"/>
+      <x:c r="I9" s="44" t="str">
         <x:f>IF(H9="","",G9-H9)</x:f>
       </x:c>
-      <x:c r="J9" s="50" t="str">
+      <x:c r="J9" s="51" t="str">
         <x:f>IF(OR(H9="",G9=0),"",(G9-H9)/G9)</x:f>
       </x:c>
-      <x:c r="K9" s="38" t="n">
+      <x:c r="K9" s="40" t="n">
         <x:v>293000</x:v>
       </x:c>
-      <x:c r="L9" s="38"/>
-      <x:c r="M9" s="42" t="str">
+      <x:c r="L9" s="40"/>
+      <x:c r="M9" s="44" t="str">
         <x:f>IF(L9="","",L9-K9)</x:f>
       </x:c>
-      <x:c r="N9" s="16"/>
+      <x:c r="N9" s="17"/>
+      <x:c r="O9" s="75" t="str">
+        <x:f>IF(COUNTA(D9,H9,L9,N9)=0,"NOT STARTED",IF(AND(A9&lt;&gt;"",B9&lt;&gt;"",C9&lt;&gt;"",D9&lt;&gt;"",G9&lt;&gt;"",H9&lt;&gt;"",K9&lt;&gt;"",L9&lt;&gt;"",N9&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="49" t="n">
+      <x:c r="A10" s="34" t="n">
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="B10" s="49" t="n">
+      <x:c r="B10" s="34" t="n">
         <x:v>46299</x:v>
       </x:c>
-      <x:c r="C10" s="38" t="n">
+      <x:c r="C10" s="40" t="n">
         <x:v>140000</x:v>
       </x:c>
-      <x:c r="D10" s="38"/>
-      <x:c r="E10" s="42" t="str">
+      <x:c r="D10" s="40"/>
+      <x:c r="E10" s="44" t="str">
         <x:f>IF(D10="","",D10-C10)</x:f>
       </x:c>
-      <x:c r="F10" s="50" t="str">
+      <x:c r="F10" s="51" t="str">
         <x:f>IF(OR(D10="",C10=0),"",(D10-C10)/C10)</x:f>
       </x:c>
-      <x:c r="G10" s="38" t="n">
+      <x:c r="G10" s="40" t="n">
         <x:v>232000</x:v>
       </x:c>
-      <x:c r="H10" s="38"/>
-      <x:c r="I10" s="42" t="str">
+      <x:c r="H10" s="40"/>
+      <x:c r="I10" s="44" t="str">
         <x:f>IF(H10="","",G10-H10)</x:f>
       </x:c>
-      <x:c r="J10" s="50" t="str">
+      <x:c r="J10" s="51" t="str">
         <x:f>IF(OR(H10="",G10=0),"",(G10-H10)/G10)</x:f>
       </x:c>
-      <x:c r="K10" s="38" t="n">
+      <x:c r="K10" s="40" t="n">
         <x:v>201000</x:v>
       </x:c>
-      <x:c r="L10" s="38"/>
-      <x:c r="M10" s="42" t="str">
+      <x:c r="L10" s="40"/>
+      <x:c r="M10" s="44" t="str">
         <x:f>IF(L10="","",L10-K10)</x:f>
       </x:c>
-      <x:c r="N10" s="16"/>
+      <x:c r="N10" s="17"/>
+      <x:c r="O10" s="75" t="str">
+        <x:f>IF(COUNTA(D10,H10,L10,N10)=0,"NOT STARTED",IF(AND(A10&lt;&gt;"",B10&lt;&gt;"",C10&lt;&gt;"",D10&lt;&gt;"",G10&lt;&gt;"",H10&lt;&gt;"",K10&lt;&gt;"",L10&lt;&gt;"",N10&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="49" t="n">
+      <x:c r="A11" s="34" t="n">
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="B11" s="49" t="n">
+      <x:c r="B11" s="34" t="n">
         <x:v>46306</x:v>
       </x:c>
-      <x:c r="C11" s="38" t="n">
+      <x:c r="C11" s="40" t="n">
         <x:v>141000</x:v>
       </x:c>
-      <x:c r="D11" s="38"/>
-      <x:c r="E11" s="42" t="str">
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="44" t="str">
         <x:f>IF(D11="","",D11-C11)</x:f>
       </x:c>
-      <x:c r="F11" s="50" t="str">
+      <x:c r="F11" s="51" t="str">
         <x:f>IF(OR(D11="",C11=0),"",(D11-C11)/C11)</x:f>
       </x:c>
-      <x:c r="G11" s="38" t="n">
+      <x:c r="G11" s="40" t="n">
         <x:v>209000</x:v>
       </x:c>
-      <x:c r="H11" s="38"/>
-      <x:c r="I11" s="42" t="str">
+      <x:c r="H11" s="40"/>
+      <x:c r="I11" s="44" t="str">
         <x:f>IF(H11="","",G11-H11)</x:f>
       </x:c>
-      <x:c r="J11" s="50" t="str">
+      <x:c r="J11" s="51" t="str">
         <x:f>IF(OR(H11="",G11=0),"",(G11-H11)/G11)</x:f>
       </x:c>
-      <x:c r="K11" s="38" t="n">
+      <x:c r="K11" s="40" t="n">
         <x:v>133000</x:v>
       </x:c>
-      <x:c r="L11" s="38"/>
-      <x:c r="M11" s="42" t="str">
+      <x:c r="L11" s="40"/>
+      <x:c r="M11" s="44" t="str">
         <x:f>IF(L11="","",L11-K11)</x:f>
       </x:c>
-      <x:c r="N11" s="16"/>
+      <x:c r="N11" s="17"/>
+      <x:c r="O11" s="75" t="str">
+        <x:f>IF(COUNTA(D11,H11,L11,N11)=0,"NOT STARTED",IF(AND(A11&lt;&gt;"",B11&lt;&gt;"",C11&lt;&gt;"",D11&lt;&gt;"",G11&lt;&gt;"",H11&lt;&gt;"",K11&lt;&gt;"",L11&lt;&gt;"",N11&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="49" t="n">
+      <x:c r="A12" s="34" t="n">
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="B12" s="49" t="n">
+      <x:c r="B12" s="34" t="n">
         <x:v>46313</x:v>
       </x:c>
-      <x:c r="C12" s="38" t="n">
+      <x:c r="C12" s="40" t="n">
         <x:v>281000</x:v>
       </x:c>
-      <x:c r="D12" s="38"/>
-      <x:c r="E12" s="42" t="str">
+      <x:c r="D12" s="40"/>
+      <x:c r="E12" s="44" t="str">
         <x:f>IF(D12="","",D12-C12)</x:f>
       </x:c>
-      <x:c r="F12" s="50" t="str">
+      <x:c r="F12" s="51" t="str">
         <x:f>IF(OR(D12="",C12=0),"",(D12-C12)/C12)</x:f>
       </x:c>
-      <x:c r="G12" s="38" t="n">
+      <x:c r="G12" s="40" t="n">
         <x:v>197000</x:v>
       </x:c>
-      <x:c r="H12" s="38"/>
-      <x:c r="I12" s="42" t="str">
+      <x:c r="H12" s="40"/>
+      <x:c r="I12" s="44" t="str">
         <x:f>IF(H12="","",G12-H12)</x:f>
       </x:c>
-      <x:c r="J12" s="50" t="str">
+      <x:c r="J12" s="51" t="str">
         <x:f>IF(OR(H12="",G12=0),"",(G12-H12)/G12)</x:f>
       </x:c>
-      <x:c r="K12" s="38" t="n">
+      <x:c r="K12" s="40" t="n">
         <x:v>217000</x:v>
       </x:c>
-      <x:c r="L12" s="38"/>
-      <x:c r="M12" s="42" t="str">
+      <x:c r="L12" s="40"/>
+      <x:c r="M12" s="44" t="str">
         <x:f>IF(L12="","",L12-K12)</x:f>
       </x:c>
-      <x:c r="N12" s="16"/>
+      <x:c r="N12" s="17"/>
+      <x:c r="O12" s="75" t="str">
+        <x:f>IF(COUNTA(D12,H12,L12,N12)=0,"NOT STARTED",IF(AND(A12&lt;&gt;"",B12&lt;&gt;"",C12&lt;&gt;"",D12&lt;&gt;"",G12&lt;&gt;"",H12&lt;&gt;"",K12&lt;&gt;"",L12&lt;&gt;"",N12&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="49" t="n">
+      <x:c r="A13" s="34" t="n">
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="B13" s="49" t="n">
+      <x:c r="B13" s="34" t="n">
         <x:v>46320</x:v>
       </x:c>
-      <x:c r="C13" s="38" t="n">
+      <x:c r="C13" s="40" t="n">
         <x:v>135000</x:v>
       </x:c>
-      <x:c r="D13" s="38"/>
-      <x:c r="E13" s="42" t="str">
+      <x:c r="D13" s="40"/>
+      <x:c r="E13" s="44" t="str">
         <x:f>IF(D13="","",D13-C13)</x:f>
       </x:c>
-      <x:c r="F13" s="50" t="str">
+      <x:c r="F13" s="51" t="str">
         <x:f>IF(OR(D13="",C13=0),"",(D13-C13)/C13)</x:f>
       </x:c>
-      <x:c r="G13" s="38" t="n">
+      <x:c r="G13" s="40" t="n">
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="H13" s="38"/>
-      <x:c r="I13" s="42" t="str">
+      <x:c r="H13" s="40"/>
+      <x:c r="I13" s="44" t="str">
         <x:f>IF(H13="","",G13-H13)</x:f>
       </x:c>
-      <x:c r="J13" s="50" t="str">
+      <x:c r="J13" s="51" t="str">
         <x:f>IF(OR(H13="",G13=0),"",(G13-H13)/G13)</x:f>
       </x:c>
-      <x:c r="K13" s="38" t="n">
+      <x:c r="K13" s="40" t="n">
         <x:v>160000</x:v>
       </x:c>
-      <x:c r="L13" s="38"/>
-      <x:c r="M13" s="42" t="str">
+      <x:c r="L13" s="40"/>
+      <x:c r="M13" s="44" t="str">
         <x:f>IF(L13="","",L13-K13)</x:f>
       </x:c>
-      <x:c r="N13" s="16"/>
+      <x:c r="N13" s="17"/>
+      <x:c r="O13" s="75" t="str">
+        <x:f>IF(COUNTA(D13,H13,L13,N13)=0,"NOT STARTED",IF(AND(A13&lt;&gt;"",B13&lt;&gt;"",C13&lt;&gt;"",D13&lt;&gt;"",G13&lt;&gt;"",H13&lt;&gt;"",K13&lt;&gt;"",L13&lt;&gt;"",N13&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="49" t="n">
+      <x:c r="A14" s="34" t="n">
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="B14" s="49" t="n">
+      <x:c r="B14" s="34" t="n">
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="C14" s="38" t="n">
+      <x:c r="C14" s="40" t="n">
         <x:v>264000</x:v>
       </x:c>
-      <x:c r="D14" s="38"/>
-      <x:c r="E14" s="42" t="str">
+      <x:c r="D14" s="40"/>
+      <x:c r="E14" s="44" t="str">
         <x:f>IF(D14="","",D14-C14)</x:f>
       </x:c>
-      <x:c r="F14" s="50" t="str">
+      <x:c r="F14" s="51" t="str">
         <x:f>IF(OR(D14="",C14=0),"",(D14-C14)/C14)</x:f>
       </x:c>
-      <x:c r="G14" s="38" t="n">
+      <x:c r="G14" s="40" t="n">
         <x:v>307000</x:v>
       </x:c>
-      <x:c r="H14" s="38"/>
-      <x:c r="I14" s="42" t="str">
+      <x:c r="H14" s="40"/>
+      <x:c r="I14" s="44" t="str">
         <x:f>IF(H14="","",G14-H14)</x:f>
       </x:c>
-      <x:c r="J14" s="50" t="str">
+      <x:c r="J14" s="51" t="str">
         <x:f>IF(OR(H14="",G14=0),"",(G14-H14)/G14)</x:f>
       </x:c>
-      <x:c r="K14" s="38" t="n">
+      <x:c r="K14" s="40" t="n">
         <x:v>117000</x:v>
       </x:c>
-      <x:c r="L14" s="38"/>
-      <x:c r="M14" s="42" t="str">
+      <x:c r="L14" s="40"/>
+      <x:c r="M14" s="44" t="str">
         <x:f>IF(L14="","",L14-K14)</x:f>
       </x:c>
-      <x:c r="N14" s="16"/>
+      <x:c r="N14" s="17"/>
+      <x:c r="O14" s="75" t="str">
+        <x:f>IF(COUNTA(D14,H14,L14,N14)=0,"NOT STARTED",IF(AND(A14&lt;&gt;"",B14&lt;&gt;"",C14&lt;&gt;"",D14&lt;&gt;"",G14&lt;&gt;"",H14&lt;&gt;"",K14&lt;&gt;"",L14&lt;&gt;"",N14&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="49" t="n">
+      <x:c r="A15" s="34" t="n">
         <x:v>46328</x:v>
       </x:c>
-      <x:c r="B15" s="49" t="n">
+      <x:c r="B15" s="34" t="n">
         <x:v>46334</x:v>
       </x:c>
-      <x:c r="C15" s="38" t="n">
+      <x:c r="C15" s="40" t="n">
         <x:v>249000</x:v>
       </x:c>
-      <x:c r="D15" s="38"/>
-      <x:c r="E15" s="42" t="str">
+      <x:c r="D15" s="40"/>
+      <x:c r="E15" s="44" t="str">
         <x:f>IF(D15="","",D15-C15)</x:f>
       </x:c>
-      <x:c r="F15" s="50" t="str">
+      <x:c r="F15" s="51" t="str">
         <x:f>IF(OR(D15="",C15=0),"",(D15-C15)/C15)</x:f>
       </x:c>
-      <x:c r="G15" s="38" t="n">
+      <x:c r="G15" s="40" t="n">
         <x:v>229000</x:v>
       </x:c>
-      <x:c r="H15" s="38"/>
-      <x:c r="I15" s="42" t="str">
+      <x:c r="H15" s="40"/>
+      <x:c r="I15" s="44" t="str">
         <x:f>IF(H15="","",G15-H15)</x:f>
       </x:c>
-      <x:c r="J15" s="50" t="str">
+      <x:c r="J15" s="51" t="str">
         <x:f>IF(OR(H15="",G15=0),"",(G15-H15)/G15)</x:f>
       </x:c>
-      <x:c r="K15" s="38" t="n">
+      <x:c r="K15" s="40" t="n">
         <x:v>137000</x:v>
       </x:c>
-      <x:c r="L15" s="38"/>
-      <x:c r="M15" s="42" t="str">
+      <x:c r="L15" s="40"/>
+      <x:c r="M15" s="44" t="str">
         <x:f>IF(L15="","",L15-K15)</x:f>
       </x:c>
-      <x:c r="N15" s="16"/>
+      <x:c r="N15" s="17"/>
+      <x:c r="O15" s="75" t="str">
+        <x:f>IF(COUNTA(D15,H15,L15,N15)=0,"NOT STARTED",IF(AND(A15&lt;&gt;"",B15&lt;&gt;"",C15&lt;&gt;"",D15&lt;&gt;"",G15&lt;&gt;"",H15&lt;&gt;"",K15&lt;&gt;"",L15&lt;&gt;"",N15&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="49" t="n">
+      <x:c r="A16" s="34" t="n">
         <x:v>46335</x:v>
       </x:c>
-      <x:c r="B16" s="49" t="n">
+      <x:c r="B16" s="34" t="n">
         <x:v>46341</x:v>
       </x:c>
-      <x:c r="C16" s="38" t="n">
+      <x:c r="C16" s="40" t="n">
         <x:v>154000</x:v>
       </x:c>
-      <x:c r="D16" s="38"/>
-      <x:c r="E16" s="42" t="str">
+      <x:c r="D16" s="40"/>
+      <x:c r="E16" s="44" t="str">
         <x:f>IF(D16="","",D16-C16)</x:f>
       </x:c>
-      <x:c r="F16" s="50" t="str">
+      <x:c r="F16" s="51" t="str">
         <x:f>IF(OR(D16="",C16=0),"",(D16-C16)/C16)</x:f>
       </x:c>
-      <x:c r="G16" s="38" t="n">
+      <x:c r="G16" s="40" t="n">
         <x:v>192000</x:v>
       </x:c>
-      <x:c r="H16" s="38"/>
-      <x:c r="I16" s="42" t="str">
+      <x:c r="H16" s="40"/>
+      <x:c r="I16" s="44" t="str">
         <x:f>IF(H16="","",G16-H16)</x:f>
       </x:c>
-      <x:c r="J16" s="50" t="str">
+      <x:c r="J16" s="51" t="str">
         <x:f>IF(OR(H16="",G16=0),"",(G16-H16)/G16)</x:f>
       </x:c>
-      <x:c r="K16" s="38" t="n">
+      <x:c r="K16" s="40" t="n">
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="L16" s="38"/>
-      <x:c r="M16" s="42" t="str">
+      <x:c r="L16" s="40"/>
+      <x:c r="M16" s="44" t="str">
         <x:f>IF(L16="","",L16-K16)</x:f>
       </x:c>
-      <x:c r="N16" s="16"/>
+      <x:c r="N16" s="17"/>
+      <x:c r="O16" s="75" t="str">
+        <x:f>IF(COUNTA(D16,H16,L16,N16)=0,"NOT STARTED",IF(AND(A16&lt;&gt;"",B16&lt;&gt;"",C16&lt;&gt;"",D16&lt;&gt;"",G16&lt;&gt;"",H16&lt;&gt;"",K16&lt;&gt;"",L16&lt;&gt;"",N16&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="49" t="n">
+      <x:c r="A17" s="34" t="n">
         <x:v>46342</x:v>
       </x:c>
-      <x:c r="B17" s="49" t="n">
+      <x:c r="B17" s="34" t="n">
         <x:v>46348</x:v>
       </x:c>
-      <x:c r="C17" s="38" t="n">
+      <x:c r="C17" s="40" t="n">
         <x:v>162000</x:v>
       </x:c>
-      <x:c r="D17" s="38"/>
-      <x:c r="E17" s="42" t="str">
+      <x:c r="D17" s="40"/>
+      <x:c r="E17" s="44" t="str">
         <x:f>IF(D17="","",D17-C17)</x:f>
       </x:c>
-      <x:c r="F17" s="50" t="str">
+      <x:c r="F17" s="51" t="str">
         <x:f>IF(OR(D17="",C17=0),"",(D17-C17)/C17)</x:f>
       </x:c>
-      <x:c r="G17" s="38" t="n">
+      <x:c r="G17" s="40" t="n">
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="H17" s="38"/>
-      <x:c r="I17" s="42" t="str">
+      <x:c r="H17" s="40"/>
+      <x:c r="I17" s="44" t="str">
         <x:f>IF(H17="","",G17-H17)</x:f>
       </x:c>
-      <x:c r="J17" s="50" t="str">
+      <x:c r="J17" s="51" t="str">
         <x:f>IF(OR(H17="",G17=0),"",(G17-H17)/G17)</x:f>
       </x:c>
-      <x:c r="K17" s="38" t="n">
+      <x:c r="K17" s="40" t="n">
         <x:v>82000</x:v>
       </x:c>
-      <x:c r="L17" s="38"/>
-      <x:c r="M17" s="42" t="str">
+      <x:c r="L17" s="40"/>
+      <x:c r="M17" s="44" t="str">
         <x:f>IF(L17="","",L17-K17)</x:f>
       </x:c>
-      <x:c r="N17" s="16"/>
+      <x:c r="N17" s="17"/>
+      <x:c r="O17" s="75" t="str">
+        <x:f>IF(COUNTA(D17,H17,L17,N17)=0,"NOT STARTED",IF(AND(A17&lt;&gt;"",B17&lt;&gt;"",C17&lt;&gt;"",D17&lt;&gt;"",G17&lt;&gt;"",H17&lt;&gt;"",K17&lt;&gt;"",L17&lt;&gt;"",N17&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="49" t="n">
+      <x:c r="A18" s="34" t="n">
         <x:v>46349</x:v>
       </x:c>
-      <x:c r="B18" s="49" t="n">
+      <x:c r="B18" s="34" t="n">
         <x:v>46355</x:v>
       </x:c>
-      <x:c r="C18" s="38" t="n">
+      <x:c r="C18" s="40" t="n">
         <x:v>168000</x:v>
       </x:c>
-      <x:c r="D18" s="38"/>
-      <x:c r="E18" s="42" t="str">
+      <x:c r="D18" s="40"/>
+      <x:c r="E18" s="44" t="str">
         <x:f>IF(D18="","",D18-C18)</x:f>
       </x:c>
-      <x:c r="F18" s="50" t="str">
+      <x:c r="F18" s="51" t="str">
         <x:f>IF(OR(D18="",C18=0),"",(D18-C18)/C18)</x:f>
       </x:c>
-      <x:c r="G18" s="38" t="n">
+      <x:c r="G18" s="40" t="n">
         <x:v>219000</x:v>
       </x:c>
-      <x:c r="H18" s="38"/>
-      <x:c r="I18" s="42" t="str">
+      <x:c r="H18" s="40"/>
+      <x:c r="I18" s="44" t="str">
         <x:f>IF(H18="","",G18-H18)</x:f>
       </x:c>
-      <x:c r="J18" s="50" t="str">
+      <x:c r="J18" s="51" t="str">
         <x:f>IF(OR(H18="",G18=0),"",(G18-H18)/G18)</x:f>
       </x:c>
-      <x:c r="K18" s="38" t="n">
+      <x:c r="K18" s="40" t="n">
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="L18" s="38"/>
-      <x:c r="M18" s="42" t="str">
+      <x:c r="L18" s="40"/>
+      <x:c r="M18" s="44" t="str">
         <x:f>IF(L18="","",L18-K18)</x:f>
       </x:c>
-      <x:c r="N18" s="16"/>
+      <x:c r="N18" s="17"/>
+      <x:c r="O18" s="75" t="str">
+        <x:f>IF(COUNTA(D18,H18,L18,N18)=0,"NOT STARTED",IF(AND(A18&lt;&gt;"",B18&lt;&gt;"",C18&lt;&gt;"",D18&lt;&gt;"",G18&lt;&gt;"",H18&lt;&gt;"",K18&lt;&gt;"",L18&lt;&gt;"",N18&lt;&gt;""),"COMPLETE","INCOMPLETE"))</x:f>
+        <x:v>NOT STARTED</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:N1"/>
-    <x:mergeCell ref="A2:N2"/>
-    <x:mergeCell ref="A4:N4"/>
+    <x:mergeCell ref="A1:O1"/>
+    <x:mergeCell ref="A2:O2"/>
+    <x:mergeCell ref="A4:O4"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="E6:E18">
     <x:cfRule type="expression" dxfId="3" priority="1">
@@ -6822,6 +7121,17 @@
       <x:formula>J6&lt;0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="O6:O18">
+    <x:cfRule type="expression" dxfId="13" priority="11">
+      <x:formula>O6="COMPLETE"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="14" priority="12">
+      <x:formula>O6="INCOMPLETE"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="15" priority="13">
+      <x:formula>O6="NOT STARTED"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -6865,564 +7175,564 @@
       <x:c r="H2" s="8"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="71"/>
-      <x:c r="B3" s="71"/>
-      <x:c r="C3" s="71"/>
-      <x:c r="D3" s="71"/>
-      <x:c r="E3" s="71"/>
-      <x:c r="F3" s="71"/>
-      <x:c r="G3" s="71"/>
-      <x:c r="H3" s="71"/>
+      <x:c r="A3" s="75"/>
+      <x:c r="B3" s="75"/>
+      <x:c r="C3" s="75"/>
+      <x:c r="D3" s="75"/>
+      <x:c r="E3" s="75"/>
+      <x:c r="F3" s="75"/>
+      <x:c r="G3" s="75"/>
+      <x:c r="H3" s="75"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="51" t="str">
+      <x:c r="A4" s="52" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="B4" s="51" t="str">
+      <x:c r="B4" s="52" t="str">
         <x:f>IF(COUNTIF(F8:F16,"PASS")=9,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C4" s="51"/>
-      <x:c r="D4" s="51" t="str">
+      <x:c r="C4" s="52"/>
+      <x:c r="D4" s="52" t="str">
         <x:v>LIQUIDITY STATUS</x:v>
       </x:c>
-      <x:c r="E4" s="51" t="str">
+      <x:c r="E4" s="52" t="str">
         <x:f>IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"BELOW BUFFER")&gt;0,"ACTION REQUIRED",IF(COUNTIF('13-Week Forecast'!$B$51:$N$51,"WATCH")&gt;0,"WATCH","OK"))</x:f>
         <x:v>ACTION REQUIRED</x:v>
       </x:c>
-      <x:c r="F4" s="71"/>
-      <x:c r="G4" s="71"/>
-      <x:c r="H4" s="71"/>
+      <x:c r="F4" s="75"/>
+      <x:c r="G4" s="75"/>
+      <x:c r="H4" s="75"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="71"/>
-      <x:c r="B5" s="71"/>
-      <x:c r="C5" s="71"/>
-      <x:c r="D5" s="71"/>
-      <x:c r="E5" s="71"/>
-      <x:c r="F5" s="71"/>
-      <x:c r="G5" s="71"/>
-      <x:c r="H5" s="71"/>
+      <x:c r="A5" s="75"/>
+      <x:c r="B5" s="75"/>
+      <x:c r="C5" s="75"/>
+      <x:c r="D5" s="75"/>
+      <x:c r="E5" s="75"/>
+      <x:c r="F5" s="75"/>
+      <x:c r="G5" s="75"/>
+      <x:c r="H5" s="75"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="71"/>
-      <x:c r="B6" s="71"/>
-      <x:c r="C6" s="71"/>
-      <x:c r="D6" s="71"/>
-      <x:c r="E6" s="71"/>
-      <x:c r="F6" s="71"/>
-      <x:c r="G6" s="71"/>
-      <x:c r="H6" s="71"/>
+      <x:c r="A6" s="75"/>
+      <x:c r="B6" s="75"/>
+      <x:c r="C6" s="75"/>
+      <x:c r="D6" s="75"/>
+      <x:c r="E6" s="75"/>
+      <x:c r="F6" s="75"/>
+      <x:c r="G6" s="75"/>
+      <x:c r="H6" s="75"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14" t="str">
+      <x:c r="A7" s="15" t="str">
         <x:v>Check</x:v>
       </x:c>
-      <x:c r="B7" s="14" t="str">
+      <x:c r="B7" s="15" t="str">
         <x:v>Actual</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="str">
+      <x:c r="C7" s="15" t="str">
         <x:v>Expected</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="str">
+      <x:c r="D7" s="15" t="str">
         <x:v>Difference</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="str">
+      <x:c r="E7" s="15" t="str">
         <x:v>Tolerance</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="str">
+      <x:c r="F7" s="15" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="str">
+      <x:c r="G7" s="15" t="str">
         <x:v>Where to fix</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="str">
+      <x:c r="H7" s="15" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="73" t="str">
+      <x:c r="A8" s="77" t="str">
         <x:v>Exactly 13 forecast weeks</x:v>
       </x:c>
-      <x:c r="B8" s="75" t="n">
+      <x:c r="B8" s="79" t="n">
         <x:f>COLUMNS('13-Week Forecast'!$B$5:$N$5)</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="75" t="n">
+      <x:c r="C8" s="79" t="n">
         <x:f>13</x:f>
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D8" s="75" t="n">
+      <x:c r="D8" s="79" t="n">
         <x:f>B8-C8</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E8" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="73" t="str">
+      <x:c r="E8" s="79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="77" t="str">
         <x:f>IF(ABS(D8)&lt;=E8,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G8" s="73" t="str">
+      <x:c r="G8" s="77" t="str">
         <x:v>13-Week Forecast!B5:N5</x:v>
       </x:c>
-      <x:c r="H8" s="73" t="str">
+      <x:c r="H8" s="77" t="str">
         <x:v>The weekly horizon must contain exactly 13 columns.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="73" t="str">
+      <x:c r="A9" s="77" t="str">
         <x:v>Forecast starts Monday</x:v>
       </x:c>
-      <x:c r="B9" s="75" t="n">
+      <x:c r="B9" s="79" t="n">
         <x:f>WEEKDAY('Assumptions'!$B$8,2)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C9" s="75" t="n">
+      <x:c r="C9" s="79" t="n">
         <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D9" s="75" t="n">
+      <x:c r="D9" s="79" t="n">
         <x:f>B9-C9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E9" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="73" t="str">
+      <x:c r="E9" s="79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="77" t="str">
         <x:f>IF(ABS(D9)&lt;=E9,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G9" s="73" t="str">
+      <x:c r="G9" s="77" t="str">
         <x:v>Assumptions!B8</x:v>
       </x:c>
-      <x:c r="H9" s="73" t="str">
+      <x:c r="H9" s="77" t="str">
         <x:v>Forecast start date must be a Monday.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="73" t="str">
+      <x:c r="A10" s="77" t="str">
         <x:v>Selected scenario recognised</x:v>
       </x:c>
-      <x:c r="B10" s="75" t="n">
+      <x:c r="B10" s="79" t="n">
         <x:f>COUNTIF('Assumptions'!$B$15:$B$17,'Assumptions'!$B$12)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="75" t="n">
+      <x:c r="C10" s="79" t="n">
         <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D10" s="75" t="n">
+      <x:c r="D10" s="79" t="n">
         <x:f>B10-C10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="73" t="str">
+      <x:c r="E10" s="79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="77" t="str">
         <x:f>IF(ABS(D10)&lt;=E10,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G10" s="73" t="str">
+      <x:c r="G10" s="77" t="str">
         <x:v>Assumptions!B12</x:v>
       </x:c>
-      <x:c r="H10" s="73" t="str">
+      <x:c r="H10" s="77" t="str">
         <x:v>Select Base, Upside or Downside.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="73" t="str">
+      <x:c r="A11" s="77" t="str">
         <x:v>Week 1 opening cash ties</x:v>
       </x:c>
-      <x:c r="B11" s="76" t="n">
+      <x:c r="B11" s="80" t="n">
         <x:f>'13-Week Forecast'!$B$46</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="C11" s="76" t="n">
+      <x:c r="C11" s="80" t="n">
         <x:f>'Assumptions'!$B$10</x:f>
         <x:v>400000</x:v>
       </x:c>
-      <x:c r="D11" s="75" t="n">
+      <x:c r="D11" s="79" t="n">
         <x:f>B11-C11</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="73" t="str">
+      <x:c r="E11" s="79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="77" t="str">
         <x:f>IF(ABS(D11)&lt;=E11,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G11" s="73" t="str">
+      <x:c r="G11" s="77" t="str">
         <x:v>13-Week Forecast!B46</x:v>
       </x:c>
-      <x:c r="H11" s="73" t="str">
+      <x:c r="H11" s="77" t="str">
         <x:v>Week 1 opening cash must link to the control panel.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="73" t="str">
+      <x:c r="A12" s="77" t="str">
         <x:v>Weekly cash roll-forward equations</x:v>
       </x:c>
-      <x:c r="B12" s="75" t="n">
+      <x:c r="B12" s="79" t="n">
         <x:f>MAX(ABS('13-Week Forecast'!$B$48-'13-Week Forecast'!$B$46-'13-Week Forecast'!$B$47),ABS('13-Week Forecast'!$C$48-'13-Week Forecast'!$C$46-'13-Week Forecast'!$C$47),ABS('13-Week Forecast'!$D$48-'13-Week Forecast'!$D$46-'13-Week Forecast'!$D$47),ABS('13-Week Forecast'!$E$48-'13-Week Forecast'!$E$46-'13-Week Forecast'!$E$47),ABS('13-Week Forecast'!$F$48-'13-Week Forecast'!$F$46-'13-Week Forecast'!$F$47),ABS('13-Week Forecast'!$G$48-'13-Week Forecast'!$G$46-'13-Week Forecast'!$G$47),ABS('13-Week Forecast'!$H$48-'13-Week Forecast'!$H$46-'13-Week Forecast'!$H$47),ABS('13-Week Forecast'!$I$48-'13-Week Forecast'!$I$46-'13-Week Forecast'!$I$47),ABS('13-Week Forecast'!$J$48-'13-Week Forecast'!$J$46-'13-Week Forecast'!$J$47),ABS('13-Week Forecast'!$K$48-'13-Week Forecast'!$K$46-'13-Week Forecast'!$K$47),ABS('13-Week Forecast'!$L$48-'13-Week Forecast'!$L$46-'13-Week Forecast'!$L$47),ABS('13-Week Forecast'!$M$48-'13-Week Forecast'!$M$46-'13-Week Forecast'!$M$47),ABS('13-Week Forecast'!$N$48-'13-Week Forecast'!$N$46-'13-Week Forecast'!$N$47),ABS('13-Week Forecast'!$C$46-'13-Week Forecast'!$B$48),ABS('13-Week Forecast'!$D$46-'13-Week Forecast'!$C$48),ABS('13-Week Forecast'!$E$46-'13-Week Forecast'!$D$48),ABS('13-Week Forecast'!$F$46-'13-Week Forecast'!$E$48),ABS('13-Week Forecast'!$G$46-'13-Week Forecast'!$F$48),ABS('13-Week Forecast'!$H$46-'13-Week Forecast'!$G$48),ABS('13-Week Forecast'!$I$46-'13-Week Forecast'!$H$48),ABS('13-Week Forecast'!$J$46-'13-Week Forecast'!$I$48),ABS('13-Week Forecast'!$K$46-'13-Week Forecast'!$J$48),ABS('13-Week Forecast'!$L$46-'13-Week Forecast'!$K$48),ABS('13-Week Forecast'!$M$46-'13-Week Forecast'!$L$48),ABS('13-Week Forecast'!$N$46-'13-Week Forecast'!$M$48))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C12" s="75" t="n">
+      <x:c r="C12" s="79" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="75" t="n">
+      <x:c r="D12" s="79" t="n">
         <x:f>B12-C12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="73" t="str">
+      <x:c r="E12" s="79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="77" t="str">
         <x:f>IF(ABS(D12)&lt;=E12,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G12" s="73" t="str">
+      <x:c r="G12" s="77" t="str">
         <x:v>13-Week Forecast!B46:N48</x:v>
       </x:c>
-      <x:c r="H12" s="73" t="str">
+      <x:c r="H12" s="77" t="str">
         <x:v>Each close must equal opening plus net movement; each opening after Week 1 must equal the prior close.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="73" t="str">
+      <x:c r="A13" s="77" t="str">
         <x:v>Cash receipt totals reconcile</x:v>
       </x:c>
-      <x:c r="B13" s="75" t="n">
+      <x:c r="B13" s="79" t="n">
         <x:f>MAX(ABS('13-Week Forecast'!$B$19-SUM('13-Week Forecast'!$B$10:$B$18)),ABS('13-Week Forecast'!$C$19-SUM('13-Week Forecast'!$C$10:$C$18)),ABS('13-Week Forecast'!$D$19-SUM('13-Week Forecast'!$D$10:$D$18)),ABS('13-Week Forecast'!$E$19-SUM('13-Week Forecast'!$E$10:$E$18)),ABS('13-Week Forecast'!$F$19-SUM('13-Week Forecast'!$F$10:$F$18)),ABS('13-Week Forecast'!$G$19-SUM('13-Week Forecast'!$G$10:$G$18)),ABS('13-Week Forecast'!$H$19-SUM('13-Week Forecast'!$H$10:$H$18)),ABS('13-Week Forecast'!$I$19-SUM('13-Week Forecast'!$I$10:$I$18)),ABS('13-Week Forecast'!$J$19-SUM('13-Week Forecast'!$J$10:$J$18)),ABS('13-Week Forecast'!$K$19-SUM('13-Week Forecast'!$K$10:$K$18)),ABS('13-Week Forecast'!$L$19-SUM('13-Week Forecast'!$L$10:$L$18)),ABS('13-Week Forecast'!$M$19-SUM('13-Week Forecast'!$M$10:$M$18)),ABS('13-Week Forecast'!$N$19-SUM('13-Week Forecast'!$N$10:$N$18)))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C13" s="75" t="n">
+      <x:c r="C13" s="79" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="75" t="n">
+      <x:c r="D13" s="79" t="n">
         <x:f>B13-C13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="73" t="str">
+      <x:c r="E13" s="79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="77" t="str">
         <x:f>IF(ABS(D13)&lt;=E13,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G13" s="73" t="str">
+      <x:c r="G13" s="77" t="str">
         <x:v>13-Week Forecast!B19:N19</x:v>
       </x:c>
-      <x:c r="H13" s="73" t="str">
+      <x:c r="H13" s="77" t="str">
         <x:v>Maximum weekly difference; includes the selected-scenario receipt adjustment.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="73" t="str">
+      <x:c r="A14" s="77" t="str">
         <x:v>Cash payment totals reconcile</x:v>
       </x:c>
-      <x:c r="B14" s="75" t="n">
+      <x:c r="B14" s="79" t="n">
         <x:f>MAX(ABS('13-Week Forecast'!$B$43-SUM('13-Week Forecast'!$B$22:$B$42)),ABS('13-Week Forecast'!$C$43-SUM('13-Week Forecast'!$C$22:$C$42)),ABS('13-Week Forecast'!$D$43-SUM('13-Week Forecast'!$D$22:$D$42)),ABS('13-Week Forecast'!$E$43-SUM('13-Week Forecast'!$E$22:$E$42)),ABS('13-Week Forecast'!$F$43-SUM('13-Week Forecast'!$F$22:$F$42)),ABS('13-Week Forecast'!$G$43-SUM('13-Week Forecast'!$G$22:$G$42)),ABS('13-Week Forecast'!$H$43-SUM('13-Week Forecast'!$H$22:$H$42)),ABS('13-Week Forecast'!$I$43-SUM('13-Week Forecast'!$I$22:$I$42)),ABS('13-Week Forecast'!$J$43-SUM('13-Week Forecast'!$J$22:$J$42)),ABS('13-Week Forecast'!$K$43-SUM('13-Week Forecast'!$K$22:$K$42)),ABS('13-Week Forecast'!$L$43-SUM('13-Week Forecast'!$L$22:$L$42)),ABS('13-Week Forecast'!$M$43-SUM('13-Week Forecast'!$M$22:$M$42)),ABS('13-Week Forecast'!$N$43-SUM('13-Week Forecast'!$N$22:$N$42)))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C14" s="75" t="n">
+      <x:c r="C14" s="79" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="75" t="n">
+      <x:c r="D14" s="79" t="n">
         <x:f>B14-C14</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="73" t="str">
+      <x:c r="E14" s="79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="77" t="str">
         <x:f>IF(ABS(D14)&lt;=E14,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G14" s="73" t="str">
+      <x:c r="G14" s="77" t="str">
         <x:v>13-Week Forecast!B43:N43</x:v>
       </x:c>
-      <x:c r="H14" s="73" t="str">
+      <x:c r="H14" s="77" t="str">
         <x:v>Maximum weekly difference; includes the selected-scenario payment adjustment.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="73" t="str">
+      <x:c r="A15" s="77" t="str">
         <x:v>Week 13 closing cash equation</x:v>
       </x:c>
-      <x:c r="B15" s="76" t="n">
+      <x:c r="B15" s="80" t="n">
         <x:f>'13-Week Forecast'!$N$48</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="C15" s="76" t="n">
+      <x:c r="C15" s="80" t="n">
         <x:f>'Assumptions'!$B$10+SUM('13-Week Forecast'!$B$47:$N$47)</x:f>
         <x:v>31000</x:v>
       </x:c>
-      <x:c r="D15" s="75" t="n">
+      <x:c r="D15" s="79" t="n">
         <x:f>B15-C15</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="73" t="str">
+      <x:c r="E15" s="79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="77" t="str">
         <x:f>IF(ABS(D15)&lt;=E15,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G15" s="73" t="str">
+      <x:c r="G15" s="77" t="str">
         <x:v>13-Week Forecast!N48</x:v>
       </x:c>
-      <x:c r="H15" s="73" t="str">
+      <x:c r="H15" s="77" t="str">
         <x:v>Week 13 close must equal opening cash plus cumulative net movement.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="73" t="str">
+      <x:c r="A16" s="77" t="str">
         <x:v>Formula-error count</x:v>
       </x:c>
-      <x:c r="B16" s="75" t="n">
-        <x:f>SUMPRODUCT(--ISERROR('Assumptions'!$B$5:$E$19))+SUMPRODUCT(--ISERROR('13-Week Forecast'!$B$5:$O$51))+SUMPRODUCT(--ISERROR('Weekly Review'!$A$4:$N$18))+SUMPRODUCT(--ISERROR('Dashboard'!$A$6:$J$30))+SUMPRODUCT(--ISERROR('Dashboard'!$P$4:$S$49))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C16" s="75" t="n">
+      <x:c r="B16" s="79" t="n">
+        <x:f>SUMPRODUCT(--ISERROR('Assumptions'!$B$5:$E$24))+SUMPRODUCT(--ISERROR('13-Week Forecast'!$B$5:$O$51))+SUMPRODUCT(--ISERROR('Weekly Review'!$A$4:$O$18))+SUMPRODUCT(--ISERROR('Dashboard'!$A$6:$J$36))+SUMPRODUCT(--ISERROR('Dashboard'!$P$4:$S$49))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="79" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="75" t="n">
+      <x:c r="D16" s="79" t="n">
         <x:f>B16-C16</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="75" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="73" t="str">
+      <x:c r="E16" s="79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="77" t="str">
         <x:f>IF(ABS(D16)&lt;=E16,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G16" s="73" t="str">
+      <x:c r="G16" s="77" t="str">
         <x:v>Assumptions, Forecast, Weekly Review and Dashboard</x:v>
       </x:c>
-      <x:c r="H16" s="73" t="str">
+      <x:c r="H16" s="77" t="str">
         <x:v>Any formula error in the model ranges fails this check.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="71"/>
-      <x:c r="B17" s="71"/>
-      <x:c r="C17" s="71"/>
-      <x:c r="D17" s="71"/>
-      <x:c r="E17" s="71"/>
-      <x:c r="F17" s="71"/>
-      <x:c r="G17" s="71"/>
-      <x:c r="H17" s="71"/>
+      <x:c r="A17" s="75"/>
+      <x:c r="B17" s="75"/>
+      <x:c r="C17" s="75"/>
+      <x:c r="D17" s="75"/>
+      <x:c r="E17" s="75"/>
+      <x:c r="F17" s="75"/>
+      <x:c r="G17" s="75"/>
+      <x:c r="H17" s="75"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="71"/>
-      <x:c r="B18" s="71"/>
-      <x:c r="C18" s="71"/>
-      <x:c r="D18" s="71"/>
-      <x:c r="E18" s="71"/>
-      <x:c r="F18" s="71"/>
-      <x:c r="G18" s="71"/>
-      <x:c r="H18" s="71"/>
+      <x:c r="A18" s="75"/>
+      <x:c r="B18" s="75"/>
+      <x:c r="C18" s="75"/>
+      <x:c r="D18" s="75"/>
+      <x:c r="E18" s="75"/>
+      <x:c r="F18" s="75"/>
+      <x:c r="G18" s="75"/>
+      <x:c r="H18" s="75"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="71"/>
-      <x:c r="B19" s="71"/>
-      <x:c r="C19" s="71"/>
-      <x:c r="D19" s="71"/>
-      <x:c r="E19" s="71"/>
-      <x:c r="F19" s="71"/>
-      <x:c r="G19" s="71"/>
-      <x:c r="H19" s="71"/>
+      <x:c r="A19" s="75"/>
+      <x:c r="B19" s="75"/>
+      <x:c r="C19" s="75"/>
+      <x:c r="D19" s="75"/>
+      <x:c r="E19" s="75"/>
+      <x:c r="F19" s="75"/>
+      <x:c r="G19" s="75"/>
+      <x:c r="H19" s="75"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="71"/>
-      <x:c r="B20" s="71"/>
-      <x:c r="C20" s="71"/>
-      <x:c r="D20" s="71"/>
-      <x:c r="E20" s="71"/>
-      <x:c r="F20" s="71"/>
-      <x:c r="G20" s="71"/>
-      <x:c r="H20" s="71"/>
+      <x:c r="A20" s="75"/>
+      <x:c r="B20" s="75"/>
+      <x:c r="C20" s="75"/>
+      <x:c r="D20" s="75"/>
+      <x:c r="E20" s="75"/>
+      <x:c r="F20" s="75"/>
+      <x:c r="G20" s="75"/>
+      <x:c r="H20" s="75"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="14" t="str">
+      <x:c r="A21" s="15" t="str">
         <x:v>Source item</x:v>
       </x:c>
-      <x:c r="B21" s="14" t="str">
+      <x:c r="B21" s="15" t="str">
         <x:v>Official URL</x:v>
       </x:c>
-      <x:c r="C21" s="14" t="str">
+      <x:c r="C21" s="15" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="D21" s="14" t="str">
+      <x:c r="D21" s="15" t="str">
         <x:v>Checked</x:v>
       </x:c>
-      <x:c r="E21" s="14" t="str">
+      <x:c r="E21" s="15" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="str">
+      <x:c r="F21" s="15" t="str">
         <x:v>Planning treatment</x:v>
       </x:c>
-      <x:c r="G21" s="71"/>
-      <x:c r="H21" s="71"/>
+      <x:c r="G21" s="75"/>
+      <x:c r="H21" s="75"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="55" t="str">
+      <x:c r="A22" s="56" t="str">
         <x:v>GST standard rate</x:v>
       </x:c>
-      <x:c r="B22" s="56" t="str">
+      <x:c r="B22" s="57" t="str">
         <x:v>https://www.legislation.gov.au/C2004A00446/latest/text</x:v>
       </x:c>
-      <x:c r="C22" s="55" t="str">
+      <x:c r="C22" s="56" t="str">
         <x:v>GST default: 10% of the value of a taxable supply.</x:v>
       </x:c>
-      <x:c r="D22" s="55" t="str">
+      <x:c r="D22" s="56" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E22" s="55" t="str">
+      <x:c r="E22" s="56" t="str">
         <x:v>The 10% default does not decide whether a transaction is taxable, GST-free, input taxed or outside the GST system.</x:v>
       </x:c>
-      <x:c r="F22" s="55" t="str">
+      <x:c r="F22" s="56" t="str">
         <x:v>Keep tax classifications user-confirmed.</x:v>
       </x:c>
-      <x:c r="G22" s="71"/>
-      <x:c r="H22" s="71"/>
+      <x:c r="G22" s="75"/>
+      <x:c r="H22" s="75"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="55" t="str">
+      <x:c r="A23" s="56" t="str">
         <x:v>BAS due dates</x:v>
       </x:c>
-      <x:c r="B23" s="56" t="str">
+      <x:c r="B23" s="57" t="str">
         <x:v>https://www.ato.gov.au/businesses-and-organisations/preparing-lodging-and-paying/business-activity-statements-bas/due-dates-for-lodging-and-paying-your-bas</x:v>
       </x:c>
-      <x:c r="C23" s="55" t="str">
+      <x:c r="C23" s="56" t="str">
         <x:v>Monthly BAS planning pattern is generally the 21st day after the taxable period; quarterly dates are planning patterns only.</x:v>
       </x:c>
-      <x:c r="D23" s="55" t="str">
+      <x:c r="D23" s="56" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E23" s="55" t="str">
+      <x:c r="E23" s="56" t="str">
         <x:v>The issued or entity-specific BAS due date controls. Online lodgement, registered-agent arrangements, holidays and entity circumstances can change the date.</x:v>
       </x:c>
-      <x:c r="F23" s="55" t="str">
+      <x:c r="F23" s="56" t="str">
         <x:v>Use issued BAS and user-entered dates.</x:v>
       </x:c>
-      <x:c r="G23" s="71"/>
-      <x:c r="H23" s="71"/>
+      <x:c r="G23" s="75"/>
+      <x:c r="H23" s="75"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="55" t="str">
+      <x:c r="A24" s="56" t="str">
         <x:v>PAYG withholding</x:v>
       </x:c>
-      <x:c r="B24" s="56" t="str">
+      <x:c r="B24" s="57" t="str">
         <x:v>https://www.ato.gov.au/businesses-and-organisations/hiring-and-paying-your-workers/payg-withholding</x:v>
       </x:c>
-      <x:c r="C24" s="55" t="str">
+      <x:c r="C24" s="56" t="str">
         <x:v>PAYG withholding payment and reporting due dates vary with business size and circumstances.</x:v>
       </x:c>
-      <x:c r="D24" s="55" t="str">
+      <x:c r="D24" s="56" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E24" s="55" t="str">
+      <x:c r="E24" s="56" t="str">
         <x:v>Confirm the applicable due date for the entity and reporting cycle.</x:v>
       </x:c>
-      <x:c r="F24" s="55" t="str">
+      <x:c r="F24" s="56" t="str">
         <x:v>Keep payment dates user-entered and confirmed.</x:v>
       </x:c>
-      <x:c r="G24" s="71"/>
-      <x:c r="H24" s="71"/>
+      <x:c r="G24" s="75"/>
+      <x:c r="H24" s="75"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="55" t="str">
+      <x:c r="A25" s="56" t="str">
         <x:v>Super guarantee</x:v>
       </x:c>
-      <x:c r="B25" s="56" t="str">
+      <x:c r="B25" s="57" t="str">
         <x:v>https://www.ato.gov.au/tax-rates-and-codes/key-superannuation-rates-and-thresholds/super-guarantee</x:v>
       </x:c>
-      <x:c r="C25" s="55" t="str">
+      <x:c r="C25" s="56" t="str">
         <x:v>Default SG rate: 12.0% from 1 July 2025, including 1 July 2026 to 30 June 2027.</x:v>
       </x:c>
-      <x:c r="D25" s="55" t="str">
+      <x:c r="D25" s="56" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E25" s="55" t="str">
+      <x:c r="E25" s="56" t="str">
         <x:v>Apply only after checking worker eligibility, earnings base and special rules.</x:v>
       </x:c>
-      <x:c r="F25" s="55" t="str">
+      <x:c r="F25" s="56" t="str">
         <x:v>Weekly super is illustrative FP&amp;A input.</x:v>
       </x:c>
-      <x:c r="G25" s="71"/>
-      <x:c r="H25" s="71"/>
+      <x:c r="G25" s="75"/>
+      <x:c r="H25" s="75"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="55" t="str">
+      <x:c r="A26" s="56" t="str">
         <x:v>Payday Super</x:v>
       </x:c>
-      <x:c r="B26" s="56" t="str">
+      <x:c r="B26" s="57" t="str">
         <x:v>https://softwaredevelopers.ato.gov.au/PaydaySuper</x:v>
       </x:c>
-      <x:c r="C26" s="55" t="str">
+      <x:c r="C26" s="56" t="str">
         <x:v>From 1 July 2026, pay SG with each pay cycle. The fund must generally receive it by the seventh business day after payday.</x:v>
       </x:c>
-      <x:c r="D26" s="55" t="str">
+      <x:c r="D26" s="56" t="str">
         <x:v>26 August 2026</x:v>
       </x:c>
-      <x:c r="E26" s="55" t="str">
+      <x:c r="E26" s="56" t="str">
         <x:v>Fund receipt, not employer submission, is the statutory timing anchor. Allow for eligible longer periods.</x:v>
       </x:c>
-      <x:c r="F26" s="55" t="str">
+      <x:c r="F26" s="56" t="str">
         <x:v>Illustrative forecast starts after the July 2026 transition.</x:v>
       </x:c>
-      <x:c r="G26" s="71"/>
-      <x:c r="H26" s="71"/>
+      <x:c r="G26" s="75"/>
+      <x:c r="H26" s="75"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="71"/>
-      <x:c r="B27" s="71"/>
-      <x:c r="C27" s="71"/>
-      <x:c r="D27" s="71"/>
-      <x:c r="E27" s="71"/>
-      <x:c r="F27" s="71"/>
-      <x:c r="G27" s="71"/>
-      <x:c r="H27" s="71"/>
+      <x:c r="A27" s="75"/>
+      <x:c r="B27" s="75"/>
+      <x:c r="C27" s="75"/>
+      <x:c r="D27" s="75"/>
+      <x:c r="E27" s="75"/>
+      <x:c r="F27" s="75"/>
+      <x:c r="G27" s="75"/>
+      <x:c r="H27" s="75"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="58" t="str">
+      <x:c r="A28" s="59" t="str">
         <x:v>Disclaimer: Illustrative FP&amp;A cash-planning model only. Statutory amounts and dates are indicative assumptions, not tax, BAS, payroll, superannuation or legal advice. Entity-specific lodgement dates and tax classifications must be confirmed by the user or adviser before relying on the model or lodging or paying.</x:v>
       </x:c>
-      <x:c r="B28" s="58"/>
-      <x:c r="C28" s="58"/>
-      <x:c r="D28" s="58"/>
-      <x:c r="E28" s="58"/>
-      <x:c r="F28" s="58"/>
-      <x:c r="G28" s="58"/>
-      <x:c r="H28" s="58"/>
+      <x:c r="B28" s="59"/>
+      <x:c r="C28" s="59"/>
+      <x:c r="D28" s="59"/>
+      <x:c r="E28" s="59"/>
+      <x:c r="F28" s="59"/>
+      <x:c r="G28" s="59"/>
+      <x:c r="H28" s="59"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="58"/>
-      <x:c r="B29" s="58"/>
-      <x:c r="C29" s="58"/>
-      <x:c r="D29" s="58"/>
-      <x:c r="E29" s="58"/>
-      <x:c r="F29" s="58"/>
-      <x:c r="G29" s="58"/>
-      <x:c r="H29" s="58"/>
+      <x:c r="A29" s="59"/>
+      <x:c r="B29" s="59"/>
+      <x:c r="C29" s="59"/>
+      <x:c r="D29" s="59"/>
+      <x:c r="E29" s="59"/>
+      <x:c r="F29" s="59"/>
+      <x:c r="G29" s="59"/>
+      <x:c r="H29" s="59"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="58"/>
-      <x:c r="B30" s="58"/>
-      <x:c r="C30" s="58"/>
-      <x:c r="D30" s="58"/>
-      <x:c r="E30" s="58"/>
-      <x:c r="F30" s="58"/>
-      <x:c r="G30" s="58"/>
-      <x:c r="H30" s="58"/>
+      <x:c r="A30" s="59"/>
+      <x:c r="B30" s="59"/>
+      <x:c r="C30" s="59"/>
+      <x:c r="D30" s="59"/>
+      <x:c r="E30" s="59"/>
+      <x:c r="F30" s="59"/>
+      <x:c r="G30" s="59"/>
+      <x:c r="H30" s="59"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7431,29 +7741,29 @@
     <x:mergeCell ref="A28:H30"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B4:B4">
-    <x:cfRule type="expression" dxfId="13" priority="1">
+    <x:cfRule type="expression" dxfId="16" priority="1">
       <x:formula>B4="PASS"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="14" priority="2">
+    <x:cfRule type="expression" dxfId="17" priority="2">
       <x:formula>B4="FAIL"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E4:E4">
-    <x:cfRule type="expression" dxfId="15" priority="3">
+    <x:cfRule type="expression" dxfId="18" priority="3">
       <x:formula>E4="ACTION REQUIRED"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="16" priority="4">
+    <x:cfRule type="expression" dxfId="19" priority="4">
       <x:formula>E4="WATCH"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="17" priority="5">
+    <x:cfRule type="expression" dxfId="20" priority="5">
       <x:formula>E4="OK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F8:F16">
-    <x:cfRule type="expression" dxfId="18" priority="6">
+    <x:cfRule type="expression" dxfId="21" priority="6">
       <x:formula>F8="PASS"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="19" priority="7">
+    <x:cfRule type="expression" dxfId="22" priority="7">
       <x:formula>F8="FAIL"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>

--- a/templates/13-week-cash-flow-forecast.xlsx
+++ b/templates/13-week-cash-flow-forecast.xlsx
@@ -3100,7 +3100,7 @@
         <x:f>IF(A33=0,"",IF(SUMIF('Weekly Review'!$H$6:$H$18,"&lt;&gt;",'Weekly Review'!$G$6:$G$18)=0,"",SUM('Weekly Review'!$I$6:$I$18)/SUMIF('Weekly Review'!$H$6:$H$18,"&lt;&gt;",'Weekly Review'!$G$6:$G$18)))</x:f>
       </x:c>
       <x:c r="D33" s="70" t="str">
-        <x:f>IF(A33=0,"",SUM('Weekly Review'!$M$6:$M$18)/A33)</x:f>
+        <x:f>IF(A33=0,"",SUMIFS('Weekly Review'!$M$6:$M$18,'Weekly Review'!$D$6:$D$18,"&lt;&gt;",'Weekly Review'!$H$6:$H$18,"&lt;&gt;",'Weekly Review'!$L$6:$L$18,"&lt;&gt;")/A33)</x:f>
       </x:c>
       <x:c r="E33" s="68" t="str">
         <x:f>IF(COUNTIF('Weekly Review'!$O$6:$O$18,"INCOMPLETE")&gt;0,"INCOMPLETE",IF(COUNTIF('Weekly Review'!$O$6:$O$18,"COMPLETE")&gt;0,"COMPLETE","NOT STARTED"))</x:f>
